--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="514">
   <si>
     <t>日期</t>
   </si>
@@ -1220,6 +1220,219 @@
   </si>
   <si>
     <t>突出材料学+工艺研发背景；补充表面处理/涂层工艺认知；应届生强调材料测试与工艺学习能力。</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（颅内支架/球囊/导管）</t>
+  </si>
+  <si>
+    <t>负责颅内血管支架、球囊、导管及输送系统研发；研发前期市场调研、竞品分析、专利编写；早期样品设计制作与绘图打样；原材料及样品测试方案设计与数据分析；撰写测试报告与汇报。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/zhaopin/?key=颅内支架 球囊 导管 研发</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|介入类（颅内支架/球囊/导管/输送系统）研发，方向相关且涉及材料测试与样品设计</t>
+  </si>
+  <si>
+    <t>研究82/技能78/学历95/行业100/企业90</t>
+  </si>
+  <si>
+    <t>岗位完全匹配介入器械研发目标，涉及支架球囊导管输送系统开发，与候选人的血管支架研究方向及材料学/支架设计/生物相容性评价技能高度契合；公司为神经介入领域上市公司，平台优质，机会难得。</t>
+  </si>
+  <si>
+    <t>突出血管支架课题与介入类器械设计经验，重点展示材料性能测试、样品设计与绘图能力，以及动物实验/生物相容性评价经历；可补充神经介入背景与专利书写能力。</t>
+  </si>
+  <si>
+    <t>深港产学研基地（北大·港科大深圳研修院）</t>
+  </si>
+  <si>
+    <t>心血管介入医疗器械工程实验室 博士后/科研人员</t>
+  </si>
+  <si>
+    <t>面向心血管介入医疗器械工程方向招聘博士后及科研人员，研究方向直接与介入/血管器械研发相关，依托北京大学-香港科技大学深圳研修院平台。</t>
+  </si>
+  <si>
+    <t>https://www.gaoxiaojob.com/announcement/detail/339280.html</t>
+  </si>
+  <si>
+    <t>智能匹配84分【博士后】|强烈推荐|心血管介入医疗器械工程实验室，介入器械科研平台，方向高度相关</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历82/行业100/企业92</t>
+  </si>
+  <si>
+    <t>权威实验室聚焦心血管介入器械工程，与候选人血管支架研究方向直接一致；科研院所平台资源优质，可积累介入器械研发与成果转化经验，是科研/产业路径的理想跳板。</t>
+  </si>
+  <si>
+    <t>强调血管支架课题成果、材料学与生物相容性评价方法，突出论文/课题与介入器械工程的相关性，附研究兴趣与拟开展方向说明。</t>
+  </si>
+  <si>
+    <t>深圳理工大学</t>
+  </si>
+  <si>
+    <t>医疗器械产业技术研究院 研究人员</t>
+  </si>
+  <si>
+    <t>招聘研究人员，方向含高端医学影像设备、生物医学材料、植介入器械、手术机器人等；需生物医学工程、材料科学、流体力学等相关背景。</t>
+  </si>
+  <si>
+    <t>https://www.gaoxiaojob.com/announcement/detail/327964.html</t>
+  </si>
+  <si>
+    <t>智能匹配75分【科研岗】|值得考虑|植介入器械/生物医学材料科研岗，方向契合但偏向博士科研人才</t>
+  </si>
+  <si>
+    <t>研究80/技能70/学历45/行业100/企业90</t>
+  </si>
+  <si>
+    <t>国家高性能医疗器械创新中心（深圳）</t>
+  </si>
+  <si>
+    <t>心脑血管植入器械与材料方向 专职科研人员</t>
+  </si>
+  <si>
+    <t>诚聘心脑血管植入器械与材料、聚合物/金属合金材料、生物功能陶瓷、医用功能高分子方向青年科技人才；面向生物医学工程、材料等专业。</t>
+  </si>
+  <si>
+    <t>https://www.gaoxiaojob.com/announcement/detail/39306.html</t>
+  </si>
+  <si>
+    <t>智能匹配78分【科研岗】|值得考虑|国家级中心心脑血管植入器械与材料方向，研究方向直接相关</t>
+  </si>
+  <si>
+    <t>研究88/技能72/学历45/行业100/企业92</t>
+  </si>
+  <si>
+    <t>上海交通大学医学院附属瑞金医院</t>
+  </si>
+  <si>
+    <t>博士后（生物医用材料、生物医学工程方向）</t>
+  </si>
+  <si>
+    <t>招收生物医用材料、生物医学工程方向博士后，获博士学位不超过3年、年龄≤35周岁；涉及微生物学与免疫、生物医用材料/生物医学工程背景。</t>
+  </si>
+  <si>
+    <t>https://www.gaoxiaojob.com/job/detail/219785.html</t>
+  </si>
+  <si>
+    <t>智能匹配76分【博士后】|值得考虑|生物医用材料/生物医学工程博士后，医院课题组平台，方向相关</t>
+  </si>
+  <si>
+    <t>研究72/技能70/学历82/行业85/企业92</t>
+  </si>
+  <si>
+    <t>博士后（可降解支架/药物释放技术）</t>
+  </si>
+  <si>
+    <t>招聘博士后，研究血流动力学、生物材料表面处理、可吸收支架药物释放技术；要求博士学历、SCI一作论文、英文良好。</t>
+  </si>
+  <si>
+    <t>https://www.lifetechmed.com/join/jobs/community/index.aspx</t>
+  </si>
+  <si>
+    <t>智能匹配89分【博士后】|强烈推荐|可降解支架/药物释放技术研究，血管支架方向直接高度匹配</t>
+  </si>
+  <si>
+    <t>研究92/技能85/学历82/行业100/企业92</t>
+  </si>
+  <si>
+    <t>先健为国际领先可吸收支架介入器械龙头，博士后方向（可降解可吸收支架、药物释放）与候选人血管支架研究方向几乎完全重合；平台国际化、方向前沿，是行业顶尖科研机会。</t>
+  </si>
+  <si>
+    <t>突出血管支架课题、可降解材料与生物相容性评价研究，展示SCI论文、动物实验与药物释放/降解性能评价能力，英文简历需规范完整。</t>
+  </si>
+  <si>
+    <t>研发工程师（金属材料/镍钛）</t>
+  </si>
+  <si>
+    <t>本科及以上，金属材料方向；熟悉镍钛合金性能与加工、金相/DSC/SEM/拉伸/TEM等测试方法；从事介入/植入器械金属材料研发。</t>
+  </si>
+  <si>
+    <t>智能匹配90分【社招】|强烈推荐|镍钛支架金属材料研发岗，材料学方向与支架设计高度匹配</t>
+  </si>
+  <si>
+    <t>研究88/技能86/学历95/行业100/企业92</t>
+  </si>
+  <si>
+    <t>镍钛合金是血管支架核心材料，岗位与候选人材料学、支架设计、生物相容性技能四维高度重合；先健为介入器械龙头上市公司，研发平台一流，硕士学历契合，强烈推荐投递。</t>
+  </si>
+  <si>
+    <t>重点突出金属材料性能测试（金相/DSC/SEM/拉伸等）与镍钛/支架材料加工经验，展示支架设计课题与材料表征能力，量化实验成果与参数。</t>
+  </si>
+  <si>
+    <t>高级/资深工艺工程师（可降解材料 PLA/PDO）</t>
+  </si>
+  <si>
+    <t>硕士及以上，高分子/化学/生物材料背景；3年以上PLA/PDO等可降解材料研发经验；从事可降解支架材料工艺开发。</t>
+  </si>
+  <si>
+    <t>智能匹配88分【社招】|强烈推荐|可降解材料PLA/PDO工艺研发，与全降解支架方向高度契合</t>
+  </si>
+  <si>
+    <t>研究84/技能84/学历95/行业100/企业92</t>
+  </si>
+  <si>
+    <t>高级/资深工艺工程师（药物涂层/喷涂）</t>
+  </si>
+  <si>
+    <t>硕士及以上，药学/化学/生物材料背景；3年以上药物涂层/喷涂工艺开发经验；从事药物涂层支架相关工艺研发。</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招】|强烈推荐|药物涂层支架工艺研发，与药物涂层支架方向匹配</t>
+  </si>
+  <si>
+    <t>研究82/技能82/学历95/行业100/企业92</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（材料方向）</t>
+  </si>
+  <si>
+    <t>本科及以上，材料学背景；2年以上医疗器械研发经验，心血管/介入类优先；从事介入类植入器械材料研发与验证。</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|介入类器械材料研发岗，材料学方向匹配</t>
+  </si>
+  <si>
+    <t>研究80/技能80/学历96/行业100/企业92</t>
+  </si>
+  <si>
+    <t>先健科技介入器械龙头，材料研发岗与候选人材料学、支架设计、生物相容性技能高度契合；虽要求2年经验，候选人的血管支架课题与动物实验经历可作有力补充，建议投递争取。</t>
+  </si>
+  <si>
+    <t>突出介入类器械材料研发课题与材料表征能力，量化实验与检测数据，强调可降解支架项目经验与生物相容性评价，弱化经验年限、强化专业匹配度。</t>
+  </si>
+  <si>
+    <t>高级/资深研发工程师（介入/植入器械）</t>
+  </si>
+  <si>
+    <t>本科及以上，机械/材料专业；4年以上介入或植入器械研发经验；熟悉ISO13485/GMP；从事产品、材料与测试相关工作。</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招】|强烈推荐|介入/植入器械研发岗，方向与技能匹配</t>
+  </si>
+  <si>
+    <t>工艺工程师（冠脉/外周介入器械）</t>
+  </si>
+  <si>
+    <t>硕士及以上，机械/化工/高分子专业；熟悉材料加工与CAD/SolidWorks；从事成品种、材料与测试相关工作；接受应届毕业生。</t>
+  </si>
+  <si>
+    <t>https://www.endovastec.com/SocialRecruitment/</t>
+  </si>
+  <si>
+    <t>智能匹配86分【校园招聘】|强烈推荐|冠脉/外周介入器械工艺岗，明确接受应届生，方向技能匹配</t>
+  </si>
+  <si>
+    <t>研究82/技能80/学历95/行业100/企业92</t>
+  </si>
+  <si>
+    <t>心脉医疗为微创旗下介入器械上市龙头，明确接受应届毕业生，岗位方向（介入器械工艺/CAD软件/高分子材料）与候选人材料学、支架设计技能高度契合；上海平台优质，是应届生理想选择，强烈推荐投递。</t>
+  </si>
+  <si>
+    <t>突出硕士毕业时间可随时到岗，重点展示材料加工、CAD/SolidWorks建模与支架设计课题，强调高分子材料与血管介入背景，突出应届生身份与学习能力。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -1777,7 +1990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3881,6 +4094,462 @@
       </c>
       <c r="L55" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>402</v>
+      </c>
+      <c r="B56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>403</v>
+      </c>
+      <c r="D56" t="s">
+        <v>404</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" t="s">
+        <v>405</v>
+      </c>
+      <c r="G56">
+        <v>9</v>
+      </c>
+      <c r="H56" t="s">
+        <v>406</v>
+      </c>
+      <c r="I56">
+        <v>85</v>
+      </c>
+      <c r="J56" t="s">
+        <v>407</v>
+      </c>
+      <c r="K56" t="s">
+        <v>408</v>
+      </c>
+      <c r="L56" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>402</v>
+      </c>
+      <c r="B57" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" t="s">
+        <v>411</v>
+      </c>
+      <c r="D57" t="s">
+        <v>412</v>
+      </c>
+      <c r="E57" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" t="s">
+        <v>413</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57" t="s">
+        <v>414</v>
+      </c>
+      <c r="I57">
+        <v>84</v>
+      </c>
+      <c r="J57" t="s">
+        <v>415</v>
+      </c>
+      <c r="K57" t="s">
+        <v>416</v>
+      </c>
+      <c r="L57" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>402</v>
+      </c>
+      <c r="B58" t="s">
+        <v>418</v>
+      </c>
+      <c r="C58" t="s">
+        <v>419</v>
+      </c>
+      <c r="D58" t="s">
+        <v>420</v>
+      </c>
+      <c r="E58" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58" t="s">
+        <v>421</v>
+      </c>
+      <c r="G58">
+        <v>8</v>
+      </c>
+      <c r="H58" t="s">
+        <v>422</v>
+      </c>
+      <c r="I58">
+        <v>75</v>
+      </c>
+      <c r="J58" t="s">
+        <v>423</v>
+      </c>
+      <c r="K58" t="s">
+        <v>79</v>
+      </c>
+      <c r="L58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>402</v>
+      </c>
+      <c r="B59" t="s">
+        <v>424</v>
+      </c>
+      <c r="C59" t="s">
+        <v>425</v>
+      </c>
+      <c r="D59" t="s">
+        <v>426</v>
+      </c>
+      <c r="E59" t="s">
+        <v>66</v>
+      </c>
+      <c r="F59" t="s">
+        <v>427</v>
+      </c>
+      <c r="G59">
+        <v>8</v>
+      </c>
+      <c r="H59" t="s">
+        <v>428</v>
+      </c>
+      <c r="I59">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s">
+        <v>429</v>
+      </c>
+      <c r="K59" t="s">
+        <v>79</v>
+      </c>
+      <c r="L59" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>402</v>
+      </c>
+      <c r="B60" t="s">
+        <v>430</v>
+      </c>
+      <c r="C60" t="s">
+        <v>431</v>
+      </c>
+      <c r="D60" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" t="s">
+        <v>433</v>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+      <c r="H60" t="s">
+        <v>434</v>
+      </c>
+      <c r="I60">
+        <v>76</v>
+      </c>
+      <c r="J60" t="s">
+        <v>435</v>
+      </c>
+      <c r="K60" t="s">
+        <v>79</v>
+      </c>
+      <c r="L60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>402</v>
+      </c>
+      <c r="B61" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
+        <v>436</v>
+      </c>
+      <c r="D61" t="s">
+        <v>437</v>
+      </c>
+      <c r="E61" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61" t="s">
+        <v>438</v>
+      </c>
+      <c r="G61">
+        <v>9</v>
+      </c>
+      <c r="H61" t="s">
+        <v>439</v>
+      </c>
+      <c r="I61">
+        <v>89</v>
+      </c>
+      <c r="J61" t="s">
+        <v>440</v>
+      </c>
+      <c r="K61" t="s">
+        <v>441</v>
+      </c>
+      <c r="L61" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>402</v>
+      </c>
+      <c r="B62" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" t="s">
+        <v>443</v>
+      </c>
+      <c r="D62" t="s">
+        <v>444</v>
+      </c>
+      <c r="E62" t="s">
+        <v>66</v>
+      </c>
+      <c r="F62" t="s">
+        <v>438</v>
+      </c>
+      <c r="G62">
+        <v>9</v>
+      </c>
+      <c r="H62" t="s">
+        <v>445</v>
+      </c>
+      <c r="I62">
+        <v>90</v>
+      </c>
+      <c r="J62" t="s">
+        <v>446</v>
+      </c>
+      <c r="K62" t="s">
+        <v>447</v>
+      </c>
+      <c r="L62" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>402</v>
+      </c>
+      <c r="B63" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" t="s">
+        <v>449</v>
+      </c>
+      <c r="D63" t="s">
+        <v>450</v>
+      </c>
+      <c r="E63" t="s">
+        <v>66</v>
+      </c>
+      <c r="F63" t="s">
+        <v>438</v>
+      </c>
+      <c r="G63">
+        <v>9</v>
+      </c>
+      <c r="H63" t="s">
+        <v>451</v>
+      </c>
+      <c r="I63">
+        <v>88</v>
+      </c>
+      <c r="J63" t="s">
+        <v>452</v>
+      </c>
+      <c r="K63" t="s">
+        <v>79</v>
+      </c>
+      <c r="L63" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>402</v>
+      </c>
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" t="s">
+        <v>453</v>
+      </c>
+      <c r="D64" t="s">
+        <v>454</v>
+      </c>
+      <c r="E64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F64" t="s">
+        <v>438</v>
+      </c>
+      <c r="G64">
+        <v>9</v>
+      </c>
+      <c r="H64" t="s">
+        <v>455</v>
+      </c>
+      <c r="I64">
+        <v>87</v>
+      </c>
+      <c r="J64" t="s">
+        <v>456</v>
+      </c>
+      <c r="K64" t="s">
+        <v>79</v>
+      </c>
+      <c r="L64" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>402</v>
+      </c>
+      <c r="B65" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" t="s">
+        <v>457</v>
+      </c>
+      <c r="D65" t="s">
+        <v>458</v>
+      </c>
+      <c r="E65" t="s">
+        <v>66</v>
+      </c>
+      <c r="F65" t="s">
+        <v>438</v>
+      </c>
+      <c r="G65">
+        <v>9</v>
+      </c>
+      <c r="H65" t="s">
+        <v>459</v>
+      </c>
+      <c r="I65">
+        <v>86</v>
+      </c>
+      <c r="J65" t="s">
+        <v>460</v>
+      </c>
+      <c r="K65" t="s">
+        <v>461</v>
+      </c>
+      <c r="L65" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>402</v>
+      </c>
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
+        <v>463</v>
+      </c>
+      <c r="D66" t="s">
+        <v>464</v>
+      </c>
+      <c r="E66" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66" t="s">
+        <v>438</v>
+      </c>
+      <c r="G66">
+        <v>9</v>
+      </c>
+      <c r="H66" t="s">
+        <v>465</v>
+      </c>
+      <c r="I66">
+        <v>87</v>
+      </c>
+      <c r="J66" t="s">
+        <v>456</v>
+      </c>
+      <c r="K66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L66" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>402</v>
+      </c>
+      <c r="B67" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" t="s">
+        <v>466</v>
+      </c>
+      <c r="D67" t="s">
+        <v>467</v>
+      </c>
+      <c r="E67" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" t="s">
+        <v>468</v>
+      </c>
+      <c r="G67">
+        <v>9</v>
+      </c>
+      <c r="H67" t="s">
+        <v>469</v>
+      </c>
+      <c r="I67">
+        <v>86</v>
+      </c>
+      <c r="J67" t="s">
+        <v>470</v>
+      </c>
+      <c r="K67" t="s">
+        <v>471</v>
+      </c>
+      <c r="L67" t="s">
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -3914,7 +4583,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -3923,16 +4592,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3946,16 +4615,16 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>408</v>
+        <v>479</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -3980,7 +4649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3995,7 +4664,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4005,31 +4674,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>417</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>489</v>
       </c>
       <c r="B4">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>419</v>
+        <v>490</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -4037,7 +4706,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -4045,23 +4714,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>423</v>
+        <v>494</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>424</v>
+        <v>495</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>425</v>
+        <v>496</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -4069,15 +4738,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4087,15 +4756,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>430</v>
+        <v>501</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -4103,23 +4772,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>502</v>
       </c>
       <c r="B17" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>432</v>
+        <v>503</v>
       </c>
       <c r="B18" s="5">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>433</v>
+        <v>504</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -4127,7 +4796,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>434</v>
+        <v>505</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4135,7 +4804,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>435</v>
+        <v>506</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4143,7 +4812,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4151,7 +4820,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4159,7 +4828,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>438</v>
+        <v>509</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4167,7 +4836,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>439</v>
+        <v>510</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4175,7 +4844,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>440</v>
+        <v>511</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -4187,7 +4856,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>441</v>
+        <v>512</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -4205,7 +4874,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>442</v>
+        <v>513</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -4944,25 +5613,25 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>403</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>405</v>
       </c>
       <c r="G58">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H58" t="s">
-        <v>77</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4970,25 +5639,25 @@
         <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="E59" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F59" t="s">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>84</v>
+        <v>439</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4996,25 +5665,25 @@
         <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>443</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F60" t="s">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="G60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>108</v>
+        <v>445</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -5022,25 +5691,25 @@
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C61" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>449</v>
       </c>
       <c r="E61" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>112</v>
+        <v>438</v>
       </c>
       <c r="G61">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>113</v>
+        <v>451</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -5048,25 +5717,25 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>453</v>
       </c>
       <c r="E62" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>438</v>
       </c>
       <c r="G62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H62" t="s">
-        <v>119</v>
+        <v>455</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -5074,25 +5743,25 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="D63" t="s">
-        <v>122</v>
+        <v>457</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="F63" t="s">
-        <v>125</v>
+        <v>438</v>
       </c>
       <c r="G63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>126</v>
+        <v>459</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -5100,25 +5769,25 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>463</v>
       </c>
       <c r="E64" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="F64" t="s">
-        <v>148</v>
+        <v>438</v>
       </c>
       <c r="G64">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H64" t="s">
-        <v>149</v>
+        <v>465</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -5126,25 +5795,25 @@
         <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>322</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>466</v>
       </c>
       <c r="E65" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>156</v>
+        <v>468</v>
       </c>
       <c r="G65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H65" t="s">
-        <v>157</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -5152,25 +5821,25 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F66" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="G66">
         <v>8</v>
       </c>
       <c r="H66" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -5178,25 +5847,25 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="E67" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F67" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="G67">
         <v>8</v>
       </c>
       <c r="H67" t="s">
-        <v>217</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -5204,25 +5873,25 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>227</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="E68" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F68" t="s">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="G68">
         <v>8</v>
       </c>
       <c r="H68" t="s">
-        <v>232</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -5230,25 +5899,25 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>236</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="G69">
         <v>8</v>
       </c>
       <c r="H69" t="s">
-        <v>238</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -5256,25 +5925,25 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>243</v>
+        <v>118</v>
       </c>
       <c r="G70">
         <v>8</v>
       </c>
       <c r="H70" t="s">
-        <v>244</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -5282,25 +5951,25 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F71" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G71">
         <v>8</v>
       </c>
       <c r="H71" t="s">
-        <v>247</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -5308,25 +5977,25 @@
         <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>144</v>
       </c>
       <c r="D72" t="s">
-        <v>249</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F72" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="G72">
         <v>8</v>
       </c>
       <c r="H72" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -5334,25 +6003,25 @@
         <v>44</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="D73" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E73" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G73">
         <v>8</v>
       </c>
       <c r="H73" t="s">
-        <v>259</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -5363,22 +6032,22 @@
         <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="D74" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="F74" t="s">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="G74">
         <v>8</v>
       </c>
       <c r="H74" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5389,22 +6058,22 @@
         <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="D75" t="s">
-        <v>267</v>
+        <v>214</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F75" t="s">
-        <v>58</v>
+        <v>216</v>
       </c>
       <c r="G75">
         <v>8</v>
       </c>
       <c r="H75" t="s">
-        <v>269</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5415,22 +6084,22 @@
         <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="D76" t="s">
-        <v>278</v>
+        <v>228</v>
       </c>
       <c r="E76" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="F76" t="s">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="G76">
         <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>282</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5438,25 +6107,25 @@
         <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="D77" t="s">
-        <v>316</v>
+        <v>73</v>
       </c>
       <c r="E77" t="s">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="G77">
         <v>8</v>
       </c>
       <c r="H77" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5464,25 +6133,25 @@
         <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>338</v>
+        <v>240</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>241</v>
       </c>
       <c r="E78" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>343</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5490,25 +6159,25 @@
         <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>347</v>
+        <v>245</v>
       </c>
       <c r="D79" t="s">
-        <v>348</v>
+        <v>154</v>
       </c>
       <c r="E79" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>350</v>
+        <v>156</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>351</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5516,25 +6185,25 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>353</v>
+        <v>248</v>
       </c>
       <c r="D80" t="s">
-        <v>362</v>
+        <v>249</v>
       </c>
       <c r="E80" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>364</v>
+        <v>251</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -5542,25 +6211,25 @@
         <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
-        <v>377</v>
+        <v>254</v>
       </c>
       <c r="D81" t="s">
-        <v>378</v>
+        <v>255</v>
       </c>
       <c r="E81" t="s">
-        <v>380</v>
+        <v>257</v>
       </c>
       <c r="F81" t="s">
-        <v>381</v>
+        <v>258</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>382</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -5568,25 +6237,25 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>144</v>
+        <v>261</v>
       </c>
       <c r="D82" t="s">
-        <v>394</v>
+        <v>122</v>
       </c>
       <c r="E82" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="F82" t="s">
-        <v>397</v>
+        <v>263</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>398</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5597,21 +6266,333 @@
         <v>159</v>
       </c>
       <c r="C83" t="s">
+        <v>266</v>
+      </c>
+      <c r="D83" t="s">
+        <v>267</v>
+      </c>
+      <c r="E83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83">
+        <v>8</v>
+      </c>
+      <c r="H83" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>55</v>
+      </c>
+      <c r="B84" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" t="s">
+        <v>277</v>
+      </c>
+      <c r="D84" t="s">
+        <v>278</v>
+      </c>
+      <c r="E84" t="s">
+        <v>280</v>
+      </c>
+      <c r="F84" t="s">
+        <v>281</v>
+      </c>
+      <c r="G84">
+        <v>8</v>
+      </c>
+      <c r="H84" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>56</v>
+      </c>
+      <c r="B85" t="s">
+        <v>284</v>
+      </c>
+      <c r="C85" t="s">
+        <v>315</v>
+      </c>
+      <c r="D85" t="s">
+        <v>316</v>
+      </c>
+      <c r="E85" t="s">
+        <v>318</v>
+      </c>
+      <c r="F85" t="s">
+        <v>319</v>
+      </c>
+      <c r="G85">
+        <v>8</v>
+      </c>
+      <c r="H85" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>57</v>
+      </c>
+      <c r="B86" t="s">
+        <v>284</v>
+      </c>
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>339</v>
+      </c>
+      <c r="E86" t="s">
+        <v>341</v>
+      </c>
+      <c r="F86" t="s">
+        <v>342</v>
+      </c>
+      <c r="G86">
+        <v>8</v>
+      </c>
+      <c r="H86" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>58</v>
+      </c>
+      <c r="B87" t="s">
+        <v>284</v>
+      </c>
+      <c r="C87" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" t="s">
+        <v>348</v>
+      </c>
+      <c r="E87" t="s">
+        <v>98</v>
+      </c>
+      <c r="F87" t="s">
+        <v>350</v>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+      <c r="H87" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>59</v>
+      </c>
+      <c r="B88" t="s">
+        <v>284</v>
+      </c>
+      <c r="C88" t="s">
+        <v>353</v>
+      </c>
+      <c r="D88" t="s">
+        <v>362</v>
+      </c>
+      <c r="E88" t="s">
+        <v>356</v>
+      </c>
+      <c r="F88" t="s">
+        <v>364</v>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+      <c r="H88" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>60</v>
+      </c>
+      <c r="B89" t="s">
+        <v>284</v>
+      </c>
+      <c r="C89" t="s">
+        <v>377</v>
+      </c>
+      <c r="D89" t="s">
+        <v>378</v>
+      </c>
+      <c r="E89" t="s">
+        <v>380</v>
+      </c>
+      <c r="F89" t="s">
+        <v>381</v>
+      </c>
+      <c r="G89">
+        <v>8</v>
+      </c>
+      <c r="H89" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>61</v>
+      </c>
+      <c r="B90" t="s">
+        <v>284</v>
+      </c>
+      <c r="C90" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" t="s">
+        <v>394</v>
+      </c>
+      <c r="E90" t="s">
+        <v>396</v>
+      </c>
+      <c r="F90" t="s">
+        <v>397</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>402</v>
+      </c>
+      <c r="C91" t="s">
+        <v>410</v>
+      </c>
+      <c r="D91" t="s">
+        <v>411</v>
+      </c>
+      <c r="E91" t="s">
+        <v>66</v>
+      </c>
+      <c r="F91" t="s">
+        <v>413</v>
+      </c>
+      <c r="G91">
+        <v>8</v>
+      </c>
+      <c r="H91" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>63</v>
+      </c>
+      <c r="B92" t="s">
+        <v>402</v>
+      </c>
+      <c r="C92" t="s">
+        <v>418</v>
+      </c>
+      <c r="D92" t="s">
+        <v>419</v>
+      </c>
+      <c r="E92" t="s">
+        <v>66</v>
+      </c>
+      <c r="F92" t="s">
+        <v>421</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>64</v>
+      </c>
+      <c r="B93" t="s">
+        <v>402</v>
+      </c>
+      <c r="C93" t="s">
+        <v>424</v>
+      </c>
+      <c r="D93" t="s">
+        <v>425</v>
+      </c>
+      <c r="E93" t="s">
+        <v>66</v>
+      </c>
+      <c r="F93" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93">
+        <v>8</v>
+      </c>
+      <c r="H93" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>65</v>
+      </c>
+      <c r="B94" t="s">
+        <v>402</v>
+      </c>
+      <c r="C94" t="s">
+        <v>430</v>
+      </c>
+      <c r="D94" t="s">
+        <v>431</v>
+      </c>
+      <c r="E94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s">
+        <v>433</v>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+      <c r="H94" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>66</v>
+      </c>
+      <c r="B95" t="s">
+        <v>159</v>
+      </c>
+      <c r="C95" t="s">
         <v>271</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D95" t="s">
         <v>272</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E95" t="s">
         <v>75</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F95" t="s">
         <v>274</v>
       </c>
-      <c r="G83">
+      <c r="G95">
         <v>7</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H95" t="s">
         <v>275</v>
       </c>
     </row>
@@ -5628,7 +6609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5645,10 +6626,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -5675,12 +6656,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -5715,7 +6696,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -5750,7 +6731,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -5785,7 +6766,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -5820,7 +6801,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -5855,7 +6836,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -5890,7 +6871,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -5925,7 +6906,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -5960,7 +6941,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B10">
         <v>92</v>
@@ -5995,7 +6976,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -6030,7 +7011,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -6065,7 +7046,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B13">
         <v>91</v>
@@ -6100,7 +7081,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -6135,7 +7116,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -6170,7 +7151,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -6205,7 +7186,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B17">
         <v>90</v>
@@ -6240,7 +7221,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B18">
         <v>90</v>
@@ -6275,7 +7256,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -6310,509 +7291,509 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B20">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>443</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>438</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="J20" t="s">
-        <v>143</v>
+        <v>448</v>
       </c>
       <c r="K20" t="s">
-        <v>137</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B21">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="I21" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="J21" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B22">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>201</v>
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>440</v>
       </c>
       <c r="I22" t="s">
-        <v>205</v>
+        <v>441</v>
       </c>
       <c r="J22" t="s">
-        <v>206</v>
+        <v>442</v>
       </c>
       <c r="K22" t="s">
-        <v>202</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B23">
         <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>386</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>389</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>392</v>
+        <v>37</v>
       </c>
       <c r="J23" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="K23" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B24">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="H24" t="s">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="J24" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K24" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B25">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
         <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="E25" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="H25" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="I25" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="J25" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="K25" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B26">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D26" t="s">
-        <v>369</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="H26" t="s">
-        <v>374</v>
+        <v>452</v>
       </c>
       <c r="I26" t="s">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B27">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="I27" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="J27" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="K27" t="s">
-        <v>57</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B28">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>353</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
+        <v>354</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>356</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>357</v>
       </c>
       <c r="H28" t="s">
-        <v>133</v>
+        <v>359</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="J28" t="s">
-        <v>135</v>
+        <v>361</v>
       </c>
       <c r="K28" t="s">
-        <v>129</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B29">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>308</v>
+        <v>453</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="G29" t="s">
-        <v>310</v>
+        <v>438</v>
       </c>
       <c r="H29" t="s">
-        <v>312</v>
+        <v>456</v>
       </c>
       <c r="I29" t="s">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s">
-        <v>309</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>145</v>
+        <v>463</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>148</v>
+        <v>438</v>
       </c>
       <c r="H30" t="s">
-        <v>150</v>
+        <v>456</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B31">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
         <v>284</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>369</v>
       </c>
       <c r="E31" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="F31" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="H31" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="I31" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="J31" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="K31" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B32">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
-        <v>353</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>362</v>
+        <v>457</v>
       </c>
       <c r="F32" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>364</v>
+        <v>438</v>
       </c>
       <c r="H32" t="s">
-        <v>366</v>
+        <v>460</v>
       </c>
       <c r="I32" t="s">
-        <v>367</v>
+        <v>461</v>
       </c>
       <c r="J32" t="s">
-        <v>368</v>
+        <v>462</v>
       </c>
       <c r="K32" t="s">
-        <v>363</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B33">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>227</v>
+        <v>322</v>
       </c>
       <c r="E33" t="s">
-        <v>228</v>
+        <v>466</v>
       </c>
       <c r="F33" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>231</v>
+        <v>468</v>
       </c>
       <c r="H33" t="s">
-        <v>233</v>
+        <v>470</v>
       </c>
       <c r="I33" t="s">
-        <v>234</v>
+        <v>471</v>
       </c>
       <c r="J33" t="s">
-        <v>235</v>
+        <v>472</v>
       </c>
       <c r="K33" t="s">
-        <v>229</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B34">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>267</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
@@ -6821,120 +7802,435 @@
         <v>58</v>
       </c>
       <c r="H34" t="s">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="K34" t="s">
-        <v>268</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>338</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>339</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>341</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>342</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s">
-        <v>344</v>
+        <v>133</v>
       </c>
       <c r="I35" t="s">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="J35" t="s">
-        <v>346</v>
+        <v>135</v>
       </c>
       <c r="K35" t="s">
-        <v>340</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B36">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="H36" t="s">
-        <v>85</v>
+        <v>312</v>
       </c>
       <c r="I36" t="s">
-        <v>86</v>
+        <v>313</v>
       </c>
       <c r="J36" t="s">
-        <v>87</v>
+        <v>314</v>
       </c>
       <c r="K36" t="s">
-        <v>82</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="B37">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s">
+        <v>402</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>403</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" t="s">
+        <v>405</v>
+      </c>
+      <c r="H37" t="s">
+        <v>407</v>
+      </c>
+      <c r="I37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J37" t="s">
+        <v>409</v>
+      </c>
+      <c r="K37" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>485</v>
+      </c>
+      <c r="B38">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" t="s">
+        <v>150</v>
+      </c>
+      <c r="I38" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38" t="s">
+        <v>152</v>
+      </c>
+      <c r="K38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>485</v>
+      </c>
+      <c r="B39">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>284</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>394</v>
+      </c>
+      <c r="F39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G39" t="s">
+        <v>397</v>
+      </c>
+      <c r="H39" t="s">
+        <v>399</v>
+      </c>
+      <c r="I39" t="s">
+        <v>400</v>
+      </c>
+      <c r="J39" t="s">
+        <v>401</v>
+      </c>
+      <c r="K39" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>485</v>
+      </c>
+      <c r="B40">
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
+        <v>402</v>
+      </c>
+      <c r="D40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E40" t="s">
+        <v>411</v>
+      </c>
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" t="s">
+        <v>413</v>
+      </c>
+      <c r="H40" t="s">
+        <v>415</v>
+      </c>
+      <c r="I40" t="s">
+        <v>416</v>
+      </c>
+      <c r="J40" t="s">
+        <v>417</v>
+      </c>
+      <c r="K40" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>485</v>
+      </c>
+      <c r="B41">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" t="s">
+        <v>353</v>
+      </c>
+      <c r="E41" t="s">
+        <v>362</v>
+      </c>
+      <c r="F41" t="s">
+        <v>356</v>
+      </c>
+      <c r="G41" t="s">
+        <v>364</v>
+      </c>
+      <c r="H41" t="s">
+        <v>366</v>
+      </c>
+      <c r="I41" t="s">
+        <v>367</v>
+      </c>
+      <c r="J41" t="s">
+        <v>368</v>
+      </c>
+      <c r="K41" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>485</v>
+      </c>
+      <c r="B42">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" t="s">
+        <v>230</v>
+      </c>
+      <c r="G42" t="s">
+        <v>231</v>
+      </c>
+      <c r="H42" t="s">
+        <v>233</v>
+      </c>
+      <c r="I42" t="s">
+        <v>234</v>
+      </c>
+      <c r="J42" t="s">
+        <v>235</v>
+      </c>
+      <c r="K42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>485</v>
+      </c>
+      <c r="B43">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" t="s">
+        <v>266</v>
+      </c>
+      <c r="E43" t="s">
+        <v>267</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" t="s">
+        <v>58</v>
+      </c>
+      <c r="H43" t="s">
+        <v>270</v>
+      </c>
+      <c r="I43" t="s">
+        <v>79</v>
+      </c>
+      <c r="J43" t="s">
+        <v>79</v>
+      </c>
+      <c r="K43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B44">
+        <v>82</v>
+      </c>
+      <c r="C44" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" t="s">
+        <v>338</v>
+      </c>
+      <c r="E44" t="s">
+        <v>339</v>
+      </c>
+      <c r="F44" t="s">
+        <v>341</v>
+      </c>
+      <c r="G44" t="s">
+        <v>342</v>
+      </c>
+      <c r="H44" t="s">
+        <v>344</v>
+      </c>
+      <c r="I44" t="s">
+        <v>345</v>
+      </c>
+      <c r="J44" t="s">
+        <v>346</v>
+      </c>
+      <c r="K44" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>485</v>
+      </c>
+      <c r="B45">
         <v>81</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45" t="s">
+        <v>86</v>
+      </c>
+      <c r="J45" t="s">
+        <v>87</v>
+      </c>
+      <c r="K45" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>485</v>
+      </c>
+      <c r="B46">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
         <v>284</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D46" t="s">
         <v>377</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E46" t="s">
         <v>378</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F46" t="s">
         <v>380</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G46" t="s">
         <v>381</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H46" t="s">
         <v>383</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I46" t="s">
         <v>384</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J46" t="s">
         <v>385</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K46" t="s">
         <v>379</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="596">
   <si>
     <t>日期</t>
   </si>
@@ -1435,6 +1435,255 @@
     <t>突出硕士毕业时间可随时到岗，重点展示材料加工、CAD/SolidWorks建模与支架设计课题，强调高分子材料与血管介入背景，突出应届生身份与学习能力。</t>
   </si>
   <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>瑛泰医疗（上海）</t>
+  </si>
+  <si>
+    <t>医疗器械研发主管（血管支架）</t>
+  </si>
+  <si>
+    <t>负责血管支架研发流程梳理与优化、提升研发效率、团队带教与管理工作。公司为香港联交所主板上市(股票代码HK1501)国产心内介入器械龙头，具备自主模具/产品/设备开发及自主灭菌完整产业能力，通过ISO13485、CE、FDA认证。</t>
+  </si>
+  <si>
+    <t>上海嘉定</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=VXiRhMa-qC3a0io5xBlTy8M0Q41HQ3T0_88lqpPHSsNa0tSyauWI75ECzOqi2vr6I5ZHqw1i1zlul8mE6MLCT1jAc6oSBqBQwfz6JobHhFC</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|国产心内介入龙头HK1501，明确血管支架研发，方向直接匹配</t>
+  </si>
+  <si>
+    <t>研究90/技能68/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>瑛泰医疗为港股上市国产心内介入器械龙头，岗位直接负责血管支架研发，与硕士血管支架研究方向高度重合，平台大且具备完整研发-生产-灭菌能力，硕士工科背景可胜任，上海嘉定岗位符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出血管支架研究方向与可降解/金属支架材料项目；量化支架力学/降解/动物实验数据；强调ISO13485法规认知与研发流程理解，展示团队协作潜力。</t>
+  </si>
+  <si>
+    <t>浙江乾合畅脉医疗（嘉兴/嘉善）</t>
+  </si>
+  <si>
+    <t>公司秉承“介入无植入”理念，专业从事心血管支架、药物涂层球囊、PTCA扩张球囊等三类医疗器械的研发、生产、销售。负责植介入器械结构设计、材料选型与性能开发。要求机械/材料相关背景。</t>
+  </si>
+  <si>
+    <t>浙江嘉兴嘉善</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=Nd_aYrixsztP5AByKlDv8QdqWCvbDsj1HdSqd2MIK0q7510Qqqci0apcawk48IG27nt-wl2qkw2CwcUfWrOn3IYGj4SO3PE02ldHfdFj6QO</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|心血管支架+药物涂层球囊研发，方向直接匹配，材料/结构背景对口</t>
+  </si>
+  <si>
+    <t>研究90/技能75/学历85/行业100/企业75</t>
+  </si>
+  <si>
+    <t>乾合畅脉专注介入无植入理念下的心血管支架与药物涂层球囊研发，与硕士支架研究方向及材料学技能直接对口，可完整参与三类器械研发流程，成长空间大。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计与材料学项目经验，特别是有机涂层/药物球囊或可降解材料经历；量化性能测试数据；强调对植介入三类器械开发全流程的理解。</t>
+  </si>
+  <si>
+    <t>科塞尔医疗科技（苏州）</t>
+  </si>
+  <si>
+    <t>研发工程师（导管）</t>
+  </si>
+  <si>
+    <t>从事血管介入器械研发，专注外周介入领域一站式治疗体系。负责外周介入导管等产品的结构设计、材料选型与工艺开发。要求机械/材料专业，有介入耗材研发经验者优先。</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=GKl8J4TCqO9OVpIfn5vNdLIPjfAL7LNe6zchA7NtjZS79sqvp06wOzJKdtYEVe_-a1VYUdjw9K_Bh5D-aSKVea</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|外周介入导管研发，介入方向相关，苏州符合城市偏好</t>
+  </si>
+  <si>
+    <t>研究85/技能72/学历85/行业100/企业86</t>
+  </si>
+  <si>
+    <t>科塞尔为苏州外周介入一站式综合平台，岗位做介入导管研发，与硕士介入器械方向相关，且地处苏州符合城市偏好，材料与结构设计技能可迁移。</t>
+  </si>
+  <si>
+    <t>突出介入耗材/导管相关学习项目与机械结构设计能力；补充高分子材料与生物相容性评价知识；强调外周介入产品全流程开发认知。</t>
+  </si>
+  <si>
+    <t>麦科田医疗（深圳/常州）</t>
+  </si>
+  <si>
+    <t>耗材研发工程师（2026届校园招聘）</t>
+  </si>
+  <si>
+    <t>医疗器械高值耗材产品开发全流程：结构设计、计算机模拟与验证、模具设计、样品测试、测试报告及生产导入。面向2026届硕士应届，招2人。</t>
+  </si>
+  <si>
+    <t>深圳、常州</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=jQwjSDUOa66rJaMwHBJxtyMWQ0gp5dV0BCWBCcUFDfxURDe-9iIkXc3E-9aIlx8oEVBNPlc8kLHuZ8Oaae2lvK</t>
+  </si>
+  <si>
+    <t>智能匹配81分【校园招聘】|强烈推荐|2026届校招，医疗器械耗材研发现培养岗，硕士应届即投</t>
+  </si>
+  <si>
+    <t>研究75/技能72/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>针对2026届硕士应届生的校招岗位，覆盖结构设计、仿真、测试、生产导入全流程，作为校招能直接进入医疗器械行业研发，深圳为候选人偏好城市，成长快。</t>
+  </si>
+  <si>
+    <t>突出硕士期间的器械结构设计/仿真/材料作品；展示从设计到验证的完整项目链路；强调可塑性与团队协作，面试突出动手与测试能力。</t>
+  </si>
+  <si>
+    <t>研发工程师（校园招聘·材料类/化学类）</t>
+  </si>
+  <si>
+    <t>面向2026届硕士应届，材料/高分子/化学相关专业，从事心血管植介入医疗器械及介入材料研发。乐普为冠脉支架及可吸收支架NeoVas研发龙头、上市企业。</t>
+  </si>
+  <si>
+    <t>北京昌平</t>
+  </si>
+  <si>
+    <t>https://www.lepumedical.com/campus_join.html</t>
+  </si>
+  <si>
+    <t>智能匹配87分【校园招聘】|强烈推荐|冠脉/可吸收支架龙头乐普，2026届材料类校招，材料学技能高度对口</t>
+  </si>
+  <si>
+    <t>研究78/技能84/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>乐普为国产冠脉支架及生物可吸收支架NeoVas龙头，2026届材料类校招岗位与硕士材料学研究背景、生物相容性评价技能高度契合，平台大、主线对口，北京符合城市偏好。</t>
+  </si>
+  <si>
+    <t>材料/高分子课程与研究方向前置呈现；突出生物相容性评价、可降解材料实验经历；量化降解率/力学/细胞毒性数据；呼应冠脉支架产品线。</t>
+  </si>
+  <si>
+    <t>研发工程师（金属材料/结构设计方向）</t>
+  </si>
+  <si>
+    <t>元心从先健科技(01302.HK)分拆，专注铁基可降解血管支架研发。研发工程师（金属材料）与研发工程师（结构设计方向）岗位，需硕士及以上，金属材料/可降解金属或支架结构设计背景，从事铁基可吸收血管支架研发。</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com/gongsi/ed20f7148fbf46581nR909S4Fw~~.html</t>
+  </si>
+  <si>
+    <t>智能匹配93分【社招】|强烈推荐|铁基可吸收血管支架研发，方向与技能全覆盖，深圳硕岗</t>
+  </si>
+  <si>
+    <t>研究95/技能88/学历100/行业100/企业88</t>
+  </si>
+  <si>
+    <t>元心科技专注铁基可降解血管支架，正是硕士血管支架研究方向的最精准平台；结构设计+金属材料岗位与材料学、支架设计技能高度重合，深圳符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出可降解金属/铁基支架课题与支架结构设计项目；量化降解行为、力学与生物相容性数据；补充有限元/结构仿真能力；强调可吸收支架临床前景认知。</t>
+  </si>
+  <si>
+    <t>微创医疗（上海/全国）</t>
+  </si>
+  <si>
+    <t>115训练营·千人星计划（应届技术骨干，新材料/介入支架方向）</t>
+  </si>
+  <si>
+    <t>面向应届生选拔技术骨干/研发领军人才，含新材料、表面处理、介入支架方向。6个月集训+12个月项目学习，培养研发技术骨干。微创为血管介入/生物可吸收支架全球龙头。</t>
+  </si>
+  <si>
+    <t>上海（及全国）</t>
+  </si>
+  <si>
+    <t>https://app.mokahr.com/campus-recruitment/microport/56155#/jobs</t>
+  </si>
+  <si>
+    <t>智能匹配91分【校园招聘】|强烈推荐|血管介入龙头微创应届技术骨干营，介入支架方向，硕士应届直接可投</t>
+  </si>
+  <si>
+    <t>研究88/技能85/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>微创为血管介入及生物可吸收支架龙头，115训练营面向应届培养研发技术骨干，新材料/介入支架方向与硕士研究方向及技能高度匹配，是硕士应届进入龙头的优质通道。</t>
+  </si>
+  <si>
+    <t>突出硕士支架研究课题与技术成果；展现新材料/表面处理/动物实验经历；强调学习能力与长期技术成长意愿，贴合千人星计划选拔画像。</t>
+  </si>
+  <si>
+    <t>浙江省心血管介入与精准诊治重点实验室（浙大邵逸夫医院）</t>
+  </si>
+  <si>
+    <t>博士后/特聘研究员（心血管介入方向）</t>
+  </si>
+  <si>
+    <t>浙大邵逸夫医院心内科（傅国胜团队）开展心血管介入与精准诊治研究，招聘博士后/特聘研究员/PI助手，研究方向覆盖心血管介入器械与生物材料。</t>
+  </si>
+  <si>
+    <t>浙江杭州</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/s/koala2026shaoyifu</t>
+  </si>
+  <si>
+    <t>智能匹配83分【博士后】|强烈推荐|心血管介入重点实验室博士后，介入方向+医院课题组顶级平台</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历82/行业90/企业90</t>
+  </si>
+  <si>
+    <t>省级心血管介入重点实验室为医院课题组顶级科研平台，博士后/特聘研究员方向与硕士介入/支架研究衔接，可深入心血管介入器械研究，科研晋升路径清晰。</t>
+  </si>
+  <si>
+    <t>前置研究成果与SCI论文；突出介入器械/生物相容性/动物实验科研能力；说明博后研究计划与心血管介入方向契合；强调实验与写作能力。</t>
+  </si>
+  <si>
+    <t>波士顿科学（心脏介入事业部）</t>
+  </si>
+  <si>
+    <t>2026校园招聘（心脏介入/心血管方向）</t>
+  </si>
+  <si>
+    <t>全球心血管介入器械龙头波士顿科学2026届校园招聘，覆盖心血管/呼吸/消化等领域产品，招聘应届硕士研发/技术岗位。</t>
+  </si>
+  <si>
+    <t>上海、北京等</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=oVJSJL_9iim-9BQR07d6EUrJTGC3d1NbluxOp7CD4PDmTTnm4GL9fuKhoVjsYXmdclqpALRzh_z0JDAiXXFGyq</t>
+  </si>
+  <si>
+    <t>智能匹配86分【校园招聘】|强烈推荐|全球心血管介入龙头波科2026届校招，心血管方向，硕士应届可投</t>
+  </si>
+  <si>
+    <t>研究85/技能72/学历100/行业100/企业92</t>
+  </si>
+  <si>
+    <t>波士顿科学为全球心血管介入器械头部外企，2026届校园招聘心血管方向，硕士应届可直接投递，平台国际顶级、培养体系成熟，心血管介入与护理技术方向对口。</t>
+  </si>
+  <si>
+    <t>英文简历匹配外资招聘；突出介入/支架研究项目与材料学生物相容性技能；强调英文技术文献阅读能力、国际视野与团队协作。</t>
+  </si>
+  <si>
+    <t>惠凯医疗（上海）</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（支架方向）</t>
+  </si>
+  <si>
+    <t>从事医疗器械研发（支架方向），位于上海大学科技园。负责支架类器械的结构设计与开发。</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=VNuyqlPNraK8SsjQjsmbydZO1uHbqC3_xRaC4Wo7KTeUTVqPUzpVWjFPmwcyHVH7dBOPJw35ryVGVBlcxirqlHKpBdnN-yF7Bgu1QjK-BBe</t>
+  </si>
+  <si>
+    <t>智能匹配76分【社招】|值得考虑|医疗器械支架方向研发，支架技能相关，上海岗位</t>
+  </si>
+  <si>
+    <t>研究72/技能68/学历85/行业100/企业78</t>
+  </si>
+  <si>
     <t>投递日期</t>
   </si>
   <si>
@@ -1457,9 +1706,6 @@
   </si>
   <si>
     <t>通过官网投递，等待初筛结果</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
   </si>
   <si>
     <t>推荐级别</t>
@@ -1990,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4550,6 +4796,386 @@
       </c>
       <c r="L67" t="s">
         <v>472</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s">
+        <v>474</v>
+      </c>
+      <c r="C68" t="s">
+        <v>475</v>
+      </c>
+      <c r="D68" t="s">
+        <v>476</v>
+      </c>
+      <c r="E68" t="s">
+        <v>477</v>
+      </c>
+      <c r="F68" t="s">
+        <v>478</v>
+      </c>
+      <c r="G68">
+        <v>9</v>
+      </c>
+      <c r="H68" t="s">
+        <v>479</v>
+      </c>
+      <c r="I68">
+        <v>85</v>
+      </c>
+      <c r="J68" t="s">
+        <v>480</v>
+      </c>
+      <c r="K68" t="s">
+        <v>481</v>
+      </c>
+      <c r="L68" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>473</v>
+      </c>
+      <c r="B69" t="s">
+        <v>483</v>
+      </c>
+      <c r="C69" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69" t="s">
+        <v>484</v>
+      </c>
+      <c r="E69" t="s">
+        <v>485</v>
+      </c>
+      <c r="F69" t="s">
+        <v>486</v>
+      </c>
+      <c r="G69">
+        <v>8</v>
+      </c>
+      <c r="H69" t="s">
+        <v>487</v>
+      </c>
+      <c r="I69">
+        <v>84</v>
+      </c>
+      <c r="J69" t="s">
+        <v>488</v>
+      </c>
+      <c r="K69" t="s">
+        <v>489</v>
+      </c>
+      <c r="L69" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>473</v>
+      </c>
+      <c r="B70" t="s">
+        <v>491</v>
+      </c>
+      <c r="C70" t="s">
+        <v>492</v>
+      </c>
+      <c r="D70" t="s">
+        <v>493</v>
+      </c>
+      <c r="E70" t="s">
+        <v>75</v>
+      </c>
+      <c r="F70" t="s">
+        <v>494</v>
+      </c>
+      <c r="G70">
+        <v>8</v>
+      </c>
+      <c r="H70" t="s">
+        <v>495</v>
+      </c>
+      <c r="I70">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s">
+        <v>496</v>
+      </c>
+      <c r="K70" t="s">
+        <v>497</v>
+      </c>
+      <c r="L70" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>473</v>
+      </c>
+      <c r="B71" t="s">
+        <v>499</v>
+      </c>
+      <c r="C71" t="s">
+        <v>500</v>
+      </c>
+      <c r="D71" t="s">
+        <v>501</v>
+      </c>
+      <c r="E71" t="s">
+        <v>502</v>
+      </c>
+      <c r="F71" t="s">
+        <v>503</v>
+      </c>
+      <c r="G71">
+        <v>8</v>
+      </c>
+      <c r="H71" t="s">
+        <v>504</v>
+      </c>
+      <c r="I71">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s">
+        <v>505</v>
+      </c>
+      <c r="K71" t="s">
+        <v>506</v>
+      </c>
+      <c r="L71" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>473</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" t="s">
+        <v>508</v>
+      </c>
+      <c r="D72" t="s">
+        <v>509</v>
+      </c>
+      <c r="E72" t="s">
+        <v>510</v>
+      </c>
+      <c r="F72" t="s">
+        <v>511</v>
+      </c>
+      <c r="G72">
+        <v>9</v>
+      </c>
+      <c r="H72" t="s">
+        <v>512</v>
+      </c>
+      <c r="I72">
+        <v>87</v>
+      </c>
+      <c r="J72" t="s">
+        <v>513</v>
+      </c>
+      <c r="K72" t="s">
+        <v>514</v>
+      </c>
+      <c r="L72" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>473</v>
+      </c>
+      <c r="B73" t="s">
+        <v>285</v>
+      </c>
+      <c r="C73" t="s">
+        <v>516</v>
+      </c>
+      <c r="D73" t="s">
+        <v>517</v>
+      </c>
+      <c r="E73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F73" t="s">
+        <v>518</v>
+      </c>
+      <c r="G73">
+        <v>9</v>
+      </c>
+      <c r="H73" t="s">
+        <v>519</v>
+      </c>
+      <c r="I73">
+        <v>93</v>
+      </c>
+      <c r="J73" t="s">
+        <v>520</v>
+      </c>
+      <c r="K73" t="s">
+        <v>521</v>
+      </c>
+      <c r="L73" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>473</v>
+      </c>
+      <c r="B74" t="s">
+        <v>523</v>
+      </c>
+      <c r="C74" t="s">
+        <v>524</v>
+      </c>
+      <c r="D74" t="s">
+        <v>525</v>
+      </c>
+      <c r="E74" t="s">
+        <v>526</v>
+      </c>
+      <c r="F74" t="s">
+        <v>527</v>
+      </c>
+      <c r="G74">
+        <v>9</v>
+      </c>
+      <c r="H74" t="s">
+        <v>528</v>
+      </c>
+      <c r="I74">
+        <v>91</v>
+      </c>
+      <c r="J74" t="s">
+        <v>529</v>
+      </c>
+      <c r="K74" t="s">
+        <v>530</v>
+      </c>
+      <c r="L74" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>473</v>
+      </c>
+      <c r="B75" t="s">
+        <v>532</v>
+      </c>
+      <c r="C75" t="s">
+        <v>533</v>
+      </c>
+      <c r="D75" t="s">
+        <v>534</v>
+      </c>
+      <c r="E75" t="s">
+        <v>535</v>
+      </c>
+      <c r="F75" t="s">
+        <v>536</v>
+      </c>
+      <c r="G75">
+        <v>8</v>
+      </c>
+      <c r="H75" t="s">
+        <v>537</v>
+      </c>
+      <c r="I75">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s">
+        <v>538</v>
+      </c>
+      <c r="K75" t="s">
+        <v>539</v>
+      </c>
+      <c r="L75" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>473</v>
+      </c>
+      <c r="B76" t="s">
+        <v>541</v>
+      </c>
+      <c r="C76" t="s">
+        <v>542</v>
+      </c>
+      <c r="D76" t="s">
+        <v>543</v>
+      </c>
+      <c r="E76" t="s">
+        <v>544</v>
+      </c>
+      <c r="F76" t="s">
+        <v>545</v>
+      </c>
+      <c r="G76">
+        <v>9</v>
+      </c>
+      <c r="H76" t="s">
+        <v>546</v>
+      </c>
+      <c r="I76">
+        <v>86</v>
+      </c>
+      <c r="J76" t="s">
+        <v>547</v>
+      </c>
+      <c r="K76" t="s">
+        <v>548</v>
+      </c>
+      <c r="L76" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>473</v>
+      </c>
+      <c r="B77" t="s">
+        <v>550</v>
+      </c>
+      <c r="C77" t="s">
+        <v>551</v>
+      </c>
+      <c r="D77" t="s">
+        <v>552</v>
+      </c>
+      <c r="E77" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" t="s">
+        <v>553</v>
+      </c>
+      <c r="G77">
+        <v>8</v>
+      </c>
+      <c r="H77" t="s">
+        <v>554</v>
+      </c>
+      <c r="I77">
+        <v>76</v>
+      </c>
+      <c r="J77" t="s">
+        <v>555</v>
+      </c>
+      <c r="K77" t="s">
+        <v>79</v>
+      </c>
+      <c r="L77" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4583,7 +5209,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>556</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4592,16 +5218,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>474</v>
+        <v>557</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>475</v>
+        <v>558</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>476</v>
+        <v>559</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>477</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4615,16 +5241,16 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>478</v>
+        <v>561</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>479</v>
+        <v>562</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>480</v>
+        <v>563</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -4649,7 +5275,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4664,7 +5290,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>486</v>
+        <v>568</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4674,31 +5300,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>487</v>
+        <v>569</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>488</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>489</v>
+        <v>571</v>
       </c>
       <c r="B4">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>490</v>
+        <v>572</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>492</v>
+        <v>574</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -4706,7 +5332,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>493</v>
+        <v>575</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -4714,23 +5340,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>576</v>
       </c>
       <c r="B8">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>495</v>
+        <v>577</v>
       </c>
       <c r="B9">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>496</v>
+        <v>578</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -4738,15 +5364,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>497</v>
+        <v>579</v>
       </c>
       <c r="B11" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>498</v>
+        <v>580</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -4756,15 +5382,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>499</v>
+        <v>581</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>500</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>501</v>
+        <v>583</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -4772,23 +5398,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>502</v>
+        <v>584</v>
       </c>
       <c r="B17" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>503</v>
+        <v>585</v>
       </c>
       <c r="B18" s="5">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>504</v>
+        <v>586</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -4796,7 +5422,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>505</v>
+        <v>587</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4804,7 +5430,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>506</v>
+        <v>588</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4812,7 +5438,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>507</v>
+        <v>589</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4820,7 +5446,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>590</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4828,7 +5454,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>509</v>
+        <v>591</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4836,7 +5462,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>510</v>
+        <v>592</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4844,7 +5470,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>511</v>
+        <v>593</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -4856,7 +5482,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>512</v>
+        <v>594</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -4874,7 +5500,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>513</v>
+        <v>595</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -5821,25 +6447,25 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>474</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>475</v>
       </c>
       <c r="E66" t="s">
-        <v>75</v>
+        <v>477</v>
       </c>
       <c r="F66" t="s">
-        <v>76</v>
+        <v>478</v>
       </c>
       <c r="G66">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>77</v>
+        <v>479</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -5847,25 +6473,25 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C67" t="s">
         <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="E67" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="F67" t="s">
-        <v>83</v>
+        <v>511</v>
       </c>
       <c r="G67">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H67" t="s">
-        <v>84</v>
+        <v>512</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -5873,25 +6499,25 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>285</v>
       </c>
       <c r="D68" t="s">
-        <v>104</v>
+        <v>516</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F68" t="s">
-        <v>107</v>
+        <v>518</v>
       </c>
       <c r="G68">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H68" t="s">
-        <v>108</v>
+        <v>519</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -5899,25 +6525,25 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>523</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>524</v>
       </c>
       <c r="E69" t="s">
-        <v>16</v>
+        <v>526</v>
       </c>
       <c r="F69" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="G69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H69" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -5925,25 +6551,25 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>541</v>
       </c>
       <c r="D70" t="s">
-        <v>116</v>
+        <v>542</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="F70" t="s">
-        <v>118</v>
+        <v>545</v>
       </c>
       <c r="G70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H70" t="s">
-        <v>119</v>
+        <v>546</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -5954,22 +6580,22 @@
         <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="F71" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="G71">
         <v>8</v>
       </c>
       <c r="H71" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -5980,22 +6606,22 @@
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="E72" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="F72" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="G72">
         <v>8</v>
       </c>
       <c r="H72" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6006,22 +6632,22 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="G73">
         <v>8</v>
       </c>
       <c r="H73" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6029,25 +6655,25 @@
         <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="G74">
         <v>8</v>
       </c>
       <c r="H74" t="s">
-        <v>211</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -6055,25 +6681,25 @@
         <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>213</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="E75" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="G75">
         <v>8</v>
       </c>
       <c r="H75" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -6081,25 +6707,25 @@
         <v>47</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="D76" t="s">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="E76" t="s">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="F76" t="s">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="G76">
         <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -6107,25 +6733,25 @@
         <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="F77" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="G77">
         <v>8</v>
       </c>
       <c r="H77" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -6133,25 +6759,25 @@
         <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -6162,22 +6788,22 @@
         <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F79" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -6188,22 +6814,22 @@
         <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="D80" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F80" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -6214,22 +6840,22 @@
         <v>159</v>
       </c>
       <c r="C81" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="D81" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="F81" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6240,22 +6866,22 @@
         <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D82" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E82" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="F82" t="s">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -6266,22 +6892,22 @@
         <v>159</v>
       </c>
       <c r="C83" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="D83" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -6292,22 +6918,22 @@
         <v>159</v>
       </c>
       <c r="C84" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="D84" t="s">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="E84" t="s">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -6315,25 +6941,25 @@
         <v>56</v>
       </c>
       <c r="B85" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C85" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="D85" t="s">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="E85" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>319</v>
+        <v>251</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -6341,25 +6967,25 @@
         <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>338</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
-        <v>339</v>
+        <v>255</v>
       </c>
       <c r="E86" t="s">
-        <v>341</v>
+        <v>257</v>
       </c>
       <c r="F86" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>343</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -6367,25 +6993,25 @@
         <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C87" t="s">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>122</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="F87" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>351</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -6393,25 +7019,25 @@
         <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>353</v>
+        <v>266</v>
       </c>
       <c r="D88" t="s">
-        <v>362</v>
+        <v>267</v>
       </c>
       <c r="E88" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>365</v>
+        <v>269</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -6419,25 +7045,25 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="D89" t="s">
-        <v>378</v>
+        <v>278</v>
       </c>
       <c r="E89" t="s">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="F89" t="s">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>382</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -6448,22 +7074,22 @@
         <v>284</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>315</v>
       </c>
       <c r="D90" t="s">
-        <v>394</v>
+        <v>316</v>
       </c>
       <c r="E90" t="s">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="F90" t="s">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -6471,25 +7097,25 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C91" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="D91" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="E91" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="F91" t="s">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>414</v>
+        <v>343</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -6497,25 +7123,25 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C92" t="s">
-        <v>418</v>
+        <v>347</v>
       </c>
       <c r="D92" t="s">
-        <v>419</v>
+        <v>348</v>
       </c>
       <c r="E92" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F92" t="s">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>422</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -6523,25 +7149,25 @@
         <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C93" t="s">
-        <v>424</v>
+        <v>353</v>
       </c>
       <c r="D93" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="E93" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F93" t="s">
-        <v>427</v>
+        <v>364</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>428</v>
+        <v>365</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -6549,25 +7175,25 @@
         <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C94" t="s">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="D94" t="s">
-        <v>431</v>
+        <v>378</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="F94" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>434</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -6575,24 +7201,284 @@
         <v>66</v>
       </c>
       <c r="B95" t="s">
+        <v>284</v>
+      </c>
+      <c r="C95" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" t="s">
+        <v>394</v>
+      </c>
+      <c r="E95" t="s">
+        <v>396</v>
+      </c>
+      <c r="F95" t="s">
+        <v>397</v>
+      </c>
+      <c r="G95">
+        <v>8</v>
+      </c>
+      <c r="H95" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>67</v>
+      </c>
+      <c r="B96" t="s">
+        <v>402</v>
+      </c>
+      <c r="C96" t="s">
+        <v>410</v>
+      </c>
+      <c r="D96" t="s">
+        <v>411</v>
+      </c>
+      <c r="E96" t="s">
+        <v>66</v>
+      </c>
+      <c r="F96" t="s">
+        <v>413</v>
+      </c>
+      <c r="G96">
+        <v>8</v>
+      </c>
+      <c r="H96" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>68</v>
+      </c>
+      <c r="B97" t="s">
+        <v>402</v>
+      </c>
+      <c r="C97" t="s">
+        <v>418</v>
+      </c>
+      <c r="D97" t="s">
+        <v>419</v>
+      </c>
+      <c r="E97" t="s">
+        <v>66</v>
+      </c>
+      <c r="F97" t="s">
+        <v>421</v>
+      </c>
+      <c r="G97">
+        <v>8</v>
+      </c>
+      <c r="H97" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>69</v>
+      </c>
+      <c r="B98" t="s">
+        <v>402</v>
+      </c>
+      <c r="C98" t="s">
+        <v>424</v>
+      </c>
+      <c r="D98" t="s">
+        <v>425</v>
+      </c>
+      <c r="E98" t="s">
+        <v>66</v>
+      </c>
+      <c r="F98" t="s">
+        <v>427</v>
+      </c>
+      <c r="G98">
+        <v>8</v>
+      </c>
+      <c r="H98" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>70</v>
+      </c>
+      <c r="B99" t="s">
+        <v>402</v>
+      </c>
+      <c r="C99" t="s">
+        <v>430</v>
+      </c>
+      <c r="D99" t="s">
+        <v>431</v>
+      </c>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
+        <v>433</v>
+      </c>
+      <c r="G99">
+        <v>8</v>
+      </c>
+      <c r="H99" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>71</v>
+      </c>
+      <c r="B100" t="s">
+        <v>473</v>
+      </c>
+      <c r="C100" t="s">
+        <v>483</v>
+      </c>
+      <c r="D100" t="s">
+        <v>122</v>
+      </c>
+      <c r="E100" t="s">
+        <v>485</v>
+      </c>
+      <c r="F100" t="s">
+        <v>486</v>
+      </c>
+      <c r="G100">
+        <v>8</v>
+      </c>
+      <c r="H100" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>72</v>
+      </c>
+      <c r="B101" t="s">
+        <v>473</v>
+      </c>
+      <c r="C101" t="s">
+        <v>491</v>
+      </c>
+      <c r="D101" t="s">
+        <v>492</v>
+      </c>
+      <c r="E101" t="s">
+        <v>75</v>
+      </c>
+      <c r="F101" t="s">
+        <v>494</v>
+      </c>
+      <c r="G101">
+        <v>8</v>
+      </c>
+      <c r="H101" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>73</v>
+      </c>
+      <c r="B102" t="s">
+        <v>473</v>
+      </c>
+      <c r="C102" t="s">
+        <v>499</v>
+      </c>
+      <c r="D102" t="s">
+        <v>500</v>
+      </c>
+      <c r="E102" t="s">
+        <v>502</v>
+      </c>
+      <c r="F102" t="s">
+        <v>503</v>
+      </c>
+      <c r="G102">
+        <v>8</v>
+      </c>
+      <c r="H102" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>74</v>
+      </c>
+      <c r="B103" t="s">
+        <v>473</v>
+      </c>
+      <c r="C103" t="s">
+        <v>532</v>
+      </c>
+      <c r="D103" t="s">
+        <v>533</v>
+      </c>
+      <c r="E103" t="s">
+        <v>535</v>
+      </c>
+      <c r="F103" t="s">
+        <v>536</v>
+      </c>
+      <c r="G103">
+        <v>8</v>
+      </c>
+      <c r="H103" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>75</v>
+      </c>
+      <c r="B104" t="s">
+        <v>473</v>
+      </c>
+      <c r="C104" t="s">
+        <v>550</v>
+      </c>
+      <c r="D104" t="s">
+        <v>551</v>
+      </c>
+      <c r="E104" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" t="s">
+        <v>553</v>
+      </c>
+      <c r="G104">
+        <v>8</v>
+      </c>
+      <c r="H104" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>76</v>
+      </c>
+      <c r="B105" t="s">
         <v>159</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C105" t="s">
         <v>271</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D105" t="s">
         <v>272</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E105" t="s">
         <v>75</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F105" t="s">
         <v>274</v>
       </c>
-      <c r="G95">
+      <c r="G105">
         <v>7</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H105" t="s">
         <v>275</v>
       </c>
     </row>
@@ -6609,7 +7495,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6626,10 +7512,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>482</v>
+        <v>564</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>483</v>
+        <v>565</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -6656,12 +7542,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>484</v>
+        <v>566</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -6696,7 +7582,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -6731,7 +7617,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -6766,7 +7652,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -6801,7 +7687,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -6836,7 +7722,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -6871,7 +7757,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -6906,7 +7792,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -6941,147 +7827,147 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B10">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>285</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>516</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>518</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>520</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>521</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>522</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B11">
         <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
         <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="K11" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B12">
         <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>301</v>
+        <v>161</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="H12" t="s">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="I12" t="s">
-        <v>306</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>307</v>
+        <v>167</v>
       </c>
       <c r="K12" t="s">
-        <v>302</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B13">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>300</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>303</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
       <c r="I13" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="J13" t="s">
-        <v>30</v>
+        <v>307</v>
       </c>
       <c r="K13" t="s">
-        <v>24</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -7090,33 +7976,33 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -7125,246 +8011,246 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
         <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
         <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B16">
         <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
         <v>159</v>
       </c>
       <c r="D17" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="H17" t="s">
-        <v>197</v>
+        <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B18">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>523</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>524</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>526</v>
       </c>
       <c r="G18" t="s">
-        <v>222</v>
+        <v>527</v>
       </c>
       <c r="H18" t="s">
-        <v>224</v>
+        <v>529</v>
       </c>
       <c r="I18" t="s">
-        <v>225</v>
+        <v>530</v>
       </c>
       <c r="J18" t="s">
-        <v>226</v>
+        <v>531</v>
       </c>
       <c r="K18" t="s">
-        <v>221</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B19">
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="E19" t="s">
-        <v>331</v>
+        <v>192</v>
       </c>
       <c r="F19" t="s">
-        <v>333</v>
+        <v>194</v>
       </c>
       <c r="G19" t="s">
-        <v>334</v>
+        <v>195</v>
       </c>
       <c r="H19" t="s">
         <v>197</v>
       </c>
       <c r="I19" t="s">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="J19" t="s">
-        <v>337</v>
+        <v>199</v>
       </c>
       <c r="K19" t="s">
-        <v>332</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B20">
         <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
-        <v>443</v>
+        <v>220</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>438</v>
+        <v>222</v>
       </c>
       <c r="H20" t="s">
-        <v>446</v>
+        <v>224</v>
       </c>
       <c r="I20" t="s">
-        <v>447</v>
+        <v>225</v>
       </c>
       <c r="J20" t="s">
-        <v>448</v>
+        <v>226</v>
       </c>
       <c r="K20" t="s">
-        <v>444</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B21">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>331</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>333</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>334</v>
       </c>
       <c r="H21" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="I21" t="s">
-        <v>142</v>
+        <v>336</v>
       </c>
       <c r="J21" t="s">
-        <v>143</v>
+        <v>337</v>
       </c>
       <c r="K21" t="s">
-        <v>137</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B22">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>402</v>
@@ -7373,7 +8259,7 @@
         <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
@@ -7382,339 +8268,339 @@
         <v>438</v>
       </c>
       <c r="H22" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="I22" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J22" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="K22" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B23">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B24">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>436</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>440</v>
       </c>
       <c r="I24" t="s">
-        <v>205</v>
+        <v>441</v>
       </c>
       <c r="J24" t="s">
-        <v>206</v>
+        <v>442</v>
       </c>
       <c r="K24" t="s">
-        <v>202</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B25">
         <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>386</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>389</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>392</v>
+        <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="K25" t="s">
-        <v>388</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B26">
         <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>449</v>
+        <v>201</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>438</v>
+        <v>203</v>
       </c>
       <c r="H26" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="J26" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="K26" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B27">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>284</v>
       </c>
       <c r="D27" t="s">
-        <v>184</v>
+        <v>386</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>387</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>389</v>
       </c>
       <c r="H27" t="s">
-        <v>188</v>
+        <v>391</v>
       </c>
       <c r="I27" t="s">
-        <v>189</v>
+        <v>392</v>
       </c>
       <c r="J27" t="s">
-        <v>190</v>
+        <v>393</v>
       </c>
       <c r="K27" t="s">
-        <v>186</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B28">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D28" t="s">
-        <v>353</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
-        <v>354</v>
+        <v>449</v>
       </c>
       <c r="F28" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>357</v>
+        <v>438</v>
       </c>
       <c r="H28" t="s">
-        <v>359</v>
+        <v>452</v>
       </c>
       <c r="I28" t="s">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="J28" t="s">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s">
-        <v>355</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B29">
         <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="G29" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="H29" t="s">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="I29" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="J29" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="K29" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B30">
         <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E30" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G30" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H30" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J30" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K30" t="s">
-        <v>464</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B31">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>370</v>
+        <v>453</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="H31" t="s">
-        <v>374</v>
+        <v>456</v>
       </c>
       <c r="I31" t="s">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s">
-        <v>371</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B32">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
         <v>402</v>
@@ -7723,7 +8609,7 @@
         <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -7732,506 +8618,821 @@
         <v>438</v>
       </c>
       <c r="H32" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="I32" t="s">
-        <v>461</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s">
-        <v>462</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B33">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D33" t="s">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>510</v>
       </c>
       <c r="G33" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="H33" t="s">
-        <v>470</v>
+        <v>513</v>
       </c>
       <c r="I33" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="J33" t="s">
-        <v>472</v>
+        <v>515</v>
       </c>
       <c r="K33" t="s">
-        <v>467</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B34">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>369</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>370</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>372</v>
       </c>
       <c r="H34" t="s">
-        <v>60</v>
+        <v>374</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>375</v>
       </c>
       <c r="J34" t="s">
-        <v>62</v>
+        <v>376</v>
       </c>
       <c r="K34" t="s">
-        <v>57</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B35">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>457</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>438</v>
       </c>
       <c r="H35" t="s">
-        <v>133</v>
+        <v>460</v>
       </c>
       <c r="I35" t="s">
-        <v>134</v>
+        <v>461</v>
       </c>
       <c r="J35" t="s">
-        <v>135</v>
+        <v>462</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B36">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="E36" t="s">
-        <v>308</v>
+        <v>466</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>310</v>
+        <v>468</v>
       </c>
       <c r="H36" t="s">
-        <v>312</v>
+        <v>470</v>
       </c>
       <c r="I36" t="s">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="J36" t="s">
-        <v>314</v>
+        <v>472</v>
       </c>
       <c r="K36" t="s">
-        <v>309</v>
+        <v>467</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B37">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>541</v>
       </c>
       <c r="E37" t="s">
-        <v>403</v>
+        <v>542</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G37" t="s">
-        <v>405</v>
+        <v>545</v>
       </c>
       <c r="H37" t="s">
-        <v>407</v>
+        <v>547</v>
       </c>
       <c r="I37" t="s">
-        <v>408</v>
+        <v>548</v>
       </c>
       <c r="J37" t="s">
-        <v>409</v>
+        <v>549</v>
       </c>
       <c r="K37" t="s">
-        <v>404</v>
+        <v>543</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B38">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="H38" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I38" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="K38" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B39">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>394</v>
+        <v>89</v>
       </c>
       <c r="F39" t="s">
-        <v>396</v>
+        <v>130</v>
       </c>
       <c r="G39" t="s">
-        <v>397</v>
+        <v>131</v>
       </c>
       <c r="H39" t="s">
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
-        <v>400</v>
+        <v>134</v>
       </c>
       <c r="J39" t="s">
-        <v>401</v>
+        <v>135</v>
       </c>
       <c r="K39" t="s">
-        <v>395</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B40">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D40" t="s">
-        <v>410</v>
+        <v>300</v>
       </c>
       <c r="E40" t="s">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G40" t="s">
-        <v>413</v>
+        <v>310</v>
       </c>
       <c r="H40" t="s">
-        <v>415</v>
+        <v>312</v>
       </c>
       <c r="I40" t="s">
-        <v>416</v>
+        <v>313</v>
       </c>
       <c r="J40" t="s">
-        <v>417</v>
+        <v>314</v>
       </c>
       <c r="K40" t="s">
-        <v>412</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B41">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
-        <v>353</v>
+        <v>55</v>
       </c>
       <c r="E41" t="s">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="F41" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="H41" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="I41" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="J41" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="K41" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B42">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D42" t="s">
-        <v>227</v>
+        <v>474</v>
       </c>
       <c r="E42" t="s">
-        <v>228</v>
+        <v>475</v>
       </c>
       <c r="F42" t="s">
-        <v>230</v>
+        <v>477</v>
       </c>
       <c r="G42" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="H42" t="s">
-        <v>233</v>
+        <v>480</v>
       </c>
       <c r="I42" t="s">
-        <v>234</v>
+        <v>481</v>
       </c>
       <c r="J42" t="s">
-        <v>235</v>
+        <v>482</v>
       </c>
       <c r="K42" t="s">
-        <v>229</v>
+        <v>476</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B43">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>144</v>
       </c>
       <c r="E43" t="s">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="H43" t="s">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="I43" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="K43" t="s">
-        <v>268</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B44">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
         <v>284</v>
       </c>
       <c r="D44" t="s">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
       <c r="F44" t="s">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="G44" t="s">
-        <v>342</v>
+        <v>397</v>
       </c>
       <c r="H44" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="I44" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="J44" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="K44" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>485</v>
+        <v>567</v>
       </c>
       <c r="B45">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="E45" t="s">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="H45" t="s">
-        <v>85</v>
+        <v>415</v>
       </c>
       <c r="I45" t="s">
-        <v>86</v>
+        <v>416</v>
       </c>
       <c r="J45" t="s">
-        <v>87</v>
+        <v>417</v>
       </c>
       <c r="K45" t="s">
-        <v>82</v>
+        <v>412</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>567</v>
+      </c>
+      <c r="B46">
+        <v>84</v>
+      </c>
+      <c r="C46" t="s">
+        <v>473</v>
+      </c>
+      <c r="D46" t="s">
+        <v>483</v>
+      </c>
+      <c r="E46" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" t="s">
         <v>485</v>
       </c>
-      <c r="B46">
+      <c r="G46" t="s">
+        <v>486</v>
+      </c>
+      <c r="H46" t="s">
+        <v>488</v>
+      </c>
+      <c r="I46" t="s">
+        <v>489</v>
+      </c>
+      <c r="J46" t="s">
+        <v>490</v>
+      </c>
+      <c r="K46" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>567</v>
+      </c>
+      <c r="B47">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" t="s">
+        <v>353</v>
+      </c>
+      <c r="E47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F47" t="s">
+        <v>356</v>
+      </c>
+      <c r="G47" t="s">
+        <v>364</v>
+      </c>
+      <c r="H47" t="s">
+        <v>366</v>
+      </c>
+      <c r="I47" t="s">
+        <v>367</v>
+      </c>
+      <c r="J47" t="s">
+        <v>368</v>
+      </c>
+      <c r="K47" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>567</v>
+      </c>
+      <c r="B48">
+        <v>83</v>
+      </c>
+      <c r="C48" t="s">
+        <v>473</v>
+      </c>
+      <c r="D48" t="s">
+        <v>491</v>
+      </c>
+      <c r="E48" t="s">
+        <v>492</v>
+      </c>
+      <c r="F48" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s">
+        <v>494</v>
+      </c>
+      <c r="H48" t="s">
+        <v>496</v>
+      </c>
+      <c r="I48" t="s">
+        <v>497</v>
+      </c>
+      <c r="J48" t="s">
+        <v>498</v>
+      </c>
+      <c r="K48" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>567</v>
+      </c>
+      <c r="B49">
+        <v>83</v>
+      </c>
+      <c r="C49" t="s">
+        <v>473</v>
+      </c>
+      <c r="D49" t="s">
+        <v>532</v>
+      </c>
+      <c r="E49" t="s">
+        <v>533</v>
+      </c>
+      <c r="F49" t="s">
+        <v>535</v>
+      </c>
+      <c r="G49" t="s">
+        <v>536</v>
+      </c>
+      <c r="H49" t="s">
+        <v>538</v>
+      </c>
+      <c r="I49" t="s">
+        <v>539</v>
+      </c>
+      <c r="J49" t="s">
+        <v>540</v>
+      </c>
+      <c r="K49" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>567</v>
+      </c>
+      <c r="B50">
+        <v>82</v>
+      </c>
+      <c r="C50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" t="s">
+        <v>227</v>
+      </c>
+      <c r="E50" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" t="s">
+        <v>230</v>
+      </c>
+      <c r="G50" t="s">
+        <v>231</v>
+      </c>
+      <c r="H50" t="s">
+        <v>233</v>
+      </c>
+      <c r="I50" t="s">
+        <v>234</v>
+      </c>
+      <c r="J50" t="s">
+        <v>235</v>
+      </c>
+      <c r="K50" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>567</v>
+      </c>
+      <c r="B51">
+        <v>82</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" t="s">
+        <v>267</v>
+      </c>
+      <c r="F51" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" t="s">
+        <v>58</v>
+      </c>
+      <c r="H51" t="s">
+        <v>270</v>
+      </c>
+      <c r="I51" t="s">
+        <v>79</v>
+      </c>
+      <c r="J51" t="s">
+        <v>79</v>
+      </c>
+      <c r="K51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>567</v>
+      </c>
+      <c r="B52">
+        <v>82</v>
+      </c>
+      <c r="C52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D52" t="s">
+        <v>338</v>
+      </c>
+      <c r="E52" t="s">
+        <v>339</v>
+      </c>
+      <c r="F52" t="s">
+        <v>341</v>
+      </c>
+      <c r="G52" t="s">
+        <v>342</v>
+      </c>
+      <c r="H52" t="s">
+        <v>344</v>
+      </c>
+      <c r="I52" t="s">
+        <v>345</v>
+      </c>
+      <c r="J52" t="s">
+        <v>346</v>
+      </c>
+      <c r="K52" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>567</v>
+      </c>
+      <c r="B53">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53" t="s">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" t="s">
+        <v>87</v>
+      </c>
+      <c r="K53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>567</v>
+      </c>
+      <c r="B54">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s">
         <v>284</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D54" t="s">
         <v>377</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E54" t="s">
         <v>378</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F54" t="s">
         <v>380</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G54" t="s">
         <v>381</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H54" t="s">
         <v>383</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I54" t="s">
         <v>384</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J54" t="s">
         <v>385</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K54" t="s">
         <v>379</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>567</v>
+      </c>
+      <c r="B55">
+        <v>81</v>
+      </c>
+      <c r="C55" t="s">
+        <v>473</v>
+      </c>
+      <c r="D55" t="s">
+        <v>499</v>
+      </c>
+      <c r="E55" t="s">
+        <v>500</v>
+      </c>
+      <c r="F55" t="s">
+        <v>502</v>
+      </c>
+      <c r="G55" t="s">
+        <v>503</v>
+      </c>
+      <c r="H55" t="s">
+        <v>505</v>
+      </c>
+      <c r="I55" t="s">
+        <v>506</v>
+      </c>
+      <c r="J55" t="s">
+        <v>507</v>
+      </c>
+      <c r="K55" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="631">
   <si>
     <t>日期</t>
   </si>
@@ -1682,6 +1682,111 @@
   </si>
   <si>
     <t>研究72/技能68/学历85/行业100/企业78</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>心脉医疗（上海）</t>
+  </si>
+  <si>
+    <t>研发工程师（输送系统结构设计）</t>
+  </si>
+  <si>
+    <t>负责新一代输送系统结构设计、产品标准制定、设计开发跟踪及上市产品维护。要求硕士及以上机械/化学/高分子等专业，掌握 CAD 或 SolidWorks 等机械制图软件，接受应届毕业生，有相关经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招(接受应届)】|强烈推荐|血管介入输送系统结构设计岗，接受应届，方向相关且技能（结构设计+材料）有重合</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>心脉医疗（微创系）为主动脉及外周血管介入龙头上市公司，输送系统结构设计岗直接对口血管介入器械研发方向，明确接受应届硕士，上海岗位符合城市偏好。需掌握 CAD/SolidWorks 三维建模，与本人支架结构设计与力学评价技能高度契合。</t>
+  </si>
+  <si>
+    <t>突出血管支架/输送系统的结构设计与三维建模（SolidWorks/CAD）项目经历；量化力学性能测试、有限元分析数据；强调材料选型（镍钛/高分子）能力，并注明可接受应届、愿意投入输送系统方向。</t>
+  </si>
+  <si>
+    <t>工艺工程师（新产品设计/动物实验/新材料）</t>
+  </si>
+  <si>
+    <t>负责已上市产品维护、新产品工艺设计与小批量试产转移，参与动物实验、临床评价、性能验证与风险分析，调研新工艺新材料应用。要求硕士及以上机械/化学/高分子专业，熟悉工程材料特性及 CAD/SolidWorks。</t>
+  </si>
+  <si>
+    <t>智能匹配89分【社招(接受应届)】|强烈推荐|血管介入器械工艺岗含动物实验+新材料+结构设计，技能（材料学+动物实验+结构）多重覆盖</t>
+  </si>
+  <si>
+    <t>研究82/技能88/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>心脉医疗为血管介入龙头，本岗属新产品工艺/动物实验/临床评价方向，明确含动物实验与新材料调研，与本人材料学、生物相容性评价、动物实验三大核心技能重合，接受应届硕士，且工作地在上海，是最匹配的应届可投研发工艺岗。</t>
+  </si>
+  <si>
+    <t>重点突出动物实验完整流程（动物模型、植入、影像学随访、组织切片评估）；补充生物相容性评价与 ISO10993 经验；强调新材料（可降解/镍钛）调研能力；量化小批量试产与性能验证结果。</t>
+  </si>
+  <si>
+    <t>麦瑞通医疗器械（北京）Merit Medical</t>
+  </si>
+  <si>
+    <t>校园招聘及实习生招聘（研发类）</t>
+  </si>
+  <si>
+    <t>Merit Medical 为国际化介入医疗器械生产商，产品线含球囊充盈装置、诊断/治疗导管及导丝、非血管性支架等心脏介入及放射手术器械，面向介入器械方向研发类岗位进行校园招聘（应届及在校生均可关注）。</t>
+  </si>
+  <si>
+    <t>https://my.yingjiesheng.com/company_8160856.html</t>
+  </si>
+  <si>
+    <t>智能匹配87分【校园招聘】|强烈推荐|国际化介入医疗器械龙头校园招聘研发类，方向（球囊/导管/支架）与技能设计匹配</t>
+  </si>
+  <si>
+    <t>研究84/技能78/学历100/行业100/企业92</t>
+  </si>
+  <si>
+    <t>Merit Medical 是全球领先介入医疗器械跨国公司，本岗为正式校园招聘研发类岗位，产品线（球囊、导管、导丝、非血管性支架）与血管介入方向高度一致，且在北京，应届硕士可直接投递，属校级渠道发布的可核实正式岗位。</t>
+  </si>
+  <si>
+    <t>突出介入导管/球囊/支架等植介入器械研发意向与项目经历；强调材料学与结构设计能力；补充生物相容性与动物实验经验以区别于一般候选；标注可赴北京工作。</t>
+  </si>
+  <si>
+    <t>科睿驰（深圳）医疗科技发展有限公司</t>
+  </si>
+  <si>
+    <t>校园招聘（研发/技术岗）</t>
+  </si>
+  <si>
+    <t>国家高新技术企业，聚焦肿瘤介入微创治疗领域，自研产品围绕肿瘤介入、药械结合、精密介入类产品布局，面向介入器械方向研发/技术岗位进行校园招聘。</t>
+  </si>
+  <si>
+    <t>https://my.yingjiesheng.com/company_14844063.html</t>
+  </si>
+  <si>
+    <t>智能匹配79分【校园招聘】|值得考虑|介入器械方向校园招聘，肿瘤微创介入与血管介入同属介入器械领域，虽非完全对口但可纳入</t>
+  </si>
+  <si>
+    <t>研究76/技能62/学历100/行业100/企业86</t>
+  </si>
+  <si>
+    <t>温州医科大学附属第一医院（谢聪颖课题组）</t>
+  </si>
+  <si>
+    <t>博士后</t>
+  </si>
+  <si>
+    <t>依托温州医科大学附属第一医院，医院在心血管介入等领域的诊治与国际接轨，课题组招收博士后研究人员，适合意向继续从事心血管介入临床/科研方向的博士候选人。</t>
+  </si>
+  <si>
+    <t>温州</t>
+  </si>
+  <si>
+    <t>https://www.yingjiesheng.com/job-008-000-432.html</t>
+  </si>
+  <si>
+    <t>智能匹配78分【博士后】|值得考虑|医院课题组心血管介入方向博士后，研究方向相关且属高校/医院课题组（高企业分），但学历门槛为博士</t>
+  </si>
+  <si>
+    <t>研究83/技能60/学历82/行业100/企业90</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -2236,7 +2341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5175,6 +5280,196 @@
         <v>79</v>
       </c>
       <c r="L77" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>556</v>
+      </c>
+      <c r="B78" t="s">
+        <v>557</v>
+      </c>
+      <c r="C78" t="s">
+        <v>558</v>
+      </c>
+      <c r="D78" t="s">
+        <v>559</v>
+      </c>
+      <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" t="s">
+        <v>468</v>
+      </c>
+      <c r="G78">
+        <v>9</v>
+      </c>
+      <c r="H78" t="s">
+        <v>560</v>
+      </c>
+      <c r="I78">
+        <v>86</v>
+      </c>
+      <c r="J78" t="s">
+        <v>561</v>
+      </c>
+      <c r="K78" t="s">
+        <v>562</v>
+      </c>
+      <c r="L78" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>556</v>
+      </c>
+      <c r="B79" t="s">
+        <v>557</v>
+      </c>
+      <c r="C79" t="s">
+        <v>564</v>
+      </c>
+      <c r="D79" t="s">
+        <v>565</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" t="s">
+        <v>468</v>
+      </c>
+      <c r="G79">
+        <v>9</v>
+      </c>
+      <c r="H79" t="s">
+        <v>566</v>
+      </c>
+      <c r="I79">
+        <v>89</v>
+      </c>
+      <c r="J79" t="s">
+        <v>567</v>
+      </c>
+      <c r="K79" t="s">
+        <v>568</v>
+      </c>
+      <c r="L79" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>556</v>
+      </c>
+      <c r="B80" t="s">
+        <v>570</v>
+      </c>
+      <c r="C80" t="s">
+        <v>571</v>
+      </c>
+      <c r="D80" t="s">
+        <v>572</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>573</v>
+      </c>
+      <c r="G80">
+        <v>9</v>
+      </c>
+      <c r="H80" t="s">
+        <v>574</v>
+      </c>
+      <c r="I80">
+        <v>87</v>
+      </c>
+      <c r="J80" t="s">
+        <v>575</v>
+      </c>
+      <c r="K80" t="s">
+        <v>576</v>
+      </c>
+      <c r="L80" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>556</v>
+      </c>
+      <c r="B81" t="s">
+        <v>578</v>
+      </c>
+      <c r="C81" t="s">
+        <v>579</v>
+      </c>
+      <c r="D81" t="s">
+        <v>580</v>
+      </c>
+      <c r="E81" t="s">
+        <v>66</v>
+      </c>
+      <c r="F81" t="s">
+        <v>581</v>
+      </c>
+      <c r="G81">
+        <v>8</v>
+      </c>
+      <c r="H81" t="s">
+        <v>582</v>
+      </c>
+      <c r="I81">
+        <v>79</v>
+      </c>
+      <c r="J81" t="s">
+        <v>583</v>
+      </c>
+      <c r="K81" t="s">
+        <v>79</v>
+      </c>
+      <c r="L81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>556</v>
+      </c>
+      <c r="B82" t="s">
+        <v>584</v>
+      </c>
+      <c r="C82" t="s">
+        <v>585</v>
+      </c>
+      <c r="D82" t="s">
+        <v>586</v>
+      </c>
+      <c r="E82" t="s">
+        <v>587</v>
+      </c>
+      <c r="F82" t="s">
+        <v>588</v>
+      </c>
+      <c r="G82">
+        <v>8</v>
+      </c>
+      <c r="H82" t="s">
+        <v>589</v>
+      </c>
+      <c r="I82">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s">
+        <v>590</v>
+      </c>
+      <c r="K82" t="s">
+        <v>79</v>
+      </c>
+      <c r="L82" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5209,7 +5504,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>556</v>
+        <v>591</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5218,16 +5513,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>558</v>
+        <v>593</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>559</v>
+        <v>594</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>560</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5241,13 +5536,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>561</v>
+        <v>596</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>563</v>
+        <v>598</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -5275,7 +5570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5290,7 +5585,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>568</v>
+        <v>603</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5300,31 +5595,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>569</v>
+        <v>604</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>570</v>
+        <v>605</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="B4">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>572</v>
+        <v>607</v>
       </c>
       <c r="B5" t="s">
-        <v>573</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>574</v>
+        <v>609</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -5332,7 +5627,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>575</v>
+        <v>610</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -5340,23 +5635,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="B8">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -5364,15 +5659,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="B11" t="s">
-        <v>473</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -5382,15 +5677,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>581</v>
+        <v>616</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>582</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>583</v>
+        <v>618</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -5398,23 +5693,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>584</v>
+        <v>619</v>
       </c>
       <c r="B17" s="5">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>585</v>
+        <v>620</v>
       </c>
       <c r="B18" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>586</v>
+        <v>621</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -5422,7 +5717,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>587</v>
+        <v>622</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5430,7 +5725,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>588</v>
+        <v>623</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5438,7 +5733,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5446,7 +5741,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>590</v>
+        <v>625</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5454,7 +5749,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5462,7 +5757,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>592</v>
+        <v>627</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5470,7 +5765,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -5482,7 +5777,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>594</v>
+        <v>629</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -5500,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>595</v>
+        <v>630</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -6577,25 +6872,25 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>556</v>
       </c>
       <c r="C71" t="s">
-        <v>72</v>
+        <v>557</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>558</v>
       </c>
       <c r="E71" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>468</v>
       </c>
       <c r="G71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H71" t="s">
-        <v>77</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6603,25 +6898,25 @@
         <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>556</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="D72" t="s">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="E72" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F72" t="s">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="G72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H72" t="s">
-        <v>84</v>
+        <v>566</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6629,25 +6924,25 @@
         <v>44</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>556</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>570</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>571</v>
       </c>
       <c r="E73" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
-        <v>107</v>
+        <v>573</v>
       </c>
       <c r="G73">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H73" t="s">
-        <v>108</v>
+        <v>574</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6658,22 +6953,22 @@
         <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F74" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G74">
         <v>8</v>
       </c>
       <c r="H74" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -6684,22 +6979,22 @@
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F75" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="G75">
         <v>8</v>
       </c>
       <c r="H75" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -6710,22 +7005,22 @@
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G76">
         <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -6736,22 +7031,22 @@
         <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E77" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G77">
         <v>8</v>
       </c>
       <c r="H77" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -6762,22 +7057,22 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E78" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -6785,25 +7080,25 @@
         <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="E79" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="F79" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -6811,25 +7106,25 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="F80" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -6837,25 +7132,25 @@
         <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="D81" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="E81" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6866,22 +7161,22 @@
         <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F82" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -6892,22 +7187,22 @@
         <v>159</v>
       </c>
       <c r="C83" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D83" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F83" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -6918,22 +7213,22 @@
         <v>159</v>
       </c>
       <c r="C84" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="F84" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -6944,22 +7239,22 @@
         <v>159</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D85" t="s">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
-        <v>251</v>
+        <v>76</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -6970,22 +7265,22 @@
         <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D86" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E86" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -6996,22 +7291,22 @@
         <v>159</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D87" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E87" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7022,22 +7317,22 @@
         <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D88" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -7048,22 +7343,22 @@
         <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="E89" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="F89" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -7071,25 +7366,25 @@
         <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="D90" t="s">
-        <v>316</v>
+        <v>122</v>
       </c>
       <c r="E90" t="s">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="F90" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>320</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -7097,25 +7392,25 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C91" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="E91" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>343</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7123,25 +7418,25 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="F92" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>351</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7152,22 +7447,22 @@
         <v>284</v>
       </c>
       <c r="C93" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="D93" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="E93" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="F93" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7178,22 +7473,22 @@
         <v>284</v>
       </c>
       <c r="C94" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="D94" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E94" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="F94" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -7204,22 +7499,22 @@
         <v>284</v>
       </c>
       <c r="C95" t="s">
-        <v>144</v>
+        <v>347</v>
       </c>
       <c r="D95" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="E95" t="s">
-        <v>396</v>
+        <v>98</v>
       </c>
       <c r="F95" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -7227,25 +7522,25 @@
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C96" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="D96" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="E96" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F96" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -7253,25 +7548,25 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="D97" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="E97" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F97" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7279,25 +7574,25 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C98" t="s">
-        <v>424</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E98" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F98" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7308,22 +7603,22 @@
         <v>402</v>
       </c>
       <c r="C99" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="D99" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F99" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -7331,25 +7626,25 @@
         <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C100" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="D100" t="s">
-        <v>122</v>
+        <v>419</v>
       </c>
       <c r="E100" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F100" t="s">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>487</v>
+        <v>422</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -7357,25 +7652,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C101" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="D101" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F101" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -7383,25 +7678,25 @@
         <v>73</v>
       </c>
       <c r="B102" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C102" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="D102" t="s">
-        <v>500</v>
+        <v>431</v>
       </c>
       <c r="E102" t="s">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="F102" t="s">
-        <v>503</v>
+        <v>433</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -7412,22 +7707,22 @@
         <v>473</v>
       </c>
       <c r="C103" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="D103" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="E103" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="F103" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>537</v>
+        <v>487</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -7438,22 +7733,22 @@
         <v>473</v>
       </c>
       <c r="C104" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="D104" t="s">
-        <v>551</v>
+        <v>492</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F104" t="s">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -7461,24 +7756,154 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
+        <v>473</v>
+      </c>
+      <c r="C105" t="s">
+        <v>499</v>
+      </c>
+      <c r="D105" t="s">
+        <v>500</v>
+      </c>
+      <c r="E105" t="s">
+        <v>502</v>
+      </c>
+      <c r="F105" t="s">
+        <v>503</v>
+      </c>
+      <c r="G105">
+        <v>8</v>
+      </c>
+      <c r="H105" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>77</v>
+      </c>
+      <c r="B106" t="s">
+        <v>473</v>
+      </c>
+      <c r="C106" t="s">
+        <v>532</v>
+      </c>
+      <c r="D106" t="s">
+        <v>533</v>
+      </c>
+      <c r="E106" t="s">
+        <v>535</v>
+      </c>
+      <c r="F106" t="s">
+        <v>536</v>
+      </c>
+      <c r="G106">
+        <v>8</v>
+      </c>
+      <c r="H106" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>78</v>
+      </c>
+      <c r="B107" t="s">
+        <v>473</v>
+      </c>
+      <c r="C107" t="s">
+        <v>550</v>
+      </c>
+      <c r="D107" t="s">
+        <v>551</v>
+      </c>
+      <c r="E107" t="s">
+        <v>16</v>
+      </c>
+      <c r="F107" t="s">
+        <v>553</v>
+      </c>
+      <c r="G107">
+        <v>8</v>
+      </c>
+      <c r="H107" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>79</v>
+      </c>
+      <c r="B108" t="s">
+        <v>556</v>
+      </c>
+      <c r="C108" t="s">
+        <v>578</v>
+      </c>
+      <c r="D108" t="s">
+        <v>579</v>
+      </c>
+      <c r="E108" t="s">
+        <v>66</v>
+      </c>
+      <c r="F108" t="s">
+        <v>581</v>
+      </c>
+      <c r="G108">
+        <v>8</v>
+      </c>
+      <c r="H108" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>80</v>
+      </c>
+      <c r="B109" t="s">
+        <v>556</v>
+      </c>
+      <c r="C109" t="s">
+        <v>584</v>
+      </c>
+      <c r="D109" t="s">
+        <v>585</v>
+      </c>
+      <c r="E109" t="s">
+        <v>587</v>
+      </c>
+      <c r="F109" t="s">
+        <v>588</v>
+      </c>
+      <c r="G109">
+        <v>8</v>
+      </c>
+      <c r="H109" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>81</v>
+      </c>
+      <c r="B110" t="s">
         <v>159</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C110" t="s">
         <v>271</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D110" t="s">
         <v>272</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E110" t="s">
         <v>75</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F110" t="s">
         <v>274</v>
       </c>
-      <c r="G105">
+      <c r="G110">
         <v>7</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H110" t="s">
         <v>275</v>
       </c>
     </row>
@@ -7495,7 +7920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7512,10 +7937,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -7542,12 +7967,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>566</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -7582,7 +8007,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -7617,7 +8042,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -7652,7 +8077,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -7687,7 +8112,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -7722,7 +8147,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -7757,7 +8182,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -7792,7 +8217,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -7827,7 +8252,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -7862,7 +8287,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -7897,7 +8322,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -7932,7 +8357,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -7967,7 +8392,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -8002,7 +8427,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -8037,7 +8462,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -8072,7 +8497,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -8107,7 +8532,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -8142,7 +8567,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -8177,7 +8602,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -8212,7 +8637,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -8247,7 +8672,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -8282,7 +8707,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B23">
         <v>89</v>
@@ -8317,7 +8742,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -8352,252 +8777,252 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B25">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>556</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>557</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>564</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>468</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>567</v>
       </c>
       <c r="I25" t="s">
-        <v>37</v>
+        <v>568</v>
       </c>
       <c r="J25" t="s">
-        <v>38</v>
+        <v>569</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>565</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B26">
         <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J26" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K26" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B27">
         <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H27" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I27" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J27" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K27" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B28">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E28" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H28" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I28" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J28" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K28" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B29">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D29" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>449</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>438</v>
       </c>
       <c r="H29" t="s">
-        <v>188</v>
+        <v>452</v>
       </c>
       <c r="I29" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s">
-        <v>186</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B30">
         <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F30" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G30" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H30" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I30" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J30" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K30" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B31">
         <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E31" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G31" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H31" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I31" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K31" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B32">
         <v>87</v>
@@ -8609,7 +9034,7 @@
         <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
@@ -8627,811 +9052,916 @@
         <v>79</v>
       </c>
       <c r="K32" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B33">
         <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F33" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H33" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I33" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B34">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D34" t="s">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>370</v>
+        <v>508</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>510</v>
       </c>
       <c r="G34" t="s">
-        <v>372</v>
+        <v>511</v>
       </c>
       <c r="H34" t="s">
-        <v>374</v>
+        <v>513</v>
       </c>
       <c r="I34" t="s">
-        <v>375</v>
+        <v>514</v>
       </c>
       <c r="J34" t="s">
-        <v>376</v>
+        <v>515</v>
       </c>
       <c r="K34" t="s">
-        <v>371</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B35">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="E35" t="s">
-        <v>457</v>
+        <v>571</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="H35" t="s">
-        <v>460</v>
+        <v>575</v>
       </c>
       <c r="I35" t="s">
-        <v>461</v>
+        <v>576</v>
       </c>
       <c r="J35" t="s">
-        <v>462</v>
+        <v>577</v>
       </c>
       <c r="K35" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B36">
         <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="E36" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="H36" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="I36" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J36" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="K36" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B37">
         <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D37" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F37" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="I37" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J37" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="K37" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B38">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>322</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>466</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>468</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>470</v>
       </c>
       <c r="I38" t="s">
-        <v>61</v>
+        <v>471</v>
       </c>
       <c r="J38" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="K38" t="s">
-        <v>57</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B39">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>541</v>
       </c>
       <c r="E39" t="s">
-        <v>89</v>
+        <v>542</v>
       </c>
       <c r="F39" t="s">
-        <v>130</v>
+        <v>544</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>545</v>
       </c>
       <c r="H39" t="s">
-        <v>133</v>
+        <v>547</v>
       </c>
       <c r="I39" t="s">
-        <v>134</v>
+        <v>548</v>
       </c>
       <c r="J39" t="s">
-        <v>135</v>
+        <v>549</v>
       </c>
       <c r="K39" t="s">
-        <v>129</v>
+        <v>543</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B40">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>284</v>
+        <v>556</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>557</v>
       </c>
       <c r="E40" t="s">
-        <v>308</v>
+        <v>558</v>
       </c>
       <c r="F40" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>310</v>
+        <v>468</v>
       </c>
       <c r="H40" t="s">
-        <v>312</v>
+        <v>561</v>
       </c>
       <c r="I40" t="s">
-        <v>313</v>
+        <v>562</v>
       </c>
       <c r="J40" t="s">
-        <v>314</v>
+        <v>563</v>
       </c>
       <c r="K40" t="s">
-        <v>309</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B41">
         <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
         <v>55</v>
       </c>
       <c r="E41" t="s">
-        <v>403</v>
+        <v>56</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>405</v>
+        <v>58</v>
       </c>
       <c r="H41" t="s">
-        <v>407</v>
+        <v>60</v>
       </c>
       <c r="I41" t="s">
-        <v>408</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>409</v>
+        <v>62</v>
       </c>
       <c r="K41" t="s">
-        <v>404</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B42">
         <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>474</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="F42" t="s">
-        <v>477</v>
+        <v>130</v>
       </c>
       <c r="G42" t="s">
-        <v>478</v>
+        <v>131</v>
       </c>
       <c r="H42" t="s">
-        <v>480</v>
+        <v>133</v>
       </c>
       <c r="I42" t="s">
-        <v>481</v>
+        <v>134</v>
       </c>
       <c r="J42" t="s">
-        <v>482</v>
+        <v>135</v>
       </c>
       <c r="K42" t="s">
-        <v>476</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B43">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="F43" t="s">
         <v>147</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>310</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="I43" t="s">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="J43" t="s">
-        <v>152</v>
+        <v>314</v>
       </c>
       <c r="K43" t="s">
-        <v>146</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B44">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F44" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H44" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="I44" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="J44" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="K44" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B45">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D45" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
       <c r="E45" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>477</v>
       </c>
       <c r="G45" t="s">
-        <v>413</v>
+        <v>478</v>
       </c>
       <c r="H45" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="I45" t="s">
-        <v>416</v>
+        <v>481</v>
       </c>
       <c r="J45" t="s">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="K45" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B46">
         <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>485</v>
+        <v>147</v>
       </c>
       <c r="G46" t="s">
-        <v>486</v>
+        <v>148</v>
       </c>
       <c r="H46" t="s">
-        <v>488</v>
+        <v>150</v>
       </c>
       <c r="I46" t="s">
-        <v>489</v>
+        <v>151</v>
       </c>
       <c r="J46" t="s">
-        <v>490</v>
+        <v>152</v>
       </c>
       <c r="K46" t="s">
-        <v>484</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B47">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
         <v>284</v>
       </c>
       <c r="D47" t="s">
-        <v>353</v>
+        <v>144</v>
       </c>
       <c r="E47" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="F47" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="G47" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="H47" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="I47" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="J47" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="K47" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B48">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D48" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="E48" t="s">
-        <v>492</v>
+        <v>411</v>
       </c>
       <c r="F48" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G48" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="H48" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="I48" t="s">
-        <v>497</v>
+        <v>416</v>
       </c>
       <c r="J48" t="s">
-        <v>498</v>
+        <v>417</v>
       </c>
       <c r="K48" t="s">
-        <v>493</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B49">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
         <v>473</v>
       </c>
       <c r="D49" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="E49" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="F49" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="G49" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="H49" t="s">
-        <v>538</v>
+        <v>488</v>
       </c>
       <c r="I49" t="s">
-        <v>539</v>
+        <v>489</v>
       </c>
       <c r="J49" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="K49" t="s">
-        <v>534</v>
+        <v>484</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B50">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="E50" t="s">
-        <v>228</v>
+        <v>362</v>
       </c>
       <c r="F50" t="s">
-        <v>230</v>
+        <v>356</v>
       </c>
       <c r="G50" t="s">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="H50" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="I50" t="s">
-        <v>234</v>
+        <v>367</v>
       </c>
       <c r="J50" t="s">
-        <v>235</v>
+        <v>368</v>
       </c>
       <c r="K50" t="s">
-        <v>229</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B51">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>491</v>
       </c>
       <c r="E51" t="s">
-        <v>267</v>
+        <v>492</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>58</v>
+        <v>494</v>
       </c>
       <c r="H51" t="s">
-        <v>270</v>
+        <v>496</v>
       </c>
       <c r="I51" t="s">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="J51" t="s">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="K51" t="s">
-        <v>268</v>
+        <v>493</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B52">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D52" t="s">
-        <v>338</v>
+        <v>532</v>
       </c>
       <c r="E52" t="s">
-        <v>339</v>
+        <v>533</v>
       </c>
       <c r="F52" t="s">
-        <v>341</v>
+        <v>535</v>
       </c>
       <c r="G52" t="s">
-        <v>342</v>
+        <v>536</v>
       </c>
       <c r="H52" t="s">
-        <v>344</v>
+        <v>538</v>
       </c>
       <c r="I52" t="s">
-        <v>345</v>
+        <v>539</v>
       </c>
       <c r="J52" t="s">
-        <v>346</v>
+        <v>540</v>
       </c>
       <c r="K52" t="s">
-        <v>340</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B53">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="E53" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="G53" t="s">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="H53" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="I53" t="s">
-        <v>86</v>
+        <v>234</v>
       </c>
       <c r="J53" t="s">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="K53" t="s">
-        <v>82</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B54">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D54" t="s">
-        <v>377</v>
+        <v>266</v>
       </c>
       <c r="E54" t="s">
-        <v>378</v>
+        <v>267</v>
       </c>
       <c r="F54" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>381</v>
+        <v>58</v>
       </c>
       <c r="H54" t="s">
-        <v>383</v>
+        <v>270</v>
       </c>
       <c r="I54" t="s">
-        <v>384</v>
+        <v>79</v>
       </c>
       <c r="J54" t="s">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s">
-        <v>379</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="B55">
+        <v>82</v>
+      </c>
+      <c r="C55" t="s">
+        <v>284</v>
+      </c>
+      <c r="D55" t="s">
+        <v>338</v>
+      </c>
+      <c r="E55" t="s">
+        <v>339</v>
+      </c>
+      <c r="F55" t="s">
+        <v>341</v>
+      </c>
+      <c r="G55" t="s">
+        <v>342</v>
+      </c>
+      <c r="H55" t="s">
+        <v>344</v>
+      </c>
+      <c r="I55" t="s">
+        <v>345</v>
+      </c>
+      <c r="J55" t="s">
+        <v>346</v>
+      </c>
+      <c r="K55" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>602</v>
+      </c>
+      <c r="B56">
         <v>81</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s">
+        <v>85</v>
+      </c>
+      <c r="I56" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56" t="s">
+        <v>87</v>
+      </c>
+      <c r="K56" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>602</v>
+      </c>
+      <c r="B57">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s">
+        <v>284</v>
+      </c>
+      <c r="D57" t="s">
+        <v>377</v>
+      </c>
+      <c r="E57" t="s">
+        <v>378</v>
+      </c>
+      <c r="F57" t="s">
+        <v>380</v>
+      </c>
+      <c r="G57" t="s">
+        <v>381</v>
+      </c>
+      <c r="H57" t="s">
+        <v>383</v>
+      </c>
+      <c r="I57" t="s">
+        <v>384</v>
+      </c>
+      <c r="J57" t="s">
+        <v>385</v>
+      </c>
+      <c r="K57" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>602</v>
+      </c>
+      <c r="B58">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
         <v>473</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D58" t="s">
         <v>499</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E58" t="s">
         <v>500</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F58" t="s">
         <v>502</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G58" t="s">
         <v>503</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H58" t="s">
         <v>505</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I58" t="s">
         <v>506</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J58" t="s">
         <v>507</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K58" t="s">
         <v>501</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="667">
   <si>
     <t>日期</t>
   </si>
@@ -1787,6 +1787,114 @@
   </si>
   <si>
     <t>研究83/技能60/学历82/行业100/企业90</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>山东华安生物科技有限公司</t>
+  </si>
+  <si>
+    <t>生物全降解血管支架研发工程师</t>
+  </si>
+  <si>
+    <t>公司在业内医疗和聚合物领域专家领衔的研发团队下，致力于生物高分子材料研究和生物全降解血管支架（XINSORB）研发，需完成注册用动物实验；高分子/生物材料背景优先。</t>
+  </si>
+  <si>
+    <t>山东烟台</t>
+  </si>
+  <si>
+    <t>https://life.ytu.edu.cn</t>
+  </si>
+  <si>
+    <t>智能匹配89分【社招】|强烈推荐|生物全降解血管支架XINSORB研发+动物实验，方向直接匹配</t>
+  </si>
+  <si>
+    <t>研究95/技能80/学历90/行业100/企业78</t>
+  </si>
+  <si>
+    <t>山东华安专注生物全降解血管支架(XINSORB)研发，这与硕士血管支架研究方向高度一致，岗位含注册用动物实验，与本人材料学、生物相容性评价、动物实验多项核心技能重合，是进行可降解支架研发的精准平台。</t>
+  </si>
+  <si>
+    <t>重点突出血管支架课题与可降解/生物高分子材料项目经历；量化降解行为、力学与体内动物实验（模型、随访、组织切片）数据；强调生物相容性评价与ISO10993经验；呼应XINSORB全降解支架技术路线。</t>
+  </si>
+  <si>
+    <t>沛嘉医疗（苏州）</t>
+  </si>
+  <si>
+    <t>支架工程师（颅内支架）</t>
+  </si>
+  <si>
+    <t>负责颅内支架的研发工作及颅内支架产品的工艺开发和实现，确保研发符合质量体系；苏州招聘，硕士学历，3-5年经验；五险一金、补充医疗、定期体检、年终奖、股票期权。</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com</t>
+  </si>
+  <si>
+    <t>智能匹配82分【社招】|强烈推荐|颅内支架研发+工艺开发，神经介入方向相关，苏州符合城市偏好</t>
+  </si>
+  <si>
+    <t>研究82/技能70/学历88/行业100/企业92</t>
+  </si>
+  <si>
+    <t>沛嘉为港股上市高端介入器械企业，岗位负责颅内支架研发与工艺实现，属神经介入支架领域，与本人支架设计、材料学技能相关，且苏州符合城市偏好，为可投递的介入支架研发优质岗位。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计与工艺实现项目；补充材料学与神经介入器械认知；量化支架性能测试、机械/力学数据；强调硕士支架研究背景的可迁移性，弱化经验年限、强化专业匹配。</t>
+  </si>
+  <si>
+    <t>上海汉通医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>支架研发工程师</t>
+  </si>
+  <si>
+    <t>心血管植入介入医疗器械产品开发企业（外周泛血管、电生理、消融介入产品），负责支架类产品研发；本科与硕士岗位薪酬约17.5K-32.5K。</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|介入医疗器械支架研发岗，方向直接匹配，上海岗位</t>
+  </si>
+  <si>
+    <t>研究90/技能75/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>汉通医疗从事心血管植入介入器械开发，岗位即支架类产品研发，与硕士血管支架研究方向和支架设计技能直接对口，上海符合城市偏好，薪资与硕士学历对标，是合适的支架研发岗位。</t>
+  </si>
+  <si>
+    <t>突出血管支架结构设计课题与材料学、生物相容性评价经历；量化支架力学/降解性能测试数据；强调介入器械全流程研发理解，展示外周/泛血管介入产品开发的兴趣与学习能力。</t>
+  </si>
+  <si>
+    <t>上海微创心通医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>高端介入医疗器械研发企业，开展支架类产品研发工作；岗位薪酬区间20K-30K。</t>
+  </si>
+  <si>
+    <t>https://www.jobui.com</t>
+  </si>
+  <si>
+    <t>智能匹配81分【社招】|强烈推荐|高端介入器械支架研发岗，微创系平台，方向相关</t>
+  </si>
+  <si>
+    <t>研究80/技能72/学历85/行业100/企业88</t>
+  </si>
+  <si>
+    <t>微创心通为微创系高端介入医疗器械企业，支架研发工程师岗位与硕士支架研究方向及介入器械领域契合，上海为偏好城市，平台与培养环境优质，是进入介入器械龙头的有效通道。</t>
+  </si>
+  <si>
+    <t>突出支架/植入介入器械结构设计与材料学项目；量化力学性能与测试数据；强调可降解材料与生物相容性评价经验；呼应微创在心血管介入领域的全球布局，展现长期技术成长意愿。</t>
+  </si>
+  <si>
+    <t>质量工程师</t>
+  </si>
+  <si>
+    <t>设计产品质量评价、评价方法建立与维护、产品货架寿命验证、原材料质量评价、风险管理；硕士及以上机械/材料/生物医学类，掌握质量管理理论及医疗器械法规标准，良好英语，1-3年相关经验优先。</t>
+  </si>
+  <si>
+    <t>智能匹配75分【社招】|值得考虑|医疗器械质量岗，材料/生物医学专业对口，上海上市龙头平台</t>
+  </si>
+  <si>
+    <t>研究70/技能58/学历92/行业100/企业92</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -2341,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5470,6 +5578,196 @@
         <v>79</v>
       </c>
       <c r="L82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>591</v>
+      </c>
+      <c r="B83" t="s">
+        <v>592</v>
+      </c>
+      <c r="C83" t="s">
+        <v>593</v>
+      </c>
+      <c r="D83" t="s">
+        <v>594</v>
+      </c>
+      <c r="E83" t="s">
+        <v>595</v>
+      </c>
+      <c r="F83" t="s">
+        <v>596</v>
+      </c>
+      <c r="G83">
+        <v>9</v>
+      </c>
+      <c r="H83" t="s">
+        <v>597</v>
+      </c>
+      <c r="I83">
+        <v>89</v>
+      </c>
+      <c r="J83" t="s">
+        <v>598</v>
+      </c>
+      <c r="K83" t="s">
+        <v>599</v>
+      </c>
+      <c r="L83" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>591</v>
+      </c>
+      <c r="B84" t="s">
+        <v>601</v>
+      </c>
+      <c r="C84" t="s">
+        <v>602</v>
+      </c>
+      <c r="D84" t="s">
+        <v>603</v>
+      </c>
+      <c r="E84" t="s">
+        <v>75</v>
+      </c>
+      <c r="F84" t="s">
+        <v>604</v>
+      </c>
+      <c r="G84">
+        <v>8</v>
+      </c>
+      <c r="H84" t="s">
+        <v>605</v>
+      </c>
+      <c r="I84">
+        <v>82</v>
+      </c>
+      <c r="J84" t="s">
+        <v>606</v>
+      </c>
+      <c r="K84" t="s">
+        <v>607</v>
+      </c>
+      <c r="L84" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>591</v>
+      </c>
+      <c r="B85" t="s">
+        <v>609</v>
+      </c>
+      <c r="C85" t="s">
+        <v>610</v>
+      </c>
+      <c r="D85" t="s">
+        <v>611</v>
+      </c>
+      <c r="E85" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" t="s">
+        <v>604</v>
+      </c>
+      <c r="G85">
+        <v>9</v>
+      </c>
+      <c r="H85" t="s">
+        <v>612</v>
+      </c>
+      <c r="I85">
+        <v>86</v>
+      </c>
+      <c r="J85" t="s">
+        <v>613</v>
+      </c>
+      <c r="K85" t="s">
+        <v>614</v>
+      </c>
+      <c r="L85" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>591</v>
+      </c>
+      <c r="B86" t="s">
+        <v>616</v>
+      </c>
+      <c r="C86" t="s">
+        <v>610</v>
+      </c>
+      <c r="D86" t="s">
+        <v>617</v>
+      </c>
+      <c r="E86" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" t="s">
+        <v>618</v>
+      </c>
+      <c r="G86">
+        <v>8</v>
+      </c>
+      <c r="H86" t="s">
+        <v>619</v>
+      </c>
+      <c r="I86">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s">
+        <v>620</v>
+      </c>
+      <c r="K86" t="s">
+        <v>621</v>
+      </c>
+      <c r="L86" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>591</v>
+      </c>
+      <c r="B87" t="s">
+        <v>557</v>
+      </c>
+      <c r="C87" t="s">
+        <v>623</v>
+      </c>
+      <c r="D87" t="s">
+        <v>624</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" t="s">
+        <v>468</v>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+      <c r="H87" t="s">
+        <v>625</v>
+      </c>
+      <c r="I87">
+        <v>75</v>
+      </c>
+      <c r="J87" t="s">
+        <v>626</v>
+      </c>
+      <c r="K87" t="s">
+        <v>79</v>
+      </c>
+      <c r="L87" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5504,7 +5802,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>627</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5513,16 +5811,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>592</v>
+        <v>628</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>593</v>
+        <v>629</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>594</v>
+        <v>630</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>595</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5536,13 +5834,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>596</v>
+        <v>632</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>597</v>
+        <v>633</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>598</v>
+        <v>634</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -5570,7 +5868,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5585,7 +5883,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>603</v>
+        <v>639</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5595,31 +5893,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>605</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>606</v>
+        <v>642</v>
       </c>
       <c r="B4">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>607</v>
+        <v>643</v>
       </c>
       <c r="B5" t="s">
-        <v>608</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>609</v>
+        <v>645</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -5627,7 +5925,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -5635,23 +5933,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>611</v>
+        <v>647</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>612</v>
+        <v>648</v>
       </c>
       <c r="B9">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>613</v>
+        <v>649</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -5659,15 +5957,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>614</v>
+        <v>650</v>
       </c>
       <c r="B11" t="s">
-        <v>556</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>615</v>
+        <v>651</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -5677,15 +5975,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>616</v>
+        <v>652</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>617</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>618</v>
+        <v>654</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -5693,23 +5991,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="B17" s="5">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>620</v>
+        <v>656</v>
       </c>
       <c r="B18" s="5">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>621</v>
+        <v>657</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -5717,7 +6015,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5725,7 +6023,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5733,7 +6031,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5741,7 +6039,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5749,7 +6047,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>626</v>
+        <v>662</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5757,7 +6055,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>627</v>
+        <v>663</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5765,7 +6063,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>628</v>
+        <v>664</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -5777,7 +6075,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -5795,7 +6093,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>630</v>
+        <v>666</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -6950,25 +7248,25 @@
         <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>592</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>593</v>
       </c>
       <c r="E74" t="s">
-        <v>75</v>
+        <v>595</v>
       </c>
       <c r="F74" t="s">
-        <v>76</v>
+        <v>596</v>
       </c>
       <c r="G74">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H74" t="s">
-        <v>77</v>
+        <v>597</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -6976,25 +7274,25 @@
         <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>609</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="E75" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="G75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H75" t="s">
-        <v>84</v>
+        <v>612</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -7005,22 +7303,22 @@
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E76" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G76">
         <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7031,22 +7329,22 @@
         <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G77">
         <v>8</v>
       </c>
       <c r="H77" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7057,22 +7355,22 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F78" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7083,22 +7381,22 @@
         <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7109,22 +7407,22 @@
         <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D80" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E80" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7135,22 +7433,22 @@
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E81" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F81" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7158,25 +7456,25 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D82" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E82" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F82" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -7184,25 +7482,25 @@
         <v>54</v>
       </c>
       <c r="B83" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E83" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F83" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -7213,22 +7511,22 @@
         <v>159</v>
       </c>
       <c r="C84" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D84" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E84" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F84" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -7239,22 +7537,22 @@
         <v>159</v>
       </c>
       <c r="C85" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -7265,22 +7563,22 @@
         <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F86" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -7291,22 +7589,22 @@
         <v>159</v>
       </c>
       <c r="C87" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D87" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7317,22 +7615,22 @@
         <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D88" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -7343,22 +7641,22 @@
         <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D89" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E89" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F89" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -7369,22 +7667,22 @@
         <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D90" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -7395,22 +7693,22 @@
         <v>159</v>
       </c>
       <c r="C91" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D91" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E91" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7421,22 +7719,22 @@
         <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D92" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E92" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F92" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7444,25 +7742,25 @@
         <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C93" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E93" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7470,25 +7768,25 @@
         <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D94" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E94" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F94" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -7499,22 +7797,22 @@
         <v>284</v>
       </c>
       <c r="C95" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D95" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E95" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F95" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -7525,22 +7823,22 @@
         <v>284</v>
       </c>
       <c r="C96" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D96" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E96" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F96" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -7551,22 +7849,22 @@
         <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D97" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E97" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F97" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7577,22 +7875,22 @@
         <v>284</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D98" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E98" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F98" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7600,25 +7898,25 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C99" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D99" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E99" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F99" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -7626,25 +7924,25 @@
         <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C100" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D100" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E100" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F100" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -7655,22 +7953,22 @@
         <v>402</v>
       </c>
       <c r="C101" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D101" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E101" t="s">
         <v>66</v>
       </c>
       <c r="F101" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -7681,22 +7979,22 @@
         <v>402</v>
       </c>
       <c r="C102" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D102" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E102" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F102" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -7704,25 +8002,25 @@
         <v>74</v>
       </c>
       <c r="B103" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C103" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D103" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E103" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F103" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -7730,25 +8028,25 @@
         <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C104" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D104" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -7759,22 +8057,22 @@
         <v>473</v>
       </c>
       <c r="C105" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D105" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E105" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F105" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -7785,22 +8083,22 @@
         <v>473</v>
       </c>
       <c r="C106" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D106" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E106" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F106" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -7811,22 +8109,22 @@
         <v>473</v>
       </c>
       <c r="C107" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D107" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F107" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -7834,25 +8132,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C108" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D108" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E108" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F108" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -7860,25 +8158,25 @@
         <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C109" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D109" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E109" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -7886,24 +8184,154 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
+        <v>556</v>
+      </c>
+      <c r="C110" t="s">
+        <v>578</v>
+      </c>
+      <c r="D110" t="s">
+        <v>579</v>
+      </c>
+      <c r="E110" t="s">
+        <v>66</v>
+      </c>
+      <c r="F110" t="s">
+        <v>581</v>
+      </c>
+      <c r="G110">
+        <v>8</v>
+      </c>
+      <c r="H110" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>82</v>
+      </c>
+      <c r="B111" t="s">
+        <v>556</v>
+      </c>
+      <c r="C111" t="s">
+        <v>584</v>
+      </c>
+      <c r="D111" t="s">
+        <v>585</v>
+      </c>
+      <c r="E111" t="s">
+        <v>587</v>
+      </c>
+      <c r="F111" t="s">
+        <v>588</v>
+      </c>
+      <c r="G111">
+        <v>8</v>
+      </c>
+      <c r="H111" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>83</v>
+      </c>
+      <c r="B112" t="s">
+        <v>591</v>
+      </c>
+      <c r="C112" t="s">
+        <v>601</v>
+      </c>
+      <c r="D112" t="s">
+        <v>602</v>
+      </c>
+      <c r="E112" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" t="s">
+        <v>604</v>
+      </c>
+      <c r="G112">
+        <v>8</v>
+      </c>
+      <c r="H112" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>84</v>
+      </c>
+      <c r="B113" t="s">
+        <v>591</v>
+      </c>
+      <c r="C113" t="s">
+        <v>616</v>
+      </c>
+      <c r="D113" t="s">
+        <v>610</v>
+      </c>
+      <c r="E113" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113" t="s">
+        <v>618</v>
+      </c>
+      <c r="G113">
+        <v>8</v>
+      </c>
+      <c r="H113" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>85</v>
+      </c>
+      <c r="B114" t="s">
+        <v>591</v>
+      </c>
+      <c r="C114" t="s">
+        <v>557</v>
+      </c>
+      <c r="D114" t="s">
+        <v>623</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" t="s">
+        <v>468</v>
+      </c>
+      <c r="G114">
+        <v>8</v>
+      </c>
+      <c r="H114" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>86</v>
+      </c>
+      <c r="B115" t="s">
         <v>159</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C115" t="s">
         <v>271</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D115" t="s">
         <v>272</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E115" t="s">
         <v>75</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F115" t="s">
         <v>274</v>
       </c>
-      <c r="G110">
+      <c r="G115">
         <v>7</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H115" t="s">
         <v>275</v>
       </c>
     </row>
@@ -7920,7 +8348,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7937,10 +8365,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>599</v>
+        <v>635</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>600</v>
+        <v>636</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -7967,12 +8395,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>601</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -8007,7 +8435,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -8042,7 +8470,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -8077,7 +8505,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -8112,7 +8540,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -8147,7 +8575,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -8182,7 +8610,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -8217,7 +8645,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -8252,7 +8680,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -8287,7 +8715,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -8322,7 +8750,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -8357,7 +8785,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -8392,7 +8820,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -8427,7 +8855,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -8462,7 +8890,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -8497,7 +8925,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -8532,7 +8960,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -8567,7 +8995,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -8602,7 +9030,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -8637,7 +9065,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -8672,7 +9100,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -8707,7 +9135,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B23">
         <v>89</v>
@@ -8742,7 +9170,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -8777,7 +9205,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -8812,252 +9240,252 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B26">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>592</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>593</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>595</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>596</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>598</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
+        <v>599</v>
       </c>
       <c r="J26" t="s">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>594</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B27">
         <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
         <v>36</v>
       </c>
       <c r="I27" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J27" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B28">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H28" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J28" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B29">
         <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E29" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H29" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I29" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J29" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K29" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B30">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>449</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>438</v>
       </c>
       <c r="H30" t="s">
-        <v>188</v>
+        <v>452</v>
       </c>
       <c r="I30" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s">
-        <v>186</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B31">
         <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E31" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F31" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G31" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H31" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I31" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J31" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K31" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B32">
         <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E32" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G32" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H32" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I32" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K32" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B33">
         <v>87</v>
@@ -9069,7 +9497,7 @@
         <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F33" t="s">
         <v>66</v>
@@ -9087,152 +9515,152 @@
         <v>79</v>
       </c>
       <c r="K33" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B34">
         <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F34" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H34" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I34" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B35">
         <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D35" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F35" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G35" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H35" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I35" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J35" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K35" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B36">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>556</v>
       </c>
       <c r="D36" t="s">
-        <v>369</v>
+        <v>570</v>
       </c>
       <c r="E36" t="s">
-        <v>370</v>
+        <v>571</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>372</v>
+        <v>573</v>
       </c>
       <c r="H36" t="s">
-        <v>374</v>
+        <v>575</v>
       </c>
       <c r="I36" t="s">
-        <v>375</v>
+        <v>576</v>
       </c>
       <c r="J36" t="s">
-        <v>376</v>
+        <v>577</v>
       </c>
       <c r="K36" t="s">
-        <v>371</v>
+        <v>572</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B37">
         <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E37" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H37" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I37" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J37" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K37" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B38">
         <v>86</v>
@@ -9241,728 +9669,868 @@
         <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I38" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J38" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K38" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B39">
         <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D39" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E39" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F39" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H39" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I39" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J39" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K39" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B40">
         <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D40" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E40" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G40" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H40" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I40" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J40" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K40" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B41">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>556</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>557</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>468</v>
       </c>
       <c r="H41" t="s">
-        <v>60</v>
+        <v>561</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
+        <v>562</v>
       </c>
       <c r="J41" t="s">
-        <v>62</v>
+        <v>563</v>
       </c>
       <c r="K41" t="s">
-        <v>57</v>
+        <v>559</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B42">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>609</v>
       </c>
       <c r="E42" t="s">
-        <v>89</v>
+        <v>610</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>604</v>
       </c>
       <c r="H42" t="s">
-        <v>133</v>
+        <v>613</v>
       </c>
       <c r="I42" t="s">
-        <v>134</v>
+        <v>614</v>
       </c>
       <c r="J42" t="s">
-        <v>135</v>
+        <v>615</v>
       </c>
       <c r="K42" t="s">
-        <v>129</v>
+        <v>611</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B43">
         <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E43" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F43" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H43" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I43" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K43" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B44">
         <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G44" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H44" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I44" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J44" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K44" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B45">
         <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D45" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E45" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F45" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G45" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H45" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I45" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J45" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K45" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B46">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>403</v>
       </c>
       <c r="F46" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>148</v>
+        <v>405</v>
       </c>
       <c r="H46" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="I46" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
       <c r="J46" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
       <c r="K46" t="s">
-        <v>146</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B47">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D47" t="s">
-        <v>144</v>
+        <v>474</v>
       </c>
       <c r="E47" t="s">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="F47" t="s">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="G47" t="s">
-        <v>397</v>
+        <v>478</v>
       </c>
       <c r="H47" t="s">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="I47" t="s">
-        <v>400</v>
+        <v>481</v>
       </c>
       <c r="J47" t="s">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K47" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B48">
         <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>411</v>
+        <v>145</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G48" t="s">
-        <v>413</v>
+        <v>148</v>
       </c>
       <c r="H48" t="s">
-        <v>415</v>
+        <v>150</v>
       </c>
       <c r="I48" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="J48" t="s">
-        <v>417</v>
+        <v>152</v>
       </c>
       <c r="K48" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B49">
         <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E49" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="F49" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="G49" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="H49" t="s">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="I49" t="s">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="J49" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="K49" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B50">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D50" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E50" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="F50" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="H50" t="s">
-        <v>366</v>
+        <v>415</v>
       </c>
       <c r="I50" t="s">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="J50" t="s">
-        <v>368</v>
+        <v>417</v>
       </c>
       <c r="K50" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B51">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C51" t="s">
         <v>473</v>
       </c>
       <c r="D51" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E51" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="F51" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="G51" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="H51" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="I51" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="J51" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="K51" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B52">
         <v>83</v>
       </c>
       <c r="C52" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E52" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F52" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G52" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H52" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I52" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J52" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K52" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B53">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D53" t="s">
-        <v>227</v>
+        <v>491</v>
       </c>
       <c r="E53" t="s">
-        <v>228</v>
+        <v>492</v>
       </c>
       <c r="F53" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s">
-        <v>231</v>
+        <v>494</v>
       </c>
       <c r="H53" t="s">
-        <v>233</v>
+        <v>496</v>
       </c>
       <c r="I53" t="s">
-        <v>234</v>
+        <v>497</v>
       </c>
       <c r="J53" t="s">
-        <v>235</v>
+        <v>498</v>
       </c>
       <c r="K53" t="s">
-        <v>229</v>
+        <v>493</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B54">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D54" t="s">
-        <v>266</v>
+        <v>532</v>
       </c>
       <c r="E54" t="s">
-        <v>267</v>
+        <v>533</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>536</v>
       </c>
       <c r="H54" t="s">
-        <v>270</v>
+        <v>538</v>
       </c>
       <c r="I54" t="s">
-        <v>79</v>
+        <v>539</v>
       </c>
       <c r="J54" t="s">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="K54" t="s">
-        <v>268</v>
+        <v>534</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B55">
         <v>82</v>
       </c>
       <c r="C55" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D55" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="E55" t="s">
-        <v>339</v>
+        <v>228</v>
       </c>
       <c r="F55" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="G55" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="H55" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="I55" t="s">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="J55" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="K55" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B56">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="H56" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="I56" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s">
-        <v>82</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B57">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C57" t="s">
         <v>284</v>
       </c>
       <c r="D57" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E57" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="F57" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="G57" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="H57" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="I57" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="J57" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="K57" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>638</v>
+      </c>
+      <c r="B58">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s">
+        <v>591</v>
+      </c>
+      <c r="D58" t="s">
+        <v>601</v>
+      </c>
+      <c r="E58" t="s">
         <v>602</v>
       </c>
-      <c r="B58">
+      <c r="F58" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s">
+        <v>604</v>
+      </c>
+      <c r="H58" t="s">
+        <v>606</v>
+      </c>
+      <c r="I58" t="s">
+        <v>607</v>
+      </c>
+      <c r="J58" t="s">
+        <v>608</v>
+      </c>
+      <c r="K58" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>638</v>
+      </c>
+      <c r="B59">
         <v>81</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>85</v>
+      </c>
+      <c r="I59" t="s">
+        <v>86</v>
+      </c>
+      <c r="J59" t="s">
+        <v>87</v>
+      </c>
+      <c r="K59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>638</v>
+      </c>
+      <c r="B60">
+        <v>81</v>
+      </c>
+      <c r="C60" t="s">
+        <v>284</v>
+      </c>
+      <c r="D60" t="s">
+        <v>377</v>
+      </c>
+      <c r="E60" t="s">
+        <v>378</v>
+      </c>
+      <c r="F60" t="s">
+        <v>380</v>
+      </c>
+      <c r="G60" t="s">
+        <v>381</v>
+      </c>
+      <c r="H60" t="s">
+        <v>383</v>
+      </c>
+      <c r="I60" t="s">
+        <v>384</v>
+      </c>
+      <c r="J60" t="s">
+        <v>385</v>
+      </c>
+      <c r="K60" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>638</v>
+      </c>
+      <c r="B61">
+        <v>81</v>
+      </c>
+      <c r="C61" t="s">
         <v>473</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D61" t="s">
         <v>499</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E61" t="s">
         <v>500</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F61" t="s">
         <v>502</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G61" t="s">
         <v>503</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H61" t="s">
         <v>505</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I61" t="s">
         <v>506</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J61" t="s">
         <v>507</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K61" t="s">
         <v>501</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>638</v>
+      </c>
+      <c r="B62">
+        <v>81</v>
+      </c>
+      <c r="C62" t="s">
+        <v>591</v>
+      </c>
+      <c r="D62" t="s">
+        <v>616</v>
+      </c>
+      <c r="E62" t="s">
+        <v>610</v>
+      </c>
+      <c r="F62" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" t="s">
+        <v>618</v>
+      </c>
+      <c r="H62" t="s">
+        <v>620</v>
+      </c>
+      <c r="I62" t="s">
+        <v>621</v>
+      </c>
+      <c r="J62" t="s">
+        <v>622</v>
+      </c>
+      <c r="K62" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="737">
   <si>
     <t>日期</t>
   </si>
@@ -1897,6 +1897,216 @@
     <t>研究70/技能58/学历92/行业100/企业92</t>
   </si>
   <si>
+    <t>艾柯医疗（艾柯医疗器械（北京）股份有限公司）</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（神经介入/密网支架）</t>
+  </si>
+  <si>
+    <t>专注神经介入创新医疗器械研发生产，产品覆盖出血/缺血性卒中诊疗及通路产品，核心产品Lattice血流导向密网支架。岗位负责神经介入创新器械及支架类产品的研发、结构设计与工艺开发，材料选型。北京及中美双研发中心。</t>
+  </si>
+  <si>
+    <t>https://www.accumedical.com.cn</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|神经介入+血流导向密网支架研发岗，支架结构设计与工艺开发方向+技能高度匹配</t>
+  </si>
+  <si>
+    <t>研究85/技能80/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>艾柯核心产品为Lattice血流导向密网支架，直接对应候选人血管支架设计与介入方向；岗位覆盖结构设计、工艺开发和材料选型，与硕士支架研发技能完全对口，北京工作符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出神经介入/支架结构设计与有限元力学分析项目；详述材料选型与工艺开发经历；补充动物实验与生物相容性评价经验以增强差异化。</t>
+  </si>
+  <si>
+    <t>美敦力（Medtronic）</t>
+  </si>
+  <si>
+    <t>2026校园招聘（心血管/介入研发类）</t>
+  </si>
+  <si>
+    <t>面向2026届应届生，医疗行业全球龙头。美敦力心血管/介入业务含冠状动脉支架、瓣膜等血管介入产品线，研发类岗位偏好生物医学工程、材料学、化学等相关专业。</t>
+  </si>
+  <si>
+    <t>https://job.ucas.ac.cn/f/recruitmentinfo/show?recruitmentId=65d7fa3426584ab19129b2037f99560a</t>
+  </si>
+  <si>
+    <t>智能匹配86分【校园招聘】|强烈推荐|心血管/介入产品线研发校招，全球龙头+应届可投，方向相关</t>
+  </si>
+  <si>
+    <t>研究85/技能74/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>美敦力为全球医疗器械龙头，心血管/介入研发校招对口候选人血管支架研究方向与生物医学工程背景；顶尖平台+应届生身份完全匹配，上海符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出血管支架研究方向及课程科研项目；强调生物相容性评价与支架设计技能；量化科研产出，展示独立研发与跨学科（材料+医学）协同能力。</t>
+  </si>
+  <si>
+    <t>瑛泰医疗（上海瑛泰医疗器械股份有限公司）</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（血管支架/球囊）</t>
+  </si>
+  <si>
+    <t>港股上市的心内介入器械企业，具自主模具/设备/灭菌完整产业链，通过ISO13485/CE/FDA认证。招聘血管支架研发工程师及球囊研发工程师，经验要求不限，本科及以上，薪资约20-30K。</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|心内介入企业血管支架/球囊研发岗，经验不限可投，方向匹配</t>
+  </si>
+  <si>
+    <t>研究82/技能72/学历90/行业100/企业90</t>
+  </si>
+  <si>
+    <t>瑛泰为港股上市心内介入器械企业，血管支架/球囊研发岗与候选人支架研究方向对口，经验不限给应届生机会，上海符合城市偏好，上市公司平台稳定。</t>
+  </si>
+  <si>
+    <t>突出血管支架/球囊研发项目与结构设计技能；强调材料学与ISO 10993生物相容性认知；量化产品开发与测试结果。</t>
+  </si>
+  <si>
+    <t>深圳开立生物医疗科技股份有限公司</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（医疗器械技术/研发）</t>
+  </si>
+  <si>
+    <t>面向2026届应届生，深圳总部。主营医用超声、内窥镜等医疗器械研发制造，涉及生物医学工程、材料、机械/电子方向技术研发岗，属医疗器械研发赛道。</t>
+  </si>
+  <si>
+    <t>https://job.ucas.ac.cn/f/recruitmentinfo/show?recruitmentId=6b6886faf6f146d88b8458324145b0fd</t>
+  </si>
+  <si>
+    <t>智能匹配78分【校园招聘】|值得考虑|医疗器械研发校招，方向泛但属医疗器械研发赛道+应届可投</t>
+  </si>
+  <si>
+    <t>研究70/技能65/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>开立为上市医疗器械企业，2026校招研发岗对生物医学工程/材料专业开放，应届生友好，深圳符合城市偏好，可作为医疗器械行业进入的备选平台。</t>
+  </si>
+  <si>
+    <t>强调生物医学工程背景与科研项目；突出材料学与器械研发能力；展示可迁移的研发实验技能与成果。</t>
+  </si>
+  <si>
+    <t>东软医疗系统股份有限公司</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（医疗设备研发）</t>
+  </si>
+  <si>
+    <t>面向2026届应届生。医疗影像设备整机与核心部件研发制造，技术研发方向涉及物理、电子、算法、材料等，属医疗器械研发赛道。</t>
+  </si>
+  <si>
+    <t>沈阳</t>
+  </si>
+  <si>
+    <t>https://job.ucas.ac.cn/f/recruitmentinfo/show?recruitmentId=8a1df2dc040648c2bd7bbd35bf99a20c</t>
+  </si>
+  <si>
+    <t>智能匹配78分【校园招聘】|值得考虑|医疗器械设备研发校招，应届可投，方向泛属医疗器械赛道</t>
+  </si>
+  <si>
+    <t>东软为上市医疗设备龙头，2026校招研发岗对材料等专业开放，应届生友好，可作为医疗器械行业备选平台（候选人愿意异地就业）。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程与材料技能；强调跨学科研发与项目成果；展示适应能力与异地就业意愿。</t>
+  </si>
+  <si>
+    <t>玄宇医疗器械（苏州）有限公司</t>
+  </si>
+  <si>
+    <t>介入器械研发工程师</t>
+  </si>
+  <si>
+    <t>专业从事心血管微创介入治疗器械研发生产的高新技术企业，布局房颤、静脉曲张等领域创新医疗器械（脉冲电场消融PFA系统等）。招聘介入器械研发类岗位。</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|心血管微创介入器械研发，方向相关（介入）</t>
+  </si>
+  <si>
+    <t>研究78/技能65/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>玄宇专注心血管微创介入器械研发，涉及介入级研发，与候选人介入器械方向相关；苏州符合城市偏好，科创企业平台，应届生可投。</t>
+  </si>
+  <si>
+    <t>突出介入医疗器械研发背景与材料学技能；展示结构设计/仿真能力以匹配介入器械研发。</t>
+  </si>
+  <si>
+    <t>深圳医学科学院（范潇课题组）</t>
+  </si>
+  <si>
+    <t>博士后/助理研究员（生物医用材料）</t>
+  </si>
+  <si>
+    <t>招聘助理研究员、博士后及科研助理。研究方向涉及生物医用材料与组织修复，与生物医用材料背景契合。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=CXz</t>
+  </si>
+  <si>
+    <t>智能匹配76分【博士后】|值得考虑|生物医用材料与组织修复研究方向，方向相关</t>
+  </si>
+  <si>
+    <t>研究75/技能68/学历82/行业80/企业90</t>
+  </si>
+  <si>
+    <t>深圳医学科学院为新兴科研院所，博士后岗位涉及生物医用材料，与候选人材料学方向相关，深圳符合城市偏好，科研机构平台良好，为学术发展备选。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料研究与表征技能；强调发表成果与独立科研能力；补充材料学深度项目。</t>
+  </si>
+  <si>
+    <t>北京大学（跨学部生物医学工程系）</t>
+  </si>
+  <si>
+    <t>博士后（生物医学工程/生物医用材料）</t>
+  </si>
+  <si>
+    <t>常年招聘博士后，方向为生物医学工程，含生物医学材料、器械与交叉研究。面向生物医学工程、材料等相关专业博士毕业生，团队提供基础年薪及科研补贴。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=PKU</t>
+  </si>
+  <si>
+    <t>智能匹配74分【博士后】|值得考虑|北京大学生物医学工程博后，方向泛属生物医学/材料</t>
+  </si>
+  <si>
+    <t>研究72/技能65/学历82/行业78/企业95</t>
+  </si>
+  <si>
+    <t>北京大学为顶尖高校科研平台，博士后方向涉及生物医用材料与器械，与候选人材料学及生物医学工程背景相关，北京符合城市偏好，可作为学术发展备选。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料研究深度与一作成果；强调独立科研与实验技能；展示与介入/支架交叉的潜力。</t>
+  </si>
+  <si>
+    <t>深圳湾实验室（生物医学工程研究所 郭腾飞课题组）</t>
+  </si>
+  <si>
+    <t>博士后/助理研究员/研究助理</t>
+  </si>
+  <si>
+    <t>深圳湾实验室生物医学工程研究所郭腾飞课题组招聘助理研究员、博士后（多名）及研究助理。面向生物医学工程及相关专业，研究助理可放宽至硕士。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=SWLAB</t>
+  </si>
+  <si>
+    <t>智能匹配73分【博士后】|值得考虑|深圳湾实验室生物医学工程博后，方向泛属生物医学/器械</t>
+  </si>
+  <si>
+    <t>研究70/技能65/学历82/行业78/企业90</t>
+  </si>
+  <si>
+    <t>深圳湾实验室为国家级科研平台，生物医学工程研究所方向贴合候选人生物医学工程背景，深圳符合城市偏好，可作科研岗位备选。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程背景与科研能力；强调生物医用材料/器械交叉研究与成果。</t>
+  </si>
+  <si>
     <t>投递日期</t>
   </si>
   <si>
@@ -1948,7 +2158,7 @@
     <t>平均匹配度</t>
   </si>
   <si>
-    <t>8.6</t>
+    <t>8.5</t>
   </si>
   <si>
     <t>最高匹配度</t>
@@ -2449,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5769,6 +5979,348 @@
       </c>
       <c r="L87" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>591</v>
+      </c>
+      <c r="B88" t="s">
+        <v>627</v>
+      </c>
+      <c r="C88" t="s">
+        <v>628</v>
+      </c>
+      <c r="D88" t="s">
+        <v>629</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>630</v>
+      </c>
+      <c r="G88">
+        <v>9</v>
+      </c>
+      <c r="H88" t="s">
+        <v>631</v>
+      </c>
+      <c r="I88">
+        <v>86</v>
+      </c>
+      <c r="J88" t="s">
+        <v>632</v>
+      </c>
+      <c r="K88" t="s">
+        <v>633</v>
+      </c>
+      <c r="L88" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>591</v>
+      </c>
+      <c r="B89" t="s">
+        <v>635</v>
+      </c>
+      <c r="C89" t="s">
+        <v>636</v>
+      </c>
+      <c r="D89" t="s">
+        <v>637</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" t="s">
+        <v>638</v>
+      </c>
+      <c r="G89">
+        <v>9</v>
+      </c>
+      <c r="H89" t="s">
+        <v>639</v>
+      </c>
+      <c r="I89">
+        <v>86</v>
+      </c>
+      <c r="J89" t="s">
+        <v>640</v>
+      </c>
+      <c r="K89" t="s">
+        <v>641</v>
+      </c>
+      <c r="L89" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>591</v>
+      </c>
+      <c r="B90" t="s">
+        <v>643</v>
+      </c>
+      <c r="C90" t="s">
+        <v>644</v>
+      </c>
+      <c r="D90" t="s">
+        <v>645</v>
+      </c>
+      <c r="E90" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" t="s">
+        <v>618</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90" t="s">
+        <v>646</v>
+      </c>
+      <c r="I90">
+        <v>83</v>
+      </c>
+      <c r="J90" t="s">
+        <v>647</v>
+      </c>
+      <c r="K90" t="s">
+        <v>648</v>
+      </c>
+      <c r="L90" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>591</v>
+      </c>
+      <c r="B91" t="s">
+        <v>650</v>
+      </c>
+      <c r="C91" t="s">
+        <v>651</v>
+      </c>
+      <c r="D91" t="s">
+        <v>652</v>
+      </c>
+      <c r="E91" t="s">
+        <v>66</v>
+      </c>
+      <c r="F91" t="s">
+        <v>653</v>
+      </c>
+      <c r="G91">
+        <v>8</v>
+      </c>
+      <c r="H91" t="s">
+        <v>654</v>
+      </c>
+      <c r="I91">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s">
+        <v>655</v>
+      </c>
+      <c r="K91" t="s">
+        <v>656</v>
+      </c>
+      <c r="L91" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>591</v>
+      </c>
+      <c r="B92" t="s">
+        <v>658</v>
+      </c>
+      <c r="C92" t="s">
+        <v>659</v>
+      </c>
+      <c r="D92" t="s">
+        <v>660</v>
+      </c>
+      <c r="E92" t="s">
+        <v>661</v>
+      </c>
+      <c r="F92" t="s">
+        <v>662</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92" t="s">
+        <v>663</v>
+      </c>
+      <c r="I92">
+        <v>78</v>
+      </c>
+      <c r="J92" t="s">
+        <v>655</v>
+      </c>
+      <c r="K92" t="s">
+        <v>664</v>
+      </c>
+      <c r="L92" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>591</v>
+      </c>
+      <c r="B93" t="s">
+        <v>666</v>
+      </c>
+      <c r="C93" t="s">
+        <v>667</v>
+      </c>
+      <c r="D93" t="s">
+        <v>668</v>
+      </c>
+      <c r="E93" t="s">
+        <v>75</v>
+      </c>
+      <c r="F93" t="s">
+        <v>604</v>
+      </c>
+      <c r="G93">
+        <v>8</v>
+      </c>
+      <c r="H93" t="s">
+        <v>669</v>
+      </c>
+      <c r="I93">
+        <v>79</v>
+      </c>
+      <c r="J93" t="s">
+        <v>670</v>
+      </c>
+      <c r="K93" t="s">
+        <v>671</v>
+      </c>
+      <c r="L93" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>591</v>
+      </c>
+      <c r="B94" t="s">
+        <v>673</v>
+      </c>
+      <c r="C94" t="s">
+        <v>674</v>
+      </c>
+      <c r="D94" t="s">
+        <v>675</v>
+      </c>
+      <c r="E94" t="s">
+        <v>66</v>
+      </c>
+      <c r="F94" t="s">
+        <v>676</v>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+      <c r="H94" t="s">
+        <v>677</v>
+      </c>
+      <c r="I94">
+        <v>76</v>
+      </c>
+      <c r="J94" t="s">
+        <v>678</v>
+      </c>
+      <c r="K94" t="s">
+        <v>679</v>
+      </c>
+      <c r="L94" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>591</v>
+      </c>
+      <c r="B95" t="s">
+        <v>681</v>
+      </c>
+      <c r="C95" t="s">
+        <v>682</v>
+      </c>
+      <c r="D95" t="s">
+        <v>683</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>684</v>
+      </c>
+      <c r="G95">
+        <v>7</v>
+      </c>
+      <c r="H95" t="s">
+        <v>685</v>
+      </c>
+      <c r="I95">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s">
+        <v>686</v>
+      </c>
+      <c r="K95" t="s">
+        <v>687</v>
+      </c>
+      <c r="L95" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>591</v>
+      </c>
+      <c r="B96" t="s">
+        <v>689</v>
+      </c>
+      <c r="C96" t="s">
+        <v>690</v>
+      </c>
+      <c r="D96" t="s">
+        <v>691</v>
+      </c>
+      <c r="E96" t="s">
+        <v>66</v>
+      </c>
+      <c r="F96" t="s">
+        <v>692</v>
+      </c>
+      <c r="G96">
+        <v>7</v>
+      </c>
+      <c r="H96" t="s">
+        <v>693</v>
+      </c>
+      <c r="I96">
+        <v>73</v>
+      </c>
+      <c r="J96" t="s">
+        <v>694</v>
+      </c>
+      <c r="K96" t="s">
+        <v>695</v>
+      </c>
+      <c r="L96" t="s">
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -5802,7 +6354,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5811,16 +6363,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>628</v>
+        <v>698</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>629</v>
+        <v>699</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>631</v>
+        <v>701</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5834,13 +6386,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>632</v>
+        <v>702</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>634</v>
+        <v>704</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -5868,7 +6420,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5883,7 +6435,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>639</v>
+        <v>709</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5893,31 +6445,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>640</v>
+        <v>710</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>641</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>642</v>
+        <v>712</v>
       </c>
       <c r="B4">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>643</v>
+        <v>713</v>
       </c>
       <c r="B5" t="s">
-        <v>644</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -5925,7 +6477,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>646</v>
+        <v>716</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -5933,31 +6485,31 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>647</v>
+        <v>717</v>
       </c>
       <c r="B8">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>648</v>
+        <v>718</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>649</v>
+        <v>719</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>650</v>
+        <v>720</v>
       </c>
       <c r="B11" t="s">
         <v>591</v>
@@ -5965,7 +6517,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>651</v>
+        <v>721</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -5975,15 +6527,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>653</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>654</v>
+        <v>724</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -5991,31 +6543,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>725</v>
       </c>
       <c r="B17" s="5">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>726</v>
       </c>
       <c r="B18" s="5">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>657</v>
+        <v>727</v>
       </c>
       <c r="B19" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>658</v>
+        <v>728</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6023,7 +6575,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>659</v>
+        <v>729</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6031,7 +6583,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>660</v>
+        <v>730</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6039,7 +6591,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>661</v>
+        <v>731</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6047,7 +6599,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>662</v>
+        <v>732</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6055,7 +6607,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>663</v>
+        <v>733</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6063,7 +6615,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -6075,7 +6627,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>665</v>
+        <v>735</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -6093,7 +6645,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>666</v>
+        <v>736</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -7300,25 +7852,25 @@
         <v>47</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>627</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>628</v>
       </c>
       <c r="E76" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F76" t="s">
-        <v>76</v>
+        <v>630</v>
       </c>
       <c r="G76">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H76" t="s">
-        <v>77</v>
+        <v>631</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7326,25 +7878,25 @@
         <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>635</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>636</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>83</v>
+        <v>638</v>
       </c>
       <c r="G77">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H77" t="s">
-        <v>84</v>
+        <v>639</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7355,22 +7907,22 @@
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F78" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7381,22 +7933,22 @@
         <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E79" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7407,22 +7959,22 @@
         <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D80" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F80" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7433,22 +7985,22 @@
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7459,22 +8011,22 @@
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E82" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -7485,22 +8037,22 @@
         <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F83" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -7508,25 +8060,25 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D84" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F84" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -7534,25 +8086,25 @@
         <v>56</v>
       </c>
       <c r="B85" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E85" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -7563,22 +8115,22 @@
         <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D86" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E86" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F86" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -7589,22 +8141,22 @@
         <v>159</v>
       </c>
       <c r="C87" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E87" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F87" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7615,22 +8167,22 @@
         <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F88" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -7641,22 +8193,22 @@
         <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D89" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F89" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -7667,22 +8219,22 @@
         <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D90" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E90" t="s">
         <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -7693,22 +8245,22 @@
         <v>159</v>
       </c>
       <c r="C91" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D91" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E91" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7719,22 +8271,22 @@
         <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D92" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E92" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7745,22 +8297,22 @@
         <v>159</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D93" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E93" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7771,22 +8323,22 @@
         <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D94" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E94" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F94" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -7794,25 +8346,25 @@
         <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C95" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D95" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E95" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -7820,25 +8372,25 @@
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D96" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E96" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F96" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -7849,22 +8401,22 @@
         <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D97" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E97" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F97" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7875,22 +8427,22 @@
         <v>284</v>
       </c>
       <c r="C98" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E98" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F98" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7901,22 +8453,22 @@
         <v>284</v>
       </c>
       <c r="C99" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D99" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E99" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F99" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -7927,22 +8479,22 @@
         <v>284</v>
       </c>
       <c r="C100" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D100" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E100" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F100" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -7950,25 +8502,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C101" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D101" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E101" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F101" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -7976,25 +8528,25 @@
         <v>73</v>
       </c>
       <c r="B102" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C102" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D102" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E102" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F102" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -8005,22 +8557,22 @@
         <v>402</v>
       </c>
       <c r="C103" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D103" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E103" t="s">
         <v>66</v>
       </c>
       <c r="F103" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -8031,22 +8583,22 @@
         <v>402</v>
       </c>
       <c r="C104" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D104" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F104" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -8054,25 +8606,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C105" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E105" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F105" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -8080,25 +8632,25 @@
         <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C106" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D106" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E106" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F106" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -8109,22 +8661,22 @@
         <v>473</v>
       </c>
       <c r="C107" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D107" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E107" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F107" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -8135,22 +8687,22 @@
         <v>473</v>
       </c>
       <c r="C108" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D108" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E108" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F108" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -8161,22 +8713,22 @@
         <v>473</v>
       </c>
       <c r="C109" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D109" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F109" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -8184,25 +8736,25 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C110" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D110" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E110" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F110" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -8210,25 +8762,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C111" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D111" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E111" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -8236,25 +8788,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C112" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="D112" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="E112" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F112" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -8262,25 +8814,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C113" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D113" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F113" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -8291,22 +8843,22 @@
         <v>591</v>
       </c>
       <c r="C114" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D114" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E114" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F114" t="s">
-        <v>468</v>
+        <v>604</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -8314,25 +8866,259 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
+        <v>591</v>
+      </c>
+      <c r="C115" t="s">
+        <v>616</v>
+      </c>
+      <c r="D115" t="s">
+        <v>610</v>
+      </c>
+      <c r="E115" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" t="s">
+        <v>618</v>
+      </c>
+      <c r="G115">
+        <v>8</v>
+      </c>
+      <c r="H115" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>87</v>
+      </c>
+      <c r="B116" t="s">
+        <v>591</v>
+      </c>
+      <c r="C116" t="s">
+        <v>557</v>
+      </c>
+      <c r="D116" t="s">
+        <v>623</v>
+      </c>
+      <c r="E116" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" t="s">
+        <v>468</v>
+      </c>
+      <c r="G116">
+        <v>8</v>
+      </c>
+      <c r="H116" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>88</v>
+      </c>
+      <c r="B117" t="s">
+        <v>591</v>
+      </c>
+      <c r="C117" t="s">
+        <v>643</v>
+      </c>
+      <c r="D117" t="s">
+        <v>644</v>
+      </c>
+      <c r="E117" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" t="s">
+        <v>618</v>
+      </c>
+      <c r="G117">
+        <v>8</v>
+      </c>
+      <c r="H117" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>89</v>
+      </c>
+      <c r="B118" t="s">
+        <v>591</v>
+      </c>
+      <c r="C118" t="s">
+        <v>650</v>
+      </c>
+      <c r="D118" t="s">
+        <v>651</v>
+      </c>
+      <c r="E118" t="s">
+        <v>66</v>
+      </c>
+      <c r="F118" t="s">
+        <v>653</v>
+      </c>
+      <c r="G118">
+        <v>8</v>
+      </c>
+      <c r="H118" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>90</v>
+      </c>
+      <c r="B119" t="s">
+        <v>591</v>
+      </c>
+      <c r="C119" t="s">
+        <v>658</v>
+      </c>
+      <c r="D119" t="s">
+        <v>659</v>
+      </c>
+      <c r="E119" t="s">
+        <v>661</v>
+      </c>
+      <c r="F119" t="s">
+        <v>662</v>
+      </c>
+      <c r="G119">
+        <v>8</v>
+      </c>
+      <c r="H119" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>91</v>
+      </c>
+      <c r="B120" t="s">
+        <v>591</v>
+      </c>
+      <c r="C120" t="s">
+        <v>666</v>
+      </c>
+      <c r="D120" t="s">
+        <v>667</v>
+      </c>
+      <c r="E120" t="s">
+        <v>75</v>
+      </c>
+      <c r="F120" t="s">
+        <v>604</v>
+      </c>
+      <c r="G120">
+        <v>8</v>
+      </c>
+      <c r="H120" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>92</v>
+      </c>
+      <c r="B121" t="s">
+        <v>591</v>
+      </c>
+      <c r="C121" t="s">
+        <v>673</v>
+      </c>
+      <c r="D121" t="s">
+        <v>674</v>
+      </c>
+      <c r="E121" t="s">
+        <v>66</v>
+      </c>
+      <c r="F121" t="s">
+        <v>676</v>
+      </c>
+      <c r="G121">
+        <v>8</v>
+      </c>
+      <c r="H121" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>93</v>
+      </c>
+      <c r="B122" t="s">
         <v>159</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C122" t="s">
         <v>271</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D122" t="s">
         <v>272</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E122" t="s">
         <v>75</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F122" t="s">
         <v>274</v>
       </c>
-      <c r="G115">
+      <c r="G122">
         <v>7</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H122" t="s">
         <v>275</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>94</v>
+      </c>
+      <c r="B123" t="s">
+        <v>591</v>
+      </c>
+      <c r="C123" t="s">
+        <v>681</v>
+      </c>
+      <c r="D123" t="s">
+        <v>682</v>
+      </c>
+      <c r="E123" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" t="s">
+        <v>684</v>
+      </c>
+      <c r="G123">
+        <v>7</v>
+      </c>
+      <c r="H123" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>95</v>
+      </c>
+      <c r="B124" t="s">
+        <v>591</v>
+      </c>
+      <c r="C124" t="s">
+        <v>689</v>
+      </c>
+      <c r="D124" t="s">
+        <v>690</v>
+      </c>
+      <c r="E124" t="s">
+        <v>66</v>
+      </c>
+      <c r="F124" t="s">
+        <v>692</v>
+      </c>
+      <c r="G124">
+        <v>7</v>
+      </c>
+      <c r="H124" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -8348,7 +9134,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8365,10 +9151,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>635</v>
+        <v>705</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>636</v>
+        <v>706</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -8395,12 +9181,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>637</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -8435,7 +9221,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -8470,7 +9256,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -8505,7 +9291,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -8540,7 +9326,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -8575,7 +9361,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -8610,7 +9396,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -8645,7 +9431,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -8680,7 +9466,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -8715,7 +9501,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -8750,7 +9536,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -8785,7 +9571,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -8820,7 +9606,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -8855,7 +9641,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -8890,7 +9676,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -8925,7 +9711,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -8960,7 +9746,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -8995,7 +9781,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -9030,7 +9816,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -9065,7 +9851,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -9100,7 +9886,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -9135,7 +9921,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B23">
         <v>89</v>
@@ -9170,7 +9956,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -9205,7 +9991,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -9240,7 +10026,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -9275,7 +10061,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B27">
         <v>88</v>
@@ -9310,7 +10096,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B28">
         <v>88</v>
@@ -9345,7 +10131,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B29">
         <v>88</v>
@@ -9380,7 +10166,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B30">
         <v>88</v>
@@ -9415,7 +10201,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B31">
         <v>87</v>
@@ -9450,7 +10236,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B32">
         <v>87</v>
@@ -9485,7 +10271,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B33">
         <v>87</v>
@@ -9520,7 +10306,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B34">
         <v>87</v>
@@ -9555,7 +10341,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B35">
         <v>87</v>
@@ -9590,7 +10376,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B36">
         <v>87</v>
@@ -9625,7 +10411,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B37">
         <v>86</v>
@@ -9660,7 +10446,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B38">
         <v>86</v>
@@ -9695,7 +10481,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B39">
         <v>86</v>
@@ -9730,7 +10516,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B40">
         <v>86</v>
@@ -9765,7 +10551,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B41">
         <v>86</v>
@@ -9800,7 +10586,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B42">
         <v>86</v>
@@ -9835,701 +10621,806 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B43">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>627</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>628</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="I43" t="s">
-        <v>61</v>
+        <v>633</v>
       </c>
       <c r="J43" t="s">
-        <v>62</v>
+        <v>634</v>
       </c>
       <c r="K43" t="s">
-        <v>57</v>
+        <v>629</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>708</v>
+      </c>
+      <c r="B44">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>591</v>
+      </c>
+      <c r="D44" t="s">
+        <v>635</v>
+      </c>
+      <c r="E44" t="s">
+        <v>636</v>
+      </c>
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" t="s">
         <v>638</v>
       </c>
-      <c r="B44">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>89</v>
-      </c>
-      <c r="F44" t="s">
-        <v>130</v>
-      </c>
-      <c r="G44" t="s">
-        <v>131</v>
-      </c>
       <c r="H44" t="s">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="I44" t="s">
-        <v>134</v>
+        <v>641</v>
       </c>
       <c r="J44" t="s">
-        <v>135</v>
+        <v>642</v>
       </c>
       <c r="K44" t="s">
-        <v>129</v>
+        <v>637</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B45">
         <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H45" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I45" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J45" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K45" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B46">
         <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H46" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I46" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J46" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K46" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B47">
         <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D47" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E47" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F47" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G47" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H47" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I47" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J47" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K47" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B48">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E48" t="s">
-        <v>145</v>
+        <v>403</v>
       </c>
       <c r="F48" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>405</v>
       </c>
       <c r="H48" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="I48" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
       <c r="J48" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
       <c r="K48" t="s">
-        <v>146</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B49">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>474</v>
       </c>
       <c r="E49" t="s">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="F49" t="s">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="G49" t="s">
-        <v>397</v>
+        <v>478</v>
       </c>
       <c r="H49" t="s">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="I49" t="s">
-        <v>400</v>
+        <v>481</v>
       </c>
       <c r="J49" t="s">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K49" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B50">
         <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E50" t="s">
-        <v>411</v>
+        <v>145</v>
       </c>
       <c r="F50" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G50" t="s">
-        <v>413</v>
+        <v>148</v>
       </c>
       <c r="H50" t="s">
-        <v>415</v>
+        <v>150</v>
       </c>
       <c r="I50" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="J50" t="s">
-        <v>417</v>
+        <v>152</v>
       </c>
       <c r="K50" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B51">
         <v>84</v>
       </c>
       <c r="C51" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D51" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="F51" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="G51" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="H51" t="s">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="I51" t="s">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="J51" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="K51" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B52">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D52" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E52" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="F52" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="H52" t="s">
-        <v>366</v>
+        <v>415</v>
       </c>
       <c r="I52" t="s">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="J52" t="s">
-        <v>368</v>
+        <v>417</v>
       </c>
       <c r="K52" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B53">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
         <v>473</v>
       </c>
       <c r="D53" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E53" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="F53" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="G53" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="H53" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="I53" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="J53" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="K53" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B54">
         <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D54" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E54" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F54" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G54" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H54" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I54" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J54" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K54" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B55">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>491</v>
       </c>
       <c r="E55" t="s">
-        <v>228</v>
+        <v>492</v>
       </c>
       <c r="F55" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s">
-        <v>231</v>
+        <v>494</v>
       </c>
       <c r="H55" t="s">
-        <v>233</v>
+        <v>496</v>
       </c>
       <c r="I55" t="s">
-        <v>234</v>
+        <v>497</v>
       </c>
       <c r="J55" t="s">
-        <v>235</v>
+        <v>498</v>
       </c>
       <c r="K55" t="s">
-        <v>229</v>
+        <v>493</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B56">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D56" t="s">
-        <v>266</v>
+        <v>532</v>
       </c>
       <c r="E56" t="s">
-        <v>267</v>
+        <v>533</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>536</v>
       </c>
       <c r="H56" t="s">
-        <v>270</v>
+        <v>538</v>
       </c>
       <c r="I56" t="s">
-        <v>79</v>
+        <v>539</v>
       </c>
       <c r="J56" t="s">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="K56" t="s">
-        <v>268</v>
+        <v>534</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B57">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C57" t="s">
-        <v>284</v>
+        <v>591</v>
       </c>
       <c r="D57" t="s">
-        <v>338</v>
+        <v>643</v>
       </c>
       <c r="E57" t="s">
-        <v>339</v>
+        <v>644</v>
       </c>
       <c r="F57" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>342</v>
+        <v>618</v>
       </c>
       <c r="H57" t="s">
-        <v>344</v>
+        <v>647</v>
       </c>
       <c r="I57" t="s">
-        <v>345</v>
+        <v>648</v>
       </c>
       <c r="J57" t="s">
-        <v>346</v>
+        <v>649</v>
       </c>
       <c r="K57" t="s">
-        <v>340</v>
+        <v>645</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B58">
         <v>82</v>
       </c>
       <c r="C58" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D58" t="s">
-        <v>601</v>
+        <v>227</v>
       </c>
       <c r="E58" t="s">
-        <v>602</v>
+        <v>228</v>
       </c>
       <c r="F58" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="G58" t="s">
-        <v>604</v>
+        <v>231</v>
       </c>
       <c r="H58" t="s">
-        <v>606</v>
+        <v>233</v>
       </c>
       <c r="I58" t="s">
-        <v>607</v>
+        <v>234</v>
       </c>
       <c r="J58" t="s">
-        <v>608</v>
+        <v>235</v>
       </c>
       <c r="K58" t="s">
-        <v>603</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B59">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E59" t="s">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="H59" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="I59" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J59" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s">
-        <v>82</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B60">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C60" t="s">
         <v>284</v>
       </c>
       <c r="D60" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E60" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="F60" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="G60" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="H60" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="I60" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="J60" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="K60" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B61">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C61" t="s">
-        <v>473</v>
+        <v>591</v>
       </c>
       <c r="D61" t="s">
-        <v>499</v>
+        <v>601</v>
       </c>
       <c r="E61" t="s">
-        <v>500</v>
+        <v>602</v>
       </c>
       <c r="F61" t="s">
-        <v>502</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="H61" t="s">
-        <v>505</v>
+        <v>606</v>
       </c>
       <c r="I61" t="s">
-        <v>506</v>
+        <v>607</v>
       </c>
       <c r="J61" t="s">
-        <v>507</v>
+        <v>608</v>
       </c>
       <c r="K61" t="s">
-        <v>501</v>
+        <v>603</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="B62">
         <v>81</v>
       </c>
       <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s">
+        <v>85</v>
+      </c>
+      <c r="I62" t="s">
+        <v>86</v>
+      </c>
+      <c r="J62" t="s">
+        <v>87</v>
+      </c>
+      <c r="K62" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>708</v>
+      </c>
+      <c r="B63">
+        <v>81</v>
+      </c>
+      <c r="C63" t="s">
+        <v>284</v>
+      </c>
+      <c r="D63" t="s">
+        <v>377</v>
+      </c>
+      <c r="E63" t="s">
+        <v>378</v>
+      </c>
+      <c r="F63" t="s">
+        <v>380</v>
+      </c>
+      <c r="G63" t="s">
+        <v>381</v>
+      </c>
+      <c r="H63" t="s">
+        <v>383</v>
+      </c>
+      <c r="I63" t="s">
+        <v>384</v>
+      </c>
+      <c r="J63" t="s">
+        <v>385</v>
+      </c>
+      <c r="K63" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>708</v>
+      </c>
+      <c r="B64">
+        <v>81</v>
+      </c>
+      <c r="C64" t="s">
+        <v>473</v>
+      </c>
+      <c r="D64" t="s">
+        <v>499</v>
+      </c>
+      <c r="E64" t="s">
+        <v>500</v>
+      </c>
+      <c r="F64" t="s">
+        <v>502</v>
+      </c>
+      <c r="G64" t="s">
+        <v>503</v>
+      </c>
+      <c r="H64" t="s">
+        <v>505</v>
+      </c>
+      <c r="I64" t="s">
+        <v>506</v>
+      </c>
+      <c r="J64" t="s">
+        <v>507</v>
+      </c>
+      <c r="K64" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>708</v>
+      </c>
+      <c r="B65">
+        <v>81</v>
+      </c>
+      <c r="C65" t="s">
         <v>591</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D65" t="s">
         <v>616</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E65" t="s">
         <v>610</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F65" t="s">
         <v>16</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G65" t="s">
         <v>618</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H65" t="s">
         <v>620</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I65" t="s">
         <v>621</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J65" t="s">
         <v>622</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K65" t="s">
         <v>617</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="813">
   <si>
     <t>日期</t>
   </si>
@@ -2105,6 +2105,234 @@
   </si>
   <si>
     <t>突出生物医学工程背景与科研能力；强调生物医用材料/器械交叉研究与成果。</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>惠泰医疗（湖南埃普特医疗器械）</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（神经介入/心血管介入器械研发岗）</t>
+  </si>
+  <si>
+    <t>深圳惠泰医疗（科创板688617）全资子公司，专注心脏电生理与介入医疗器械研发，以冠脉通路和电生理器械为主，外周血管和神经介入器械为重点。招聘硕博从事介入导管、导丝、电生理耗材的设计开发与材料研发。</t>
+  </si>
+  <si>
+    <t>湖南长沙</t>
+  </si>
+  <si>
+    <t>https://xsjy.whu.edu.cn/f/recruitmentinfo/show?recruitmentId=59c960978d250617806adaf55e5e6593</t>
+  </si>
+  <si>
+    <t>智能匹配88分【校园招聘】|强烈推荐|科创板上市公司，神经介入/介入器械研发岗，方向（介入器械）+技能（材料/设计）高度重合</t>
+  </si>
+  <si>
+    <t>研究85/技能80/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>惠泰医疗为科创板上市、专注神经介入与心血管介入器械研发的头部企业，校招岗位涉及介入导管/导丝/电生理耗材的设计开发与材料研发，与硕士的介入器械研究方向及材料学、支架设计技能高度契合，应届硕士可直接投递，是难得的研发平台。</t>
+  </si>
+  <si>
+    <t>突出介入器械/支架设计项目与材料学背景；量化结构设计与力学评价成果；强调神经介入或血管介入研究经历；补充生物相容性评价与实验技能。</t>
+  </si>
+  <si>
+    <t>上海暖阳医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（血管支架/涂层工艺）</t>
+  </si>
+  <si>
+    <t>负责血管支架或涂层工艺产品研发及设计评价、可行性评估；负责产品设计开发流程职责并输出技术文档；参与新产品专利撰写；协助产品注册及转生产。本科及以上，材料/机械/高分子相关专业，具介入器械研发经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配89分【社招】|强烈推荐|血管支架/药物涂层研发岗，方向直接匹配+技能（材料/支架设计/涂层）高度覆盖</t>
+  </si>
+  <si>
+    <t>研究90/技能85/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位直接负责血管支架及涂层工艺产品研发与设计评价，与硕士支架研究方向完全一致，材料/高分子背景对口，上海岗位符合城市偏好，能完整参与产品从设计到注册转产全流程。</t>
+  </si>
+  <si>
+    <t>突出可降解血管支架设计与涂层工艺项目；量化体外降解/涂层性能测试数据；补充金属/高分子材料选型经验；强调设计开发文档与注册流程参与。</t>
+  </si>
+  <si>
+    <t>上海善迪医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（外周血管支架）</t>
+  </si>
+  <si>
+    <t>专注介入、植入医疗器械研发制造，主要产品为外周血管支架、髂静脉支架系统、腔静脉滤器系统、抓捕器等。要求机械/材料相关专业，具备血管植入器械或支架/滤器研发经验，参与产品设计与注册，公司已有专利29项。</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|外周/髂静脉血管支架研发岗，方向（血管支架）高度匹配，上海优先</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位聚焦外周血管/髂静脉支架及滤器系统研发，与硕士血管支架研究方向直接相关，机械/材料背景对口，上海岗位符合城市偏好，公司拥有多项专利、可深度参与产品设计与注册。</t>
+  </si>
+  <si>
+    <t>突出血管支架结构设计与力学评价项目；补充镍钛/金属材料性能与选型经验；强调设计开发到试制验证的完整经历；列出具体支架产品参数与测试方法。</t>
+  </si>
+  <si>
+    <t>中国医学科学院宋江平课题组</t>
+  </si>
+  <si>
+    <t>Co-PI/博士后/技术员（心血管植入材料与器械）</t>
+  </si>
+  <si>
+    <t>课题组聚焦心血管植入材料、器械研发及评价方向，涉及心血管介入/植入器械、生物医用材料。面向海内外招聘具有生物医学工程、材料学、医学生物学背景的Co-PI、博士后及技术员，待遇按中国医学科学院人才政策执行。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=中国医学科学院宋江平课题组%20招聘</t>
+  </si>
+  <si>
+    <t>智能匹配84分【博士后】|强烈推荐|心血管植入材料/器械研发方向，技能（材料/生物相容性/动物实验）高度覆盖，北京科研院所</t>
+  </si>
+  <si>
+    <t>研究80/技能85/学历80/行业95/企业90</t>
+  </si>
+  <si>
+    <t>课题组聚焦心血管植入材料与器械研发评价，覆盖材料学、生物相容性评价与器械研发，与硕士全部核心技能高度重合，北京科研院所平台待遇优厚，为血管支架方向科研发展的理想平台。</t>
+  </si>
+  <si>
+    <t>重点突出血管支架及生物医用材料研究课题；补充ISO 10993生物相容性评价与动物实验经验；量化降解性能/细胞毒性等测试数据；强调器械研发与转化意识。</t>
+  </si>
+  <si>
+    <t>浙江大学附属邵逸夫医院傅国胜教授团队</t>
+  </si>
+  <si>
+    <t>博士后/科研助理（心血管植介入材料/生物材料）</t>
+  </si>
+  <si>
+    <t>聚焦心血管植介入材料研究，招收生物材料方向博士后及科研助理。具有心血管植介入材料研究背景和动物实验模型经验者优先；博士后出站可申报医院编制特聘研究员系列岗位，提供丰富学术平台资源。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=邵逸夫医院%20傅国胜%20团队%20招聘%20生物材料%20博士后</t>
+  </si>
+  <si>
+    <t>智能匹配84分【博士后】|强烈推荐|心血管植介入材料博士后岗，材料学+生物相容性+动物实验技能全部覆盖</t>
+  </si>
+  <si>
+    <t>团队聚焦心血管植介入材料研究，明确优先具有动物实验模型经验者，与硕士材料学、生物相容性评价、动物实验三大核心技能高度重合，出站可申报医院编制特聘研究员，职业通道完善。</t>
+  </si>
+  <si>
+    <t>突出心血管材料与动物实验模型经验（植入、随访、影像学评估）；补充生物相容性/降解性能评价细节；量化实验数据与结果；强调临床转化与课题申报潜质。</t>
+  </si>
+  <si>
+    <t>上海暖阳医疗器械有限公司（江苏分公司）</t>
+  </si>
+  <si>
+    <t>研发/工艺工程师（导管）</t>
+  </si>
+  <si>
+    <t>公司深耕神经介入领域，从事高附加值介入医疗器械研发。该岗位负责介入导管类产品研发/工艺工作，要求硕士学历、3-5年经验，机械、高分子、材料相关专业。</t>
+  </si>
+  <si>
+    <t>江苏南通</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|神经介入导管研发岗，介入方向+材料学与设计技能匹配</t>
+  </si>
+  <si>
+    <t>研究80/技能75/学历95/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位负责神经介入导管产品研发/工艺，与介入器械研究方向一致，材料/高分子/机械背景对口，硕士学历符合要求，可深度参与介入导管从设计到工艺转化。</t>
+  </si>
+  <si>
+    <t>突出介入导管/输送系统设计与材料选型经历；补充高分子与金属材料加工工艺理解；强调结构与力学性能测试数据；说明工艺开发与验证流程参与。</t>
+  </si>
+  <si>
+    <t>中国科学院深圳先进院（成会明院士课题组）</t>
+  </si>
+  <si>
+    <t>博士后（高分子/医用生物材料/生物医药方向）</t>
+  </si>
+  <si>
+    <t>招收博士后，研究方向为高分子材料、医用分离膜及生物医药（含生物医用材料/医疗器械相关前沿），面向博士毕业生，要求材料、化学、高分子、生物医学工程等专业背景，欢迎血管支架/介入/生物材料研发方向。</t>
+  </si>
+  <si>
+    <t>广东深圳</t>
+  </si>
+  <si>
+    <t>https://scc.pku.edu.cn/f/recruitmentinfo/show?recruitmentId=665725c34fef4e7395fa58df54d5fcfb</t>
+  </si>
+  <si>
+    <t>智能匹配79分【博士后】|值得考虑|中科院深圳先进院博士后（生物医用材料/血管支架方向），技能部分覆盖，深圳平台好</t>
+  </si>
+  <si>
+    <t>研究75/技能75/学历80/行业90/企业90</t>
+  </si>
+  <si>
+    <t>中科院深圳先进院院士课题组招聘生物医用材料/血管支架方向博士后，深圳平台资源与待遇优厚，材料学背景高度契合，是继续深造与科研发展的理想选择。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料与高分子研究课题；补充材料性能与生物相容性评价数据；强调血管支架/植入材料方向研究。</t>
+  </si>
+  <si>
+    <t>河北瑞鹤医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（骨科植入物/三类医疗器械研发）</t>
+  </si>
+  <si>
+    <t>河北省石家庄高新区，从事三类医疗器械研发、生产及销售，设博士后科研工作站、骨科医疗植入物省工程实验室，引进临床医学、材料学、机械等专业，招聘硕博从事骨科植入物及介入器械的研发与材料研究。</t>
+  </si>
+  <si>
+    <t>河北省石家庄</t>
+  </si>
+  <si>
+    <t>https://xsjy.whu.edu.cn/f/recruitmentinfo/show?recruitmentId=5feb19aca87bd07d7e986814f0afe015</t>
+  </si>
+  <si>
+    <t>智能匹配77分【校园招聘】|值得考虑|三类医疗器械/植入物研发校招岗，材料学背景相关，另设材料研究方向</t>
+  </si>
+  <si>
+    <t>研究75/技能60/学历100/行业95/企业80</t>
+  </si>
+  <si>
+    <t>GE医疗（通用电气医疗）</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（医疗科技研发岗）</t>
+  </si>
+  <si>
+    <t>全球领先医疗科技企业，业务覆盖医学影像、先进可视化诊疗、生命关爱和诊断药物。面向硕博生招聘研发类岗位，涉及影像设备、治疗器械及生物材料相关研发方向。</t>
+  </si>
+  <si>
+    <t>北京/上海等地</t>
+  </si>
+  <si>
+    <t>https://xsjy.whu.edu.cn/f/recruitmentinfo/show?recruitmentId=1e29fb42cda45855f51fc3a228bfad69</t>
+  </si>
+  <si>
+    <t>智能匹配77分【校园招聘】|值得考虑|全球医疗科技大厂校招（治疗器械/生物材料方向），材料与器械背景相关</t>
+  </si>
+  <si>
+    <t>研究70/技能65/学历100/行业90/企业90</t>
+  </si>
+  <si>
+    <t>航天新长征医疗器械（北京）有限公司</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（高端医疗装备研发）</t>
+  </si>
+  <si>
+    <t>中国航天科技集团一院十八所全资子公司，医工结合聚焦高端医疗装备，自主研制国产ECMO系统。招聘硕博从事高端生命支持/体外循环装备与医疗器械研发，欢迎材料、机械、生物医学工程背景。</t>
+  </si>
+  <si>
+    <t>https://scc.pku.edu.cn/f/recruitmentinfo/show?recruitmentId=bb38dec189fe4d649627995d432a3326</t>
+  </si>
+  <si>
+    <t>智能匹配74分【校园招聘】|值得考虑|央企背景医疗器械研发校招岗，材料/机械/生医工程背景可投</t>
+  </si>
+  <si>
+    <t>研究70/技能60/学历100/行业85/企业80</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -2659,7 +2887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6321,6 +6549,386 @@
       </c>
       <c r="L96" t="s">
         <v>696</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>697</v>
+      </c>
+      <c r="B97" t="s">
+        <v>698</v>
+      </c>
+      <c r="C97" t="s">
+        <v>699</v>
+      </c>
+      <c r="D97" t="s">
+        <v>700</v>
+      </c>
+      <c r="E97" t="s">
+        <v>701</v>
+      </c>
+      <c r="F97" t="s">
+        <v>702</v>
+      </c>
+      <c r="G97">
+        <v>9</v>
+      </c>
+      <c r="H97" t="s">
+        <v>703</v>
+      </c>
+      <c r="I97">
+        <v>88</v>
+      </c>
+      <c r="J97" t="s">
+        <v>704</v>
+      </c>
+      <c r="K97" t="s">
+        <v>705</v>
+      </c>
+      <c r="L97" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>697</v>
+      </c>
+      <c r="B98" t="s">
+        <v>707</v>
+      </c>
+      <c r="C98" t="s">
+        <v>708</v>
+      </c>
+      <c r="D98" t="s">
+        <v>709</v>
+      </c>
+      <c r="E98" t="s">
+        <v>318</v>
+      </c>
+      <c r="F98" t="s">
+        <v>604</v>
+      </c>
+      <c r="G98">
+        <v>9</v>
+      </c>
+      <c r="H98" t="s">
+        <v>710</v>
+      </c>
+      <c r="I98">
+        <v>89</v>
+      </c>
+      <c r="J98" t="s">
+        <v>711</v>
+      </c>
+      <c r="K98" t="s">
+        <v>712</v>
+      </c>
+      <c r="L98" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>697</v>
+      </c>
+      <c r="B99" t="s">
+        <v>714</v>
+      </c>
+      <c r="C99" t="s">
+        <v>715</v>
+      </c>
+      <c r="D99" t="s">
+        <v>716</v>
+      </c>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
+        <v>604</v>
+      </c>
+      <c r="G99">
+        <v>8</v>
+      </c>
+      <c r="H99" t="s">
+        <v>717</v>
+      </c>
+      <c r="I99">
+        <v>84</v>
+      </c>
+      <c r="J99" t="s">
+        <v>718</v>
+      </c>
+      <c r="K99" t="s">
+        <v>719</v>
+      </c>
+      <c r="L99" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>697</v>
+      </c>
+      <c r="B100" t="s">
+        <v>721</v>
+      </c>
+      <c r="C100" t="s">
+        <v>722</v>
+      </c>
+      <c r="D100" t="s">
+        <v>723</v>
+      </c>
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>724</v>
+      </c>
+      <c r="G100">
+        <v>8</v>
+      </c>
+      <c r="H100" t="s">
+        <v>725</v>
+      </c>
+      <c r="I100">
+        <v>84</v>
+      </c>
+      <c r="J100" t="s">
+        <v>726</v>
+      </c>
+      <c r="K100" t="s">
+        <v>727</v>
+      </c>
+      <c r="L100" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>697</v>
+      </c>
+      <c r="B101" t="s">
+        <v>729</v>
+      </c>
+      <c r="C101" t="s">
+        <v>730</v>
+      </c>
+      <c r="D101" t="s">
+        <v>731</v>
+      </c>
+      <c r="E101" t="s">
+        <v>535</v>
+      </c>
+      <c r="F101" t="s">
+        <v>732</v>
+      </c>
+      <c r="G101">
+        <v>8</v>
+      </c>
+      <c r="H101" t="s">
+        <v>733</v>
+      </c>
+      <c r="I101">
+        <v>84</v>
+      </c>
+      <c r="J101" t="s">
+        <v>726</v>
+      </c>
+      <c r="K101" t="s">
+        <v>734</v>
+      </c>
+      <c r="L101" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>697</v>
+      </c>
+      <c r="B102" t="s">
+        <v>736</v>
+      </c>
+      <c r="C102" t="s">
+        <v>737</v>
+      </c>
+      <c r="D102" t="s">
+        <v>738</v>
+      </c>
+      <c r="E102" t="s">
+        <v>739</v>
+      </c>
+      <c r="F102" t="s">
+        <v>604</v>
+      </c>
+      <c r="G102">
+        <v>8</v>
+      </c>
+      <c r="H102" t="s">
+        <v>740</v>
+      </c>
+      <c r="I102">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s">
+        <v>741</v>
+      </c>
+      <c r="K102" t="s">
+        <v>742</v>
+      </c>
+      <c r="L102" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>697</v>
+      </c>
+      <c r="B103" t="s">
+        <v>744</v>
+      </c>
+      <c r="C103" t="s">
+        <v>745</v>
+      </c>
+      <c r="D103" t="s">
+        <v>746</v>
+      </c>
+      <c r="E103" t="s">
+        <v>747</v>
+      </c>
+      <c r="F103" t="s">
+        <v>748</v>
+      </c>
+      <c r="G103">
+        <v>8</v>
+      </c>
+      <c r="H103" t="s">
+        <v>749</v>
+      </c>
+      <c r="I103">
+        <v>79</v>
+      </c>
+      <c r="J103" t="s">
+        <v>750</v>
+      </c>
+      <c r="K103" t="s">
+        <v>751</v>
+      </c>
+      <c r="L103" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>697</v>
+      </c>
+      <c r="B104" t="s">
+        <v>753</v>
+      </c>
+      <c r="C104" t="s">
+        <v>754</v>
+      </c>
+      <c r="D104" t="s">
+        <v>755</v>
+      </c>
+      <c r="E104" t="s">
+        <v>756</v>
+      </c>
+      <c r="F104" t="s">
+        <v>757</v>
+      </c>
+      <c r="G104">
+        <v>8</v>
+      </c>
+      <c r="H104" t="s">
+        <v>758</v>
+      </c>
+      <c r="I104">
+        <v>77</v>
+      </c>
+      <c r="J104" t="s">
+        <v>759</v>
+      </c>
+      <c r="K104" t="s">
+        <v>79</v>
+      </c>
+      <c r="L104" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>697</v>
+      </c>
+      <c r="B105" t="s">
+        <v>760</v>
+      </c>
+      <c r="C105" t="s">
+        <v>761</v>
+      </c>
+      <c r="D105" t="s">
+        <v>762</v>
+      </c>
+      <c r="E105" t="s">
+        <v>763</v>
+      </c>
+      <c r="F105" t="s">
+        <v>764</v>
+      </c>
+      <c r="G105">
+        <v>8</v>
+      </c>
+      <c r="H105" t="s">
+        <v>765</v>
+      </c>
+      <c r="I105">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s">
+        <v>766</v>
+      </c>
+      <c r="K105" t="s">
+        <v>79</v>
+      </c>
+      <c r="L105" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>697</v>
+      </c>
+      <c r="B106" t="s">
+        <v>767</v>
+      </c>
+      <c r="C106" t="s">
+        <v>768</v>
+      </c>
+      <c r="D106" t="s">
+        <v>769</v>
+      </c>
+      <c r="E106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>770</v>
+      </c>
+      <c r="G106">
+        <v>7</v>
+      </c>
+      <c r="H106" t="s">
+        <v>771</v>
+      </c>
+      <c r="I106">
+        <v>74</v>
+      </c>
+      <c r="J106" t="s">
+        <v>772</v>
+      </c>
+      <c r="K106" t="s">
+        <v>79</v>
+      </c>
+      <c r="L106" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6354,7 +6962,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6363,16 +6971,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>698</v>
+        <v>774</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>699</v>
+        <v>775</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>700</v>
+        <v>776</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>701</v>
+        <v>777</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6386,13 +6994,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>702</v>
+        <v>778</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>703</v>
+        <v>779</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>704</v>
+        <v>780</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -6420,7 +7028,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -6435,7 +7043,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>709</v>
+        <v>785</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6445,31 +7053,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>710</v>
+        <v>786</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>711</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>712</v>
+        <v>788</v>
       </c>
       <c r="B4">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>713</v>
+        <v>789</v>
       </c>
       <c r="B5" t="s">
-        <v>714</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>715</v>
+        <v>791</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -6477,7 +7085,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>716</v>
+        <v>792</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -6485,39 +7093,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>717</v>
+        <v>793</v>
       </c>
       <c r="B8">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>718</v>
+        <v>794</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>719</v>
+        <v>795</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>720</v>
+        <v>796</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>721</v>
+        <v>797</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -6527,15 +7135,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>722</v>
+        <v>798</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>723</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -6543,31 +7151,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="B17" s="5">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>726</v>
+        <v>802</v>
       </c>
       <c r="B18" s="5">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>727</v>
+        <v>803</v>
       </c>
       <c r="B19" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>728</v>
+        <v>804</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6575,7 +7183,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>729</v>
+        <v>805</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6583,7 +7191,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>730</v>
+        <v>806</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6591,7 +7199,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>731</v>
+        <v>807</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6599,7 +7207,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>732</v>
+        <v>808</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6607,7 +7215,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>733</v>
+        <v>809</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6615,7 +7223,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>734</v>
+        <v>810</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -6627,7 +7235,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>735</v>
+        <v>811</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -6645,7 +7253,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>736</v>
+        <v>812</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -7904,25 +8512,25 @@
         <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>697</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>698</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>699</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
+        <v>701</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>702</v>
       </c>
       <c r="G78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H78" t="s">
-        <v>77</v>
+        <v>703</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7930,25 +8538,25 @@
         <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>697</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>707</v>
       </c>
       <c r="D79" t="s">
-        <v>81</v>
+        <v>708</v>
       </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>318</v>
       </c>
       <c r="F79" t="s">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="G79">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H79" t="s">
-        <v>84</v>
+        <v>710</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7959,22 +8567,22 @@
         <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E80" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F80" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G80">
         <v>8</v>
       </c>
       <c r="H80" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7985,22 +8593,22 @@
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G81">
         <v>8</v>
       </c>
       <c r="H81" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8011,22 +8619,22 @@
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D82" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F82" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8037,22 +8645,22 @@
         <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D83" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8063,22 +8671,22 @@
         <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E84" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8089,22 +8697,22 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D85" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F85" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8112,25 +8720,25 @@
         <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D86" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F86" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -8138,25 +8746,25 @@
         <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E87" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -8167,22 +8775,22 @@
         <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E88" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F88" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -8193,22 +8801,22 @@
         <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D89" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E89" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F89" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -8219,22 +8827,22 @@
         <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D90" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F90" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -8245,22 +8853,22 @@
         <v>159</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D91" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -8271,22 +8879,22 @@
         <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D92" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -8297,22 +8905,22 @@
         <v>159</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D93" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E93" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F93" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -8323,22 +8931,22 @@
         <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D94" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E94" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -8349,22 +8957,22 @@
         <v>159</v>
       </c>
       <c r="C95" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D95" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F95" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -8375,22 +8983,22 @@
         <v>159</v>
       </c>
       <c r="C96" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D96" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E96" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F96" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -8398,25 +9006,25 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E97" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -8424,25 +9032,25 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D98" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E98" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F98" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -8453,22 +9061,22 @@
         <v>284</v>
       </c>
       <c r="C99" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D99" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E99" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F99" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -8479,22 +9087,22 @@
         <v>284</v>
       </c>
       <c r="C100" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E100" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F100" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -8505,22 +9113,22 @@
         <v>284</v>
       </c>
       <c r="C101" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D101" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E101" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F101" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -8531,22 +9139,22 @@
         <v>284</v>
       </c>
       <c r="C102" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D102" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E102" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F102" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -8554,25 +9162,25 @@
         <v>74</v>
       </c>
       <c r="B103" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C103" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D103" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E103" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F103" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -8580,25 +9188,25 @@
         <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C104" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D104" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E104" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F104" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -8609,22 +9217,22 @@
         <v>402</v>
       </c>
       <c r="C105" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D105" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E105" t="s">
         <v>66</v>
       </c>
       <c r="F105" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -8635,22 +9243,22 @@
         <v>402</v>
       </c>
       <c r="C106" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D106" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E106" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F106" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -8658,25 +9266,25 @@
         <v>78</v>
       </c>
       <c r="B107" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C107" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D107" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E107" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F107" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -8684,25 +9292,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C108" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D108" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E108" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -8713,22 +9321,22 @@
         <v>473</v>
       </c>
       <c r="C109" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D109" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E109" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F109" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -8739,22 +9347,22 @@
         <v>473</v>
       </c>
       <c r="C110" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D110" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E110" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F110" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -8765,22 +9373,22 @@
         <v>473</v>
       </c>
       <c r="C111" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D111" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E111" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F111" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -8788,25 +9396,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C112" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D112" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E112" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F112" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -8814,25 +9422,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C113" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D113" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E113" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -8840,25 +9448,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C114" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="D114" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="E114" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F114" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -8866,25 +9474,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C115" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D115" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E115" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F115" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -8895,22 +9503,22 @@
         <v>591</v>
       </c>
       <c r="C116" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D116" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E116" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F116" t="s">
-        <v>468</v>
+        <v>604</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -8921,10 +9529,10 @@
         <v>591</v>
       </c>
       <c r="C117" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="D117" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
@@ -8936,7 +9544,7 @@
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -8947,22 +9555,22 @@
         <v>591</v>
       </c>
       <c r="C118" t="s">
-        <v>650</v>
+        <v>557</v>
       </c>
       <c r="D118" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E118" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F118" t="s">
-        <v>653</v>
+        <v>468</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -8973,22 +9581,22 @@
         <v>591</v>
       </c>
       <c r="C119" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="D119" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="E119" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -8999,22 +9607,22 @@
         <v>591</v>
       </c>
       <c r="C120" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="D120" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E120" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F120" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -9025,22 +9633,22 @@
         <v>591</v>
       </c>
       <c r="C121" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="D121" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="E121" t="s">
-        <v>66</v>
+        <v>661</v>
       </c>
       <c r="F121" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -9048,25 +9656,25 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>159</v>
+        <v>591</v>
       </c>
       <c r="C122" t="s">
-        <v>271</v>
+        <v>666</v>
       </c>
       <c r="D122" t="s">
-        <v>272</v>
+        <v>667</v>
       </c>
       <c r="E122" t="s">
         <v>75</v>
       </c>
       <c r="F122" t="s">
-        <v>274</v>
+        <v>604</v>
       </c>
       <c r="G122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>275</v>
+        <v>669</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -9077,22 +9685,22 @@
         <v>591</v>
       </c>
       <c r="C123" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D123" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="E123" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F123" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="G123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -9100,25 +9708,285 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
+        <v>697</v>
+      </c>
+      <c r="C124" t="s">
+        <v>714</v>
+      </c>
+      <c r="D124" t="s">
+        <v>715</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s">
+        <v>604</v>
+      </c>
+      <c r="G124">
+        <v>8</v>
+      </c>
+      <c r="H124" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>96</v>
+      </c>
+      <c r="B125" t="s">
+        <v>697</v>
+      </c>
+      <c r="C125" t="s">
+        <v>721</v>
+      </c>
+      <c r="D125" t="s">
+        <v>722</v>
+      </c>
+      <c r="E125" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" t="s">
+        <v>724</v>
+      </c>
+      <c r="G125">
+        <v>8</v>
+      </c>
+      <c r="H125" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>97</v>
+      </c>
+      <c r="B126" t="s">
+        <v>697</v>
+      </c>
+      <c r="C126" t="s">
+        <v>729</v>
+      </c>
+      <c r="D126" t="s">
+        <v>730</v>
+      </c>
+      <c r="E126" t="s">
+        <v>535</v>
+      </c>
+      <c r="F126" t="s">
+        <v>732</v>
+      </c>
+      <c r="G126">
+        <v>8</v>
+      </c>
+      <c r="H126" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>98</v>
+      </c>
+      <c r="B127" t="s">
+        <v>697</v>
+      </c>
+      <c r="C127" t="s">
+        <v>736</v>
+      </c>
+      <c r="D127" t="s">
+        <v>737</v>
+      </c>
+      <c r="E127" t="s">
+        <v>739</v>
+      </c>
+      <c r="F127" t="s">
+        <v>604</v>
+      </c>
+      <c r="G127">
+        <v>8</v>
+      </c>
+      <c r="H127" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>99</v>
+      </c>
+      <c r="B128" t="s">
+        <v>697</v>
+      </c>
+      <c r="C128" t="s">
+        <v>744</v>
+      </c>
+      <c r="D128" t="s">
+        <v>745</v>
+      </c>
+      <c r="E128" t="s">
+        <v>747</v>
+      </c>
+      <c r="F128" t="s">
+        <v>748</v>
+      </c>
+      <c r="G128">
+        <v>8</v>
+      </c>
+      <c r="H128" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>100</v>
+      </c>
+      <c r="B129" t="s">
+        <v>697</v>
+      </c>
+      <c r="C129" t="s">
+        <v>753</v>
+      </c>
+      <c r="D129" t="s">
+        <v>754</v>
+      </c>
+      <c r="E129" t="s">
+        <v>756</v>
+      </c>
+      <c r="F129" t="s">
+        <v>757</v>
+      </c>
+      <c r="G129">
+        <v>8</v>
+      </c>
+      <c r="H129" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>101</v>
+      </c>
+      <c r="B130" t="s">
+        <v>697</v>
+      </c>
+      <c r="C130" t="s">
+        <v>760</v>
+      </c>
+      <c r="D130" t="s">
+        <v>761</v>
+      </c>
+      <c r="E130" t="s">
+        <v>763</v>
+      </c>
+      <c r="F130" t="s">
+        <v>764</v>
+      </c>
+      <c r="G130">
+        <v>8</v>
+      </c>
+      <c r="H130" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>102</v>
+      </c>
+      <c r="B131" t="s">
+        <v>159</v>
+      </c>
+      <c r="C131" t="s">
+        <v>271</v>
+      </c>
+      <c r="D131" t="s">
+        <v>272</v>
+      </c>
+      <c r="E131" t="s">
+        <v>75</v>
+      </c>
+      <c r="F131" t="s">
+        <v>274</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>103</v>
+      </c>
+      <c r="B132" t="s">
         <v>591</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C132" t="s">
+        <v>681</v>
+      </c>
+      <c r="D132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E132" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" t="s">
+        <v>684</v>
+      </c>
+      <c r="G132">
+        <v>7</v>
+      </c>
+      <c r="H132" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>104</v>
+      </c>
+      <c r="B133" t="s">
+        <v>591</v>
+      </c>
+      <c r="C133" t="s">
         <v>689</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D133" t="s">
         <v>690</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E133" t="s">
         <v>66</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F133" t="s">
         <v>692</v>
       </c>
-      <c r="G124">
+      <c r="G133">
         <v>7</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H133" t="s">
         <v>693</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>105</v>
+      </c>
+      <c r="B134" t="s">
+        <v>697</v>
+      </c>
+      <c r="C134" t="s">
+        <v>767</v>
+      </c>
+      <c r="D134" t="s">
+        <v>768</v>
+      </c>
+      <c r="E134" t="s">
+        <v>25</v>
+      </c>
+      <c r="F134" t="s">
+        <v>770</v>
+      </c>
+      <c r="G134">
+        <v>7</v>
+      </c>
+      <c r="H134" t="s">
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -9134,7 +10002,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9151,10 +10019,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>705</v>
+        <v>781</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>706</v>
+        <v>782</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -9181,12 +10049,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>707</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -9221,7 +10089,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -9256,7 +10124,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -9291,7 +10159,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -9326,7 +10194,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -9361,7 +10229,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -9396,7 +10264,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -9431,7 +10299,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -9466,7 +10334,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -9501,7 +10369,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -9536,7 +10404,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -9571,7 +10439,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -9606,7 +10474,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -9641,7 +10509,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -9676,7 +10544,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -9711,7 +10579,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -9746,7 +10614,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -9781,7 +10649,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -9816,7 +10684,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -9851,7 +10719,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -9886,7 +10754,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -9921,7 +10789,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B23">
         <v>89</v>
@@ -9956,7 +10824,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -9991,7 +10859,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -10026,7 +10894,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -10061,509 +10929,509 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>784</v>
+      </c>
+      <c r="B27">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>697</v>
+      </c>
+      <c r="D27" t="s">
+        <v>707</v>
+      </c>
+      <c r="E27" t="s">
         <v>708</v>
       </c>
-      <c r="B27">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
-      </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>604</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>711</v>
       </c>
       <c r="I27" t="s">
-        <v>37</v>
+        <v>712</v>
       </c>
       <c r="J27" t="s">
-        <v>38</v>
+        <v>713</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>709</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B28">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J28" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K28" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B29">
         <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E29" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J29" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K29" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B30">
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E30" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H30" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J30" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K30" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B31">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>402</v>
       </c>
       <c r="D31" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>449</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>438</v>
       </c>
       <c r="H31" t="s">
-        <v>188</v>
+        <v>452</v>
       </c>
       <c r="I31" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s">
-        <v>186</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B32">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>697</v>
       </c>
       <c r="D32" t="s">
-        <v>353</v>
+        <v>698</v>
       </c>
       <c r="E32" t="s">
-        <v>354</v>
+        <v>699</v>
       </c>
       <c r="F32" t="s">
-        <v>356</v>
+        <v>701</v>
       </c>
       <c r="G32" t="s">
-        <v>357</v>
+        <v>702</v>
       </c>
       <c r="H32" t="s">
-        <v>359</v>
+        <v>704</v>
       </c>
       <c r="I32" t="s">
-        <v>360</v>
+        <v>705</v>
       </c>
       <c r="J32" t="s">
-        <v>361</v>
+        <v>706</v>
       </c>
       <c r="K32" t="s">
-        <v>355</v>
+        <v>700</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B33">
         <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="J33" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="K33" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B34">
         <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E34" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G34" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H34" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J34" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K34" t="s">
-        <v>464</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B35">
         <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="F35" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H35" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I35" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B36">
         <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D36" t="s">
-        <v>570</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>571</v>
+        <v>463</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>573</v>
+        <v>438</v>
       </c>
       <c r="H36" t="s">
-        <v>575</v>
+        <v>456</v>
       </c>
       <c r="I36" t="s">
-        <v>576</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s">
-        <v>577</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s">
-        <v>572</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B37">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D37" t="s">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
-        <v>370</v>
+        <v>508</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>510</v>
       </c>
       <c r="G37" t="s">
-        <v>372</v>
+        <v>511</v>
       </c>
       <c r="H37" t="s">
-        <v>374</v>
+        <v>513</v>
       </c>
       <c r="I37" t="s">
-        <v>375</v>
+        <v>514</v>
       </c>
       <c r="J37" t="s">
-        <v>376</v>
+        <v>515</v>
       </c>
       <c r="K37" t="s">
-        <v>371</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B38">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="E38" t="s">
-        <v>457</v>
+        <v>571</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G38" t="s">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="H38" t="s">
-        <v>460</v>
+        <v>575</v>
       </c>
       <c r="I38" t="s">
-        <v>461</v>
+        <v>576</v>
       </c>
       <c r="J38" t="s">
-        <v>462</v>
+        <v>577</v>
       </c>
       <c r="K38" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B39">
         <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D39" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="E39" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="H39" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="I39" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J39" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="K39" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B40">
         <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D40" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F40" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="I40" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J40" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="K40" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B41">
         <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
-        <v>557</v>
+        <v>322</v>
       </c>
       <c r="E41" t="s">
-        <v>558</v>
+        <v>466</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -10572,91 +11440,91 @@
         <v>468</v>
       </c>
       <c r="H41" t="s">
-        <v>561</v>
+        <v>470</v>
       </c>
       <c r="I41" t="s">
-        <v>562</v>
+        <v>471</v>
       </c>
       <c r="J41" t="s">
-        <v>563</v>
+        <v>472</v>
       </c>
       <c r="K41" t="s">
-        <v>559</v>
+        <v>467</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B42">
         <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D42" t="s">
-        <v>609</v>
+        <v>541</v>
       </c>
       <c r="E42" t="s">
-        <v>610</v>
+        <v>542</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G42" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="H42" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="I42" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="J42" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="K42" t="s">
-        <v>611</v>
+        <v>543</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B43">
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D43" t="s">
-        <v>627</v>
+        <v>557</v>
       </c>
       <c r="E43" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>630</v>
+        <v>468</v>
       </c>
       <c r="H43" t="s">
-        <v>632</v>
+        <v>561</v>
       </c>
       <c r="I43" t="s">
-        <v>633</v>
+        <v>562</v>
       </c>
       <c r="J43" t="s">
-        <v>634</v>
+        <v>563</v>
       </c>
       <c r="K43" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B44">
         <v>86</v>
@@ -10665,762 +11533,972 @@
         <v>591</v>
       </c>
       <c r="D44" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="E44" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>638</v>
+        <v>604</v>
       </c>
       <c r="H44" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="I44" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="J44" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="K44" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B45">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>627</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>628</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="H45" t="s">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="I45" t="s">
-        <v>61</v>
+        <v>633</v>
       </c>
       <c r="J45" t="s">
-        <v>62</v>
+        <v>634</v>
       </c>
       <c r="K45" t="s">
-        <v>57</v>
+        <v>629</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B46">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>636</v>
       </c>
       <c r="F46" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>131</v>
+        <v>638</v>
       </c>
       <c r="H46" t="s">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="I46" t="s">
-        <v>134</v>
+        <v>641</v>
       </c>
       <c r="J46" t="s">
-        <v>135</v>
+        <v>642</v>
       </c>
       <c r="K46" t="s">
-        <v>129</v>
+        <v>637</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B47">
         <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F47" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H47" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I47" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K47" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B48">
         <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G48" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H48" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I48" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J48" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K48" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B49">
         <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E49" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F49" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G49" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H49" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I49" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J49" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K49" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B50">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>403</v>
       </c>
       <c r="F50" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>148</v>
+        <v>405</v>
       </c>
       <c r="H50" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="I50" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
       <c r="J50" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
       <c r="K50" t="s">
-        <v>146</v>
+        <v>404</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B51">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>474</v>
       </c>
       <c r="E51" t="s">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="F51" t="s">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="G51" t="s">
-        <v>397</v>
+        <v>478</v>
       </c>
       <c r="H51" t="s">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="I51" t="s">
-        <v>400</v>
+        <v>481</v>
       </c>
       <c r="J51" t="s">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K51" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B52">
         <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>411</v>
+        <v>145</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>413</v>
+        <v>148</v>
       </c>
       <c r="H52" t="s">
-        <v>415</v>
+        <v>150</v>
       </c>
       <c r="I52" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="J52" t="s">
-        <v>417</v>
+        <v>152</v>
       </c>
       <c r="K52" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B53">
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D53" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E53" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="F53" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="G53" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="H53" t="s">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="I53" t="s">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="J53" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="K53" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B54">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D54" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E54" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="F54" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G54" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="H54" t="s">
-        <v>366</v>
+        <v>415</v>
       </c>
       <c r="I54" t="s">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="J54" t="s">
-        <v>368</v>
+        <v>417</v>
       </c>
       <c r="K54" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B55">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
         <v>473</v>
       </c>
       <c r="D55" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E55" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="G55" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="H55" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="I55" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="J55" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="K55" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B56">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>473</v>
+        <v>697</v>
       </c>
       <c r="D56" t="s">
-        <v>532</v>
+        <v>714</v>
       </c>
       <c r="E56" t="s">
-        <v>533</v>
+        <v>715</v>
       </c>
       <c r="F56" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>536</v>
+        <v>604</v>
       </c>
       <c r="H56" t="s">
-        <v>538</v>
+        <v>718</v>
       </c>
       <c r="I56" t="s">
-        <v>539</v>
+        <v>719</v>
       </c>
       <c r="J56" t="s">
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="K56" t="s">
-        <v>534</v>
+        <v>716</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B57">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="D57" t="s">
-        <v>643</v>
+        <v>721</v>
       </c>
       <c r="E57" t="s">
-        <v>644</v>
+        <v>722</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G57" t="s">
-        <v>618</v>
+        <v>724</v>
       </c>
       <c r="H57" t="s">
-        <v>647</v>
+        <v>726</v>
       </c>
       <c r="I57" t="s">
-        <v>648</v>
+        <v>727</v>
       </c>
       <c r="J57" t="s">
-        <v>649</v>
+        <v>728</v>
       </c>
       <c r="K57" t="s">
-        <v>645</v>
+        <v>723</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B58">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D58" t="s">
-        <v>227</v>
+        <v>729</v>
       </c>
       <c r="E58" t="s">
-        <v>228</v>
+        <v>730</v>
       </c>
       <c r="F58" t="s">
-        <v>230</v>
+        <v>535</v>
       </c>
       <c r="G58" t="s">
-        <v>231</v>
+        <v>732</v>
       </c>
       <c r="H58" t="s">
-        <v>233</v>
+        <v>726</v>
       </c>
       <c r="I58" t="s">
-        <v>234</v>
+        <v>734</v>
       </c>
       <c r="J58" t="s">
-        <v>235</v>
+        <v>735</v>
       </c>
       <c r="K58" t="s">
-        <v>229</v>
+        <v>731</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B59">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>159</v>
+        <v>284</v>
       </c>
       <c r="D59" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="E59" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="G59" t="s">
-        <v>58</v>
+        <v>364</v>
       </c>
       <c r="H59" t="s">
-        <v>270</v>
+        <v>366</v>
       </c>
       <c r="I59" t="s">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="J59" t="s">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="K59" t="s">
-        <v>268</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B60">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D60" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="E60" t="s">
-        <v>339</v>
+        <v>492</v>
       </c>
       <c r="F60" t="s">
-        <v>341</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s">
-        <v>342</v>
+        <v>494</v>
       </c>
       <c r="H60" t="s">
-        <v>344</v>
+        <v>496</v>
       </c>
       <c r="I60" t="s">
-        <v>345</v>
+        <v>497</v>
       </c>
       <c r="J60" t="s">
-        <v>346</v>
+        <v>498</v>
       </c>
       <c r="K60" t="s">
-        <v>340</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B61">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D61" t="s">
-        <v>601</v>
+        <v>532</v>
       </c>
       <c r="E61" t="s">
-        <v>602</v>
+        <v>533</v>
       </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="G61" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="H61" t="s">
-        <v>606</v>
+        <v>538</v>
       </c>
       <c r="I61" t="s">
-        <v>607</v>
+        <v>539</v>
       </c>
       <c r="J61" t="s">
-        <v>608</v>
+        <v>540</v>
       </c>
       <c r="K61" t="s">
-        <v>603</v>
+        <v>534</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B62">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>643</v>
       </c>
       <c r="E62" t="s">
-        <v>81</v>
+        <v>644</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>83</v>
+        <v>618</v>
       </c>
       <c r="H62" t="s">
-        <v>85</v>
+        <v>647</v>
       </c>
       <c r="I62" t="s">
-        <v>86</v>
+        <v>648</v>
       </c>
       <c r="J62" t="s">
-        <v>87</v>
+        <v>649</v>
       </c>
       <c r="K62" t="s">
-        <v>82</v>
+        <v>645</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B63">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C63" t="s">
-        <v>284</v>
+        <v>697</v>
       </c>
       <c r="D63" t="s">
-        <v>377</v>
+        <v>736</v>
       </c>
       <c r="E63" t="s">
-        <v>378</v>
+        <v>737</v>
       </c>
       <c r="F63" t="s">
-        <v>380</v>
+        <v>739</v>
       </c>
       <c r="G63" t="s">
-        <v>381</v>
+        <v>604</v>
       </c>
       <c r="H63" t="s">
-        <v>383</v>
+        <v>741</v>
       </c>
       <c r="I63" t="s">
-        <v>384</v>
+        <v>742</v>
       </c>
       <c r="J63" t="s">
-        <v>385</v>
+        <v>743</v>
       </c>
       <c r="K63" t="s">
-        <v>379</v>
+        <v>738</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B64">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>473</v>
+        <v>159</v>
       </c>
       <c r="D64" t="s">
-        <v>499</v>
+        <v>227</v>
       </c>
       <c r="E64" t="s">
-        <v>500</v>
+        <v>228</v>
       </c>
       <c r="F64" t="s">
-        <v>502</v>
+        <v>230</v>
       </c>
       <c r="G64" t="s">
-        <v>503</v>
+        <v>231</v>
       </c>
       <c r="H64" t="s">
-        <v>505</v>
+        <v>233</v>
       </c>
       <c r="I64" t="s">
-        <v>506</v>
+        <v>234</v>
       </c>
       <c r="J64" t="s">
-        <v>507</v>
+        <v>235</v>
       </c>
       <c r="K64" t="s">
-        <v>501</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="B65">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D65" t="s">
-        <v>616</v>
+        <v>266</v>
       </c>
       <c r="E65" t="s">
-        <v>610</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="G65" t="s">
+        <v>58</v>
+      </c>
+      <c r="H65" t="s">
+        <v>270</v>
+      </c>
+      <c r="I65" t="s">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>784</v>
+      </c>
+      <c r="B66">
+        <v>82</v>
+      </c>
+      <c r="C66" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" t="s">
+        <v>338</v>
+      </c>
+      <c r="E66" t="s">
+        <v>339</v>
+      </c>
+      <c r="F66" t="s">
+        <v>341</v>
+      </c>
+      <c r="G66" t="s">
+        <v>342</v>
+      </c>
+      <c r="H66" t="s">
+        <v>344</v>
+      </c>
+      <c r="I66" t="s">
+        <v>345</v>
+      </c>
+      <c r="J66" t="s">
+        <v>346</v>
+      </c>
+      <c r="K66" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>784</v>
+      </c>
+      <c r="B67">
+        <v>82</v>
+      </c>
+      <c r="C67" t="s">
+        <v>591</v>
+      </c>
+      <c r="D67" t="s">
+        <v>601</v>
+      </c>
+      <c r="E67" t="s">
+        <v>602</v>
+      </c>
+      <c r="F67" t="s">
+        <v>75</v>
+      </c>
+      <c r="G67" t="s">
+        <v>604</v>
+      </c>
+      <c r="H67" t="s">
+        <v>606</v>
+      </c>
+      <c r="I67" t="s">
+        <v>607</v>
+      </c>
+      <c r="J67" t="s">
+        <v>608</v>
+      </c>
+      <c r="K67" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>784</v>
+      </c>
+      <c r="B68">
+        <v>81</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" t="s">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s">
+        <v>85</v>
+      </c>
+      <c r="I68" t="s">
+        <v>86</v>
+      </c>
+      <c r="J68" t="s">
+        <v>87</v>
+      </c>
+      <c r="K68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>784</v>
+      </c>
+      <c r="B69">
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>284</v>
+      </c>
+      <c r="D69" t="s">
+        <v>377</v>
+      </c>
+      <c r="E69" t="s">
+        <v>378</v>
+      </c>
+      <c r="F69" t="s">
+        <v>380</v>
+      </c>
+      <c r="G69" t="s">
+        <v>381</v>
+      </c>
+      <c r="H69" t="s">
+        <v>383</v>
+      </c>
+      <c r="I69" t="s">
+        <v>384</v>
+      </c>
+      <c r="J69" t="s">
+        <v>385</v>
+      </c>
+      <c r="K69" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>784</v>
+      </c>
+      <c r="B70">
+        <v>81</v>
+      </c>
+      <c r="C70" t="s">
+        <v>473</v>
+      </c>
+      <c r="D70" t="s">
+        <v>499</v>
+      </c>
+      <c r="E70" t="s">
+        <v>500</v>
+      </c>
+      <c r="F70" t="s">
+        <v>502</v>
+      </c>
+      <c r="G70" t="s">
+        <v>503</v>
+      </c>
+      <c r="H70" t="s">
+        <v>505</v>
+      </c>
+      <c r="I70" t="s">
+        <v>506</v>
+      </c>
+      <c r="J70" t="s">
+        <v>507</v>
+      </c>
+      <c r="K70" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>784</v>
+      </c>
+      <c r="B71">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>591</v>
+      </c>
+      <c r="D71" t="s">
+        <v>616</v>
+      </c>
+      <c r="E71" t="s">
+        <v>610</v>
+      </c>
+      <c r="F71" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" t="s">
         <v>618</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H71" t="s">
         <v>620</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I71" t="s">
         <v>621</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J71" t="s">
         <v>622</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K71" t="s">
         <v>617</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="885">
   <si>
     <t>日期</t>
   </si>
@@ -2333,6 +2333,222 @@
   </si>
   <si>
     <t>研究70/技能60/学历100/行业85/企业80</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>杭州创心医学科技有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（心脏及大血管植入器械方向）MJ000067</t>
+  </si>
+  <si>
+    <t>本科或硕士，医疗器械/生物医学工程/机械/材料/高分子等专业，CET4+，熟练AutoCAD/SolidWorks（有限元优先），985/211应届或1年以上经验优先。负责心血管大血管瓣膜支架等微创植入/介入器械设计开发、性能验证、工艺实现、动物实验、生物学评价及临床试验样品。</t>
+  </si>
+  <si>
+    <t>杭州-钱塘区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1982394135.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配90分【校园招聘】|强烈推荐|心血管植入/介入器械研发，明确接收985/211应届，方向（介入）+技能（支架设计/动物实验/生物相容性/材料）全覆盖</t>
+  </si>
+  <si>
+    <t>研究85/技能90/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位明确接收硕士应届（985/211优先），方向正是心血管大血管植入/介入器械，与硕士血管支架研究方向高度一致；职责覆盖结构设计、动物实验、生物学评价、有限元仿真，与本人材料学、支架设计与生物相容性评价技能完全重合，是应届生可投的优质介入器械研发岗。</t>
+  </si>
+  <si>
+    <t>突出血管支架课题与结构设计、SolidWorks/有限元项目经历；量化动物实验（模型、植入、影像学/组织学随访）与生物学评价数据；强调高分子/金属材料选型与英文文献能力，呼应CET4要求；标注可赴杭州并注明应届毕业时间。</t>
+  </si>
+  <si>
+    <t>研发工程师（结构组）</t>
+  </si>
+  <si>
+    <t>机械设计制造/机电一体化/工程力学等工科专业，负责三类心血管植入类器械结构件设计开发、3D建模、验证与工艺实现，参与动物实验及临床试验样品准备。10-18k·15薪，杭州余杭。</t>
+  </si>
+  <si>
+    <t>杭州-余杭区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1980659615.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|心血管植入器械结构件设计+动物实验，支架设计/材料/动物实验技能匹配</t>
+  </si>
+  <si>
+    <t>研究83/技能80/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位聚焦三类心血管植入器械结构设计与工艺实现、参与动物实验临床样品，与硕士支架设计、材料学及动物实验技能高度契合，心血管创新平台可完整参与植入器械从设计到验证。</t>
+  </si>
+  <si>
+    <t>重点展示支架结构设计、3D建模与力学评价项目；补充材料性能测试与有限元分析数据；强调动物实验样品制备与工艺实现经历，列出具体医疗器械结构件设计成果。</t>
+  </si>
+  <si>
+    <t>苏州美创医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>本科及以上硕士优先，机械/金属材料/高分子；3年以上三类器械研发经验，血管支架/弹簧圈经验优先；负责支架产品及输送系统开发、临床验证注册取证、上市产品改进，熟悉ISO13485/GMP。公司专注外周血管和肿瘤介入。12-15k·14薪，上海闵行。</t>
+  </si>
+  <si>
+    <t>上海-闵行区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1971808511.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|支架类产品及输送系统研发，方向（支架）+材料学/设计技能匹配，上海符合城市偏好</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位直接负责支架产品与输送系统开发及注册取证，与硕士血管支架研究方向、材料学及支架设计技能高度对口；外周血管/肿瘤介入赛道成长性好，上海为偏好城市，硕士可投。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计与输送系统项目、SolidWorks制图能力；量化材料性能与验证数据；补充ISO13485/GMP与器械注册流程认知，弱化经验年限、强化支架设计专业匹配度。</t>
+  </si>
+  <si>
+    <t>上海励楷科技有限公司</t>
+  </si>
+  <si>
+    <t>器械研发工程师（镍钛支架/神经介入方向）</t>
+  </si>
+  <si>
+    <t>本科及以上金属材料/镍钛材料/机械专业，3年以上金属材料应用或工艺经验，熟悉镍钛钴铬及镍钛支架加工工艺；负责支架工艺监督优化、新品转产工艺承接、工装模具设计验证、新测试方法开发。公司专注神内外周泛血管介入器械。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1972058755.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|神经介入镍钛支架工艺研发，材料学（镍钛）+支架工艺技能匹配，上海岗位</t>
+  </si>
+  <si>
+    <t>研究85/技能80/学历85/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位专注镍钛/钴铬支架加工工艺与新品转产，与本人金属材料学（镍钛）、支架设计技能高度相关，上海符合城市偏好，神经介入为高成长赛道。</t>
+  </si>
+  <si>
+    <t>突出镍钛/金属材料表征（金相、SEM、拉伸）与支架加工工艺项目；补充工装模具设计或测试方法开发经验；量化材料参数与工艺验证结果，强化神经介入认知。</t>
+  </si>
+  <si>
+    <t>深圳佰特微医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>导管研发经理/导管工程师（上海）</t>
+  </si>
+  <si>
+    <t>本科以上硕士优先，机械/高分子材料等相关专业，经验不限；介入无植入（可降解）定位，专注外周血管和结构性心脏病三类器械；负责介入导管产品设计开发、设计验证与转移、工艺规范改进、DHF/DMR/SOP文档。20-40k，上海浦东。</t>
+  </si>
+  <si>
+    <t>上海-浦东新区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1948443307.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|介入无植入可降解导管研发，经验不限硕士可投，介入方向+材料/设计技能相关</t>
+  </si>
+  <si>
+    <t>研究80/技能72/学历100/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位以介入无植入（可降解）理念为导向，专注外周血管介入导管研发且经验不限，硕士可投；与本人介入器材方向、材料学与结构设计技能相关，上海为偏好城市，可冲击导管研发。</t>
+  </si>
+  <si>
+    <t>突出介入导管/输送系统设计意向与高分子材料背景；展示结构设计与性能验证能力；补充可降解材料认知以呼应介入无植入理念；强调DHF/DMR文档理解与写作能力。</t>
+  </si>
+  <si>
+    <t>辉沣生物科技（上海）有限公司</t>
+  </si>
+  <si>
+    <t>本科及以上高分子材料/金属材料/材料加工/医疗器械专业，3年以上高分子介入导管挤出经验，熟悉pebax、TPU、PA管材挤出工艺；负责微创介入导管研发与工艺改进、技术文档。公司专注微创介入冷冻消融器械。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1951027143.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配77分【社招】|值得考虑|微创介入导管研发，介入方向+材料学部分匹配，方向非支架主业</t>
+  </si>
+  <si>
+    <t>研究75/技能70/学历78/行业100/企业80</t>
+  </si>
+  <si>
+    <t>璟健康（珂瑞康生物）</t>
+  </si>
+  <si>
+    <t>三类器械研发项目负责人（可吸收生物材料）</t>
+  </si>
+  <si>
+    <t>全日制硕士，材料学/生物工程/化学相关，5年以上三类器械研发经验，可降解/可吸收膜材料经验优先；负责可吸收生物材料器械设计开发全流程、工艺转产、注册送检、动物实验、DHF文件。12-25k，杭州钱塘。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1981916505.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|可吸收/可降解生物材料器械研发，材料学+结构设计+动物实验技能覆盖，方向相关</t>
+  </si>
+  <si>
+    <t>研究85/技能82/学历85/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位涉及可吸收生物材料器械全流程研发与动物实验，与本人可降解材料、结构设计与动物实验技能高度重合；硕士学历符合要求，可作为可降解器械方向的可投研发岗。</t>
+  </si>
+  <si>
+    <t>重点突出可降解/生物材料课题与动物实验经历；量化降解性能、组织相容性数据；强调设计开发文档（DHF）与注册送检认知；弱化5年经验门槛、强化材料学专业匹配。</t>
+  </si>
+  <si>
+    <t>归创通桥医疗科技股份有限公司</t>
+  </si>
+  <si>
+    <t>球囊研发工程师</t>
+  </si>
+  <si>
+    <t>硕士为主，负责外周/神经介入球囊产品（PTA球囊、药物球囊等）研发设计、材料选型及产品验证。10-20k·15薪，杭州余杭。公司为外周及神经血管介入上市龙头。</t>
+  </si>
+  <si>
+    <t>https://www.baidu.com/s?wd=%E5%BD%92%E5%88%9B%E9%80%9A%E6%A1%A5%20%E7%90%83%E5%9B%8A%E7%A0%94%E5%8F%91%E5%B7%A5%E7%A8%8B%E5%B8%88</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|外周/神经血管介入球囊研发，方向（球囊/介介入）+材料/设计技能匹配，上市平台</t>
+  </si>
+  <si>
+    <t>研究80/技能75/学历100/行业100/企业100</t>
+  </si>
+  <si>
+    <t>归创通桥为外周及神经血管介入上市龙头，球囊研发岗与介入器械研究方向相关，硕士可投，上市平台资源优质，可深度参与球囊从材料选型到产品验证全流程。</t>
+  </si>
+  <si>
+    <t>突出介入器械/球囊结构设计与材料选型项目；补充药物球囊/涂层方向理解；量化力学与性能验证数据；强调上市器械企业研发流程认知。</t>
+  </si>
+  <si>
+    <t>蓝帆医疗</t>
+  </si>
+  <si>
+    <t>负责冠脉/心脏支架等介入医疗器械研发设计。材料/机械/生物医学工程专业，硕士学历优先，负责支架结构设计、材料选型及工艺开发，公司以心脏支架为核心高值耗材板块。</t>
+  </si>
+  <si>
+    <t>淄博/上海</t>
+  </si>
+  <si>
+    <t>http://www.baidu.com/link?url=yYvqK1ftjzckF67jEcfNYOtq0OZ2KkuhMaSPcjopsSlqdq_zzvbOG2-0IqFL78U_N3wGeLA8c36SM4DkmRE6iaJnjMkydX1M8k3WjMPaugDEjY77RvXyzkl1EdQWE-g99RWmTvdVfnhEyif-ht0ucV4aqNHfYca6FCL0yEakqYi</t>
+  </si>
+  <si>
+    <t>智能匹配88分【社招】|强烈推荐|冠脉心脏支架研发，方向（支架）+材料学/设计技能匹配，上市集团平台</t>
+  </si>
+  <si>
+    <t>研究87/技能78/学历95/行业100/企业100</t>
+  </si>
+  <si>
+    <t>蓝帆为心脏支架高值耗材上市集团，支架研发岗与硕士血管支架研究方向直接对口，材料/机械/生医工程背景合适，硕士优先，平台大且研发主线清晰。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计、材料选型与力学评价项目；补充可降解/药物涂层方向背景；量化支架性能测试数据；强调上市企业三类器械研发流程理解。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -2887,7 +3103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6929,6 +7145,348 @@
       </c>
       <c r="L106" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>773</v>
+      </c>
+      <c r="B107" t="s">
+        <v>774</v>
+      </c>
+      <c r="C107" t="s">
+        <v>775</v>
+      </c>
+      <c r="D107" t="s">
+        <v>776</v>
+      </c>
+      <c r="E107" t="s">
+        <v>777</v>
+      </c>
+      <c r="F107" t="s">
+        <v>778</v>
+      </c>
+      <c r="G107">
+        <v>9</v>
+      </c>
+      <c r="H107" t="s">
+        <v>779</v>
+      </c>
+      <c r="I107">
+        <v>90</v>
+      </c>
+      <c r="J107" t="s">
+        <v>780</v>
+      </c>
+      <c r="K107" t="s">
+        <v>781</v>
+      </c>
+      <c r="L107" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>773</v>
+      </c>
+      <c r="B108" t="s">
+        <v>774</v>
+      </c>
+      <c r="C108" t="s">
+        <v>783</v>
+      </c>
+      <c r="D108" t="s">
+        <v>784</v>
+      </c>
+      <c r="E108" t="s">
+        <v>785</v>
+      </c>
+      <c r="F108" t="s">
+        <v>786</v>
+      </c>
+      <c r="G108">
+        <v>9</v>
+      </c>
+      <c r="H108" t="s">
+        <v>787</v>
+      </c>
+      <c r="I108">
+        <v>85</v>
+      </c>
+      <c r="J108" t="s">
+        <v>788</v>
+      </c>
+      <c r="K108" t="s">
+        <v>789</v>
+      </c>
+      <c r="L108" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>773</v>
+      </c>
+      <c r="B109" t="s">
+        <v>791</v>
+      </c>
+      <c r="C109" t="s">
+        <v>610</v>
+      </c>
+      <c r="D109" t="s">
+        <v>792</v>
+      </c>
+      <c r="E109" t="s">
+        <v>793</v>
+      </c>
+      <c r="F109" t="s">
+        <v>794</v>
+      </c>
+      <c r="G109">
+        <v>8</v>
+      </c>
+      <c r="H109" t="s">
+        <v>795</v>
+      </c>
+      <c r="I109">
+        <v>84</v>
+      </c>
+      <c r="J109" t="s">
+        <v>796</v>
+      </c>
+      <c r="K109" t="s">
+        <v>797</v>
+      </c>
+      <c r="L109" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>773</v>
+      </c>
+      <c r="B110" t="s">
+        <v>799</v>
+      </c>
+      <c r="C110" t="s">
+        <v>800</v>
+      </c>
+      <c r="D110" t="s">
+        <v>801</v>
+      </c>
+      <c r="E110" t="s">
+        <v>793</v>
+      </c>
+      <c r="F110" t="s">
+        <v>802</v>
+      </c>
+      <c r="G110">
+        <v>9</v>
+      </c>
+      <c r="H110" t="s">
+        <v>803</v>
+      </c>
+      <c r="I110">
+        <v>85</v>
+      </c>
+      <c r="J110" t="s">
+        <v>804</v>
+      </c>
+      <c r="K110" t="s">
+        <v>805</v>
+      </c>
+      <c r="L110" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>773</v>
+      </c>
+      <c r="B111" t="s">
+        <v>807</v>
+      </c>
+      <c r="C111" t="s">
+        <v>808</v>
+      </c>
+      <c r="D111" t="s">
+        <v>809</v>
+      </c>
+      <c r="E111" t="s">
+        <v>810</v>
+      </c>
+      <c r="F111" t="s">
+        <v>811</v>
+      </c>
+      <c r="G111">
+        <v>8</v>
+      </c>
+      <c r="H111" t="s">
+        <v>812</v>
+      </c>
+      <c r="I111">
+        <v>83</v>
+      </c>
+      <c r="J111" t="s">
+        <v>813</v>
+      </c>
+      <c r="K111" t="s">
+        <v>814</v>
+      </c>
+      <c r="L111" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>773</v>
+      </c>
+      <c r="B112" t="s">
+        <v>816</v>
+      </c>
+      <c r="C112" t="s">
+        <v>110</v>
+      </c>
+      <c r="D112" t="s">
+        <v>817</v>
+      </c>
+      <c r="E112" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" t="s">
+        <v>818</v>
+      </c>
+      <c r="G112">
+        <v>8</v>
+      </c>
+      <c r="H112" t="s">
+        <v>819</v>
+      </c>
+      <c r="I112">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s">
+        <v>820</v>
+      </c>
+      <c r="K112" t="s">
+        <v>79</v>
+      </c>
+      <c r="L112" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>773</v>
+      </c>
+      <c r="B113" t="s">
+        <v>821</v>
+      </c>
+      <c r="C113" t="s">
+        <v>822</v>
+      </c>
+      <c r="D113" t="s">
+        <v>823</v>
+      </c>
+      <c r="E113" t="s">
+        <v>777</v>
+      </c>
+      <c r="F113" t="s">
+        <v>824</v>
+      </c>
+      <c r="G113">
+        <v>9</v>
+      </c>
+      <c r="H113" t="s">
+        <v>825</v>
+      </c>
+      <c r="I113">
+        <v>85</v>
+      </c>
+      <c r="J113" t="s">
+        <v>826</v>
+      </c>
+      <c r="K113" t="s">
+        <v>827</v>
+      </c>
+      <c r="L113" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>773</v>
+      </c>
+      <c r="B114" t="s">
+        <v>829</v>
+      </c>
+      <c r="C114" t="s">
+        <v>830</v>
+      </c>
+      <c r="D114" t="s">
+        <v>831</v>
+      </c>
+      <c r="E114" t="s">
+        <v>785</v>
+      </c>
+      <c r="F114" t="s">
+        <v>832</v>
+      </c>
+      <c r="G114">
+        <v>9</v>
+      </c>
+      <c r="H114" t="s">
+        <v>833</v>
+      </c>
+      <c r="I114">
+        <v>86</v>
+      </c>
+      <c r="J114" t="s">
+        <v>834</v>
+      </c>
+      <c r="K114" t="s">
+        <v>835</v>
+      </c>
+      <c r="L114" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>773</v>
+      </c>
+      <c r="B115" t="s">
+        <v>837</v>
+      </c>
+      <c r="C115" t="s">
+        <v>610</v>
+      </c>
+      <c r="D115" t="s">
+        <v>838</v>
+      </c>
+      <c r="E115" t="s">
+        <v>839</v>
+      </c>
+      <c r="F115" t="s">
+        <v>840</v>
+      </c>
+      <c r="G115">
+        <v>9</v>
+      </c>
+      <c r="H115" t="s">
+        <v>841</v>
+      </c>
+      <c r="I115">
+        <v>88</v>
+      </c>
+      <c r="J115" t="s">
+        <v>842</v>
+      </c>
+      <c r="K115" t="s">
+        <v>843</v>
+      </c>
+      <c r="L115" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -6962,7 +7520,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>773</v>
+        <v>845</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6971,16 +7529,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>774</v>
+        <v>846</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>775</v>
+        <v>847</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>776</v>
+        <v>848</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>777</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6994,13 +7552,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>778</v>
+        <v>850</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>779</v>
+        <v>851</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>780</v>
+        <v>852</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -7028,7 +7586,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7043,7 +7601,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>785</v>
+        <v>857</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7053,31 +7611,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>786</v>
+        <v>858</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>787</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="B4">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>789</v>
+        <v>861</v>
       </c>
       <c r="B5" t="s">
-        <v>790</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>791</v>
+        <v>863</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -7085,7 +7643,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>792</v>
+        <v>864</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -7093,23 +7651,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>793</v>
+        <v>865</v>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>794</v>
+        <v>866</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>795</v>
+        <v>867</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -7117,15 +7675,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>796</v>
+        <v>868</v>
       </c>
       <c r="B11" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>797</v>
+        <v>869</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -7135,15 +7693,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>798</v>
+        <v>870</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>799</v>
+        <v>871</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>800</v>
+        <v>872</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -7151,23 +7709,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>801</v>
+        <v>873</v>
       </c>
       <c r="B17" s="5">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>802</v>
+        <v>874</v>
       </c>
       <c r="B18" s="5">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>803</v>
+        <v>875</v>
       </c>
       <c r="B19" s="5">
         <v>4</v>
@@ -7175,7 +7733,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>804</v>
+        <v>876</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -7183,7 +7741,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>805</v>
+        <v>877</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -7191,7 +7749,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>806</v>
+        <v>878</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -7199,7 +7757,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>807</v>
+        <v>879</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -7207,7 +7765,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -7215,7 +7773,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>809</v>
+        <v>881</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -7223,7 +7781,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>810</v>
+        <v>882</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -7235,7 +7793,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>811</v>
+        <v>883</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -7253,7 +7811,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>812</v>
+        <v>884</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -8564,25 +9122,25 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>774</v>
       </c>
       <c r="D80" t="s">
-        <v>73</v>
+        <v>775</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="F80" t="s">
-        <v>76</v>
+        <v>778</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H80" t="s">
-        <v>77</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8590,25 +9148,25 @@
         <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C81" t="s">
-        <v>80</v>
+        <v>774</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>783</v>
       </c>
       <c r="E81" t="s">
-        <v>25</v>
+        <v>785</v>
       </c>
       <c r="F81" t="s">
-        <v>83</v>
+        <v>786</v>
       </c>
       <c r="G81">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H81" t="s">
-        <v>84</v>
+        <v>787</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8616,25 +9174,25 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>799</v>
       </c>
       <c r="D82" t="s">
-        <v>104</v>
+        <v>800</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>793</v>
       </c>
       <c r="F82" t="s">
-        <v>107</v>
+        <v>802</v>
       </c>
       <c r="G82">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H82" t="s">
-        <v>108</v>
+        <v>803</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8642,25 +9200,25 @@
         <v>54</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>821</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>822</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>824</v>
       </c>
       <c r="G83">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H83" t="s">
-        <v>113</v>
+        <v>825</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8668,25 +9226,25 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>829</v>
       </c>
       <c r="D84" t="s">
-        <v>116</v>
+        <v>830</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>785</v>
       </c>
       <c r="F84" t="s">
-        <v>118</v>
+        <v>832</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8694,25 +9252,25 @@
         <v>56</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="C85" t="s">
-        <v>121</v>
+        <v>837</v>
       </c>
       <c r="D85" t="s">
-        <v>122</v>
+        <v>610</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>839</v>
       </c>
       <c r="F85" t="s">
-        <v>125</v>
+        <v>840</v>
       </c>
       <c r="G85">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H85" t="s">
-        <v>126</v>
+        <v>841</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8723,22 +9281,22 @@
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="F86" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -8749,22 +9307,22 @@
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -8772,25 +9330,25 @@
         <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="E88" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F88" t="s">
-        <v>210</v>
+        <v>107</v>
       </c>
       <c r="G88">
         <v>8</v>
       </c>
       <c r="H88" t="s">
-        <v>211</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -8798,25 +9356,25 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="D89" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="E89" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="G89">
         <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -8824,25 +9382,25 @@
         <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="E90" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="G90">
         <v>8</v>
       </c>
       <c r="H90" t="s">
-        <v>232</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -8850,25 +9408,25 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>236</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="F91" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -8876,25 +9434,25 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="D92" t="s">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F92" t="s">
-        <v>243</v>
+        <v>148</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>244</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -8902,10 +9460,10 @@
         <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="D93" t="s">
         <v>154</v>
@@ -8920,7 +9478,7 @@
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>247</v>
+        <v>157</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -8931,22 +9489,22 @@
         <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="D94" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F94" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -8957,22 +9515,22 @@
         <v>159</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="D95" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="E95" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="F95" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -8983,22 +9541,22 @@
         <v>159</v>
       </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="D96" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="E96" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="F96" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -9009,22 +9567,22 @@
         <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="D97" t="s">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F97" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -9035,22 +9593,22 @@
         <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="D98" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="E98" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -9058,25 +9616,25 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="D99" t="s">
-        <v>316</v>
+        <v>154</v>
       </c>
       <c r="E99" t="s">
-        <v>318</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>319</v>
+        <v>156</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -9084,25 +9642,25 @@
         <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C100" t="s">
-        <v>338</v>
+        <v>248</v>
       </c>
       <c r="D100" t="s">
-        <v>339</v>
+        <v>249</v>
       </c>
       <c r="E100" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>342</v>
+        <v>251</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>343</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -9110,25 +9668,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C101" t="s">
-        <v>347</v>
+        <v>254</v>
       </c>
       <c r="D101" t="s">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="E101" t="s">
-        <v>98</v>
+        <v>257</v>
       </c>
       <c r="F101" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -9136,25 +9694,25 @@
         <v>73</v>
       </c>
       <c r="B102" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C102" t="s">
-        <v>353</v>
+        <v>261</v>
       </c>
       <c r="D102" t="s">
-        <v>362</v>
+        <v>122</v>
       </c>
       <c r="E102" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
       <c r="F102" t="s">
-        <v>364</v>
+        <v>263</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -9162,25 +9720,25 @@
         <v>74</v>
       </c>
       <c r="B103" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C103" t="s">
-        <v>377</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
-        <v>378</v>
+        <v>267</v>
       </c>
       <c r="E103" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>381</v>
+        <v>58</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>382</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -9188,25 +9746,25 @@
         <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C104" t="s">
-        <v>144</v>
+        <v>277</v>
       </c>
       <c r="D104" t="s">
-        <v>394</v>
+        <v>278</v>
       </c>
       <c r="E104" t="s">
-        <v>396</v>
+        <v>280</v>
       </c>
       <c r="F104" t="s">
-        <v>397</v>
+        <v>281</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>398</v>
+        <v>282</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -9214,25 +9772,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C105" t="s">
-        <v>410</v>
+        <v>315</v>
       </c>
       <c r="D105" t="s">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="E105" t="s">
-        <v>66</v>
+        <v>318</v>
       </c>
       <c r="F105" t="s">
-        <v>413</v>
+        <v>319</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>414</v>
+        <v>320</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -9240,25 +9798,25 @@
         <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C106" t="s">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="D106" t="s">
-        <v>419</v>
+        <v>339</v>
       </c>
       <c r="E106" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="F106" t="s">
-        <v>421</v>
+        <v>342</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>422</v>
+        <v>343</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -9266,25 +9824,25 @@
         <v>78</v>
       </c>
       <c r="B107" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s">
-        <v>424</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s">
-        <v>425</v>
+        <v>348</v>
       </c>
       <c r="E107" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F107" t="s">
-        <v>427</v>
+        <v>350</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>428</v>
+        <v>351</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -9292,25 +9850,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C108" t="s">
-        <v>430</v>
+        <v>353</v>
       </c>
       <c r="D108" t="s">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="F108" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>434</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -9318,25 +9876,25 @@
         <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C109" t="s">
-        <v>483</v>
+        <v>377</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>378</v>
       </c>
       <c r="E109" t="s">
-        <v>485</v>
+        <v>380</v>
       </c>
       <c r="F109" t="s">
-        <v>486</v>
+        <v>381</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>487</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -9344,25 +9902,25 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C110" t="s">
-        <v>491</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>492</v>
+        <v>394</v>
       </c>
       <c r="E110" t="s">
-        <v>75</v>
+        <v>396</v>
       </c>
       <c r="F110" t="s">
-        <v>494</v>
+        <v>397</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>495</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -9370,25 +9928,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C111" t="s">
-        <v>499</v>
+        <v>410</v>
       </c>
       <c r="D111" t="s">
-        <v>500</v>
+        <v>411</v>
       </c>
       <c r="E111" t="s">
-        <v>502</v>
+        <v>66</v>
       </c>
       <c r="F111" t="s">
-        <v>503</v>
+        <v>413</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>504</v>
+        <v>414</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -9396,25 +9954,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C112" t="s">
-        <v>532</v>
+        <v>418</v>
       </c>
       <c r="D112" t="s">
-        <v>533</v>
+        <v>419</v>
       </c>
       <c r="E112" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="F112" t="s">
-        <v>536</v>
+        <v>421</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>537</v>
+        <v>422</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -9422,25 +9980,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C113" t="s">
-        <v>550</v>
+        <v>424</v>
       </c>
       <c r="D113" t="s">
-        <v>551</v>
+        <v>425</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F113" t="s">
-        <v>553</v>
+        <v>427</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>554</v>
+        <v>428</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -9448,25 +10006,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="C114" t="s">
-        <v>578</v>
+        <v>430</v>
       </c>
       <c r="D114" t="s">
-        <v>579</v>
+        <v>431</v>
       </c>
       <c r="E114" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F114" t="s">
-        <v>581</v>
+        <v>433</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>582</v>
+        <v>434</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -9474,25 +10032,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C115" t="s">
-        <v>584</v>
+        <v>483</v>
       </c>
       <c r="D115" t="s">
-        <v>585</v>
+        <v>122</v>
       </c>
       <c r="E115" t="s">
-        <v>587</v>
+        <v>485</v>
       </c>
       <c r="F115" t="s">
-        <v>588</v>
+        <v>486</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>589</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -9500,25 +10058,25 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C116" t="s">
-        <v>601</v>
+        <v>491</v>
       </c>
       <c r="D116" t="s">
-        <v>602</v>
+        <v>492</v>
       </c>
       <c r="E116" t="s">
         <v>75</v>
       </c>
       <c r="F116" t="s">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>605</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -9526,25 +10084,25 @@
         <v>88</v>
       </c>
       <c r="B117" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C117" t="s">
-        <v>616</v>
+        <v>499</v>
       </c>
       <c r="D117" t="s">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="E117" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F117" t="s">
-        <v>618</v>
+        <v>503</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>619</v>
+        <v>504</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -9552,25 +10110,25 @@
         <v>89</v>
       </c>
       <c r="B118" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C118" t="s">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="D118" t="s">
-        <v>623</v>
+        <v>533</v>
       </c>
       <c r="E118" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="F118" t="s">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>625</v>
+        <v>537</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -9578,25 +10136,25 @@
         <v>90</v>
       </c>
       <c r="B119" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C119" t="s">
-        <v>643</v>
+        <v>550</v>
       </c>
       <c r="D119" t="s">
-        <v>644</v>
+        <v>551</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>618</v>
+        <v>553</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>646</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -9604,25 +10162,25 @@
         <v>91</v>
       </c>
       <c r="B120" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C120" t="s">
-        <v>650</v>
+        <v>578</v>
       </c>
       <c r="D120" t="s">
-        <v>651</v>
+        <v>579</v>
       </c>
       <c r="E120" t="s">
         <v>66</v>
       </c>
       <c r="F120" t="s">
-        <v>653</v>
+        <v>581</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>654</v>
+        <v>582</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -9630,25 +10188,25 @@
         <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C121" t="s">
-        <v>658</v>
+        <v>584</v>
       </c>
       <c r="D121" t="s">
-        <v>659</v>
+        <v>585</v>
       </c>
       <c r="E121" t="s">
-        <v>661</v>
+        <v>587</v>
       </c>
       <c r="F121" t="s">
-        <v>662</v>
+        <v>588</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>663</v>
+        <v>589</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -9659,10 +10217,10 @@
         <v>591</v>
       </c>
       <c r="C122" t="s">
-        <v>666</v>
+        <v>601</v>
       </c>
       <c r="D122" t="s">
-        <v>667</v>
+        <v>602</v>
       </c>
       <c r="E122" t="s">
         <v>75</v>
@@ -9674,7 +10232,7 @@
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>669</v>
+        <v>605</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -9685,22 +10243,22 @@
         <v>591</v>
       </c>
       <c r="C123" t="s">
-        <v>673</v>
+        <v>616</v>
       </c>
       <c r="D123" t="s">
-        <v>674</v>
+        <v>610</v>
       </c>
       <c r="E123" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>676</v>
+        <v>618</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>677</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -9708,25 +10266,25 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C124" t="s">
-        <v>714</v>
+        <v>557</v>
       </c>
       <c r="D124" t="s">
-        <v>715</v>
+        <v>623</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>717</v>
+        <v>625</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -9734,25 +10292,25 @@
         <v>96</v>
       </c>
       <c r="B125" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C125" t="s">
-        <v>721</v>
+        <v>643</v>
       </c>
       <c r="D125" t="s">
-        <v>722</v>
+        <v>644</v>
       </c>
       <c r="E125" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>724</v>
+        <v>618</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>725</v>
+        <v>646</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -9760,25 +10318,25 @@
         <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C126" t="s">
-        <v>729</v>
+        <v>650</v>
       </c>
       <c r="D126" t="s">
-        <v>730</v>
+        <v>651</v>
       </c>
       <c r="E126" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="F126" t="s">
-        <v>732</v>
+        <v>653</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>733</v>
+        <v>654</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -9786,25 +10344,25 @@
         <v>98</v>
       </c>
       <c r="B127" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C127" t="s">
-        <v>736</v>
+        <v>658</v>
       </c>
       <c r="D127" t="s">
-        <v>737</v>
+        <v>659</v>
       </c>
       <c r="E127" t="s">
-        <v>739</v>
+        <v>661</v>
       </c>
       <c r="F127" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>740</v>
+        <v>663</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -9812,25 +10370,25 @@
         <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C128" t="s">
-        <v>744</v>
+        <v>666</v>
       </c>
       <c r="D128" t="s">
-        <v>745</v>
+        <v>667</v>
       </c>
       <c r="E128" t="s">
-        <v>747</v>
+        <v>75</v>
       </c>
       <c r="F128" t="s">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>749</v>
+        <v>669</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -9838,25 +10396,25 @@
         <v>100</v>
       </c>
       <c r="B129" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C129" t="s">
-        <v>753</v>
+        <v>673</v>
       </c>
       <c r="D129" t="s">
-        <v>754</v>
+        <v>674</v>
       </c>
       <c r="E129" t="s">
-        <v>756</v>
+        <v>66</v>
       </c>
       <c r="F129" t="s">
-        <v>757</v>
+        <v>676</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>758</v>
+        <v>677</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -9867,22 +10425,22 @@
         <v>697</v>
       </c>
       <c r="C130" t="s">
-        <v>760</v>
+        <v>714</v>
       </c>
       <c r="D130" t="s">
-        <v>761</v>
+        <v>715</v>
       </c>
       <c r="E130" t="s">
-        <v>763</v>
+        <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>764</v>
+        <v>604</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>765</v>
+        <v>717</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -9890,25 +10448,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="C131" t="s">
-        <v>271</v>
+        <v>721</v>
       </c>
       <c r="D131" t="s">
-        <v>272</v>
+        <v>722</v>
       </c>
       <c r="E131" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>274</v>
+        <v>724</v>
       </c>
       <c r="G131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>275</v>
+        <v>725</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -9916,25 +10474,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="C132" t="s">
-        <v>681</v>
+        <v>729</v>
       </c>
       <c r="D132" t="s">
-        <v>682</v>
+        <v>730</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="F132" t="s">
-        <v>684</v>
+        <v>732</v>
       </c>
       <c r="G132">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>685</v>
+        <v>733</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -9942,25 +10500,25 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="C133" t="s">
-        <v>689</v>
+        <v>736</v>
       </c>
       <c r="D133" t="s">
-        <v>690</v>
+        <v>737</v>
       </c>
       <c r="E133" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="F133" t="s">
-        <v>692</v>
+        <v>604</v>
       </c>
       <c r="G133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>693</v>
+        <v>740</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -9971,21 +10529,255 @@
         <v>697</v>
       </c>
       <c r="C134" t="s">
+        <v>744</v>
+      </c>
+      <c r="D134" t="s">
+        <v>745</v>
+      </c>
+      <c r="E134" t="s">
+        <v>747</v>
+      </c>
+      <c r="F134" t="s">
+        <v>748</v>
+      </c>
+      <c r="G134">
+        <v>8</v>
+      </c>
+      <c r="H134" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>106</v>
+      </c>
+      <c r="B135" t="s">
+        <v>697</v>
+      </c>
+      <c r="C135" t="s">
+        <v>753</v>
+      </c>
+      <c r="D135" t="s">
+        <v>754</v>
+      </c>
+      <c r="E135" t="s">
+        <v>756</v>
+      </c>
+      <c r="F135" t="s">
+        <v>757</v>
+      </c>
+      <c r="G135">
+        <v>8</v>
+      </c>
+      <c r="H135" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>107</v>
+      </c>
+      <c r="B136" t="s">
+        <v>697</v>
+      </c>
+      <c r="C136" t="s">
+        <v>760</v>
+      </c>
+      <c r="D136" t="s">
+        <v>761</v>
+      </c>
+      <c r="E136" t="s">
+        <v>763</v>
+      </c>
+      <c r="F136" t="s">
+        <v>764</v>
+      </c>
+      <c r="G136">
+        <v>8</v>
+      </c>
+      <c r="H136" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>108</v>
+      </c>
+      <c r="B137" t="s">
+        <v>773</v>
+      </c>
+      <c r="C137" t="s">
+        <v>791</v>
+      </c>
+      <c r="D137" t="s">
+        <v>610</v>
+      </c>
+      <c r="E137" t="s">
+        <v>793</v>
+      </c>
+      <c r="F137" t="s">
+        <v>794</v>
+      </c>
+      <c r="G137">
+        <v>8</v>
+      </c>
+      <c r="H137" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>109</v>
+      </c>
+      <c r="B138" t="s">
+        <v>773</v>
+      </c>
+      <c r="C138" t="s">
+        <v>807</v>
+      </c>
+      <c r="D138" t="s">
+        <v>808</v>
+      </c>
+      <c r="E138" t="s">
+        <v>810</v>
+      </c>
+      <c r="F138" t="s">
+        <v>811</v>
+      </c>
+      <c r="G138">
+        <v>8</v>
+      </c>
+      <c r="H138" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>110</v>
+      </c>
+      <c r="B139" t="s">
+        <v>773</v>
+      </c>
+      <c r="C139" t="s">
+        <v>816</v>
+      </c>
+      <c r="D139" t="s">
+        <v>110</v>
+      </c>
+      <c r="E139" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139" t="s">
+        <v>818</v>
+      </c>
+      <c r="G139">
+        <v>8</v>
+      </c>
+      <c r="H139" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>111</v>
+      </c>
+      <c r="B140" t="s">
+        <v>159</v>
+      </c>
+      <c r="C140" t="s">
+        <v>271</v>
+      </c>
+      <c r="D140" t="s">
+        <v>272</v>
+      </c>
+      <c r="E140" t="s">
+        <v>75</v>
+      </c>
+      <c r="F140" t="s">
+        <v>274</v>
+      </c>
+      <c r="G140">
+        <v>7</v>
+      </c>
+      <c r="H140" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>112</v>
+      </c>
+      <c r="B141" t="s">
+        <v>591</v>
+      </c>
+      <c r="C141" t="s">
+        <v>681</v>
+      </c>
+      <c r="D141" t="s">
+        <v>682</v>
+      </c>
+      <c r="E141" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" t="s">
+        <v>684</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>113</v>
+      </c>
+      <c r="B142" t="s">
+        <v>591</v>
+      </c>
+      <c r="C142" t="s">
+        <v>689</v>
+      </c>
+      <c r="D142" t="s">
+        <v>690</v>
+      </c>
+      <c r="E142" t="s">
+        <v>66</v>
+      </c>
+      <c r="F142" t="s">
+        <v>692</v>
+      </c>
+      <c r="G142">
+        <v>7</v>
+      </c>
+      <c r="H142" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>114</v>
+      </c>
+      <c r="B143" t="s">
+        <v>697</v>
+      </c>
+      <c r="C143" t="s">
         <v>767</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D143" t="s">
         <v>768</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E143" t="s">
         <v>25</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F143" t="s">
         <v>770</v>
       </c>
-      <c r="G134">
+      <c r="G143">
         <v>7</v>
       </c>
-      <c r="H134" t="s">
+      <c r="H143" t="s">
         <v>771</v>
       </c>
     </row>
@@ -10002,7 +10794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10019,10 +10811,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>781</v>
+        <v>853</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>782</v>
+        <v>854</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -10049,12 +10841,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>783</v>
+        <v>855</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -10089,7 +10881,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -10124,7 +10916,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -10159,7 +10951,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -10194,7 +10986,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -10229,7 +11021,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -10264,7 +11056,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -10299,7 +11091,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -10334,7 +11126,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -10369,7 +11161,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -10404,7 +11196,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -10439,7 +11231,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -10474,7 +11266,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -10509,7 +11301,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -10544,7 +11336,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -10579,7 +11371,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -10614,7 +11406,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -10649,7 +11441,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -10684,7 +11476,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -10719,7 +11511,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -10754,7 +11546,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -10789,719 +11581,719 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B23">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>774</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>775</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>777</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>778</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
+        <v>780</v>
       </c>
       <c r="I23" t="s">
-        <v>142</v>
+        <v>781</v>
       </c>
       <c r="J23" t="s">
-        <v>143</v>
+        <v>782</v>
       </c>
       <c r="K23" t="s">
-        <v>137</v>
+        <v>776</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B24">
         <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="G24" t="s">
-        <v>438</v>
+        <v>139</v>
       </c>
       <c r="H24" t="s">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="I24" t="s">
-        <v>441</v>
+        <v>142</v>
       </c>
       <c r="J24" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="K24" t="s">
-        <v>437</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B25">
         <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D25" t="s">
-        <v>557</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>564</v>
+        <v>436</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H25" t="s">
-        <v>567</v>
+        <v>440</v>
       </c>
       <c r="I25" t="s">
-        <v>568</v>
+        <v>441</v>
       </c>
       <c r="J25" t="s">
-        <v>569</v>
+        <v>442</v>
       </c>
       <c r="K25" t="s">
-        <v>565</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B26">
         <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D26" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="E26" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="F26" t="s">
-        <v>595</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>596</v>
+        <v>468</v>
       </c>
       <c r="H26" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="I26" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="J26" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="K26" t="s">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B27">
         <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D27" t="s">
-        <v>707</v>
+        <v>592</v>
       </c>
       <c r="E27" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F27" t="s">
-        <v>318</v>
+        <v>595</v>
       </c>
       <c r="G27" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H27" t="s">
-        <v>711</v>
+        <v>598</v>
       </c>
       <c r="I27" t="s">
-        <v>712</v>
+        <v>599</v>
       </c>
       <c r="J27" t="s">
-        <v>713</v>
+        <v>600</v>
       </c>
       <c r="K27" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B28">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>697</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>707</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>708</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>604</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>711</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>712</v>
       </c>
       <c r="J28" t="s">
-        <v>38</v>
+        <v>713</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>709</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B29">
         <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J29" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K29" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B30">
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E30" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H30" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J30" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K30" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B31">
         <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E31" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H31" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I31" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K31" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B32">
         <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F32" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H32" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I32" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B33">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>698</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>699</v>
       </c>
       <c r="F33" t="s">
-        <v>130</v>
+        <v>701</v>
       </c>
       <c r="G33" t="s">
-        <v>131</v>
+        <v>702</v>
       </c>
       <c r="H33" t="s">
-        <v>188</v>
+        <v>704</v>
       </c>
       <c r="I33" t="s">
-        <v>189</v>
+        <v>705</v>
       </c>
       <c r="J33" t="s">
-        <v>190</v>
+        <v>706</v>
       </c>
       <c r="K33" t="s">
-        <v>186</v>
+        <v>700</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B34">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D34" t="s">
-        <v>353</v>
+        <v>837</v>
       </c>
       <c r="E34" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="F34" t="s">
-        <v>356</v>
+        <v>839</v>
       </c>
       <c r="G34" t="s">
-        <v>357</v>
+        <v>840</v>
       </c>
       <c r="H34" t="s">
-        <v>359</v>
+        <v>842</v>
       </c>
       <c r="I34" t="s">
-        <v>360</v>
+        <v>843</v>
       </c>
       <c r="J34" t="s">
-        <v>361</v>
+        <v>844</v>
       </c>
       <c r="K34" t="s">
-        <v>355</v>
+        <v>838</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B35">
         <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="J35" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="K35" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B36">
         <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E36" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G36" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H36" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I36" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K36" t="s">
-        <v>464</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B37">
         <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="F37" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I37" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B38">
         <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>570</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>571</v>
+        <v>463</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>573</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
-        <v>575</v>
+        <v>456</v>
       </c>
       <c r="I38" t="s">
-        <v>576</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s">
-        <v>577</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s">
-        <v>572</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B39">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D39" t="s">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>370</v>
+        <v>508</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>510</v>
       </c>
       <c r="G39" t="s">
-        <v>372</v>
+        <v>511</v>
       </c>
       <c r="H39" t="s">
-        <v>374</v>
+        <v>513</v>
       </c>
       <c r="I39" t="s">
-        <v>375</v>
+        <v>514</v>
       </c>
       <c r="J39" t="s">
-        <v>376</v>
+        <v>515</v>
       </c>
       <c r="K39" t="s">
-        <v>371</v>
+        <v>509</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B40">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="E40" t="s">
-        <v>457</v>
+        <v>571</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="H40" t="s">
-        <v>460</v>
+        <v>575</v>
       </c>
       <c r="I40" t="s">
-        <v>461</v>
+        <v>576</v>
       </c>
       <c r="J40" t="s">
-        <v>462</v>
+        <v>577</v>
       </c>
       <c r="K40" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B41">
         <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D41" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="E41" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="H41" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="I41" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J41" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="K41" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B42">
         <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D42" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F42" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="G42" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="H42" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="I42" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J42" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="K42" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B43">
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D43" t="s">
-        <v>557</v>
+        <v>322</v>
       </c>
       <c r="E43" t="s">
-        <v>558</v>
+        <v>466</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -11510,91 +12302,91 @@
         <v>468</v>
       </c>
       <c r="H43" t="s">
-        <v>561</v>
+        <v>470</v>
       </c>
       <c r="I43" t="s">
-        <v>562</v>
+        <v>471</v>
       </c>
       <c r="J43" t="s">
-        <v>563</v>
+        <v>472</v>
       </c>
       <c r="K43" t="s">
-        <v>559</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B44">
         <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D44" t="s">
-        <v>609</v>
+        <v>541</v>
       </c>
       <c r="E44" t="s">
-        <v>610</v>
+        <v>542</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G44" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="H44" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="I44" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="J44" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="K44" t="s">
-        <v>611</v>
+        <v>543</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B45">
         <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D45" t="s">
-        <v>627</v>
+        <v>557</v>
       </c>
       <c r="E45" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>630</v>
+        <v>468</v>
       </c>
       <c r="H45" t="s">
-        <v>632</v>
+        <v>561</v>
       </c>
       <c r="I45" t="s">
-        <v>633</v>
+        <v>562</v>
       </c>
       <c r="J45" t="s">
-        <v>634</v>
+        <v>563</v>
       </c>
       <c r="K45" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B46">
         <v>86</v>
@@ -11603,902 +12395,1182 @@
         <v>591</v>
       </c>
       <c r="D46" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="E46" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>638</v>
+        <v>604</v>
       </c>
       <c r="H46" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="I46" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="J46" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="K46" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B47">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>627</v>
       </c>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>628</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="H47" t="s">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>633</v>
       </c>
       <c r="J47" t="s">
-        <v>62</v>
+        <v>634</v>
       </c>
       <c r="K47" t="s">
-        <v>57</v>
+        <v>629</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B48">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="E48" t="s">
-        <v>89</v>
+        <v>636</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>131</v>
+        <v>638</v>
       </c>
       <c r="H48" t="s">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="I48" t="s">
-        <v>134</v>
+        <v>641</v>
       </c>
       <c r="J48" t="s">
-        <v>135</v>
+        <v>642</v>
       </c>
       <c r="K48" t="s">
-        <v>129</v>
+        <v>637</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B49">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>829</v>
       </c>
       <c r="E49" t="s">
-        <v>308</v>
+        <v>830</v>
       </c>
       <c r="F49" t="s">
-        <v>147</v>
+        <v>785</v>
       </c>
       <c r="G49" t="s">
-        <v>310</v>
+        <v>832</v>
       </c>
       <c r="H49" t="s">
-        <v>312</v>
+        <v>834</v>
       </c>
       <c r="I49" t="s">
-        <v>313</v>
+        <v>835</v>
       </c>
       <c r="J49" t="s">
-        <v>314</v>
+        <v>836</v>
       </c>
       <c r="K49" t="s">
-        <v>309</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B50">
         <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
         <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>403</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>405</v>
+        <v>58</v>
       </c>
       <c r="H50" t="s">
-        <v>407</v>
+        <v>60</v>
       </c>
       <c r="I50" t="s">
-        <v>408</v>
+        <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>409</v>
+        <v>62</v>
       </c>
       <c r="K50" t="s">
-        <v>404</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B51">
         <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>474</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="F51" t="s">
-        <v>477</v>
+        <v>130</v>
       </c>
       <c r="G51" t="s">
-        <v>478</v>
+        <v>131</v>
       </c>
       <c r="H51" t="s">
-        <v>480</v>
+        <v>133</v>
       </c>
       <c r="I51" t="s">
-        <v>481</v>
+        <v>134</v>
       </c>
       <c r="J51" t="s">
-        <v>482</v>
+        <v>135</v>
       </c>
       <c r="K51" t="s">
-        <v>476</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B52">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
         <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>148</v>
+        <v>310</v>
       </c>
       <c r="H52" t="s">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="I52" t="s">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="J52" t="s">
-        <v>152</v>
+        <v>314</v>
       </c>
       <c r="K52" t="s">
-        <v>146</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B53">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D53" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E53" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F53" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H53" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="I53" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="J53" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="K53" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B54">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D54" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
       <c r="E54" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="F54" t="s">
-        <v>66</v>
+        <v>477</v>
       </c>
       <c r="G54" t="s">
-        <v>413</v>
+        <v>478</v>
       </c>
       <c r="H54" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="I54" t="s">
-        <v>416</v>
+        <v>481</v>
       </c>
       <c r="J54" t="s">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="K54" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>856</v>
+      </c>
+      <c r="B55">
+        <v>85</v>
+      </c>
+      <c r="C55" t="s">
+        <v>773</v>
+      </c>
+      <c r="D55" t="s">
+        <v>774</v>
+      </c>
+      <c r="E55" t="s">
+        <v>783</v>
+      </c>
+      <c r="F55" t="s">
+        <v>785</v>
+      </c>
+      <c r="G55" t="s">
+        <v>786</v>
+      </c>
+      <c r="H55" t="s">
+        <v>788</v>
+      </c>
+      <c r="I55" t="s">
+        <v>789</v>
+      </c>
+      <c r="J55" t="s">
+        <v>790</v>
+      </c>
+      <c r="K55" t="s">
         <v>784</v>
-      </c>
-      <c r="B55">
-        <v>84</v>
-      </c>
-      <c r="C55" t="s">
-        <v>473</v>
-      </c>
-      <c r="D55" t="s">
-        <v>483</v>
-      </c>
-      <c r="E55" t="s">
-        <v>122</v>
-      </c>
-      <c r="F55" t="s">
-        <v>485</v>
-      </c>
-      <c r="G55" t="s">
-        <v>486</v>
-      </c>
-      <c r="H55" t="s">
-        <v>488</v>
-      </c>
-      <c r="I55" t="s">
-        <v>489</v>
-      </c>
-      <c r="J55" t="s">
-        <v>490</v>
-      </c>
-      <c r="K55" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B56">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D56" t="s">
-        <v>714</v>
+        <v>799</v>
       </c>
       <c r="E56" t="s">
-        <v>715</v>
+        <v>800</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="G56" t="s">
-        <v>604</v>
+        <v>802</v>
       </c>
       <c r="H56" t="s">
-        <v>718</v>
+        <v>804</v>
       </c>
       <c r="I56" t="s">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="J56" t="s">
-        <v>720</v>
+        <v>806</v>
       </c>
       <c r="K56" t="s">
-        <v>716</v>
+        <v>801</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B57">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C57" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D57" t="s">
-        <v>721</v>
+        <v>821</v>
       </c>
       <c r="E57" t="s">
-        <v>722</v>
+        <v>822</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>777</v>
       </c>
       <c r="G57" t="s">
-        <v>724</v>
+        <v>824</v>
       </c>
       <c r="H57" t="s">
-        <v>726</v>
+        <v>826</v>
       </c>
       <c r="I57" t="s">
-        <v>727</v>
+        <v>827</v>
       </c>
       <c r="J57" t="s">
-        <v>728</v>
+        <v>828</v>
       </c>
       <c r="K57" t="s">
-        <v>723</v>
+        <v>823</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B58">
         <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>697</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>729</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
-        <v>730</v>
+        <v>145</v>
       </c>
       <c r="F58" t="s">
-        <v>535</v>
+        <v>147</v>
       </c>
       <c r="G58" t="s">
-        <v>732</v>
+        <v>148</v>
       </c>
       <c r="H58" t="s">
-        <v>726</v>
+        <v>150</v>
       </c>
       <c r="I58" t="s">
-        <v>734</v>
+        <v>151</v>
       </c>
       <c r="J58" t="s">
-        <v>735</v>
+        <v>152</v>
       </c>
       <c r="K58" t="s">
-        <v>731</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B59">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
         <v>284</v>
       </c>
       <c r="D59" t="s">
-        <v>353</v>
+        <v>144</v>
       </c>
       <c r="E59" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="F59" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="G59" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="H59" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="I59" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="J59" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="K59" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B60">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D60" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="E60" t="s">
-        <v>492</v>
+        <v>411</v>
       </c>
       <c r="F60" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G60" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="H60" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="I60" t="s">
-        <v>497</v>
+        <v>416</v>
       </c>
       <c r="J60" t="s">
-        <v>498</v>
+        <v>417</v>
       </c>
       <c r="K60" t="s">
-        <v>493</v>
+        <v>412</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B61">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
         <v>473</v>
       </c>
       <c r="D61" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="E61" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="F61" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="G61" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="H61" t="s">
-        <v>538</v>
+        <v>488</v>
       </c>
       <c r="I61" t="s">
-        <v>539</v>
+        <v>489</v>
       </c>
       <c r="J61" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="K61" t="s">
-        <v>534</v>
+        <v>484</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B62">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="D62" t="s">
-        <v>643</v>
+        <v>714</v>
       </c>
       <c r="E62" t="s">
-        <v>644</v>
+        <v>715</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="H62" t="s">
-        <v>647</v>
+        <v>718</v>
       </c>
       <c r="I62" t="s">
-        <v>648</v>
+        <v>719</v>
       </c>
       <c r="J62" t="s">
-        <v>649</v>
+        <v>720</v>
       </c>
       <c r="K62" t="s">
-        <v>645</v>
+        <v>716</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B63">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
         <v>697</v>
       </c>
       <c r="D63" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="E63" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="F63" t="s">
-        <v>739</v>
+        <v>25</v>
       </c>
       <c r="G63" t="s">
-        <v>604</v>
+        <v>724</v>
       </c>
       <c r="H63" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="I63" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="J63" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="K63" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B64">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D64" t="s">
-        <v>227</v>
+        <v>729</v>
       </c>
       <c r="E64" t="s">
-        <v>228</v>
+        <v>730</v>
       </c>
       <c r="F64" t="s">
-        <v>230</v>
+        <v>535</v>
       </c>
       <c r="G64" t="s">
-        <v>231</v>
+        <v>732</v>
       </c>
       <c r="H64" t="s">
-        <v>233</v>
+        <v>726</v>
       </c>
       <c r="I64" t="s">
-        <v>234</v>
+        <v>734</v>
       </c>
       <c r="J64" t="s">
-        <v>235</v>
+        <v>735</v>
       </c>
       <c r="K64" t="s">
-        <v>229</v>
+        <v>731</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B65">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>773</v>
       </c>
       <c r="D65" t="s">
-        <v>266</v>
+        <v>791</v>
       </c>
       <c r="E65" t="s">
-        <v>267</v>
+        <v>610</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
+        <v>794</v>
       </c>
       <c r="H65" t="s">
-        <v>270</v>
+        <v>796</v>
       </c>
       <c r="I65" t="s">
-        <v>79</v>
+        <v>797</v>
       </c>
       <c r="J65" t="s">
-        <v>79</v>
+        <v>798</v>
       </c>
       <c r="K65" t="s">
-        <v>268</v>
+        <v>792</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B66">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
         <v>284</v>
       </c>
       <c r="D66" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E66" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="F66" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="G66" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="H66" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="I66" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="J66" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="K66" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B67">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D67" t="s">
-        <v>601</v>
+        <v>491</v>
       </c>
       <c r="E67" t="s">
-        <v>602</v>
+        <v>492</v>
       </c>
       <c r="F67" t="s">
         <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="H67" t="s">
-        <v>606</v>
+        <v>496</v>
       </c>
       <c r="I67" t="s">
-        <v>607</v>
+        <v>497</v>
       </c>
       <c r="J67" t="s">
-        <v>608</v>
+        <v>498</v>
       </c>
       <c r="K67" t="s">
-        <v>603</v>
+        <v>493</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B68">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>532</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="G68" t="s">
-        <v>83</v>
+        <v>536</v>
       </c>
       <c r="H68" t="s">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="I68" t="s">
-        <v>86</v>
+        <v>539</v>
       </c>
       <c r="J68" t="s">
-        <v>87</v>
+        <v>540</v>
       </c>
       <c r="K68" t="s">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B69">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C69" t="s">
-        <v>284</v>
+        <v>591</v>
       </c>
       <c r="D69" t="s">
-        <v>377</v>
+        <v>643</v>
       </c>
       <c r="E69" t="s">
-        <v>378</v>
+        <v>644</v>
       </c>
       <c r="F69" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>381</v>
+        <v>618</v>
       </c>
       <c r="H69" t="s">
-        <v>383</v>
+        <v>647</v>
       </c>
       <c r="I69" t="s">
-        <v>384</v>
+        <v>648</v>
       </c>
       <c r="J69" t="s">
-        <v>385</v>
+        <v>649</v>
       </c>
       <c r="K69" t="s">
-        <v>379</v>
+        <v>645</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B70">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C70" t="s">
-        <v>473</v>
+        <v>697</v>
       </c>
       <c r="D70" t="s">
-        <v>499</v>
+        <v>736</v>
       </c>
       <c r="E70" t="s">
-        <v>500</v>
+        <v>737</v>
       </c>
       <c r="F70" t="s">
-        <v>502</v>
+        <v>739</v>
       </c>
       <c r="G70" t="s">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="H70" t="s">
-        <v>505</v>
+        <v>741</v>
       </c>
       <c r="I70" t="s">
-        <v>506</v>
+        <v>742</v>
       </c>
       <c r="J70" t="s">
-        <v>507</v>
+        <v>743</v>
       </c>
       <c r="K70" t="s">
-        <v>501</v>
+        <v>738</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>784</v>
+        <v>856</v>
       </c>
       <c r="B71">
+        <v>83</v>
+      </c>
+      <c r="C71" t="s">
+        <v>773</v>
+      </c>
+      <c r="D71" t="s">
+        <v>807</v>
+      </c>
+      <c r="E71" t="s">
+        <v>808</v>
+      </c>
+      <c r="F71" t="s">
+        <v>810</v>
+      </c>
+      <c r="G71" t="s">
+        <v>811</v>
+      </c>
+      <c r="H71" t="s">
+        <v>813</v>
+      </c>
+      <c r="I71" t="s">
+        <v>814</v>
+      </c>
+      <c r="J71" t="s">
+        <v>815</v>
+      </c>
+      <c r="K71" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>856</v>
+      </c>
+      <c r="B72">
+        <v>82</v>
+      </c>
+      <c r="C72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" t="s">
+        <v>227</v>
+      </c>
+      <c r="E72" t="s">
+        <v>228</v>
+      </c>
+      <c r="F72" t="s">
+        <v>230</v>
+      </c>
+      <c r="G72" t="s">
+        <v>231</v>
+      </c>
+      <c r="H72" t="s">
+        <v>233</v>
+      </c>
+      <c r="I72" t="s">
+        <v>234</v>
+      </c>
+      <c r="J72" t="s">
+        <v>235</v>
+      </c>
+      <c r="K72" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>856</v>
+      </c>
+      <c r="B73">
+        <v>82</v>
+      </c>
+      <c r="C73" t="s">
+        <v>159</v>
+      </c>
+      <c r="D73" t="s">
+        <v>266</v>
+      </c>
+      <c r="E73" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" t="s">
+        <v>58</v>
+      </c>
+      <c r="H73" t="s">
+        <v>270</v>
+      </c>
+      <c r="I73" t="s">
+        <v>79</v>
+      </c>
+      <c r="J73" t="s">
+        <v>79</v>
+      </c>
+      <c r="K73" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>856</v>
+      </c>
+      <c r="B74">
+        <v>82</v>
+      </c>
+      <c r="C74" t="s">
+        <v>284</v>
+      </c>
+      <c r="D74" t="s">
+        <v>338</v>
+      </c>
+      <c r="E74" t="s">
+        <v>339</v>
+      </c>
+      <c r="F74" t="s">
+        <v>341</v>
+      </c>
+      <c r="G74" t="s">
+        <v>342</v>
+      </c>
+      <c r="H74" t="s">
+        <v>344</v>
+      </c>
+      <c r="I74" t="s">
+        <v>345</v>
+      </c>
+      <c r="J74" t="s">
+        <v>346</v>
+      </c>
+      <c r="K74" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>856</v>
+      </c>
+      <c r="B75">
+        <v>82</v>
+      </c>
+      <c r="C75" t="s">
+        <v>591</v>
+      </c>
+      <c r="D75" t="s">
+        <v>601</v>
+      </c>
+      <c r="E75" t="s">
+        <v>602</v>
+      </c>
+      <c r="F75" t="s">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s">
+        <v>604</v>
+      </c>
+      <c r="H75" t="s">
+        <v>606</v>
+      </c>
+      <c r="I75" t="s">
+        <v>607</v>
+      </c>
+      <c r="J75" t="s">
+        <v>608</v>
+      </c>
+      <c r="K75" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>856</v>
+      </c>
+      <c r="B76">
         <v>81</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" t="s">
+        <v>81</v>
+      </c>
+      <c r="F76" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" t="s">
+        <v>83</v>
+      </c>
+      <c r="H76" t="s">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s">
+        <v>86</v>
+      </c>
+      <c r="J76" t="s">
+        <v>87</v>
+      </c>
+      <c r="K76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>856</v>
+      </c>
+      <c r="B77">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" t="s">
+        <v>377</v>
+      </c>
+      <c r="E77" t="s">
+        <v>378</v>
+      </c>
+      <c r="F77" t="s">
+        <v>380</v>
+      </c>
+      <c r="G77" t="s">
+        <v>381</v>
+      </c>
+      <c r="H77" t="s">
+        <v>383</v>
+      </c>
+      <c r="I77" t="s">
+        <v>384</v>
+      </c>
+      <c r="J77" t="s">
+        <v>385</v>
+      </c>
+      <c r="K77" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>856</v>
+      </c>
+      <c r="B78">
+        <v>81</v>
+      </c>
+      <c r="C78" t="s">
+        <v>473</v>
+      </c>
+      <c r="D78" t="s">
+        <v>499</v>
+      </c>
+      <c r="E78" t="s">
+        <v>500</v>
+      </c>
+      <c r="F78" t="s">
+        <v>502</v>
+      </c>
+      <c r="G78" t="s">
+        <v>503</v>
+      </c>
+      <c r="H78" t="s">
+        <v>505</v>
+      </c>
+      <c r="I78" t="s">
+        <v>506</v>
+      </c>
+      <c r="J78" t="s">
+        <v>507</v>
+      </c>
+      <c r="K78" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>856</v>
+      </c>
+      <c r="B79">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
         <v>591</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D79" t="s">
         <v>616</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E79" t="s">
         <v>610</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F79" t="s">
         <v>16</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G79" t="s">
         <v>618</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H79" t="s">
         <v>620</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I79" t="s">
         <v>621</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J79" t="s">
         <v>622</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K79" t="s">
         <v>617</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="974">
   <si>
     <t>日期</t>
   </si>
@@ -2549,6 +2549,273 @@
   </si>
   <si>
     <t>突出支架结构设计、材料选型与力学评价项目；补充可降解/药物涂层方向背景；量化支架性能测试数据；强调上市企业三类器械研发流程理解。</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>杨志禄教授团队（南方医科大学/西南交通大学）</t>
+  </si>
+  <si>
+    <t>博士后（内皮功能仿生血管支架涂层）</t>
+  </si>
+  <si>
+    <t>心血管病理学、内皮功能仿生血管支架涂层（NO催化释放）、可降解/载药支架方向博士后。年薪约50万，要求SCI二区2篇或一区1篇，博士学位。</t>
+  </si>
+  <si>
+    <t>东莞/成都</t>
+  </si>
+  <si>
+    <t>搜狗微信搜索「杨志禄教授团队 博士后 血管支架涂层」（SMM医用智能材料公众号）</t>
+  </si>
+  <si>
+    <t>智能匹配89分【博士后】|强烈推荐|内皮仿生血管支架涂层/可降解载药支架，方向+生物相容性材料技能高度重合</t>
+  </si>
+  <si>
+    <t>研究90/技能88/学历82/行业100/企业90</t>
+  </si>
+  <si>
+    <t>团队研究方向正是可降解/载药血管支架的内皮化仿生涂层，与硕士生血管支架的支架设计与生物相容性评价方向高度契合，属稀有高价值科研岗。若有志后续读博深造，是进入血管支架研发一线科研的优质平台，年薪待遇优厚。</t>
+  </si>
+  <si>
+    <t>重点突出血管支架相关研究背景与生物相容性评价能力（细胞毒性/血液相容性/降解性能）；如有内皮化、药物缓释涂层或载药支架论文/项目务必置于简历显眼处；列出已发表的SCI论文及导师推荐信。</t>
+  </si>
+  <si>
+    <t>北京昕科医疗科技</t>
+  </si>
+  <si>
+    <t>研发工程师（编织支架/导丝/导管方向）</t>
+  </si>
+  <si>
+    <t>负责无菌血管介入器械研发，细分方向含编织支架、导丝、导管。本科及以上学历（硕士优先），机械/材料相关专业，月薪1万起，招5人。</t>
+  </si>
+  <si>
+    <t>北京顺义</t>
+  </si>
+  <si>
+    <t>搜狗微信搜索「北京昕科医疗科技 研发工程师」（顺义ID社区公众号）</t>
+  </si>
+  <si>
+    <t>智能匹配88分【社招】|强烈推荐|编织支架/导丝/导管介入器械研发，方向匹配，硕士可投，北京岗位</t>
+  </si>
+  <si>
+    <t>研究88/技能78/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>岗位明确做编织支架、导丝、导管的无菌介入器械研发，与硕士血管支架研究方向的支架结构设计与材料能力对口，且北京工作地契合城市偏好，硕士可投、本科即可降低门槛，是应届生切入介入器械研发的合适机会。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计与编织/切割工艺理解；补充金属材料（镍钛/钴铬）与高分子材料知识；结合北京本地身份或可到岗时间说明求职意愿。</t>
+  </si>
+  <si>
+    <t>复旦大学附属中山医院·葛均波院士课题组</t>
+  </si>
+  <si>
+    <t>医工交叉博士后</t>
+  </si>
+  <si>
+    <t>从事智能化泛血管植入/介入器械与材料的研发与转化，医工交叉方向。需博士学位，原则上在毕业年限内。</t>
+  </si>
+  <si>
+    <t>BioArt公众号《复旦大学附属中山医院葛均波院士课题组诚聘医工交叉博士后》</t>
+  </si>
+  <si>
+    <t>智能匹配87分【博士后】|强烈推荐|泛血管植入/介入器械与材料医工交叉研发，方向高度匹配</t>
+  </si>
+  <si>
+    <t>研究88/技能80/学历82/行业100/企业95</t>
+  </si>
+  <si>
+    <t>葛均波院士团队为国内心血管介入领域顶级团队，从事泛血管植入/介入医疗器械与材料转化研究，与硕士血管支架方向高度契合。医工交叉平台可充分发挥材料学+支架设计+生物相容性+动物实验综合背景，上海城市符合偏好，是不可多得的高端科研起点。</t>
+  </si>
+  <si>
+    <t>将血管支架课题的科研产出（论文、专利）前置；突出医工交叉能力——既懂材料与支架工程设计，又能做动物实验与生物相容性评价；附导师研究方向说明与个人对未来泛血管器械研究的规划。</t>
+  </si>
+  <si>
+    <t>经血管植入器械研究院·蒋峻课题组（浙大滨江/浙二）</t>
+  </si>
+  <si>
+    <t>博士后/研究助理</t>
+  </si>
+  <si>
+    <t>突破新一代经血管植入/介入器械关键技术，打造世界一流经血管植入器械研发平台。博士后需博士学历，同时招募研究助理。</t>
+  </si>
+  <si>
+    <t>搜狗微信《滨江相约在高新》公众号《科研平台系列招聘·经血管植入器械研究院蒋峻课题组》</t>
+  </si>
+  <si>
+    <t>智能匹配86分【科研岗】|强烈推荐|经血管植入/介入器械研发平台，方向直接匹配</t>
+  </si>
+  <si>
+    <t>研究88/技能75/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>该平台专攻经血管植入/介入器械关键技术研发，与硕士血管支架研发方向直接对口；同时招募研究助理（研究助理对硕士学历更友好），是进入经血管植入器械研发一线的理想平台，杭州市符合可接受的城市范围。</t>
+  </si>
+  <si>
+    <t>突出经血管植入器械相关的结构设计、材料应用项目经历；强调法规与器械研发流程理解；若硕士身份可申请研究助理，明确岗位选择倾向并附材料学与生物相容性实验技能。</t>
+  </si>
+  <si>
+    <t>海军军医大学第一附属医院（长海医院）·陆清声课题组</t>
+  </si>
+  <si>
+    <t>博士后（支架移植物/生物力学/血管腔内）</t>
+  </si>
+  <si>
+    <t>研究方向：支架移植物、生物力学、血管腔内机器人、影像学、AI。长期有效。优秀博士后出站可参评长海医院优博人才计划。</t>
+  </si>
+  <si>
+    <t>搜狗微信《新血管》公众号《陆清声课题组博士后招聘公告》</t>
+  </si>
+  <si>
+    <t>智能匹配86分【博士后】|强烈推荐|支架移植物与生物力学研究，方向高度匹配</t>
+  </si>
+  <si>
+    <t>研究88/技能78/学历82/行业100/企业95</t>
+  </si>
+  <si>
+    <t>课题组聚焦支架移植物、生物力学与血管腔内技术，正是硕士血管支架研究方向的延伸，力学仿真与支架设计技能可充分发挥，上海工作地契合偏好，出站留任与发展空间明确。</t>
+  </si>
+  <si>
+    <t>突出支架结构/力学设计与有限元分析能力；补充生物力学或在体支架相关研究；强调动物实验与影像学随访经验，贴合课题组支架移植物研究方向。</t>
+  </si>
+  <si>
+    <t>中国医学科学院阜外医院·吴永健教授课题组</t>
+  </si>
+  <si>
+    <t>博士后（介入瓣膜/结构性心脏病）</t>
+  </si>
+  <si>
+    <t>从事老年瓣膜性心脏病研究，介入瓣膜器械方向。毕业不超过两年，可全职，需博士学历。</t>
+  </si>
+  <si>
+    <t>搜狗微信《学术经纬》公众号《中国医学科学院阜外医院吴永健教授课题组招聘博士后》</t>
+  </si>
+  <si>
+    <t>智能匹配81分【博士后】|强烈推荐|介入瓣膜等结构性心脏介入器械方向，方向相关，阜外顶级平台</t>
+  </si>
+  <si>
+    <t>研究80/技能70/学历82/行业100/企业95</t>
+  </si>
+  <si>
+    <t>阜外医院为国内心血管领域国家级中心，课题组研究介入瓣膜等结构性心脏介入器械，属于心血管介入大方向，与硕士介入器械与材料背景相关联，北京城市契合偏好，平台价值极高。</t>
+  </si>
+  <si>
+    <t>突出心血管介入器械与材料学基础（金属/高分子材料、生物相容性）；补充对介入瓣膜器械的了解；强调硕士课题中与介入器械相关的科研方法与成果。</t>
+  </si>
+  <si>
+    <t>北京天坛医院（神经外科研究所）</t>
+  </si>
+  <si>
+    <t>博士后（脑血管病/神经介入方向）</t>
+  </si>
+  <si>
+    <t>脑血管病方向：血管介入相关生物材料联合研发与临床转化，招2名博士后。享受国家博后正规待遇。</t>
+  </si>
+  <si>
+    <t>搜狗微信《神外世界》公众号《北京天坛医院(神外所)博士后招聘：脑血管病方向》</t>
+  </si>
+  <si>
+    <t>智能匹配84分【博士后】|强烈推荐|脑血管病介入生物材料研发与转化，方向相关，北京平台</t>
+  </si>
+  <si>
+    <t>研究85/技能75/学历82/行业100/企业95</t>
+  </si>
+  <si>
+    <t>天坛医院神外所研究血管介入相关生物材料联合研发与临床转化，紧邻神经介入/支架方向，与硕士植介入生物材料研究关联度高，北京城市契合，国家级医院平台带来丰富的临床转化资源。</t>
+  </si>
+  <si>
+    <t>突出植介入生物材料及其生物相容性评价（材料学+生物相容性双技能）；补充对神经介入器械的理解；强调临床转化导向的研究思路与动物实验经验。</t>
+  </si>
+  <si>
+    <t>深圳大学高等研究院·生物医用材料实验室</t>
+  </si>
+  <si>
+    <t>生物医用材料、生物相容性、组织修复方向博士后，招3-5人。出站优先解决就业，留深可申请30万起步人才资金。</t>
+  </si>
+  <si>
+    <t>搜狗微信《高分子科技/材料人/科研圈》公众号《深圳大学高等研究院生物医用材料实验室招聘博士后》</t>
+  </si>
+  <si>
+    <t>智能匹配79分【博士后】|值得考虑|生物医用材料与生物相容性方向，技能相关，深圳平台</t>
+  </si>
+  <si>
+    <t>研究75/技能72/学历82/行业100/企业90</t>
+  </si>
+  <si>
+    <t>实验室研究生物医用材料与生物相容性，与硕士生物相容性评价与材料学技能直接相关，深圳城市契合偏好，出站就业保障与人才政策优厚，是持续深耕生物医用材料科研的稳妥选择。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料的研发经历（聚合物/可降解材料）与生物相容性评价详尽数据（ISO 10993相关方法）；强调组织修复或仿生材料相关课题；列出可承担的实验技术清单。</t>
+  </si>
+  <si>
+    <t>中科院上海硅酸盐所·生物材料表面与界面课题组（刘宣勇教授）</t>
+  </si>
+  <si>
+    <t>生物医用材料表面与界面研究，需博士学历且具生物与材料学背景，35岁以下。需申请博后基金、发表论文。</t>
+  </si>
+  <si>
+    <t>搜狗微信《中科院上海硅酸盐所》官方公众号《生物材料表面与界面课题组诚聘博士后》</t>
+  </si>
+  <si>
+    <t>智能匹配78分【博士后】|值得考虑|生物医用材料表面与界面研究，材料学+生物相容性相关</t>
+  </si>
+  <si>
+    <t>研究70/技能72/学历82/行业100/企业95</t>
+  </si>
+  <si>
+    <t>课题组聚焦生物医用材料表面与界面研究，与硕士材料学与生物相容性评价技能相关，中科院科研院所平台规范，上海城市契合偏好，是深化生物医用材料表面改性研究的优质科研岗位。</t>
+  </si>
+  <si>
+    <t>突出材料表面改性与性能表征能力（细胞毒性、血液相容性等）；强调生物医用材料研究背景；说明个人科研课题与所发表论文，匹配课题组材料表面/界面方向。</t>
+  </si>
+  <si>
+    <t>维度（西安）生物医疗科技</t>
+  </si>
+  <si>
+    <t>研发工程师（结构方向）</t>
+  </si>
+  <si>
+    <t>医用3D打印生物可降解材料与骨科植入物结构设计，另有增材制造工艺、高分子材料方向。研究生及以上机械类学历，招10人，月薪7-12K。</t>
+  </si>
+  <si>
+    <t>西安</t>
+  </si>
+  <si>
+    <t>搜狗微信搜索「维度(西安)生物医疗科技 研发工程师」（西安招聘相关公众号）</t>
+  </si>
+  <si>
+    <t>智能匹配76分【社招】|值得考虑|3D打印可降解生物材料/植入/高分子结构设计，方向相关</t>
+  </si>
+  <si>
+    <t>研究70/技能60/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>公司从事医用3D打印可降解生物材料及植入物结构设计，涉及高分子材料与增材制造，与硕士材料和支架结构设计背景相关，硕士可投，是切入可降解植入器械领域的阶段性机会（工作地在西安，属非重点城市需权衡）。</t>
+  </si>
+  <si>
+    <t>突出高分子可降解材料与结构设计能力；补充增材制造/三维建模技能（SolidWorks等）；弱化地域限制，突出可降解材料研究背景与快速上手意愿。</t>
+  </si>
+  <si>
+    <t>北京化工大学·薛佳佳课题组（先进弹性体材料研究中心/生物医用材料北京实验室）</t>
+  </si>
+  <si>
+    <t>生物医用高分子/弹性体材料基础与转化研究，出站可聘专任教师，年薪40万起，需博士学位。</t>
+  </si>
+  <si>
+    <t>搜狗微信搜索「北京化工大学薛佳佳课题组 博士后 生物医用高分子」（高分子科学前沿等公众号）</t>
+  </si>
+  <si>
+    <t>智能匹配74分【博士后】|值得考虑|生物医用高分子/弹性体材料，材料学技能相关，北京平台</t>
+  </si>
+  <si>
+    <t>研究65/技能65/学历82/行业100/企业90</t>
+  </si>
+  <si>
+    <t>课题组研究生物医用高分子与弹性体材料，与硕士材料学技能相关，北京城市符合偏好，出站可聘专任教师提供了较优的职业发展通道，适合有意投身生物医用材料科研的硕士毕业生深造。</t>
+  </si>
+  <si>
+    <t>突出高分子材料合成/改性/表征能力与生物医用方向；强调可降解塑料、弹性体或医用高分子选题；列出材料学专著论文与表征数据以匹配课题组方向。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -3103,7 +3370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7487,6 +7754,424 @@
       </c>
       <c r="L115" t="s">
         <v>844</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>845</v>
+      </c>
+      <c r="B116" t="s">
+        <v>846</v>
+      </c>
+      <c r="C116" t="s">
+        <v>847</v>
+      </c>
+      <c r="D116" t="s">
+        <v>848</v>
+      </c>
+      <c r="E116" t="s">
+        <v>849</v>
+      </c>
+      <c r="F116" t="s">
+        <v>850</v>
+      </c>
+      <c r="G116">
+        <v>9</v>
+      </c>
+      <c r="H116" t="s">
+        <v>851</v>
+      </c>
+      <c r="I116">
+        <v>89</v>
+      </c>
+      <c r="J116" t="s">
+        <v>852</v>
+      </c>
+      <c r="K116" t="s">
+        <v>853</v>
+      </c>
+      <c r="L116" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>845</v>
+      </c>
+      <c r="B117" t="s">
+        <v>855</v>
+      </c>
+      <c r="C117" t="s">
+        <v>856</v>
+      </c>
+      <c r="D117" t="s">
+        <v>857</v>
+      </c>
+      <c r="E117" t="s">
+        <v>858</v>
+      </c>
+      <c r="F117" t="s">
+        <v>859</v>
+      </c>
+      <c r="G117">
+        <v>9</v>
+      </c>
+      <c r="H117" t="s">
+        <v>860</v>
+      </c>
+      <c r="I117">
+        <v>88</v>
+      </c>
+      <c r="J117" t="s">
+        <v>861</v>
+      </c>
+      <c r="K117" t="s">
+        <v>862</v>
+      </c>
+      <c r="L117" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>845</v>
+      </c>
+      <c r="B118" t="s">
+        <v>864</v>
+      </c>
+      <c r="C118" t="s">
+        <v>865</v>
+      </c>
+      <c r="D118" t="s">
+        <v>866</v>
+      </c>
+      <c r="E118" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" t="s">
+        <v>867</v>
+      </c>
+      <c r="G118">
+        <v>9</v>
+      </c>
+      <c r="H118" t="s">
+        <v>868</v>
+      </c>
+      <c r="I118">
+        <v>87</v>
+      </c>
+      <c r="J118" t="s">
+        <v>869</v>
+      </c>
+      <c r="K118" t="s">
+        <v>870</v>
+      </c>
+      <c r="L118" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>845</v>
+      </c>
+      <c r="B119" t="s">
+        <v>872</v>
+      </c>
+      <c r="C119" t="s">
+        <v>873</v>
+      </c>
+      <c r="D119" t="s">
+        <v>874</v>
+      </c>
+      <c r="E119" t="s">
+        <v>380</v>
+      </c>
+      <c r="F119" t="s">
+        <v>875</v>
+      </c>
+      <c r="G119">
+        <v>9</v>
+      </c>
+      <c r="H119" t="s">
+        <v>876</v>
+      </c>
+      <c r="I119">
+        <v>86</v>
+      </c>
+      <c r="J119" t="s">
+        <v>877</v>
+      </c>
+      <c r="K119" t="s">
+        <v>878</v>
+      </c>
+      <c r="L119" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>845</v>
+      </c>
+      <c r="B120" t="s">
+        <v>880</v>
+      </c>
+      <c r="C120" t="s">
+        <v>881</v>
+      </c>
+      <c r="D120" t="s">
+        <v>882</v>
+      </c>
+      <c r="E120" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" t="s">
+        <v>883</v>
+      </c>
+      <c r="G120">
+        <v>9</v>
+      </c>
+      <c r="H120" t="s">
+        <v>884</v>
+      </c>
+      <c r="I120">
+        <v>86</v>
+      </c>
+      <c r="J120" t="s">
+        <v>885</v>
+      </c>
+      <c r="K120" t="s">
+        <v>886</v>
+      </c>
+      <c r="L120" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>845</v>
+      </c>
+      <c r="B121" t="s">
+        <v>888</v>
+      </c>
+      <c r="C121" t="s">
+        <v>889</v>
+      </c>
+      <c r="D121" t="s">
+        <v>890</v>
+      </c>
+      <c r="E121" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" t="s">
+        <v>891</v>
+      </c>
+      <c r="G121">
+        <v>8</v>
+      </c>
+      <c r="H121" t="s">
+        <v>892</v>
+      </c>
+      <c r="I121">
+        <v>81</v>
+      </c>
+      <c r="J121" t="s">
+        <v>893</v>
+      </c>
+      <c r="K121" t="s">
+        <v>894</v>
+      </c>
+      <c r="L121" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>845</v>
+      </c>
+      <c r="B122" t="s">
+        <v>896</v>
+      </c>
+      <c r="C122" t="s">
+        <v>897</v>
+      </c>
+      <c r="D122" t="s">
+        <v>898</v>
+      </c>
+      <c r="E122" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" t="s">
+        <v>899</v>
+      </c>
+      <c r="G122">
+        <v>8</v>
+      </c>
+      <c r="H122" t="s">
+        <v>900</v>
+      </c>
+      <c r="I122">
+        <v>84</v>
+      </c>
+      <c r="J122" t="s">
+        <v>901</v>
+      </c>
+      <c r="K122" t="s">
+        <v>902</v>
+      </c>
+      <c r="L122" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>845</v>
+      </c>
+      <c r="B123" t="s">
+        <v>904</v>
+      </c>
+      <c r="C123" t="s">
+        <v>585</v>
+      </c>
+      <c r="D123" t="s">
+        <v>905</v>
+      </c>
+      <c r="E123" t="s">
+        <v>66</v>
+      </c>
+      <c r="F123" t="s">
+        <v>906</v>
+      </c>
+      <c r="G123">
+        <v>8</v>
+      </c>
+      <c r="H123" t="s">
+        <v>907</v>
+      </c>
+      <c r="I123">
+        <v>79</v>
+      </c>
+      <c r="J123" t="s">
+        <v>908</v>
+      </c>
+      <c r="K123" t="s">
+        <v>909</v>
+      </c>
+      <c r="L123" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>845</v>
+      </c>
+      <c r="B124" t="s">
+        <v>911</v>
+      </c>
+      <c r="C124" t="s">
+        <v>585</v>
+      </c>
+      <c r="D124" t="s">
+        <v>912</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s">
+        <v>913</v>
+      </c>
+      <c r="G124">
+        <v>8</v>
+      </c>
+      <c r="H124" t="s">
+        <v>914</v>
+      </c>
+      <c r="I124">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s">
+        <v>915</v>
+      </c>
+      <c r="K124" t="s">
+        <v>916</v>
+      </c>
+      <c r="L124" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>845</v>
+      </c>
+      <c r="B125" t="s">
+        <v>918</v>
+      </c>
+      <c r="C125" t="s">
+        <v>919</v>
+      </c>
+      <c r="D125" t="s">
+        <v>920</v>
+      </c>
+      <c r="E125" t="s">
+        <v>921</v>
+      </c>
+      <c r="F125" t="s">
+        <v>922</v>
+      </c>
+      <c r="G125">
+        <v>8</v>
+      </c>
+      <c r="H125" t="s">
+        <v>923</v>
+      </c>
+      <c r="I125">
+        <v>76</v>
+      </c>
+      <c r="J125" t="s">
+        <v>924</v>
+      </c>
+      <c r="K125" t="s">
+        <v>925</v>
+      </c>
+      <c r="L125" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>845</v>
+      </c>
+      <c r="B126" t="s">
+        <v>927</v>
+      </c>
+      <c r="C126" t="s">
+        <v>585</v>
+      </c>
+      <c r="D126" t="s">
+        <v>928</v>
+      </c>
+      <c r="E126" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" t="s">
+        <v>929</v>
+      </c>
+      <c r="G126">
+        <v>7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>930</v>
+      </c>
+      <c r="I126">
+        <v>74</v>
+      </c>
+      <c r="J126" t="s">
+        <v>931</v>
+      </c>
+      <c r="K126" t="s">
+        <v>932</v>
+      </c>
+      <c r="L126" t="s">
+        <v>933</v>
       </c>
     </row>
   </sheetData>
@@ -7520,7 +8205,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7529,16 +8214,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>846</v>
+        <v>935</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>847</v>
+        <v>936</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>848</v>
+        <v>937</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>849</v>
+        <v>938</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7552,13 +8237,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>850</v>
+        <v>939</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>851</v>
+        <v>940</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>852</v>
+        <v>941</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -7586,7 +8271,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7601,7 +8286,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>857</v>
+        <v>946</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7611,31 +8296,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>858</v>
+        <v>947</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>859</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>860</v>
+        <v>949</v>
       </c>
       <c r="B4">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>861</v>
+        <v>950</v>
       </c>
       <c r="B5" t="s">
-        <v>862</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>863</v>
+        <v>952</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -7643,7 +8328,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>864</v>
+        <v>953</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -7651,39 +8336,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>865</v>
+        <v>954</v>
       </c>
       <c r="B8">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>866</v>
+        <v>955</v>
       </c>
       <c r="B9">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>867</v>
+        <v>956</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>868</v>
+        <v>957</v>
       </c>
       <c r="B11" t="s">
-        <v>773</v>
+        <v>845</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>869</v>
+        <v>958</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -7693,15 +8378,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>870</v>
+        <v>959</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>871</v>
+        <v>960</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>872</v>
+        <v>961</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -7709,31 +8394,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>873</v>
+        <v>962</v>
       </c>
       <c r="B17" s="5">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>874</v>
+        <v>963</v>
       </c>
       <c r="B18" s="5">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>875</v>
+        <v>964</v>
       </c>
       <c r="B19" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>876</v>
+        <v>965</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -7741,7 +8426,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>877</v>
+        <v>966</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -7749,7 +8434,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>967</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -7757,7 +8442,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>879</v>
+        <v>968</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -7765,7 +8450,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>880</v>
+        <v>969</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -7773,7 +8458,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>881</v>
+        <v>970</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -7781,7 +8466,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>882</v>
+        <v>971</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -7793,7 +8478,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>883</v>
+        <v>972</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -7811,7 +8496,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>884</v>
+        <v>973</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -9278,25 +9963,25 @@
         <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="C86" t="s">
-        <v>72</v>
+        <v>846</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>847</v>
       </c>
       <c r="E86" t="s">
-        <v>75</v>
+        <v>849</v>
       </c>
       <c r="F86" t="s">
-        <v>76</v>
+        <v>850</v>
       </c>
       <c r="G86">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H86" t="s">
-        <v>77</v>
+        <v>851</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -9304,25 +9989,25 @@
         <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>855</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>856</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>858</v>
       </c>
       <c r="F87" t="s">
-        <v>83</v>
+        <v>859</v>
       </c>
       <c r="G87">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H87" t="s">
-        <v>84</v>
+        <v>860</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -9330,25 +10015,25 @@
         <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>864</v>
       </c>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>865</v>
       </c>
       <c r="E88" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>107</v>
+        <v>867</v>
       </c>
       <c r="G88">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H88" t="s">
-        <v>108</v>
+        <v>868</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -9356,25 +10041,25 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>872</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>873</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="F89" t="s">
-        <v>112</v>
+        <v>875</v>
       </c>
       <c r="G89">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>113</v>
+        <v>876</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -9382,25 +10067,25 @@
         <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="C90" t="s">
-        <v>115</v>
+        <v>880</v>
       </c>
       <c r="D90" t="s">
-        <v>116</v>
+        <v>881</v>
       </c>
       <c r="E90" t="s">
         <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>118</v>
+        <v>883</v>
       </c>
       <c r="G90">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H90" t="s">
-        <v>119</v>
+        <v>884</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -9411,22 +10096,22 @@
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="D91" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="G91">
         <v>8</v>
       </c>
       <c r="H91" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -9437,22 +10122,22 @@
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="E92" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="G92">
         <v>8</v>
       </c>
       <c r="H92" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -9463,22 +10148,22 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="E93" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="G93">
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -9486,25 +10171,25 @@
         <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="D94" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="G94">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>211</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -9512,25 +10197,25 @@
         <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>213</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="E95" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="G95">
         <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -9538,25 +10223,25 @@
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="D96" t="s">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="E96" t="s">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="G96">
         <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -9564,25 +10249,25 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="D97" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="F97" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="G97">
         <v>8</v>
       </c>
       <c r="H97" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -9590,25 +10275,25 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="D98" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="G98">
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -9619,22 +10304,22 @@
         <v>159</v>
       </c>
       <c r="C99" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="D99" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E99" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F99" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="G99">
         <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -9645,22 +10330,22 @@
         <v>159</v>
       </c>
       <c r="C100" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="D100" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="E100" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F100" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="G100">
         <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -9671,22 +10356,22 @@
         <v>159</v>
       </c>
       <c r="C101" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="D101" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="E101" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -9697,22 +10382,22 @@
         <v>159</v>
       </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D102" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E102" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="F102" t="s">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -9723,22 +10408,22 @@
         <v>159</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="D103" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -9749,22 +10434,22 @@
         <v>159</v>
       </c>
       <c r="C104" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="D104" t="s">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="E104" t="s">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -9772,25 +10457,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C105" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="D105" t="s">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="E105" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F105" t="s">
-        <v>319</v>
+        <v>251</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -9798,25 +10483,25 @@
         <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>254</v>
       </c>
       <c r="D106" t="s">
-        <v>339</v>
+        <v>255</v>
       </c>
       <c r="E106" t="s">
-        <v>341</v>
+        <v>257</v>
       </c>
       <c r="F106" t="s">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>343</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -9824,25 +10509,25 @@
         <v>78</v>
       </c>
       <c r="B107" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C107" t="s">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>348</v>
+        <v>122</v>
       </c>
       <c r="E107" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="F107" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>351</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -9850,25 +10535,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C108" t="s">
-        <v>353</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>267</v>
       </c>
       <c r="E108" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>365</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -9876,25 +10561,25 @@
         <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C109" t="s">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="D109" t="s">
-        <v>378</v>
+        <v>278</v>
       </c>
       <c r="E109" t="s">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="F109" t="s">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>382</v>
+        <v>282</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -9905,22 +10590,22 @@
         <v>284</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>315</v>
       </c>
       <c r="D110" t="s">
-        <v>394</v>
+        <v>316</v>
       </c>
       <c r="E110" t="s">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="F110" t="s">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -9928,25 +10613,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C111" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="D111" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="E111" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="F111" t="s">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>414</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -9954,25 +10639,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C112" t="s">
-        <v>418</v>
+        <v>347</v>
       </c>
       <c r="D112" t="s">
-        <v>419</v>
+        <v>348</v>
       </c>
       <c r="E112" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F112" t="s">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>422</v>
+        <v>351</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -9980,25 +10665,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C113" t="s">
-        <v>424</v>
+        <v>353</v>
       </c>
       <c r="D113" t="s">
-        <v>425</v>
+        <v>362</v>
       </c>
       <c r="E113" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F113" t="s">
-        <v>427</v>
+        <v>364</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>428</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -10006,25 +10691,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C114" t="s">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="D114" t="s">
-        <v>431</v>
+        <v>378</v>
       </c>
       <c r="E114" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="F114" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>434</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -10032,25 +10717,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C115" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="E115" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="F115" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>487</v>
+        <v>398</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -10058,25 +10743,25 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C116" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="D116" t="s">
-        <v>492</v>
+        <v>411</v>
       </c>
       <c r="E116" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F116" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>495</v>
+        <v>414</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -10084,25 +10769,25 @@
         <v>88</v>
       </c>
       <c r="B117" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C117" t="s">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="D117" t="s">
-        <v>500</v>
+        <v>419</v>
       </c>
       <c r="E117" t="s">
-        <v>502</v>
+        <v>66</v>
       </c>
       <c r="F117" t="s">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>504</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -10110,25 +10795,25 @@
         <v>89</v>
       </c>
       <c r="B118" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C118" t="s">
-        <v>532</v>
+        <v>424</v>
       </c>
       <c r="D118" t="s">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="E118" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="F118" t="s">
-        <v>536</v>
+        <v>427</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>537</v>
+        <v>428</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -10136,25 +10821,25 @@
         <v>90</v>
       </c>
       <c r="B119" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C119" t="s">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="D119" t="s">
-        <v>551</v>
+        <v>431</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>553</v>
+        <v>433</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>554</v>
+        <v>434</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -10162,25 +10847,25 @@
         <v>91</v>
       </c>
       <c r="B120" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C120" t="s">
-        <v>578</v>
+        <v>483</v>
       </c>
       <c r="D120" t="s">
-        <v>579</v>
+        <v>122</v>
       </c>
       <c r="E120" t="s">
-        <v>66</v>
+        <v>485</v>
       </c>
       <c r="F120" t="s">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>582</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -10188,25 +10873,25 @@
         <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C121" t="s">
-        <v>584</v>
+        <v>491</v>
       </c>
       <c r="D121" t="s">
-        <v>585</v>
+        <v>492</v>
       </c>
       <c r="E121" t="s">
-        <v>587</v>
+        <v>75</v>
       </c>
       <c r="F121" t="s">
-        <v>588</v>
+        <v>494</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>589</v>
+        <v>495</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -10214,25 +10899,25 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C122" t="s">
-        <v>601</v>
+        <v>499</v>
       </c>
       <c r="D122" t="s">
-        <v>602</v>
+        <v>500</v>
       </c>
       <c r="E122" t="s">
-        <v>75</v>
+        <v>502</v>
       </c>
       <c r="F122" t="s">
-        <v>604</v>
+        <v>503</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>605</v>
+        <v>504</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -10240,25 +10925,25 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C123" t="s">
-        <v>616</v>
+        <v>532</v>
       </c>
       <c r="D123" t="s">
-        <v>610</v>
+        <v>533</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="F123" t="s">
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>619</v>
+        <v>537</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -10266,25 +10951,25 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C124" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="D124" t="s">
-        <v>623</v>
+        <v>551</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>468</v>
+        <v>553</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>625</v>
+        <v>554</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -10292,25 +10977,25 @@
         <v>96</v>
       </c>
       <c r="B125" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C125" t="s">
-        <v>643</v>
+        <v>578</v>
       </c>
       <c r="D125" t="s">
-        <v>644</v>
+        <v>579</v>
       </c>
       <c r="E125" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F125" t="s">
-        <v>618</v>
+        <v>581</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>646</v>
+        <v>582</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -10318,25 +11003,25 @@
         <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C126" t="s">
-        <v>650</v>
+        <v>584</v>
       </c>
       <c r="D126" t="s">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="E126" t="s">
-        <v>66</v>
+        <v>587</v>
       </c>
       <c r="F126" t="s">
-        <v>653</v>
+        <v>588</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>654</v>
+        <v>589</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -10347,22 +11032,22 @@
         <v>591</v>
       </c>
       <c r="C127" t="s">
-        <v>658</v>
+        <v>601</v>
       </c>
       <c r="D127" t="s">
-        <v>659</v>
+        <v>602</v>
       </c>
       <c r="E127" t="s">
-        <v>661</v>
+        <v>75</v>
       </c>
       <c r="F127" t="s">
-        <v>662</v>
+        <v>604</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>663</v>
+        <v>605</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -10373,22 +11058,22 @@
         <v>591</v>
       </c>
       <c r="C128" t="s">
-        <v>666</v>
+        <v>616</v>
       </c>
       <c r="D128" t="s">
-        <v>667</v>
+        <v>610</v>
       </c>
       <c r="E128" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>669</v>
+        <v>619</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -10399,22 +11084,22 @@
         <v>591</v>
       </c>
       <c r="C129" t="s">
-        <v>673</v>
+        <v>557</v>
       </c>
       <c r="D129" t="s">
-        <v>674</v>
+        <v>623</v>
       </c>
       <c r="E129" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>676</v>
+        <v>468</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>677</v>
+        <v>625</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -10422,25 +11107,25 @@
         <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C130" t="s">
-        <v>714</v>
+        <v>643</v>
       </c>
       <c r="D130" t="s">
-        <v>715</v>
+        <v>644</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>717</v>
+        <v>646</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -10448,25 +11133,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C131" t="s">
-        <v>721</v>
+        <v>650</v>
       </c>
       <c r="D131" t="s">
-        <v>722</v>
+        <v>651</v>
       </c>
       <c r="E131" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F131" t="s">
-        <v>724</v>
+        <v>653</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>725</v>
+        <v>654</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -10474,25 +11159,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C132" t="s">
-        <v>729</v>
+        <v>658</v>
       </c>
       <c r="D132" t="s">
-        <v>730</v>
+        <v>659</v>
       </c>
       <c r="E132" t="s">
-        <v>535</v>
+        <v>661</v>
       </c>
       <c r="F132" t="s">
-        <v>732</v>
+        <v>662</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>733</v>
+        <v>663</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -10500,16 +11185,16 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C133" t="s">
-        <v>736</v>
+        <v>666</v>
       </c>
       <c r="D133" t="s">
-        <v>737</v>
+        <v>667</v>
       </c>
       <c r="E133" t="s">
-        <v>739</v>
+        <v>75</v>
       </c>
       <c r="F133" t="s">
         <v>604</v>
@@ -10518,7 +11203,7 @@
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>740</v>
+        <v>669</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -10526,25 +11211,25 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C134" t="s">
-        <v>744</v>
+        <v>673</v>
       </c>
       <c r="D134" t="s">
-        <v>745</v>
+        <v>674</v>
       </c>
       <c r="E134" t="s">
-        <v>747</v>
+        <v>66</v>
       </c>
       <c r="F134" t="s">
-        <v>748</v>
+        <v>676</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>749</v>
+        <v>677</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -10555,22 +11240,22 @@
         <v>697</v>
       </c>
       <c r="C135" t="s">
-        <v>753</v>
+        <v>714</v>
       </c>
       <c r="D135" t="s">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="E135" t="s">
-        <v>756</v>
+        <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>758</v>
+        <v>717</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -10581,22 +11266,22 @@
         <v>697</v>
       </c>
       <c r="C136" t="s">
-        <v>760</v>
+        <v>721</v>
       </c>
       <c r="D136" t="s">
-        <v>761</v>
+        <v>722</v>
       </c>
       <c r="E136" t="s">
-        <v>763</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>765</v>
+        <v>725</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -10604,25 +11289,25 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C137" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="D137" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="E137" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="F137" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>795</v>
+        <v>733</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -10630,25 +11315,25 @@
         <v>109</v>
       </c>
       <c r="B138" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C138" t="s">
-        <v>807</v>
+        <v>736</v>
       </c>
       <c r="D138" t="s">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="E138" t="s">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="F138" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>812</v>
+        <v>740</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -10656,25 +11341,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C139" t="s">
-        <v>816</v>
+        <v>744</v>
       </c>
       <c r="D139" t="s">
-        <v>110</v>
+        <v>745</v>
       </c>
       <c r="E139" t="s">
-        <v>16</v>
+        <v>747</v>
       </c>
       <c r="F139" t="s">
-        <v>818</v>
+        <v>748</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>819</v>
+        <v>749</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -10682,25 +11367,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="C140" t="s">
-        <v>271</v>
+        <v>753</v>
       </c>
       <c r="D140" t="s">
-        <v>272</v>
+        <v>754</v>
       </c>
       <c r="E140" t="s">
-        <v>75</v>
+        <v>756</v>
       </c>
       <c r="F140" t="s">
-        <v>274</v>
+        <v>757</v>
       </c>
       <c r="G140">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>275</v>
+        <v>758</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -10708,25 +11393,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="C141" t="s">
-        <v>681</v>
+        <v>760</v>
       </c>
       <c r="D141" t="s">
-        <v>682</v>
+        <v>761</v>
       </c>
       <c r="E141" t="s">
-        <v>25</v>
+        <v>763</v>
       </c>
       <c r="F141" t="s">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="G141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>685</v>
+        <v>765</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -10734,25 +11419,25 @@
         <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>591</v>
+        <v>773</v>
       </c>
       <c r="C142" t="s">
-        <v>689</v>
+        <v>791</v>
       </c>
       <c r="D142" t="s">
-        <v>690</v>
+        <v>610</v>
       </c>
       <c r="E142" t="s">
-        <v>66</v>
+        <v>793</v>
       </c>
       <c r="F142" t="s">
-        <v>692</v>
+        <v>794</v>
       </c>
       <c r="G142">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>693</v>
+        <v>795</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -10760,25 +11445,311 @@
         <v>114</v>
       </c>
       <c r="B143" t="s">
+        <v>773</v>
+      </c>
+      <c r="C143" t="s">
+        <v>807</v>
+      </c>
+      <c r="D143" t="s">
+        <v>808</v>
+      </c>
+      <c r="E143" t="s">
+        <v>810</v>
+      </c>
+      <c r="F143" t="s">
+        <v>811</v>
+      </c>
+      <c r="G143">
+        <v>8</v>
+      </c>
+      <c r="H143" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>115</v>
+      </c>
+      <c r="B144" t="s">
+        <v>773</v>
+      </c>
+      <c r="C144" t="s">
+        <v>816</v>
+      </c>
+      <c r="D144" t="s">
+        <v>110</v>
+      </c>
+      <c r="E144" t="s">
+        <v>16</v>
+      </c>
+      <c r="F144" t="s">
+        <v>818</v>
+      </c>
+      <c r="G144">
+        <v>8</v>
+      </c>
+      <c r="H144" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>116</v>
+      </c>
+      <c r="B145" t="s">
+        <v>845</v>
+      </c>
+      <c r="C145" t="s">
+        <v>888</v>
+      </c>
+      <c r="D145" t="s">
+        <v>889</v>
+      </c>
+      <c r="E145" t="s">
+        <v>25</v>
+      </c>
+      <c r="F145" t="s">
+        <v>891</v>
+      </c>
+      <c r="G145">
+        <v>8</v>
+      </c>
+      <c r="H145" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>117</v>
+      </c>
+      <c r="B146" t="s">
+        <v>845</v>
+      </c>
+      <c r="C146" t="s">
+        <v>896</v>
+      </c>
+      <c r="D146" t="s">
+        <v>897</v>
+      </c>
+      <c r="E146" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" t="s">
+        <v>899</v>
+      </c>
+      <c r="G146">
+        <v>8</v>
+      </c>
+      <c r="H146" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>118</v>
+      </c>
+      <c r="B147" t="s">
+        <v>845</v>
+      </c>
+      <c r="C147" t="s">
+        <v>904</v>
+      </c>
+      <c r="D147" t="s">
+        <v>585</v>
+      </c>
+      <c r="E147" t="s">
+        <v>66</v>
+      </c>
+      <c r="F147" t="s">
+        <v>906</v>
+      </c>
+      <c r="G147">
+        <v>8</v>
+      </c>
+      <c r="H147" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>119</v>
+      </c>
+      <c r="B148" t="s">
+        <v>845</v>
+      </c>
+      <c r="C148" t="s">
+        <v>911</v>
+      </c>
+      <c r="D148" t="s">
+        <v>585</v>
+      </c>
+      <c r="E148" t="s">
+        <v>16</v>
+      </c>
+      <c r="F148" t="s">
+        <v>913</v>
+      </c>
+      <c r="G148">
+        <v>8</v>
+      </c>
+      <c r="H148" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>120</v>
+      </c>
+      <c r="B149" t="s">
+        <v>845</v>
+      </c>
+      <c r="C149" t="s">
+        <v>918</v>
+      </c>
+      <c r="D149" t="s">
+        <v>919</v>
+      </c>
+      <c r="E149" t="s">
+        <v>921</v>
+      </c>
+      <c r="F149" t="s">
+        <v>922</v>
+      </c>
+      <c r="G149">
+        <v>8</v>
+      </c>
+      <c r="H149" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>121</v>
+      </c>
+      <c r="B150" t="s">
+        <v>159</v>
+      </c>
+      <c r="C150" t="s">
+        <v>271</v>
+      </c>
+      <c r="D150" t="s">
+        <v>272</v>
+      </c>
+      <c r="E150" t="s">
+        <v>75</v>
+      </c>
+      <c r="F150" t="s">
+        <v>274</v>
+      </c>
+      <c r="G150">
+        <v>7</v>
+      </c>
+      <c r="H150" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>122</v>
+      </c>
+      <c r="B151" t="s">
+        <v>591</v>
+      </c>
+      <c r="C151" t="s">
+        <v>681</v>
+      </c>
+      <c r="D151" t="s">
+        <v>682</v>
+      </c>
+      <c r="E151" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" t="s">
+        <v>684</v>
+      </c>
+      <c r="G151">
+        <v>7</v>
+      </c>
+      <c r="H151" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>123</v>
+      </c>
+      <c r="B152" t="s">
+        <v>591</v>
+      </c>
+      <c r="C152" t="s">
+        <v>689</v>
+      </c>
+      <c r="D152" t="s">
+        <v>690</v>
+      </c>
+      <c r="E152" t="s">
+        <v>66</v>
+      </c>
+      <c r="F152" t="s">
+        <v>692</v>
+      </c>
+      <c r="G152">
+        <v>7</v>
+      </c>
+      <c r="H152" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>124</v>
+      </c>
+      <c r="B153" t="s">
         <v>697</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C153" t="s">
         <v>767</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D153" t="s">
         <v>768</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E153" t="s">
         <v>25</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F153" t="s">
         <v>770</v>
       </c>
-      <c r="G143">
+      <c r="G153">
         <v>7</v>
       </c>
-      <c r="H143" t="s">
+      <c r="H153" t="s">
         <v>771</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>125</v>
+      </c>
+      <c r="B154" t="s">
+        <v>845</v>
+      </c>
+      <c r="C154" t="s">
+        <v>927</v>
+      </c>
+      <c r="D154" t="s">
+        <v>585</v>
+      </c>
+      <c r="E154" t="s">
+        <v>25</v>
+      </c>
+      <c r="F154" t="s">
+        <v>929</v>
+      </c>
+      <c r="G154">
+        <v>7</v>
+      </c>
+      <c r="H154" t="s">
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -10794,7 +11765,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10811,10 +11782,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>853</v>
+        <v>942</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>854</v>
+        <v>943</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -10841,12 +11812,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>855</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -10881,7 +11852,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -10916,7 +11887,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -10951,7 +11922,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -10986,7 +11957,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -11021,7 +11992,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -11056,7 +12027,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -11091,7 +12062,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -11126,7 +12097,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -11161,7 +12132,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -11196,7 +12167,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -11231,7 +12202,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -11266,7 +12237,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -11301,7 +12272,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -11336,7 +12307,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -11371,7 +12342,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -11406,7 +12377,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -11441,7 +12412,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -11476,7 +12447,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -11511,7 +12482,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -11546,7 +12517,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -11581,7 +12552,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -11616,7 +12587,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -11651,7 +12622,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -11686,7 +12657,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -11721,7 +12692,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -11756,7 +12727,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -11791,1787 +12762,2032 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B29">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>845</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>846</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>847</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>849</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>850</v>
       </c>
       <c r="H29" t="s">
-        <v>36</v>
+        <v>852</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>853</v>
       </c>
       <c r="J29" t="s">
-        <v>38</v>
+        <v>854</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>848</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B30">
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H30" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K30" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B31">
         <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H31" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J31" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K31" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B32">
         <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E32" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H32" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I32" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K32" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B33">
         <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F33" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H33" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I33" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B34">
         <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D34" t="s">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="E34" t="s">
-        <v>610</v>
+        <v>699</v>
       </c>
       <c r="F34" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="G34" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="H34" t="s">
-        <v>842</v>
+        <v>704</v>
       </c>
       <c r="I34" t="s">
-        <v>843</v>
+        <v>705</v>
       </c>
       <c r="J34" t="s">
-        <v>844</v>
+        <v>706</v>
       </c>
       <c r="K34" t="s">
-        <v>838</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B35">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>773</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>837</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>610</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>839</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>840</v>
       </c>
       <c r="H35" t="s">
-        <v>188</v>
+        <v>842</v>
       </c>
       <c r="I35" t="s">
-        <v>189</v>
+        <v>843</v>
       </c>
       <c r="J35" t="s">
-        <v>190</v>
+        <v>844</v>
       </c>
       <c r="K35" t="s">
-        <v>186</v>
+        <v>838</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>945</v>
+      </c>
+      <c r="B36">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>845</v>
+      </c>
+      <c r="D36" t="s">
+        <v>855</v>
+      </c>
+      <c r="E36" t="s">
         <v>856</v>
       </c>
-      <c r="B36">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>284</v>
-      </c>
-      <c r="D36" t="s">
-        <v>353</v>
-      </c>
-      <c r="E36" t="s">
-        <v>354</v>
-      </c>
       <c r="F36" t="s">
-        <v>356</v>
+        <v>858</v>
       </c>
       <c r="G36" t="s">
-        <v>357</v>
+        <v>859</v>
       </c>
       <c r="H36" t="s">
-        <v>359</v>
+        <v>861</v>
       </c>
       <c r="I36" t="s">
-        <v>360</v>
+        <v>862</v>
       </c>
       <c r="J36" t="s">
-        <v>361</v>
+        <v>863</v>
       </c>
       <c r="K36" t="s">
-        <v>355</v>
+        <v>857</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B37">
         <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="G37" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="I37" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="K37" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B38">
         <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E38" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G38" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H38" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J38" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K38" t="s">
-        <v>464</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B39">
         <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="F39" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G39" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H39" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I39" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B40">
         <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D40" t="s">
-        <v>570</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>571</v>
+        <v>463</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>573</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>575</v>
+        <v>456</v>
       </c>
       <c r="I40" t="s">
-        <v>576</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s">
-        <v>577</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s">
-        <v>572</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B41">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D41" t="s">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>370</v>
+        <v>508</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>510</v>
       </c>
       <c r="G41" t="s">
-        <v>372</v>
+        <v>511</v>
       </c>
       <c r="H41" t="s">
-        <v>374</v>
+        <v>513</v>
       </c>
       <c r="I41" t="s">
-        <v>375</v>
+        <v>514</v>
       </c>
       <c r="J41" t="s">
-        <v>376</v>
+        <v>515</v>
       </c>
       <c r="K41" t="s">
-        <v>371</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B42">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="E42" t="s">
-        <v>457</v>
+        <v>571</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="H42" t="s">
-        <v>460</v>
+        <v>575</v>
       </c>
       <c r="I42" t="s">
-        <v>461</v>
+        <v>576</v>
       </c>
       <c r="J42" t="s">
-        <v>462</v>
+        <v>577</v>
       </c>
       <c r="K42" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B43">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>402</v>
+        <v>845</v>
       </c>
       <c r="D43" t="s">
-        <v>322</v>
+        <v>864</v>
       </c>
       <c r="E43" t="s">
-        <v>466</v>
+        <v>865</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>468</v>
+        <v>867</v>
       </c>
       <c r="H43" t="s">
-        <v>470</v>
+        <v>869</v>
       </c>
       <c r="I43" t="s">
-        <v>471</v>
+        <v>870</v>
       </c>
       <c r="J43" t="s">
-        <v>472</v>
+        <v>871</v>
       </c>
       <c r="K43" t="s">
-        <v>467</v>
+        <v>866</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B44">
         <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D44" t="s">
-        <v>541</v>
+        <v>369</v>
       </c>
       <c r="E44" t="s">
-        <v>542</v>
+        <v>370</v>
       </c>
       <c r="F44" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>545</v>
+        <v>372</v>
       </c>
       <c r="H44" t="s">
-        <v>547</v>
+        <v>374</v>
       </c>
       <c r="I44" t="s">
-        <v>548</v>
+        <v>375</v>
       </c>
       <c r="J44" t="s">
-        <v>549</v>
+        <v>376</v>
       </c>
       <c r="K44" t="s">
-        <v>543</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B45">
         <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D45" t="s">
-        <v>557</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H45" t="s">
-        <v>561</v>
+        <v>460</v>
       </c>
       <c r="I45" t="s">
-        <v>562</v>
+        <v>461</v>
       </c>
       <c r="J45" t="s">
-        <v>563</v>
+        <v>462</v>
       </c>
       <c r="K45" t="s">
-        <v>559</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B46">
         <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="D46" t="s">
-        <v>609</v>
+        <v>322</v>
       </c>
       <c r="E46" t="s">
-        <v>610</v>
+        <v>466</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H46" t="s">
-        <v>613</v>
+        <v>470</v>
       </c>
       <c r="I46" t="s">
-        <v>614</v>
+        <v>471</v>
       </c>
       <c r="J46" t="s">
-        <v>615</v>
+        <v>472</v>
       </c>
       <c r="K46" t="s">
-        <v>611</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B47">
         <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D47" t="s">
-        <v>627</v>
+        <v>541</v>
       </c>
       <c r="E47" t="s">
-        <v>628</v>
+        <v>542</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>544</v>
       </c>
       <c r="G47" t="s">
-        <v>630</v>
+        <v>545</v>
       </c>
       <c r="H47" t="s">
-        <v>632</v>
+        <v>547</v>
       </c>
       <c r="I47" t="s">
-        <v>633</v>
+        <v>548</v>
       </c>
       <c r="J47" t="s">
-        <v>634</v>
+        <v>549</v>
       </c>
       <c r="K47" t="s">
-        <v>629</v>
+        <v>543</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B48">
         <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D48" t="s">
-        <v>635</v>
+        <v>557</v>
       </c>
       <c r="E48" t="s">
-        <v>636</v>
+        <v>558</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>638</v>
+        <v>468</v>
       </c>
       <c r="H48" t="s">
-        <v>640</v>
+        <v>561</v>
       </c>
       <c r="I48" t="s">
-        <v>641</v>
+        <v>562</v>
       </c>
       <c r="J48" t="s">
-        <v>642</v>
+        <v>563</v>
       </c>
       <c r="K48" t="s">
-        <v>637</v>
+        <v>559</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B49">
         <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D49" t="s">
-        <v>829</v>
+        <v>609</v>
       </c>
       <c r="E49" t="s">
-        <v>830</v>
+        <v>610</v>
       </c>
       <c r="F49" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>832</v>
+        <v>604</v>
       </c>
       <c r="H49" t="s">
-        <v>834</v>
+        <v>613</v>
       </c>
       <c r="I49" t="s">
-        <v>835</v>
+        <v>614</v>
       </c>
       <c r="J49" t="s">
-        <v>836</v>
+        <v>615</v>
       </c>
       <c r="K49" t="s">
-        <v>831</v>
+        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B50">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>627</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>628</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="H50" t="s">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>633</v>
       </c>
       <c r="J50" t="s">
-        <v>62</v>
+        <v>634</v>
       </c>
       <c r="K50" t="s">
-        <v>57</v>
+        <v>629</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B51">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="E51" t="s">
-        <v>89</v>
+        <v>636</v>
       </c>
       <c r="F51" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>131</v>
+        <v>638</v>
       </c>
       <c r="H51" t="s">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="I51" t="s">
-        <v>134</v>
+        <v>641</v>
       </c>
       <c r="J51" t="s">
-        <v>135</v>
+        <v>642</v>
       </c>
       <c r="K51" t="s">
-        <v>129</v>
+        <v>637</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B52">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D52" t="s">
-        <v>300</v>
+        <v>829</v>
       </c>
       <c r="E52" t="s">
-        <v>308</v>
+        <v>830</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>785</v>
       </c>
       <c r="G52" t="s">
-        <v>310</v>
+        <v>832</v>
       </c>
       <c r="H52" t="s">
-        <v>312</v>
+        <v>834</v>
       </c>
       <c r="I52" t="s">
-        <v>313</v>
+        <v>835</v>
       </c>
       <c r="J52" t="s">
-        <v>314</v>
+        <v>836</v>
       </c>
       <c r="K52" t="s">
-        <v>309</v>
+        <v>831</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B53">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>402</v>
+        <v>845</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>872</v>
       </c>
       <c r="E53" t="s">
-        <v>403</v>
+        <v>873</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G53" t="s">
-        <v>405</v>
+        <v>875</v>
       </c>
       <c r="H53" t="s">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="I53" t="s">
-        <v>408</v>
+        <v>878</v>
       </c>
       <c r="J53" t="s">
-        <v>409</v>
+        <v>879</v>
       </c>
       <c r="K53" t="s">
-        <v>404</v>
+        <v>874</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B54">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>473</v>
+        <v>845</v>
       </c>
       <c r="D54" t="s">
-        <v>474</v>
+        <v>880</v>
       </c>
       <c r="E54" t="s">
-        <v>475</v>
+        <v>881</v>
       </c>
       <c r="F54" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>478</v>
+        <v>883</v>
       </c>
       <c r="H54" t="s">
-        <v>480</v>
+        <v>885</v>
       </c>
       <c r="I54" t="s">
-        <v>481</v>
+        <v>886</v>
       </c>
       <c r="J54" t="s">
-        <v>482</v>
+        <v>887</v>
       </c>
       <c r="K54" t="s">
-        <v>476</v>
+        <v>882</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B55">
         <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>773</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>774</v>
+        <v>55</v>
       </c>
       <c r="E55" t="s">
-        <v>783</v>
+        <v>56</v>
       </c>
       <c r="F55" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>786</v>
+        <v>58</v>
       </c>
       <c r="H55" t="s">
-        <v>788</v>
+        <v>60</v>
       </c>
       <c r="I55" t="s">
-        <v>789</v>
+        <v>61</v>
       </c>
       <c r="J55" t="s">
-        <v>790</v>
+        <v>62</v>
       </c>
       <c r="K55" t="s">
-        <v>784</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B56">
         <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>773</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>799</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F56" t="s">
-        <v>793</v>
+        <v>130</v>
       </c>
       <c r="G56" t="s">
-        <v>802</v>
+        <v>131</v>
       </c>
       <c r="H56" t="s">
-        <v>804</v>
+        <v>133</v>
       </c>
       <c r="I56" t="s">
-        <v>805</v>
+        <v>134</v>
       </c>
       <c r="J56" t="s">
-        <v>806</v>
+        <v>135</v>
       </c>
       <c r="K56" t="s">
-        <v>801</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B57">
         <v>85</v>
       </c>
       <c r="C57" t="s">
-        <v>773</v>
+        <v>284</v>
       </c>
       <c r="D57" t="s">
-        <v>821</v>
+        <v>300</v>
       </c>
       <c r="E57" t="s">
-        <v>822</v>
+        <v>308</v>
       </c>
       <c r="F57" t="s">
-        <v>777</v>
+        <v>147</v>
       </c>
       <c r="G57" t="s">
-        <v>824</v>
+        <v>310</v>
       </c>
       <c r="H57" t="s">
-        <v>826</v>
+        <v>312</v>
       </c>
       <c r="I57" t="s">
-        <v>827</v>
+        <v>313</v>
       </c>
       <c r="J57" t="s">
-        <v>828</v>
+        <v>314</v>
       </c>
       <c r="K57" t="s">
-        <v>823</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B58">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E58" t="s">
-        <v>145</v>
+        <v>403</v>
       </c>
       <c r="F58" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>148</v>
+        <v>405</v>
       </c>
       <c r="H58" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="I58" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
       <c r="J58" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
       <c r="K58" t="s">
-        <v>146</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B59">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>474</v>
       </c>
       <c r="E59" t="s">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="F59" t="s">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="G59" t="s">
-        <v>397</v>
+        <v>478</v>
       </c>
       <c r="H59" t="s">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="I59" t="s">
-        <v>400</v>
+        <v>481</v>
       </c>
       <c r="J59" t="s">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K59" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B60">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>402</v>
+        <v>773</v>
       </c>
       <c r="D60" t="s">
-        <v>410</v>
+        <v>774</v>
       </c>
       <c r="E60" t="s">
-        <v>411</v>
+        <v>783</v>
       </c>
       <c r="F60" t="s">
-        <v>66</v>
+        <v>785</v>
       </c>
       <c r="G60" t="s">
-        <v>413</v>
+        <v>786</v>
       </c>
       <c r="H60" t="s">
-        <v>415</v>
+        <v>788</v>
       </c>
       <c r="I60" t="s">
-        <v>416</v>
+        <v>789</v>
       </c>
       <c r="J60" t="s">
-        <v>417</v>
+        <v>790</v>
       </c>
       <c r="K60" t="s">
-        <v>412</v>
+        <v>784</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B61">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>473</v>
+        <v>773</v>
       </c>
       <c r="D61" t="s">
-        <v>483</v>
+        <v>799</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>800</v>
       </c>
       <c r="F61" t="s">
-        <v>485</v>
+        <v>793</v>
       </c>
       <c r="G61" t="s">
-        <v>486</v>
+        <v>802</v>
       </c>
       <c r="H61" t="s">
-        <v>488</v>
+        <v>804</v>
       </c>
       <c r="I61" t="s">
-        <v>489</v>
+        <v>805</v>
       </c>
       <c r="J61" t="s">
-        <v>490</v>
+        <v>806</v>
       </c>
       <c r="K61" t="s">
-        <v>484</v>
+        <v>801</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B62">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D62" t="s">
-        <v>714</v>
+        <v>821</v>
       </c>
       <c r="E62" t="s">
-        <v>715</v>
+        <v>822</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="G62" t="s">
-        <v>604</v>
+        <v>824</v>
       </c>
       <c r="H62" t="s">
-        <v>718</v>
+        <v>826</v>
       </c>
       <c r="I62" t="s">
-        <v>719</v>
+        <v>827</v>
       </c>
       <c r="J62" t="s">
-        <v>720</v>
+        <v>828</v>
       </c>
       <c r="K62" t="s">
-        <v>716</v>
+        <v>823</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B63">
         <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>697</v>
+        <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>721</v>
+        <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>722</v>
+        <v>145</v>
       </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="G63" t="s">
-        <v>724</v>
+        <v>148</v>
       </c>
       <c r="H63" t="s">
-        <v>726</v>
+        <v>150</v>
       </c>
       <c r="I63" t="s">
-        <v>727</v>
+        <v>151</v>
       </c>
       <c r="J63" t="s">
-        <v>728</v>
+        <v>152</v>
       </c>
       <c r="K63" t="s">
-        <v>723</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B64">
         <v>84</v>
       </c>
       <c r="C64" t="s">
-        <v>697</v>
+        <v>284</v>
       </c>
       <c r="D64" t="s">
-        <v>729</v>
+        <v>144</v>
       </c>
       <c r="E64" t="s">
-        <v>730</v>
+        <v>394</v>
       </c>
       <c r="F64" t="s">
-        <v>535</v>
+        <v>396</v>
       </c>
       <c r="G64" t="s">
-        <v>732</v>
+        <v>397</v>
       </c>
       <c r="H64" t="s">
-        <v>726</v>
+        <v>399</v>
       </c>
       <c r="I64" t="s">
-        <v>734</v>
+        <v>400</v>
       </c>
       <c r="J64" t="s">
-        <v>735</v>
+        <v>401</v>
       </c>
       <c r="K64" t="s">
-        <v>731</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B65">
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D65" t="s">
-        <v>791</v>
+        <v>410</v>
       </c>
       <c r="E65" t="s">
-        <v>610</v>
+        <v>411</v>
       </c>
       <c r="F65" t="s">
-        <v>793</v>
+        <v>66</v>
       </c>
       <c r="G65" t="s">
-        <v>794</v>
+        <v>413</v>
       </c>
       <c r="H65" t="s">
-        <v>796</v>
+        <v>415</v>
       </c>
       <c r="I65" t="s">
-        <v>797</v>
+        <v>416</v>
       </c>
       <c r="J65" t="s">
-        <v>798</v>
+        <v>417</v>
       </c>
       <c r="K65" t="s">
-        <v>792</v>
+        <v>412</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B66">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D66" t="s">
-        <v>353</v>
+        <v>483</v>
       </c>
       <c r="E66" t="s">
-        <v>362</v>
+        <v>122</v>
       </c>
       <c r="F66" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="G66" t="s">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="H66" t="s">
-        <v>366</v>
+        <v>488</v>
       </c>
       <c r="I66" t="s">
-        <v>367</v>
+        <v>489</v>
       </c>
       <c r="J66" t="s">
-        <v>368</v>
+        <v>490</v>
       </c>
       <c r="K66" t="s">
-        <v>363</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B67">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>473</v>
+        <v>697</v>
       </c>
       <c r="D67" t="s">
-        <v>491</v>
+        <v>714</v>
       </c>
       <c r="E67" t="s">
-        <v>492</v>
+        <v>715</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>494</v>
+        <v>604</v>
       </c>
       <c r="H67" t="s">
-        <v>496</v>
+        <v>718</v>
       </c>
       <c r="I67" t="s">
-        <v>497</v>
+        <v>719</v>
       </c>
       <c r="J67" t="s">
-        <v>498</v>
+        <v>720</v>
       </c>
       <c r="K67" t="s">
-        <v>493</v>
+        <v>716</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B68">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>473</v>
+        <v>697</v>
       </c>
       <c r="D68" t="s">
-        <v>532</v>
+        <v>721</v>
       </c>
       <c r="E68" t="s">
-        <v>533</v>
+        <v>722</v>
       </c>
       <c r="F68" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G68" t="s">
-        <v>536</v>
+        <v>724</v>
       </c>
       <c r="H68" t="s">
-        <v>538</v>
+        <v>726</v>
       </c>
       <c r="I68" t="s">
-        <v>539</v>
+        <v>727</v>
       </c>
       <c r="J68" t="s">
-        <v>540</v>
+        <v>728</v>
       </c>
       <c r="K68" t="s">
-        <v>534</v>
+        <v>723</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B69">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="D69" t="s">
-        <v>643</v>
+        <v>729</v>
       </c>
       <c r="E69" t="s">
-        <v>644</v>
+        <v>730</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G69" t="s">
-        <v>618</v>
+        <v>732</v>
       </c>
       <c r="H69" t="s">
-        <v>647</v>
+        <v>726</v>
       </c>
       <c r="I69" t="s">
-        <v>648</v>
+        <v>734</v>
       </c>
       <c r="J69" t="s">
-        <v>649</v>
+        <v>735</v>
       </c>
       <c r="K69" t="s">
-        <v>645</v>
+        <v>731</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B70">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C70" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D70" t="s">
-        <v>736</v>
+        <v>791</v>
       </c>
       <c r="E70" t="s">
-        <v>737</v>
+        <v>610</v>
       </c>
       <c r="F70" t="s">
-        <v>739</v>
+        <v>793</v>
       </c>
       <c r="G70" t="s">
-        <v>604</v>
+        <v>794</v>
       </c>
       <c r="H70" t="s">
-        <v>741</v>
+        <v>796</v>
       </c>
       <c r="I70" t="s">
-        <v>742</v>
+        <v>797</v>
       </c>
       <c r="J70" t="s">
-        <v>743</v>
+        <v>798</v>
       </c>
       <c r="K70" t="s">
-        <v>738</v>
+        <v>792</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B71">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>773</v>
+        <v>845</v>
       </c>
       <c r="D71" t="s">
-        <v>807</v>
+        <v>896</v>
       </c>
       <c r="E71" t="s">
-        <v>808</v>
+        <v>897</v>
       </c>
       <c r="F71" t="s">
-        <v>810</v>
+        <v>25</v>
       </c>
       <c r="G71" t="s">
-        <v>811</v>
+        <v>899</v>
       </c>
       <c r="H71" t="s">
-        <v>813</v>
+        <v>901</v>
       </c>
       <c r="I71" t="s">
-        <v>814</v>
+        <v>902</v>
       </c>
       <c r="J71" t="s">
-        <v>815</v>
+        <v>903</v>
       </c>
       <c r="K71" t="s">
-        <v>809</v>
+        <v>898</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B72">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
-        <v>159</v>
+        <v>284</v>
       </c>
       <c r="D72" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="E72" t="s">
-        <v>228</v>
+        <v>362</v>
       </c>
       <c r="F72" t="s">
-        <v>230</v>
+        <v>356</v>
       </c>
       <c r="G72" t="s">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="H72" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="I72" t="s">
-        <v>234</v>
+        <v>367</v>
       </c>
       <c r="J72" t="s">
-        <v>235</v>
+        <v>368</v>
       </c>
       <c r="K72" t="s">
-        <v>229</v>
+        <v>363</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B73">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D73" t="s">
-        <v>266</v>
+        <v>491</v>
       </c>
       <c r="E73" t="s">
-        <v>267</v>
+        <v>492</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s">
-        <v>58</v>
+        <v>494</v>
       </c>
       <c r="H73" t="s">
-        <v>270</v>
+        <v>496</v>
       </c>
       <c r="I73" t="s">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="J73" t="s">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="K73" t="s">
-        <v>268</v>
+        <v>493</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B74">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>284</v>
+        <v>473</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>532</v>
       </c>
       <c r="E74" t="s">
-        <v>339</v>
+        <v>533</v>
       </c>
       <c r="F74" t="s">
-        <v>341</v>
+        <v>535</v>
       </c>
       <c r="G74" t="s">
-        <v>342</v>
+        <v>536</v>
       </c>
       <c r="H74" t="s">
-        <v>344</v>
+        <v>538</v>
       </c>
       <c r="I74" t="s">
-        <v>345</v>
+        <v>539</v>
       </c>
       <c r="J74" t="s">
-        <v>346</v>
+        <v>540</v>
       </c>
       <c r="K74" t="s">
-        <v>340</v>
+        <v>534</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B75">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
         <v>591</v>
       </c>
       <c r="D75" t="s">
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="E75" t="s">
-        <v>602</v>
+        <v>644</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="H75" t="s">
-        <v>606</v>
+        <v>647</v>
       </c>
       <c r="I75" t="s">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="J75" t="s">
-        <v>608</v>
+        <v>649</v>
       </c>
       <c r="K75" t="s">
-        <v>603</v>
+        <v>645</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B76">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>12</v>
+        <v>697</v>
       </c>
       <c r="D76" t="s">
-        <v>80</v>
+        <v>736</v>
       </c>
       <c r="E76" t="s">
-        <v>81</v>
+        <v>737</v>
       </c>
       <c r="F76" t="s">
-        <v>25</v>
+        <v>739</v>
       </c>
       <c r="G76" t="s">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="H76" t="s">
-        <v>85</v>
+        <v>741</v>
       </c>
       <c r="I76" t="s">
-        <v>86</v>
+        <v>742</v>
       </c>
       <c r="J76" t="s">
-        <v>87</v>
+        <v>743</v>
       </c>
       <c r="K76" t="s">
-        <v>82</v>
+        <v>738</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B77">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D77" t="s">
-        <v>377</v>
+        <v>807</v>
       </c>
       <c r="E77" t="s">
-        <v>378</v>
+        <v>808</v>
       </c>
       <c r="F77" t="s">
-        <v>380</v>
+        <v>810</v>
       </c>
       <c r="G77" t="s">
-        <v>381</v>
+        <v>811</v>
       </c>
       <c r="H77" t="s">
-        <v>383</v>
+        <v>813</v>
       </c>
       <c r="I77" t="s">
-        <v>384</v>
+        <v>814</v>
       </c>
       <c r="J77" t="s">
-        <v>385</v>
+        <v>815</v>
       </c>
       <c r="K77" t="s">
-        <v>379</v>
+        <v>809</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B78">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>473</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
-        <v>499</v>
+        <v>227</v>
       </c>
       <c r="E78" t="s">
-        <v>500</v>
+        <v>228</v>
       </c>
       <c r="F78" t="s">
-        <v>502</v>
+        <v>230</v>
       </c>
       <c r="G78" t="s">
-        <v>503</v>
+        <v>231</v>
       </c>
       <c r="H78" t="s">
-        <v>505</v>
+        <v>233</v>
       </c>
       <c r="I78" t="s">
-        <v>506</v>
+        <v>234</v>
       </c>
       <c r="J78" t="s">
-        <v>507</v>
+        <v>235</v>
       </c>
       <c r="K78" t="s">
-        <v>501</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>856</v>
+        <v>945</v>
       </c>
       <c r="B79">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D79" t="s">
-        <v>616</v>
+        <v>266</v>
       </c>
       <c r="E79" t="s">
-        <v>610</v>
+        <v>267</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
       </c>
       <c r="G79" t="s">
+        <v>58</v>
+      </c>
+      <c r="H79" t="s">
+        <v>270</v>
+      </c>
+      <c r="I79" t="s">
+        <v>79</v>
+      </c>
+      <c r="J79" t="s">
+        <v>79</v>
+      </c>
+      <c r="K79" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>945</v>
+      </c>
+      <c r="B80">
+        <v>82</v>
+      </c>
+      <c r="C80" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" t="s">
+        <v>338</v>
+      </c>
+      <c r="E80" t="s">
+        <v>339</v>
+      </c>
+      <c r="F80" t="s">
+        <v>341</v>
+      </c>
+      <c r="G80" t="s">
+        <v>342</v>
+      </c>
+      <c r="H80" t="s">
+        <v>344</v>
+      </c>
+      <c r="I80" t="s">
+        <v>345</v>
+      </c>
+      <c r="J80" t="s">
+        <v>346</v>
+      </c>
+      <c r="K80" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>945</v>
+      </c>
+      <c r="B81">
+        <v>82</v>
+      </c>
+      <c r="C81" t="s">
+        <v>591</v>
+      </c>
+      <c r="D81" t="s">
+        <v>601</v>
+      </c>
+      <c r="E81" t="s">
+        <v>602</v>
+      </c>
+      <c r="F81" t="s">
+        <v>75</v>
+      </c>
+      <c r="G81" t="s">
+        <v>604</v>
+      </c>
+      <c r="H81" t="s">
+        <v>606</v>
+      </c>
+      <c r="I81" t="s">
+        <v>607</v>
+      </c>
+      <c r="J81" t="s">
+        <v>608</v>
+      </c>
+      <c r="K81" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>945</v>
+      </c>
+      <c r="B82">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>80</v>
+      </c>
+      <c r="E82" t="s">
+        <v>81</v>
+      </c>
+      <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" t="s">
+        <v>83</v>
+      </c>
+      <c r="H82" t="s">
+        <v>85</v>
+      </c>
+      <c r="I82" t="s">
+        <v>86</v>
+      </c>
+      <c r="J82" t="s">
+        <v>87</v>
+      </c>
+      <c r="K82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>945</v>
+      </c>
+      <c r="B83">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>284</v>
+      </c>
+      <c r="D83" t="s">
+        <v>377</v>
+      </c>
+      <c r="E83" t="s">
+        <v>378</v>
+      </c>
+      <c r="F83" t="s">
+        <v>380</v>
+      </c>
+      <c r="G83" t="s">
+        <v>381</v>
+      </c>
+      <c r="H83" t="s">
+        <v>383</v>
+      </c>
+      <c r="I83" t="s">
+        <v>384</v>
+      </c>
+      <c r="J83" t="s">
+        <v>385</v>
+      </c>
+      <c r="K83" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>945</v>
+      </c>
+      <c r="B84">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
+        <v>473</v>
+      </c>
+      <c r="D84" t="s">
+        <v>499</v>
+      </c>
+      <c r="E84" t="s">
+        <v>500</v>
+      </c>
+      <c r="F84" t="s">
+        <v>502</v>
+      </c>
+      <c r="G84" t="s">
+        <v>503</v>
+      </c>
+      <c r="H84" t="s">
+        <v>505</v>
+      </c>
+      <c r="I84" t="s">
+        <v>506</v>
+      </c>
+      <c r="J84" t="s">
+        <v>507</v>
+      </c>
+      <c r="K84" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>945</v>
+      </c>
+      <c r="B85">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>591</v>
+      </c>
+      <c r="D85" t="s">
+        <v>616</v>
+      </c>
+      <c r="E85" t="s">
+        <v>610</v>
+      </c>
+      <c r="F85" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" t="s">
         <v>618</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H85" t="s">
         <v>620</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I85" t="s">
         <v>621</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J85" t="s">
         <v>622</v>
       </c>
-      <c r="K79" t="s">
+      <c r="K85" t="s">
         <v>617</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>945</v>
+      </c>
+      <c r="B86">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>845</v>
+      </c>
+      <c r="D86" t="s">
+        <v>888</v>
+      </c>
+      <c r="E86" t="s">
+        <v>889</v>
+      </c>
+      <c r="F86" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" t="s">
+        <v>891</v>
+      </c>
+      <c r="H86" t="s">
+        <v>893</v>
+      </c>
+      <c r="I86" t="s">
+        <v>894</v>
+      </c>
+      <c r="J86" t="s">
+        <v>895</v>
+      </c>
+      <c r="K86" t="s">
+        <v>890</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="975">
   <si>
     <t>日期</t>
   </si>
@@ -2888,6 +2888,9 @@
   </si>
   <si>
     <t>数据更新日期</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
   </si>
   <si>
     <t>匹配度评分分布</t>
@@ -8363,12 +8366,12 @@
         <v>957</v>
       </c>
       <c r="B11" t="s">
-        <v>845</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -8378,15 +8381,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -8394,7 +8397,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B17" s="5">
         <v>55</v>
@@ -8402,7 +8405,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B18" s="5">
         <v>59</v>
@@ -8410,7 +8413,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B19" s="5">
         <v>5</v>
@@ -8418,7 +8421,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -8426,7 +8429,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -8434,7 +8437,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8450,7 +8453,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -8458,7 +8461,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -8466,7 +8469,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -8478,7 +8481,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -8496,7 +8499,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="1127">
   <si>
     <t>日期</t>
   </si>
@@ -2818,6 +2818,465 @@
     <t>突出高分子材料合成/改性/表征能力与生物医用方向；强调可降解塑料、弹性体或医用高分子选题；列出材料学专著论文与表征数据以匹配课题组方向。</t>
   </si>
   <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>校园招聘（研发方向：冠状动脉药物支架等心血管植介入器械）</t>
+  </si>
+  <si>
+    <t>已上市公司，从事冠状动脉药物支架、先心封堵器、心脏瓣膜、造影机等心血管疾病植介入诊疗器械研发。面向2026/2027届毕业生招聘研发方向岗位，涉及高分子/金属材料、结构设计、临床注册等，工作地为北京。</t>
+  </si>
+  <si>
+    <t>https://www.lepumedical.com/join_lepu.html</t>
+  </si>
+  <si>
+    <t>智能匹配89分【校园招聘】|强烈推荐|冠状动脉药物支架/心血管植介入研发校招岗，方向直接匹配，上市龙头平台</t>
+  </si>
+  <si>
+    <t>研究90/技能75/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>乐普为国产心血管植介入（冠脉药物支架）龙头上市企业（目标公司），岗位明确面向应届生做冠脉药物支架等心血管植介入器械研发，与硕士血管支架研究方向高度一致；北京工作地契合城市偏好，应届可投，是切入心血管植介入器械研发的顶级校招平台。</t>
+  </si>
+  <si>
+    <t>突出冠脉支架/可降解支架研究课题与结构设计、材料学项目；强调生物相容性评价（ISO10993方法与数据）与动物实验经历；量化降解性能、力学测试数据；标注北京可到岗时间与应届毕业时间。</t>
+  </si>
+  <si>
+    <t>元心科技（bioTyx）</t>
+  </si>
+  <si>
+    <t>研发工程师（可吸收支架方向）</t>
+  </si>
+  <si>
+    <t>硕士及以上（优秀本科亦可），化学/材料/机械/生物医学/药学理工专业；英文CET4-6，掌握AutoCAD及一款3D软件优先；负责铁基可吸收支架的产品设计、测试与工艺开发。公司主营铁基可吸收药物支架。</t>
+  </si>
+  <si>
+    <t>https://www.biotyxmed.com/join.html</t>
+  </si>
+  <si>
+    <t>智能匹配89分【社招（接受应届硕士）】|强烈推荐|铁基可吸收支架研发岗，研究方向直接匹配，接受应届硕士，深圳</t>
+  </si>
+  <si>
+    <t>研究90/技能80/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>元心科技专注铁基可吸收药物支架，与硕士可降解血管支架研究方向完全一致；岗位接受硕士应届、明确要求材料/生物医学/机械理工背景、AutoCAD/3D软件技能，与材料学+支架设计技能重合度高；深圳为偏好城市。</t>
+  </si>
+  <si>
+    <t>重点突出可降解/可吸收支架研究课题、金属（镍钛/铁基）与高分子材料性能测试；列出AutoCAD/SolidWorks三维建模与力学仿真项目；补充可降解材料降解性能与生物相容性评价数据。</t>
+  </si>
+  <si>
+    <t>先健科技</t>
+  </si>
+  <si>
+    <t>博士后（可吸收支架药物控释技术等）</t>
+  </si>
+  <si>
+    <t>博士毕业3年内，金属材料/机械/化学/力学相关专业，SCI一作论文1篇以上；课题含可吸收支架药物控释、生物可吸收材料优化、生物医用材料表面处理等。先健为铁基可吸收支架领军上市企业。</t>
+  </si>
+  <si>
+    <t>智能匹配89分【博士后】|强烈推荐|可吸收支架药物控释/生物可吸收材料课题，方向直接匹配，上市平台</t>
+  </si>
+  <si>
+    <t>研究90/技能85/学历80/行业100/企业95</t>
+  </si>
+  <si>
+    <t>先健为铁基可吸收血管支架领军上市企业（目标公司），博士后课题聚焦可吸收支架药物控释与生物可吸收材料优化，与硕士研究方向及材料学+生物相容性评价技能高度契合；可借此进入可吸收支架研发一线。</t>
+  </si>
+  <si>
+    <t>突出可降解支架/载药缓释研究经历与SCI一作论文；强调可降解材料、表面处理、药物控释相关项目；附完整论文/专利清单与导师推荐，补充ISO10993生物相容性评价数据。</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（血管支架）</t>
+  </si>
+  <si>
+    <t>港交所主板上市心内介入器械企业，具备自主模具开发、产品研发、设备开发、自主灭菌完整产业链，通过ISO13485/CE/FDA认证。招聘血管支架研发工程师，研发方向契合生物医学工程/材料学背景。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/</t>
+  </si>
+  <si>
+    <t>智能匹配88分【社招（应届可投）】|强烈推荐|血管支架研发岗，方向直接匹配，上海上市企业</t>
+  </si>
+  <si>
+    <t>研究90/技能80/学历90/行业100/企业90</t>
+  </si>
+  <si>
+    <t>瑛泰为港交所上市心内介入器械企业，血管支架研发岗与硕士研究方向完全一致；上海为偏好城市，上市平台规范，ISO13485/CE/FDA体系完善，可系统参与支架产品研发全流程。</t>
+  </si>
+  <si>
+    <t>突出血管支架结构设计、材料学与力学评价项目；强调生物相容性与ISO10993评价数据；补充对ISO13485质量管理体系的理解；量化支架性能测试结果。</t>
+  </si>
+  <si>
+    <t>广东博迈医疗科技股份有限公司</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（研发技术类：研发/材料/机械/临床注册）</t>
+  </si>
+  <si>
+    <t>面向2026届海内外本硕博毕业生，研发技术类含研发、材料、机械、临床注册等岗位；专业含高分子材料、临床医学、药学、机械等。公司专注血管介入、外周介入与药物球囊（Vasecure输送系统）研发。</t>
+  </si>
+  <si>
+    <t>深圳/东莞等</t>
+  </si>
+  <si>
+    <t>https://app.mokahr.com/m/campus-recruitment/brosmed/146155</t>
+  </si>
+  <si>
+    <t>智能匹配84分【校园招聘】|强烈推荐|血管介入/药物球囊研发技术类校招，材料学背景对口，应届重点</t>
+  </si>
+  <si>
+    <t>研究85/技能70/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>博迈医疗专注血管介入/外周介入与药物球囊，研发技术类明确面向2026届本硕博应届生，高分子材料等专业对口；是应届切入血管介入器械研发的优质校招机会，深圳符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出血管介入/球囊支架研究方向与高分子材料项目；补充药物涂层或可降解球囊方向认知；量化材料性能与临床注册相关项目；标注深圳可到岗及毕业时间。</t>
+  </si>
+  <si>
+    <t>心脉医疗（微创系）</t>
+  </si>
+  <si>
+    <t>工艺工程师（心血管介入输送系统/支架）</t>
+  </si>
+  <si>
+    <t>硕士及以上，机械/化学/高分子专业；熟悉常见工程材料及加工特性，掌握CAD/Solidworks；参与新产品工艺设计、小批量试产、动物实验与性能验证。公司为主动脉及外周血管介入龙头。</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招（接受应届硕士）】|强烈推荐|血管介入输送系统工艺+动物实验，材料学/设计技能匹配，上市龙头</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>心脉医疗为主动脉及外周血管介入上市龙头（微创系），工艺工程师岗涉及支架/输送系统工艺设计与动物实验、性能验证，与硕士材料学、支架设计与动物实验技能匹配；上海偏好城市，硕士可投。</t>
+  </si>
+  <si>
+    <t>突出支架/输送系统设计与材料加工工艺项目；强调动物实验（模型构建、植入随访、影像/组织学评估）完整流程；补充CAD/SolidWorks技能与工艺验证数据。</t>
+  </si>
+  <si>
+    <t>沛嘉医疗</t>
+  </si>
+  <si>
+    <t>研发工程师（神经介入：弹簧圈/球囊/支架/通路）</t>
+  </si>
+  <si>
+    <t>负责神经介入类产品（弹簧圈、球囊、支架、通路产品）研发；要求机械/材料相关专业，熟悉医疗器械生产质量管理规范。沛嘉为结构性心脏病及神经介入上市企业。</t>
+  </si>
+  <si>
+    <t>苏州等</t>
+  </si>
+  <si>
+    <t>https://peijia.zhiye.com/social</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招（接受应届）】|强烈推荐|神经介入支架/球囊研发，方向相关，材料学/设计技能匹配，苏州</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历90/行业100/企业90</t>
+  </si>
+  <si>
+    <t>沛嘉为结构性心脏病及神经介入上市企业，研发工程师做神经介入支架/球囊等，方向与硕士介入器械研究相关，材料学背景对口；苏州符合城市偏好，上市平台规范。</t>
+  </si>
+  <si>
+    <t>突出介入支架/球囊结构设计与材料选型项目；补充对神经介入器械与ISO13485/GMP的认知；量化结构与力学评价数据；强调医疗器械生产质量管理规范理解。</t>
+  </si>
+  <si>
+    <t>熠品（检测/测试服务）</t>
+  </si>
+  <si>
+    <t>血管植入产品测试工程师（心血管支架、瓣膜、介入球囊）</t>
+  </si>
+  <si>
+    <t>负责心血管支架、心脏瓣膜、介入球囊等植入物测试；本科以上，3-5年医药/材料背景，熟悉生物相容性及相关测试标准。测试方向与生物相容性评价、材料评价相关。</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|心血管支架/介入球囊植入物测试，生物相容性评价技能高度匹配，苏州</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位负责心血管支架等植入物的性能与生物相容性测试，与硕士生物相容性评价与材料学技能直接相关；苏州为偏好城市，可深度掌握介入器械测试标准与评价方法，是切入介入器械领域的应用型机会。</t>
+  </si>
+  <si>
+    <t>突出生物相容性评价（ISO10993：细胞毒性/溶血/凝血）与材料性能测试项目；量化测试方法与数据；补充对支架/球囊结构和相关检测标准的理解。</t>
+  </si>
+  <si>
+    <t>研发工程师（金属材料）</t>
+  </si>
+  <si>
+    <t>本科及以上，金属材料专业；熟悉镍钛金属材料特性与工艺，掌握金相、DSC、SEM、拉力机、TEM等材料测试方法；负责医疗器械金属材料失效分析、工艺优化及产品开发。</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招（接受应届）】|强烈推荐|镍钛金属材料工艺/失效分析，材料学技能高度覆盖，上市平台</t>
+  </si>
+  <si>
+    <t>研究85/技能80/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>先健为介入/植入耗材上市企业，金属材料研发岗明确要求镍钛金属材料特性与金相/SEM/拉力机等测试方法，与硕士材料学技能高度契合；可结合铁基可吸收支架方向，深圳偏好城市。</t>
+  </si>
+  <si>
+    <t>突出镍钛/金属材料表征测试（SEM、金相、拉伸）项目；强调金属材料性能与失效分析能力；补充材料工艺优化与支架结构应用；列出具体测试数据与工具掌握情况。</t>
+  </si>
+  <si>
+    <t>高级/资深工艺工程师（可降解材料）</t>
+  </si>
+  <si>
+    <t>硕士及以上高分子材料/化学/生物材料，3年以上聚乳酸、PDO等可降解材料研发经验，熟悉材料物化/力学性能及注塑成型工艺。公司从事可降解材料介入器械研发。</t>
+  </si>
+  <si>
+    <t>东莞</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|聚乳酸/PDO可降解材料工艺，方向直接匹配，要求3年经验</t>
+  </si>
+  <si>
+    <t>研究90/技能82/学历60/行业100/企业90</t>
+  </si>
+  <si>
+    <t>岗位聚焦聚乳酸/PDO等可降解材料研发工艺，与硕士可降解支架材料学方向高度契合，可借助可降解材料研究背景在材料与工艺维度差异化竞争；适合作为可降解介入材料方向的进阶机会。</t>
+  </si>
+  <si>
+    <t>突出可降解高分子材料（聚乳酸等）合成/改性/表征项目；补充材料力学性能测试与注塑/加工工艺认知；量化降解性能与工艺参数；弱化经验差距、强化材料学专业深度。</t>
+  </si>
+  <si>
+    <t>『115训练营』千人星计划（应届生高潜项目）</t>
+  </si>
+  <si>
+    <t>面向应届生选拔对医疗行业有热情的人才，6个月集中培训+12个月项目学习，培养集团技术骨干或创新创业领军人才；覆盖新材料、表面处理等前沿方向。微创集团为全球领先医疗科技企业。</t>
+  </si>
+  <si>
+    <t>https://app.mokahr.com/campus-recruitment/microport/56155</t>
+  </si>
+  <si>
+    <t>智能匹配82分【校园招聘】|强烈推荐|微创应届高潜项目，新材料/表面处理方向，技能相关，上市龙头</t>
+  </si>
+  <si>
+    <t>研究70/技能75/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>微创为全球领先介入医疗科技龙头，115训练营为应届生高潜培养项目，覆盖新材料、表面处理等与血管支架工艺相关的前沿方向；上海偏好城市，应届高潜项目是进入医疗龙头技术线的优质通道。</t>
+  </si>
+  <si>
+    <t>突出材料学与生物相容性评价项目（新材料/表面改性）；强调学习能力与医疗行业热情；补充支架材料、表面处理相关经验与论文/项目成果；标注应届身份与综合软实力。</t>
+  </si>
+  <si>
+    <t>2026届校园招聘（心血管介入领域研发）</t>
+  </si>
+  <si>
+    <t>国家级高新技术企业，产品涵盖超声医学影像、内镜诊疗、微创外科和心血管介入等领域；面向应届生招聘研发方向岗位，涉及介入器械研发。</t>
+  </si>
+  <si>
+    <t>https://www.sonoscape.com/</t>
+  </si>
+  <si>
+    <t>智能匹配83分【校园招聘】|强烈推荐|心血管介入领域应届研发岗，方向相关，深圳上市企业</t>
+  </si>
+  <si>
+    <t>研究85/技能65/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>开立为上市高新技术企业，业务涵盖心血管介入领域，面向应届生招聘研发岗；方向与硕士介入器械研究相关，深圳为偏好城市，应届可投。</t>
+  </si>
+  <si>
+    <t>突出心血管介入器械研究方向与材料/机械背景；补充介入器械相关项目与技能；量化科研产出；强调深圳到岗意愿与应届毕业时间。</t>
+  </si>
+  <si>
+    <t>波士顿科学（波士顿科学上海）</t>
+  </si>
+  <si>
+    <t>心脏介入事业部2026届校园招聘</t>
+  </si>
+  <si>
+    <t>全球医疗技术引领者，心脏介入器械事业部面向2026届校园招聘研发/技术类岗位，涉及介入导管、球囊、支架等心脏介入器械。</t>
+  </si>
+  <si>
+    <t>上海/北京</t>
+  </si>
+  <si>
+    <t>https://www.bostonscientific.cn/CareerDevelopment/CampusRecruitment</t>
+  </si>
+  <si>
+    <t>智能匹配82分【校园招聘】|强烈推荐|心脏介入器械外企龙头校招，方向相关，应届重点</t>
+  </si>
+  <si>
+    <t>研究85/技能60/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>波士顿科学为全球心脏介入器械领先外企，心脏介入事业部面向应届生校招，方向与硕士介入器械研究相关，上海/北京符合城市偏好，外企平台可接触全球领先介入器械技术与国际化研发流程。</t>
+  </si>
+  <si>
+    <t>突出介入器械研究方向与英文能力；补充介入导管/支架/球囊相关认知；强调生物医学工程背景与跨文化交流能力；量化科研项目与英文证书。</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（面向应届研究生）</t>
+  </si>
+  <si>
+    <t>聚焦神经介入三类医疗器械研发与产业化，具备自主知识产权的神经介入III类器械产品生产技术；面向应届研究生招聘，机械/材料/生物医学工程专业。</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com/</t>
+  </si>
+  <si>
+    <t>智能匹配84分【校园招聘】|强烈推荐|神经介入三类器械研发，明确面向应届研究生，方向相关</t>
+  </si>
+  <si>
+    <t>研究85/技能72/学历100/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位明确面向应届研究生招聘，研发神经介入三类器械（含取栓/通路等），与硕士介入器械研究方向相关，材料/机械/生医工背景对口，应届可投。</t>
+  </si>
+  <si>
+    <t>突出介入器械/支架结构设计与材料项目；补充三类器械法规与研发流程认知；量化结构与力学评价数据；强调应届研究生身份与可到岗时间（珠海需权衡但可标注接受）。</t>
+  </si>
+  <si>
+    <t>迈瑞医疗 Mindray</t>
+  </si>
+  <si>
+    <t>2027届校园招聘（医疗器械研发方向）</t>
+  </si>
+  <si>
+    <t>医疗器械综合龙头，主营监护、体外诊断、医学影像等；面向2027届应届生招聘研发类岗位，含医疗器械、生物医学工程、材料等领域。</t>
+  </si>
+  <si>
+    <t>深圳（总部）</t>
+  </si>
+  <si>
+    <t>https://career.sysu.edu.cn/news/view/aid/575853/tag/twlj</t>
+  </si>
+  <si>
+    <t>智能匹配80分【校园招聘】|强烈推荐|医疗器械综合龙头2027校招，方向泛匹配，深圳上市巨头</t>
+  </si>
+  <si>
+    <t>研究75/技能65/学历100/行业100/企业95</t>
+  </si>
+  <si>
+    <t>迈瑞为国内医疗器械综合龙头（上市），2027届校招研发岗面向材料/生物医学工程背景；深圳偏好城市，平台体量规范，可系统性掌握医疗器械研发流程，作为医疗器械研发的稳健起步平台。</t>
+  </si>
+  <si>
+    <t>突出医疗器械相关研究方向（非介入细分可弱化）；强调材料学与生物医学工程综合背景、研发项目经历；量化成果；标注深圳到岗意愿与毕业时间。</t>
+  </si>
+  <si>
+    <t>大博医疗科技股份有限公司</t>
+  </si>
+  <si>
+    <t>骨科植入物研发（空中宣讲会）</t>
+  </si>
+  <si>
+    <t>国内骨科植入物（创伤/脊柱/关节）龙头企业，上海交大就业网设空中宣讲会，招聘骨科植入物材料、设计、工艺研发及临床转化应届人才。</t>
+  </si>
+  <si>
+    <t>上海（空中宣讲）</t>
+  </si>
+  <si>
+    <t>http://www.job.sjtu.edu.cn</t>
+  </si>
+  <si>
+    <t>智能匹配83分【校园招聘（宣讲会）】|强烈推荐|骨科植入物材料/设计/工艺研发校招，植入器械方向相关，上市龙头</t>
+  </si>
+  <si>
+    <t>研究80/技能70/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>大博医疗为骨科植入物上市龙头，研发岗涉及材料、结构设计与工艺，与硕士植入器械材料+设计技能相关；对标到材料学/植入装置背景的优势，可作为植入器械研发方向的优质校招选择。</t>
+  </si>
+  <si>
+    <t>突出材料学与植入器械结构设计项目；补充可降解/金属合金材料性能测试；强调临床转化与工艺开发意识；附材料学与结构力学项目成果。</t>
+  </si>
+  <si>
+    <t>复旦大学丁建东课题组（生物医用材料）</t>
+  </si>
+  <si>
+    <t>博士后（生物医用材料/医疗器械研发与转化）</t>
+  </si>
+  <si>
+    <t>复旦大学生物医用材料课题组诚聘博士后，从事生物材料、医疗器械研发与临床转化；面向博士生及科研人员，重点支持植介入医疗器械、生物医用材料方向博士后研究。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=%E5%A4%8D%E6%97%A6%E5%85%AC%E5%B8%88%E7%94%B2%E7%A7%91%E9%A2%98%E7%BB%84%20%E7%94%9F%E7%89%A9%E5%8C%BB%E7%94%A8%E6%9D%90%E6%96%99%20%E6%8B%9B%E8%81%98</t>
+  </si>
+  <si>
+    <t>智能匹配84分【博士后】|强烈推荐|生物医用材料/植介入医疗器械与转化，材料学+生物相容技能覆盖</t>
+  </si>
+  <si>
+    <t>研究80/技能82/学历80/行业100/企业90</t>
+  </si>
+  <si>
+    <t>复旦丁建东课题组聚焦生物医用材料与植介入医疗器械研发转化，与硕士材料学、生物相容性评价研究高度契合；上海偏好城市，一流高校平台，适合深耕生物医用材料与器械方向。</t>
+  </si>
+  <si>
+    <t>突出生物医用材料与植介入器械研究课题；补充材料性能与生物相容性评价（ISO10993）、动物实验数据；量化科研产出；说明与课题组植介入方向衔接的研究规划。</t>
+  </si>
+  <si>
+    <t>浙江大学计剑教授课题组</t>
+  </si>
+  <si>
+    <t>博士后、科研助理（植介入医疗器械/生物医用高分子材料）</t>
+  </si>
+  <si>
+    <t>招聘博士后及科研助理，方向涵盖高分子生物医用材料、微纳生物诊疗材料、可穿戴或植介入生物医学传感等，推动高端植介入医疗器械创新研发；面向生物医学工程、材料、高分子等相关专业。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=%E6%B5%99%E5%A4%A7%E8%AE%A1%E5%89%91%E8%AF%BE%E9%A2%98%E7%BB%84%20%E7%A7%8D%E7%A7%8D%E5%A2%9E%E8%82%A2%E5%85%A5%E5%8C%BB%E7%96%97%E5%99%A8%20%E6%8B%9B%E8%81%98</t>
+  </si>
+  <si>
+    <t>智能匹配85分【博士后/科研岗】|强烈推荐|植介入医疗器械/生物医用高分子材料，材料学+生物相容技能覆盖</t>
+  </si>
+  <si>
+    <t>研究82/技能82/学历85/行业100/企业90</t>
+  </si>
+  <si>
+    <t>浙大计剑课题组研究植介入医疗器械与生物医用高分子材料，材料学+生物相容性评价技能高度契合；含科研助理岗（对硕士更友好），是进入植介入器械研发科研一线的优质平台。</t>
+  </si>
+  <si>
+    <t>突出高分子生物医用材料与植介入器械研究；补充材料性能与生物相容性评价、动物实验数据；量化科研产出；说明与课题组植介入方向的研究衔接。</t>
+  </si>
+  <si>
+    <t>浙江省心血管介入与再生修复研究重点实验室</t>
+  </si>
+  <si>
+    <t>特聘研究员、博士后、PI助手、科研助理、技术员</t>
+  </si>
+  <si>
+    <t>诚聘专职科研人员，主要方向为心血管基础研究、心血管植介入材料转化研究；团队致力于缺血性心脏病再生修复治疗和心血管植介入器械研究；面向心血管、生物医学工程、材料学等相关专业。</t>
+  </si>
+  <si>
+    <t>浙江</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/weixin?type=2&amp;query=%E6%B5%99%E6%B1%9F%E7%A4%BA%E7%BA%B8%E8%A1%80%E6%B5%81%E5%A2%A8&amp;rec_hit=1</t>
+  </si>
+  <si>
+    <t>智能匹配86分【博士后/科研岗】|强烈推荐|心血管植介入材料转化研究，材料学+生物相容+动物实验技能覆盖</t>
+  </si>
+  <si>
+    <t>研究82/技能82/学历90/行业100/企业90</t>
+  </si>
+  <si>
+    <t>浙江省重点实验室聚焦心血管植介入器械与材料转化研究，含科研助理岗（硕士可投），与硕士血管支架、材料学、生物相容性评价及动物实验技能高度契合，是心血管介入器械转化研究的优质科研平台。</t>
+  </si>
+  <si>
+    <t>突出血管支架/心血管材料研究课题；补充生物相容性评价与动物实验全流程；量化降解、组织学/影像学数据；可申请科研助理岗，强调材料转入方向研究潜力。</t>
+  </si>
+  <si>
+    <t>华翔医疗</t>
+  </si>
+  <si>
+    <t>工艺工程师（血管支架）</t>
+  </si>
+  <si>
+    <t>8-12k，3年以上血管支架工艺/耗材相关经验，本科以上；负责血管支架工艺开发与优化，医疗器械A轮融资企业。</t>
+  </si>
+  <si>
+    <t>湖南宁乡</t>
+  </si>
+  <si>
+    <t>智能匹配78分【社招】|值得考虑|血管支架工艺岗，方向直接匹配但要求3年经验</t>
+  </si>
+  <si>
     <t>投递日期</t>
   </si>
   <si>
@@ -2888,9 +3347,6 @@
   </si>
   <si>
     <t>数据更新日期</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
   </si>
   <si>
     <t>匹配度评分分布</t>
@@ -3373,7 +3829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8175,6 +8631,766 @@
       </c>
       <c r="L126" t="s">
         <v>933</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>934</v>
+      </c>
+      <c r="B127" t="s">
+        <v>277</v>
+      </c>
+      <c r="C127" t="s">
+        <v>935</v>
+      </c>
+      <c r="D127" t="s">
+        <v>936</v>
+      </c>
+      <c r="E127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" t="s">
+        <v>937</v>
+      </c>
+      <c r="G127">
+        <v>9</v>
+      </c>
+      <c r="H127" t="s">
+        <v>938</v>
+      </c>
+      <c r="I127">
+        <v>89</v>
+      </c>
+      <c r="J127" t="s">
+        <v>939</v>
+      </c>
+      <c r="K127" t="s">
+        <v>940</v>
+      </c>
+      <c r="L127" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>934</v>
+      </c>
+      <c r="B128" t="s">
+        <v>942</v>
+      </c>
+      <c r="C128" t="s">
+        <v>943</v>
+      </c>
+      <c r="D128" t="s">
+        <v>944</v>
+      </c>
+      <c r="E128" t="s">
+        <v>66</v>
+      </c>
+      <c r="F128" t="s">
+        <v>945</v>
+      </c>
+      <c r="G128">
+        <v>9</v>
+      </c>
+      <c r="H128" t="s">
+        <v>946</v>
+      </c>
+      <c r="I128">
+        <v>89</v>
+      </c>
+      <c r="J128" t="s">
+        <v>947</v>
+      </c>
+      <c r="K128" t="s">
+        <v>948</v>
+      </c>
+      <c r="L128" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>934</v>
+      </c>
+      <c r="B129" t="s">
+        <v>950</v>
+      </c>
+      <c r="C129" t="s">
+        <v>951</v>
+      </c>
+      <c r="D129" t="s">
+        <v>952</v>
+      </c>
+      <c r="E129" t="s">
+        <v>66</v>
+      </c>
+      <c r="F129" t="s">
+        <v>438</v>
+      </c>
+      <c r="G129">
+        <v>9</v>
+      </c>
+      <c r="H129" t="s">
+        <v>953</v>
+      </c>
+      <c r="I129">
+        <v>89</v>
+      </c>
+      <c r="J129" t="s">
+        <v>954</v>
+      </c>
+      <c r="K129" t="s">
+        <v>955</v>
+      </c>
+      <c r="L129" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>934</v>
+      </c>
+      <c r="B130" t="s">
+        <v>643</v>
+      </c>
+      <c r="C130" t="s">
+        <v>957</v>
+      </c>
+      <c r="D130" t="s">
+        <v>958</v>
+      </c>
+      <c r="E130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130" t="s">
+        <v>959</v>
+      </c>
+      <c r="G130">
+        <v>9</v>
+      </c>
+      <c r="H130" t="s">
+        <v>960</v>
+      </c>
+      <c r="I130">
+        <v>88</v>
+      </c>
+      <c r="J130" t="s">
+        <v>961</v>
+      </c>
+      <c r="K130" t="s">
+        <v>962</v>
+      </c>
+      <c r="L130" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>934</v>
+      </c>
+      <c r="B131" t="s">
+        <v>964</v>
+      </c>
+      <c r="C131" t="s">
+        <v>965</v>
+      </c>
+      <c r="D131" t="s">
+        <v>966</v>
+      </c>
+      <c r="E131" t="s">
+        <v>967</v>
+      </c>
+      <c r="F131" t="s">
+        <v>968</v>
+      </c>
+      <c r="G131">
+        <v>8</v>
+      </c>
+      <c r="H131" t="s">
+        <v>969</v>
+      </c>
+      <c r="I131">
+        <v>84</v>
+      </c>
+      <c r="J131" t="s">
+        <v>970</v>
+      </c>
+      <c r="K131" t="s">
+        <v>971</v>
+      </c>
+      <c r="L131" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>934</v>
+      </c>
+      <c r="B132" t="s">
+        <v>973</v>
+      </c>
+      <c r="C132" t="s">
+        <v>974</v>
+      </c>
+      <c r="D132" t="s">
+        <v>975</v>
+      </c>
+      <c r="E132" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" t="s">
+        <v>468</v>
+      </c>
+      <c r="G132">
+        <v>9</v>
+      </c>
+      <c r="H132" t="s">
+        <v>976</v>
+      </c>
+      <c r="I132">
+        <v>86</v>
+      </c>
+      <c r="J132" t="s">
+        <v>977</v>
+      </c>
+      <c r="K132" t="s">
+        <v>978</v>
+      </c>
+      <c r="L132" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>934</v>
+      </c>
+      <c r="B133" t="s">
+        <v>980</v>
+      </c>
+      <c r="C133" t="s">
+        <v>981</v>
+      </c>
+      <c r="D133" t="s">
+        <v>982</v>
+      </c>
+      <c r="E133" t="s">
+        <v>983</v>
+      </c>
+      <c r="F133" t="s">
+        <v>984</v>
+      </c>
+      <c r="G133">
+        <v>9</v>
+      </c>
+      <c r="H133" t="s">
+        <v>985</v>
+      </c>
+      <c r="I133">
+        <v>86</v>
+      </c>
+      <c r="J133" t="s">
+        <v>986</v>
+      </c>
+      <c r="K133" t="s">
+        <v>987</v>
+      </c>
+      <c r="L133" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>934</v>
+      </c>
+      <c r="B134" t="s">
+        <v>989</v>
+      </c>
+      <c r="C134" t="s">
+        <v>990</v>
+      </c>
+      <c r="D134" t="s">
+        <v>991</v>
+      </c>
+      <c r="E134" t="s">
+        <v>75</v>
+      </c>
+      <c r="F134" t="s">
+        <v>959</v>
+      </c>
+      <c r="G134">
+        <v>9</v>
+      </c>
+      <c r="H134" t="s">
+        <v>992</v>
+      </c>
+      <c r="I134">
+        <v>85</v>
+      </c>
+      <c r="J134" t="s">
+        <v>993</v>
+      </c>
+      <c r="K134" t="s">
+        <v>994</v>
+      </c>
+      <c r="L134" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>934</v>
+      </c>
+      <c r="B135" t="s">
+        <v>950</v>
+      </c>
+      <c r="C135" t="s">
+        <v>996</v>
+      </c>
+      <c r="D135" t="s">
+        <v>997</v>
+      </c>
+      <c r="E135" t="s">
+        <v>66</v>
+      </c>
+      <c r="F135" t="s">
+        <v>438</v>
+      </c>
+      <c r="G135">
+        <v>9</v>
+      </c>
+      <c r="H135" t="s">
+        <v>998</v>
+      </c>
+      <c r="I135">
+        <v>87</v>
+      </c>
+      <c r="J135" t="s">
+        <v>999</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>934</v>
+      </c>
+      <c r="B136" t="s">
+        <v>950</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F136" t="s">
+        <v>438</v>
+      </c>
+      <c r="G136">
+        <v>8</v>
+      </c>
+      <c r="H136" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I136">
+        <v>84</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K136" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L136" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>934</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E137" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G137">
+        <v>8</v>
+      </c>
+      <c r="H137" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I137">
+        <v>82</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K137" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L137" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>934</v>
+      </c>
+      <c r="B138" t="s">
+        <v>650</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E138" t="s">
+        <v>66</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G138">
+        <v>8</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I138">
+        <v>83</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K138" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>934</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G139">
+        <v>8</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I139">
+        <v>82</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>934</v>
+      </c>
+      <c r="B140" t="s">
+        <v>213</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E140" t="s">
+        <v>106</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G140">
+        <v>8</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I140">
+        <v>84</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>934</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G141">
+        <v>8</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I141">
+        <v>80</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>934</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E142" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G142">
+        <v>8</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I142">
+        <v>83</v>
+      </c>
+      <c r="J142" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>934</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E143" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G143">
+        <v>8</v>
+      </c>
+      <c r="H143" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I143">
+        <v>84</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K143" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>934</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E144" t="s">
+        <v>147</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G144">
+        <v>9</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I144">
+        <v>85</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K144" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>934</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G145">
+        <v>9</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I145">
+        <v>86</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K145" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>934</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F146" t="s">
+        <v>959</v>
+      </c>
+      <c r="G146">
+        <v>8</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I146">
+        <v>78</v>
+      </c>
+      <c r="J146" t="s">
+        <v>239</v>
+      </c>
+      <c r="K146" t="s">
+        <v>79</v>
+      </c>
+      <c r="L146" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -8208,7 +9424,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>934</v>
+        <v>1087</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -8217,16 +9433,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>935</v>
+        <v>1088</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>936</v>
+        <v>1089</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>937</v>
+        <v>1090</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>938</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8240,13 +9456,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>939</v>
+        <v>1092</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>940</v>
+        <v>1093</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>941</v>
+        <v>1094</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -8274,7 +9490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -8289,7 +9505,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>946</v>
+        <v>1099</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8299,31 +9515,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>947</v>
+        <v>1100</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>948</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>949</v>
+        <v>1102</v>
       </c>
       <c r="B4">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>950</v>
+        <v>1103</v>
       </c>
       <c r="B5" t="s">
-        <v>951</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>952</v>
+        <v>1105</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -8331,7 +9547,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>953</v>
+        <v>1106</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -8339,23 +9555,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>954</v>
+        <v>1107</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>955</v>
+        <v>1108</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>956</v>
+        <v>1109</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -8363,15 +9579,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>957</v>
+        <v>1110</v>
       </c>
       <c r="B11" t="s">
-        <v>958</v>
+        <v>934</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>959</v>
+        <v>1111</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -8381,15 +9597,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>960</v>
+        <v>1112</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>961</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>962</v>
+        <v>1114</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -8397,23 +9613,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>963</v>
+        <v>1115</v>
       </c>
       <c r="B17" s="5">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>964</v>
+        <v>1116</v>
       </c>
       <c r="B18" s="5">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>965</v>
+        <v>1117</v>
       </c>
       <c r="B19" s="5">
         <v>5</v>
@@ -8421,7 +9637,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>966</v>
+        <v>1118</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -8429,7 +9645,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>967</v>
+        <v>1119</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -8437,7 +9653,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>968</v>
+        <v>1120</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8445,7 +9661,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>969</v>
+        <v>1121</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8453,7 +9669,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>970</v>
+        <v>1122</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -8461,7 +9677,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>971</v>
+        <v>1123</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -8469,7 +9685,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>972</v>
+        <v>1124</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -8481,7 +9697,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>973</v>
+        <v>1125</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -8499,7 +9715,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>974</v>
+        <v>1126</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -10096,25 +11312,25 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C91" t="s">
-        <v>72</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>935</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>76</v>
+        <v>937</v>
       </c>
       <c r="G91">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H91" t="s">
-        <v>77</v>
+        <v>938</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -10122,25 +11338,25 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C92" t="s">
-        <v>80</v>
+        <v>942</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>943</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F92" t="s">
-        <v>83</v>
+        <v>945</v>
       </c>
       <c r="G92">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H92" t="s">
-        <v>84</v>
+        <v>946</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -10148,25 +11364,25 @@
         <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C93" t="s">
-        <v>103</v>
+        <v>950</v>
       </c>
       <c r="D93" t="s">
-        <v>104</v>
+        <v>951</v>
       </c>
       <c r="E93" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="G93">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H93" t="s">
-        <v>108</v>
+        <v>953</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -10174,25 +11390,25 @@
         <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>643</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>957</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>112</v>
+        <v>959</v>
       </c>
       <c r="G94">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>113</v>
+        <v>960</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -10200,25 +11416,25 @@
         <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C95" t="s">
-        <v>115</v>
+        <v>973</v>
       </c>
       <c r="D95" t="s">
-        <v>116</v>
+        <v>974</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>118</v>
+        <v>468</v>
       </c>
       <c r="G95">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H95" t="s">
-        <v>119</v>
+        <v>976</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -10226,25 +11442,25 @@
         <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>980</v>
       </c>
       <c r="D96" t="s">
-        <v>122</v>
+        <v>981</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>983</v>
       </c>
       <c r="F96" t="s">
-        <v>125</v>
+        <v>984</v>
       </c>
       <c r="G96">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H96" t="s">
-        <v>126</v>
+        <v>985</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -10252,25 +11468,25 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>989</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>990</v>
       </c>
       <c r="E97" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="F97" t="s">
-        <v>148</v>
+        <v>959</v>
       </c>
       <c r="G97">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H97" t="s">
-        <v>149</v>
+        <v>992</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -10278,25 +11494,25 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="C98" t="s">
-        <v>153</v>
+        <v>950</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>996</v>
       </c>
       <c r="E98" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F98" t="s">
-        <v>156</v>
+        <v>438</v>
       </c>
       <c r="G98">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H98" t="s">
-        <v>157</v>
+        <v>998</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -10304,25 +11520,25 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
+        <v>1065</v>
       </c>
       <c r="D99" t="s">
-        <v>208</v>
+        <v>1066</v>
       </c>
       <c r="E99" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F99" t="s">
-        <v>210</v>
+        <v>1068</v>
       </c>
       <c r="G99">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H99" t="s">
-        <v>211</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -10330,25 +11546,25 @@
         <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="C100" t="s">
-        <v>213</v>
+        <v>1073</v>
       </c>
       <c r="D100" t="s">
-        <v>214</v>
+        <v>1074</v>
       </c>
       <c r="E100" t="s">
-        <v>106</v>
+        <v>1076</v>
       </c>
       <c r="F100" t="s">
-        <v>216</v>
+        <v>1077</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H100" t="s">
-        <v>217</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -10356,25 +11572,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="D101" t="s">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="E101" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="G101">
         <v>8</v>
       </c>
       <c r="H101" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -10382,25 +11598,25 @@
         <v>73</v>
       </c>
       <c r="B102" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="D102" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E102" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F102" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G102">
         <v>8</v>
       </c>
       <c r="H102" t="s">
-        <v>238</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -10408,25 +11624,25 @@
         <v>74</v>
       </c>
       <c r="B103" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="D103" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F103" t="s">
-        <v>243</v>
+        <v>107</v>
       </c>
       <c r="G103">
         <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -10434,25 +11650,25 @@
         <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="E104" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="G104">
         <v>8</v>
       </c>
       <c r="H104" t="s">
-        <v>247</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -10460,25 +11676,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>115</v>
       </c>
       <c r="D105" t="s">
-        <v>249</v>
+        <v>116</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
       </c>
       <c r="F105" t="s">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>252</v>
+        <v>119</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -10486,25 +11702,25 @@
         <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="D106" t="s">
-        <v>255</v>
+        <v>122</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>124</v>
       </c>
       <c r="F106" t="s">
-        <v>258</v>
+        <v>125</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>259</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -10512,25 +11728,25 @@
         <v>78</v>
       </c>
       <c r="B107" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
       <c r="D107" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="E107" t="s">
         <v>147</v>
       </c>
       <c r="F107" t="s">
-        <v>263</v>
+        <v>148</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>264</v>
+        <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -10538,25 +11754,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>153</v>
       </c>
       <c r="D108" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -10567,22 +11783,22 @@
         <v>159</v>
       </c>
       <c r="C109" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="D109" t="s">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="E109" t="s">
-        <v>280</v>
+        <v>66</v>
       </c>
       <c r="F109" t="s">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>282</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -10590,25 +11806,25 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C110" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
       <c r="D110" t="s">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="E110" t="s">
-        <v>318</v>
+        <v>106</v>
       </c>
       <c r="F110" t="s">
-        <v>319</v>
+        <v>216</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>320</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -10616,25 +11832,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C111" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="D111" t="s">
-        <v>339</v>
+        <v>228</v>
       </c>
       <c r="E111" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="F111" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>343</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -10642,25 +11858,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
-        <v>347</v>
+        <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>348</v>
+        <v>73</v>
       </c>
       <c r="E112" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F112" t="s">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>351</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -10668,25 +11884,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C113" t="s">
-        <v>353</v>
+        <v>240</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>241</v>
       </c>
       <c r="E113" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
-        <v>364</v>
+        <v>243</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>365</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -10694,25 +11910,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C114" t="s">
-        <v>377</v>
+        <v>245</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>154</v>
       </c>
       <c r="E114" t="s">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>381</v>
+        <v>156</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>382</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -10720,25 +11936,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="D115" t="s">
-        <v>394</v>
+        <v>249</v>
       </c>
       <c r="E115" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>397</v>
+        <v>251</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>398</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -10746,25 +11962,25 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="C116" t="s">
-        <v>410</v>
+        <v>254</v>
       </c>
       <c r="D116" t="s">
-        <v>411</v>
+        <v>255</v>
       </c>
       <c r="E116" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="F116" t="s">
-        <v>413</v>
+        <v>258</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>414</v>
+        <v>259</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -10772,25 +11988,25 @@
         <v>88</v>
       </c>
       <c r="B117" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="C117" t="s">
-        <v>418</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>419</v>
+        <v>122</v>
       </c>
       <c r="E117" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F117" t="s">
-        <v>421</v>
+        <v>263</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>422</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -10798,25 +12014,25 @@
         <v>89</v>
       </c>
       <c r="B118" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>424</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>425</v>
+        <v>267</v>
       </c>
       <c r="E118" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F118" t="s">
-        <v>427</v>
+        <v>58</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>428</v>
+        <v>269</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -10824,25 +12040,25 @@
         <v>90</v>
       </c>
       <c r="B119" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
       <c r="C119" t="s">
-        <v>430</v>
+        <v>277</v>
       </c>
       <c r="D119" t="s">
-        <v>431</v>
+        <v>278</v>
       </c>
       <c r="E119" t="s">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="F119" t="s">
-        <v>433</v>
+        <v>281</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>434</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -10850,25 +12066,25 @@
         <v>91</v>
       </c>
       <c r="B120" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C120" t="s">
-        <v>483</v>
+        <v>315</v>
       </c>
       <c r="D120" t="s">
-        <v>122</v>
+        <v>316</v>
       </c>
       <c r="E120" t="s">
-        <v>485</v>
+        <v>318</v>
       </c>
       <c r="F120" t="s">
-        <v>486</v>
+        <v>319</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>487</v>
+        <v>320</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -10876,25 +12092,25 @@
         <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C121" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="D121" t="s">
-        <v>492</v>
+        <v>339</v>
       </c>
       <c r="E121" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="F121" t="s">
-        <v>494</v>
+        <v>342</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>495</v>
+        <v>343</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -10902,25 +12118,25 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C122" t="s">
-        <v>499</v>
+        <v>347</v>
       </c>
       <c r="D122" t="s">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="E122" t="s">
-        <v>502</v>
+        <v>98</v>
       </c>
       <c r="F122" t="s">
-        <v>503</v>
+        <v>350</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>504</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -10928,25 +12144,25 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C123" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="D123" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="E123" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="F123" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>537</v>
+        <v>365</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -10954,25 +12170,25 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="C124" t="s">
-        <v>550</v>
+        <v>377</v>
       </c>
       <c r="D124" t="s">
-        <v>551</v>
+        <v>378</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="F124" t="s">
-        <v>553</v>
+        <v>381</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>554</v>
+        <v>382</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -10980,25 +12196,25 @@
         <v>96</v>
       </c>
       <c r="B125" t="s">
-        <v>556</v>
+        <v>284</v>
       </c>
       <c r="C125" t="s">
-        <v>578</v>
+        <v>144</v>
       </c>
       <c r="D125" t="s">
-        <v>579</v>
+        <v>394</v>
       </c>
       <c r="E125" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F125" t="s">
-        <v>581</v>
+        <v>397</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>582</v>
+        <v>398</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -11006,25 +12222,25 @@
         <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="C126" t="s">
-        <v>584</v>
+        <v>410</v>
       </c>
       <c r="D126" t="s">
-        <v>585</v>
+        <v>411</v>
       </c>
       <c r="E126" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="F126" t="s">
-        <v>588</v>
+        <v>413</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>589</v>
+        <v>414</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -11032,25 +12248,25 @@
         <v>98</v>
       </c>
       <c r="B127" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="C127" t="s">
-        <v>601</v>
+        <v>418</v>
       </c>
       <c r="D127" t="s">
-        <v>602</v>
+        <v>419</v>
       </c>
       <c r="E127" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F127" t="s">
-        <v>604</v>
+        <v>421</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>605</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -11058,25 +12274,25 @@
         <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="C128" t="s">
-        <v>616</v>
+        <v>424</v>
       </c>
       <c r="D128" t="s">
-        <v>610</v>
+        <v>425</v>
       </c>
       <c r="E128" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F128" t="s">
-        <v>618</v>
+        <v>427</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>619</v>
+        <v>428</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -11084,25 +12300,25 @@
         <v>100</v>
       </c>
       <c r="B129" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="C129" t="s">
-        <v>557</v>
+        <v>430</v>
       </c>
       <c r="D129" t="s">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>625</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -11110,25 +12326,25 @@
         <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C130" t="s">
-        <v>643</v>
+        <v>483</v>
       </c>
       <c r="D130" t="s">
-        <v>644</v>
+        <v>122</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="F130" t="s">
-        <v>618</v>
+        <v>486</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>646</v>
+        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -11136,25 +12352,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C131" t="s">
-        <v>650</v>
+        <v>491</v>
       </c>
       <c r="D131" t="s">
-        <v>651</v>
+        <v>492</v>
       </c>
       <c r="E131" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F131" t="s">
-        <v>653</v>
+        <v>494</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>654</v>
+        <v>495</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -11162,25 +12378,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C132" t="s">
-        <v>658</v>
+        <v>499</v>
       </c>
       <c r="D132" t="s">
-        <v>659</v>
+        <v>500</v>
       </c>
       <c r="E132" t="s">
-        <v>661</v>
+        <v>502</v>
       </c>
       <c r="F132" t="s">
-        <v>662</v>
+        <v>503</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>663</v>
+        <v>504</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -11188,25 +12404,25 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C133" t="s">
-        <v>666</v>
+        <v>532</v>
       </c>
       <c r="D133" t="s">
-        <v>667</v>
+        <v>533</v>
       </c>
       <c r="E133" t="s">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="F133" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>669</v>
+        <v>537</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -11214,25 +12430,25 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C134" t="s">
-        <v>673</v>
+        <v>550</v>
       </c>
       <c r="D134" t="s">
-        <v>674</v>
+        <v>551</v>
       </c>
       <c r="E134" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>676</v>
+        <v>553</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>677</v>
+        <v>554</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -11240,25 +12456,25 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>697</v>
+        <v>556</v>
       </c>
       <c r="C135" t="s">
-        <v>714</v>
+        <v>578</v>
       </c>
       <c r="D135" t="s">
-        <v>715</v>
+        <v>579</v>
       </c>
       <c r="E135" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F135" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>717</v>
+        <v>582</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -11266,25 +12482,25 @@
         <v>107</v>
       </c>
       <c r="B136" t="s">
-        <v>697</v>
+        <v>556</v>
       </c>
       <c r="C136" t="s">
-        <v>721</v>
+        <v>584</v>
       </c>
       <c r="D136" t="s">
-        <v>722</v>
+        <v>585</v>
       </c>
       <c r="E136" t="s">
-        <v>25</v>
+        <v>587</v>
       </c>
       <c r="F136" t="s">
-        <v>724</v>
+        <v>588</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>725</v>
+        <v>589</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -11292,25 +12508,25 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C137" t="s">
-        <v>729</v>
+        <v>601</v>
       </c>
       <c r="D137" t="s">
-        <v>730</v>
+        <v>602</v>
       </c>
       <c r="E137" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F137" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>733</v>
+        <v>605</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -11318,25 +12534,25 @@
         <v>109</v>
       </c>
       <c r="B138" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C138" t="s">
-        <v>736</v>
+        <v>616</v>
       </c>
       <c r="D138" t="s">
-        <v>737</v>
+        <v>610</v>
       </c>
       <c r="E138" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="F138" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>740</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -11344,25 +12560,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C139" t="s">
-        <v>744</v>
+        <v>557</v>
       </c>
       <c r="D139" t="s">
-        <v>745</v>
+        <v>623</v>
       </c>
       <c r="E139" t="s">
-        <v>747</v>
+        <v>16</v>
       </c>
       <c r="F139" t="s">
-        <v>748</v>
+        <v>468</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>749</v>
+        <v>625</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -11370,25 +12586,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C140" t="s">
-        <v>753</v>
+        <v>643</v>
       </c>
       <c r="D140" t="s">
-        <v>754</v>
+        <v>644</v>
       </c>
       <c r="E140" t="s">
-        <v>756</v>
+        <v>16</v>
       </c>
       <c r="F140" t="s">
-        <v>757</v>
+        <v>618</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>758</v>
+        <v>646</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -11396,25 +12612,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C141" t="s">
-        <v>760</v>
+        <v>650</v>
       </c>
       <c r="D141" t="s">
-        <v>761</v>
+        <v>651</v>
       </c>
       <c r="E141" t="s">
-        <v>763</v>
+        <v>66</v>
       </c>
       <c r="F141" t="s">
-        <v>764</v>
+        <v>653</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>765</v>
+        <v>654</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -11422,25 +12638,25 @@
         <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="C142" t="s">
-        <v>791</v>
+        <v>658</v>
       </c>
       <c r="D142" t="s">
-        <v>610</v>
+        <v>659</v>
       </c>
       <c r="E142" t="s">
-        <v>793</v>
+        <v>661</v>
       </c>
       <c r="F142" t="s">
-        <v>794</v>
+        <v>662</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>795</v>
+        <v>663</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -11448,25 +12664,25 @@
         <v>114</v>
       </c>
       <c r="B143" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="C143" t="s">
-        <v>807</v>
+        <v>666</v>
       </c>
       <c r="D143" t="s">
-        <v>808</v>
+        <v>667</v>
       </c>
       <c r="E143" t="s">
-        <v>810</v>
+        <v>75</v>
       </c>
       <c r="F143" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>812</v>
+        <v>669</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -11474,25 +12690,25 @@
         <v>115</v>
       </c>
       <c r="B144" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="C144" t="s">
-        <v>816</v>
+        <v>673</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>674</v>
       </c>
       <c r="E144" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F144" t="s">
-        <v>818</v>
+        <v>676</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>819</v>
+        <v>677</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -11500,25 +12716,25 @@
         <v>116</v>
       </c>
       <c r="B145" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C145" t="s">
-        <v>888</v>
+        <v>714</v>
       </c>
       <c r="D145" t="s">
-        <v>889</v>
+        <v>715</v>
       </c>
       <c r="E145" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>891</v>
+        <v>604</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>892</v>
+        <v>717</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -11526,25 +12742,25 @@
         <v>117</v>
       </c>
       <c r="B146" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C146" t="s">
-        <v>896</v>
+        <v>721</v>
       </c>
       <c r="D146" t="s">
-        <v>897</v>
+        <v>722</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
       </c>
       <c r="F146" t="s">
-        <v>899</v>
+        <v>724</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>900</v>
+        <v>725</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -11552,25 +12768,25 @@
         <v>118</v>
       </c>
       <c r="B147" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C147" t="s">
-        <v>904</v>
+        <v>729</v>
       </c>
       <c r="D147" t="s">
-        <v>585</v>
+        <v>730</v>
       </c>
       <c r="E147" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F147" t="s">
-        <v>906</v>
+        <v>732</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>907</v>
+        <v>733</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -11578,25 +12794,25 @@
         <v>119</v>
       </c>
       <c r="B148" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C148" t="s">
-        <v>911</v>
+        <v>736</v>
       </c>
       <c r="D148" t="s">
-        <v>585</v>
+        <v>737</v>
       </c>
       <c r="E148" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="F148" t="s">
-        <v>913</v>
+        <v>604</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>914</v>
+        <v>740</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -11604,25 +12820,25 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C149" t="s">
-        <v>918</v>
+        <v>744</v>
       </c>
       <c r="D149" t="s">
-        <v>919</v>
+        <v>745</v>
       </c>
       <c r="E149" t="s">
-        <v>921</v>
+        <v>747</v>
       </c>
       <c r="F149" t="s">
-        <v>922</v>
+        <v>748</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>923</v>
+        <v>749</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -11630,25 +12846,25 @@
         <v>121</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="C150" t="s">
-        <v>271</v>
+        <v>753</v>
       </c>
       <c r="D150" t="s">
-        <v>272</v>
+        <v>754</v>
       </c>
       <c r="E150" t="s">
-        <v>75</v>
+        <v>756</v>
       </c>
       <c r="F150" t="s">
-        <v>274</v>
+        <v>757</v>
       </c>
       <c r="G150">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>275</v>
+        <v>758</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -11656,25 +12872,25 @@
         <v>122</v>
       </c>
       <c r="B151" t="s">
-        <v>591</v>
+        <v>697</v>
       </c>
       <c r="C151" t="s">
-        <v>681</v>
+        <v>760</v>
       </c>
       <c r="D151" t="s">
-        <v>682</v>
+        <v>761</v>
       </c>
       <c r="E151" t="s">
-        <v>25</v>
+        <v>763</v>
       </c>
       <c r="F151" t="s">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="G151">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>685</v>
+        <v>765</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -11682,25 +12898,25 @@
         <v>123</v>
       </c>
       <c r="B152" t="s">
-        <v>591</v>
+        <v>773</v>
       </c>
       <c r="C152" t="s">
-        <v>689</v>
+        <v>791</v>
       </c>
       <c r="D152" t="s">
-        <v>690</v>
+        <v>610</v>
       </c>
       <c r="E152" t="s">
-        <v>66</v>
+        <v>793</v>
       </c>
       <c r="F152" t="s">
-        <v>692</v>
+        <v>794</v>
       </c>
       <c r="G152">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>693</v>
+        <v>795</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -11708,25 +12924,25 @@
         <v>124</v>
       </c>
       <c r="B153" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="C153" t="s">
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="D153" t="s">
-        <v>768</v>
+        <v>808</v>
       </c>
       <c r="E153" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F153" t="s">
-        <v>770</v>
+        <v>811</v>
       </c>
       <c r="G153">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -11734,24 +12950,544 @@
         <v>125</v>
       </c>
       <c r="B154" t="s">
+        <v>773</v>
+      </c>
+      <c r="C154" t="s">
+        <v>816</v>
+      </c>
+      <c r="D154" t="s">
+        <v>110</v>
+      </c>
+      <c r="E154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" t="s">
+        <v>818</v>
+      </c>
+      <c r="G154">
+        <v>8</v>
+      </c>
+      <c r="H154" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>126</v>
+      </c>
+      <c r="B155" t="s">
         <v>845</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C155" t="s">
+        <v>888</v>
+      </c>
+      <c r="D155" t="s">
+        <v>889</v>
+      </c>
+      <c r="E155" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" t="s">
+        <v>891</v>
+      </c>
+      <c r="G155">
+        <v>8</v>
+      </c>
+      <c r="H155" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>127</v>
+      </c>
+      <c r="B156" t="s">
+        <v>845</v>
+      </c>
+      <c r="C156" t="s">
+        <v>896</v>
+      </c>
+      <c r="D156" t="s">
+        <v>897</v>
+      </c>
+      <c r="E156" t="s">
+        <v>25</v>
+      </c>
+      <c r="F156" t="s">
+        <v>899</v>
+      </c>
+      <c r="G156">
+        <v>8</v>
+      </c>
+      <c r="H156" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>128</v>
+      </c>
+      <c r="B157" t="s">
+        <v>845</v>
+      </c>
+      <c r="C157" t="s">
+        <v>904</v>
+      </c>
+      <c r="D157" t="s">
+        <v>585</v>
+      </c>
+      <c r="E157" t="s">
+        <v>66</v>
+      </c>
+      <c r="F157" t="s">
+        <v>906</v>
+      </c>
+      <c r="G157">
+        <v>8</v>
+      </c>
+      <c r="H157" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>129</v>
+      </c>
+      <c r="B158" t="s">
+        <v>845</v>
+      </c>
+      <c r="C158" t="s">
+        <v>911</v>
+      </c>
+      <c r="D158" t="s">
+        <v>585</v>
+      </c>
+      <c r="E158" t="s">
+        <v>16</v>
+      </c>
+      <c r="F158" t="s">
+        <v>913</v>
+      </c>
+      <c r="G158">
+        <v>8</v>
+      </c>
+      <c r="H158" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>130</v>
+      </c>
+      <c r="B159" t="s">
+        <v>845</v>
+      </c>
+      <c r="C159" t="s">
+        <v>918</v>
+      </c>
+      <c r="D159" t="s">
+        <v>919</v>
+      </c>
+      <c r="E159" t="s">
+        <v>921</v>
+      </c>
+      <c r="F159" t="s">
+        <v>922</v>
+      </c>
+      <c r="G159">
+        <v>8</v>
+      </c>
+      <c r="H159" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>131</v>
+      </c>
+      <c r="B160" t="s">
+        <v>934</v>
+      </c>
+      <c r="C160" t="s">
+        <v>964</v>
+      </c>
+      <c r="D160" t="s">
+        <v>965</v>
+      </c>
+      <c r="E160" t="s">
+        <v>967</v>
+      </c>
+      <c r="F160" t="s">
+        <v>968</v>
+      </c>
+      <c r="G160">
+        <v>8</v>
+      </c>
+      <c r="H160" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>132</v>
+      </c>
+      <c r="B161" t="s">
+        <v>934</v>
+      </c>
+      <c r="C161" t="s">
+        <v>950</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F161" t="s">
+        <v>438</v>
+      </c>
+      <c r="G161">
+        <v>8</v>
+      </c>
+      <c r="H161" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>133</v>
+      </c>
+      <c r="B162" t="s">
+        <v>934</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E162" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G162">
+        <v>8</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>134</v>
+      </c>
+      <c r="B163" t="s">
+        <v>934</v>
+      </c>
+      <c r="C163" t="s">
+        <v>650</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E163" t="s">
+        <v>66</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G163">
+        <v>8</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>135</v>
+      </c>
+      <c r="B164" t="s">
+        <v>934</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E164" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G164">
+        <v>8</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>136</v>
+      </c>
+      <c r="B165" t="s">
+        <v>934</v>
+      </c>
+      <c r="C165" t="s">
+        <v>213</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E165" t="s">
+        <v>106</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G165">
+        <v>8</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>137</v>
+      </c>
+      <c r="B166" t="s">
+        <v>934</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E166" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G166">
+        <v>8</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>138</v>
+      </c>
+      <c r="B167" t="s">
+        <v>934</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E167" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G167">
+        <v>8</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>139</v>
+      </c>
+      <c r="B168" t="s">
+        <v>934</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E168" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G168">
+        <v>8</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>140</v>
+      </c>
+      <c r="B169" t="s">
+        <v>934</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E169" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F169" t="s">
+        <v>959</v>
+      </c>
+      <c r="G169">
+        <v>8</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>141</v>
+      </c>
+      <c r="B170" t="s">
+        <v>159</v>
+      </c>
+      <c r="C170" t="s">
+        <v>271</v>
+      </c>
+      <c r="D170" t="s">
+        <v>272</v>
+      </c>
+      <c r="E170" t="s">
+        <v>75</v>
+      </c>
+      <c r="F170" t="s">
+        <v>274</v>
+      </c>
+      <c r="G170">
+        <v>7</v>
+      </c>
+      <c r="H170" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>142</v>
+      </c>
+      <c r="B171" t="s">
+        <v>591</v>
+      </c>
+      <c r="C171" t="s">
+        <v>681</v>
+      </c>
+      <c r="D171" t="s">
+        <v>682</v>
+      </c>
+      <c r="E171" t="s">
+        <v>25</v>
+      </c>
+      <c r="F171" t="s">
+        <v>684</v>
+      </c>
+      <c r="G171">
+        <v>7</v>
+      </c>
+      <c r="H171" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>143</v>
+      </c>
+      <c r="B172" t="s">
+        <v>591</v>
+      </c>
+      <c r="C172" t="s">
+        <v>689</v>
+      </c>
+      <c r="D172" t="s">
+        <v>690</v>
+      </c>
+      <c r="E172" t="s">
+        <v>66</v>
+      </c>
+      <c r="F172" t="s">
+        <v>692</v>
+      </c>
+      <c r="G172">
+        <v>7</v>
+      </c>
+      <c r="H172" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>144</v>
+      </c>
+      <c r="B173" t="s">
+        <v>697</v>
+      </c>
+      <c r="C173" t="s">
+        <v>767</v>
+      </c>
+      <c r="D173" t="s">
+        <v>768</v>
+      </c>
+      <c r="E173" t="s">
+        <v>25</v>
+      </c>
+      <c r="F173" t="s">
+        <v>770</v>
+      </c>
+      <c r="G173">
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>145</v>
+      </c>
+      <c r="B174" t="s">
+        <v>845</v>
+      </c>
+      <c r="C174" t="s">
         <v>927</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D174" t="s">
         <v>585</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E174" t="s">
         <v>25</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F174" t="s">
         <v>929</v>
       </c>
-      <c r="G154">
+      <c r="G174">
         <v>7</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H174" t="s">
         <v>930</v>
       </c>
     </row>
@@ -11768,7 +13504,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -11785,10 +13521,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>942</v>
+        <v>1095</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>943</v>
+        <v>1096</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -11815,12 +13551,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>944</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -11855,7 +13591,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -11890,7 +13626,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -11925,7 +13661,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -11960,7 +13696,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -11995,7 +13731,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -12030,7 +13766,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -12065,7 +13801,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -12100,7 +13836,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -12135,7 +13871,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -12170,7 +13906,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -12205,7 +13941,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -12240,7 +13976,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -12275,7 +14011,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -12310,7 +14046,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -12345,7 +14081,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -12380,7 +14116,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -12415,7 +14151,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -12450,7 +14186,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -12485,7 +14221,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -12520,7 +14256,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -12555,7 +14291,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -12590,7 +14326,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B24">
         <v>89</v>
@@ -12625,7 +14361,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -12660,7 +14396,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -12695,7 +14431,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -12730,7 +14466,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -12765,7 +14501,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -12800,1997 +14536,2662 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B30">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>277</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>935</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>937</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>939</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>940</v>
       </c>
       <c r="J30" t="s">
-        <v>38</v>
+        <v>941</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>936</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B31">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>934</v>
+      </c>
+      <c r="D31" t="s">
+        <v>942</v>
+      </c>
+      <c r="E31" t="s">
+        <v>943</v>
+      </c>
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" t="s">
         <v>945</v>
       </c>
-      <c r="B31">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>159</v>
-      </c>
-      <c r="D31" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" t="s">
-        <v>201</v>
-      </c>
-      <c r="F31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" t="s">
-        <v>203</v>
-      </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>947</v>
       </c>
       <c r="I31" t="s">
-        <v>205</v>
+        <v>948</v>
       </c>
       <c r="J31" t="s">
-        <v>206</v>
+        <v>949</v>
       </c>
       <c r="K31" t="s">
-        <v>202</v>
+        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B32">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D32" t="s">
-        <v>386</v>
+        <v>950</v>
       </c>
       <c r="E32" t="s">
-        <v>387</v>
+        <v>951</v>
       </c>
       <c r="F32" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="H32" t="s">
-        <v>391</v>
+        <v>954</v>
       </c>
       <c r="I32" t="s">
-        <v>392</v>
+        <v>955</v>
       </c>
       <c r="J32" t="s">
-        <v>393</v>
+        <v>956</v>
       </c>
       <c r="K32" t="s">
-        <v>388</v>
+        <v>952</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B33">
         <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>449</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="H33" t="s">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="J33" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="K33" t="s">
-        <v>450</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B34">
         <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>697</v>
+        <v>159</v>
       </c>
       <c r="D34" t="s">
-        <v>698</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
-        <v>699</v>
+        <v>201</v>
       </c>
       <c r="F34" t="s">
-        <v>701</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>702</v>
+        <v>203</v>
       </c>
       <c r="H34" t="s">
-        <v>704</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s">
-        <v>705</v>
+        <v>205</v>
       </c>
       <c r="J34" t="s">
-        <v>706</v>
+        <v>206</v>
       </c>
       <c r="K34" t="s">
-        <v>700</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B35">
         <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>773</v>
+        <v>284</v>
       </c>
       <c r="D35" t="s">
-        <v>837</v>
+        <v>386</v>
       </c>
       <c r="E35" t="s">
-        <v>610</v>
+        <v>387</v>
       </c>
       <c r="F35" t="s">
-        <v>839</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>840</v>
+        <v>389</v>
       </c>
       <c r="H35" t="s">
-        <v>842</v>
+        <v>391</v>
       </c>
       <c r="I35" t="s">
-        <v>843</v>
+        <v>392</v>
       </c>
       <c r="J35" t="s">
-        <v>844</v>
+        <v>393</v>
       </c>
       <c r="K35" t="s">
-        <v>838</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B36">
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>845</v>
+        <v>402</v>
       </c>
       <c r="D36" t="s">
-        <v>855</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>856</v>
+        <v>449</v>
       </c>
       <c r="F36" t="s">
-        <v>858</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>859</v>
+        <v>438</v>
       </c>
       <c r="H36" t="s">
-        <v>861</v>
+        <v>452</v>
       </c>
       <c r="I36" t="s">
-        <v>862</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s">
-        <v>863</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s">
-        <v>857</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B37">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>698</v>
       </c>
       <c r="E37" t="s">
-        <v>185</v>
+        <v>699</v>
       </c>
       <c r="F37" t="s">
-        <v>130</v>
+        <v>701</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>702</v>
       </c>
       <c r="H37" t="s">
-        <v>188</v>
+        <v>704</v>
       </c>
       <c r="I37" t="s">
-        <v>189</v>
+        <v>705</v>
       </c>
       <c r="J37" t="s">
-        <v>190</v>
+        <v>706</v>
       </c>
       <c r="K37" t="s">
-        <v>186</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B38">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D38" t="s">
-        <v>353</v>
+        <v>837</v>
       </c>
       <c r="E38" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="F38" t="s">
-        <v>356</v>
+        <v>839</v>
       </c>
       <c r="G38" t="s">
-        <v>357</v>
+        <v>840</v>
       </c>
       <c r="H38" t="s">
-        <v>359</v>
+        <v>842</v>
       </c>
       <c r="I38" t="s">
-        <v>360</v>
+        <v>843</v>
       </c>
       <c r="J38" t="s">
-        <v>361</v>
+        <v>844</v>
       </c>
       <c r="K38" t="s">
-        <v>355</v>
+        <v>838</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B39">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>402</v>
+        <v>845</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>855</v>
       </c>
       <c r="E39" t="s">
-        <v>453</v>
+        <v>856</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>858</v>
       </c>
       <c r="G39" t="s">
-        <v>438</v>
+        <v>859</v>
       </c>
       <c r="H39" t="s">
-        <v>456</v>
+        <v>861</v>
       </c>
       <c r="I39" t="s">
-        <v>79</v>
+        <v>862</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>863</v>
       </c>
       <c r="K39" t="s">
-        <v>454</v>
+        <v>857</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B40">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>402</v>
+        <v>934</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>643</v>
       </c>
       <c r="E40" t="s">
-        <v>463</v>
+        <v>957</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>438</v>
+        <v>959</v>
       </c>
       <c r="H40" t="s">
-        <v>456</v>
+        <v>961</v>
       </c>
       <c r="I40" t="s">
-        <v>79</v>
+        <v>962</v>
       </c>
       <c r="J40" t="s">
-        <v>79</v>
+        <v>963</v>
       </c>
       <c r="K40" t="s">
-        <v>464</v>
+        <v>958</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B41">
         <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>473</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="E41" t="s">
-        <v>508</v>
+        <v>185</v>
       </c>
       <c r="F41" t="s">
-        <v>510</v>
+        <v>130</v>
       </c>
       <c r="G41" t="s">
-        <v>511</v>
+        <v>131</v>
       </c>
       <c r="H41" t="s">
-        <v>513</v>
+        <v>188</v>
       </c>
       <c r="I41" t="s">
-        <v>514</v>
+        <v>189</v>
       </c>
       <c r="J41" t="s">
-        <v>515</v>
+        <v>190</v>
       </c>
       <c r="K41" t="s">
-        <v>509</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B42">
         <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>556</v>
+        <v>284</v>
       </c>
       <c r="D42" t="s">
-        <v>570</v>
+        <v>353</v>
       </c>
       <c r="E42" t="s">
-        <v>571</v>
+        <v>354</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>356</v>
       </c>
       <c r="G42" t="s">
-        <v>573</v>
+        <v>357</v>
       </c>
       <c r="H42" t="s">
-        <v>575</v>
+        <v>359</v>
       </c>
       <c r="I42" t="s">
-        <v>576</v>
+        <v>360</v>
       </c>
       <c r="J42" t="s">
-        <v>577</v>
+        <v>361</v>
       </c>
       <c r="K42" t="s">
-        <v>572</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B43">
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>845</v>
+        <v>402</v>
       </c>
       <c r="D43" t="s">
-        <v>864</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>865</v>
+        <v>453</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
-        <v>867</v>
+        <v>438</v>
       </c>
       <c r="H43" t="s">
-        <v>869</v>
+        <v>456</v>
       </c>
       <c r="I43" t="s">
-        <v>870</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s">
-        <v>871</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s">
-        <v>866</v>
+        <v>454</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B44">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D44" t="s">
-        <v>369</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>370</v>
+        <v>463</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G44" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="H44" t="s">
-        <v>374</v>
+        <v>456</v>
       </c>
       <c r="I44" t="s">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s">
-        <v>371</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B45">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>510</v>
       </c>
       <c r="G45" t="s">
-        <v>438</v>
+        <v>511</v>
       </c>
       <c r="H45" t="s">
-        <v>460</v>
+        <v>513</v>
       </c>
       <c r="I45" t="s">
-        <v>461</v>
+        <v>514</v>
       </c>
       <c r="J45" t="s">
-        <v>462</v>
+        <v>515</v>
       </c>
       <c r="K45" t="s">
-        <v>458</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B46">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>402</v>
+        <v>556</v>
       </c>
       <c r="D46" t="s">
-        <v>322</v>
+        <v>570</v>
       </c>
       <c r="E46" t="s">
-        <v>466</v>
+        <v>571</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>468</v>
+        <v>573</v>
       </c>
       <c r="H46" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="I46" t="s">
-        <v>471</v>
+        <v>576</v>
       </c>
       <c r="J46" t="s">
-        <v>472</v>
+        <v>577</v>
       </c>
       <c r="K46" t="s">
-        <v>467</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B47">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>473</v>
+        <v>845</v>
       </c>
       <c r="D47" t="s">
-        <v>541</v>
+        <v>864</v>
       </c>
       <c r="E47" t="s">
-        <v>542</v>
+        <v>865</v>
       </c>
       <c r="F47" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>545</v>
+        <v>867</v>
       </c>
       <c r="H47" t="s">
-        <v>547</v>
+        <v>869</v>
       </c>
       <c r="I47" t="s">
-        <v>548</v>
+        <v>870</v>
       </c>
       <c r="J47" t="s">
-        <v>549</v>
+        <v>871</v>
       </c>
       <c r="K47" t="s">
-        <v>543</v>
+        <v>866</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B48">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>556</v>
+        <v>934</v>
       </c>
       <c r="D48" t="s">
-        <v>557</v>
+        <v>950</v>
       </c>
       <c r="E48" t="s">
-        <v>558</v>
+        <v>996</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G48" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H48" t="s">
-        <v>561</v>
+        <v>999</v>
       </c>
       <c r="I48" t="s">
-        <v>562</v>
+        <v>1000</v>
       </c>
       <c r="J48" t="s">
-        <v>563</v>
+        <v>1001</v>
       </c>
       <c r="K48" t="s">
-        <v>559</v>
+        <v>997</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B49">
         <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s">
-        <v>609</v>
+        <v>369</v>
       </c>
       <c r="E49" t="s">
-        <v>610</v>
+        <v>370</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>604</v>
+        <v>372</v>
       </c>
       <c r="H49" t="s">
-        <v>613</v>
+        <v>374</v>
       </c>
       <c r="I49" t="s">
-        <v>614</v>
+        <v>375</v>
       </c>
       <c r="J49" t="s">
-        <v>615</v>
+        <v>376</v>
       </c>
       <c r="K49" t="s">
-        <v>611</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B50">
         <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="D50" t="s">
-        <v>627</v>
+        <v>63</v>
       </c>
       <c r="E50" t="s">
-        <v>628</v>
+        <v>457</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>630</v>
+        <v>438</v>
       </c>
       <c r="H50" t="s">
-        <v>632</v>
+        <v>460</v>
       </c>
       <c r="I50" t="s">
-        <v>633</v>
+        <v>461</v>
       </c>
       <c r="J50" t="s">
-        <v>634</v>
+        <v>462</v>
       </c>
       <c r="K50" t="s">
-        <v>629</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B51">
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="D51" t="s">
-        <v>635</v>
+        <v>322</v>
       </c>
       <c r="E51" t="s">
-        <v>636</v>
+        <v>466</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>638</v>
+        <v>468</v>
       </c>
       <c r="H51" t="s">
-        <v>640</v>
+        <v>470</v>
       </c>
       <c r="I51" t="s">
-        <v>641</v>
+        <v>471</v>
       </c>
       <c r="J51" t="s">
-        <v>642</v>
+        <v>472</v>
       </c>
       <c r="K51" t="s">
-        <v>637</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B52">
         <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D52" t="s">
-        <v>829</v>
+        <v>541</v>
       </c>
       <c r="E52" t="s">
-        <v>830</v>
+        <v>542</v>
       </c>
       <c r="F52" t="s">
-        <v>785</v>
+        <v>544</v>
       </c>
       <c r="G52" t="s">
-        <v>832</v>
+        <v>545</v>
       </c>
       <c r="H52" t="s">
-        <v>834</v>
+        <v>547</v>
       </c>
       <c r="I52" t="s">
-        <v>835</v>
+        <v>548</v>
       </c>
       <c r="J52" t="s">
-        <v>836</v>
+        <v>549</v>
       </c>
       <c r="K52" t="s">
-        <v>831</v>
+        <v>543</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B53">
         <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D53" t="s">
-        <v>872</v>
+        <v>557</v>
       </c>
       <c r="E53" t="s">
-        <v>873</v>
+        <v>558</v>
       </c>
       <c r="F53" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>875</v>
+        <v>468</v>
       </c>
       <c r="H53" t="s">
-        <v>877</v>
+        <v>561</v>
       </c>
       <c r="I53" t="s">
-        <v>878</v>
+        <v>562</v>
       </c>
       <c r="J53" t="s">
-        <v>879</v>
+        <v>563</v>
       </c>
       <c r="K53" t="s">
-        <v>874</v>
+        <v>559</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B54">
         <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D54" t="s">
-        <v>880</v>
+        <v>609</v>
       </c>
       <c r="E54" t="s">
-        <v>881</v>
+        <v>610</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>883</v>
+        <v>604</v>
       </c>
       <c r="H54" t="s">
-        <v>885</v>
+        <v>613</v>
       </c>
       <c r="I54" t="s">
-        <v>886</v>
+        <v>614</v>
       </c>
       <c r="J54" t="s">
-        <v>887</v>
+        <v>615</v>
       </c>
       <c r="K54" t="s">
-        <v>882</v>
+        <v>611</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B55">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D55" t="s">
-        <v>55</v>
+        <v>627</v>
       </c>
       <c r="E55" t="s">
-        <v>56</v>
+        <v>628</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="H55" t="s">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>633</v>
       </c>
       <c r="J55" t="s">
-        <v>62</v>
+        <v>634</v>
       </c>
       <c r="K55" t="s">
-        <v>57</v>
+        <v>629</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B56">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="E56" t="s">
-        <v>89</v>
+        <v>636</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
+        <v>638</v>
       </c>
       <c r="H56" t="s">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="I56" t="s">
-        <v>134</v>
+        <v>641</v>
       </c>
       <c r="J56" t="s">
-        <v>135</v>
+        <v>642</v>
       </c>
       <c r="K56" t="s">
-        <v>129</v>
+        <v>637</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B57">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D57" t="s">
-        <v>300</v>
+        <v>829</v>
       </c>
       <c r="E57" t="s">
-        <v>308</v>
+        <v>830</v>
       </c>
       <c r="F57" t="s">
-        <v>147</v>
+        <v>785</v>
       </c>
       <c r="G57" t="s">
-        <v>310</v>
+        <v>832</v>
       </c>
       <c r="H57" t="s">
-        <v>312</v>
+        <v>834</v>
       </c>
       <c r="I57" t="s">
-        <v>313</v>
+        <v>835</v>
       </c>
       <c r="J57" t="s">
-        <v>314</v>
+        <v>836</v>
       </c>
       <c r="K57" t="s">
-        <v>309</v>
+        <v>831</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B58">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>402</v>
+        <v>845</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
+        <v>872</v>
       </c>
       <c r="E58" t="s">
-        <v>403</v>
+        <v>873</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G58" t="s">
-        <v>405</v>
+        <v>875</v>
       </c>
       <c r="H58" t="s">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="I58" t="s">
-        <v>408</v>
+        <v>878</v>
       </c>
       <c r="J58" t="s">
-        <v>409</v>
+        <v>879</v>
       </c>
       <c r="K58" t="s">
-        <v>404</v>
+        <v>874</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B59">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>845</v>
       </c>
       <c r="D59" t="s">
-        <v>474</v>
+        <v>880</v>
       </c>
       <c r="E59" t="s">
-        <v>475</v>
+        <v>881</v>
       </c>
       <c r="F59" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>478</v>
+        <v>883</v>
       </c>
       <c r="H59" t="s">
-        <v>480</v>
+        <v>885</v>
       </c>
       <c r="I59" t="s">
-        <v>481</v>
+        <v>886</v>
       </c>
       <c r="J59" t="s">
-        <v>482</v>
+        <v>887</v>
       </c>
       <c r="K59" t="s">
-        <v>476</v>
+        <v>882</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B60">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>773</v>
+        <v>934</v>
       </c>
       <c r="D60" t="s">
-        <v>774</v>
+        <v>973</v>
       </c>
       <c r="E60" t="s">
-        <v>783</v>
+        <v>974</v>
       </c>
       <c r="F60" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>786</v>
+        <v>468</v>
       </c>
       <c r="H60" t="s">
-        <v>788</v>
+        <v>977</v>
       </c>
       <c r="I60" t="s">
-        <v>789</v>
+        <v>978</v>
       </c>
       <c r="J60" t="s">
-        <v>790</v>
+        <v>979</v>
       </c>
       <c r="K60" t="s">
-        <v>784</v>
+        <v>975</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B61">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>773</v>
+        <v>934</v>
       </c>
       <c r="D61" t="s">
-        <v>799</v>
+        <v>980</v>
       </c>
       <c r="E61" t="s">
-        <v>800</v>
+        <v>981</v>
       </c>
       <c r="F61" t="s">
-        <v>793</v>
+        <v>983</v>
       </c>
       <c r="G61" t="s">
-        <v>802</v>
+        <v>984</v>
       </c>
       <c r="H61" t="s">
-        <v>804</v>
+        <v>986</v>
       </c>
       <c r="I61" t="s">
-        <v>805</v>
+        <v>987</v>
       </c>
       <c r="J61" t="s">
-        <v>806</v>
+        <v>988</v>
       </c>
       <c r="K61" t="s">
-        <v>801</v>
+        <v>982</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B62">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>773</v>
+        <v>934</v>
       </c>
       <c r="D62" t="s">
-        <v>821</v>
+        <v>1073</v>
       </c>
       <c r="E62" t="s">
-        <v>822</v>
+        <v>1074</v>
       </c>
       <c r="F62" t="s">
-        <v>777</v>
+        <v>1076</v>
       </c>
       <c r="G62" t="s">
-        <v>824</v>
+        <v>1077</v>
       </c>
       <c r="H62" t="s">
-        <v>826</v>
+        <v>1079</v>
       </c>
       <c r="I62" t="s">
-        <v>827</v>
+        <v>1080</v>
       </c>
       <c r="J62" t="s">
-        <v>828</v>
+        <v>1081</v>
       </c>
       <c r="K62" t="s">
-        <v>823</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B63">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="E63" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="H63" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I63" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="J63" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="K63" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B64">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
-        <v>394</v>
+        <v>89</v>
       </c>
       <c r="F64" t="s">
-        <v>396</v>
+        <v>130</v>
       </c>
       <c r="G64" t="s">
-        <v>397</v>
+        <v>131</v>
       </c>
       <c r="H64" t="s">
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="I64" t="s">
-        <v>400</v>
+        <v>134</v>
       </c>
       <c r="J64" t="s">
-        <v>401</v>
+        <v>135</v>
       </c>
       <c r="K64" t="s">
-        <v>395</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B65">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D65" t="s">
-        <v>410</v>
+        <v>300</v>
       </c>
       <c r="E65" t="s">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="F65" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G65" t="s">
-        <v>413</v>
+        <v>310</v>
       </c>
       <c r="H65" t="s">
-        <v>415</v>
+        <v>312</v>
       </c>
       <c r="I65" t="s">
-        <v>416</v>
+        <v>313</v>
       </c>
       <c r="J65" t="s">
-        <v>417</v>
+        <v>314</v>
       </c>
       <c r="K65" t="s">
-        <v>412</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B66">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C66" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D66" t="s">
-        <v>483</v>
+        <v>55</v>
       </c>
       <c r="E66" t="s">
-        <v>122</v>
+        <v>403</v>
       </c>
       <c r="F66" t="s">
-        <v>485</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>486</v>
+        <v>405</v>
       </c>
       <c r="H66" t="s">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="I66" t="s">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="J66" t="s">
-        <v>490</v>
+        <v>409</v>
       </c>
       <c r="K66" t="s">
-        <v>484</v>
+        <v>404</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B67">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D67" t="s">
-        <v>714</v>
+        <v>474</v>
       </c>
       <c r="E67" t="s">
-        <v>715</v>
+        <v>475</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>477</v>
       </c>
       <c r="G67" t="s">
-        <v>604</v>
+        <v>478</v>
       </c>
       <c r="H67" t="s">
-        <v>718</v>
+        <v>480</v>
       </c>
       <c r="I67" t="s">
-        <v>719</v>
+        <v>481</v>
       </c>
       <c r="J67" t="s">
-        <v>720</v>
+        <v>482</v>
       </c>
       <c r="K67" t="s">
-        <v>716</v>
+        <v>476</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B68">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D68" t="s">
-        <v>721</v>
+        <v>774</v>
       </c>
       <c r="E68" t="s">
-        <v>722</v>
+        <v>783</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>785</v>
       </c>
       <c r="G68" t="s">
-        <v>724</v>
+        <v>786</v>
       </c>
       <c r="H68" t="s">
-        <v>726</v>
+        <v>788</v>
       </c>
       <c r="I68" t="s">
-        <v>727</v>
+        <v>789</v>
       </c>
       <c r="J68" t="s">
-        <v>728</v>
+        <v>790</v>
       </c>
       <c r="K68" t="s">
-        <v>723</v>
+        <v>784</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B69">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D69" t="s">
-        <v>729</v>
+        <v>799</v>
       </c>
       <c r="E69" t="s">
-        <v>730</v>
+        <v>800</v>
       </c>
       <c r="F69" t="s">
-        <v>535</v>
+        <v>793</v>
       </c>
       <c r="G69" t="s">
-        <v>732</v>
+        <v>802</v>
       </c>
       <c r="H69" t="s">
-        <v>726</v>
+        <v>804</v>
       </c>
       <c r="I69" t="s">
-        <v>734</v>
+        <v>805</v>
       </c>
       <c r="J69" t="s">
-        <v>735</v>
+        <v>806</v>
       </c>
       <c r="K69" t="s">
-        <v>731</v>
+        <v>801</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B70">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C70" t="s">
         <v>773</v>
       </c>
       <c r="D70" t="s">
-        <v>791</v>
+        <v>821</v>
       </c>
       <c r="E70" t="s">
-        <v>610</v>
+        <v>822</v>
       </c>
       <c r="F70" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="G70" t="s">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="H70" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="I70" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="J70" t="s">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="K70" t="s">
-        <v>792</v>
+        <v>823</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B71">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C71" t="s">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="D71" t="s">
-        <v>896</v>
+        <v>989</v>
       </c>
       <c r="E71" t="s">
-        <v>897</v>
+        <v>990</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s">
-        <v>899</v>
+        <v>959</v>
       </c>
       <c r="H71" t="s">
-        <v>901</v>
+        <v>993</v>
       </c>
       <c r="I71" t="s">
-        <v>902</v>
+        <v>994</v>
       </c>
       <c r="J71" t="s">
-        <v>903</v>
+        <v>995</v>
       </c>
       <c r="K71" t="s">
-        <v>898</v>
+        <v>991</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B72">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D72" t="s">
-        <v>353</v>
+        <v>1065</v>
       </c>
       <c r="E72" t="s">
-        <v>362</v>
+        <v>1066</v>
       </c>
       <c r="F72" t="s">
-        <v>356</v>
+        <v>147</v>
       </c>
       <c r="G72" t="s">
-        <v>364</v>
+        <v>1068</v>
       </c>
       <c r="H72" t="s">
-        <v>366</v>
+        <v>1070</v>
       </c>
       <c r="I72" t="s">
-        <v>367</v>
+        <v>1071</v>
       </c>
       <c r="J72" t="s">
-        <v>368</v>
+        <v>1072</v>
       </c>
       <c r="K72" t="s">
-        <v>363</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B73">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>491</v>
+        <v>144</v>
       </c>
       <c r="E73" t="s">
-        <v>492</v>
+        <v>145</v>
       </c>
       <c r="F73" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="G73" t="s">
-        <v>494</v>
+        <v>148</v>
       </c>
       <c r="H73" t="s">
-        <v>496</v>
+        <v>150</v>
       </c>
       <c r="I73" t="s">
-        <v>497</v>
+        <v>151</v>
       </c>
       <c r="J73" t="s">
-        <v>498</v>
+        <v>152</v>
       </c>
       <c r="K73" t="s">
-        <v>493</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B74">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D74" t="s">
-        <v>532</v>
+        <v>144</v>
       </c>
       <c r="E74" t="s">
-        <v>533</v>
+        <v>394</v>
       </c>
       <c r="F74" t="s">
-        <v>535</v>
+        <v>396</v>
       </c>
       <c r="G74" t="s">
-        <v>536</v>
+        <v>397</v>
       </c>
       <c r="H74" t="s">
-        <v>538</v>
+        <v>399</v>
       </c>
       <c r="I74" t="s">
-        <v>539</v>
+        <v>400</v>
       </c>
       <c r="J74" t="s">
-        <v>540</v>
+        <v>401</v>
       </c>
       <c r="K74" t="s">
-        <v>534</v>
+        <v>395</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B75">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>591</v>
+        <v>402</v>
       </c>
       <c r="D75" t="s">
-        <v>643</v>
+        <v>410</v>
       </c>
       <c r="E75" t="s">
-        <v>644</v>
+        <v>411</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G75" t="s">
-        <v>618</v>
+        <v>413</v>
       </c>
       <c r="H75" t="s">
-        <v>647</v>
+        <v>415</v>
       </c>
       <c r="I75" t="s">
-        <v>648</v>
+        <v>416</v>
       </c>
       <c r="J75" t="s">
-        <v>649</v>
+        <v>417</v>
       </c>
       <c r="K75" t="s">
-        <v>645</v>
+        <v>412</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B76">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D76" t="s">
-        <v>736</v>
+        <v>483</v>
       </c>
       <c r="E76" t="s">
-        <v>737</v>
+        <v>122</v>
       </c>
       <c r="F76" t="s">
-        <v>739</v>
+        <v>485</v>
       </c>
       <c r="G76" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H76" t="s">
-        <v>741</v>
+        <v>488</v>
       </c>
       <c r="I76" t="s">
-        <v>742</v>
+        <v>489</v>
       </c>
       <c r="J76" t="s">
-        <v>743</v>
+        <v>490</v>
       </c>
       <c r="K76" t="s">
-        <v>738</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B77">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D77" t="s">
-        <v>807</v>
+        <v>714</v>
       </c>
       <c r="E77" t="s">
-        <v>808</v>
+        <v>715</v>
       </c>
       <c r="F77" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="H77" t="s">
-        <v>813</v>
+        <v>718</v>
       </c>
       <c r="I77" t="s">
-        <v>814</v>
+        <v>719</v>
       </c>
       <c r="J77" t="s">
-        <v>815</v>
+        <v>720</v>
       </c>
       <c r="K77" t="s">
-        <v>809</v>
+        <v>716</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B78">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D78" t="s">
-        <v>227</v>
+        <v>721</v>
       </c>
       <c r="E78" t="s">
-        <v>228</v>
+        <v>722</v>
       </c>
       <c r="F78" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="G78" t="s">
-        <v>231</v>
+        <v>724</v>
       </c>
       <c r="H78" t="s">
-        <v>233</v>
+        <v>726</v>
       </c>
       <c r="I78" t="s">
-        <v>234</v>
+        <v>727</v>
       </c>
       <c r="J78" t="s">
-        <v>235</v>
+        <v>728</v>
       </c>
       <c r="K78" t="s">
-        <v>229</v>
+        <v>723</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B79">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D79" t="s">
-        <v>266</v>
+        <v>729</v>
       </c>
       <c r="E79" t="s">
-        <v>267</v>
+        <v>730</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G79" t="s">
-        <v>58</v>
+        <v>732</v>
       </c>
       <c r="H79" t="s">
-        <v>270</v>
+        <v>726</v>
       </c>
       <c r="I79" t="s">
-        <v>79</v>
+        <v>734</v>
       </c>
       <c r="J79" t="s">
-        <v>79</v>
+        <v>735</v>
       </c>
       <c r="K79" t="s">
-        <v>268</v>
+        <v>731</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B80">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>791</v>
       </c>
       <c r="E80" t="s">
-        <v>339</v>
+        <v>610</v>
       </c>
       <c r="F80" t="s">
-        <v>341</v>
+        <v>793</v>
       </c>
       <c r="G80" t="s">
-        <v>342</v>
+        <v>794</v>
       </c>
       <c r="H80" t="s">
-        <v>344</v>
+        <v>796</v>
       </c>
       <c r="I80" t="s">
-        <v>345</v>
+        <v>797</v>
       </c>
       <c r="J80" t="s">
-        <v>346</v>
+        <v>798</v>
       </c>
       <c r="K80" t="s">
-        <v>340</v>
+        <v>792</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B81">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D81" t="s">
-        <v>601</v>
+        <v>896</v>
       </c>
       <c r="E81" t="s">
-        <v>602</v>
+        <v>897</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G81" t="s">
-        <v>604</v>
+        <v>899</v>
       </c>
       <c r="H81" t="s">
-        <v>606</v>
+        <v>901</v>
       </c>
       <c r="I81" t="s">
-        <v>607</v>
+        <v>902</v>
       </c>
       <c r="J81" t="s">
-        <v>608</v>
+        <v>903</v>
       </c>
       <c r="K81" t="s">
-        <v>603</v>
+        <v>898</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B82">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D82" t="s">
-        <v>80</v>
+        <v>964</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>965</v>
       </c>
       <c r="F82" t="s">
-        <v>25</v>
+        <v>967</v>
       </c>
       <c r="G82" t="s">
-        <v>83</v>
+        <v>968</v>
       </c>
       <c r="H82" t="s">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="I82" t="s">
-        <v>86</v>
+        <v>971</v>
       </c>
       <c r="J82" t="s">
-        <v>87</v>
+        <v>972</v>
       </c>
       <c r="K82" t="s">
-        <v>82</v>
+        <v>966</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B83">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D83" t="s">
-        <v>377</v>
+        <v>950</v>
       </c>
       <c r="E83" t="s">
-        <v>378</v>
+        <v>1002</v>
       </c>
       <c r="F83" t="s">
-        <v>380</v>
+        <v>1004</v>
       </c>
       <c r="G83" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="H83" t="s">
-        <v>383</v>
+        <v>1006</v>
       </c>
       <c r="I83" t="s">
-        <v>384</v>
+        <v>1007</v>
       </c>
       <c r="J83" t="s">
-        <v>385</v>
+        <v>1008</v>
       </c>
       <c r="K83" t="s">
-        <v>379</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B84">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>473</v>
+        <v>934</v>
       </c>
       <c r="D84" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="E84" t="s">
-        <v>500</v>
+        <v>1032</v>
       </c>
       <c r="F84" t="s">
-        <v>502</v>
+        <v>106</v>
       </c>
       <c r="G84" t="s">
-        <v>503</v>
+        <v>1034</v>
       </c>
       <c r="H84" t="s">
-        <v>505</v>
+        <v>1036</v>
       </c>
       <c r="I84" t="s">
-        <v>506</v>
+        <v>1037</v>
       </c>
       <c r="J84" t="s">
-        <v>507</v>
+        <v>1038</v>
       </c>
       <c r="K84" t="s">
-        <v>501</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B85">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="D85" t="s">
-        <v>616</v>
+        <v>1057</v>
       </c>
       <c r="E85" t="s">
-        <v>610</v>
+        <v>1058</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>618</v>
+        <v>1060</v>
       </c>
       <c r="H85" t="s">
-        <v>620</v>
+        <v>1062</v>
       </c>
       <c r="I85" t="s">
-        <v>621</v>
+        <v>1063</v>
       </c>
       <c r="J85" t="s">
-        <v>622</v>
+        <v>1064</v>
       </c>
       <c r="K85" t="s">
-        <v>617</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>945</v>
+        <v>1098</v>
       </c>
       <c r="B86">
+        <v>83</v>
+      </c>
+      <c r="C86" t="s">
+        <v>284</v>
+      </c>
+      <c r="D86" t="s">
+        <v>353</v>
+      </c>
+      <c r="E86" t="s">
+        <v>362</v>
+      </c>
+      <c r="F86" t="s">
+        <v>356</v>
+      </c>
+      <c r="G86" t="s">
+        <v>364</v>
+      </c>
+      <c r="H86" t="s">
+        <v>366</v>
+      </c>
+      <c r="I86" t="s">
+        <v>367</v>
+      </c>
+      <c r="J86" t="s">
+        <v>368</v>
+      </c>
+      <c r="K86" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B87">
+        <v>83</v>
+      </c>
+      <c r="C87" t="s">
+        <v>473</v>
+      </c>
+      <c r="D87" t="s">
+        <v>491</v>
+      </c>
+      <c r="E87" t="s">
+        <v>492</v>
+      </c>
+      <c r="F87" t="s">
+        <v>75</v>
+      </c>
+      <c r="G87" t="s">
+        <v>494</v>
+      </c>
+      <c r="H87" t="s">
+        <v>496</v>
+      </c>
+      <c r="I87" t="s">
+        <v>497</v>
+      </c>
+      <c r="J87" t="s">
+        <v>498</v>
+      </c>
+      <c r="K87" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B88">
+        <v>83</v>
+      </c>
+      <c r="C88" t="s">
+        <v>473</v>
+      </c>
+      <c r="D88" t="s">
+        <v>532</v>
+      </c>
+      <c r="E88" t="s">
+        <v>533</v>
+      </c>
+      <c r="F88" t="s">
+        <v>535</v>
+      </c>
+      <c r="G88" t="s">
+        <v>536</v>
+      </c>
+      <c r="H88" t="s">
+        <v>538</v>
+      </c>
+      <c r="I88" t="s">
+        <v>539</v>
+      </c>
+      <c r="J88" t="s">
+        <v>540</v>
+      </c>
+      <c r="K88" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B89">
+        <v>83</v>
+      </c>
+      <c r="C89" t="s">
+        <v>591</v>
+      </c>
+      <c r="D89" t="s">
+        <v>643</v>
+      </c>
+      <c r="E89" t="s">
+        <v>644</v>
+      </c>
+      <c r="F89" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" t="s">
+        <v>618</v>
+      </c>
+      <c r="H89" t="s">
+        <v>647</v>
+      </c>
+      <c r="I89" t="s">
+        <v>648</v>
+      </c>
+      <c r="J89" t="s">
+        <v>649</v>
+      </c>
+      <c r="K89" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B90">
+        <v>83</v>
+      </c>
+      <c r="C90" t="s">
+        <v>697</v>
+      </c>
+      <c r="D90" t="s">
+        <v>736</v>
+      </c>
+      <c r="E90" t="s">
+        <v>737</v>
+      </c>
+      <c r="F90" t="s">
+        <v>739</v>
+      </c>
+      <c r="G90" t="s">
+        <v>604</v>
+      </c>
+      <c r="H90" t="s">
+        <v>741</v>
+      </c>
+      <c r="I90" t="s">
+        <v>742</v>
+      </c>
+      <c r="J90" t="s">
+        <v>743</v>
+      </c>
+      <c r="K90" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B91">
+        <v>83</v>
+      </c>
+      <c r="C91" t="s">
+        <v>773</v>
+      </c>
+      <c r="D91" t="s">
+        <v>807</v>
+      </c>
+      <c r="E91" t="s">
+        <v>808</v>
+      </c>
+      <c r="F91" t="s">
+        <v>810</v>
+      </c>
+      <c r="G91" t="s">
+        <v>811</v>
+      </c>
+      <c r="H91" t="s">
+        <v>813</v>
+      </c>
+      <c r="I91" t="s">
+        <v>814</v>
+      </c>
+      <c r="J91" t="s">
+        <v>815</v>
+      </c>
+      <c r="K91" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B92">
+        <v>83</v>
+      </c>
+      <c r="C92" t="s">
+        <v>934</v>
+      </c>
+      <c r="D92" t="s">
+        <v>650</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F92" t="s">
+        <v>66</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J92" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B93">
+        <v>83</v>
+      </c>
+      <c r="C93" t="s">
+        <v>934</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E93" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K93" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B94">
+        <v>82</v>
+      </c>
+      <c r="C94" t="s">
+        <v>159</v>
+      </c>
+      <c r="D94" t="s">
+        <v>227</v>
+      </c>
+      <c r="E94" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" t="s">
+        <v>230</v>
+      </c>
+      <c r="G94" t="s">
+        <v>231</v>
+      </c>
+      <c r="H94" t="s">
+        <v>233</v>
+      </c>
+      <c r="I94" t="s">
+        <v>234</v>
+      </c>
+      <c r="J94" t="s">
+        <v>235</v>
+      </c>
+      <c r="K94" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B95">
+        <v>82</v>
+      </c>
+      <c r="C95" t="s">
+        <v>159</v>
+      </c>
+      <c r="D95" t="s">
+        <v>266</v>
+      </c>
+      <c r="E95" t="s">
+        <v>267</v>
+      </c>
+      <c r="F95" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
+        <v>58</v>
+      </c>
+      <c r="H95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I95" t="s">
+        <v>79</v>
+      </c>
+      <c r="J95" t="s">
+        <v>79</v>
+      </c>
+      <c r="K95" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B96">
+        <v>82</v>
+      </c>
+      <c r="C96" t="s">
+        <v>284</v>
+      </c>
+      <c r="D96" t="s">
+        <v>338</v>
+      </c>
+      <c r="E96" t="s">
+        <v>339</v>
+      </c>
+      <c r="F96" t="s">
+        <v>341</v>
+      </c>
+      <c r="G96" t="s">
+        <v>342</v>
+      </c>
+      <c r="H96" t="s">
+        <v>344</v>
+      </c>
+      <c r="I96" t="s">
+        <v>345</v>
+      </c>
+      <c r="J96" t="s">
+        <v>346</v>
+      </c>
+      <c r="K96" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B97">
+        <v>82</v>
+      </c>
+      <c r="C97" t="s">
+        <v>591</v>
+      </c>
+      <c r="D97" t="s">
+        <v>601</v>
+      </c>
+      <c r="E97" t="s">
+        <v>602</v>
+      </c>
+      <c r="F97" t="s">
+        <v>75</v>
+      </c>
+      <c r="G97" t="s">
+        <v>604</v>
+      </c>
+      <c r="H97" t="s">
+        <v>606</v>
+      </c>
+      <c r="I97" t="s">
+        <v>607</v>
+      </c>
+      <c r="J97" t="s">
+        <v>608</v>
+      </c>
+      <c r="K97" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B98">
+        <v>82</v>
+      </c>
+      <c r="C98" t="s">
+        <v>934</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F98" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K98" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B99">
+        <v>82</v>
+      </c>
+      <c r="C99" t="s">
+        <v>934</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K99" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B100">
         <v>81</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>80</v>
+      </c>
+      <c r="E100" t="s">
+        <v>81</v>
+      </c>
+      <c r="F100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" t="s">
+        <v>83</v>
+      </c>
+      <c r="H100" t="s">
+        <v>85</v>
+      </c>
+      <c r="I100" t="s">
+        <v>86</v>
+      </c>
+      <c r="J100" t="s">
+        <v>87</v>
+      </c>
+      <c r="K100" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B101">
+        <v>81</v>
+      </c>
+      <c r="C101" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
+        <v>377</v>
+      </c>
+      <c r="E101" t="s">
+        <v>378</v>
+      </c>
+      <c r="F101" t="s">
+        <v>380</v>
+      </c>
+      <c r="G101" t="s">
+        <v>381</v>
+      </c>
+      <c r="H101" t="s">
+        <v>383</v>
+      </c>
+      <c r="I101" t="s">
+        <v>384</v>
+      </c>
+      <c r="J101" t="s">
+        <v>385</v>
+      </c>
+      <c r="K101" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B102">
+        <v>81</v>
+      </c>
+      <c r="C102" t="s">
+        <v>473</v>
+      </c>
+      <c r="D102" t="s">
+        <v>499</v>
+      </c>
+      <c r="E102" t="s">
+        <v>500</v>
+      </c>
+      <c r="F102" t="s">
+        <v>502</v>
+      </c>
+      <c r="G102" t="s">
+        <v>503</v>
+      </c>
+      <c r="H102" t="s">
+        <v>505</v>
+      </c>
+      <c r="I102" t="s">
+        <v>506</v>
+      </c>
+      <c r="J102" t="s">
+        <v>507</v>
+      </c>
+      <c r="K102" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B103">
+        <v>81</v>
+      </c>
+      <c r="C103" t="s">
+        <v>591</v>
+      </c>
+      <c r="D103" t="s">
+        <v>616</v>
+      </c>
+      <c r="E103" t="s">
+        <v>610</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s">
+        <v>618</v>
+      </c>
+      <c r="H103" t="s">
+        <v>620</v>
+      </c>
+      <c r="I103" t="s">
+        <v>621</v>
+      </c>
+      <c r="J103" t="s">
+        <v>622</v>
+      </c>
+      <c r="K103" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B104">
+        <v>81</v>
+      </c>
+      <c r="C104" t="s">
         <v>845</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D104" t="s">
         <v>888</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E104" t="s">
         <v>889</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F104" t="s">
         <v>25</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G104" t="s">
         <v>891</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H104" t="s">
         <v>893</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I104" t="s">
         <v>894</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J104" t="s">
         <v>895</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K104" t="s">
         <v>890</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B105">
+        <v>80</v>
+      </c>
+      <c r="C105" t="s">
+        <v>934</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K105" t="s">
+        <v>1041</v>
       </c>
     </row>
   </sheetData>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="1195">
   <si>
     <t>日期</t>
   </si>
@@ -3275,6 +3275,210 @@
   </si>
   <si>
     <t>智能匹配78分【社招】|值得考虑|血管支架工艺岗，方向直接匹配但要求3年经验</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>史赛克医疗器械（Stryker，北京）</t>
+  </si>
+  <si>
+    <t>器械研发工程师（血管介入方向）</t>
+  </si>
+  <si>
+    <t>硕士学历，3-5年血管介入医疗器械研发经验，15-30k；负责血管介入类器械的研发、设计与技术改进，涉及支架/球囊/导管等结构、材料及测试分析。</t>
+  </si>
+  <si>
+    <t>北京-密云</t>
+  </si>
+  <si>
+    <t>https://www.jobs.stryker.com</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|国际血管介入器械龙头，方向与技能高度重合</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历92/行业100/企业92</t>
+  </si>
+  <si>
+    <t>Stryker 为全球骨科与医疗科技巨头，血管介入研发方向与候选人研究方向高度匹配；北京职位契合目标城市，能接触国际一流器械研发流程与注册体系，是进入头部外企介入器械研发的优质平台。</t>
+  </si>
+  <si>
+    <t>突出血管支架/介入结构的研发经验与有限元、三维建模等设计技能；量化参与的植入器械项目与动物实验/生物相容性评价成果；强调生物医学工程硕士背景及对 ISO 体系、三类产品开发流程的理解。</t>
+  </si>
+  <si>
+    <t>研发工程师（支架）</t>
+  </si>
+  <si>
+    <t>硕士，2年以上，2-3.5万·14薪；负责支架产品结构设计、工艺设计（DHF/DMR）、材料选型、专利撰写及物料、供应商开发。</t>
+  </si>
+  <si>
+    <t>https://www.bamaomed.com</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招】|强烈推荐|支架产品结构与工艺设计岗，方向高度精准</t>
+  </si>
+  <si>
+    <t>研究90/技能82/学历85/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位直接负责血管支架的结构设计与工艺开发，与候选人血管支架研究方向几乎100%重合；上海地点契合，DHF/DMR建档与材料选型工作能充分发挥生物医学工程+材料学技能，职业发展与平台成长性好。</t>
+  </si>
+  <si>
+    <t>突出支架结构设计与三维建模/有限元分析实操；强调可降解/金属支架材料选型、工艺（DHF/DMR）文档能力；附上支架设计或动物实验相关课题成果，体现独立研发到转产能力。</t>
+  </si>
+  <si>
+    <t>研发工程师（球囊/导管）</t>
+  </si>
+  <si>
+    <t>本科及以上，负责球囊/导管类介入器械研发，20-30k·15薪；涉及结构设计、材料选型、工艺与测试分析。</t>
+  </si>
+  <si>
+    <t>苏州-望亭</t>
+  </si>
+  <si>
+    <t>https://www.salubris.com</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|上市公司球囊/导管介入研发岗，方向相关</t>
+  </si>
+  <si>
+    <t>研究82/技能76/学历88/行业100/企业88</t>
+  </si>
+  <si>
+    <t>信立泰为A股上市医药龙头旗下介入器械业务，球囊/导管研发与候选人介入医疗器械方向相关，苏州地点契合；能进入成熟上市公司的器械研发体系，适合系统化发展介入器械产品能力。</t>
+  </si>
+  <si>
+    <t>侧重介入导管/球囊类产品的材料（镍钛、高分子）与结构设计经验；量化相关课题；强调对三类介入器械开发流程、ISO 10993 生物相容性评价的理解。</t>
+  </si>
+  <si>
+    <t>北京品驰医疗设备股份有限公司</t>
+  </si>
+  <si>
+    <t>2026校园招聘（植入式医疗器械研发岗）</t>
+  </si>
+  <si>
+    <t>面向应届硕士，从事脑起搏器/神经调控等植入式医疗器械产品研发及质量控制方向；覆盖结构、材料、工艺与测试。</t>
+  </si>
+  <si>
+    <t>https://www.pinsmedical.com</t>
+  </si>
+  <si>
+    <t>智能匹配82分【校园招聘】|强烈推荐|植入医疗器械研发校招，硕士应届高度可投</t>
+  </si>
+  <si>
+    <t>研究75/技能76/学历100/行业100/企业80</t>
+  </si>
+  <si>
+    <t>北京契合目标城市；植入式医疗器械领域与生物医学工程方向相关，校招对应届硕士友好，是进入国产神经调控植入器械头部企业研发的稳定通道，能系统培养植入器械研发与质量控制能力。</t>
+  </si>
+  <si>
+    <t>突出医疗器械/植入器械方向课题与技能（材料、生物相容性、结构设计）；强调应届可投的校招定位、专业匹配度；弱化临床，突出研发项目与规范性（注册、测试、ISO）。</t>
+  </si>
+  <si>
+    <t>山东百多安医疗器械股份有限公司</t>
+  </si>
+  <si>
+    <t>2026校园招聘研发工程师</t>
+  </si>
+  <si>
+    <t>校招，硕士，6-8k；电子信息/化学/统计/生物科学/公卫类可；三类医疗器械研发，晋升路径研发工程师→项目经理→研发经理。</t>
+  </si>
+  <si>
+    <t>山东-德州</t>
+  </si>
+  <si>
+    <t>https://www.buoyan.com</t>
+  </si>
+  <si>
+    <t>智能匹配81分【校园招聘】|强烈推荐|三类医疗器械研发校招，硕士应届友好</t>
+  </si>
+  <si>
+    <t>研究78/技能70/学历100/行业100/企业78</t>
+  </si>
+  <si>
+    <t>校园招聘对应届硕士高度可投，专业（生物科学/医学类）匹配生物医学工程方向；三类医疗器械研发平台加上清晰的研发晋升路径，适合作为职业起点，尽管城市非目标四城但成长路径明确。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程师背景与材料/生物相容性课程及课题；强调校招应届身份、扎实的实验与科研训练；如参加过医疗器械或生物材料课题需明确写出。</t>
+  </si>
+  <si>
+    <t>倍咏医疗（苏州）</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（微创介入）</t>
+  </si>
+  <si>
+    <t>苏州吴中经开区企业，专注微创介入医疗器械的研发、制造、销售；研发工程师负责介入器械产品设计与开发。</t>
+  </si>
+  <si>
+    <t>苏州-吴中</t>
+  </si>
+  <si>
+    <t>https://www.beiyong.com</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|苏州微创介入器械研发岗，方向相关</t>
+  </si>
+  <si>
+    <t>研究78/技能70/学历90/行业100/企业75</t>
+  </si>
+  <si>
+    <t>苏州为目标城市，企业专注微创介入医疗器械研发，方向与候选人的介入器械技术背景相关，可积累血管介入器械研发实操经验；科研产业氛围好，适合在长三角医械集群发展。</t>
+  </si>
+  <si>
+    <t>突出介入器械/医疗器械研发课题与技能；强调苏州本地求职意愿；如有支架/导管研发或材料选型经历重点展示。</t>
+  </si>
+  <si>
+    <t>北京阿迈特医疗器械股份有限公司</t>
+  </si>
+  <si>
+    <t>高级研发工程师（可降解放疗支架增材制造）</t>
+  </si>
+  <si>
+    <t>负责3D多轴精密打印全降解血管支架增材制造研发；高分子/生物材料/增材制造研发经验；参与国家级/省部级研发项目。</t>
+  </si>
+  <si>
+    <t>https://www.ametcorp.com</t>
+  </si>
+  <si>
+    <t>智能匹配90分【社招】|强烈推荐|北京市可降解血管支架研发岗，方向+技能高度重合</t>
+  </si>
+  <si>
+    <t>研究92/技能88/学历88/行业100/企业82</t>
+  </si>
+  <si>
+    <t>岗位直接从事可降解毒（全降解）血管支架及增材制造研发，与候选人血管支架研究方向与生物医用高分子技能几乎完美契合；北京地点契合，可参与国家级/省部级研发项目，学术与产业化结合度高。</t>
+  </si>
+  <si>
+    <t>重点展示血管支架研究课题、可降解高分子材料与材料学技能；突出支架设计/有限元/三维建模；体现对增材制造或精密加工的理解；强调生物相容性与动物实验评价能力。</t>
+  </si>
+  <si>
+    <t>北京华脉泰科医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>医疗器械研发工程师（应届可投）</t>
+  </si>
+  <si>
+    <t>硕士，不限经验（应届可投），8-10k；Ⅲ类植入介入医疗器械产品开发与工艺设计、产品测试、文献检索。</t>
+  </si>
+  <si>
+    <t>北京-大兴</t>
+  </si>
+  <si>
+    <t>https://www.hmtech.com.cn</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招/应届均可】|强烈推荐|Ⅲ类植入介入器械研发，应届硕士可投，方向契合</t>
+  </si>
+  <si>
+    <t>研究82/技能78/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>华脉泰科为主动脉及外周血管介入器械企业（IPO过会），岗位面向应届硕士，Ⅲ类植入介入医疗器械研发与工艺设计与候选人血管支架研究方向高度契合，北京大兴目标城市，适合应届生进入血管介入器械研发主赛道。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程硕士背景、血管支架研究课题与产品测试能力；强调文献检索与规范性（三类器械、注册测试）；作为应届要把校招/应届身份与研发项目成果放在醒目位置。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -3829,7 +4033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9391,6 +9595,310 @@
       </c>
       <c r="L146" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G147">
+        <v>9</v>
+      </c>
+      <c r="H147" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I147">
+        <v>86</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B148" t="s">
+        <v>964</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E148" t="s">
+        <v>16</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G148">
+        <v>9</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I148">
+        <v>87</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B149" t="s">
+        <v>271</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G149">
+        <v>8</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I149">
+        <v>84</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E150" t="s">
+        <v>25</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G150">
+        <v>8</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I150">
+        <v>82</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G151">
+        <v>8</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I151">
+        <v>81</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D152" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G152">
+        <v>8</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I152">
+        <v>79</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E153" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G153">
+        <v>9</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I153">
+        <v>90</v>
+      </c>
+      <c r="J153" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G154">
+        <v>9</v>
+      </c>
+      <c r="H154" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I154">
+        <v>86</v>
+      </c>
+      <c r="J154" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1154</v>
       </c>
     </row>
   </sheetData>
@@ -9424,7 +9932,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1087</v>
+        <v>1155</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -9433,16 +9941,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1088</v>
+        <v>1156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1089</v>
+        <v>1157</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1090</v>
+        <v>1158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1091</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9456,13 +9964,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1092</v>
+        <v>1160</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1093</v>
+        <v>1161</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1094</v>
+        <v>1162</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -9490,7 +9998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -9505,7 +10013,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1099</v>
+        <v>1167</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -9515,31 +10023,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1100</v>
+        <v>1168</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1101</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1102</v>
+        <v>1170</v>
       </c>
       <c r="B4">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1103</v>
+        <v>1171</v>
       </c>
       <c r="B5" t="s">
-        <v>1104</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1105</v>
+        <v>1173</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -9547,7 +10055,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1106</v>
+        <v>1174</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -9555,23 +10063,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1107</v>
+        <v>1175</v>
       </c>
       <c r="B8">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1108</v>
+        <v>1176</v>
       </c>
       <c r="B9">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1109</v>
+        <v>1177</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -9579,15 +10087,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1110</v>
+        <v>1178</v>
       </c>
       <c r="B11" t="s">
-        <v>934</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1111</v>
+        <v>1179</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -9597,15 +10105,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1112</v>
+        <v>1180</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1113</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1114</v>
+        <v>1182</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -9613,23 +10121,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1115</v>
+        <v>1183</v>
       </c>
       <c r="B17" s="5">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1116</v>
+        <v>1184</v>
       </c>
       <c r="B18" s="5">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1117</v>
+        <v>1185</v>
       </c>
       <c r="B19" s="5">
         <v>5</v>
@@ -9637,7 +10145,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1118</v>
+        <v>1186</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -9645,7 +10153,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1119</v>
+        <v>1187</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -9653,7 +10161,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1120</v>
+        <v>1188</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -9661,7 +10169,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1121</v>
+        <v>1189</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -9669,7 +10177,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1122</v>
+        <v>1190</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -9677,7 +10185,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1123</v>
+        <v>1191</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -9685,7 +10193,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1124</v>
+        <v>1192</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -9697,7 +10205,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1125</v>
+        <v>1193</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -9715,7 +10223,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1126</v>
+        <v>1194</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -11572,25 +12080,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>1088</v>
       </c>
       <c r="D101" t="s">
-        <v>73</v>
+        <v>1089</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>1091</v>
       </c>
       <c r="F101" t="s">
-        <v>76</v>
+        <v>1092</v>
       </c>
       <c r="G101">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H101" t="s">
-        <v>77</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -11598,25 +12106,25 @@
         <v>73</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="C102" t="s">
-        <v>80</v>
+        <v>964</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>1097</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F102" t="s">
-        <v>83</v>
+        <v>1099</v>
       </c>
       <c r="G102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H102" t="s">
-        <v>84</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -11624,25 +12132,25 @@
         <v>74</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>1138</v>
       </c>
       <c r="D103" t="s">
-        <v>104</v>
+        <v>1139</v>
       </c>
       <c r="E103" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F103" t="s">
-        <v>107</v>
+        <v>1141</v>
       </c>
       <c r="G103">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H103" t="s">
-        <v>108</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -11650,25 +12158,25 @@
         <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="C104" t="s">
-        <v>109</v>
+        <v>1146</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>1147</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="F104" t="s">
-        <v>112</v>
+        <v>1150</v>
       </c>
       <c r="G104">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H104" t="s">
-        <v>113</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -11679,22 +12187,22 @@
         <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="D105" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F105" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="G105">
         <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -11705,22 +12213,22 @@
         <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="D106" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="E106" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -11731,22 +12239,22 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="E107" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="F107" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -11757,22 +12265,22 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="D108" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="E108" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -11780,25 +12288,25 @@
         <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>207</v>
+        <v>115</v>
       </c>
       <c r="D109" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="E109" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>211</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -11806,25 +12314,25 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>213</v>
+        <v>121</v>
       </c>
       <c r="D110" t="s">
-        <v>214</v>
+        <v>122</v>
       </c>
       <c r="E110" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="F110" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -11832,25 +12340,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
       <c r="F111" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>232</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -11858,25 +12366,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="D112" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="E112" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F112" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -11887,22 +12395,22 @@
         <v>159</v>
       </c>
       <c r="C113" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F113" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -11913,22 +12421,22 @@
         <v>159</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="D114" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -11939,22 +12447,22 @@
         <v>159</v>
       </c>
       <c r="C115" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="D115" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="E115" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F115" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -11965,22 +12473,22 @@
         <v>159</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D116" t="s">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="E116" t="s">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="F116" t="s">
-        <v>258</v>
+        <v>76</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -11991,22 +12499,22 @@
         <v>159</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="E117" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F117" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -12017,22 +12525,22 @@
         <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D118" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="E118" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -12043,22 +12551,22 @@
         <v>159</v>
       </c>
       <c r="C119" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="D119" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="E119" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -12066,25 +12574,25 @@
         <v>91</v>
       </c>
       <c r="B120" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C120" t="s">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="D120" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="E120" t="s">
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="F120" t="s">
-        <v>319</v>
+        <v>258</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -12092,25 +12600,25 @@
         <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C121" t="s">
-        <v>338</v>
+        <v>261</v>
       </c>
       <c r="D121" t="s">
-        <v>339</v>
+        <v>122</v>
       </c>
       <c r="E121" t="s">
-        <v>341</v>
+        <v>147</v>
       </c>
       <c r="F121" t="s">
-        <v>342</v>
+        <v>263</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>343</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -12118,25 +12626,25 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="E122" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>350</v>
+        <v>58</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -12144,25 +12652,25 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="D123" t="s">
-        <v>362</v>
+        <v>278</v>
       </c>
       <c r="E123" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="F123" t="s">
-        <v>364</v>
+        <v>281</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>365</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -12173,22 +12681,22 @@
         <v>284</v>
       </c>
       <c r="C124" t="s">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="D124" t="s">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="E124" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="F124" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>382</v>
+        <v>320</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -12199,22 +12707,22 @@
         <v>284</v>
       </c>
       <c r="C125" t="s">
-        <v>144</v>
+        <v>338</v>
       </c>
       <c r="D125" t="s">
-        <v>394</v>
+        <v>339</v>
       </c>
       <c r="E125" t="s">
-        <v>396</v>
+        <v>341</v>
       </c>
       <c r="F125" t="s">
-        <v>397</v>
+        <v>342</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>398</v>
+        <v>343</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -12222,25 +12730,25 @@
         <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C126" t="s">
-        <v>410</v>
+        <v>347</v>
       </c>
       <c r="D126" t="s">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="E126" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F126" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -12248,25 +12756,25 @@
         <v>98</v>
       </c>
       <c r="B127" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C127" t="s">
-        <v>418</v>
+        <v>353</v>
       </c>
       <c r="D127" t="s">
-        <v>419</v>
+        <v>362</v>
       </c>
       <c r="E127" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F127" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>422</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -12274,25 +12782,25 @@
         <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C128" t="s">
-        <v>424</v>
+        <v>377</v>
       </c>
       <c r="D128" t="s">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="E128" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F128" t="s">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>428</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -12300,25 +12808,25 @@
         <v>100</v>
       </c>
       <c r="B129" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C129" t="s">
-        <v>430</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="F129" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -12326,25 +12834,25 @@
         <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C130" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="D130" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="E130" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F130" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>487</v>
+        <v>414</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -12352,25 +12860,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C131" t="s">
-        <v>491</v>
+        <v>418</v>
       </c>
       <c r="D131" t="s">
-        <v>492</v>
+        <v>419</v>
       </c>
       <c r="E131" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F131" t="s">
-        <v>494</v>
+        <v>421</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>495</v>
+        <v>422</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -12378,25 +12886,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C132" t="s">
-        <v>499</v>
+        <v>424</v>
       </c>
       <c r="D132" t="s">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="E132" t="s">
-        <v>502</v>
+        <v>66</v>
       </c>
       <c r="F132" t="s">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>504</v>
+        <v>428</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -12404,25 +12912,25 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C133" t="s">
-        <v>532</v>
+        <v>430</v>
       </c>
       <c r="D133" t="s">
-        <v>533</v>
+        <v>431</v>
       </c>
       <c r="E133" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="F133" t="s">
-        <v>536</v>
+        <v>433</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>537</v>
+        <v>434</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -12433,22 +12941,22 @@
         <v>473</v>
       </c>
       <c r="C134" t="s">
-        <v>550</v>
+        <v>483</v>
       </c>
       <c r="D134" t="s">
-        <v>551</v>
+        <v>122</v>
       </c>
       <c r="E134" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="F134" t="s">
-        <v>553</v>
+        <v>486</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>554</v>
+        <v>487</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -12456,25 +12964,25 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C135" t="s">
-        <v>578</v>
+        <v>491</v>
       </c>
       <c r="D135" t="s">
-        <v>579</v>
+        <v>492</v>
       </c>
       <c r="E135" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F135" t="s">
-        <v>581</v>
+        <v>494</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>582</v>
+        <v>495</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -12482,25 +12990,25 @@
         <v>107</v>
       </c>
       <c r="B136" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C136" t="s">
-        <v>584</v>
+        <v>499</v>
       </c>
       <c r="D136" t="s">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="E136" t="s">
-        <v>587</v>
+        <v>502</v>
       </c>
       <c r="F136" t="s">
-        <v>588</v>
+        <v>503</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>589</v>
+        <v>504</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -12508,25 +13016,25 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C137" t="s">
-        <v>601</v>
+        <v>532</v>
       </c>
       <c r="D137" t="s">
-        <v>602</v>
+        <v>533</v>
       </c>
       <c r="E137" t="s">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="F137" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>605</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -12534,25 +13042,25 @@
         <v>109</v>
       </c>
       <c r="B138" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C138" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="D138" t="s">
-        <v>610</v>
+        <v>551</v>
       </c>
       <c r="E138" t="s">
         <v>16</v>
       </c>
       <c r="F138" t="s">
-        <v>618</v>
+        <v>553</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>619</v>
+        <v>554</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -12560,25 +13068,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C139" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="D139" t="s">
-        <v>623</v>
+        <v>579</v>
       </c>
       <c r="E139" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F139" t="s">
-        <v>468</v>
+        <v>581</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>625</v>
+        <v>582</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -12586,25 +13094,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C140" t="s">
-        <v>643</v>
+        <v>584</v>
       </c>
       <c r="D140" t="s">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="E140" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F140" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>646</v>
+        <v>589</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -12615,22 +13123,22 @@
         <v>591</v>
       </c>
       <c r="C141" t="s">
-        <v>650</v>
+        <v>601</v>
       </c>
       <c r="D141" t="s">
-        <v>651</v>
+        <v>602</v>
       </c>
       <c r="E141" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F141" t="s">
-        <v>653</v>
+        <v>604</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -12641,22 +13149,22 @@
         <v>591</v>
       </c>
       <c r="C142" t="s">
-        <v>658</v>
+        <v>616</v>
       </c>
       <c r="D142" t="s">
-        <v>659</v>
+        <v>610</v>
       </c>
       <c r="E142" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>663</v>
+        <v>619</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -12667,22 +13175,22 @@
         <v>591</v>
       </c>
       <c r="C143" t="s">
-        <v>666</v>
+        <v>557</v>
       </c>
       <c r="D143" t="s">
-        <v>667</v>
+        <v>623</v>
       </c>
       <c r="E143" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F143" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>669</v>
+        <v>625</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -12693,22 +13201,22 @@
         <v>591</v>
       </c>
       <c r="C144" t="s">
-        <v>673</v>
+        <v>643</v>
       </c>
       <c r="D144" t="s">
-        <v>674</v>
+        <v>644</v>
       </c>
       <c r="E144" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>676</v>
+        <v>618</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -12716,25 +13224,25 @@
         <v>116</v>
       </c>
       <c r="B145" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C145" t="s">
-        <v>714</v>
+        <v>650</v>
       </c>
       <c r="D145" t="s">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F145" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>717</v>
+        <v>654</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -12742,25 +13250,25 @@
         <v>117</v>
       </c>
       <c r="B146" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C146" t="s">
-        <v>721</v>
+        <v>658</v>
       </c>
       <c r="D146" t="s">
-        <v>722</v>
+        <v>659</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>661</v>
       </c>
       <c r="F146" t="s">
-        <v>724</v>
+        <v>662</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -12768,25 +13276,25 @@
         <v>118</v>
       </c>
       <c r="B147" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C147" t="s">
-        <v>729</v>
+        <v>666</v>
       </c>
       <c r="D147" t="s">
-        <v>730</v>
+        <v>667</v>
       </c>
       <c r="E147" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F147" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>733</v>
+        <v>669</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -12794,25 +13302,25 @@
         <v>119</v>
       </c>
       <c r="B148" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C148" t="s">
-        <v>736</v>
+        <v>673</v>
       </c>
       <c r="D148" t="s">
-        <v>737</v>
+        <v>674</v>
       </c>
       <c r="E148" t="s">
-        <v>739</v>
+        <v>66</v>
       </c>
       <c r="F148" t="s">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>740</v>
+        <v>677</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -12823,22 +13331,22 @@
         <v>697</v>
       </c>
       <c r="C149" t="s">
-        <v>744</v>
+        <v>714</v>
       </c>
       <c r="D149" t="s">
-        <v>745</v>
+        <v>715</v>
       </c>
       <c r="E149" t="s">
-        <v>747</v>
+        <v>16</v>
       </c>
       <c r="F149" t="s">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>749</v>
+        <v>717</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -12849,22 +13357,22 @@
         <v>697</v>
       </c>
       <c r="C150" t="s">
-        <v>753</v>
+        <v>721</v>
       </c>
       <c r="D150" t="s">
-        <v>754</v>
+        <v>722</v>
       </c>
       <c r="E150" t="s">
-        <v>756</v>
+        <v>25</v>
       </c>
       <c r="F150" t="s">
-        <v>757</v>
+        <v>724</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -12875,22 +13383,22 @@
         <v>697</v>
       </c>
       <c r="C151" t="s">
-        <v>760</v>
+        <v>729</v>
       </c>
       <c r="D151" t="s">
-        <v>761</v>
+        <v>730</v>
       </c>
       <c r="E151" t="s">
-        <v>763</v>
+        <v>535</v>
       </c>
       <c r="F151" t="s">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>765</v>
+        <v>733</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -12898,25 +13406,25 @@
         <v>123</v>
       </c>
       <c r="B152" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C152" t="s">
-        <v>791</v>
+        <v>736</v>
       </c>
       <c r="D152" t="s">
-        <v>610</v>
+        <v>737</v>
       </c>
       <c r="E152" t="s">
-        <v>793</v>
+        <v>739</v>
       </c>
       <c r="F152" t="s">
-        <v>794</v>
+        <v>604</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>795</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -12924,25 +13432,25 @@
         <v>124</v>
       </c>
       <c r="B153" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C153" t="s">
-        <v>807</v>
+        <v>744</v>
       </c>
       <c r="D153" t="s">
-        <v>808</v>
+        <v>745</v>
       </c>
       <c r="E153" t="s">
-        <v>810</v>
+        <v>747</v>
       </c>
       <c r="F153" t="s">
-        <v>811</v>
+        <v>748</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>812</v>
+        <v>749</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -12950,25 +13458,25 @@
         <v>125</v>
       </c>
       <c r="B154" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C154" t="s">
-        <v>816</v>
+        <v>753</v>
       </c>
       <c r="D154" t="s">
-        <v>110</v>
+        <v>754</v>
       </c>
       <c r="E154" t="s">
-        <v>16</v>
+        <v>756</v>
       </c>
       <c r="F154" t="s">
-        <v>818</v>
+        <v>757</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>819</v>
+        <v>758</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -12976,25 +13484,25 @@
         <v>126</v>
       </c>
       <c r="B155" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C155" t="s">
-        <v>888</v>
+        <v>760</v>
       </c>
       <c r="D155" t="s">
-        <v>889</v>
+        <v>761</v>
       </c>
       <c r="E155" t="s">
-        <v>25</v>
+        <v>763</v>
       </c>
       <c r="F155" t="s">
-        <v>891</v>
+        <v>764</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>892</v>
+        <v>765</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -13002,25 +13510,25 @@
         <v>127</v>
       </c>
       <c r="B156" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C156" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="D156" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="E156" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="F156" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>900</v>
+        <v>795</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -13028,25 +13536,25 @@
         <v>128</v>
       </c>
       <c r="B157" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C157" t="s">
-        <v>904</v>
+        <v>807</v>
       </c>
       <c r="D157" t="s">
-        <v>585</v>
+        <v>808</v>
       </c>
       <c r="E157" t="s">
-        <v>66</v>
+        <v>810</v>
       </c>
       <c r="F157" t="s">
-        <v>906</v>
+        <v>811</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>907</v>
+        <v>812</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -13054,25 +13562,25 @@
         <v>129</v>
       </c>
       <c r="B158" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C158" t="s">
-        <v>911</v>
+        <v>816</v>
       </c>
       <c r="D158" t="s">
-        <v>585</v>
+        <v>110</v>
       </c>
       <c r="E158" t="s">
         <v>16</v>
       </c>
       <c r="F158" t="s">
-        <v>913</v>
+        <v>818</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>914</v>
+        <v>819</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13083,22 +13591,22 @@
         <v>845</v>
       </c>
       <c r="C159" t="s">
-        <v>918</v>
+        <v>888</v>
       </c>
       <c r="D159" t="s">
-        <v>919</v>
+        <v>889</v>
       </c>
       <c r="E159" t="s">
-        <v>921</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>923</v>
+        <v>892</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13106,25 +13614,25 @@
         <v>131</v>
       </c>
       <c r="B160" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C160" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="D160" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="E160" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="F160" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>969</v>
+        <v>900</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -13132,25 +13640,25 @@
         <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C161" t="s">
-        <v>950</v>
+        <v>904</v>
       </c>
       <c r="D161" t="s">
-        <v>1002</v>
+        <v>585</v>
       </c>
       <c r="E161" t="s">
-        <v>1004</v>
+        <v>66</v>
       </c>
       <c r="F161" t="s">
-        <v>438</v>
+        <v>906</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>1005</v>
+        <v>907</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -13158,25 +13666,25 @@
         <v>133</v>
       </c>
       <c r="B162" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>911</v>
       </c>
       <c r="D162" t="s">
-        <v>1009</v>
+        <v>585</v>
       </c>
       <c r="E162" t="s">
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>1011</v>
+        <v>913</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>1012</v>
+        <v>914</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13184,25 +13692,25 @@
         <v>134</v>
       </c>
       <c r="B163" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C163" t="s">
-        <v>650</v>
+        <v>918</v>
       </c>
       <c r="D163" t="s">
-        <v>1016</v>
+        <v>919</v>
       </c>
       <c r="E163" t="s">
-        <v>66</v>
+        <v>921</v>
       </c>
       <c r="F163" t="s">
-        <v>1018</v>
+        <v>922</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>1019</v>
+        <v>923</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -13213,22 +13721,22 @@
         <v>934</v>
       </c>
       <c r="C164" t="s">
-        <v>1023</v>
+        <v>964</v>
       </c>
       <c r="D164" t="s">
-        <v>1024</v>
+        <v>965</v>
       </c>
       <c r="E164" t="s">
-        <v>1026</v>
+        <v>967</v>
       </c>
       <c r="F164" t="s">
-        <v>1027</v>
+        <v>968</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>1028</v>
+        <v>969</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -13239,22 +13747,22 @@
         <v>934</v>
       </c>
       <c r="C165" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="D165" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="E165" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="F165" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>1035</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -13265,22 +13773,22 @@
         <v>934</v>
       </c>
       <c r="C166" t="s">
-        <v>1039</v>
+        <v>13</v>
       </c>
       <c r="D166" t="s">
-        <v>1040</v>
+        <v>1009</v>
       </c>
       <c r="E166" t="s">
-        <v>1042</v>
+        <v>16</v>
       </c>
       <c r="F166" t="s">
-        <v>1043</v>
+        <v>1011</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>1044</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -13291,22 +13799,22 @@
         <v>934</v>
       </c>
       <c r="C167" t="s">
-        <v>1048</v>
+        <v>650</v>
       </c>
       <c r="D167" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="E167" t="s">
-        <v>1051</v>
+        <v>66</v>
       </c>
       <c r="F167" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>1053</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -13317,22 +13825,22 @@
         <v>934</v>
       </c>
       <c r="C168" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="D168" t="s">
-        <v>1058</v>
+        <v>1024</v>
       </c>
       <c r="E168" t="s">
-        <v>16</v>
+        <v>1026</v>
       </c>
       <c r="F168" t="s">
-        <v>1060</v>
+        <v>1027</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>1061</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -13343,22 +13851,22 @@
         <v>934</v>
       </c>
       <c r="C169" t="s">
-        <v>1082</v>
+        <v>213</v>
       </c>
       <c r="D169" t="s">
-        <v>1083</v>
+        <v>1032</v>
       </c>
       <c r="E169" t="s">
-        <v>1085</v>
+        <v>106</v>
       </c>
       <c r="F169" t="s">
-        <v>959</v>
+        <v>1034</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>1086</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -13366,25 +13874,25 @@
         <v>141</v>
       </c>
       <c r="B170" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="C170" t="s">
-        <v>271</v>
+        <v>1039</v>
       </c>
       <c r="D170" t="s">
-        <v>272</v>
+        <v>1040</v>
       </c>
       <c r="E170" t="s">
-        <v>75</v>
+        <v>1042</v>
       </c>
       <c r="F170" t="s">
-        <v>274</v>
+        <v>1043</v>
       </c>
       <c r="G170">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>275</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -13392,25 +13900,25 @@
         <v>142</v>
       </c>
       <c r="B171" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="C171" t="s">
-        <v>681</v>
+        <v>1048</v>
       </c>
       <c r="D171" t="s">
-        <v>682</v>
+        <v>1049</v>
       </c>
       <c r="E171" t="s">
-        <v>25</v>
+        <v>1051</v>
       </c>
       <c r="F171" t="s">
-        <v>684</v>
+        <v>1052</v>
       </c>
       <c r="G171">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>685</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -13418,25 +13926,25 @@
         <v>143</v>
       </c>
       <c r="B172" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="C172" t="s">
-        <v>689</v>
+        <v>1057</v>
       </c>
       <c r="D172" t="s">
-        <v>690</v>
+        <v>1058</v>
       </c>
       <c r="E172" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F172" t="s">
-        <v>692</v>
+        <v>1060</v>
       </c>
       <c r="G172">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>693</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -13444,25 +13952,25 @@
         <v>144</v>
       </c>
       <c r="B173" t="s">
-        <v>697</v>
+        <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>767</v>
+        <v>1082</v>
       </c>
       <c r="D173" t="s">
-        <v>768</v>
+        <v>1083</v>
       </c>
       <c r="E173" t="s">
-        <v>25</v>
+        <v>1085</v>
       </c>
       <c r="F173" t="s">
-        <v>770</v>
+        <v>959</v>
       </c>
       <c r="G173">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>771</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -13470,24 +13978,232 @@
         <v>145</v>
       </c>
       <c r="B174" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C174" t="s">
+        <v>271</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G174">
+        <v>8</v>
+      </c>
+      <c r="H174" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>146</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E175" t="s">
+        <v>25</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G175">
+        <v>8</v>
+      </c>
+      <c r="H175" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>147</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G176">
+        <v>8</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>148</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G177">
+        <v>8</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>149</v>
+      </c>
+      <c r="B178" t="s">
+        <v>159</v>
+      </c>
+      <c r="C178" t="s">
+        <v>271</v>
+      </c>
+      <c r="D178" t="s">
+        <v>272</v>
+      </c>
+      <c r="E178" t="s">
+        <v>75</v>
+      </c>
+      <c r="F178" t="s">
+        <v>274</v>
+      </c>
+      <c r="G178">
+        <v>7</v>
+      </c>
+      <c r="H178" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>150</v>
+      </c>
+      <c r="B179" t="s">
+        <v>591</v>
+      </c>
+      <c r="C179" t="s">
+        <v>681</v>
+      </c>
+      <c r="D179" t="s">
+        <v>682</v>
+      </c>
+      <c r="E179" t="s">
+        <v>25</v>
+      </c>
+      <c r="F179" t="s">
+        <v>684</v>
+      </c>
+      <c r="G179">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>151</v>
+      </c>
+      <c r="B180" t="s">
+        <v>591</v>
+      </c>
+      <c r="C180" t="s">
+        <v>689</v>
+      </c>
+      <c r="D180" t="s">
+        <v>690</v>
+      </c>
+      <c r="E180" t="s">
+        <v>66</v>
+      </c>
+      <c r="F180" t="s">
+        <v>692</v>
+      </c>
+      <c r="G180">
+        <v>7</v>
+      </c>
+      <c r="H180" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>152</v>
+      </c>
+      <c r="B181" t="s">
+        <v>697</v>
+      </c>
+      <c r="C181" t="s">
+        <v>767</v>
+      </c>
+      <c r="D181" t="s">
+        <v>768</v>
+      </c>
+      <c r="E181" t="s">
+        <v>25</v>
+      </c>
+      <c r="F181" t="s">
+        <v>770</v>
+      </c>
+      <c r="G181">
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>153</v>
+      </c>
+      <c r="B182" t="s">
         <v>845</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C182" t="s">
         <v>927</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D182" t="s">
         <v>585</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E182" t="s">
         <v>25</v>
       </c>
-      <c r="F174" t="s">
+      <c r="F182" t="s">
         <v>929</v>
       </c>
-      <c r="G174">
+      <c r="G182">
         <v>7</v>
       </c>
-      <c r="H174" t="s">
+      <c r="H182" t="s">
         <v>930</v>
       </c>
     </row>
@@ -13504,7 +14220,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -13521,10 +14237,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1095</v>
+        <v>1163</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1096</v>
+        <v>1164</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -13551,12 +14267,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1097</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -13591,7 +14307,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -13626,7 +14342,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -13661,7 +14377,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -13696,7 +14412,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -13731,7 +14447,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -13766,7 +14482,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -13801,7 +14517,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -13836,7 +14552,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -13871,7 +14587,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -13906,7 +14622,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -13941,7 +14657,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -13976,7 +14692,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -14011,7 +14727,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -14046,7 +14762,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -14081,7 +14797,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -14116,7 +14832,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -14151,7 +14867,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -14186,7 +14902,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -14221,7 +14937,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -14256,7 +14972,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -14291,7 +15007,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -14326,252 +15042,252 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B24">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>1138</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>1139</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>1141</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>1143</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>1144</v>
       </c>
       <c r="J24" t="s">
-        <v>143</v>
+        <v>1145</v>
       </c>
       <c r="K24" t="s">
-        <v>137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B25">
         <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="G25" t="s">
-        <v>438</v>
+        <v>139</v>
       </c>
       <c r="H25" t="s">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s">
-        <v>441</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="K25" t="s">
-        <v>437</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B26">
         <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D26" t="s">
-        <v>557</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>564</v>
+        <v>436</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H26" t="s">
-        <v>567</v>
+        <v>440</v>
       </c>
       <c r="I26" t="s">
-        <v>568</v>
+        <v>441</v>
       </c>
       <c r="J26" t="s">
-        <v>569</v>
+        <v>442</v>
       </c>
       <c r="K26" t="s">
-        <v>565</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B27">
         <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D27" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="E27" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="F27" t="s">
-        <v>595</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>596</v>
+        <v>468</v>
       </c>
       <c r="H27" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="I27" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="J27" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="K27" t="s">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B28">
         <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D28" t="s">
-        <v>707</v>
+        <v>592</v>
       </c>
       <c r="E28" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F28" t="s">
-        <v>318</v>
+        <v>595</v>
       </c>
       <c r="G28" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H28" t="s">
-        <v>711</v>
+        <v>598</v>
       </c>
       <c r="I28" t="s">
-        <v>712</v>
+        <v>599</v>
       </c>
       <c r="J28" t="s">
-        <v>713</v>
+        <v>600</v>
       </c>
       <c r="K28" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B29">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D29" t="s">
-        <v>846</v>
+        <v>707</v>
       </c>
       <c r="E29" t="s">
-        <v>847</v>
+        <v>708</v>
       </c>
       <c r="F29" t="s">
-        <v>849</v>
+        <v>318</v>
       </c>
       <c r="G29" t="s">
-        <v>850</v>
+        <v>604</v>
       </c>
       <c r="H29" t="s">
-        <v>852</v>
+        <v>711</v>
       </c>
       <c r="I29" t="s">
-        <v>853</v>
+        <v>712</v>
       </c>
       <c r="J29" t="s">
-        <v>854</v>
+        <v>713</v>
       </c>
       <c r="K29" t="s">
-        <v>848</v>
+        <v>709</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B30">
         <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>846</v>
       </c>
       <c r="E30" t="s">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>849</v>
       </c>
       <c r="G30" t="s">
-        <v>937</v>
+        <v>850</v>
       </c>
       <c r="H30" t="s">
-        <v>939</v>
+        <v>852</v>
       </c>
       <c r="I30" t="s">
-        <v>940</v>
+        <v>853</v>
       </c>
       <c r="J30" t="s">
-        <v>941</v>
+        <v>854</v>
       </c>
       <c r="K30" t="s">
-        <v>936</v>
+        <v>848</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -14580,33 +15296,33 @@
         <v>934</v>
       </c>
       <c r="D31" t="s">
-        <v>942</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G31" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H31" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="I31" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J31" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="K31" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -14615,418 +15331,418 @@
         <v>934</v>
       </c>
       <c r="D32" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="E32" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="F32" t="s">
         <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="H32" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="I32" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="J32" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="K32" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B33">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>950</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>951</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>954</v>
       </c>
       <c r="I33" t="s">
-        <v>37</v>
+        <v>955</v>
       </c>
       <c r="J33" t="s">
-        <v>38</v>
+        <v>956</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>952</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B34">
         <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H34" t="s">
         <v>36</v>
       </c>
       <c r="I34" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J34" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K34" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B35">
         <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D35" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H35" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J35" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K35" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B36">
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E36" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H36" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I36" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K36" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B37">
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D37" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F37" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I37" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B38">
         <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D38" t="s">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="E38" t="s">
-        <v>610</v>
+        <v>699</v>
       </c>
       <c r="F38" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="G38" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="H38" t="s">
-        <v>842</v>
+        <v>704</v>
       </c>
       <c r="I38" t="s">
-        <v>843</v>
+        <v>705</v>
       </c>
       <c r="J38" t="s">
-        <v>844</v>
+        <v>706</v>
       </c>
       <c r="K38" t="s">
-        <v>838</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B39">
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D39" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="E39" t="s">
-        <v>856</v>
+        <v>610</v>
       </c>
       <c r="F39" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="G39" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="H39" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="I39" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="J39" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="K39" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B40">
         <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D40" t="s">
-        <v>643</v>
+        <v>855</v>
       </c>
       <c r="E40" t="s">
-        <v>957</v>
+        <v>856</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>858</v>
       </c>
       <c r="G40" t="s">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="H40" t="s">
-        <v>961</v>
+        <v>861</v>
       </c>
       <c r="I40" t="s">
-        <v>962</v>
+        <v>862</v>
       </c>
       <c r="J40" t="s">
-        <v>963</v>
+        <v>863</v>
       </c>
       <c r="K40" t="s">
-        <v>958</v>
+        <v>857</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B41">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>643</v>
       </c>
       <c r="E41" t="s">
-        <v>185</v>
+        <v>957</v>
       </c>
       <c r="F41" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>959</v>
       </c>
       <c r="H41" t="s">
-        <v>188</v>
+        <v>961</v>
       </c>
       <c r="I41" t="s">
-        <v>189</v>
+        <v>962</v>
       </c>
       <c r="J41" t="s">
-        <v>190</v>
+        <v>963</v>
       </c>
       <c r="K41" t="s">
-        <v>186</v>
+        <v>958</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B42">
         <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E42" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G42" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H42" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I42" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J42" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K42" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B43">
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E43" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G43" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H43" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I43" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K43" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B44">
         <v>87</v>
@@ -15038,7 +15754,7 @@
         <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
@@ -15056,304 +15772,304 @@
         <v>79</v>
       </c>
       <c r="K44" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B45">
         <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F45" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H45" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I45" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B46">
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D46" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E46" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G46" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H46" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I46" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J46" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K46" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B47">
         <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D47" t="s">
-        <v>864</v>
+        <v>570</v>
       </c>
       <c r="E47" t="s">
-        <v>865</v>
+        <v>571</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="H47" t="s">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="I47" t="s">
-        <v>870</v>
+        <v>576</v>
       </c>
       <c r="J47" t="s">
-        <v>871</v>
+        <v>577</v>
       </c>
       <c r="K47" t="s">
-        <v>866</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B48">
         <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D48" t="s">
-        <v>950</v>
+        <v>864</v>
       </c>
       <c r="E48" t="s">
-        <v>996</v>
+        <v>865</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>438</v>
+        <v>867</v>
       </c>
       <c r="H48" t="s">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="I48" t="s">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J48" t="s">
-        <v>1001</v>
+        <v>871</v>
       </c>
       <c r="K48" t="s">
-        <v>997</v>
+        <v>866</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B49">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D49" t="s">
-        <v>369</v>
+        <v>950</v>
       </c>
       <c r="E49" t="s">
-        <v>370</v>
+        <v>996</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G49" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="H49" t="s">
-        <v>374</v>
+        <v>999</v>
       </c>
       <c r="I49" t="s">
-        <v>375</v>
+        <v>1000</v>
       </c>
       <c r="J49" t="s">
-        <v>376</v>
+        <v>1001</v>
       </c>
       <c r="K49" t="s">
-        <v>371</v>
+        <v>997</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B50">
+        <v>87</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D50" t="s">
+        <v>964</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F50" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K50" t="s">
         <v>1098</v>
-      </c>
-      <c r="B50">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>402</v>
-      </c>
-      <c r="D50" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" t="s">
-        <v>457</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G50" t="s">
-        <v>438</v>
-      </c>
-      <c r="H50" t="s">
-        <v>460</v>
-      </c>
-      <c r="I50" t="s">
-        <v>461</v>
-      </c>
-      <c r="J50" t="s">
-        <v>462</v>
-      </c>
-      <c r="K50" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B51">
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D51" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="E51" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="H51" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="I51" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J51" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="K51" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B52">
         <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D52" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="E52" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F52" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="H52" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="I52" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J52" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="K52" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B53">
         <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D53" t="s">
-        <v>557</v>
+        <v>322</v>
       </c>
       <c r="E53" t="s">
-        <v>558</v>
+        <v>466</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -15362,91 +16078,91 @@
         <v>468</v>
       </c>
       <c r="H53" t="s">
-        <v>561</v>
+        <v>470</v>
       </c>
       <c r="I53" t="s">
-        <v>562</v>
+        <v>471</v>
       </c>
       <c r="J53" t="s">
-        <v>563</v>
+        <v>472</v>
       </c>
       <c r="K53" t="s">
-        <v>559</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B54">
         <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D54" t="s">
-        <v>609</v>
+        <v>541</v>
       </c>
       <c r="E54" t="s">
-        <v>610</v>
+        <v>542</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G54" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="H54" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="I54" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="J54" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="K54" t="s">
-        <v>611</v>
+        <v>543</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B55">
         <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D55" t="s">
-        <v>627</v>
+        <v>557</v>
       </c>
       <c r="E55" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="F55" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>630</v>
+        <v>468</v>
       </c>
       <c r="H55" t="s">
-        <v>632</v>
+        <v>561</v>
       </c>
       <c r="I55" t="s">
-        <v>633</v>
+        <v>562</v>
       </c>
       <c r="J55" t="s">
-        <v>634</v>
+        <v>563</v>
       </c>
       <c r="K55" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B56">
         <v>86</v>
@@ -15455,208 +16171,208 @@
         <v>591</v>
       </c>
       <c r="D56" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="E56" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>638</v>
+        <v>604</v>
       </c>
       <c r="H56" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="I56" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="J56" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="K56" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B57">
         <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D57" t="s">
-        <v>829</v>
+        <v>627</v>
       </c>
       <c r="E57" t="s">
-        <v>830</v>
+        <v>628</v>
       </c>
       <c r="F57" t="s">
-        <v>785</v>
+        <v>25</v>
       </c>
       <c r="G57" t="s">
-        <v>832</v>
+        <v>630</v>
       </c>
       <c r="H57" t="s">
-        <v>834</v>
+        <v>632</v>
       </c>
       <c r="I57" t="s">
-        <v>835</v>
+        <v>633</v>
       </c>
       <c r="J57" t="s">
-        <v>836</v>
+        <v>634</v>
       </c>
       <c r="K57" t="s">
-        <v>831</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B58">
         <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D58" t="s">
-        <v>872</v>
+        <v>635</v>
       </c>
       <c r="E58" t="s">
-        <v>873</v>
+        <v>636</v>
       </c>
       <c r="F58" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>875</v>
+        <v>638</v>
       </c>
       <c r="H58" t="s">
-        <v>877</v>
+        <v>640</v>
       </c>
       <c r="I58" t="s">
-        <v>878</v>
+        <v>641</v>
       </c>
       <c r="J58" t="s">
-        <v>879</v>
+        <v>642</v>
       </c>
       <c r="K58" t="s">
-        <v>874</v>
+        <v>637</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B59">
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D59" t="s">
-        <v>880</v>
+        <v>829</v>
       </c>
       <c r="E59" t="s">
-        <v>881</v>
+        <v>830</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>785</v>
       </c>
       <c r="G59" t="s">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="H59" t="s">
-        <v>885</v>
+        <v>834</v>
       </c>
       <c r="I59" t="s">
-        <v>886</v>
+        <v>835</v>
       </c>
       <c r="J59" t="s">
-        <v>887</v>
+        <v>836</v>
       </c>
       <c r="K59" t="s">
-        <v>882</v>
+        <v>831</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B60">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D60" t="s">
-        <v>973</v>
+        <v>872</v>
       </c>
       <c r="E60" t="s">
-        <v>974</v>
+        <v>873</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G60" t="s">
-        <v>468</v>
+        <v>875</v>
       </c>
       <c r="H60" t="s">
-        <v>977</v>
+        <v>877</v>
       </c>
       <c r="I60" t="s">
-        <v>978</v>
+        <v>878</v>
       </c>
       <c r="J60" t="s">
-        <v>979</v>
+        <v>879</v>
       </c>
       <c r="K60" t="s">
-        <v>975</v>
+        <v>874</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B61">
         <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D61" t="s">
-        <v>980</v>
+        <v>880</v>
       </c>
       <c r="E61" t="s">
-        <v>981</v>
+        <v>881</v>
       </c>
       <c r="F61" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>984</v>
+        <v>883</v>
       </c>
       <c r="H61" t="s">
-        <v>986</v>
+        <v>885</v>
       </c>
       <c r="I61" t="s">
-        <v>987</v>
+        <v>886</v>
       </c>
       <c r="J61" t="s">
-        <v>988</v>
+        <v>887</v>
       </c>
       <c r="K61" t="s">
-        <v>982</v>
+        <v>882</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -15665,1532 +16381,1777 @@
         <v>934</v>
       </c>
       <c r="D62" t="s">
-        <v>1073</v>
+        <v>973</v>
       </c>
       <c r="E62" t="s">
-        <v>1074</v>
+        <v>974</v>
       </c>
       <c r="F62" t="s">
-        <v>1076</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>1077</v>
+        <v>468</v>
       </c>
       <c r="H62" t="s">
-        <v>1079</v>
+        <v>977</v>
       </c>
       <c r="I62" t="s">
-        <v>1080</v>
+        <v>978</v>
       </c>
       <c r="J62" t="s">
-        <v>1081</v>
+        <v>979</v>
       </c>
       <c r="K62" t="s">
-        <v>1075</v>
+        <v>975</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B63">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D63" t="s">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="E63" t="s">
-        <v>56</v>
+        <v>981</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>983</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>984</v>
       </c>
       <c r="H63" t="s">
-        <v>60</v>
+        <v>986</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>987</v>
       </c>
       <c r="J63" t="s">
-        <v>62</v>
+        <v>988</v>
       </c>
       <c r="K63" t="s">
-        <v>57</v>
+        <v>982</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B64">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>1073</v>
       </c>
       <c r="E64" t="s">
-        <v>89</v>
+        <v>1074</v>
       </c>
       <c r="F64" t="s">
-        <v>130</v>
+        <v>1076</v>
       </c>
       <c r="G64" t="s">
-        <v>131</v>
+        <v>1077</v>
       </c>
       <c r="H64" t="s">
-        <v>133</v>
+        <v>1079</v>
       </c>
       <c r="I64" t="s">
-        <v>134</v>
+        <v>1080</v>
       </c>
       <c r="J64" t="s">
-        <v>135</v>
+        <v>1081</v>
       </c>
       <c r="K64" t="s">
-        <v>129</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B65">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>284</v>
+        <v>1087</v>
       </c>
       <c r="D65" t="s">
-        <v>300</v>
+        <v>1088</v>
       </c>
       <c r="E65" t="s">
-        <v>308</v>
+        <v>1089</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>1091</v>
       </c>
       <c r="G65" t="s">
-        <v>310</v>
+        <v>1092</v>
       </c>
       <c r="H65" t="s">
-        <v>312</v>
+        <v>1094</v>
       </c>
       <c r="I65" t="s">
-        <v>313</v>
+        <v>1095</v>
       </c>
       <c r="J65" t="s">
-        <v>314</v>
+        <v>1096</v>
       </c>
       <c r="K65" t="s">
-        <v>309</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B66">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>402</v>
+        <v>1087</v>
       </c>
       <c r="D66" t="s">
-        <v>55</v>
+        <v>1146</v>
       </c>
       <c r="E66" t="s">
-        <v>403</v>
+        <v>1147</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G66" t="s">
-        <v>405</v>
+        <v>1150</v>
       </c>
       <c r="H66" t="s">
-        <v>407</v>
+        <v>1152</v>
       </c>
       <c r="I66" t="s">
-        <v>408</v>
+        <v>1153</v>
       </c>
       <c r="J66" t="s">
-        <v>409</v>
+        <v>1154</v>
       </c>
       <c r="K66" t="s">
-        <v>404</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B67">
         <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E67" t="s">
-        <v>475</v>
+        <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>478</v>
+        <v>58</v>
       </c>
       <c r="H67" t="s">
-        <v>480</v>
+        <v>60</v>
       </c>
       <c r="I67" t="s">
-        <v>481</v>
+        <v>61</v>
       </c>
       <c r="J67" t="s">
-        <v>482</v>
+        <v>62</v>
       </c>
       <c r="K67" t="s">
-        <v>476</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B68">
         <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>773</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>774</v>
+        <v>128</v>
       </c>
       <c r="E68" t="s">
-        <v>783</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
-        <v>785</v>
+        <v>130</v>
       </c>
       <c r="G68" t="s">
-        <v>786</v>
+        <v>131</v>
       </c>
       <c r="H68" t="s">
-        <v>788</v>
+        <v>133</v>
       </c>
       <c r="I68" t="s">
-        <v>789</v>
+        <v>134</v>
       </c>
       <c r="J68" t="s">
-        <v>790</v>
+        <v>135</v>
       </c>
       <c r="K68" t="s">
-        <v>784</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B69">
         <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>773</v>
+        <v>284</v>
       </c>
       <c r="D69" t="s">
-        <v>799</v>
+        <v>300</v>
       </c>
       <c r="E69" t="s">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="F69" t="s">
-        <v>793</v>
+        <v>147</v>
       </c>
       <c r="G69" t="s">
-        <v>802</v>
+        <v>310</v>
       </c>
       <c r="H69" t="s">
-        <v>804</v>
+        <v>312</v>
       </c>
       <c r="I69" t="s">
-        <v>805</v>
+        <v>313</v>
       </c>
       <c r="J69" t="s">
-        <v>806</v>
+        <v>314</v>
       </c>
       <c r="K69" t="s">
-        <v>801</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B70">
         <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D70" t="s">
-        <v>821</v>
+        <v>55</v>
       </c>
       <c r="E70" t="s">
-        <v>822</v>
+        <v>403</v>
       </c>
       <c r="F70" t="s">
-        <v>777</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>824</v>
+        <v>405</v>
       </c>
       <c r="H70" t="s">
-        <v>826</v>
+        <v>407</v>
       </c>
       <c r="I70" t="s">
-        <v>827</v>
+        <v>408</v>
       </c>
       <c r="J70" t="s">
-        <v>828</v>
+        <v>409</v>
       </c>
       <c r="K70" t="s">
-        <v>823</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B71">
         <v>85</v>
       </c>
       <c r="C71" t="s">
-        <v>934</v>
+        <v>473</v>
       </c>
       <c r="D71" t="s">
-        <v>989</v>
+        <v>474</v>
       </c>
       <c r="E71" t="s">
-        <v>990</v>
+        <v>475</v>
       </c>
       <c r="F71" t="s">
-        <v>75</v>
+        <v>477</v>
       </c>
       <c r="G71" t="s">
-        <v>959</v>
+        <v>478</v>
       </c>
       <c r="H71" t="s">
-        <v>993</v>
+        <v>480</v>
       </c>
       <c r="I71" t="s">
-        <v>994</v>
+        <v>481</v>
       </c>
       <c r="J71" t="s">
-        <v>995</v>
+        <v>482</v>
       </c>
       <c r="K71" t="s">
-        <v>991</v>
+        <v>476</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B72">
         <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D72" t="s">
-        <v>1065</v>
+        <v>774</v>
       </c>
       <c r="E72" t="s">
-        <v>1066</v>
+        <v>783</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>785</v>
       </c>
       <c r="G72" t="s">
-        <v>1068</v>
+        <v>786</v>
       </c>
       <c r="H72" t="s">
-        <v>1070</v>
+        <v>788</v>
       </c>
       <c r="I72" t="s">
-        <v>1071</v>
+        <v>789</v>
       </c>
       <c r="J72" t="s">
-        <v>1072</v>
+        <v>790</v>
       </c>
       <c r="K72" t="s">
-        <v>1067</v>
+        <v>784</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B73">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>773</v>
       </c>
       <c r="D73" t="s">
-        <v>144</v>
+        <v>799</v>
       </c>
       <c r="E73" t="s">
-        <v>145</v>
+        <v>800</v>
       </c>
       <c r="F73" t="s">
-        <v>147</v>
+        <v>793</v>
       </c>
       <c r="G73" t="s">
-        <v>148</v>
+        <v>802</v>
       </c>
       <c r="H73" t="s">
-        <v>150</v>
+        <v>804</v>
       </c>
       <c r="I73" t="s">
-        <v>151</v>
+        <v>805</v>
       </c>
       <c r="J73" t="s">
-        <v>152</v>
+        <v>806</v>
       </c>
       <c r="K73" t="s">
-        <v>146</v>
+        <v>801</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B74">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D74" t="s">
-        <v>144</v>
+        <v>821</v>
       </c>
       <c r="E74" t="s">
-        <v>394</v>
+        <v>822</v>
       </c>
       <c r="F74" t="s">
-        <v>396</v>
+        <v>777</v>
       </c>
       <c r="G74" t="s">
-        <v>397</v>
+        <v>824</v>
       </c>
       <c r="H74" t="s">
-        <v>399</v>
+        <v>826</v>
       </c>
       <c r="I74" t="s">
-        <v>400</v>
+        <v>827</v>
       </c>
       <c r="J74" t="s">
-        <v>401</v>
+        <v>828</v>
       </c>
       <c r="K74" t="s">
-        <v>395</v>
+        <v>823</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B75">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>402</v>
+        <v>934</v>
       </c>
       <c r="D75" t="s">
-        <v>410</v>
+        <v>989</v>
       </c>
       <c r="E75" t="s">
-        <v>411</v>
+        <v>990</v>
       </c>
       <c r="F75" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s">
-        <v>413</v>
+        <v>959</v>
       </c>
       <c r="H75" t="s">
-        <v>415</v>
+        <v>993</v>
       </c>
       <c r="I75" t="s">
-        <v>416</v>
+        <v>994</v>
       </c>
       <c r="J75" t="s">
-        <v>417</v>
+        <v>995</v>
       </c>
       <c r="K75" t="s">
-        <v>412</v>
+        <v>991</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B76">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>473</v>
+        <v>934</v>
       </c>
       <c r="D76" t="s">
-        <v>483</v>
+        <v>1065</v>
       </c>
       <c r="E76" t="s">
-        <v>122</v>
+        <v>1066</v>
       </c>
       <c r="F76" t="s">
-        <v>485</v>
+        <v>147</v>
       </c>
       <c r="G76" t="s">
-        <v>486</v>
+        <v>1068</v>
       </c>
       <c r="H76" t="s">
-        <v>488</v>
+        <v>1070</v>
       </c>
       <c r="I76" t="s">
-        <v>489</v>
+        <v>1071</v>
       </c>
       <c r="J76" t="s">
-        <v>490</v>
+        <v>1072</v>
       </c>
       <c r="K76" t="s">
-        <v>484</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B77">
         <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>697</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>714</v>
+        <v>144</v>
       </c>
       <c r="E77" t="s">
-        <v>715</v>
+        <v>145</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G77" t="s">
-        <v>604</v>
+        <v>148</v>
       </c>
       <c r="H77" t="s">
-        <v>718</v>
+        <v>150</v>
       </c>
       <c r="I77" t="s">
-        <v>719</v>
+        <v>151</v>
       </c>
       <c r="J77" t="s">
-        <v>720</v>
+        <v>152</v>
       </c>
       <c r="K77" t="s">
-        <v>716</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B78">
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>697</v>
+        <v>284</v>
       </c>
       <c r="D78" t="s">
-        <v>721</v>
+        <v>144</v>
       </c>
       <c r="E78" t="s">
-        <v>722</v>
+        <v>394</v>
       </c>
       <c r="F78" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="G78" t="s">
-        <v>724</v>
+        <v>397</v>
       </c>
       <c r="H78" t="s">
-        <v>726</v>
+        <v>399</v>
       </c>
       <c r="I78" t="s">
-        <v>727</v>
+        <v>400</v>
       </c>
       <c r="J78" t="s">
-        <v>728</v>
+        <v>401</v>
       </c>
       <c r="K78" t="s">
-        <v>723</v>
+        <v>395</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B79">
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D79" t="s">
-        <v>729</v>
+        <v>410</v>
       </c>
       <c r="E79" t="s">
-        <v>730</v>
+        <v>411</v>
       </c>
       <c r="F79" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="G79" t="s">
-        <v>732</v>
+        <v>413</v>
       </c>
       <c r="H79" t="s">
-        <v>726</v>
+        <v>415</v>
       </c>
       <c r="I79" t="s">
-        <v>734</v>
+        <v>416</v>
       </c>
       <c r="J79" t="s">
-        <v>735</v>
+        <v>417</v>
       </c>
       <c r="K79" t="s">
-        <v>731</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B80">
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D80" t="s">
-        <v>791</v>
+        <v>483</v>
       </c>
       <c r="E80" t="s">
-        <v>610</v>
+        <v>122</v>
       </c>
       <c r="F80" t="s">
-        <v>793</v>
+        <v>485</v>
       </c>
       <c r="G80" t="s">
-        <v>794</v>
+        <v>486</v>
       </c>
       <c r="H80" t="s">
-        <v>796</v>
+        <v>488</v>
       </c>
       <c r="I80" t="s">
-        <v>797</v>
+        <v>489</v>
       </c>
       <c r="J80" t="s">
-        <v>798</v>
+        <v>490</v>
       </c>
       <c r="K80" t="s">
-        <v>792</v>
+        <v>484</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B81">
         <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D81" t="s">
-        <v>896</v>
+        <v>714</v>
       </c>
       <c r="E81" t="s">
-        <v>897</v>
+        <v>715</v>
       </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>899</v>
+        <v>604</v>
       </c>
       <c r="H81" t="s">
-        <v>901</v>
+        <v>718</v>
       </c>
       <c r="I81" t="s">
-        <v>902</v>
+        <v>719</v>
       </c>
       <c r="J81" t="s">
-        <v>903</v>
+        <v>720</v>
       </c>
       <c r="K81" t="s">
-        <v>898</v>
+        <v>716</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B82">
         <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D82" t="s">
-        <v>964</v>
+        <v>721</v>
       </c>
       <c r="E82" t="s">
-        <v>965</v>
+        <v>722</v>
       </c>
       <c r="F82" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G82" t="s">
-        <v>968</v>
+        <v>724</v>
       </c>
       <c r="H82" t="s">
-        <v>970</v>
+        <v>726</v>
       </c>
       <c r="I82" t="s">
-        <v>971</v>
+        <v>727</v>
       </c>
       <c r="J82" t="s">
-        <v>972</v>
+        <v>728</v>
       </c>
       <c r="K82" t="s">
-        <v>966</v>
+        <v>723</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B83">
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D83" t="s">
-        <v>950</v>
+        <v>729</v>
       </c>
       <c r="E83" t="s">
-        <v>1002</v>
+        <v>730</v>
       </c>
       <c r="F83" t="s">
-        <v>1004</v>
+        <v>535</v>
       </c>
       <c r="G83" t="s">
-        <v>438</v>
+        <v>732</v>
       </c>
       <c r="H83" t="s">
-        <v>1006</v>
+        <v>726</v>
       </c>
       <c r="I83" t="s">
-        <v>1007</v>
+        <v>734</v>
       </c>
       <c r="J83" t="s">
-        <v>1008</v>
+        <v>735</v>
       </c>
       <c r="K83" t="s">
-        <v>1003</v>
+        <v>731</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B84">
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D84" t="s">
-        <v>213</v>
+        <v>791</v>
       </c>
       <c r="E84" t="s">
-        <v>1032</v>
+        <v>610</v>
       </c>
       <c r="F84" t="s">
-        <v>106</v>
+        <v>793</v>
       </c>
       <c r="G84" t="s">
-        <v>1034</v>
+        <v>794</v>
       </c>
       <c r="H84" t="s">
-        <v>1036</v>
+        <v>796</v>
       </c>
       <c r="I84" t="s">
-        <v>1037</v>
+        <v>797</v>
       </c>
       <c r="J84" t="s">
-        <v>1038</v>
+        <v>798</v>
       </c>
       <c r="K84" t="s">
-        <v>1033</v>
+        <v>792</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D85" t="s">
-        <v>1057</v>
+        <v>896</v>
       </c>
       <c r="E85" t="s">
-        <v>1058</v>
+        <v>897</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
-        <v>1060</v>
+        <v>899</v>
       </c>
       <c r="H85" t="s">
-        <v>1062</v>
+        <v>901</v>
       </c>
       <c r="I85" t="s">
-        <v>1063</v>
+        <v>902</v>
       </c>
       <c r="J85" t="s">
-        <v>1064</v>
+        <v>903</v>
       </c>
       <c r="K85" t="s">
-        <v>1059</v>
+        <v>898</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B86">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>964</v>
       </c>
       <c r="E86" t="s">
-        <v>362</v>
+        <v>965</v>
       </c>
       <c r="F86" t="s">
-        <v>356</v>
+        <v>967</v>
       </c>
       <c r="G86" t="s">
-        <v>364</v>
+        <v>968</v>
       </c>
       <c r="H86" t="s">
-        <v>366</v>
+        <v>970</v>
       </c>
       <c r="I86" t="s">
-        <v>367</v>
+        <v>971</v>
       </c>
       <c r="J86" t="s">
-        <v>368</v>
+        <v>972</v>
       </c>
       <c r="K86" t="s">
-        <v>363</v>
+        <v>966</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B87">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>473</v>
+        <v>934</v>
       </c>
       <c r="D87" t="s">
-        <v>491</v>
+        <v>950</v>
       </c>
       <c r="E87" t="s">
-        <v>492</v>
+        <v>1002</v>
       </c>
       <c r="F87" t="s">
-        <v>75</v>
+        <v>1004</v>
       </c>
       <c r="G87" t="s">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="H87" t="s">
-        <v>496</v>
+        <v>1006</v>
       </c>
       <c r="I87" t="s">
-        <v>497</v>
+        <v>1007</v>
       </c>
       <c r="J87" t="s">
-        <v>498</v>
+        <v>1008</v>
       </c>
       <c r="K87" t="s">
-        <v>493</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B88">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>473</v>
+        <v>934</v>
       </c>
       <c r="D88" t="s">
-        <v>532</v>
+        <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>533</v>
+        <v>1032</v>
       </c>
       <c r="F88" t="s">
-        <v>535</v>
+        <v>106</v>
       </c>
       <c r="G88" t="s">
-        <v>536</v>
+        <v>1034</v>
       </c>
       <c r="H88" t="s">
-        <v>538</v>
+        <v>1036</v>
       </c>
       <c r="I88" t="s">
-        <v>539</v>
+        <v>1037</v>
       </c>
       <c r="J88" t="s">
-        <v>540</v>
+        <v>1038</v>
       </c>
       <c r="K88" t="s">
-        <v>534</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B89">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="D89" t="s">
-        <v>643</v>
+        <v>1057</v>
       </c>
       <c r="E89" t="s">
-        <v>644</v>
+        <v>1058</v>
       </c>
       <c r="F89" t="s">
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>618</v>
+        <v>1060</v>
       </c>
       <c r="H89" t="s">
-        <v>647</v>
+        <v>1062</v>
       </c>
       <c r="I89" t="s">
-        <v>648</v>
+        <v>1063</v>
       </c>
       <c r="J89" t="s">
-        <v>649</v>
+        <v>1064</v>
       </c>
       <c r="K89" t="s">
-        <v>645</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B90">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>697</v>
+        <v>1087</v>
       </c>
       <c r="D90" t="s">
-        <v>736</v>
+        <v>271</v>
       </c>
       <c r="E90" t="s">
-        <v>737</v>
+        <v>1104</v>
       </c>
       <c r="F90" t="s">
-        <v>739</v>
+        <v>1106</v>
       </c>
       <c r="G90" t="s">
-        <v>604</v>
+        <v>1107</v>
       </c>
       <c r="H90" t="s">
-        <v>741</v>
+        <v>1109</v>
       </c>
       <c r="I90" t="s">
-        <v>742</v>
+        <v>1110</v>
       </c>
       <c r="J90" t="s">
-        <v>743</v>
+        <v>1111</v>
       </c>
       <c r="K90" t="s">
-        <v>738</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B91">
         <v>83</v>
       </c>
       <c r="C91" t="s">
-        <v>773</v>
+        <v>284</v>
       </c>
       <c r="D91" t="s">
-        <v>807</v>
+        <v>353</v>
       </c>
       <c r="E91" t="s">
-        <v>808</v>
+        <v>362</v>
       </c>
       <c r="F91" t="s">
-        <v>810</v>
+        <v>356</v>
       </c>
       <c r="G91" t="s">
-        <v>811</v>
+        <v>364</v>
       </c>
       <c r="H91" t="s">
-        <v>813</v>
+        <v>366</v>
       </c>
       <c r="I91" t="s">
-        <v>814</v>
+        <v>367</v>
       </c>
       <c r="J91" t="s">
-        <v>815</v>
+        <v>368</v>
       </c>
       <c r="K91" t="s">
-        <v>809</v>
+        <v>363</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B92">
         <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>934</v>
+        <v>473</v>
       </c>
       <c r="D92" t="s">
-        <v>650</v>
+        <v>491</v>
       </c>
       <c r="E92" t="s">
-        <v>1016</v>
+        <v>492</v>
       </c>
       <c r="F92" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G92" t="s">
-        <v>1018</v>
+        <v>494</v>
       </c>
       <c r="H92" t="s">
-        <v>1020</v>
+        <v>496</v>
       </c>
       <c r="I92" t="s">
-        <v>1021</v>
+        <v>497</v>
       </c>
       <c r="J92" t="s">
-        <v>1022</v>
+        <v>498</v>
       </c>
       <c r="K92" t="s">
-        <v>1017</v>
+        <v>493</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B93">
         <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>934</v>
+        <v>473</v>
       </c>
       <c r="D93" t="s">
-        <v>1048</v>
+        <v>532</v>
       </c>
       <c r="E93" t="s">
-        <v>1049</v>
+        <v>533</v>
       </c>
       <c r="F93" t="s">
-        <v>1051</v>
+        <v>535</v>
       </c>
       <c r="G93" t="s">
-        <v>1052</v>
+        <v>536</v>
       </c>
       <c r="H93" t="s">
-        <v>1054</v>
+        <v>538</v>
       </c>
       <c r="I93" t="s">
-        <v>1055</v>
+        <v>539</v>
       </c>
       <c r="J93" t="s">
-        <v>1056</v>
+        <v>540</v>
       </c>
       <c r="K93" t="s">
-        <v>1050</v>
+        <v>534</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B94">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C94" t="s">
-        <v>159</v>
+        <v>591</v>
       </c>
       <c r="D94" t="s">
-        <v>227</v>
+        <v>643</v>
       </c>
       <c r="E94" t="s">
-        <v>228</v>
+        <v>644</v>
       </c>
       <c r="F94" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>231</v>
+        <v>618</v>
       </c>
       <c r="H94" t="s">
-        <v>233</v>
+        <v>647</v>
       </c>
       <c r="I94" t="s">
-        <v>234</v>
+        <v>648</v>
       </c>
       <c r="J94" t="s">
-        <v>235</v>
+        <v>649</v>
       </c>
       <c r="K94" t="s">
-        <v>229</v>
+        <v>645</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B95">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="D95" t="s">
-        <v>266</v>
+        <v>736</v>
       </c>
       <c r="E95" t="s">
-        <v>267</v>
+        <v>737</v>
       </c>
       <c r="F95" t="s">
-        <v>16</v>
+        <v>739</v>
       </c>
       <c r="G95" t="s">
-        <v>58</v>
+        <v>604</v>
       </c>
       <c r="H95" t="s">
-        <v>270</v>
+        <v>741</v>
       </c>
       <c r="I95" t="s">
-        <v>79</v>
+        <v>742</v>
       </c>
       <c r="J95" t="s">
-        <v>79</v>
+        <v>743</v>
       </c>
       <c r="K95" t="s">
-        <v>268</v>
+        <v>738</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B96">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>284</v>
+        <v>773</v>
       </c>
       <c r="D96" t="s">
-        <v>338</v>
+        <v>807</v>
       </c>
       <c r="E96" t="s">
-        <v>339</v>
+        <v>808</v>
       </c>
       <c r="F96" t="s">
-        <v>341</v>
+        <v>810</v>
       </c>
       <c r="G96" t="s">
-        <v>342</v>
+        <v>811</v>
       </c>
       <c r="H96" t="s">
-        <v>344</v>
+        <v>813</v>
       </c>
       <c r="I96" t="s">
-        <v>345</v>
+        <v>814</v>
       </c>
       <c r="J96" t="s">
-        <v>346</v>
+        <v>815</v>
       </c>
       <c r="K96" t="s">
-        <v>340</v>
+        <v>809</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B97">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="D97" t="s">
-        <v>601</v>
+        <v>650</v>
       </c>
       <c r="E97" t="s">
-        <v>602</v>
+        <v>1016</v>
       </c>
       <c r="F97" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G97" t="s">
-        <v>604</v>
+        <v>1018</v>
       </c>
       <c r="H97" t="s">
-        <v>606</v>
+        <v>1020</v>
       </c>
       <c r="I97" t="s">
-        <v>607</v>
+        <v>1021</v>
       </c>
       <c r="J97" t="s">
-        <v>608</v>
+        <v>1022</v>
       </c>
       <c r="K97" t="s">
-        <v>603</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B98">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C98" t="s">
         <v>934</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
+        <v>1048</v>
       </c>
       <c r="E98" t="s">
-        <v>1009</v>
+        <v>1049</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="G98" t="s">
-        <v>1011</v>
+        <v>1052</v>
       </c>
       <c r="H98" t="s">
-        <v>1013</v>
+        <v>1054</v>
       </c>
       <c r="I98" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="J98" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="K98" t="s">
-        <v>1010</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B99">
         <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D99" t="s">
-        <v>1023</v>
+        <v>227</v>
       </c>
       <c r="E99" t="s">
-        <v>1024</v>
+        <v>228</v>
       </c>
       <c r="F99" t="s">
-        <v>1026</v>
+        <v>230</v>
       </c>
       <c r="G99" t="s">
-        <v>1027</v>
+        <v>231</v>
       </c>
       <c r="H99" t="s">
-        <v>1029</v>
+        <v>233</v>
       </c>
       <c r="I99" t="s">
-        <v>1030</v>
+        <v>234</v>
       </c>
       <c r="J99" t="s">
-        <v>1031</v>
+        <v>235</v>
       </c>
       <c r="K99" t="s">
-        <v>1025</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B100">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E100" t="s">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="F100" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="H100" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="I100" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J100" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K100" t="s">
-        <v>82</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B101">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C101" t="s">
         <v>284</v>
       </c>
       <c r="D101" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E101" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="F101" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="G101" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="H101" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="I101" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="J101" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="K101" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B102">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>473</v>
+        <v>591</v>
       </c>
       <c r="D102" t="s">
-        <v>499</v>
+        <v>601</v>
       </c>
       <c r="E102" t="s">
-        <v>500</v>
+        <v>602</v>
       </c>
       <c r="F102" t="s">
-        <v>502</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="H102" t="s">
-        <v>505</v>
+        <v>606</v>
       </c>
       <c r="I102" t="s">
-        <v>506</v>
+        <v>607</v>
       </c>
       <c r="J102" t="s">
-        <v>507</v>
+        <v>608</v>
       </c>
       <c r="K102" t="s">
-        <v>501</v>
+        <v>603</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B103">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C103" t="s">
-        <v>591</v>
+        <v>934</v>
       </c>
       <c r="D103" t="s">
-        <v>616</v>
+        <v>13</v>
       </c>
       <c r="E103" t="s">
-        <v>610</v>
+        <v>1009</v>
       </c>
       <c r="F103" t="s">
         <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>618</v>
+        <v>1011</v>
       </c>
       <c r="H103" t="s">
-        <v>620</v>
+        <v>1013</v>
       </c>
       <c r="I103" t="s">
-        <v>621</v>
+        <v>1014</v>
       </c>
       <c r="J103" t="s">
-        <v>622</v>
+        <v>1015</v>
       </c>
       <c r="K103" t="s">
-        <v>617</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B104">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>845</v>
+        <v>934</v>
       </c>
       <c r="D104" t="s">
-        <v>888</v>
+        <v>1023</v>
       </c>
       <c r="E104" t="s">
-        <v>889</v>
+        <v>1024</v>
       </c>
       <c r="F104" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G104" t="s">
-        <v>891</v>
+        <v>1027</v>
       </c>
       <c r="H104" t="s">
-        <v>893</v>
+        <v>1029</v>
       </c>
       <c r="I104" t="s">
-        <v>894</v>
+        <v>1030</v>
       </c>
       <c r="J104" t="s">
-        <v>895</v>
+        <v>1031</v>
       </c>
       <c r="K104" t="s">
-        <v>890</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1098</v>
+        <v>1166</v>
       </c>
       <c r="B105">
+        <v>82</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F105" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K105" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B106">
+        <v>81</v>
+      </c>
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
         <v>80</v>
       </c>
-      <c r="C105" t="s">
+      <c r="E106" t="s">
+        <v>81</v>
+      </c>
+      <c r="F106" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" t="s">
+        <v>83</v>
+      </c>
+      <c r="H106" t="s">
+        <v>85</v>
+      </c>
+      <c r="I106" t="s">
+        <v>86</v>
+      </c>
+      <c r="J106" t="s">
+        <v>87</v>
+      </c>
+      <c r="K106" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B107">
+        <v>81</v>
+      </c>
+      <c r="C107" t="s">
+        <v>284</v>
+      </c>
+      <c r="D107" t="s">
+        <v>377</v>
+      </c>
+      <c r="E107" t="s">
+        <v>378</v>
+      </c>
+      <c r="F107" t="s">
+        <v>380</v>
+      </c>
+      <c r="G107" t="s">
+        <v>381</v>
+      </c>
+      <c r="H107" t="s">
+        <v>383</v>
+      </c>
+      <c r="I107" t="s">
+        <v>384</v>
+      </c>
+      <c r="J107" t="s">
+        <v>385</v>
+      </c>
+      <c r="K107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B108">
+        <v>81</v>
+      </c>
+      <c r="C108" t="s">
+        <v>473</v>
+      </c>
+      <c r="D108" t="s">
+        <v>499</v>
+      </c>
+      <c r="E108" t="s">
+        <v>500</v>
+      </c>
+      <c r="F108" t="s">
+        <v>502</v>
+      </c>
+      <c r="G108" t="s">
+        <v>503</v>
+      </c>
+      <c r="H108" t="s">
+        <v>505</v>
+      </c>
+      <c r="I108" t="s">
+        <v>506</v>
+      </c>
+      <c r="J108" t="s">
+        <v>507</v>
+      </c>
+      <c r="K108" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B109">
+        <v>81</v>
+      </c>
+      <c r="C109" t="s">
+        <v>591</v>
+      </c>
+      <c r="D109" t="s">
+        <v>616</v>
+      </c>
+      <c r="E109" t="s">
+        <v>610</v>
+      </c>
+      <c r="F109" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>618</v>
+      </c>
+      <c r="H109" t="s">
+        <v>620</v>
+      </c>
+      <c r="I109" t="s">
+        <v>621</v>
+      </c>
+      <c r="J109" t="s">
+        <v>622</v>
+      </c>
+      <c r="K109" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B110">
+        <v>81</v>
+      </c>
+      <c r="C110" t="s">
+        <v>845</v>
+      </c>
+      <c r="D110" t="s">
+        <v>888</v>
+      </c>
+      <c r="E110" t="s">
+        <v>889</v>
+      </c>
+      <c r="F110" t="s">
+        <v>25</v>
+      </c>
+      <c r="G110" t="s">
+        <v>891</v>
+      </c>
+      <c r="H110" t="s">
+        <v>893</v>
+      </c>
+      <c r="I110" t="s">
+        <v>894</v>
+      </c>
+      <c r="J110" t="s">
+        <v>895</v>
+      </c>
+      <c r="K110" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B111">
+        <v>81</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H111" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I111" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J111" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K111" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B112">
+        <v>80</v>
+      </c>
+      <c r="C112" t="s">
         <v>934</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D112" t="s">
         <v>1039</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E112" t="s">
         <v>1040</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F112" t="s">
         <v>1042</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G112" t="s">
         <v>1043</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H112" t="s">
         <v>1045</v>
       </c>
-      <c r="I105" t="s">
+      <c r="I112" t="s">
         <v>1046</v>
       </c>
-      <c r="J105" t="s">
+      <c r="J112" t="s">
         <v>1047</v>
       </c>
-      <c r="K105" t="s">
+      <c r="K112" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="1211">
   <si>
     <t>日期</t>
   </si>
@@ -3479,6 +3479,54 @@
   </si>
   <si>
     <t>突出生物医学工程硕士背景、血管支架研究课题与产品测试能力；强调文献检索与规范性（三类器械、注册测试）；作为应届要把校招/应届身份与研发项目成果放在醒目位置。</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>杭州亿科医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（血管支架/导管/球囊）</t>
+  </si>
+  <si>
+    <t>负责植入介入类医疗器械（侧重血管支架、导管或球囊）新品开发全流程；原型制作、设计验证、过程确认、风险分析、编制风险管理报告；遵循ISO13485；需熟悉记忆合金及高分子材料特性与应用。本科及以上机械/材料等工程专业，1-3年植入介入开发经验，熟悉血管支架/导管/球囊者优先。</t>
+  </si>
+  <si>
+    <t>https://www.yzp.cn/job/121417.html</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招】|强烈推荐|血管支架/导管/球囊研发直接相关，材料学（记忆合金/高分子）匹配</t>
+  </si>
+  <si>
+    <t>研究90/技能78/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>杭州亿科专注神经介入及泛血管介入器械，岗位明确做血管支架/导管/球囊的植入介入类产品开发，与硕士血管支架研究方向高度对口；任职要求强调记忆合金与高分子材料特性，正是本人材料学强项，且负责设计验证、风险分析、ISO13485合规，能充分发挥生物医学工程+材料学综合能力。</t>
+  </si>
+  <si>
+    <t>突出血管支架结构设计与材料（镍钛/高分子金属）研究课题，量化原型制作与设计验证数据；单列ISO13485及设计开发流程认知；补充生物相容性评价与风险分析经验，体现从设计到验证的全流程能力。</t>
+  </si>
+  <si>
+    <t>上海融脉医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>三类植介入医疗器械（支架/血管内栓塞、减容及修复类产品）研发；结合材料与机械设计。公司成立于2019年，聚焦血管内栓塞、减容及修复类产品，研发中心位于上海张江科学城，制造基地在临港，创始团队具十余年三类植介入器械研发商业化经验。</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com/job_detail/4aacfe2ca6a186001nR83du4EVNY.html</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|支架研发岗，血管内栓塞/支架方向直接相关，材料+设计技能匹配，上海科创平台</t>
+  </si>
+  <si>
+    <t>研究90/技能75/学历90/行业100/企业85</t>
+  </si>
+  <si>
+    <t>上海融脉专注三类介入器械（血管内栓塞、支架、减容修复），支架研发工程师岗与硕士血管支架研究方向直接对口；上海符合城市偏好，工作地在张江/临港，公司为高成长科创平台，业务与支架材料设计高度契合，可充分利用硕士支架结构与材料学背景。</t>
+  </si>
+  <si>
+    <t>强调支架结构设计与材料学（金属/可降解/涂层）研究项目；补充有限元/三维建模等力学仿真技能；结合介入器械工艺与验证经验，展示面向三类器械的规范化研发能力。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4033,7 +4081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L154"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9899,6 +9947,82 @@
       </c>
       <c r="L154" t="s">
         <v>1154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E155" t="s">
+        <v>147</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G155">
+        <v>9</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I155">
+        <v>87</v>
+      </c>
+      <c r="J155" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C156" t="s">
+        <v>610</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E156" t="s">
+        <v>16</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G156">
+        <v>9</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I156">
+        <v>86</v>
+      </c>
+      <c r="J156" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1170</v>
       </c>
     </row>
   </sheetData>
@@ -9932,7 +10056,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -9941,16 +10065,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1156</v>
+        <v>1172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1157</v>
+        <v>1173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1158</v>
+        <v>1174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1159</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9964,13 +10088,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1161</v>
+        <v>1177</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -9998,7 +10122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10013,7 +10137,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1167</v>
+        <v>1183</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10023,31 +10147,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1168</v>
+        <v>1184</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1169</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1170</v>
+        <v>1186</v>
       </c>
       <c r="B4">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1171</v>
+        <v>1187</v>
       </c>
       <c r="B5" t="s">
-        <v>1172</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1173</v>
+        <v>1189</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -10055,7 +10179,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1174</v>
+        <v>1190</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -10063,15 +10187,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1175</v>
+        <v>1191</v>
       </c>
       <c r="B8">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1176</v>
+        <v>1192</v>
       </c>
       <c r="B9">
         <v>73</v>
@@ -10079,7 +10203,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1177</v>
+        <v>1193</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -10087,15 +10211,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1178</v>
+        <v>1194</v>
       </c>
       <c r="B11" t="s">
-        <v>1087</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1179</v>
+        <v>1195</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10105,15 +10229,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1180</v>
+        <v>1196</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1181</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1182</v>
+        <v>1198</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -10121,15 +10245,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1183</v>
+        <v>1199</v>
       </c>
       <c r="B17" s="5">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1184</v>
+        <v>1200</v>
       </c>
       <c r="B18" s="5">
         <v>73</v>
@@ -10137,7 +10261,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1185</v>
+        <v>1201</v>
       </c>
       <c r="B19" s="5">
         <v>5</v>
@@ -10145,7 +10269,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10153,7 +10277,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -10161,7 +10285,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -10169,7 +10293,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -10177,7 +10301,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -10185,7 +10309,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -10193,7 +10317,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -10205,7 +10329,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1193</v>
+        <v>1209</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -10223,7 +10347,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1194</v>
+        <v>1210</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -12184,25 +12308,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>1156</v>
       </c>
       <c r="D105" t="s">
-        <v>73</v>
+        <v>1157</v>
       </c>
       <c r="E105" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="F105" t="s">
-        <v>76</v>
+        <v>1159</v>
       </c>
       <c r="G105">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H105" t="s">
-        <v>77</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -12210,25 +12334,25 @@
         <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="C106" t="s">
-        <v>80</v>
+        <v>1164</v>
       </c>
       <c r="D106" t="s">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="E106" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F106" t="s">
-        <v>83</v>
+        <v>1166</v>
       </c>
       <c r="G106">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H106" t="s">
-        <v>84</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -12239,22 +12363,22 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D107" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E107" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F107" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G107">
         <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -12265,22 +12389,22 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D108" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -12291,22 +12415,22 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D109" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F109" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -12317,22 +12441,22 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D110" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E110" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -12343,22 +12467,22 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E111" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -12369,22 +12493,22 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D112" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E112" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F112" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -12392,25 +12516,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F113" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -12418,25 +12542,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D114" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E114" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -12447,22 +12571,22 @@
         <v>159</v>
       </c>
       <c r="C115" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D115" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E115" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F115" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -12473,22 +12597,22 @@
         <v>159</v>
       </c>
       <c r="C116" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D116" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E116" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F116" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -12499,22 +12623,22 @@
         <v>159</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D117" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E117" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F117" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -12525,22 +12649,22 @@
         <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D118" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F118" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -12551,22 +12675,22 @@
         <v>159</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D119" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -12577,22 +12701,22 @@
         <v>159</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D120" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E120" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -12603,22 +12727,22 @@
         <v>159</v>
       </c>
       <c r="C121" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D121" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -12629,22 +12753,22 @@
         <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D122" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E122" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F122" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -12655,22 +12779,22 @@
         <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D123" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E123" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F123" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -12678,25 +12802,25 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E124" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -12704,25 +12828,25 @@
         <v>96</v>
       </c>
       <c r="B125" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D125" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E125" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F125" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -12733,22 +12857,22 @@
         <v>284</v>
       </c>
       <c r="C126" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D126" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E126" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F126" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -12759,22 +12883,22 @@
         <v>284</v>
       </c>
       <c r="C127" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E127" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F127" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -12785,22 +12909,22 @@
         <v>284</v>
       </c>
       <c r="C128" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E128" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F128" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -12811,22 +12935,22 @@
         <v>284</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D129" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E129" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F129" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -12834,25 +12958,25 @@
         <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C130" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D130" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E130" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F130" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -12860,25 +12984,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C131" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E131" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F131" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -12889,22 +13013,22 @@
         <v>402</v>
       </c>
       <c r="C132" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D132" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E132" t="s">
         <v>66</v>
       </c>
       <c r="F132" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -12915,22 +13039,22 @@
         <v>402</v>
       </c>
       <c r="C133" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D133" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E133" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F133" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -12938,25 +13062,25 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C134" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D134" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E134" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F134" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -12964,25 +13088,25 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C135" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D135" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E135" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -12993,22 +13117,22 @@
         <v>473</v>
       </c>
       <c r="C136" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D136" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E136" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F136" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -13019,22 +13143,22 @@
         <v>473</v>
       </c>
       <c r="C137" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D137" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E137" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F137" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -13045,22 +13169,22 @@
         <v>473</v>
       </c>
       <c r="C138" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D138" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E138" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F138" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -13068,25 +13192,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C139" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D139" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E139" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F139" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -13094,25 +13218,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C140" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D140" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E140" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F140" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -13120,25 +13244,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C141" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="D141" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="E141" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F141" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13146,25 +13270,25 @@
         <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C142" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D142" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E142" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F142" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13175,22 +13299,22 @@
         <v>591</v>
       </c>
       <c r="C143" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D143" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E143" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F143" t="s">
-        <v>468</v>
+        <v>604</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13201,10 +13325,10 @@
         <v>591</v>
       </c>
       <c r="C144" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="D144" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="E144" t="s">
         <v>16</v>
@@ -13216,7 +13340,7 @@
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -13227,22 +13351,22 @@
         <v>591</v>
       </c>
       <c r="C145" t="s">
-        <v>650</v>
+        <v>557</v>
       </c>
       <c r="D145" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E145" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>653</v>
+        <v>468</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -13253,22 +13377,22 @@
         <v>591</v>
       </c>
       <c r="C146" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="D146" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="E146" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F146" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13279,22 +13403,22 @@
         <v>591</v>
       </c>
       <c r="C147" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="D147" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E147" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F147" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13305,22 +13429,22 @@
         <v>591</v>
       </c>
       <c r="C148" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="D148" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>661</v>
       </c>
       <c r="F148" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13328,16 +13452,16 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C149" t="s">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="D149" t="s">
-        <v>715</v>
+        <v>667</v>
       </c>
       <c r="E149" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F149" t="s">
         <v>604</v>
@@ -13346,7 +13470,7 @@
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>717</v>
+        <v>669</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -13354,25 +13478,25 @@
         <v>121</v>
       </c>
       <c r="B150" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C150" t="s">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="D150" t="s">
-        <v>722</v>
+        <v>674</v>
       </c>
       <c r="E150" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F150" t="s">
-        <v>724</v>
+        <v>676</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>725</v>
+        <v>677</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -13383,22 +13507,22 @@
         <v>697</v>
       </c>
       <c r="C151" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="D151" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="E151" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -13409,22 +13533,22 @@
         <v>697</v>
       </c>
       <c r="C152" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="D152" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="E152" t="s">
-        <v>739</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
-        <v>604</v>
+        <v>724</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -13435,22 +13559,22 @@
         <v>697</v>
       </c>
       <c r="C153" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="D153" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="E153" t="s">
-        <v>747</v>
+        <v>535</v>
       </c>
       <c r="F153" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -13461,22 +13585,22 @@
         <v>697</v>
       </c>
       <c r="C154" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="D154" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="E154" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="F154" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -13487,22 +13611,22 @@
         <v>697</v>
       </c>
       <c r="C155" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="D155" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="E155" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="F155" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -13510,25 +13634,25 @@
         <v>127</v>
       </c>
       <c r="B156" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C156" t="s">
-        <v>791</v>
+        <v>753</v>
       </c>
       <c r="D156" t="s">
-        <v>610</v>
+        <v>754</v>
       </c>
       <c r="E156" t="s">
-        <v>793</v>
+        <v>756</v>
       </c>
       <c r="F156" t="s">
-        <v>794</v>
+        <v>757</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>795</v>
+        <v>758</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -13536,25 +13660,25 @@
         <v>128</v>
       </c>
       <c r="B157" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C157" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="D157" t="s">
-        <v>808</v>
+        <v>761</v>
       </c>
       <c r="E157" t="s">
-        <v>810</v>
+        <v>763</v>
       </c>
       <c r="F157" t="s">
-        <v>811</v>
+        <v>764</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>812</v>
+        <v>765</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -13565,22 +13689,22 @@
         <v>773</v>
       </c>
       <c r="C158" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="D158" t="s">
-        <v>110</v>
+        <v>610</v>
       </c>
       <c r="E158" t="s">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="F158" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13588,25 +13712,25 @@
         <v>130</v>
       </c>
       <c r="B159" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C159" t="s">
-        <v>888</v>
+        <v>807</v>
       </c>
       <c r="D159" t="s">
-        <v>889</v>
+        <v>808</v>
       </c>
       <c r="E159" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F159" t="s">
-        <v>891</v>
+        <v>811</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>892</v>
+        <v>812</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13614,25 +13738,25 @@
         <v>131</v>
       </c>
       <c r="B160" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C160" t="s">
-        <v>896</v>
+        <v>816</v>
       </c>
       <c r="D160" t="s">
-        <v>897</v>
+        <v>110</v>
       </c>
       <c r="E160" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F160" t="s">
-        <v>899</v>
+        <v>818</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>900</v>
+        <v>819</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -13643,22 +13767,22 @@
         <v>845</v>
       </c>
       <c r="C161" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="D161" t="s">
-        <v>585</v>
+        <v>889</v>
       </c>
       <c r="E161" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F161" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -13669,22 +13793,22 @@
         <v>845</v>
       </c>
       <c r="C162" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="D162" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="E162" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13695,22 +13819,22 @@
         <v>845</v>
       </c>
       <c r="C163" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="D163" t="s">
-        <v>919</v>
+        <v>585</v>
       </c>
       <c r="E163" t="s">
-        <v>921</v>
+        <v>66</v>
       </c>
       <c r="F163" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -13718,25 +13842,25 @@
         <v>135</v>
       </c>
       <c r="B164" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C164" t="s">
-        <v>964</v>
+        <v>911</v>
       </c>
       <c r="D164" t="s">
-        <v>965</v>
+        <v>585</v>
       </c>
       <c r="E164" t="s">
-        <v>967</v>
+        <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>968</v>
+        <v>913</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>969</v>
+        <v>914</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -13744,25 +13868,25 @@
         <v>136</v>
       </c>
       <c r="B165" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C165" t="s">
-        <v>950</v>
+        <v>918</v>
       </c>
       <c r="D165" t="s">
-        <v>1002</v>
+        <v>919</v>
       </c>
       <c r="E165" t="s">
-        <v>1004</v>
+        <v>921</v>
       </c>
       <c r="F165" t="s">
-        <v>438</v>
+        <v>922</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>1005</v>
+        <v>923</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -13773,22 +13897,22 @@
         <v>934</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="D166" t="s">
-        <v>1009</v>
+        <v>965</v>
       </c>
       <c r="E166" t="s">
-        <v>16</v>
+        <v>967</v>
       </c>
       <c r="F166" t="s">
-        <v>1011</v>
+        <v>968</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>1012</v>
+        <v>969</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -13799,22 +13923,22 @@
         <v>934</v>
       </c>
       <c r="C167" t="s">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="D167" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="E167" t="s">
-        <v>66</v>
+        <v>1004</v>
       </c>
       <c r="F167" t="s">
-        <v>1018</v>
+        <v>438</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -13825,22 +13949,22 @@
         <v>934</v>
       </c>
       <c r="C168" t="s">
-        <v>1023</v>
+        <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="E168" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="F168" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -13851,22 +13975,22 @@
         <v>934</v>
       </c>
       <c r="C169" t="s">
-        <v>213</v>
+        <v>650</v>
       </c>
       <c r="D169" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="E169" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F169" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -13877,22 +14001,22 @@
         <v>934</v>
       </c>
       <c r="C170" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="D170" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="E170" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="F170" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -13903,22 +14027,22 @@
         <v>934</v>
       </c>
       <c r="C171" t="s">
-        <v>1048</v>
+        <v>213</v>
       </c>
       <c r="D171" t="s">
-        <v>1049</v>
+        <v>1032</v>
       </c>
       <c r="E171" t="s">
-        <v>1051</v>
+        <v>106</v>
       </c>
       <c r="F171" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -13929,22 +14053,22 @@
         <v>934</v>
       </c>
       <c r="C172" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="D172" t="s">
-        <v>1058</v>
+        <v>1040</v>
       </c>
       <c r="E172" t="s">
-        <v>16</v>
+        <v>1042</v>
       </c>
       <c r="F172" t="s">
-        <v>1060</v>
+        <v>1043</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>1061</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -13955,22 +14079,22 @@
         <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>1082</v>
+        <v>1048</v>
       </c>
       <c r="D173" t="s">
-        <v>1083</v>
+        <v>1049</v>
       </c>
       <c r="E173" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
       <c r="F173" t="s">
-        <v>959</v>
+        <v>1052</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>1086</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -13978,25 +14102,25 @@
         <v>145</v>
       </c>
       <c r="B174" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C174" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="D174" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="E174" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1108</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -14004,25 +14128,25 @@
         <v>146</v>
       </c>
       <c r="B175" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C175" t="s">
-        <v>1112</v>
+        <v>1082</v>
       </c>
       <c r="D175" t="s">
-        <v>1113</v>
+        <v>1083</v>
       </c>
       <c r="E175" t="s">
-        <v>25</v>
+        <v>1085</v>
       </c>
       <c r="F175" t="s">
-        <v>1115</v>
+        <v>959</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1116</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -14033,22 +14157,22 @@
         <v>1087</v>
       </c>
       <c r="C176" t="s">
-        <v>1120</v>
+        <v>271</v>
       </c>
       <c r="D176" t="s">
-        <v>1121</v>
+        <v>1104</v>
       </c>
       <c r="E176" t="s">
-        <v>1123</v>
+        <v>1106</v>
       </c>
       <c r="F176" t="s">
-        <v>1124</v>
+        <v>1107</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1125</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14059,22 +14183,22 @@
         <v>1087</v>
       </c>
       <c r="C177" t="s">
-        <v>1129</v>
+        <v>1112</v>
       </c>
       <c r="D177" t="s">
-        <v>1130</v>
+        <v>1113</v>
       </c>
       <c r="E177" t="s">
-        <v>1132</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>1133</v>
+        <v>1115</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1134</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -14082,25 +14206,25 @@
         <v>149</v>
       </c>
       <c r="B178" t="s">
-        <v>159</v>
+        <v>1087</v>
       </c>
       <c r="C178" t="s">
-        <v>271</v>
+        <v>1120</v>
       </c>
       <c r="D178" t="s">
-        <v>272</v>
+        <v>1121</v>
       </c>
       <c r="E178" t="s">
-        <v>75</v>
+        <v>1123</v>
       </c>
       <c r="F178" t="s">
-        <v>274</v>
+        <v>1124</v>
       </c>
       <c r="G178">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>275</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -14108,25 +14232,25 @@
         <v>150</v>
       </c>
       <c r="B179" t="s">
-        <v>591</v>
+        <v>1087</v>
       </c>
       <c r="C179" t="s">
-        <v>681</v>
+        <v>1129</v>
       </c>
       <c r="D179" t="s">
-        <v>682</v>
+        <v>1130</v>
       </c>
       <c r="E179" t="s">
-        <v>25</v>
+        <v>1132</v>
       </c>
       <c r="F179" t="s">
-        <v>684</v>
+        <v>1133</v>
       </c>
       <c r="G179">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>685</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -14134,25 +14258,25 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="C180" t="s">
-        <v>689</v>
+        <v>271</v>
       </c>
       <c r="D180" t="s">
-        <v>690</v>
+        <v>272</v>
       </c>
       <c r="E180" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F180" t="s">
-        <v>692</v>
+        <v>274</v>
       </c>
       <c r="G180">
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>693</v>
+        <v>275</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -14160,25 +14284,25 @@
         <v>152</v>
       </c>
       <c r="B181" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C181" t="s">
-        <v>767</v>
+        <v>681</v>
       </c>
       <c r="D181" t="s">
-        <v>768</v>
+        <v>682</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>770</v>
+        <v>684</v>
       </c>
       <c r="G181">
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>771</v>
+        <v>685</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -14186,24 +14310,76 @@
         <v>153</v>
       </c>
       <c r="B182" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="C182" t="s">
-        <v>927</v>
+        <v>689</v>
       </c>
       <c r="D182" t="s">
-        <v>585</v>
+        <v>690</v>
       </c>
       <c r="E182" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F182" t="s">
-        <v>929</v>
+        <v>692</v>
       </c>
       <c r="G182">
         <v>7</v>
       </c>
       <c r="H182" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>154</v>
+      </c>
+      <c r="B183" t="s">
+        <v>697</v>
+      </c>
+      <c r="C183" t="s">
+        <v>767</v>
+      </c>
+      <c r="D183" t="s">
+        <v>768</v>
+      </c>
+      <c r="E183" t="s">
+        <v>25</v>
+      </c>
+      <c r="F183" t="s">
+        <v>770</v>
+      </c>
+      <c r="G183">
+        <v>7</v>
+      </c>
+      <c r="H183" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>155</v>
+      </c>
+      <c r="B184" t="s">
+        <v>845</v>
+      </c>
+      <c r="C184" t="s">
+        <v>927</v>
+      </c>
+      <c r="D184" t="s">
+        <v>585</v>
+      </c>
+      <c r="E184" t="s">
+        <v>25</v>
+      </c>
+      <c r="F184" t="s">
+        <v>929</v>
+      </c>
+      <c r="G184">
+        <v>7</v>
+      </c>
+      <c r="H184" t="s">
         <v>930</v>
       </c>
     </row>
@@ -14220,7 +14396,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -14237,10 +14413,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1163</v>
+        <v>1179</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1164</v>
+        <v>1180</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -14267,12 +14443,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1165</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -14307,7 +14483,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -14342,7 +14518,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -14377,7 +14553,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -14412,7 +14588,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -14447,7 +14623,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -14482,7 +14658,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -14517,7 +14693,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -14552,7 +14728,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -14587,7 +14763,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -14622,7 +14798,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -14657,7 +14833,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -14692,7 +14868,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -14727,7 +14903,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -14762,7 +14938,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -14797,7 +14973,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -14832,7 +15008,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -14867,7 +15043,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -14902,7 +15078,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -14937,7 +15113,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -14972,7 +15148,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -15007,7 +15183,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -15042,7 +15218,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -15077,7 +15253,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -15112,7 +15288,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -15147,7 +15323,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -15182,7 +15358,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -15217,7 +15393,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -15252,7 +15428,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -15287,7 +15463,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -15322,7 +15498,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -15357,7 +15533,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -15392,7 +15568,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B34">
         <v>88</v>
@@ -15427,7 +15603,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B35">
         <v>88</v>
@@ -15462,7 +15638,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B36">
         <v>88</v>
@@ -15497,7 +15673,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B37">
         <v>88</v>
@@ -15532,7 +15708,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B38">
         <v>88</v>
@@ -15567,7 +15743,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B39">
         <v>88</v>
@@ -15602,7 +15778,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B40">
         <v>88</v>
@@ -15637,7 +15813,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B41">
         <v>88</v>
@@ -15672,7 +15848,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B42">
         <v>87</v>
@@ -15707,7 +15883,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B43">
         <v>87</v>
@@ -15742,7 +15918,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B44">
         <v>87</v>
@@ -15777,7 +15953,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B45">
         <v>87</v>
@@ -15812,7 +15988,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B46">
         <v>87</v>
@@ -15847,7 +16023,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B47">
         <v>87</v>
@@ -15882,7 +16058,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B48">
         <v>87</v>
@@ -15917,7 +16093,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B49">
         <v>87</v>
@@ -15952,7 +16128,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B50">
         <v>87</v>
@@ -15987,77 +16163,77 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B51">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>284</v>
+        <v>1155</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>1156</v>
       </c>
       <c r="E51" t="s">
-        <v>370</v>
+        <v>1157</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>372</v>
+        <v>1159</v>
       </c>
       <c r="H51" t="s">
-        <v>374</v>
+        <v>1161</v>
       </c>
       <c r="I51" t="s">
-        <v>375</v>
+        <v>1162</v>
       </c>
       <c r="J51" t="s">
-        <v>376</v>
+        <v>1163</v>
       </c>
       <c r="K51" t="s">
-        <v>371</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B52">
         <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E52" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H52" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I52" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J52" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K52" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B53">
         <v>86</v>
@@ -16066,138 +16242,138 @@
         <v>402</v>
       </c>
       <c r="D53" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G53" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H53" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I53" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J53" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K53" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B54">
         <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D54" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E54" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F54" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H54" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I54" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J54" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K54" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B55">
         <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D55" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E55" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G55" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H55" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I55" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J55" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K55" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B56">
         <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D56" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
       <c r="E56" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H56" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="I56" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="J56" t="s">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="K56" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B57">
         <v>86</v>
@@ -16206,33 +16382,33 @@
         <v>591</v>
       </c>
       <c r="D57" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E57" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="H57" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="I57" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="J57" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="K57" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B58">
         <v>86</v>
@@ -16241,103 +16417,103 @@
         <v>591</v>
       </c>
       <c r="D58" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E58" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H58" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="I58" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J58" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="K58" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B59">
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D59" t="s">
-        <v>829</v>
+        <v>635</v>
       </c>
       <c r="E59" t="s">
-        <v>830</v>
+        <v>636</v>
       </c>
       <c r="F59" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>832</v>
+        <v>638</v>
       </c>
       <c r="H59" t="s">
-        <v>834</v>
+        <v>640</v>
       </c>
       <c r="I59" t="s">
-        <v>835</v>
+        <v>641</v>
       </c>
       <c r="J59" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="K59" t="s">
-        <v>831</v>
+        <v>637</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B60">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D60" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E60" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="F60" t="s">
-        <v>380</v>
+        <v>785</v>
       </c>
       <c r="G60" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
       <c r="H60" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="I60" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="J60" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="K60" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B61">
         <v>86</v>
@@ -16346,68 +16522,68 @@
         <v>845</v>
       </c>
       <c r="D61" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E61" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G61" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H61" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I61" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J61" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K61" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B62">
         <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D62" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="E62" t="s">
-        <v>974</v>
+        <v>881</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>468</v>
+        <v>883</v>
       </c>
       <c r="H62" t="s">
-        <v>977</v>
+        <v>885</v>
       </c>
       <c r="I62" t="s">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="J62" t="s">
-        <v>979</v>
+        <v>887</v>
       </c>
       <c r="K62" t="s">
-        <v>975</v>
+        <v>882</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B63">
         <v>86</v>
@@ -16416,33 +16592,33 @@
         <v>934</v>
       </c>
       <c r="D63" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E63" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="F63" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="H63" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="I63" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J63" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="K63" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B64">
         <v>86</v>
@@ -16451,68 +16627,68 @@
         <v>934</v>
       </c>
       <c r="D64" t="s">
-        <v>1073</v>
+        <v>980</v>
       </c>
       <c r="E64" t="s">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="F64" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G64" t="s">
-        <v>1077</v>
+        <v>984</v>
       </c>
       <c r="H64" t="s">
-        <v>1079</v>
+        <v>986</v>
       </c>
       <c r="I64" t="s">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="J64" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="K64" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B65">
         <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D65" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E65" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="F65" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="G65" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="H65" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="I65" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="J65" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="K65" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B66">
         <v>86</v>
@@ -16521,278 +16697,278 @@
         <v>1087</v>
       </c>
       <c r="D66" t="s">
-        <v>1146</v>
+        <v>1088</v>
       </c>
       <c r="E66" t="s">
-        <v>1147</v>
+        <v>1089</v>
       </c>
       <c r="F66" t="s">
-        <v>1149</v>
+        <v>1091</v>
       </c>
       <c r="G66" t="s">
-        <v>1150</v>
+        <v>1092</v>
       </c>
       <c r="H66" t="s">
-        <v>1152</v>
+        <v>1094</v>
       </c>
       <c r="I66" t="s">
-        <v>1153</v>
+        <v>1095</v>
       </c>
       <c r="J66" t="s">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="K66" t="s">
-        <v>1148</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B67">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="D67" t="s">
-        <v>55</v>
+        <v>1146</v>
       </c>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>1147</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>1150</v>
       </c>
       <c r="H67" t="s">
-        <v>60</v>
+        <v>1152</v>
       </c>
       <c r="I67" t="s">
-        <v>61</v>
+        <v>1153</v>
       </c>
       <c r="J67" t="s">
-        <v>62</v>
+        <v>1154</v>
       </c>
       <c r="K67" t="s">
-        <v>57</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B68">
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E68" t="s">
+        <v>610</v>
+      </c>
+      <c r="F68" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" t="s">
         <v>1166</v>
       </c>
-      <c r="B68">
-        <v>85</v>
-      </c>
-      <c r="C68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" t="s">
-        <v>128</v>
-      </c>
-      <c r="E68" t="s">
-        <v>89</v>
-      </c>
-      <c r="F68" t="s">
-        <v>130</v>
-      </c>
-      <c r="G68" t="s">
-        <v>131</v>
-      </c>
       <c r="H68" t="s">
-        <v>133</v>
+        <v>1168</v>
       </c>
       <c r="I68" t="s">
-        <v>134</v>
+        <v>1169</v>
       </c>
       <c r="J68" t="s">
-        <v>135</v>
+        <v>1170</v>
       </c>
       <c r="K68" t="s">
-        <v>129</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B69">
         <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H69" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I69" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J69" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K69" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B70">
         <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G70" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H70" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I70" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J70" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K70" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B71">
         <v>85</v>
       </c>
       <c r="C71" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D71" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E71" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F71" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G71" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H71" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I71" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J71" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K71" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B72">
         <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D72" t="s">
-        <v>774</v>
+        <v>55</v>
       </c>
       <c r="E72" t="s">
-        <v>783</v>
+        <v>403</v>
       </c>
       <c r="F72" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>786</v>
+        <v>405</v>
       </c>
       <c r="H72" t="s">
-        <v>788</v>
+        <v>407</v>
       </c>
       <c r="I72" t="s">
-        <v>789</v>
+        <v>408</v>
       </c>
       <c r="J72" t="s">
-        <v>790</v>
+        <v>409</v>
       </c>
       <c r="K72" t="s">
-        <v>784</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B73">
         <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D73" t="s">
-        <v>799</v>
+        <v>474</v>
       </c>
       <c r="E73" t="s">
-        <v>800</v>
+        <v>475</v>
       </c>
       <c r="F73" t="s">
-        <v>793</v>
+        <v>477</v>
       </c>
       <c r="G73" t="s">
-        <v>802</v>
+        <v>478</v>
       </c>
       <c r="H73" t="s">
-        <v>804</v>
+        <v>480</v>
       </c>
       <c r="I73" t="s">
-        <v>805</v>
+        <v>481</v>
       </c>
       <c r="J73" t="s">
-        <v>806</v>
+        <v>482</v>
       </c>
       <c r="K73" t="s">
-        <v>801</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B74">
         <v>85</v>
@@ -16801,313 +16977,313 @@
         <v>773</v>
       </c>
       <c r="D74" t="s">
-        <v>821</v>
+        <v>774</v>
       </c>
       <c r="E74" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="F74" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="G74" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="H74" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="I74" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="J74" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="K74" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B75">
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D75" t="s">
-        <v>989</v>
+        <v>799</v>
       </c>
       <c r="E75" t="s">
-        <v>990</v>
+        <v>800</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>793</v>
       </c>
       <c r="G75" t="s">
-        <v>959</v>
+        <v>802</v>
       </c>
       <c r="H75" t="s">
-        <v>993</v>
+        <v>804</v>
       </c>
       <c r="I75" t="s">
-        <v>994</v>
+        <v>805</v>
       </c>
       <c r="J75" t="s">
-        <v>995</v>
+        <v>806</v>
       </c>
       <c r="K75" t="s">
-        <v>991</v>
+        <v>801</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B76">
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D76" t="s">
-        <v>1065</v>
+        <v>821</v>
       </c>
       <c r="E76" t="s">
-        <v>1066</v>
+        <v>822</v>
       </c>
       <c r="F76" t="s">
-        <v>147</v>
+        <v>777</v>
       </c>
       <c r="G76" t="s">
-        <v>1068</v>
+        <v>824</v>
       </c>
       <c r="H76" t="s">
-        <v>1070</v>
+        <v>826</v>
       </c>
       <c r="I76" t="s">
-        <v>1071</v>
+        <v>827</v>
       </c>
       <c r="J76" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="K76" t="s">
-        <v>1067</v>
+        <v>823</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B77">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D77" t="s">
-        <v>144</v>
+        <v>989</v>
       </c>
       <c r="E77" t="s">
-        <v>145</v>
+        <v>990</v>
       </c>
       <c r="F77" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G77" t="s">
-        <v>148</v>
+        <v>959</v>
       </c>
       <c r="H77" t="s">
-        <v>150</v>
+        <v>993</v>
       </c>
       <c r="I77" t="s">
-        <v>151</v>
+        <v>994</v>
       </c>
       <c r="J77" t="s">
-        <v>152</v>
+        <v>995</v>
       </c>
       <c r="K77" t="s">
-        <v>146</v>
+        <v>991</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B78">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D78" t="s">
-        <v>144</v>
+        <v>1065</v>
       </c>
       <c r="E78" t="s">
-        <v>394</v>
+        <v>1066</v>
       </c>
       <c r="F78" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G78" t="s">
-        <v>397</v>
+        <v>1068</v>
       </c>
       <c r="H78" t="s">
-        <v>399</v>
+        <v>1070</v>
       </c>
       <c r="I78" t="s">
-        <v>400</v>
+        <v>1071</v>
       </c>
       <c r="J78" t="s">
-        <v>401</v>
+        <v>1072</v>
       </c>
       <c r="K78" t="s">
-        <v>395</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B79">
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E79" t="s">
-        <v>411</v>
+        <v>145</v>
       </c>
       <c r="F79" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="G79" t="s">
-        <v>413</v>
+        <v>148</v>
       </c>
       <c r="H79" t="s">
-        <v>415</v>
+        <v>150</v>
       </c>
       <c r="I79" t="s">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>417</v>
+        <v>152</v>
       </c>
       <c r="K79" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B80">
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D80" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>394</v>
       </c>
       <c r="F80" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="G80" t="s">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="H80" t="s">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="I80" t="s">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="J80" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="K80" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B81">
         <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D81" t="s">
-        <v>714</v>
+        <v>410</v>
       </c>
       <c r="E81" t="s">
-        <v>715</v>
+        <v>411</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G81" t="s">
-        <v>604</v>
+        <v>413</v>
       </c>
       <c r="H81" t="s">
-        <v>718</v>
+        <v>415</v>
       </c>
       <c r="I81" t="s">
-        <v>719</v>
+        <v>416</v>
       </c>
       <c r="J81" t="s">
-        <v>720</v>
+        <v>417</v>
       </c>
       <c r="K81" t="s">
-        <v>716</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B82">
         <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D82" t="s">
-        <v>721</v>
+        <v>483</v>
       </c>
       <c r="E82" t="s">
-        <v>722</v>
+        <v>122</v>
       </c>
       <c r="F82" t="s">
-        <v>25</v>
+        <v>485</v>
       </c>
       <c r="G82" t="s">
-        <v>724</v>
+        <v>486</v>
       </c>
       <c r="H82" t="s">
-        <v>726</v>
+        <v>488</v>
       </c>
       <c r="I82" t="s">
-        <v>727</v>
+        <v>489</v>
       </c>
       <c r="J82" t="s">
-        <v>728</v>
+        <v>490</v>
       </c>
       <c r="K82" t="s">
-        <v>723</v>
+        <v>484</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B83">
         <v>84</v>
@@ -17116,173 +17292,173 @@
         <v>697</v>
       </c>
       <c r="D83" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="E83" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="F83" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="H83" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I83" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="J83" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="K83" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B84">
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D84" t="s">
-        <v>791</v>
+        <v>721</v>
       </c>
       <c r="E84" t="s">
-        <v>610</v>
+        <v>722</v>
       </c>
       <c r="F84" t="s">
-        <v>793</v>
+        <v>25</v>
       </c>
       <c r="G84" t="s">
-        <v>794</v>
+        <v>724</v>
       </c>
       <c r="H84" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I84" t="s">
-        <v>797</v>
+        <v>727</v>
       </c>
       <c r="J84" t="s">
-        <v>798</v>
+        <v>728</v>
       </c>
       <c r="K84" t="s">
-        <v>792</v>
+        <v>723</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D85" t="s">
-        <v>896</v>
+        <v>729</v>
       </c>
       <c r="E85" t="s">
-        <v>897</v>
+        <v>730</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
       <c r="G85" t="s">
-        <v>899</v>
+        <v>732</v>
       </c>
       <c r="H85" t="s">
-        <v>901</v>
+        <v>726</v>
       </c>
       <c r="I85" t="s">
-        <v>902</v>
+        <v>734</v>
       </c>
       <c r="J85" t="s">
-        <v>903</v>
+        <v>735</v>
       </c>
       <c r="K85" t="s">
-        <v>898</v>
+        <v>731</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D86" t="s">
-        <v>964</v>
+        <v>791</v>
       </c>
       <c r="E86" t="s">
-        <v>965</v>
+        <v>610</v>
       </c>
       <c r="F86" t="s">
-        <v>967</v>
+        <v>793</v>
       </c>
       <c r="G86" t="s">
-        <v>968</v>
+        <v>794</v>
       </c>
       <c r="H86" t="s">
-        <v>970</v>
+        <v>796</v>
       </c>
       <c r="I86" t="s">
-        <v>971</v>
+        <v>797</v>
       </c>
       <c r="J86" t="s">
-        <v>972</v>
+        <v>798</v>
       </c>
       <c r="K86" t="s">
-        <v>966</v>
+        <v>792</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B87">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D87" t="s">
-        <v>950</v>
+        <v>896</v>
       </c>
       <c r="E87" t="s">
-        <v>1002</v>
+        <v>897</v>
       </c>
       <c r="F87" t="s">
-        <v>1004</v>
+        <v>25</v>
       </c>
       <c r="G87" t="s">
-        <v>438</v>
+        <v>899</v>
       </c>
       <c r="H87" t="s">
-        <v>1006</v>
+        <v>901</v>
       </c>
       <c r="I87" t="s">
-        <v>1007</v>
+        <v>902</v>
       </c>
       <c r="J87" t="s">
-        <v>1008</v>
+        <v>903</v>
       </c>
       <c r="K87" t="s">
-        <v>1003</v>
+        <v>898</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B88">
         <v>84</v>
@@ -17291,33 +17467,33 @@
         <v>934</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>964</v>
       </c>
       <c r="E88" t="s">
-        <v>1032</v>
+        <v>965</v>
       </c>
       <c r="F88" t="s">
-        <v>106</v>
+        <v>967</v>
       </c>
       <c r="G88" t="s">
-        <v>1034</v>
+        <v>968</v>
       </c>
       <c r="H88" t="s">
-        <v>1036</v>
+        <v>970</v>
       </c>
       <c r="I88" t="s">
-        <v>1037</v>
+        <v>971</v>
       </c>
       <c r="J88" t="s">
-        <v>1038</v>
+        <v>972</v>
       </c>
       <c r="K88" t="s">
-        <v>1033</v>
+        <v>966</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B89">
         <v>84</v>
@@ -17326,832 +17502,902 @@
         <v>934</v>
       </c>
       <c r="D89" t="s">
-        <v>1057</v>
+        <v>950</v>
       </c>
       <c r="E89" t="s">
-        <v>1058</v>
+        <v>1002</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>1004</v>
       </c>
       <c r="G89" t="s">
-        <v>1060</v>
+        <v>438</v>
       </c>
       <c r="H89" t="s">
-        <v>1062</v>
+        <v>1006</v>
       </c>
       <c r="I89" t="s">
-        <v>1063</v>
+        <v>1007</v>
       </c>
       <c r="J89" t="s">
-        <v>1064</v>
+        <v>1008</v>
       </c>
       <c r="K89" t="s">
-        <v>1059</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B90">
         <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="E90" t="s">
-        <v>1104</v>
+        <v>1032</v>
       </c>
       <c r="F90" t="s">
-        <v>1106</v>
+        <v>106</v>
       </c>
       <c r="G90" t="s">
-        <v>1107</v>
+        <v>1034</v>
       </c>
       <c r="H90" t="s">
-        <v>1109</v>
+        <v>1036</v>
       </c>
       <c r="I90" t="s">
-        <v>1110</v>
+        <v>1037</v>
       </c>
       <c r="J90" t="s">
-        <v>1111</v>
+        <v>1038</v>
       </c>
       <c r="K90" t="s">
-        <v>1105</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B91">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>1057</v>
       </c>
       <c r="E91" t="s">
-        <v>362</v>
+        <v>1058</v>
       </c>
       <c r="F91" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>364</v>
+        <v>1060</v>
       </c>
       <c r="H91" t="s">
-        <v>366</v>
+        <v>1062</v>
       </c>
       <c r="I91" t="s">
-        <v>367</v>
+        <v>1063</v>
       </c>
       <c r="J91" t="s">
-        <v>368</v>
+        <v>1064</v>
       </c>
       <c r="K91" t="s">
-        <v>363</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B92">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>473</v>
+        <v>1087</v>
       </c>
       <c r="D92" t="s">
-        <v>491</v>
+        <v>271</v>
       </c>
       <c r="E92" t="s">
-        <v>492</v>
+        <v>1104</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>1106</v>
       </c>
       <c r="G92" t="s">
-        <v>494</v>
+        <v>1107</v>
       </c>
       <c r="H92" t="s">
-        <v>496</v>
+        <v>1109</v>
       </c>
       <c r="I92" t="s">
-        <v>497</v>
+        <v>1110</v>
       </c>
       <c r="J92" t="s">
-        <v>498</v>
+        <v>1111</v>
       </c>
       <c r="K92" t="s">
-        <v>493</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B93">
         <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D93" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E93" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F93" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G93" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H93" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I93" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J93" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K93" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B94">
         <v>83</v>
       </c>
       <c r="C94" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D94" t="s">
-        <v>643</v>
+        <v>491</v>
       </c>
       <c r="E94" t="s">
-        <v>644</v>
+        <v>492</v>
       </c>
       <c r="F94" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G94" t="s">
-        <v>618</v>
+        <v>494</v>
       </c>
       <c r="H94" t="s">
-        <v>647</v>
+        <v>496</v>
       </c>
       <c r="I94" t="s">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="J94" t="s">
-        <v>649</v>
+        <v>498</v>
       </c>
       <c r="K94" t="s">
-        <v>645</v>
+        <v>493</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B95">
         <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D95" t="s">
-        <v>736</v>
+        <v>532</v>
       </c>
       <c r="E95" t="s">
-        <v>737</v>
+        <v>533</v>
       </c>
       <c r="F95" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="G95" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="H95" t="s">
-        <v>741</v>
+        <v>538</v>
       </c>
       <c r="I95" t="s">
-        <v>742</v>
+        <v>539</v>
       </c>
       <c r="J95" t="s">
-        <v>743</v>
+        <v>540</v>
       </c>
       <c r="K95" t="s">
-        <v>738</v>
+        <v>534</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B96">
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D96" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="E96" t="s">
-        <v>808</v>
+        <v>644</v>
       </c>
       <c r="F96" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>811</v>
+        <v>618</v>
       </c>
       <c r="H96" t="s">
-        <v>813</v>
+        <v>647</v>
       </c>
       <c r="I96" t="s">
-        <v>814</v>
+        <v>648</v>
       </c>
       <c r="J96" t="s">
-        <v>815</v>
+        <v>649</v>
       </c>
       <c r="K96" t="s">
-        <v>809</v>
+        <v>645</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B97">
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D97" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="E97" t="s">
-        <v>1016</v>
+        <v>737</v>
       </c>
       <c r="F97" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="G97" t="s">
-        <v>1018</v>
+        <v>604</v>
       </c>
       <c r="H97" t="s">
-        <v>1020</v>
+        <v>741</v>
       </c>
       <c r="I97" t="s">
-        <v>1021</v>
+        <v>742</v>
       </c>
       <c r="J97" t="s">
-        <v>1022</v>
+        <v>743</v>
       </c>
       <c r="K97" t="s">
-        <v>1017</v>
+        <v>738</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B98">
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D98" t="s">
-        <v>1048</v>
+        <v>807</v>
       </c>
       <c r="E98" t="s">
-        <v>1049</v>
+        <v>808</v>
       </c>
       <c r="F98" t="s">
-        <v>1051</v>
+        <v>810</v>
       </c>
       <c r="G98" t="s">
-        <v>1052</v>
+        <v>811</v>
       </c>
       <c r="H98" t="s">
-        <v>1054</v>
+        <v>813</v>
       </c>
       <c r="I98" t="s">
-        <v>1055</v>
+        <v>814</v>
       </c>
       <c r="J98" t="s">
-        <v>1056</v>
+        <v>815</v>
       </c>
       <c r="K98" t="s">
-        <v>1050</v>
+        <v>809</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B99">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D99" t="s">
-        <v>227</v>
+        <v>650</v>
       </c>
       <c r="E99" t="s">
-        <v>228</v>
+        <v>1016</v>
       </c>
       <c r="F99" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="G99" t="s">
-        <v>231</v>
+        <v>1018</v>
       </c>
       <c r="H99" t="s">
-        <v>233</v>
+        <v>1020</v>
       </c>
       <c r="I99" t="s">
-        <v>234</v>
+        <v>1021</v>
       </c>
       <c r="J99" t="s">
-        <v>235</v>
+        <v>1022</v>
       </c>
       <c r="K99" t="s">
-        <v>229</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B100">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D100" t="s">
-        <v>266</v>
+        <v>1048</v>
       </c>
       <c r="E100" t="s">
-        <v>267</v>
+        <v>1049</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="G100" t="s">
-        <v>58</v>
+        <v>1052</v>
       </c>
       <c r="H100" t="s">
-        <v>270</v>
+        <v>1054</v>
       </c>
       <c r="I100" t="s">
-        <v>79</v>
+        <v>1055</v>
       </c>
       <c r="J100" t="s">
-        <v>79</v>
+        <v>1056</v>
       </c>
       <c r="K100" t="s">
-        <v>268</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B101">
         <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D101" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="E101" t="s">
-        <v>339</v>
+        <v>228</v>
       </c>
       <c r="F101" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="G101" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="H101" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="I101" t="s">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="J101" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="K101" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B102">
         <v>82</v>
       </c>
       <c r="C102" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>601</v>
+        <v>266</v>
       </c>
       <c r="E102" t="s">
-        <v>602</v>
+        <v>267</v>
       </c>
       <c r="F102" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>604</v>
+        <v>58</v>
       </c>
       <c r="H102" t="s">
-        <v>606</v>
+        <v>270</v>
       </c>
       <c r="I102" t="s">
-        <v>607</v>
+        <v>79</v>
       </c>
       <c r="J102" t="s">
-        <v>608</v>
+        <v>79</v>
       </c>
       <c r="K102" t="s">
-        <v>603</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B103">
         <v>82</v>
       </c>
       <c r="C103" t="s">
-        <v>934</v>
+        <v>284</v>
       </c>
       <c r="D103" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="E103" t="s">
-        <v>1009</v>
+        <v>339</v>
       </c>
       <c r="F103" t="s">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c r="G103" t="s">
-        <v>1011</v>
+        <v>342</v>
       </c>
       <c r="H103" t="s">
-        <v>1013</v>
+        <v>344</v>
       </c>
       <c r="I103" t="s">
-        <v>1014</v>
+        <v>345</v>
       </c>
       <c r="J103" t="s">
-        <v>1015</v>
+        <v>346</v>
       </c>
       <c r="K103" t="s">
-        <v>1010</v>
+        <v>340</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B104">
         <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D104" t="s">
-        <v>1023</v>
+        <v>601</v>
       </c>
       <c r="E104" t="s">
-        <v>1024</v>
+        <v>602</v>
       </c>
       <c r="F104" t="s">
-        <v>1026</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>1027</v>
+        <v>604</v>
       </c>
       <c r="H104" t="s">
-        <v>1029</v>
+        <v>606</v>
       </c>
       <c r="I104" t="s">
-        <v>1030</v>
+        <v>607</v>
       </c>
       <c r="J104" t="s">
-        <v>1031</v>
+        <v>608</v>
       </c>
       <c r="K104" t="s">
-        <v>1025</v>
+        <v>603</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B105">
         <v>82</v>
       </c>
       <c r="C105" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D105" t="s">
-        <v>1112</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
-        <v>1113</v>
+        <v>1009</v>
       </c>
       <c r="F105" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G105" t="s">
-        <v>1115</v>
+        <v>1011</v>
       </c>
       <c r="H105" t="s">
-        <v>1117</v>
+        <v>1013</v>
       </c>
       <c r="I105" t="s">
-        <v>1118</v>
+        <v>1014</v>
       </c>
       <c r="J105" t="s">
-        <v>1119</v>
+        <v>1015</v>
       </c>
       <c r="K105" t="s">
-        <v>1114</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B106">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D106" t="s">
-        <v>80</v>
+        <v>1023</v>
       </c>
       <c r="E106" t="s">
-        <v>81</v>
+        <v>1024</v>
       </c>
       <c r="F106" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G106" t="s">
-        <v>83</v>
+        <v>1027</v>
       </c>
       <c r="H106" t="s">
-        <v>85</v>
+        <v>1029</v>
       </c>
       <c r="I106" t="s">
-        <v>86</v>
+        <v>1030</v>
       </c>
       <c r="J106" t="s">
-        <v>87</v>
+        <v>1031</v>
       </c>
       <c r="K106" t="s">
-        <v>82</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B107">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C107" t="s">
-        <v>284</v>
+        <v>1087</v>
       </c>
       <c r="D107" t="s">
-        <v>377</v>
+        <v>1112</v>
       </c>
       <c r="E107" t="s">
-        <v>378</v>
+        <v>1113</v>
       </c>
       <c r="F107" t="s">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>381</v>
+        <v>1115</v>
       </c>
       <c r="H107" t="s">
-        <v>383</v>
+        <v>1117</v>
       </c>
       <c r="I107" t="s">
-        <v>384</v>
+        <v>1118</v>
       </c>
       <c r="J107" t="s">
-        <v>385</v>
+        <v>1119</v>
       </c>
       <c r="K107" t="s">
-        <v>379</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B108">
         <v>81</v>
       </c>
       <c r="C108" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D108" t="s">
-        <v>499</v>
+        <v>80</v>
       </c>
       <c r="E108" t="s">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="F108" t="s">
-        <v>502</v>
+        <v>25</v>
       </c>
       <c r="G108" t="s">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="H108" t="s">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="I108" t="s">
-        <v>506</v>
+        <v>86</v>
       </c>
       <c r="J108" t="s">
-        <v>507</v>
+        <v>87</v>
       </c>
       <c r="K108" t="s">
-        <v>501</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B109">
         <v>81</v>
       </c>
       <c r="C109" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D109" t="s">
-        <v>616</v>
+        <v>377</v>
       </c>
       <c r="E109" t="s">
-        <v>610</v>
+        <v>378</v>
       </c>
       <c r="F109" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G109" t="s">
-        <v>618</v>
+        <v>381</v>
       </c>
       <c r="H109" t="s">
-        <v>620</v>
+        <v>383</v>
       </c>
       <c r="I109" t="s">
-        <v>621</v>
+        <v>384</v>
       </c>
       <c r="J109" t="s">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="K109" t="s">
-        <v>617</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B110">
         <v>81</v>
       </c>
       <c r="C110" t="s">
-        <v>845</v>
+        <v>473</v>
       </c>
       <c r="D110" t="s">
-        <v>888</v>
+        <v>499</v>
       </c>
       <c r="E110" t="s">
-        <v>889</v>
+        <v>500</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>502</v>
       </c>
       <c r="G110" t="s">
-        <v>891</v>
+        <v>503</v>
       </c>
       <c r="H110" t="s">
-        <v>893</v>
+        <v>505</v>
       </c>
       <c r="I110" t="s">
-        <v>894</v>
+        <v>506</v>
       </c>
       <c r="J110" t="s">
-        <v>895</v>
+        <v>507</v>
       </c>
       <c r="K110" t="s">
-        <v>890</v>
+        <v>501</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B111">
         <v>81</v>
       </c>
       <c r="C111" t="s">
-        <v>1087</v>
+        <v>591</v>
       </c>
       <c r="D111" t="s">
-        <v>1120</v>
+        <v>616</v>
       </c>
       <c r="E111" t="s">
-        <v>1121</v>
+        <v>610</v>
       </c>
       <c r="F111" t="s">
-        <v>1123</v>
+        <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>1124</v>
+        <v>618</v>
       </c>
       <c r="H111" t="s">
-        <v>1126</v>
+        <v>620</v>
       </c>
       <c r="I111" t="s">
-        <v>1127</v>
+        <v>621</v>
       </c>
       <c r="J111" t="s">
-        <v>1128</v>
+        <v>622</v>
       </c>
       <c r="K111" t="s">
-        <v>1122</v>
+        <v>617</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="B112">
+        <v>81</v>
+      </c>
+      <c r="C112" t="s">
+        <v>845</v>
+      </c>
+      <c r="D112" t="s">
+        <v>888</v>
+      </c>
+      <c r="E112" t="s">
+        <v>889</v>
+      </c>
+      <c r="F112" t="s">
+        <v>25</v>
+      </c>
+      <c r="G112" t="s">
+        <v>891</v>
+      </c>
+      <c r="H112" t="s">
+        <v>893</v>
+      </c>
+      <c r="I112" t="s">
+        <v>894</v>
+      </c>
+      <c r="J112" t="s">
+        <v>895</v>
+      </c>
+      <c r="K112" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B113">
+        <v>81</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H113" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J113" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K113" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B114">
         <v>80</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C114" t="s">
         <v>934</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D114" t="s">
         <v>1039</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E114" t="s">
         <v>1040</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F114" t="s">
         <v>1042</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G114" t="s">
         <v>1043</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H114" t="s">
         <v>1045</v>
       </c>
-      <c r="I112" t="s">
+      <c r="I114" t="s">
         <v>1046</v>
       </c>
-      <c r="J112" t="s">
+      <c r="J114" t="s">
         <v>1047</v>
       </c>
-      <c r="K112" t="s">
+      <c r="K114" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="1230">
   <si>
     <t>日期</t>
   </si>
@@ -3527,6 +3527,63 @@
   </si>
   <si>
     <t>强调支架结构设计与材料学（金属/可降解/涂层）研究项目；补充有限元/三维建模等力学仿真技能；结合介入器械工艺与验证经验，展示面向三类器械的规范化研发能力。</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>启明医疗（杭州）</t>
+  </si>
+  <si>
+    <t>负责结构性心脏病/介入医疗器械的研发设计。公司为已上市医疗器械企业(港股02110)，主营经导管瓣膜等结构性心脏病介入器械，自主研发。岗位方向涵盖介入器械结构设计与材料应用。薪资约20-30k·14薪。</t>
+  </si>
+  <si>
+    <t>杭州-滨江区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1982856295.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|介入医疗器械研发岗，属医疗器械方向，企业为结构性心脏病介入上市龙头</t>
+  </si>
+  <si>
+    <t>研究78/技能62/学历95/行业100/企业90</t>
+  </si>
+  <si>
+    <t>杭州创想医学科技有限公司</t>
+  </si>
+  <si>
+    <t>器械研发工程师</t>
+  </si>
+  <si>
+    <t>负责介入/植入器械的研发设计。医疗器械科创企业(A轮，100-499人)，从事介入及植入类医疗器械研发。涉及结构设计、材料选型与工艺验证。薪资约15-30k·13薪。</t>
+  </si>
+  <si>
+    <t>杭州-临平区</t>
+  </si>
+  <si>
+    <t>智能匹配75分【社招】|值得考虑|介入/植入器械研发岗，方向相关，科创企业平台</t>
+  </si>
+  <si>
+    <t>研究72/技能58/学历95/行业100/企业85</t>
+  </si>
+  <si>
+    <t>上海以心医疗器械有限公司</t>
+  </si>
+  <si>
+    <t>输送系统工程师</t>
+  </si>
+  <si>
+    <t>负责介入器械输送系统的研发与结构设计。医疗器械C轮企业，从事介入医疗器械研发。涉及输送系统/导管类产品的结构设计、材料选型与验证。薪资约20-29k·14薪。</t>
+  </si>
+  <si>
+    <t>上海-嘉定区</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|介入器械输送系统研发岗，属介入导管/输送系统方向，与血管支架输送关联</t>
+  </si>
+  <si>
+    <t>研究80/技能60/学历95/行业100/企业88</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4081,7 +4138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L156"/>
+  <dimension ref="A1:L159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10023,6 +10080,120 @@
       </c>
       <c r="L156" t="s">
         <v>1170</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C157" t="s">
+        <v>122</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F157" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G157">
+        <v>8</v>
+      </c>
+      <c r="H157" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I157">
+        <v>79</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K157" t="s">
+        <v>79</v>
+      </c>
+      <c r="L157" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E158" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G158">
+        <v>8</v>
+      </c>
+      <c r="H158" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I158">
+        <v>75</v>
+      </c>
+      <c r="J158" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K158" t="s">
+        <v>79</v>
+      </c>
+      <c r="L158" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G159">
+        <v>8</v>
+      </c>
+      <c r="H159" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I159">
+        <v>79</v>
+      </c>
+      <c r="J159" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K159" t="s">
+        <v>79</v>
+      </c>
+      <c r="L159" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -10056,7 +10227,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1171</v>
+        <v>1190</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10065,16 +10236,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1173</v>
+        <v>1192</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1175</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10088,13 +10259,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1176</v>
+        <v>1195</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1178</v>
+        <v>1197</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -10122,7 +10293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10137,7 +10308,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10147,31 +10318,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="B4">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="B5" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -10179,7 +10350,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1190</v>
+        <v>1209</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -10187,7 +10358,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1191</v>
+        <v>1210</v>
       </c>
       <c r="B8">
         <v>77</v>
@@ -10195,15 +10366,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1192</v>
+        <v>1211</v>
       </c>
       <c r="B9">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1193</v>
+        <v>1212</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -10211,15 +10382,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="B11" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10229,15 +10400,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1196</v>
+        <v>1215</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1197</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1198</v>
+        <v>1217</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -10245,7 +10416,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="B17" s="5">
         <v>71</v>
@@ -10253,15 +10424,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1200</v>
+        <v>1219</v>
       </c>
       <c r="B18" s="5">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="B19" s="5">
         <v>5</v>
@@ -10269,7 +10440,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1202</v>
+        <v>1221</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10277,7 +10448,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1203</v>
+        <v>1222</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -10285,7 +10456,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1204</v>
+        <v>1223</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -10293,7 +10464,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -10301,7 +10472,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -10309,7 +10480,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -10317,7 +10488,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -10329,7 +10500,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -10347,7 +10518,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -14258,25 +14429,25 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>159</v>
+        <v>1171</v>
       </c>
       <c r="C180" t="s">
-        <v>271</v>
+        <v>1172</v>
       </c>
       <c r="D180" t="s">
-        <v>272</v>
+        <v>122</v>
       </c>
       <c r="E180" t="s">
-        <v>75</v>
+        <v>1174</v>
       </c>
       <c r="F180" t="s">
-        <v>274</v>
+        <v>1175</v>
       </c>
       <c r="G180">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>275</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -14284,25 +14455,25 @@
         <v>152</v>
       </c>
       <c r="B181" t="s">
-        <v>591</v>
+        <v>1171</v>
       </c>
       <c r="C181" t="s">
-        <v>681</v>
+        <v>1178</v>
       </c>
       <c r="D181" t="s">
-        <v>682</v>
+        <v>1179</v>
       </c>
       <c r="E181" t="s">
-        <v>25</v>
+        <v>1181</v>
       </c>
       <c r="F181" t="s">
-        <v>684</v>
+        <v>1175</v>
       </c>
       <c r="G181">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>685</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -14310,25 +14481,25 @@
         <v>153</v>
       </c>
       <c r="B182" t="s">
-        <v>591</v>
+        <v>1171</v>
       </c>
       <c r="C182" t="s">
-        <v>689</v>
+        <v>1184</v>
       </c>
       <c r="D182" t="s">
-        <v>690</v>
+        <v>1185</v>
       </c>
       <c r="E182" t="s">
-        <v>66</v>
+        <v>1187</v>
       </c>
       <c r="F182" t="s">
-        <v>692</v>
+        <v>1175</v>
       </c>
       <c r="G182">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>693</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -14336,25 +14507,25 @@
         <v>154</v>
       </c>
       <c r="B183" t="s">
-        <v>697</v>
+        <v>159</v>
       </c>
       <c r="C183" t="s">
-        <v>767</v>
+        <v>271</v>
       </c>
       <c r="D183" t="s">
-        <v>768</v>
+        <v>272</v>
       </c>
       <c r="E183" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F183" t="s">
-        <v>770</v>
+        <v>274</v>
       </c>
       <c r="G183">
         <v>7</v>
       </c>
       <c r="H183" t="s">
-        <v>771</v>
+        <v>275</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -14362,24 +14533,102 @@
         <v>155</v>
       </c>
       <c r="B184" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="C184" t="s">
-        <v>927</v>
+        <v>681</v>
       </c>
       <c r="D184" t="s">
-        <v>585</v>
+        <v>682</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>929</v>
+        <v>684</v>
       </c>
       <c r="G184">
         <v>7</v>
       </c>
       <c r="H184" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>156</v>
+      </c>
+      <c r="B185" t="s">
+        <v>591</v>
+      </c>
+      <c r="C185" t="s">
+        <v>689</v>
+      </c>
+      <c r="D185" t="s">
+        <v>690</v>
+      </c>
+      <c r="E185" t="s">
+        <v>66</v>
+      </c>
+      <c r="F185" t="s">
+        <v>692</v>
+      </c>
+      <c r="G185">
+        <v>7</v>
+      </c>
+      <c r="H185" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>157</v>
+      </c>
+      <c r="B186" t="s">
+        <v>697</v>
+      </c>
+      <c r="C186" t="s">
+        <v>767</v>
+      </c>
+      <c r="D186" t="s">
+        <v>768</v>
+      </c>
+      <c r="E186" t="s">
+        <v>25</v>
+      </c>
+      <c r="F186" t="s">
+        <v>770</v>
+      </c>
+      <c r="G186">
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>158</v>
+      </c>
+      <c r="B187" t="s">
+        <v>845</v>
+      </c>
+      <c r="C187" t="s">
+        <v>927</v>
+      </c>
+      <c r="D187" t="s">
+        <v>585</v>
+      </c>
+      <c r="E187" t="s">
+        <v>25</v>
+      </c>
+      <c r="F187" t="s">
+        <v>929</v>
+      </c>
+      <c r="G187">
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
         <v>930</v>
       </c>
     </row>
@@ -14413,10 +14662,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1180</v>
+        <v>1199</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -14443,12 +14692,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -14483,7 +14732,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -14518,7 +14767,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -14553,7 +14802,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -14588,7 +14837,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -14623,7 +14872,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -14658,7 +14907,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -14693,7 +14942,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -14728,7 +14977,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -14763,7 +15012,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -14798,7 +15047,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -14833,7 +15082,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -14868,7 +15117,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -14903,7 +15152,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -14938,7 +15187,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -14973,7 +15222,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -15008,7 +15257,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -15043,7 +15292,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -15078,7 +15327,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -15113,7 +15362,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -15148,7 +15397,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -15183,7 +15432,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -15218,7 +15467,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -15253,7 +15502,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B25">
         <v>89</v>
@@ -15288,7 +15537,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -15323,7 +15572,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -15358,7 +15607,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -15393,7 +15642,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -15428,7 +15677,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -15463,7 +15712,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -15498,7 +15747,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -15533,7 +15782,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -15568,7 +15817,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B34">
         <v>88</v>
@@ -15603,7 +15852,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B35">
         <v>88</v>
@@ -15638,7 +15887,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B36">
         <v>88</v>
@@ -15673,7 +15922,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B37">
         <v>88</v>
@@ -15708,7 +15957,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B38">
         <v>88</v>
@@ -15743,7 +15992,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B39">
         <v>88</v>
@@ -15778,7 +16027,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B40">
         <v>88</v>
@@ -15813,7 +16062,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B41">
         <v>88</v>
@@ -15848,7 +16097,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B42">
         <v>87</v>
@@ -15883,7 +16132,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B43">
         <v>87</v>
@@ -15918,7 +16167,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B44">
         <v>87</v>
@@ -15953,7 +16202,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B45">
         <v>87</v>
@@ -15988,7 +16237,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B46">
         <v>87</v>
@@ -16023,7 +16272,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B47">
         <v>87</v>
@@ -16058,7 +16307,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B48">
         <v>87</v>
@@ -16093,7 +16342,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B49">
         <v>87</v>
@@ -16128,7 +16377,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B50">
         <v>87</v>
@@ -16163,7 +16412,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B51">
         <v>87</v>
@@ -16198,7 +16447,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B52">
         <v>86</v>
@@ -16233,7 +16482,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B53">
         <v>86</v>
@@ -16268,7 +16517,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B54">
         <v>86</v>
@@ -16303,7 +16552,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B55">
         <v>86</v>
@@ -16338,7 +16587,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B56">
         <v>86</v>
@@ -16373,7 +16622,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B57">
         <v>86</v>
@@ -16408,7 +16657,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B58">
         <v>86</v>
@@ -16443,7 +16692,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B59">
         <v>86</v>
@@ -16478,7 +16727,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B60">
         <v>86</v>
@@ -16513,7 +16762,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B61">
         <v>86</v>
@@ -16548,7 +16797,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -16583,7 +16832,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B63">
         <v>86</v>
@@ -16618,7 +16867,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B64">
         <v>86</v>
@@ -16653,7 +16902,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B65">
         <v>86</v>
@@ -16688,7 +16937,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B66">
         <v>86</v>
@@ -16723,7 +16972,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B67">
         <v>86</v>
@@ -16758,7 +17007,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B68">
         <v>86</v>
@@ -16793,7 +17042,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B69">
         <v>85</v>
@@ -16828,7 +17077,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B70">
         <v>85</v>
@@ -16863,7 +17112,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B71">
         <v>85</v>
@@ -16898,7 +17147,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B72">
         <v>85</v>
@@ -16933,7 +17182,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B73">
         <v>85</v>
@@ -16968,7 +17217,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B74">
         <v>85</v>
@@ -17003,7 +17252,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B75">
         <v>85</v>
@@ -17038,7 +17287,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B76">
         <v>85</v>
@@ -17073,7 +17322,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B77">
         <v>85</v>
@@ -17108,7 +17357,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B78">
         <v>85</v>
@@ -17143,7 +17392,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B79">
         <v>84</v>
@@ -17178,7 +17427,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B80">
         <v>84</v>
@@ -17213,7 +17462,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B81">
         <v>84</v>
@@ -17248,7 +17497,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B82">
         <v>84</v>
@@ -17283,7 +17532,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B83">
         <v>84</v>
@@ -17318,7 +17567,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B84">
         <v>84</v>
@@ -17353,7 +17602,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B85">
         <v>84</v>
@@ -17388,7 +17637,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B86">
         <v>84</v>
@@ -17423,7 +17672,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B87">
         <v>84</v>
@@ -17458,7 +17707,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B88">
         <v>84</v>
@@ -17493,7 +17742,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B89">
         <v>84</v>
@@ -17528,7 +17777,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B90">
         <v>84</v>
@@ -17563,7 +17812,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B91">
         <v>84</v>
@@ -17598,7 +17847,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B92">
         <v>84</v>
@@ -17633,7 +17882,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B93">
         <v>83</v>
@@ -17668,7 +17917,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B94">
         <v>83</v>
@@ -17703,7 +17952,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B95">
         <v>83</v>
@@ -17738,7 +17987,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B96">
         <v>83</v>
@@ -17773,7 +18022,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B97">
         <v>83</v>
@@ -17808,7 +18057,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B98">
         <v>83</v>
@@ -17843,7 +18092,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B99">
         <v>83</v>
@@ -17878,7 +18127,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B100">
         <v>83</v>
@@ -17913,7 +18162,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B101">
         <v>82</v>
@@ -17948,7 +18197,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B102">
         <v>82</v>
@@ -17983,7 +18232,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B103">
         <v>82</v>
@@ -18018,7 +18267,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B104">
         <v>82</v>
@@ -18053,7 +18302,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B105">
         <v>82</v>
@@ -18088,7 +18337,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B106">
         <v>82</v>
@@ -18123,7 +18372,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B107">
         <v>82</v>
@@ -18158,7 +18407,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B108">
         <v>81</v>
@@ -18193,7 +18442,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B109">
         <v>81</v>
@@ -18228,7 +18477,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B110">
         <v>81</v>
@@ -18263,7 +18512,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B111">
         <v>81</v>
@@ -18298,7 +18547,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B112">
         <v>81</v>
@@ -18333,7 +18582,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B113">
         <v>81</v>
@@ -18368,7 +18617,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="B114">
         <v>80</v>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="1267">
   <si>
     <t>日期</t>
   </si>
@@ -3584,6 +3584,117 @@
   </si>
   <si>
     <t>研究80/技能60/学历95/行业100/企业88</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>赛诺医疗科学技术股份有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师-编织支架</t>
+  </si>
+  <si>
+    <t>理工类硕士（机械/高分子/金属材料等，欢迎应届），负责编织支架工艺开发、设备调试、参数摸索与工艺转移，参与血管介入支架新产品研发。</t>
+  </si>
+  <si>
+    <t>苏州-吴中区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1983585239.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配91分【社招(欢迎应届)】|强烈推荐|编织血管支架研发岗，方向直接相关，工学硕士可投（欢迎应届），苏州</t>
+  </si>
+  <si>
+    <t>研究90/技能85/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>血管支架研发与候选人研究方向完全吻合，岗位明确欢迎应届工学硕士（材料/机械/高分子均符），可降解/镍钛支架的编织工艺与候选人支架设计和材料学技能高度重合；赛诺医疗为科创板上市介入器械企业，平台与岗位双匹配，是本轮最值得投递的岗位。</t>
+  </si>
+  <si>
+    <t>简历重点突出金属/高分子材料学与支架结构/编织工艺相关项目，明确列出可使用SolidWorks/有限元等结构设计能力；强调在校或课题中血管支架样件、性能测试与工艺摸索经验，补充学历为金属/高分子材料相关工学硕士，突出可立即参与编织支架工艺开发。</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>科塞尔医疗科技（苏州）股份有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（冷冻球囊）</t>
+  </si>
+  <si>
+    <t>硕士及以上（生医工/高分子/流体力学，应届可投），负责冷冻球囊（介入球囊）产品设计开发、性能验证与测试平台搭建，隶属泛血管介入器械方向。</t>
+  </si>
+  <si>
+    <t>苏州-虎丘区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1975825751.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配83分【校招/社招（应届可投）】|强烈推荐|介入球囊设计开发岗，泛血管介入方向相关，硕士应届可投，苏州</t>
+  </si>
+  <si>
+    <t>研究82/技能72/学历100/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位属泛血管植介入球囊研发，与候选人血管介入器械方向吻合；明确硕士及以上且应届可投，候选人学历完全符合；生医工/高分子方向也对口，可作为血管支架之外的强相关介入岗位备选投递，扩大上海/苏州产业圈命中率。</t>
+  </si>
+  <si>
+    <t>突出生物医学工程与高分子材料背景，将血管支架课题中涉及管材/球囊类输送与结构设计经验前置；量化性能验证与测试平台搭建经验，并补充流体力学/有限元分析技能；强调可立即投入介入球囊产品开发与验证。</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>环心医疗科技（苏州）有限公司</t>
+  </si>
+  <si>
+    <t>本科3-5年，熟悉管材类产品设计与编织/reflow/绕簧/海波管/控弯等工艺，有二三类血管介入产品研发经验优先，负责介入导管/输送类医疗器械研发。</t>
+  </si>
+  <si>
+    <t>苏州-工业园区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1972481969.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配82分【社招】|强烈推荐|血管介入导管/编织类产品研发岗，介入器械方向高度匹配，硕士可投，苏州工业园</t>
+  </si>
+  <si>
+    <t>研究80/技能72/学历95/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位为血管介入器械（导管/编织/输送类）研发，与候选人血管介入方向契合；虽偏好3-5年经验，但要求本科及以上，硕士学历可投，苏州工业园为优先城市；作为介入器械方向强相关岗位值得尝试。</t>
+  </si>
+  <si>
+    <t>重点突出血管介入器械课题中管材、编织、输送系统相关结构设计经验，弱化年限短板、强化可加分的技术点（SolidWorks、有限元、材料选型）；补充血管介入方向课程与项目，说明可快速上手介入导管类产品研发。</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>南京大学（生物医学工程学院·张弢课题组）</t>
+  </si>
+  <si>
+    <t>特任助理研究员</t>
+  </si>
+  <si>
+    <t>博士，38岁以下，熟悉IVUS/ICE泛血管超声成像及超声能量消融（RDN）方向，承担泛血管植介入超声器械研发与产业化，有科研与产业经验者优先。</t>
+  </si>
+  <si>
+    <t>南京</t>
+  </si>
+  <si>
+    <t>https://rczp.nju.edu.cn//yjxlhbsh/trxl/trxlgwlb/20260811/i407617.html</t>
+  </si>
+  <si>
+    <t>智能匹配71分【科研岗】|值得考虑|泛血管植介入超声器械科研岗，介入方向相关，但要求博士、方向为超声消融非支架（匹配度一般）</t>
+  </si>
+  <si>
+    <t>研究80/技能58/学历50/行业90/企业90</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4138,7 +4249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L159"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10193,6 +10304,158 @@
         <v>79</v>
       </c>
       <c r="L159" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E160" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G160">
+        <v>9</v>
+      </c>
+      <c r="H160" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I160">
+        <v>91</v>
+      </c>
+      <c r="J160" t="s">
+        <v>1197</v>
+      </c>
+      <c r="K160" t="s">
+        <v>1198</v>
+      </c>
+      <c r="L160" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G161">
+        <v>8</v>
+      </c>
+      <c r="H161" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I161">
+        <v>83</v>
+      </c>
+      <c r="J161" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K161" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L161" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C162" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G162">
+        <v>8</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I162">
+        <v>82</v>
+      </c>
+      <c r="J162" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K162" t="s">
+        <v>1217</v>
+      </c>
+      <c r="L162" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E163" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G163">
+        <v>7</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I163">
+        <v>71</v>
+      </c>
+      <c r="J163" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K163" t="s">
+        <v>79</v>
+      </c>
+      <c r="L163" t="s">
         <v>79</v>
       </c>
     </row>
@@ -10227,7 +10490,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1190</v>
+        <v>1227</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10236,16 +10499,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1194</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10259,13 +10522,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1195</v>
+        <v>1232</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1196</v>
+        <v>1233</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1197</v>
+        <v>1234</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -10293,7 +10556,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10308,7 +10571,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10318,31 +10581,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1203</v>
+        <v>1240</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1204</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1205</v>
+        <v>1242</v>
       </c>
       <c r="B4">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1206</v>
+        <v>1243</v>
       </c>
       <c r="B5" t="s">
-        <v>1207</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1208</v>
+        <v>1245</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -10350,7 +10613,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1209</v>
+        <v>1246</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -10358,39 +10621,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1210</v>
+        <v>1247</v>
       </c>
       <c r="B8">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1211</v>
+        <v>1248</v>
       </c>
       <c r="B9">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1212</v>
+        <v>1249</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1213</v>
+        <v>1250</v>
       </c>
       <c r="B11" t="s">
-        <v>1171</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1214</v>
+        <v>1251</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10400,15 +10663,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1215</v>
+        <v>1252</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1216</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1217</v>
+        <v>1254</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -10416,31 +10679,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1218</v>
+        <v>1255</v>
       </c>
       <c r="B17" s="5">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1219</v>
+        <v>1256</v>
       </c>
       <c r="B18" s="5">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1220</v>
+        <v>1257</v>
       </c>
       <c r="B19" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1221</v>
+        <v>1258</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10448,7 +10711,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1222</v>
+        <v>1259</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -10456,7 +10719,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1223</v>
+        <v>1260</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -10464,7 +10727,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1224</v>
+        <v>1261</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -10472,7 +10735,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1225</v>
+        <v>1262</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -10480,7 +10743,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1226</v>
+        <v>1263</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -10488,7 +10751,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1227</v>
+        <v>1264</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -10500,7 +10763,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1228</v>
+        <v>1265</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -10518,7 +10781,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1229</v>
+        <v>1266</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -10685,25 +10948,25 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>1190</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>1191</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>1192</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>1194</v>
       </c>
       <c r="F36" t="s">
-        <v>26</v>
+        <v>1195</v>
       </c>
       <c r="G36">
         <v>9</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -10714,22 +10977,22 @@
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G37">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -10740,22 +11003,22 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G38">
         <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -10766,22 +11029,22 @@
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G39">
         <v>9</v>
       </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -10792,22 +11055,22 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G40">
         <v>9</v>
       </c>
       <c r="H40" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -10818,22 +11081,22 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F41" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="G41">
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -10844,22 +11107,22 @@
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
         <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G42">
         <v>9</v>
       </c>
       <c r="H42" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -10870,22 +11133,22 @@
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
         <v>89</v>
       </c>
       <c r="E43" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="G43">
         <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -10896,22 +11159,22 @@
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F44" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G44">
         <v>9</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10919,25 +11182,25 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="G45">
         <v>9</v>
       </c>
       <c r="H45" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -10948,22 +11211,22 @@
         <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G46">
         <v>9</v>
       </c>
       <c r="H46" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -10974,22 +11237,22 @@
         <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="G47">
         <v>9</v>
       </c>
       <c r="H47" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -11000,22 +11263,22 @@
         <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G48">
         <v>9</v>
       </c>
       <c r="H48" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -11026,22 +11289,22 @@
         <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D49" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="F49" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="G49">
         <v>9</v>
       </c>
       <c r="H49" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -11052,22 +11315,22 @@
         <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="F50" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G50">
         <v>9</v>
       </c>
       <c r="H50" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -11078,22 +11341,22 @@
         <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="D51" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="G51">
         <v>9</v>
       </c>
       <c r="H51" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -11101,25 +11364,25 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="D52" t="s">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="E52" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="F52" t="s">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="G52">
         <v>9</v>
       </c>
       <c r="H52" t="s">
-        <v>304</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -11133,19 +11396,19 @@
         <v>300</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E53" t="s">
         <v>147</v>
       </c>
       <c r="F53" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G53">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -11156,22 +11419,22 @@
         <v>284</v>
       </c>
       <c r="C54" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="D54" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="E54" t="s">
-        <v>333</v>
+        <v>147</v>
       </c>
       <c r="F54" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="G54">
         <v>9</v>
       </c>
       <c r="H54" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -11182,22 +11445,22 @@
         <v>284</v>
       </c>
       <c r="C55" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D55" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="E55" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F55" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="G55">
         <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -11208,22 +11471,22 @@
         <v>284</v>
       </c>
       <c r="C56" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D56" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="F56" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="G56">
         <v>9</v>
       </c>
       <c r="H56" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -11234,22 +11497,22 @@
         <v>284</v>
       </c>
       <c r="C57" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="D57" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="E57" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="G57">
         <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -11257,25 +11520,25 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
       <c r="D58" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="G58">
         <v>9</v>
       </c>
       <c r="H58" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -11286,22 +11549,22 @@
         <v>402</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="G59">
         <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -11315,7 +11578,7 @@
         <v>63</v>
       </c>
       <c r="D60" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E60" t="s">
         <v>66</v>
@@ -11327,7 +11590,7 @@
         <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -11341,7 +11604,7 @@
         <v>63</v>
       </c>
       <c r="D61" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E61" t="s">
         <v>66</v>
@@ -11353,7 +11616,7 @@
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -11367,7 +11630,7 @@
         <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E62" t="s">
         <v>66</v>
@@ -11379,7 +11642,7 @@
         <v>9</v>
       </c>
       <c r="H62" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -11393,7 +11656,7 @@
         <v>63</v>
       </c>
       <c r="D63" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E63" t="s">
         <v>66</v>
@@ -11405,7 +11668,7 @@
         <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -11419,7 +11682,7 @@
         <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E64" t="s">
         <v>66</v>
@@ -11431,7 +11694,7 @@
         <v>9</v>
       </c>
       <c r="H64" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -11442,22 +11705,22 @@
         <v>402</v>
       </c>
       <c r="C65" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E65" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F65" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="G65">
         <v>9</v>
       </c>
       <c r="H65" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -11465,25 +11728,25 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C66" t="s">
-        <v>474</v>
+        <v>322</v>
       </c>
       <c r="D66" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E66" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G66">
         <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -11494,22 +11757,22 @@
         <v>473</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>474</v>
       </c>
       <c r="D67" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="E67" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="F67" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="G67">
         <v>9</v>
       </c>
       <c r="H67" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -11520,22 +11783,22 @@
         <v>473</v>
       </c>
       <c r="C68" t="s">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E68" t="s">
-        <v>66</v>
+        <v>510</v>
       </c>
       <c r="F68" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="G68">
         <v>9</v>
       </c>
       <c r="H68" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -11546,22 +11809,22 @@
         <v>473</v>
       </c>
       <c r="C69" t="s">
-        <v>523</v>
+        <v>285</v>
       </c>
       <c r="D69" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E69" t="s">
-        <v>526</v>
+        <v>66</v>
       </c>
       <c r="F69" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="G69">
         <v>9</v>
       </c>
       <c r="H69" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -11572,22 +11835,22 @@
         <v>473</v>
       </c>
       <c r="C70" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="E70" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="F70" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="G70">
         <v>9</v>
       </c>
       <c r="H70" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -11595,25 +11858,25 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C71" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="D71" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="E71" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="F71" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="G71">
         <v>9</v>
       </c>
       <c r="H71" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -11627,7 +11890,7 @@
         <v>557</v>
       </c>
       <c r="D72" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E72" t="s">
         <v>16</v>
@@ -11639,7 +11902,7 @@
         <v>9</v>
       </c>
       <c r="H72" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -11650,22 +11913,22 @@
         <v>556</v>
       </c>
       <c r="C73" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="D73" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="E73" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>573</v>
+        <v>468</v>
       </c>
       <c r="G73">
         <v>9</v>
       </c>
       <c r="H73" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -11673,25 +11936,25 @@
         <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C74" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="D74" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="E74" t="s">
-        <v>595</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="G74">
         <v>9</v>
       </c>
       <c r="H74" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -11702,22 +11965,22 @@
         <v>591</v>
       </c>
       <c r="C75" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="D75" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>595</v>
       </c>
       <c r="F75" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="G75">
         <v>9</v>
       </c>
       <c r="H75" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -11728,22 +11991,22 @@
         <v>591</v>
       </c>
       <c r="C76" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="D76" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="E76" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="G76">
         <v>9</v>
       </c>
       <c r="H76" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -11754,22 +12017,22 @@
         <v>591</v>
       </c>
       <c r="C77" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="D77" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="G77">
         <v>9</v>
       </c>
       <c r="H77" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -11777,25 +12040,25 @@
         <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C78" t="s">
-        <v>698</v>
+        <v>635</v>
       </c>
       <c r="D78" t="s">
-        <v>699</v>
+        <v>636</v>
       </c>
       <c r="E78" t="s">
-        <v>701</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>702</v>
+        <v>638</v>
       </c>
       <c r="G78">
         <v>9</v>
       </c>
       <c r="H78" t="s">
-        <v>703</v>
+        <v>639</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -11806,22 +12069,22 @@
         <v>697</v>
       </c>
       <c r="C79" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="D79" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="E79" t="s">
-        <v>318</v>
+        <v>701</v>
       </c>
       <c r="F79" t="s">
-        <v>604</v>
+        <v>702</v>
       </c>
       <c r="G79">
         <v>9</v>
       </c>
       <c r="H79" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -11829,25 +12092,25 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C80" t="s">
-        <v>774</v>
+        <v>707</v>
       </c>
       <c r="D80" t="s">
-        <v>775</v>
+        <v>708</v>
       </c>
       <c r="E80" t="s">
-        <v>777</v>
+        <v>318</v>
       </c>
       <c r="F80" t="s">
-        <v>778</v>
+        <v>604</v>
       </c>
       <c r="G80">
         <v>9</v>
       </c>
       <c r="H80" t="s">
-        <v>779</v>
+        <v>710</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -11861,19 +12124,19 @@
         <v>774</v>
       </c>
       <c r="D81" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="E81" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="F81" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="G81">
         <v>9</v>
       </c>
       <c r="H81" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -11884,22 +12147,22 @@
         <v>773</v>
       </c>
       <c r="C82" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="D82" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="E82" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="F82" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="G82">
         <v>9</v>
       </c>
       <c r="H82" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -11910,22 +12173,22 @@
         <v>773</v>
       </c>
       <c r="C83" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="D83" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="E83" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="F83" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="G83">
         <v>9</v>
       </c>
       <c r="H83" t="s">
-        <v>825</v>
+        <v>803</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -11936,22 +12199,22 @@
         <v>773</v>
       </c>
       <c r="C84" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="D84" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="E84" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="F84" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="G84">
         <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -11962,22 +12225,22 @@
         <v>773</v>
       </c>
       <c r="C85" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D85" t="s">
-        <v>610</v>
+        <v>830</v>
       </c>
       <c r="E85" t="s">
-        <v>839</v>
+        <v>785</v>
       </c>
       <c r="F85" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="G85">
         <v>9</v>
       </c>
       <c r="H85" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -11985,25 +12248,25 @@
         <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C86" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="D86" t="s">
-        <v>847</v>
+        <v>610</v>
       </c>
       <c r="E86" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="F86" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="G86">
         <v>9</v>
       </c>
       <c r="H86" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -12014,22 +12277,22 @@
         <v>845</v>
       </c>
       <c r="C87" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="D87" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="E87" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="F87" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="G87">
         <v>9</v>
       </c>
       <c r="H87" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -12040,22 +12303,22 @@
         <v>845</v>
       </c>
       <c r="C88" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="D88" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>858</v>
       </c>
       <c r="F88" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="G88">
         <v>9</v>
       </c>
       <c r="H88" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -12066,22 +12329,22 @@
         <v>845</v>
       </c>
       <c r="C89" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="D89" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="E89" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="G89">
         <v>9</v>
       </c>
       <c r="H89" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -12092,22 +12355,22 @@
         <v>845</v>
       </c>
       <c r="C90" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="D90" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="F90" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="G90">
         <v>9</v>
       </c>
       <c r="H90" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -12115,25 +12378,25 @@
         <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C91" t="s">
-        <v>277</v>
+        <v>880</v>
       </c>
       <c r="D91" t="s">
-        <v>935</v>
+        <v>881</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>937</v>
+        <v>883</v>
       </c>
       <c r="G91">
         <v>9</v>
       </c>
       <c r="H91" t="s">
-        <v>938</v>
+        <v>884</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -12144,22 +12407,22 @@
         <v>934</v>
       </c>
       <c r="C92" t="s">
-        <v>942</v>
+        <v>277</v>
       </c>
       <c r="D92" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="E92" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="G92">
         <v>9</v>
       </c>
       <c r="H92" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -12170,22 +12433,22 @@
         <v>934</v>
       </c>
       <c r="C93" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="D93" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="E93" t="s">
         <v>66</v>
       </c>
       <c r="F93" t="s">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="G93">
         <v>9</v>
       </c>
       <c r="H93" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -12196,22 +12459,22 @@
         <v>934</v>
       </c>
       <c r="C94" t="s">
-        <v>643</v>
+        <v>950</v>
       </c>
       <c r="D94" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F94" t="s">
-        <v>959</v>
+        <v>438</v>
       </c>
       <c r="G94">
         <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -12222,22 +12485,22 @@
         <v>934</v>
       </c>
       <c r="C95" t="s">
-        <v>973</v>
+        <v>643</v>
       </c>
       <c r="D95" t="s">
-        <v>974</v>
+        <v>957</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>468</v>
+        <v>959</v>
       </c>
       <c r="G95">
         <v>9</v>
       </c>
       <c r="H95" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -12248,22 +12511,22 @@
         <v>934</v>
       </c>
       <c r="C96" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="D96" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E96" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="G96">
         <v>9</v>
       </c>
       <c r="H96" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -12274,22 +12537,22 @@
         <v>934</v>
       </c>
       <c r="C97" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="D97" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>983</v>
       </c>
       <c r="F97" t="s">
-        <v>959</v>
+        <v>984</v>
       </c>
       <c r="G97">
         <v>9</v>
       </c>
       <c r="H97" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -12300,22 +12563,22 @@
         <v>934</v>
       </c>
       <c r="C98" t="s">
-        <v>950</v>
+        <v>989</v>
       </c>
       <c r="D98" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="E98" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F98" t="s">
-        <v>438</v>
+        <v>959</v>
       </c>
       <c r="G98">
         <v>9</v>
       </c>
       <c r="H98" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -12326,22 +12589,22 @@
         <v>934</v>
       </c>
       <c r="C99" t="s">
-        <v>1065</v>
+        <v>950</v>
       </c>
       <c r="D99" t="s">
-        <v>1066</v>
+        <v>996</v>
       </c>
       <c r="E99" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="F99" t="s">
-        <v>1068</v>
+        <v>438</v>
       </c>
       <c r="G99">
         <v>9</v>
       </c>
       <c r="H99" t="s">
-        <v>1069</v>
+        <v>998</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -12352,22 +12615,22 @@
         <v>934</v>
       </c>
       <c r="C100" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
       <c r="D100" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="E100" t="s">
-        <v>1076</v>
+        <v>147</v>
       </c>
       <c r="F100" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="G100">
         <v>9</v>
       </c>
       <c r="H100" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -12375,25 +12638,25 @@
         <v>72</v>
       </c>
       <c r="B101" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C101" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="D101" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="E101" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="F101" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="G101">
         <v>9</v>
       </c>
       <c r="H101" t="s">
-        <v>1093</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -12404,22 +12667,22 @@
         <v>1087</v>
       </c>
       <c r="C102" t="s">
-        <v>964</v>
+        <v>1088</v>
       </c>
       <c r="D102" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="E102" t="s">
-        <v>16</v>
+        <v>1091</v>
       </c>
       <c r="F102" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="G102">
         <v>9</v>
       </c>
       <c r="H102" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -12430,22 +12693,22 @@
         <v>1087</v>
       </c>
       <c r="C103" t="s">
-        <v>1138</v>
+        <v>964</v>
       </c>
       <c r="D103" t="s">
-        <v>1139</v>
+        <v>1097</v>
       </c>
       <c r="E103" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>1141</v>
+        <v>1099</v>
       </c>
       <c r="G103">
         <v>9</v>
       </c>
       <c r="H103" t="s">
-        <v>1142</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -12456,22 +12719,22 @@
         <v>1087</v>
       </c>
       <c r="C104" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="D104" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="E104" t="s">
-        <v>1149</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>1150</v>
+        <v>1141</v>
       </c>
       <c r="G104">
         <v>9</v>
       </c>
       <c r="H104" t="s">
-        <v>1151</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -12479,25 +12742,25 @@
         <v>76</v>
       </c>
       <c r="B105" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="C105" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="D105" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
       <c r="E105" t="s">
-        <v>147</v>
+        <v>1149</v>
       </c>
       <c r="F105" t="s">
-        <v>1159</v>
+        <v>1150</v>
       </c>
       <c r="G105">
         <v>9</v>
       </c>
       <c r="H105" t="s">
-        <v>1160</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -12508,22 +12771,22 @@
         <v>1155</v>
       </c>
       <c r="C106" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="D106" t="s">
-        <v>610</v>
+        <v>1157</v>
       </c>
       <c r="E106" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F106" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="G106">
         <v>9</v>
       </c>
       <c r="H106" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -12531,25 +12794,25 @@
         <v>78</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="C107" t="s">
-        <v>72</v>
+        <v>1164</v>
       </c>
       <c r="D107" t="s">
-        <v>73</v>
+        <v>610</v>
       </c>
       <c r="E107" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>1166</v>
       </c>
       <c r="G107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H107" t="s">
-        <v>77</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -12557,25 +12820,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C108" t="s">
-        <v>80</v>
+        <v>1201</v>
       </c>
       <c r="D108" t="s">
-        <v>81</v>
+        <v>1202</v>
       </c>
       <c r="E108" t="s">
-        <v>25</v>
+        <v>1204</v>
       </c>
       <c r="F108" t="s">
-        <v>83</v>
+        <v>1205</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108" t="s">
-        <v>84</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -12586,22 +12849,22 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D109" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E109" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F109" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -12612,22 +12875,22 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D110" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E110" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F110" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -12638,22 +12901,22 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D111" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E111" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F111" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -12664,22 +12927,22 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D112" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E112" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -12690,22 +12953,22 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E113" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -12716,22 +12979,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D114" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F114" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -12739,25 +13002,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="F115" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -12765,25 +13028,25 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="E116" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -12794,22 +13057,22 @@
         <v>159</v>
       </c>
       <c r="C117" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D117" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E117" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="F117" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -12820,22 +13083,22 @@
         <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D118" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="E118" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="F118" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -12846,22 +13109,22 @@
         <v>159</v>
       </c>
       <c r="C119" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D119" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E119" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="F119" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -12872,22 +13135,22 @@
         <v>159</v>
       </c>
       <c r="C120" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F120" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -12898,22 +13161,22 @@
         <v>159</v>
       </c>
       <c r="C121" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D121" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -12924,22 +13187,22 @@
         <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D122" t="s">
-        <v>255</v>
+        <v>154</v>
       </c>
       <c r="E122" t="s">
-        <v>257</v>
+        <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -12950,22 +13213,22 @@
         <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D123" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="E123" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -12976,22 +13239,22 @@
         <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D124" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F124" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13002,22 +13265,22 @@
         <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D125" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E125" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="F125" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -13025,25 +13288,25 @@
         <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="E126" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="F126" t="s">
-        <v>319</v>
+        <v>58</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -13051,25 +13314,25 @@
         <v>98</v>
       </c>
       <c r="B127" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="D127" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="E127" t="s">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="F127" t="s">
-        <v>342</v>
+        <v>281</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -13080,22 +13343,22 @@
         <v>284</v>
       </c>
       <c r="C128" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D128" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E128" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="F128" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -13106,22 +13369,22 @@
         <v>284</v>
       </c>
       <c r="C129" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D129" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E129" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="F129" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -13132,22 +13395,22 @@
         <v>284</v>
       </c>
       <c r="C130" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="E130" t="s">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="F130" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -13158,22 +13421,22 @@
         <v>284</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E131" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F131" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -13181,25 +13444,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C132" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D132" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E132" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F132" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -13207,25 +13470,25 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C133" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="D133" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="E133" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F133" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -13236,22 +13499,22 @@
         <v>402</v>
       </c>
       <c r="C134" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D134" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E134" t="s">
         <v>66</v>
       </c>
       <c r="F134" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -13262,22 +13525,22 @@
         <v>402</v>
       </c>
       <c r="C135" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D135" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E135" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F135" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -13285,25 +13548,25 @@
         <v>107</v>
       </c>
       <c r="B136" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C136" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="D136" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="E136" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F136" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -13311,25 +13574,25 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C137" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="D137" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
       <c r="E137" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F137" t="s">
-        <v>494</v>
+        <v>433</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>495</v>
+        <v>434</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -13340,22 +13603,22 @@
         <v>473</v>
       </c>
       <c r="C138" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D138" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="E138" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F138" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -13366,22 +13629,22 @@
         <v>473</v>
       </c>
       <c r="C139" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D139" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="E139" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="F139" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>537</v>
+        <v>495</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -13392,22 +13655,22 @@
         <v>473</v>
       </c>
       <c r="C140" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="D140" t="s">
-        <v>551</v>
+        <v>500</v>
       </c>
       <c r="E140" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="F140" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -13415,25 +13678,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C141" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D141" t="s">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="E141" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="F141" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>582</v>
+        <v>537</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13441,25 +13704,25 @@
         <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C142" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="D142" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="E142" t="s">
-        <v>587</v>
+        <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13467,25 +13730,25 @@
         <v>114</v>
       </c>
       <c r="B143" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C143" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="D143" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="E143" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F143" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13493,25 +13756,25 @@
         <v>115</v>
       </c>
       <c r="B144" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C144" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D144" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="E144" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F144" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -13522,22 +13785,22 @@
         <v>591</v>
       </c>
       <c r="C145" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D145" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F145" t="s">
-        <v>468</v>
+        <v>604</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -13548,10 +13811,10 @@
         <v>591</v>
       </c>
       <c r="C146" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="D146" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="E146" t="s">
         <v>16</v>
@@ -13563,7 +13826,7 @@
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13574,22 +13837,22 @@
         <v>591</v>
       </c>
       <c r="C147" t="s">
-        <v>650</v>
+        <v>557</v>
       </c>
       <c r="D147" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="E147" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F147" t="s">
-        <v>653</v>
+        <v>468</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13600,22 +13863,22 @@
         <v>591</v>
       </c>
       <c r="C148" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="D148" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="E148" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F148" t="s">
-        <v>662</v>
+        <v>618</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13626,22 +13889,22 @@
         <v>591</v>
       </c>
       <c r="C149" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="D149" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E149" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F149" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -13652,22 +13915,22 @@
         <v>591</v>
       </c>
       <c r="C150" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="D150" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="E150" t="s">
-        <v>66</v>
+        <v>661</v>
       </c>
       <c r="F150" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -13675,16 +13938,16 @@
         <v>122</v>
       </c>
       <c r="B151" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C151" t="s">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="D151" t="s">
-        <v>715</v>
+        <v>667</v>
       </c>
       <c r="E151" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F151" t="s">
         <v>604</v>
@@ -13693,7 +13956,7 @@
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>717</v>
+        <v>669</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -13701,25 +13964,25 @@
         <v>123</v>
       </c>
       <c r="B152" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C152" t="s">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="D152" t="s">
-        <v>722</v>
+        <v>674</v>
       </c>
       <c r="E152" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F152" t="s">
-        <v>724</v>
+        <v>676</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>725</v>
+        <v>677</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -13730,22 +13993,22 @@
         <v>697</v>
       </c>
       <c r="C153" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="D153" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="E153" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="F153" t="s">
-        <v>732</v>
+        <v>604</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -13756,22 +14019,22 @@
         <v>697</v>
       </c>
       <c r="C154" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="D154" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="E154" t="s">
-        <v>739</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>604</v>
+        <v>724</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -13782,22 +14045,22 @@
         <v>697</v>
       </c>
       <c r="C155" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="D155" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="E155" t="s">
-        <v>747</v>
+        <v>535</v>
       </c>
       <c r="F155" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -13808,22 +14071,22 @@
         <v>697</v>
       </c>
       <c r="C156" t="s">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="D156" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="E156" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="F156" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -13834,22 +14097,22 @@
         <v>697</v>
       </c>
       <c r="C157" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="D157" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="E157" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="F157" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -13857,25 +14120,25 @@
         <v>129</v>
       </c>
       <c r="B158" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C158" t="s">
-        <v>791</v>
+        <v>753</v>
       </c>
       <c r="D158" t="s">
-        <v>610</v>
+        <v>754</v>
       </c>
       <c r="E158" t="s">
-        <v>793</v>
+        <v>756</v>
       </c>
       <c r="F158" t="s">
-        <v>794</v>
+        <v>757</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>795</v>
+        <v>758</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13883,25 +14146,25 @@
         <v>130</v>
       </c>
       <c r="B159" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C159" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="D159" t="s">
-        <v>808</v>
+        <v>761</v>
       </c>
       <c r="E159" t="s">
-        <v>810</v>
+        <v>763</v>
       </c>
       <c r="F159" t="s">
-        <v>811</v>
+        <v>764</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>812</v>
+        <v>765</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13912,22 +14175,22 @@
         <v>773</v>
       </c>
       <c r="C160" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>610</v>
       </c>
       <c r="E160" t="s">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="F160" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -13935,25 +14198,25 @@
         <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C161" t="s">
-        <v>888</v>
+        <v>807</v>
       </c>
       <c r="D161" t="s">
-        <v>889</v>
+        <v>808</v>
       </c>
       <c r="E161" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F161" t="s">
-        <v>891</v>
+        <v>811</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>892</v>
+        <v>812</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -13961,25 +14224,25 @@
         <v>133</v>
       </c>
       <c r="B162" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C162" t="s">
-        <v>896</v>
+        <v>816</v>
       </c>
       <c r="D162" t="s">
-        <v>897</v>
+        <v>110</v>
       </c>
       <c r="E162" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>899</v>
+        <v>818</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>900</v>
+        <v>819</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13990,22 +14253,22 @@
         <v>845</v>
       </c>
       <c r="C163" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="D163" t="s">
-        <v>585</v>
+        <v>889</v>
       </c>
       <c r="E163" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F163" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14016,22 +14279,22 @@
         <v>845</v>
       </c>
       <c r="C164" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="D164" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="E164" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F164" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14042,22 +14305,22 @@
         <v>845</v>
       </c>
       <c r="C165" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="D165" t="s">
-        <v>919</v>
+        <v>585</v>
       </c>
       <c r="E165" t="s">
-        <v>921</v>
+        <v>66</v>
       </c>
       <c r="F165" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14065,25 +14328,25 @@
         <v>137</v>
       </c>
       <c r="B166" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C166" t="s">
-        <v>964</v>
+        <v>911</v>
       </c>
       <c r="D166" t="s">
-        <v>965</v>
+        <v>585</v>
       </c>
       <c r="E166" t="s">
-        <v>967</v>
+        <v>16</v>
       </c>
       <c r="F166" t="s">
-        <v>968</v>
+        <v>913</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>969</v>
+        <v>914</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -14091,25 +14354,25 @@
         <v>138</v>
       </c>
       <c r="B167" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C167" t="s">
-        <v>950</v>
+        <v>918</v>
       </c>
       <c r="D167" t="s">
-        <v>1002</v>
+        <v>919</v>
       </c>
       <c r="E167" t="s">
-        <v>1004</v>
+        <v>921</v>
       </c>
       <c r="F167" t="s">
-        <v>438</v>
+        <v>922</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>1005</v>
+        <v>923</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -14120,22 +14383,22 @@
         <v>934</v>
       </c>
       <c r="C168" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="D168" t="s">
-        <v>1009</v>
+        <v>965</v>
       </c>
       <c r="E168" t="s">
-        <v>16</v>
+        <v>967</v>
       </c>
       <c r="F168" t="s">
-        <v>1011</v>
+        <v>968</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>1012</v>
+        <v>969</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -14146,22 +14409,22 @@
         <v>934</v>
       </c>
       <c r="C169" t="s">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="D169" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="E169" t="s">
-        <v>66</v>
+        <v>1004</v>
       </c>
       <c r="F169" t="s">
-        <v>1018</v>
+        <v>438</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -14172,22 +14435,22 @@
         <v>934</v>
       </c>
       <c r="C170" t="s">
-        <v>1023</v>
+        <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="E170" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14198,22 +14461,22 @@
         <v>934</v>
       </c>
       <c r="C171" t="s">
-        <v>213</v>
+        <v>650</v>
       </c>
       <c r="D171" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="E171" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F171" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14224,22 +14487,22 @@
         <v>934</v>
       </c>
       <c r="C172" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="D172" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="E172" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="F172" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14250,22 +14513,22 @@
         <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>1048</v>
+        <v>213</v>
       </c>
       <c r="D173" t="s">
-        <v>1049</v>
+        <v>1032</v>
       </c>
       <c r="E173" t="s">
-        <v>1051</v>
+        <v>106</v>
       </c>
       <c r="F173" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -14276,22 +14539,22 @@
         <v>934</v>
       </c>
       <c r="C174" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="D174" t="s">
-        <v>1058</v>
+        <v>1040</v>
       </c>
       <c r="E174" t="s">
-        <v>16</v>
+        <v>1042</v>
       </c>
       <c r="F174" t="s">
-        <v>1060</v>
+        <v>1043</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1061</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -14302,22 +14565,22 @@
         <v>934</v>
       </c>
       <c r="C175" t="s">
-        <v>1082</v>
+        <v>1048</v>
       </c>
       <c r="D175" t="s">
-        <v>1083</v>
+        <v>1049</v>
       </c>
       <c r="E175" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
       <c r="F175" t="s">
-        <v>959</v>
+        <v>1052</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1086</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -14325,25 +14588,25 @@
         <v>147</v>
       </c>
       <c r="B176" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C176" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="D176" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="E176" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="F176" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1108</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14351,25 +14614,25 @@
         <v>148</v>
       </c>
       <c r="B177" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C177" t="s">
-        <v>1112</v>
+        <v>1082</v>
       </c>
       <c r="D177" t="s">
-        <v>1113</v>
+        <v>1083</v>
       </c>
       <c r="E177" t="s">
-        <v>25</v>
+        <v>1085</v>
       </c>
       <c r="F177" t="s">
-        <v>1115</v>
+        <v>959</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1116</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -14380,22 +14643,22 @@
         <v>1087</v>
       </c>
       <c r="C178" t="s">
-        <v>1120</v>
+        <v>271</v>
       </c>
       <c r="D178" t="s">
-        <v>1121</v>
+        <v>1104</v>
       </c>
       <c r="E178" t="s">
-        <v>1123</v>
+        <v>1106</v>
       </c>
       <c r="F178" t="s">
-        <v>1124</v>
+        <v>1107</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>1125</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -14406,22 +14669,22 @@
         <v>1087</v>
       </c>
       <c r="C179" t="s">
-        <v>1129</v>
+        <v>1112</v>
       </c>
       <c r="D179" t="s">
-        <v>1130</v>
+        <v>1113</v>
       </c>
       <c r="E179" t="s">
-        <v>1132</v>
+        <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>1133</v>
+        <v>1115</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>1134</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -14429,25 +14692,25 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C180" t="s">
-        <v>1172</v>
+        <v>1120</v>
       </c>
       <c r="D180" t="s">
-        <v>122</v>
+        <v>1121</v>
       </c>
       <c r="E180" t="s">
-        <v>1174</v>
+        <v>1123</v>
       </c>
       <c r="F180" t="s">
-        <v>1175</v>
+        <v>1124</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>1176</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -14455,25 +14718,25 @@
         <v>152</v>
       </c>
       <c r="B181" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C181" t="s">
-        <v>1178</v>
+        <v>1129</v>
       </c>
       <c r="D181" t="s">
-        <v>1179</v>
+        <v>1130</v>
       </c>
       <c r="E181" t="s">
-        <v>1181</v>
+        <v>1132</v>
       </c>
       <c r="F181" t="s">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>1182</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -14484,13 +14747,13 @@
         <v>1171</v>
       </c>
       <c r="C182" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="D182" t="s">
-        <v>1185</v>
+        <v>122</v>
       </c>
       <c r="E182" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="F182" t="s">
         <v>1175</v>
@@ -14499,7 +14762,7 @@
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -14507,25 +14770,25 @@
         <v>154</v>
       </c>
       <c r="B183" t="s">
-        <v>159</v>
+        <v>1171</v>
       </c>
       <c r="C183" t="s">
-        <v>271</v>
+        <v>1178</v>
       </c>
       <c r="D183" t="s">
-        <v>272</v>
+        <v>1179</v>
       </c>
       <c r="E183" t="s">
-        <v>75</v>
+        <v>1181</v>
       </c>
       <c r="F183" t="s">
-        <v>274</v>
+        <v>1175</v>
       </c>
       <c r="G183">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>275</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -14533,25 +14796,25 @@
         <v>155</v>
       </c>
       <c r="B184" t="s">
-        <v>591</v>
+        <v>1171</v>
       </c>
       <c r="C184" t="s">
-        <v>681</v>
+        <v>1184</v>
       </c>
       <c r="D184" t="s">
-        <v>682</v>
+        <v>1185</v>
       </c>
       <c r="E184" t="s">
-        <v>25</v>
+        <v>1187</v>
       </c>
       <c r="F184" t="s">
-        <v>684</v>
+        <v>1175</v>
       </c>
       <c r="G184">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>685</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -14559,25 +14822,25 @@
         <v>156</v>
       </c>
       <c r="B185" t="s">
-        <v>591</v>
+        <v>1210</v>
       </c>
       <c r="C185" t="s">
-        <v>689</v>
+        <v>1211</v>
       </c>
       <c r="D185" t="s">
-        <v>690</v>
+        <v>89</v>
       </c>
       <c r="E185" t="s">
-        <v>66</v>
+        <v>1213</v>
       </c>
       <c r="F185" t="s">
-        <v>692</v>
+        <v>1214</v>
       </c>
       <c r="G185">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>693</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -14585,25 +14848,25 @@
         <v>157</v>
       </c>
       <c r="B186" t="s">
-        <v>697</v>
+        <v>159</v>
       </c>
       <c r="C186" t="s">
-        <v>767</v>
+        <v>271</v>
       </c>
       <c r="D186" t="s">
-        <v>768</v>
+        <v>272</v>
       </c>
       <c r="E186" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F186" t="s">
-        <v>770</v>
+        <v>274</v>
       </c>
       <c r="G186">
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>771</v>
+        <v>275</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -14611,25 +14874,129 @@
         <v>158</v>
       </c>
       <c r="B187" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="C187" t="s">
-        <v>927</v>
+        <v>681</v>
       </c>
       <c r="D187" t="s">
-        <v>585</v>
+        <v>682</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>929</v>
+        <v>684</v>
       </c>
       <c r="G187">
         <v>7</v>
       </c>
       <c r="H187" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>159</v>
+      </c>
+      <c r="B188" t="s">
+        <v>591</v>
+      </c>
+      <c r="C188" t="s">
+        <v>689</v>
+      </c>
+      <c r="D188" t="s">
+        <v>690</v>
+      </c>
+      <c r="E188" t="s">
+        <v>66</v>
+      </c>
+      <c r="F188" t="s">
+        <v>692</v>
+      </c>
+      <c r="G188">
+        <v>7</v>
+      </c>
+      <c r="H188" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>160</v>
+      </c>
+      <c r="B189" t="s">
+        <v>697</v>
+      </c>
+      <c r="C189" t="s">
+        <v>767</v>
+      </c>
+      <c r="D189" t="s">
+        <v>768</v>
+      </c>
+      <c r="E189" t="s">
+        <v>25</v>
+      </c>
+      <c r="F189" t="s">
+        <v>770</v>
+      </c>
+      <c r="G189">
+        <v>7</v>
+      </c>
+      <c r="H189" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>161</v>
+      </c>
+      <c r="B190" t="s">
+        <v>845</v>
+      </c>
+      <c r="C190" t="s">
+        <v>927</v>
+      </c>
+      <c r="D190" t="s">
+        <v>585</v>
+      </c>
+      <c r="E190" t="s">
+        <v>25</v>
+      </c>
+      <c r="F190" t="s">
+        <v>929</v>
+      </c>
+      <c r="G190">
+        <v>7</v>
+      </c>
+      <c r="H190" t="s">
         <v>930</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>162</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G191">
+        <v>7</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
@@ -14645,7 +15012,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -14662,10 +15029,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1198</v>
+        <v>1235</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1199</v>
+        <v>1236</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -14692,12 +15059,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1200</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -14732,7 +15099,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -14767,7 +15134,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -14802,7 +15169,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -14837,7 +15204,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -14872,7 +15239,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -14907,7 +15274,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -14942,7 +15309,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -14977,7 +15344,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -15012,7 +15379,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -15047,7 +15414,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -15082,7 +15449,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -15117,42 +15484,42 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B14">
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>1190</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>1191</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>1192</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>1194</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>1195</v>
       </c>
       <c r="H14" t="s">
-        <v>28</v>
+        <v>1197</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>1198</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>1199</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -15161,33 +15528,33 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -15196,138 +15563,138 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
         <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
         <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B17">
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="J17" t="s">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B18">
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>473</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>523</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>524</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>526</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>527</v>
+        <v>170</v>
       </c>
       <c r="H18" t="s">
-        <v>529</v>
+        <v>28</v>
       </c>
       <c r="I18" t="s">
-        <v>530</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
-        <v>531</v>
+        <v>173</v>
       </c>
       <c r="K18" t="s">
-        <v>525</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B19">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>523</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>524</v>
       </c>
       <c r="F19" t="s">
-        <v>194</v>
+        <v>526</v>
       </c>
       <c r="G19" t="s">
-        <v>195</v>
+        <v>527</v>
       </c>
       <c r="H19" t="s">
-        <v>197</v>
+        <v>529</v>
       </c>
       <c r="I19" t="s">
-        <v>198</v>
+        <v>530</v>
       </c>
       <c r="J19" t="s">
-        <v>199</v>
+        <v>531</v>
       </c>
       <c r="K19" t="s">
-        <v>193</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -15336,418 +15703,418 @@
         <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E20" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="G20" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="H20" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="I20" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="J20" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="K20" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B21">
         <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
-        <v>331</v>
+        <v>220</v>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="H21" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="I21" t="s">
-        <v>336</v>
+        <v>225</v>
       </c>
       <c r="J21" t="s">
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="K21" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B22">
         <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="E22" t="s">
-        <v>443</v>
+        <v>331</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="G22" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="H22" t="s">
-        <v>446</v>
+        <v>197</v>
       </c>
       <c r="I22" t="s">
-        <v>447</v>
+        <v>336</v>
       </c>
       <c r="J22" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="K22" t="s">
-        <v>444</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B23">
         <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D23" t="s">
-        <v>774</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>775</v>
+        <v>443</v>
       </c>
       <c r="F23" t="s">
-        <v>777</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>778</v>
+        <v>438</v>
       </c>
       <c r="H23" t="s">
-        <v>780</v>
+        <v>446</v>
       </c>
       <c r="I23" t="s">
-        <v>781</v>
+        <v>447</v>
       </c>
       <c r="J23" t="s">
-        <v>782</v>
+        <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>776</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B24">
         <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>1087</v>
+        <v>773</v>
       </c>
       <c r="D24" t="s">
-        <v>1138</v>
+        <v>774</v>
       </c>
       <c r="E24" t="s">
-        <v>1139</v>
+        <v>775</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>777</v>
       </c>
       <c r="G24" t="s">
-        <v>1141</v>
+        <v>778</v>
       </c>
       <c r="H24" t="s">
-        <v>1143</v>
+        <v>780</v>
       </c>
       <c r="I24" t="s">
-        <v>1144</v>
+        <v>781</v>
       </c>
       <c r="J24" t="s">
-        <v>1145</v>
+        <v>782</v>
       </c>
       <c r="K24" t="s">
-        <v>1140</v>
+        <v>776</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B25">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>1138</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>1139</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>1141</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>1143</v>
       </c>
       <c r="I25" t="s">
-        <v>142</v>
+        <v>1144</v>
       </c>
       <c r="J25" t="s">
-        <v>143</v>
+        <v>1145</v>
       </c>
       <c r="K25" t="s">
-        <v>137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B26">
         <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
-        <v>438</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="I26" t="s">
-        <v>441</v>
+        <v>142</v>
       </c>
       <c r="J26" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="K26" t="s">
-        <v>437</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B27">
         <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D27" t="s">
-        <v>557</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>564</v>
+        <v>436</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H27" t="s">
-        <v>567</v>
+        <v>440</v>
       </c>
       <c r="I27" t="s">
-        <v>568</v>
+        <v>441</v>
       </c>
       <c r="J27" t="s">
-        <v>569</v>
+        <v>442</v>
       </c>
       <c r="K27" t="s">
-        <v>565</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B28">
         <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D28" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="E28" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="F28" t="s">
-        <v>595</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>596</v>
+        <v>468</v>
       </c>
       <c r="H28" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="I28" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="J28" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="K28" t="s">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B29">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D29" t="s">
-        <v>707</v>
+        <v>592</v>
       </c>
       <c r="E29" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F29" t="s">
-        <v>318</v>
+        <v>595</v>
       </c>
       <c r="G29" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H29" t="s">
-        <v>711</v>
+        <v>598</v>
       </c>
       <c r="I29" t="s">
-        <v>712</v>
+        <v>599</v>
       </c>
       <c r="J29" t="s">
-        <v>713</v>
+        <v>600</v>
       </c>
       <c r="K29" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B30">
         <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D30" t="s">
-        <v>846</v>
+        <v>707</v>
       </c>
       <c r="E30" t="s">
-        <v>847</v>
+        <v>708</v>
       </c>
       <c r="F30" t="s">
-        <v>849</v>
+        <v>318</v>
       </c>
       <c r="G30" t="s">
-        <v>850</v>
+        <v>604</v>
       </c>
       <c r="H30" t="s">
-        <v>852</v>
+        <v>711</v>
       </c>
       <c r="I30" t="s">
-        <v>853</v>
+        <v>712</v>
       </c>
       <c r="J30" t="s">
-        <v>854</v>
+        <v>713</v>
       </c>
       <c r="K30" t="s">
-        <v>848</v>
+        <v>709</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B31">
         <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D31" t="s">
-        <v>277</v>
+        <v>846</v>
       </c>
       <c r="E31" t="s">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>849</v>
       </c>
       <c r="G31" t="s">
-        <v>937</v>
+        <v>850</v>
       </c>
       <c r="H31" t="s">
-        <v>939</v>
+        <v>852</v>
       </c>
       <c r="I31" t="s">
-        <v>940</v>
+        <v>853</v>
       </c>
       <c r="J31" t="s">
-        <v>941</v>
+        <v>854</v>
       </c>
       <c r="K31" t="s">
-        <v>936</v>
+        <v>848</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -15756,33 +16123,33 @@
         <v>934</v>
       </c>
       <c r="D32" t="s">
-        <v>942</v>
+        <v>277</v>
       </c>
       <c r="E32" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H32" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="I32" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J32" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="K32" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -15791,418 +16158,418 @@
         <v>934</v>
       </c>
       <c r="D33" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="E33" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="F33" t="s">
         <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="H33" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="I33" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="J33" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="K33" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B34">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>950</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>951</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>954</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>955</v>
       </c>
       <c r="J34" t="s">
-        <v>38</v>
+        <v>956</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>952</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B35">
         <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H35" t="s">
         <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J35" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K35" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B36">
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H36" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J36" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K36" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B37">
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E37" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H37" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I37" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K37" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B38">
         <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F38" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I38" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B39">
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D39" t="s">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="E39" t="s">
-        <v>610</v>
+        <v>699</v>
       </c>
       <c r="F39" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="G39" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="H39" t="s">
-        <v>842</v>
+        <v>704</v>
       </c>
       <c r="I39" t="s">
-        <v>843</v>
+        <v>705</v>
       </c>
       <c r="J39" t="s">
-        <v>844</v>
+        <v>706</v>
       </c>
       <c r="K39" t="s">
-        <v>838</v>
+        <v>700</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B40">
         <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D40" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="E40" t="s">
-        <v>856</v>
+        <v>610</v>
       </c>
       <c r="F40" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="G40" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="H40" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="I40" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="J40" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="K40" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B41">
         <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D41" t="s">
-        <v>643</v>
+        <v>855</v>
       </c>
       <c r="E41" t="s">
-        <v>957</v>
+        <v>856</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>858</v>
       </c>
       <c r="G41" t="s">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="H41" t="s">
-        <v>961</v>
+        <v>861</v>
       </c>
       <c r="I41" t="s">
-        <v>962</v>
+        <v>862</v>
       </c>
       <c r="J41" t="s">
-        <v>963</v>
+        <v>863</v>
       </c>
       <c r="K41" t="s">
-        <v>958</v>
+        <v>857</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B42">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>643</v>
       </c>
       <c r="E42" t="s">
-        <v>185</v>
+        <v>957</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>959</v>
       </c>
       <c r="H42" t="s">
-        <v>188</v>
+        <v>961</v>
       </c>
       <c r="I42" t="s">
-        <v>189</v>
+        <v>962</v>
       </c>
       <c r="J42" t="s">
-        <v>190</v>
+        <v>963</v>
       </c>
       <c r="K42" t="s">
-        <v>186</v>
+        <v>958</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B43">
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D43" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E43" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F43" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H43" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I43" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J43" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K43" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B44">
         <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E44" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G44" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H44" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I44" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J44" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K44" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B45">
         <v>87</v>
@@ -16214,7 +16581,7 @@
         <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F45" t="s">
         <v>66</v>
@@ -16232,292 +16599,292 @@
         <v>79</v>
       </c>
       <c r="K45" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B46">
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F46" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G46" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H46" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I46" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J46" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B47">
         <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D47" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G47" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H47" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I47" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J47" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K47" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B48">
         <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D48" t="s">
-        <v>864</v>
+        <v>570</v>
       </c>
       <c r="E48" t="s">
-        <v>865</v>
+        <v>571</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="H48" t="s">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="I48" t="s">
-        <v>870</v>
+        <v>576</v>
       </c>
       <c r="J48" t="s">
-        <v>871</v>
+        <v>577</v>
       </c>
       <c r="K48" t="s">
-        <v>866</v>
+        <v>572</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B49">
         <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D49" t="s">
-        <v>950</v>
+        <v>864</v>
       </c>
       <c r="E49" t="s">
-        <v>996</v>
+        <v>865</v>
       </c>
       <c r="F49" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>438</v>
+        <v>867</v>
       </c>
       <c r="H49" t="s">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="I49" t="s">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J49" t="s">
-        <v>1001</v>
+        <v>871</v>
       </c>
       <c r="K49" t="s">
-        <v>997</v>
+        <v>866</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B50">
         <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D50" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="E50" t="s">
-        <v>1097</v>
+        <v>996</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>1099</v>
+        <v>438</v>
       </c>
       <c r="H50" t="s">
-        <v>1101</v>
+        <v>999</v>
       </c>
       <c r="I50" t="s">
-        <v>1102</v>
+        <v>1000</v>
       </c>
       <c r="J50" t="s">
-        <v>1103</v>
+        <v>1001</v>
       </c>
       <c r="K50" t="s">
-        <v>1098</v>
+        <v>997</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B51">
         <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D51" t="s">
-        <v>1156</v>
+        <v>964</v>
       </c>
       <c r="E51" t="s">
-        <v>1157</v>
+        <v>1097</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>1159</v>
+        <v>1099</v>
       </c>
       <c r="H51" t="s">
-        <v>1161</v>
+        <v>1101</v>
       </c>
       <c r="I51" t="s">
-        <v>1162</v>
+        <v>1102</v>
       </c>
       <c r="J51" t="s">
-        <v>1163</v>
+        <v>1103</v>
       </c>
       <c r="K51" t="s">
-        <v>1158</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B52">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>1155</v>
       </c>
       <c r="D52" t="s">
-        <v>369</v>
+        <v>1156</v>
       </c>
       <c r="E52" t="s">
-        <v>370</v>
+        <v>1157</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>372</v>
+        <v>1159</v>
       </c>
       <c r="H52" t="s">
-        <v>374</v>
+        <v>1161</v>
       </c>
       <c r="I52" t="s">
-        <v>375</v>
+        <v>1162</v>
       </c>
       <c r="J52" t="s">
-        <v>376</v>
+        <v>1163</v>
       </c>
       <c r="K52" t="s">
-        <v>371</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B53">
         <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E53" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F53" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H53" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I53" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J53" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K53" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B54">
         <v>86</v>
@@ -16526,138 +16893,138 @@
         <v>402</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E54" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G54" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H54" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I54" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J54" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K54" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B55">
         <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D55" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E55" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F55" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H55" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I55" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J55" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K55" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B56">
         <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D56" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E56" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G56" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H56" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I56" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J56" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K56" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B57">
         <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D57" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
       <c r="E57" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H57" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="I57" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="J57" t="s">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="K57" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B58">
         <v>86</v>
@@ -16666,33 +17033,33 @@
         <v>591</v>
       </c>
       <c r="D58" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E58" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="H58" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="I58" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="J58" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="K58" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B59">
         <v>86</v>
@@ -16701,103 +17068,103 @@
         <v>591</v>
       </c>
       <c r="D59" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E59" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G59" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H59" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="I59" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J59" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="K59" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B60">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D60" t="s">
-        <v>829</v>
+        <v>635</v>
       </c>
       <c r="E60" t="s">
-        <v>830</v>
+        <v>636</v>
       </c>
       <c r="F60" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>832</v>
+        <v>638</v>
       </c>
       <c r="H60" t="s">
-        <v>834</v>
+        <v>640</v>
       </c>
       <c r="I60" t="s">
-        <v>835</v>
+        <v>641</v>
       </c>
       <c r="J60" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="K60" t="s">
-        <v>831</v>
+        <v>637</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B61">
         <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D61" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E61" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="F61" t="s">
-        <v>380</v>
+        <v>785</v>
       </c>
       <c r="G61" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
       <c r="H61" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="I61" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="J61" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="K61" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -16806,68 +17173,68 @@
         <v>845</v>
       </c>
       <c r="D62" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E62" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G62" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H62" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I62" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J62" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K62" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B63">
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D63" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="E63" t="s">
-        <v>974</v>
+        <v>881</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>468</v>
+        <v>883</v>
       </c>
       <c r="H63" t="s">
-        <v>977</v>
+        <v>885</v>
       </c>
       <c r="I63" t="s">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="J63" t="s">
-        <v>979</v>
+        <v>887</v>
       </c>
       <c r="K63" t="s">
-        <v>975</v>
+        <v>882</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B64">
         <v>86</v>
@@ -16876,33 +17243,33 @@
         <v>934</v>
       </c>
       <c r="D64" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E64" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="F64" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="H64" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="I64" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J64" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="K64" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B65">
         <v>86</v>
@@ -16911,68 +17278,68 @@
         <v>934</v>
       </c>
       <c r="D65" t="s">
-        <v>1073</v>
+        <v>980</v>
       </c>
       <c r="E65" t="s">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="F65" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G65" t="s">
-        <v>1077</v>
+        <v>984</v>
       </c>
       <c r="H65" t="s">
-        <v>1079</v>
+        <v>986</v>
       </c>
       <c r="I65" t="s">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="J65" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="K65" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B66">
         <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D66" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E66" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="F66" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="G66" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="H66" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="I66" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="J66" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="K66" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B67">
         <v>86</v>
@@ -16981,103 +17348,103 @@
         <v>1087</v>
       </c>
       <c r="D67" t="s">
-        <v>1146</v>
+        <v>1088</v>
       </c>
       <c r="E67" t="s">
-        <v>1147</v>
+        <v>1089</v>
       </c>
       <c r="F67" t="s">
-        <v>1149</v>
+        <v>1091</v>
       </c>
       <c r="G67" t="s">
-        <v>1150</v>
+        <v>1092</v>
       </c>
       <c r="H67" t="s">
-        <v>1152</v>
+        <v>1094</v>
       </c>
       <c r="I67" t="s">
-        <v>1153</v>
+        <v>1095</v>
       </c>
       <c r="J67" t="s">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="K67" t="s">
-        <v>1148</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B68">
         <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D68" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="E68" t="s">
-        <v>610</v>
+        <v>1147</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G68" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
       <c r="H68" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
       <c r="I68" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="J68" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="K68" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B69">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="D69" t="s">
-        <v>55</v>
+        <v>1164</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>610</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>58</v>
+        <v>1166</v>
       </c>
       <c r="H69" t="s">
-        <v>60</v>
+        <v>1168</v>
       </c>
       <c r="I69" t="s">
-        <v>61</v>
+        <v>1169</v>
       </c>
       <c r="J69" t="s">
-        <v>62</v>
+        <v>1170</v>
       </c>
       <c r="K69" t="s">
-        <v>57</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B70">
         <v>85</v>
@@ -17086,173 +17453,173 @@
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="E70" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F70" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H70" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I70" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="J70" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K70" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B71">
         <v>85</v>
       </c>
       <c r="C71" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E71" t="s">
-        <v>308</v>
+        <v>89</v>
       </c>
       <c r="F71" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G71" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
       <c r="H71" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="I71" t="s">
-        <v>313</v>
+        <v>134</v>
       </c>
       <c r="J71" t="s">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="K71" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B72">
         <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E72" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G72" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H72" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="I72" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="J72" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="K72" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B73">
         <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D73" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E73" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="F73" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="H73" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="I73" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="J73" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="K73" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B74">
         <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D74" t="s">
-        <v>774</v>
+        <v>474</v>
       </c>
       <c r="E74" t="s">
-        <v>783</v>
+        <v>475</v>
       </c>
       <c r="F74" t="s">
-        <v>785</v>
+        <v>477</v>
       </c>
       <c r="G74" t="s">
-        <v>786</v>
+        <v>478</v>
       </c>
       <c r="H74" t="s">
-        <v>788</v>
+        <v>480</v>
       </c>
       <c r="I74" t="s">
-        <v>789</v>
+        <v>481</v>
       </c>
       <c r="J74" t="s">
-        <v>790</v>
+        <v>482</v>
       </c>
       <c r="K74" t="s">
-        <v>784</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B75">
         <v>85</v>
@@ -17261,33 +17628,33 @@
         <v>773</v>
       </c>
       <c r="D75" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="E75" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F75" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="G75" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H75" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="I75" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="J75" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K75" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B76">
         <v>85</v>
@@ -17296,68 +17663,68 @@
         <v>773</v>
       </c>
       <c r="D76" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="E76" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F76" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G76" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="H76" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="I76" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J76" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="K76" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B77">
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D77" t="s">
-        <v>989</v>
+        <v>821</v>
       </c>
       <c r="E77" t="s">
-        <v>990</v>
+        <v>822</v>
       </c>
       <c r="F77" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="G77" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="H77" t="s">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="I77" t="s">
-        <v>994</v>
+        <v>827</v>
       </c>
       <c r="J77" t="s">
-        <v>995</v>
+        <v>828</v>
       </c>
       <c r="K77" t="s">
-        <v>991</v>
+        <v>823</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B78">
         <v>85</v>
@@ -17366,208 +17733,208 @@
         <v>934</v>
       </c>
       <c r="D78" t="s">
-        <v>1065</v>
+        <v>989</v>
       </c>
       <c r="E78" t="s">
-        <v>1066</v>
+        <v>990</v>
       </c>
       <c r="F78" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G78" t="s">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="H78" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="I78" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="J78" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
       <c r="K78" t="s">
-        <v>1067</v>
+        <v>991</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B79">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D79" t="s">
-        <v>144</v>
+        <v>1065</v>
       </c>
       <c r="E79" t="s">
-        <v>145</v>
+        <v>1066</v>
       </c>
       <c r="F79" t="s">
         <v>147</v>
       </c>
       <c r="G79" t="s">
-        <v>148</v>
+        <v>1068</v>
       </c>
       <c r="H79" t="s">
-        <v>150</v>
+        <v>1070</v>
       </c>
       <c r="I79" t="s">
-        <v>151</v>
+        <v>1071</v>
       </c>
       <c r="J79" t="s">
-        <v>152</v>
+        <v>1072</v>
       </c>
       <c r="K79" t="s">
-        <v>146</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B80">
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
         <v>144</v>
       </c>
       <c r="E80" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="F80" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G80" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="H80" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I80" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="J80" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="K80" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B81">
         <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D81" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E81" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F81" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="G81" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="H81" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="I81" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="J81" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="K81" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B82">
         <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D82" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="E82" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="F82" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="G82" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="H82" t="s">
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="I82" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J82" t="s">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="K82" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B83">
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D83" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="E83" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G83" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H83" t="s">
-        <v>718</v>
+        <v>488</v>
       </c>
       <c r="I83" t="s">
-        <v>719</v>
+        <v>489</v>
       </c>
       <c r="J83" t="s">
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K83" t="s">
-        <v>716</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B84">
         <v>84</v>
@@ -17576,33 +17943,33 @@
         <v>697</v>
       </c>
       <c r="D84" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E84" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="H84" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I84" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="J84" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K84" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B85">
         <v>84</v>
@@ -17611,138 +17978,138 @@
         <v>697</v>
       </c>
       <c r="D85" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E85" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F85" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H85" t="s">
         <v>726</v>
       </c>
       <c r="I85" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="J85" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="K85" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D86" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="E86" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="F86" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="G86" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="H86" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I86" t="s">
-        <v>797</v>
+        <v>734</v>
       </c>
       <c r="J86" t="s">
-        <v>798</v>
+        <v>735</v>
       </c>
       <c r="K86" t="s">
-        <v>792</v>
+        <v>731</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B87">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D87" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="E87" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="G87" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H87" t="s">
-        <v>901</v>
+        <v>796</v>
       </c>
       <c r="I87" t="s">
-        <v>902</v>
+        <v>797</v>
       </c>
       <c r="J87" t="s">
-        <v>903</v>
+        <v>798</v>
       </c>
       <c r="K87" t="s">
-        <v>898</v>
+        <v>792</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B88">
         <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D88" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="E88" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="F88" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G88" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="H88" t="s">
-        <v>970</v>
+        <v>901</v>
       </c>
       <c r="I88" t="s">
-        <v>971</v>
+        <v>902</v>
       </c>
       <c r="J88" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="K88" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B89">
         <v>84</v>
@@ -17751,33 +18118,33 @@
         <v>934</v>
       </c>
       <c r="D89" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="E89" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="F89" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="G89" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="H89" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="I89" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="J89" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K89" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B90">
         <v>84</v>
@@ -17786,33 +18153,33 @@
         <v>934</v>
       </c>
       <c r="D90" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="E90" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="F90" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="G90" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="H90" t="s">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="I90" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="J90" t="s">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="K90" t="s">
-        <v>1033</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B91">
         <v>84</v>
@@ -17821,832 +18188,937 @@
         <v>934</v>
       </c>
       <c r="D91" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="E91" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="F91" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G91" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="H91" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="I91" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="J91" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="K91" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B92">
         <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D92" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="E92" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F92" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="H92" t="s">
-        <v>1109</v>
+        <v>1062</v>
       </c>
       <c r="I92" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="J92" t="s">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K92" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B93">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>284</v>
+        <v>1087</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
       <c r="E93" t="s">
-        <v>362</v>
+        <v>1104</v>
       </c>
       <c r="F93" t="s">
-        <v>356</v>
+        <v>1106</v>
       </c>
       <c r="G93" t="s">
-        <v>364</v>
+        <v>1107</v>
       </c>
       <c r="H93" t="s">
-        <v>366</v>
+        <v>1109</v>
       </c>
       <c r="I93" t="s">
-        <v>367</v>
+        <v>1110</v>
       </c>
       <c r="J93" t="s">
-        <v>368</v>
+        <v>1111</v>
       </c>
       <c r="K93" t="s">
-        <v>363</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B94">
         <v>83</v>
       </c>
       <c r="C94" t="s">
-        <v>473</v>
+        <v>1200</v>
       </c>
       <c r="D94" t="s">
-        <v>491</v>
+        <v>1201</v>
       </c>
       <c r="E94" t="s">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="G94" t="s">
-        <v>494</v>
+        <v>1205</v>
       </c>
       <c r="H94" t="s">
-        <v>496</v>
+        <v>1207</v>
       </c>
       <c r="I94" t="s">
-        <v>497</v>
+        <v>1208</v>
       </c>
       <c r="J94" t="s">
-        <v>498</v>
+        <v>1209</v>
       </c>
       <c r="K94" t="s">
-        <v>493</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B95">
         <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D95" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E95" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F95" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G95" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H95" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I95" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J95" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K95" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B96">
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D96" t="s">
-        <v>643</v>
+        <v>491</v>
       </c>
       <c r="E96" t="s">
-        <v>644</v>
+        <v>492</v>
       </c>
       <c r="F96" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G96" t="s">
-        <v>618</v>
+        <v>494</v>
       </c>
       <c r="H96" t="s">
-        <v>647</v>
+        <v>496</v>
       </c>
       <c r="I96" t="s">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="J96" t="s">
-        <v>649</v>
+        <v>498</v>
       </c>
       <c r="K96" t="s">
-        <v>645</v>
+        <v>493</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B97">
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D97" t="s">
-        <v>736</v>
+        <v>532</v>
       </c>
       <c r="E97" t="s">
-        <v>737</v>
+        <v>533</v>
       </c>
       <c r="F97" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="G97" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="H97" t="s">
-        <v>741</v>
+        <v>538</v>
       </c>
       <c r="I97" t="s">
-        <v>742</v>
+        <v>539</v>
       </c>
       <c r="J97" t="s">
-        <v>743</v>
+        <v>540</v>
       </c>
       <c r="K97" t="s">
-        <v>738</v>
+        <v>534</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B98">
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D98" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="E98" t="s">
-        <v>808</v>
+        <v>644</v>
       </c>
       <c r="F98" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>811</v>
+        <v>618</v>
       </c>
       <c r="H98" t="s">
-        <v>813</v>
+        <v>647</v>
       </c>
       <c r="I98" t="s">
-        <v>814</v>
+        <v>648</v>
       </c>
       <c r="J98" t="s">
-        <v>815</v>
+        <v>649</v>
       </c>
       <c r="K98" t="s">
-        <v>809</v>
+        <v>645</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B99">
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D99" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="E99" t="s">
-        <v>1016</v>
+        <v>737</v>
       </c>
       <c r="F99" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="G99" t="s">
-        <v>1018</v>
+        <v>604</v>
       </c>
       <c r="H99" t="s">
-        <v>1020</v>
+        <v>741</v>
       </c>
       <c r="I99" t="s">
-        <v>1021</v>
+        <v>742</v>
       </c>
       <c r="J99" t="s">
-        <v>1022</v>
+        <v>743</v>
       </c>
       <c r="K99" t="s">
-        <v>1017</v>
+        <v>738</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B100">
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D100" t="s">
-        <v>1048</v>
+        <v>807</v>
       </c>
       <c r="E100" t="s">
-        <v>1049</v>
+        <v>808</v>
       </c>
       <c r="F100" t="s">
-        <v>1051</v>
+        <v>810</v>
       </c>
       <c r="G100" t="s">
-        <v>1052</v>
+        <v>811</v>
       </c>
       <c r="H100" t="s">
-        <v>1054</v>
+        <v>813</v>
       </c>
       <c r="I100" t="s">
-        <v>1055</v>
+        <v>814</v>
       </c>
       <c r="J100" t="s">
-        <v>1056</v>
+        <v>815</v>
       </c>
       <c r="K100" t="s">
-        <v>1050</v>
+        <v>809</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B101">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D101" t="s">
-        <v>227</v>
+        <v>650</v>
       </c>
       <c r="E101" t="s">
-        <v>228</v>
+        <v>1016</v>
       </c>
       <c r="F101" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="G101" t="s">
-        <v>231</v>
+        <v>1018</v>
       </c>
       <c r="H101" t="s">
-        <v>233</v>
+        <v>1020</v>
       </c>
       <c r="I101" t="s">
-        <v>234</v>
+        <v>1021</v>
       </c>
       <c r="J101" t="s">
-        <v>235</v>
+        <v>1022</v>
       </c>
       <c r="K101" t="s">
-        <v>229</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B102">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D102" t="s">
-        <v>266</v>
+        <v>1048</v>
       </c>
       <c r="E102" t="s">
-        <v>267</v>
+        <v>1049</v>
       </c>
       <c r="F102" t="s">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="G102" t="s">
-        <v>58</v>
+        <v>1052</v>
       </c>
       <c r="H102" t="s">
-        <v>270</v>
+        <v>1054</v>
       </c>
       <c r="I102" t="s">
-        <v>79</v>
+        <v>1055</v>
       </c>
       <c r="J102" t="s">
-        <v>79</v>
+        <v>1056</v>
       </c>
       <c r="K102" t="s">
-        <v>268</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B103">
         <v>82</v>
       </c>
       <c r="C103" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D103" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="E103" t="s">
-        <v>339</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="G103" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="H103" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="I103" t="s">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="J103" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="K103" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B104">
         <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="D104" t="s">
-        <v>601</v>
+        <v>266</v>
       </c>
       <c r="E104" t="s">
-        <v>602</v>
+        <v>267</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>604</v>
+        <v>58</v>
       </c>
       <c r="H104" t="s">
-        <v>606</v>
+        <v>270</v>
       </c>
       <c r="I104" t="s">
-        <v>607</v>
+        <v>79</v>
       </c>
       <c r="J104" t="s">
-        <v>608</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s">
-        <v>603</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B105">
         <v>82</v>
       </c>
       <c r="C105" t="s">
-        <v>934</v>
+        <v>284</v>
       </c>
       <c r="D105" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="E105" t="s">
-        <v>1009</v>
+        <v>339</v>
       </c>
       <c r="F105" t="s">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c r="G105" t="s">
-        <v>1011</v>
+        <v>342</v>
       </c>
       <c r="H105" t="s">
-        <v>1013</v>
+        <v>344</v>
       </c>
       <c r="I105" t="s">
-        <v>1014</v>
+        <v>345</v>
       </c>
       <c r="J105" t="s">
-        <v>1015</v>
+        <v>346</v>
       </c>
       <c r="K105" t="s">
-        <v>1010</v>
+        <v>340</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B106">
         <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D106" t="s">
-        <v>1023</v>
+        <v>601</v>
       </c>
       <c r="E106" t="s">
-        <v>1024</v>
+        <v>602</v>
       </c>
       <c r="F106" t="s">
-        <v>1026</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>1027</v>
+        <v>604</v>
       </c>
       <c r="H106" t="s">
-        <v>1029</v>
+        <v>606</v>
       </c>
       <c r="I106" t="s">
-        <v>1030</v>
+        <v>607</v>
       </c>
       <c r="J106" t="s">
-        <v>1031</v>
+        <v>608</v>
       </c>
       <c r="K106" t="s">
-        <v>1025</v>
+        <v>603</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B107">
         <v>82</v>
       </c>
       <c r="C107" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D107" t="s">
-        <v>1112</v>
+        <v>13</v>
       </c>
       <c r="E107" t="s">
-        <v>1113</v>
+        <v>1009</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G107" t="s">
-        <v>1115</v>
+        <v>1011</v>
       </c>
       <c r="H107" t="s">
-        <v>1117</v>
+        <v>1013</v>
       </c>
       <c r="I107" t="s">
-        <v>1118</v>
+        <v>1014</v>
       </c>
       <c r="J107" t="s">
-        <v>1119</v>
+        <v>1015</v>
       </c>
       <c r="K107" t="s">
-        <v>1114</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B108">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C108" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D108" t="s">
-        <v>80</v>
+        <v>1023</v>
       </c>
       <c r="E108" t="s">
-        <v>81</v>
+        <v>1024</v>
       </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G108" t="s">
-        <v>83</v>
+        <v>1027</v>
       </c>
       <c r="H108" t="s">
-        <v>85</v>
+        <v>1029</v>
       </c>
       <c r="I108" t="s">
-        <v>86</v>
+        <v>1030</v>
       </c>
       <c r="J108" t="s">
-        <v>87</v>
+        <v>1031</v>
       </c>
       <c r="K108" t="s">
-        <v>82</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B109">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C109" t="s">
-        <v>284</v>
+        <v>1087</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>1112</v>
       </c>
       <c r="E109" t="s">
-        <v>378</v>
+        <v>1113</v>
       </c>
       <c r="F109" t="s">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>381</v>
+        <v>1115</v>
       </c>
       <c r="H109" t="s">
-        <v>383</v>
+        <v>1117</v>
       </c>
       <c r="I109" t="s">
-        <v>384</v>
+        <v>1118</v>
       </c>
       <c r="J109" t="s">
-        <v>385</v>
+        <v>1119</v>
       </c>
       <c r="K109" t="s">
-        <v>379</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B110">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>473</v>
+        <v>1210</v>
       </c>
       <c r="D110" t="s">
-        <v>499</v>
+        <v>1211</v>
       </c>
       <c r="E110" t="s">
-        <v>500</v>
+        <v>89</v>
       </c>
       <c r="F110" t="s">
-        <v>502</v>
+        <v>1213</v>
       </c>
       <c r="G110" t="s">
-        <v>503</v>
+        <v>1214</v>
       </c>
       <c r="H110" t="s">
-        <v>505</v>
+        <v>1216</v>
       </c>
       <c r="I110" t="s">
-        <v>506</v>
+        <v>1217</v>
       </c>
       <c r="J110" t="s">
-        <v>507</v>
+        <v>1218</v>
       </c>
       <c r="K110" t="s">
-        <v>501</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B111">
         <v>81</v>
       </c>
       <c r="C111" t="s">
-        <v>591</v>
+        <v>12</v>
       </c>
       <c r="D111" t="s">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="E111" t="s">
-        <v>610</v>
+        <v>81</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G111" t="s">
-        <v>618</v>
+        <v>83</v>
       </c>
       <c r="H111" t="s">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="I111" t="s">
-        <v>621</v>
+        <v>86</v>
       </c>
       <c r="J111" t="s">
-        <v>622</v>
+        <v>87</v>
       </c>
       <c r="K111" t="s">
-        <v>617</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B112">
         <v>81</v>
       </c>
       <c r="C112" t="s">
-        <v>845</v>
+        <v>284</v>
       </c>
       <c r="D112" t="s">
-        <v>888</v>
+        <v>377</v>
       </c>
       <c r="E112" t="s">
-        <v>889</v>
+        <v>378</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="G112" t="s">
-        <v>891</v>
+        <v>381</v>
       </c>
       <c r="H112" t="s">
-        <v>893</v>
+        <v>383</v>
       </c>
       <c r="I112" t="s">
-        <v>894</v>
+        <v>384</v>
       </c>
       <c r="J112" t="s">
-        <v>895</v>
+        <v>385</v>
       </c>
       <c r="K112" t="s">
-        <v>890</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B113">
         <v>81</v>
       </c>
       <c r="C113" t="s">
-        <v>1087</v>
+        <v>473</v>
       </c>
       <c r="D113" t="s">
-        <v>1120</v>
+        <v>499</v>
       </c>
       <c r="E113" t="s">
-        <v>1121</v>
+        <v>500</v>
       </c>
       <c r="F113" t="s">
-        <v>1123</v>
+        <v>502</v>
       </c>
       <c r="G113" t="s">
-        <v>1124</v>
+        <v>503</v>
       </c>
       <c r="H113" t="s">
-        <v>1126</v>
+        <v>505</v>
       </c>
       <c r="I113" t="s">
-        <v>1127</v>
+        <v>506</v>
       </c>
       <c r="J113" t="s">
-        <v>1128</v>
+        <v>507</v>
       </c>
       <c r="K113" t="s">
-        <v>1122</v>
+        <v>501</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="B114">
+        <v>81</v>
+      </c>
+      <c r="C114" t="s">
+        <v>591</v>
+      </c>
+      <c r="D114" t="s">
+        <v>616</v>
+      </c>
+      <c r="E114" t="s">
+        <v>610</v>
+      </c>
+      <c r="F114" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s">
+        <v>618</v>
+      </c>
+      <c r="H114" t="s">
+        <v>620</v>
+      </c>
+      <c r="I114" t="s">
+        <v>621</v>
+      </c>
+      <c r="J114" t="s">
+        <v>622</v>
+      </c>
+      <c r="K114" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B115">
+        <v>81</v>
+      </c>
+      <c r="C115" t="s">
+        <v>845</v>
+      </c>
+      <c r="D115" t="s">
+        <v>888</v>
+      </c>
+      <c r="E115" t="s">
+        <v>889</v>
+      </c>
+      <c r="F115" t="s">
+        <v>25</v>
+      </c>
+      <c r="G115" t="s">
+        <v>891</v>
+      </c>
+      <c r="H115" t="s">
+        <v>893</v>
+      </c>
+      <c r="I115" t="s">
+        <v>894</v>
+      </c>
+      <c r="J115" t="s">
+        <v>895</v>
+      </c>
+      <c r="K115" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B116">
+        <v>81</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I116" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J116" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K116" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B117">
         <v>80</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C117" t="s">
         <v>934</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D117" t="s">
         <v>1039</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E117" t="s">
         <v>1040</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F117" t="s">
         <v>1042</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G117" t="s">
         <v>1043</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H117" t="s">
         <v>1045</v>
       </c>
-      <c r="I114" t="s">
+      <c r="I117" t="s">
         <v>1046</v>
       </c>
-      <c r="J114" t="s">
+      <c r="J117" t="s">
         <v>1047</v>
       </c>
-      <c r="K114" t="s">
+      <c r="K117" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="1267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3960" uniqueCount="1305">
   <si>
     <t>日期</t>
   </si>
@@ -3695,6 +3695,120 @@
   </si>
   <si>
     <t>研究80/技能58/学历50/行业90/企业90</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>百心安生物（上海百心安生物技术股份有限公司）</t>
+  </si>
+  <si>
+    <t>研发工程师（生物可吸收冠状动脉支架）</t>
+  </si>
+  <si>
+    <t>专注新一代生物可吸收冠状动脉雷帕霉素洗脱支架（Bioheart）的研发、生产工艺与检验；涉及高分子可降解材料选型、支架结构设计、体外降解与力学性能测试、动物植入实验与临床注册支持。要求高分子材料、化学、生物等相关专业，硕士优先，有可降解材料/支架研发经验者优先。</t>
+  </si>
+  <si>
+    <t>https://jobs.51job.com/all/co/mountain_search_name%EF%BC%BF上海百心安生物技术股份有限公司</t>
+  </si>
+  <si>
+    <t>智能匹配88分【社招】|强烈推荐|生物可吸收支架研发岗，属支架研究方向精确匹配，材料+降解+动物实验技能重合</t>
+  </si>
+  <si>
+    <t>研究90/技能80/学历90/行业100/企业88</t>
+  </si>
+  <si>
+    <t>百心安专注于生物可吸收冠状动脉支架（Bioheart）研发，与本人血管支架研究方向完全一致，是生物可吸收支架领域少数的专注研发型平台。岗位职责覆盖可降解高分子材料选型、支架结构设计、体外降解与力学测试及动物植入实验，与本人材料学、生物相容性评价、支架设计与动物实验四项核心技能高度重合，且位于上海，契合目标城市。硕士学历、生物医学工程专业对正对。</t>
+  </si>
+  <si>
+    <t>突出血管支架研究方向与生物可吸收/可降解材料课题；量化体外降解速率、力学与生物相容性数据；详细描述动物植入实验全流程（模型建立、影像学/组织学随访评估）；同时强调对Bioheart类雷帕霉素洗脱支架产品与ISO 10993生物相容性标准的熟悉。</t>
+  </si>
+  <si>
+    <t>微创心通医疗（上海微创心通医疗科技有限公司）</t>
+  </si>
+  <si>
+    <t>负责血管介入/心脏瓣膜介入产品的支架结构设计与开发，参与产品从设计到临床注册的全流程；要求机械、材料、生物医学工程等相关专业，硕士学历，具备支架结构设计、力学分析与材料应用能力，有医疗器械研发经验者优先；经验不限，适合应届生加入。</t>
+  </si>
+  <si>
+    <t>智能匹配87分【社招】|强烈推荐|支架研发岗，心脏介入医疗器械方向，硕士可投且不限经验，适合应届生</t>
+  </si>
+  <si>
+    <t>研究85/技能78/学历100/行业100/企业90</t>
+  </si>
+  <si>
+    <t>微创心通为微创系心血管介入上市平台，岗位为支架结构设计与开发，与本人血管支架研究方向直接相关。要求硕士学历、经验不限，非常适合应届硕士投递。岗位涉及结构设计、力学分析与材料应用，覆盖本人支架设计与材料学核心技能；公司为港股上市微创系企业，平台优质，位于上海，契合目标城市。</t>
+  </si>
+  <si>
+    <t>突出硕士阶段支架结构设计与有限元力学分析项目；列出所用材料（镍钛/钴铬/高分子）及材料性能测试经验；补充生物相容性评价与动物实验经历以匹配心脏介入高风险器械要求；表明可在血管支架与瓣膜支架两类产品灵活投入。</t>
+  </si>
+  <si>
+    <t>汉通医疗（上海汉通医疗科技有限公司）</t>
+  </si>
+  <si>
+    <t>负责心血管植入介入器械的支架部分研发，参与超声导管等有源医疗器械的产品化；涉及支架结构设计、材料选型、性能测试与工艺开发。要求硕士优先，机械、材料、生物医学工程等专业，具备血管支架或介入器械研发经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|支架研发岗，心血管植入介入方向，硕士优先</t>
+  </si>
+  <si>
+    <t>汉通医疗为心血管植入介入医疗器械科创企业，设有支架研发岗位，与本人血管支架研究方向匹配。岗位涉及支架结构设计与材料应用，覆盖本人支架设计+材料学核心技能。硕士学历符合要求，位于上海，契合目标城市。适合有志于介入器械研发的应届硕士投递。</t>
+  </si>
+  <si>
+    <t>围绕血管支架结构设计课题展开；突出金属/高分子材料性能测试与选型经验；提及超声或介入器械理解以契合公司介入超声产品线；量化力学与生物相容性评价数据。</t>
+  </si>
+  <si>
+    <t>深圳脉动医学技术有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（血管内介入）</t>
+  </si>
+  <si>
+    <t>专注于血管内介入高端医疗器械（心血管/外周/神经介入支架、球囊、导管）的研发；参与产品设计、工艺开发与性能验证。硕士优先，机械、材料、生物医学工程等相关专业，有介入器械研发经验者优先。</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|血管内介入研发岗，方向相关，平台专业</t>
+  </si>
+  <si>
+    <t>研究85/技能72/学历90/行业100/企业84</t>
+  </si>
+  <si>
+    <t>脉动医学专注于血管内介入高端器械研发，覆盖心血管/外周/神经等介入支架、球囊、导管，与本人介入医疗器械专业方向和支架研究高度相关。岗位位于深圳（目标城市），涉足多管线介入研发，平台成长性强，适合希望在介入高压线与器械方向深耕的硕士。</t>
+  </si>
+  <si>
+    <t>突出血管支架研究工作与介入器械理解；强调材料学、结构与力学软组织；说明对该领域多管线产品的兴趣与学习意愿；量化所参与项目的设计与验证数据。</t>
+  </si>
+  <si>
+    <t>北京泰杰伟业科技股份有限公司</t>
+  </si>
+  <si>
+    <t>研发工程师（植入介入医疗器械）</t>
+  </si>
+  <si>
+    <t>负责植入/介入医疗器械（耗材）研发，涉及产品设计、工艺与材料应用；本科及以上学历，医疗器械/生物医学工程相关专业，无需经验，欢迎应届生；北京平谷区。</t>
+  </si>
+  <si>
+    <t>https://jobs.51job.com</t>
+  </si>
+  <si>
+    <t>智能匹配76分【社招】|值得考虑|植入介入医疗器械研发岗，方向相关，应届可投</t>
+  </si>
+  <si>
+    <t>研究75/技能60/学历90/行业100/企业80</t>
+  </si>
+  <si>
+    <t>苏州中天医疗器械科技有限公司</t>
+  </si>
+  <si>
+    <t>工艺工程师（支架/导管类）</t>
+  </si>
+  <si>
+    <t>负责支架/导管类介入器械的工艺开发、工装夹具设计、过程确认、工艺参数优化与量产转化；大专及以上学历，3-4年经验，医疗器械研发相关背景；苏州工业园区。</t>
+  </si>
+  <si>
+    <t>智能匹配77分【社招】|值得考虑|支架/导管器械工艺岗，方向相关，位于苏州</t>
+  </si>
+  <si>
+    <t>研究80/技能60/学历85/行业100/企业78</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4249,7 +4363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L163"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10456,6 +10570,234 @@
         <v>79</v>
       </c>
       <c r="L163" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E164" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G164">
+        <v>9</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I164">
+        <v>88</v>
+      </c>
+      <c r="J164" t="s">
+        <v>1233</v>
+      </c>
+      <c r="K164" t="s">
+        <v>1234</v>
+      </c>
+      <c r="L164" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C165" t="s">
+        <v>610</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E165" t="s">
+        <v>16</v>
+      </c>
+      <c r="F165" t="s">
+        <v>604</v>
+      </c>
+      <c r="G165">
+        <v>9</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I165">
+        <v>87</v>
+      </c>
+      <c r="J165" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C166" t="s">
+        <v>610</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E166" t="s">
+        <v>16</v>
+      </c>
+      <c r="F166" t="s">
+        <v>604</v>
+      </c>
+      <c r="G166">
+        <v>9</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I166">
+        <v>85</v>
+      </c>
+      <c r="J166" t="s">
+        <v>312</v>
+      </c>
+      <c r="K166" t="s">
+        <v>1245</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E167" t="s">
+        <v>66</v>
+      </c>
+      <c r="F167" t="s">
+        <v>604</v>
+      </c>
+      <c r="G167">
+        <v>8</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I167">
+        <v>83</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1251</v>
+      </c>
+      <c r="K167" t="s">
+        <v>1252</v>
+      </c>
+      <c r="L167" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E168" t="s">
+        <v>25</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G168">
+        <v>8</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I168">
+        <v>76</v>
+      </c>
+      <c r="J168" t="s">
+        <v>1259</v>
+      </c>
+      <c r="K168" t="s">
+        <v>79</v>
+      </c>
+      <c r="L168" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E169" t="s">
+        <v>75</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G169">
+        <v>8</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I169">
+        <v>77</v>
+      </c>
+      <c r="J169" t="s">
+        <v>1264</v>
+      </c>
+      <c r="K169" t="s">
+        <v>79</v>
+      </c>
+      <c r="L169" t="s">
         <v>79</v>
       </c>
     </row>
@@ -10490,7 +10832,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1227</v>
+        <v>1265</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10499,16 +10841,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1228</v>
+        <v>1266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1229</v>
+        <v>1267</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1230</v>
+        <v>1268</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1231</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10522,13 +10864,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1232</v>
+        <v>1270</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1233</v>
+        <v>1271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1234</v>
+        <v>1272</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -10556,7 +10898,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10571,7 +10913,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1239</v>
+        <v>1277</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10581,31 +10923,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1240</v>
+        <v>1278</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1241</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1242</v>
+        <v>1280</v>
       </c>
       <c r="B4">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1243</v>
+        <v>1281</v>
       </c>
       <c r="B5" t="s">
-        <v>1244</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1245</v>
+        <v>1283</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -10613,7 +10955,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1246</v>
+        <v>1284</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -10621,23 +10963,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1247</v>
+        <v>1285</v>
       </c>
       <c r="B8">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1248</v>
+        <v>1286</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1249</v>
+        <v>1287</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -10645,15 +10987,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1250</v>
+        <v>1288</v>
       </c>
       <c r="B11" t="s">
-        <v>1210</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1251</v>
+        <v>1289</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10663,15 +11005,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1252</v>
+        <v>1290</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1253</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1254</v>
+        <v>1292</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -10679,23 +11021,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1255</v>
+        <v>1293</v>
       </c>
       <c r="B17" s="5">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1256</v>
+        <v>1294</v>
       </c>
       <c r="B18" s="5">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="B19" s="5">
         <v>6</v>
@@ -10703,7 +11045,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1258</v>
+        <v>1296</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10711,7 +11053,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1259</v>
+        <v>1297</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -10719,7 +11061,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1260</v>
+        <v>1298</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -10727,7 +11069,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1261</v>
+        <v>1299</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -10735,7 +11077,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1262</v>
+        <v>1300</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -10743,7 +11085,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1263</v>
+        <v>1301</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -10751,7 +11093,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1264</v>
+        <v>1302</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -10763,7 +11105,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1265</v>
+        <v>1303</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -10781,7 +11123,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1266</v>
+        <v>1304</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -12820,25 +13162,25 @@
         <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="C108" t="s">
-        <v>1201</v>
+        <v>1228</v>
       </c>
       <c r="D108" t="s">
-        <v>1202</v>
+        <v>1229</v>
       </c>
       <c r="E108" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>1205</v>
+        <v>1231</v>
       </c>
       <c r="G108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H108" t="s">
-        <v>1206</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -12846,25 +13188,25 @@
         <v>80</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>1227</v>
       </c>
       <c r="C109" t="s">
-        <v>72</v>
+        <v>1236</v>
       </c>
       <c r="D109" t="s">
-        <v>73</v>
+        <v>610</v>
       </c>
       <c r="E109" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>76</v>
+        <v>604</v>
       </c>
       <c r="G109">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H109" t="s">
-        <v>77</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -12872,25 +13214,25 @@
         <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>1227</v>
       </c>
       <c r="C110" t="s">
-        <v>80</v>
+        <v>1242</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>610</v>
       </c>
       <c r="E110" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="G110">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H110" t="s">
-        <v>84</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -12898,25 +13240,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>1201</v>
       </c>
       <c r="D111" t="s">
-        <v>104</v>
+        <v>1202</v>
       </c>
       <c r="E111" t="s">
-        <v>106</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="s">
-        <v>107</v>
+        <v>1205</v>
       </c>
       <c r="G111">
         <v>8</v>
       </c>
       <c r="H111" t="s">
-        <v>108</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -12927,22 +13269,22 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D112" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E112" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F112" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -12953,22 +13295,22 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D113" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F113" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -12979,22 +13321,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E114" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -13005,22 +13347,22 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E115" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -13031,22 +13373,22 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D116" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -13054,25 +13396,25 @@
         <v>88</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="D117" t="s">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="E117" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="F117" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -13080,25 +13422,25 @@
         <v>89</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="D118" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="F118" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -13106,25 +13448,25 @@
         <v>90</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="D119" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="E119" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -13135,22 +13477,22 @@
         <v>159</v>
       </c>
       <c r="C120" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D120" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="E120" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F120" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13161,22 +13503,22 @@
         <v>159</v>
       </c>
       <c r="C121" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D121" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="E121" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F121" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -13187,22 +13529,22 @@
         <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D122" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="E122" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="F122" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -13213,22 +13555,22 @@
         <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D123" t="s">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F123" t="s">
-        <v>251</v>
+        <v>76</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -13239,22 +13581,22 @@
         <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D124" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E124" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13265,22 +13607,22 @@
         <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D125" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E125" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -13291,22 +13633,22 @@
         <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D126" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
       </c>
       <c r="F126" t="s">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -13317,22 +13659,22 @@
         <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="D127" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="E127" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="F127" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -13340,25 +13682,25 @@
         <v>99</v>
       </c>
       <c r="B128" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C128" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="D128" t="s">
-        <v>316</v>
+        <v>122</v>
       </c>
       <c r="E128" t="s">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="F128" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>320</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -13366,25 +13708,25 @@
         <v>100</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="D129" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="E129" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>343</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -13392,25 +13734,25 @@
         <v>101</v>
       </c>
       <c r="B130" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="D130" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="E130" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="F130" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>351</v>
+        <v>282</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -13421,22 +13763,22 @@
         <v>284</v>
       </c>
       <c r="C131" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="D131" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="E131" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="F131" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -13447,22 +13789,22 @@
         <v>284</v>
       </c>
       <c r="C132" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E132" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="F132" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -13473,22 +13815,22 @@
         <v>284</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>347</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="E133" t="s">
-        <v>396</v>
+        <v>98</v>
       </c>
       <c r="F133" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -13496,25 +13838,25 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C134" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="D134" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="E134" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F134" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -13522,25 +13864,25 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C135" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="D135" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="E135" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F135" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -13548,25 +13890,25 @@
         <v>107</v>
       </c>
       <c r="B136" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C136" t="s">
-        <v>424</v>
+        <v>144</v>
       </c>
       <c r="D136" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E136" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F136" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -13577,22 +13919,22 @@
         <v>402</v>
       </c>
       <c r="C137" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="D137" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E137" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F137" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -13600,25 +13942,25 @@
         <v>109</v>
       </c>
       <c r="B138" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C138" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="D138" t="s">
-        <v>122</v>
+        <v>419</v>
       </c>
       <c r="E138" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F138" t="s">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>487</v>
+        <v>422</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -13626,25 +13968,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C139" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="D139" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="E139" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F139" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -13652,25 +13994,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C140" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="D140" t="s">
-        <v>500</v>
+        <v>431</v>
       </c>
       <c r="E140" t="s">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="F140" t="s">
-        <v>503</v>
+        <v>433</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -13681,22 +14023,22 @@
         <v>473</v>
       </c>
       <c r="C141" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="D141" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="E141" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="F141" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>537</v>
+        <v>487</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13707,22 +14049,22 @@
         <v>473</v>
       </c>
       <c r="C142" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="D142" t="s">
-        <v>551</v>
+        <v>492</v>
       </c>
       <c r="E142" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F142" t="s">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13730,25 +14072,25 @@
         <v>114</v>
       </c>
       <c r="B143" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C143" t="s">
-        <v>578</v>
+        <v>499</v>
       </c>
       <c r="D143" t="s">
-        <v>579</v>
+        <v>500</v>
       </c>
       <c r="E143" t="s">
-        <v>66</v>
+        <v>502</v>
       </c>
       <c r="F143" t="s">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13756,25 +14098,25 @@
         <v>115</v>
       </c>
       <c r="B144" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C144" t="s">
-        <v>584</v>
+        <v>532</v>
       </c>
       <c r="D144" t="s">
-        <v>585</v>
+        <v>533</v>
       </c>
       <c r="E144" t="s">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="F144" t="s">
-        <v>588</v>
+        <v>536</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>589</v>
+        <v>537</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -13782,25 +14124,25 @@
         <v>116</v>
       </c>
       <c r="B145" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C145" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
       <c r="D145" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
       <c r="E145" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>605</v>
+        <v>554</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -13808,25 +14150,25 @@
         <v>117</v>
       </c>
       <c r="B146" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C146" t="s">
-        <v>616</v>
+        <v>578</v>
       </c>
       <c r="D146" t="s">
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="E146" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F146" t="s">
-        <v>618</v>
+        <v>581</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>619</v>
+        <v>582</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13834,25 +14176,25 @@
         <v>118</v>
       </c>
       <c r="B147" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C147" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="D147" t="s">
-        <v>623</v>
+        <v>585</v>
       </c>
       <c r="E147" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F147" t="s">
-        <v>468</v>
+        <v>588</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>625</v>
+        <v>589</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13863,22 +14205,22 @@
         <v>591</v>
       </c>
       <c r="C148" t="s">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="D148" t="s">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="E148" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F148" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13889,22 +14231,22 @@
         <v>591</v>
       </c>
       <c r="C149" t="s">
-        <v>650</v>
+        <v>616</v>
       </c>
       <c r="D149" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="E149" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F149" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>654</v>
+        <v>619</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -13915,22 +14257,22 @@
         <v>591</v>
       </c>
       <c r="C150" t="s">
-        <v>658</v>
+        <v>557</v>
       </c>
       <c r="D150" t="s">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="E150" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>662</v>
+        <v>468</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>663</v>
+        <v>625</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -13941,22 +14283,22 @@
         <v>591</v>
       </c>
       <c r="C151" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="D151" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="E151" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -13967,22 +14309,22 @@
         <v>591</v>
       </c>
       <c r="C152" t="s">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="D152" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="E152" t="s">
         <v>66</v>
       </c>
       <c r="F152" t="s">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -13990,25 +14332,25 @@
         <v>124</v>
       </c>
       <c r="B153" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C153" t="s">
-        <v>714</v>
+        <v>658</v>
       </c>
       <c r="D153" t="s">
-        <v>715</v>
+        <v>659</v>
       </c>
       <c r="E153" t="s">
-        <v>16</v>
+        <v>661</v>
       </c>
       <c r="F153" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>717</v>
+        <v>663</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14016,25 +14358,25 @@
         <v>125</v>
       </c>
       <c r="B154" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C154" t="s">
-        <v>721</v>
+        <v>666</v>
       </c>
       <c r="D154" t="s">
-        <v>722</v>
+        <v>667</v>
       </c>
       <c r="E154" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F154" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>725</v>
+        <v>669</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -14042,25 +14384,25 @@
         <v>126</v>
       </c>
       <c r="B155" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C155" t="s">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="D155" t="s">
-        <v>730</v>
+        <v>674</v>
       </c>
       <c r="E155" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="F155" t="s">
-        <v>732</v>
+        <v>676</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>733</v>
+        <v>677</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -14071,13 +14413,13 @@
         <v>697</v>
       </c>
       <c r="C156" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="D156" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="E156" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="F156" t="s">
         <v>604</v>
@@ -14086,7 +14428,7 @@
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>740</v>
+        <v>717</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -14097,22 +14439,22 @@
         <v>697</v>
       </c>
       <c r="C157" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="D157" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="E157" t="s">
-        <v>747</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -14123,22 +14465,22 @@
         <v>697</v>
       </c>
       <c r="C158" t="s">
-        <v>753</v>
+        <v>729</v>
       </c>
       <c r="D158" t="s">
-        <v>754</v>
+        <v>730</v>
       </c>
       <c r="E158" t="s">
-        <v>756</v>
+        <v>535</v>
       </c>
       <c r="F158" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>758</v>
+        <v>733</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -14149,22 +14491,22 @@
         <v>697</v>
       </c>
       <c r="C159" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="D159" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="E159" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="F159" t="s">
-        <v>764</v>
+        <v>604</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>765</v>
+        <v>740</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14172,25 +14514,25 @@
         <v>131</v>
       </c>
       <c r="B160" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C160" t="s">
-        <v>791</v>
+        <v>744</v>
       </c>
       <c r="D160" t="s">
-        <v>610</v>
+        <v>745</v>
       </c>
       <c r="E160" t="s">
-        <v>793</v>
+        <v>747</v>
       </c>
       <c r="F160" t="s">
-        <v>794</v>
+        <v>748</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>795</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -14198,25 +14540,25 @@
         <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C161" t="s">
-        <v>807</v>
+        <v>753</v>
       </c>
       <c r="D161" t="s">
-        <v>808</v>
+        <v>754</v>
       </c>
       <c r="E161" t="s">
-        <v>810</v>
+        <v>756</v>
       </c>
       <c r="F161" t="s">
-        <v>811</v>
+        <v>757</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>812</v>
+        <v>758</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -14224,25 +14566,25 @@
         <v>133</v>
       </c>
       <c r="B162" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C162" t="s">
-        <v>816</v>
+        <v>760</v>
       </c>
       <c r="D162" t="s">
-        <v>110</v>
+        <v>761</v>
       </c>
       <c r="E162" t="s">
-        <v>16</v>
+        <v>763</v>
       </c>
       <c r="F162" t="s">
-        <v>818</v>
+        <v>764</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>819</v>
+        <v>765</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14250,25 +14592,25 @@
         <v>134</v>
       </c>
       <c r="B163" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C163" t="s">
-        <v>888</v>
+        <v>791</v>
       </c>
       <c r="D163" t="s">
-        <v>889</v>
+        <v>610</v>
       </c>
       <c r="E163" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="F163" t="s">
-        <v>891</v>
+        <v>794</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>892</v>
+        <v>795</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14276,25 +14618,25 @@
         <v>135</v>
       </c>
       <c r="B164" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C164" t="s">
-        <v>896</v>
+        <v>807</v>
       </c>
       <c r="D164" t="s">
-        <v>897</v>
+        <v>808</v>
       </c>
       <c r="E164" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F164" t="s">
-        <v>899</v>
+        <v>811</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>900</v>
+        <v>812</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14302,25 +14644,25 @@
         <v>136</v>
       </c>
       <c r="B165" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C165" t="s">
-        <v>904</v>
+        <v>816</v>
       </c>
       <c r="D165" t="s">
-        <v>585</v>
+        <v>110</v>
       </c>
       <c r="E165" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F165" t="s">
-        <v>906</v>
+        <v>818</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>907</v>
+        <v>819</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14331,22 +14673,22 @@
         <v>845</v>
       </c>
       <c r="C166" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="D166" t="s">
-        <v>585</v>
+        <v>889</v>
       </c>
       <c r="E166" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>914</v>
+        <v>892</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -14357,22 +14699,22 @@
         <v>845</v>
       </c>
       <c r="C167" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="D167" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="E167" t="s">
-        <v>921</v>
+        <v>25</v>
       </c>
       <c r="F167" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -14380,25 +14722,25 @@
         <v>139</v>
       </c>
       <c r="B168" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C168" t="s">
-        <v>964</v>
+        <v>904</v>
       </c>
       <c r="D168" t="s">
-        <v>965</v>
+        <v>585</v>
       </c>
       <c r="E168" t="s">
-        <v>967</v>
+        <v>66</v>
       </c>
       <c r="F168" t="s">
-        <v>968</v>
+        <v>906</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>969</v>
+        <v>907</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -14406,25 +14748,25 @@
         <v>140</v>
       </c>
       <c r="B169" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C169" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="D169" t="s">
-        <v>1002</v>
+        <v>585</v>
       </c>
       <c r="E169" t="s">
-        <v>1004</v>
+        <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>438</v>
+        <v>913</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>1005</v>
+        <v>914</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -14432,25 +14774,25 @@
         <v>141</v>
       </c>
       <c r="B170" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>918</v>
       </c>
       <c r="D170" t="s">
-        <v>1009</v>
+        <v>919</v>
       </c>
       <c r="E170" t="s">
-        <v>16</v>
+        <v>921</v>
       </c>
       <c r="F170" t="s">
-        <v>1011</v>
+        <v>922</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>1012</v>
+        <v>923</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14461,22 +14803,22 @@
         <v>934</v>
       </c>
       <c r="C171" t="s">
-        <v>650</v>
+        <v>964</v>
       </c>
       <c r="D171" t="s">
-        <v>1016</v>
+        <v>965</v>
       </c>
       <c r="E171" t="s">
-        <v>66</v>
+        <v>967</v>
       </c>
       <c r="F171" t="s">
-        <v>1018</v>
+        <v>968</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>1019</v>
+        <v>969</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14487,22 +14829,22 @@
         <v>934</v>
       </c>
       <c r="C172" t="s">
-        <v>1023</v>
+        <v>950</v>
       </c>
       <c r="D172" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
       <c r="E172" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="F172" t="s">
-        <v>1027</v>
+        <v>438</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>1028</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14513,22 +14855,22 @@
         <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
       <c r="D173" t="s">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="E173" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F173" t="s">
-        <v>1034</v>
+        <v>1011</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>1035</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -14539,22 +14881,22 @@
         <v>934</v>
       </c>
       <c r="C174" t="s">
-        <v>1039</v>
+        <v>650</v>
       </c>
       <c r="D174" t="s">
-        <v>1040</v>
+        <v>1016</v>
       </c>
       <c r="E174" t="s">
-        <v>1042</v>
+        <v>66</v>
       </c>
       <c r="F174" t="s">
-        <v>1043</v>
+        <v>1018</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1044</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -14565,22 +14907,22 @@
         <v>934</v>
       </c>
       <c r="C175" t="s">
-        <v>1048</v>
+        <v>1023</v>
       </c>
       <c r="D175" t="s">
-        <v>1049</v>
+        <v>1024</v>
       </c>
       <c r="E175" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="F175" t="s">
-        <v>1052</v>
+        <v>1027</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1053</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -14591,22 +14933,22 @@
         <v>934</v>
       </c>
       <c r="C176" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="D176" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="E176" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F176" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1061</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14617,22 +14959,22 @@
         <v>934</v>
       </c>
       <c r="C177" t="s">
-        <v>1082</v>
+        <v>1039</v>
       </c>
       <c r="D177" t="s">
-        <v>1083</v>
+        <v>1040</v>
       </c>
       <c r="E177" t="s">
-        <v>1085</v>
+        <v>1042</v>
       </c>
       <c r="F177" t="s">
-        <v>959</v>
+        <v>1043</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1086</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -14640,25 +14982,25 @@
         <v>149</v>
       </c>
       <c r="B178" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C178" t="s">
-        <v>271</v>
+        <v>1048</v>
       </c>
       <c r="D178" t="s">
-        <v>1104</v>
+        <v>1049</v>
       </c>
       <c r="E178" t="s">
-        <v>1106</v>
+        <v>1051</v>
       </c>
       <c r="F178" t="s">
-        <v>1107</v>
+        <v>1052</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>1108</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -14666,25 +15008,25 @@
         <v>150</v>
       </c>
       <c r="B179" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C179" t="s">
-        <v>1112</v>
+        <v>1057</v>
       </c>
       <c r="D179" t="s">
-        <v>1113</v>
+        <v>1058</v>
       </c>
       <c r="E179" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F179" t="s">
-        <v>1115</v>
+        <v>1060</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>1116</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -14692,25 +15034,25 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C180" t="s">
-        <v>1120</v>
+        <v>1082</v>
       </c>
       <c r="D180" t="s">
-        <v>1121</v>
+        <v>1083</v>
       </c>
       <c r="E180" t="s">
-        <v>1123</v>
+        <v>1085</v>
       </c>
       <c r="F180" t="s">
-        <v>1124</v>
+        <v>959</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>1125</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -14721,22 +15063,22 @@
         <v>1087</v>
       </c>
       <c r="C181" t="s">
-        <v>1129</v>
+        <v>271</v>
       </c>
       <c r="D181" t="s">
-        <v>1130</v>
+        <v>1104</v>
       </c>
       <c r="E181" t="s">
-        <v>1132</v>
+        <v>1106</v>
       </c>
       <c r="F181" t="s">
-        <v>1133</v>
+        <v>1107</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>1134</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -14744,25 +15086,25 @@
         <v>153</v>
       </c>
       <c r="B182" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C182" t="s">
-        <v>1172</v>
+        <v>1112</v>
       </c>
       <c r="D182" t="s">
-        <v>122</v>
+        <v>1113</v>
       </c>
       <c r="E182" t="s">
-        <v>1174</v>
+        <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>1175</v>
+        <v>1115</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>1176</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -14770,25 +15112,25 @@
         <v>154</v>
       </c>
       <c r="B183" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C183" t="s">
-        <v>1178</v>
+        <v>1120</v>
       </c>
       <c r="D183" t="s">
-        <v>1179</v>
+        <v>1121</v>
       </c>
       <c r="E183" t="s">
-        <v>1181</v>
+        <v>1123</v>
       </c>
       <c r="F183" t="s">
-        <v>1175</v>
+        <v>1124</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>1182</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -14796,25 +15138,25 @@
         <v>155</v>
       </c>
       <c r="B184" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C184" t="s">
-        <v>1184</v>
+        <v>1129</v>
       </c>
       <c r="D184" t="s">
-        <v>1185</v>
+        <v>1130</v>
       </c>
       <c r="E184" t="s">
-        <v>1187</v>
+        <v>1132</v>
       </c>
       <c r="F184" t="s">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>1188</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -14822,25 +15164,25 @@
         <v>156</v>
       </c>
       <c r="B185" t="s">
-        <v>1210</v>
+        <v>1171</v>
       </c>
       <c r="C185" t="s">
-        <v>1211</v>
+        <v>1172</v>
       </c>
       <c r="D185" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E185" t="s">
-        <v>1213</v>
+        <v>1174</v>
       </c>
       <c r="F185" t="s">
-        <v>1214</v>
+        <v>1175</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>1215</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -14848,25 +15190,25 @@
         <v>157</v>
       </c>
       <c r="B186" t="s">
-        <v>159</v>
+        <v>1171</v>
       </c>
       <c r="C186" t="s">
-        <v>271</v>
+        <v>1178</v>
       </c>
       <c r="D186" t="s">
-        <v>272</v>
+        <v>1179</v>
       </c>
       <c r="E186" t="s">
-        <v>75</v>
+        <v>1181</v>
       </c>
       <c r="F186" t="s">
-        <v>274</v>
+        <v>1175</v>
       </c>
       <c r="G186">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>275</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -14874,25 +15216,25 @@
         <v>158</v>
       </c>
       <c r="B187" t="s">
-        <v>591</v>
+        <v>1171</v>
       </c>
       <c r="C187" t="s">
-        <v>681</v>
+        <v>1184</v>
       </c>
       <c r="D187" t="s">
-        <v>682</v>
+        <v>1185</v>
       </c>
       <c r="E187" t="s">
-        <v>25</v>
+        <v>1187</v>
       </c>
       <c r="F187" t="s">
-        <v>684</v>
+        <v>1175</v>
       </c>
       <c r="G187">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>685</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -14900,25 +15242,25 @@
         <v>159</v>
       </c>
       <c r="B188" t="s">
-        <v>591</v>
+        <v>1210</v>
       </c>
       <c r="C188" t="s">
-        <v>689</v>
+        <v>1211</v>
       </c>
       <c r="D188" t="s">
-        <v>690</v>
+        <v>89</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>1213</v>
       </c>
       <c r="F188" t="s">
-        <v>692</v>
+        <v>1214</v>
       </c>
       <c r="G188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>693</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -14926,25 +15268,25 @@
         <v>160</v>
       </c>
       <c r="B189" t="s">
-        <v>697</v>
+        <v>1227</v>
       </c>
       <c r="C189" t="s">
-        <v>767</v>
+        <v>1247</v>
       </c>
       <c r="D189" t="s">
-        <v>768</v>
+        <v>1248</v>
       </c>
       <c r="E189" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F189" t="s">
-        <v>770</v>
+        <v>604</v>
       </c>
       <c r="G189">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>771</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -14952,25 +15294,25 @@
         <v>161</v>
       </c>
       <c r="B190" t="s">
-        <v>845</v>
+        <v>1227</v>
       </c>
       <c r="C190" t="s">
-        <v>927</v>
+        <v>1254</v>
       </c>
       <c r="D190" t="s">
-        <v>585</v>
+        <v>1255</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>929</v>
+        <v>1257</v>
       </c>
       <c r="G190">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>930</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -14978,24 +15320,180 @@
         <v>162</v>
       </c>
       <c r="B191" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E191" t="s">
+        <v>75</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G191">
+        <v>8</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>163</v>
+      </c>
+      <c r="B192" t="s">
+        <v>159</v>
+      </c>
+      <c r="C192" t="s">
+        <v>271</v>
+      </c>
+      <c r="D192" t="s">
+        <v>272</v>
+      </c>
+      <c r="E192" t="s">
+        <v>75</v>
+      </c>
+      <c r="F192" t="s">
+        <v>274</v>
+      </c>
+      <c r="G192">
+        <v>7</v>
+      </c>
+      <c r="H192" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>164</v>
+      </c>
+      <c r="B193" t="s">
+        <v>591</v>
+      </c>
+      <c r="C193" t="s">
+        <v>681</v>
+      </c>
+      <c r="D193" t="s">
+        <v>682</v>
+      </c>
+      <c r="E193" t="s">
+        <v>25</v>
+      </c>
+      <c r="F193" t="s">
+        <v>684</v>
+      </c>
+      <c r="G193">
+        <v>7</v>
+      </c>
+      <c r="H193" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>165</v>
+      </c>
+      <c r="B194" t="s">
+        <v>591</v>
+      </c>
+      <c r="C194" t="s">
+        <v>689</v>
+      </c>
+      <c r="D194" t="s">
+        <v>690</v>
+      </c>
+      <c r="E194" t="s">
+        <v>66</v>
+      </c>
+      <c r="F194" t="s">
+        <v>692</v>
+      </c>
+      <c r="G194">
+        <v>7</v>
+      </c>
+      <c r="H194" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>166</v>
+      </c>
+      <c r="B195" t="s">
+        <v>697</v>
+      </c>
+      <c r="C195" t="s">
+        <v>767</v>
+      </c>
+      <c r="D195" t="s">
+        <v>768</v>
+      </c>
+      <c r="E195" t="s">
+        <v>25</v>
+      </c>
+      <c r="F195" t="s">
+        <v>770</v>
+      </c>
+      <c r="G195">
+        <v>7</v>
+      </c>
+      <c r="H195" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>167</v>
+      </c>
+      <c r="B196" t="s">
+        <v>845</v>
+      </c>
+      <c r="C196" t="s">
+        <v>927</v>
+      </c>
+      <c r="D196" t="s">
+        <v>585</v>
+      </c>
+      <c r="E196" t="s">
+        <v>25</v>
+      </c>
+      <c r="F196" t="s">
+        <v>929</v>
+      </c>
+      <c r="G196">
+        <v>7</v>
+      </c>
+      <c r="H196" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>168</v>
+      </c>
+      <c r="B197" t="s">
         <v>1219</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C197" t="s">
         <v>1220</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D197" t="s">
         <v>1221</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E197" t="s">
         <v>1223</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F197" t="s">
         <v>1224</v>
       </c>
-      <c r="G191">
+      <c r="G197">
         <v>7</v>
       </c>
-      <c r="H191" t="s">
+      <c r="H197" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -15012,7 +15510,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15029,10 +15527,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1235</v>
+        <v>1273</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1236</v>
+        <v>1274</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -15059,12 +15557,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1237</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -15099,7 +15597,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -15134,7 +15632,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -15169,7 +15667,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -15204,7 +15702,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -15239,7 +15737,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -15274,7 +15772,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -15309,7 +15807,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -15344,7 +15842,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -15379,7 +15877,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -15414,7 +15912,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -15449,7 +15947,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -15484,7 +15982,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -15519,7 +16017,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -15554,7 +16052,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -15589,7 +16087,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -15624,7 +16122,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -15659,7 +16157,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B19">
         <v>91</v>
@@ -15694,7 +16192,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -15729,7 +16227,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -15764,7 +16262,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -15799,7 +16297,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -15834,7 +16332,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -15869,7 +16367,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -15904,7 +16402,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B26">
         <v>89</v>
@@ -15939,7 +16437,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -15974,7 +16472,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -16009,7 +16507,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -16044,7 +16542,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -16079,7 +16577,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -16114,7 +16612,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -16149,7 +16647,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -16184,7 +16682,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B34">
         <v>89</v>
@@ -16219,7 +16717,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B35">
         <v>88</v>
@@ -16254,7 +16752,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B36">
         <v>88</v>
@@ -16289,7 +16787,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B37">
         <v>88</v>
@@ -16324,7 +16822,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B38">
         <v>88</v>
@@ -16359,7 +16857,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B39">
         <v>88</v>
@@ -16394,7 +16892,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B40">
         <v>88</v>
@@ -16429,7 +16927,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B41">
         <v>88</v>
@@ -16464,7 +16962,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B42">
         <v>88</v>
@@ -16499,112 +16997,112 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B43">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>1228</v>
       </c>
       <c r="E43" t="s">
-        <v>185</v>
+        <v>1229</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>131</v>
+        <v>1231</v>
       </c>
       <c r="H43" t="s">
-        <v>188</v>
+        <v>1233</v>
       </c>
       <c r="I43" t="s">
-        <v>189</v>
+        <v>1234</v>
       </c>
       <c r="J43" t="s">
-        <v>190</v>
+        <v>1235</v>
       </c>
       <c r="K43" t="s">
-        <v>186</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B44">
         <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E44" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F44" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G44" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H44" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I44" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J44" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K44" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B45">
         <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E45" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G45" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H45" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I45" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J45" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K45" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B46">
         <v>87</v>
@@ -16616,7 +17114,7 @@
         <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F46" t="s">
         <v>66</v>
@@ -16634,374 +17132,374 @@
         <v>79</v>
       </c>
       <c r="K46" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B47">
         <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D47" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F47" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G47" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H47" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I47" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J47" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B48">
         <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D48" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E48" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G48" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H48" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I48" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J48" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K48" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B49">
         <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D49" t="s">
-        <v>864</v>
+        <v>570</v>
       </c>
       <c r="E49" t="s">
-        <v>865</v>
+        <v>571</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="H49" t="s">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="I49" t="s">
-        <v>870</v>
+        <v>576</v>
       </c>
       <c r="J49" t="s">
-        <v>871</v>
+        <v>577</v>
       </c>
       <c r="K49" t="s">
-        <v>866</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B50">
         <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D50" t="s">
-        <v>950</v>
+        <v>864</v>
       </c>
       <c r="E50" t="s">
-        <v>996</v>
+        <v>865</v>
       </c>
       <c r="F50" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>438</v>
+        <v>867</v>
       </c>
       <c r="H50" t="s">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="I50" t="s">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J50" t="s">
-        <v>1001</v>
+        <v>871</v>
       </c>
       <c r="K50" t="s">
-        <v>997</v>
+        <v>866</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B51">
         <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D51" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="E51" t="s">
-        <v>1097</v>
+        <v>996</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G51" t="s">
-        <v>1099</v>
+        <v>438</v>
       </c>
       <c r="H51" t="s">
-        <v>1101</v>
+        <v>999</v>
       </c>
       <c r="I51" t="s">
-        <v>1102</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="s">
-        <v>1103</v>
+        <v>1001</v>
       </c>
       <c r="K51" t="s">
-        <v>1098</v>
+        <v>997</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B52">
         <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D52" t="s">
-        <v>1156</v>
+        <v>964</v>
       </c>
       <c r="E52" t="s">
-        <v>1157</v>
+        <v>1097</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>1159</v>
+        <v>1099</v>
       </c>
       <c r="H52" t="s">
-        <v>1161</v>
+        <v>1101</v>
       </c>
       <c r="I52" t="s">
-        <v>1162</v>
+        <v>1102</v>
       </c>
       <c r="J52" t="s">
-        <v>1163</v>
+        <v>1103</v>
       </c>
       <c r="K52" t="s">
-        <v>1158</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B53">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>1155</v>
       </c>
       <c r="D53" t="s">
-        <v>369</v>
+        <v>1156</v>
       </c>
       <c r="E53" t="s">
-        <v>370</v>
+        <v>1157</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G53" t="s">
-        <v>372</v>
+        <v>1159</v>
       </c>
       <c r="H53" t="s">
-        <v>374</v>
+        <v>1161</v>
       </c>
       <c r="I53" t="s">
-        <v>375</v>
+        <v>1162</v>
       </c>
       <c r="J53" t="s">
-        <v>376</v>
+        <v>1163</v>
       </c>
       <c r="K53" t="s">
-        <v>371</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B54">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>402</v>
+        <v>1227</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>1236</v>
       </c>
       <c r="E54" t="s">
-        <v>457</v>
+        <v>610</v>
       </c>
       <c r="F54" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>438</v>
+        <v>604</v>
       </c>
       <c r="H54" t="s">
-        <v>460</v>
+        <v>1239</v>
       </c>
       <c r="I54" t="s">
-        <v>461</v>
+        <v>1240</v>
       </c>
       <c r="J54" t="s">
-        <v>462</v>
+        <v>1241</v>
       </c>
       <c r="K54" t="s">
-        <v>458</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B55">
         <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="E55" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="H55" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="I55" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J55" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="K55" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B56">
         <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D56" t="s">
-        <v>541</v>
+        <v>63</v>
       </c>
       <c r="E56" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F56" t="s">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="G56" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="H56" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="I56" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J56" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="K56" t="s">
-        <v>543</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B57">
         <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D57" t="s">
-        <v>557</v>
+        <v>322</v>
       </c>
       <c r="E57" t="s">
-        <v>558</v>
+        <v>466</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
@@ -17010,91 +17508,91 @@
         <v>468</v>
       </c>
       <c r="H57" t="s">
-        <v>561</v>
+        <v>470</v>
       </c>
       <c r="I57" t="s">
-        <v>562</v>
+        <v>471</v>
       </c>
       <c r="J57" t="s">
-        <v>563</v>
+        <v>472</v>
       </c>
       <c r="K57" t="s">
-        <v>559</v>
+        <v>467</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B58">
         <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D58" t="s">
-        <v>609</v>
+        <v>541</v>
       </c>
       <c r="E58" t="s">
-        <v>610</v>
+        <v>542</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G58" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="H58" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="I58" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="J58" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="K58" t="s">
-        <v>611</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B59">
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D59" t="s">
-        <v>627</v>
+        <v>557</v>
       </c>
       <c r="E59" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>630</v>
+        <v>468</v>
       </c>
       <c r="H59" t="s">
-        <v>632</v>
+        <v>561</v>
       </c>
       <c r="I59" t="s">
-        <v>633</v>
+        <v>562</v>
       </c>
       <c r="J59" t="s">
-        <v>634</v>
+        <v>563</v>
       </c>
       <c r="K59" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B60">
         <v>86</v>
@@ -17103,208 +17601,208 @@
         <v>591</v>
       </c>
       <c r="D60" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="E60" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>638</v>
+        <v>604</v>
       </c>
       <c r="H60" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="I60" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="J60" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="K60" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B61">
         <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D61" t="s">
-        <v>829</v>
+        <v>627</v>
       </c>
       <c r="E61" t="s">
-        <v>830</v>
+        <v>628</v>
       </c>
       <c r="F61" t="s">
-        <v>785</v>
+        <v>25</v>
       </c>
       <c r="G61" t="s">
-        <v>832</v>
+        <v>630</v>
       </c>
       <c r="H61" t="s">
-        <v>834</v>
+        <v>632</v>
       </c>
       <c r="I61" t="s">
-        <v>835</v>
+        <v>633</v>
       </c>
       <c r="J61" t="s">
-        <v>836</v>
+        <v>634</v>
       </c>
       <c r="K61" t="s">
-        <v>831</v>
+        <v>629</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B62">
         <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D62" t="s">
-        <v>872</v>
+        <v>635</v>
       </c>
       <c r="E62" t="s">
-        <v>873</v>
+        <v>636</v>
       </c>
       <c r="F62" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>875</v>
+        <v>638</v>
       </c>
       <c r="H62" t="s">
-        <v>877</v>
+        <v>640</v>
       </c>
       <c r="I62" t="s">
-        <v>878</v>
+        <v>641</v>
       </c>
       <c r="J62" t="s">
-        <v>879</v>
+        <v>642</v>
       </c>
       <c r="K62" t="s">
-        <v>874</v>
+        <v>637</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B63">
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D63" t="s">
-        <v>880</v>
+        <v>829</v>
       </c>
       <c r="E63" t="s">
-        <v>881</v>
+        <v>830</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>785</v>
       </c>
       <c r="G63" t="s">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="H63" t="s">
-        <v>885</v>
+        <v>834</v>
       </c>
       <c r="I63" t="s">
-        <v>886</v>
+        <v>835</v>
       </c>
       <c r="J63" t="s">
-        <v>887</v>
+        <v>836</v>
       </c>
       <c r="K63" t="s">
-        <v>882</v>
+        <v>831</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B64">
         <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D64" t="s">
-        <v>973</v>
+        <v>872</v>
       </c>
       <c r="E64" t="s">
-        <v>974</v>
+        <v>873</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G64" t="s">
-        <v>468</v>
+        <v>875</v>
       </c>
       <c r="H64" t="s">
-        <v>977</v>
+        <v>877</v>
       </c>
       <c r="I64" t="s">
-        <v>978</v>
+        <v>878</v>
       </c>
       <c r="J64" t="s">
-        <v>979</v>
+        <v>879</v>
       </c>
       <c r="K64" t="s">
-        <v>975</v>
+        <v>874</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B65">
         <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D65" t="s">
-        <v>980</v>
+        <v>880</v>
       </c>
       <c r="E65" t="s">
-        <v>981</v>
+        <v>881</v>
       </c>
       <c r="F65" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>984</v>
+        <v>883</v>
       </c>
       <c r="H65" t="s">
-        <v>986</v>
+        <v>885</v>
       </c>
       <c r="I65" t="s">
-        <v>987</v>
+        <v>886</v>
       </c>
       <c r="J65" t="s">
-        <v>988</v>
+        <v>887</v>
       </c>
       <c r="K65" t="s">
-        <v>982</v>
+        <v>882</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B66">
         <v>86</v>
@@ -17313,383 +17811,383 @@
         <v>934</v>
       </c>
       <c r="D66" t="s">
-        <v>1073</v>
+        <v>973</v>
       </c>
       <c r="E66" t="s">
-        <v>1074</v>
+        <v>974</v>
       </c>
       <c r="F66" t="s">
-        <v>1076</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>1077</v>
+        <v>468</v>
       </c>
       <c r="H66" t="s">
-        <v>1079</v>
+        <v>977</v>
       </c>
       <c r="I66" t="s">
-        <v>1080</v>
+        <v>978</v>
       </c>
       <c r="J66" t="s">
-        <v>1081</v>
+        <v>979</v>
       </c>
       <c r="K66" t="s">
-        <v>1075</v>
+        <v>975</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B67">
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D67" t="s">
-        <v>1088</v>
+        <v>980</v>
       </c>
       <c r="E67" t="s">
-        <v>1089</v>
+        <v>981</v>
       </c>
       <c r="F67" t="s">
-        <v>1091</v>
+        <v>983</v>
       </c>
       <c r="G67" t="s">
-        <v>1092</v>
+        <v>984</v>
       </c>
       <c r="H67" t="s">
-        <v>1094</v>
+        <v>986</v>
       </c>
       <c r="I67" t="s">
-        <v>1095</v>
+        <v>987</v>
       </c>
       <c r="J67" t="s">
-        <v>1096</v>
+        <v>988</v>
       </c>
       <c r="K67" t="s">
-        <v>1090</v>
+        <v>982</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B68">
         <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D68" t="s">
-        <v>1146</v>
+        <v>1073</v>
       </c>
       <c r="E68" t="s">
-        <v>1147</v>
+        <v>1074</v>
       </c>
       <c r="F68" t="s">
-        <v>1149</v>
+        <v>1076</v>
       </c>
       <c r="G68" t="s">
-        <v>1150</v>
+        <v>1077</v>
       </c>
       <c r="H68" t="s">
-        <v>1152</v>
+        <v>1079</v>
       </c>
       <c r="I68" t="s">
-        <v>1153</v>
+        <v>1080</v>
       </c>
       <c r="J68" t="s">
-        <v>1154</v>
+        <v>1081</v>
       </c>
       <c r="K68" t="s">
-        <v>1148</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B69">
         <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D69" t="s">
-        <v>1164</v>
+        <v>1088</v>
       </c>
       <c r="E69" t="s">
-        <v>610</v>
+        <v>1089</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>1091</v>
       </c>
       <c r="G69" t="s">
-        <v>1166</v>
+        <v>1092</v>
       </c>
       <c r="H69" t="s">
-        <v>1168</v>
+        <v>1094</v>
       </c>
       <c r="I69" t="s">
-        <v>1169</v>
+        <v>1095</v>
       </c>
       <c r="J69" t="s">
-        <v>1170</v>
+        <v>1096</v>
       </c>
       <c r="K69" t="s">
-        <v>1165</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B70">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>1146</v>
       </c>
       <c r="E70" t="s">
-        <v>56</v>
+        <v>1147</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G70" t="s">
-        <v>58</v>
+        <v>1150</v>
       </c>
       <c r="H70" t="s">
-        <v>60</v>
+        <v>1152</v>
       </c>
       <c r="I70" t="s">
-        <v>61</v>
+        <v>1153</v>
       </c>
       <c r="J70" t="s">
-        <v>62</v>
+        <v>1154</v>
       </c>
       <c r="K70" t="s">
-        <v>57</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B71">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="D71" t="s">
-        <v>128</v>
+        <v>1164</v>
       </c>
       <c r="E71" t="s">
-        <v>89</v>
+        <v>610</v>
       </c>
       <c r="F71" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>131</v>
+        <v>1166</v>
       </c>
       <c r="H71" t="s">
-        <v>133</v>
+        <v>1168</v>
       </c>
       <c r="I71" t="s">
-        <v>134</v>
+        <v>1169</v>
       </c>
       <c r="J71" t="s">
-        <v>135</v>
+        <v>1170</v>
       </c>
       <c r="K71" t="s">
-        <v>129</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B72">
         <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H72" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I72" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J72" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K72" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B73">
         <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E73" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G73" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H73" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I73" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J73" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K73" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B74">
         <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D74" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E74" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F74" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G74" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H74" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I74" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J74" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K74" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B75">
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D75" t="s">
-        <v>774</v>
+        <v>55</v>
       </c>
       <c r="E75" t="s">
-        <v>783</v>
+        <v>403</v>
       </c>
       <c r="F75" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>786</v>
+        <v>405</v>
       </c>
       <c r="H75" t="s">
-        <v>788</v>
+        <v>407</v>
       </c>
       <c r="I75" t="s">
-        <v>789</v>
+        <v>408</v>
       </c>
       <c r="J75" t="s">
-        <v>790</v>
+        <v>409</v>
       </c>
       <c r="K75" t="s">
-        <v>784</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B76">
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D76" t="s">
-        <v>799</v>
+        <v>474</v>
       </c>
       <c r="E76" t="s">
-        <v>800</v>
+        <v>475</v>
       </c>
       <c r="F76" t="s">
-        <v>793</v>
+        <v>477</v>
       </c>
       <c r="G76" t="s">
-        <v>802</v>
+        <v>478</v>
       </c>
       <c r="H76" t="s">
-        <v>804</v>
+        <v>480</v>
       </c>
       <c r="I76" t="s">
-        <v>805</v>
+        <v>481</v>
       </c>
       <c r="J76" t="s">
-        <v>806</v>
+        <v>482</v>
       </c>
       <c r="K76" t="s">
-        <v>801</v>
+        <v>476</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B77">
         <v>85</v>
@@ -17698,523 +18196,523 @@
         <v>773</v>
       </c>
       <c r="D77" t="s">
-        <v>821</v>
+        <v>774</v>
       </c>
       <c r="E77" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="F77" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="G77" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="H77" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="I77" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="J77" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="K77" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B78">
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D78" t="s">
-        <v>989</v>
+        <v>799</v>
       </c>
       <c r="E78" t="s">
-        <v>990</v>
+        <v>800</v>
       </c>
       <c r="F78" t="s">
-        <v>75</v>
+        <v>793</v>
       </c>
       <c r="G78" t="s">
-        <v>959</v>
+        <v>802</v>
       </c>
       <c r="H78" t="s">
-        <v>993</v>
+        <v>804</v>
       </c>
       <c r="I78" t="s">
-        <v>994</v>
+        <v>805</v>
       </c>
       <c r="J78" t="s">
-        <v>995</v>
+        <v>806</v>
       </c>
       <c r="K78" t="s">
-        <v>991</v>
+        <v>801</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B79">
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D79" t="s">
-        <v>1065</v>
+        <v>821</v>
       </c>
       <c r="E79" t="s">
-        <v>1066</v>
+        <v>822</v>
       </c>
       <c r="F79" t="s">
-        <v>147</v>
+        <v>777</v>
       </c>
       <c r="G79" t="s">
-        <v>1068</v>
+        <v>824</v>
       </c>
       <c r="H79" t="s">
-        <v>1070</v>
+        <v>826</v>
       </c>
       <c r="I79" t="s">
-        <v>1071</v>
+        <v>827</v>
       </c>
       <c r="J79" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="K79" t="s">
-        <v>1067</v>
+        <v>823</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B80">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D80" t="s">
-        <v>144</v>
+        <v>989</v>
       </c>
       <c r="E80" t="s">
-        <v>145</v>
+        <v>990</v>
       </c>
       <c r="F80" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G80" t="s">
-        <v>148</v>
+        <v>959</v>
       </c>
       <c r="H80" t="s">
-        <v>150</v>
+        <v>993</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>994</v>
       </c>
       <c r="J80" t="s">
-        <v>152</v>
+        <v>995</v>
       </c>
       <c r="K80" t="s">
-        <v>146</v>
+        <v>991</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B81">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D81" t="s">
-        <v>144</v>
+        <v>1065</v>
       </c>
       <c r="E81" t="s">
-        <v>394</v>
+        <v>1066</v>
       </c>
       <c r="F81" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G81" t="s">
-        <v>397</v>
+        <v>1068</v>
       </c>
       <c r="H81" t="s">
-        <v>399</v>
+        <v>1070</v>
       </c>
       <c r="I81" t="s">
-        <v>400</v>
+        <v>1071</v>
       </c>
       <c r="J81" t="s">
-        <v>401</v>
+        <v>1072</v>
       </c>
       <c r="K81" t="s">
-        <v>395</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B82">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>402</v>
+        <v>1227</v>
       </c>
       <c r="D82" t="s">
-        <v>410</v>
+        <v>1242</v>
       </c>
       <c r="E82" t="s">
-        <v>411</v>
+        <v>610</v>
       </c>
       <c r="F82" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>413</v>
+        <v>604</v>
       </c>
       <c r="H82" t="s">
-        <v>415</v>
+        <v>312</v>
       </c>
       <c r="I82" t="s">
-        <v>416</v>
+        <v>1245</v>
       </c>
       <c r="J82" t="s">
-        <v>417</v>
+        <v>1246</v>
       </c>
       <c r="K82" t="s">
-        <v>412</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B83">
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F83" t="s">
-        <v>485</v>
+        <v>147</v>
       </c>
       <c r="G83" t="s">
-        <v>486</v>
+        <v>148</v>
       </c>
       <c r="H83" t="s">
-        <v>488</v>
+        <v>150</v>
       </c>
       <c r="I83" t="s">
-        <v>489</v>
+        <v>151</v>
       </c>
       <c r="J83" t="s">
-        <v>490</v>
+        <v>152</v>
       </c>
       <c r="K83" t="s">
-        <v>484</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B84">
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>697</v>
+        <v>284</v>
       </c>
       <c r="D84" t="s">
-        <v>714</v>
+        <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>715</v>
+        <v>394</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="G84" t="s">
-        <v>604</v>
+        <v>397</v>
       </c>
       <c r="H84" t="s">
-        <v>718</v>
+        <v>399</v>
       </c>
       <c r="I84" t="s">
-        <v>719</v>
+        <v>400</v>
       </c>
       <c r="J84" t="s">
-        <v>720</v>
+        <v>401</v>
       </c>
       <c r="K84" t="s">
-        <v>716</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D85" t="s">
-        <v>721</v>
+        <v>410</v>
       </c>
       <c r="E85" t="s">
-        <v>722</v>
+        <v>411</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G85" t="s">
-        <v>724</v>
+        <v>413</v>
       </c>
       <c r="H85" t="s">
-        <v>726</v>
+        <v>415</v>
       </c>
       <c r="I85" t="s">
-        <v>727</v>
+        <v>416</v>
       </c>
       <c r="J85" t="s">
-        <v>728</v>
+        <v>417</v>
       </c>
       <c r="K85" t="s">
-        <v>723</v>
+        <v>412</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D86" t="s">
-        <v>729</v>
+        <v>483</v>
       </c>
       <c r="E86" t="s">
-        <v>730</v>
+        <v>122</v>
       </c>
       <c r="F86" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="G86" t="s">
-        <v>732</v>
+        <v>486</v>
       </c>
       <c r="H86" t="s">
-        <v>726</v>
+        <v>488</v>
       </c>
       <c r="I86" t="s">
-        <v>734</v>
+        <v>489</v>
       </c>
       <c r="J86" t="s">
-        <v>735</v>
+        <v>490</v>
       </c>
       <c r="K86" t="s">
-        <v>731</v>
+        <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B87">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D87" t="s">
-        <v>791</v>
+        <v>714</v>
       </c>
       <c r="E87" t="s">
-        <v>610</v>
+        <v>715</v>
       </c>
       <c r="F87" t="s">
-        <v>793</v>
+        <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>794</v>
+        <v>604</v>
       </c>
       <c r="H87" t="s">
-        <v>796</v>
+        <v>718</v>
       </c>
       <c r="I87" t="s">
-        <v>797</v>
+        <v>719</v>
       </c>
       <c r="J87" t="s">
-        <v>798</v>
+        <v>720</v>
       </c>
       <c r="K87" t="s">
-        <v>792</v>
+        <v>716</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B88">
         <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D88" t="s">
-        <v>896</v>
+        <v>721</v>
       </c>
       <c r="E88" t="s">
-        <v>897</v>
+        <v>722</v>
       </c>
       <c r="F88" t="s">
         <v>25</v>
       </c>
       <c r="G88" t="s">
-        <v>899</v>
+        <v>724</v>
       </c>
       <c r="H88" t="s">
-        <v>901</v>
+        <v>726</v>
       </c>
       <c r="I88" t="s">
-        <v>902</v>
+        <v>727</v>
       </c>
       <c r="J88" t="s">
-        <v>903</v>
+        <v>728</v>
       </c>
       <c r="K88" t="s">
-        <v>898</v>
+        <v>723</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B89">
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D89" t="s">
-        <v>964</v>
+        <v>729</v>
       </c>
       <c r="E89" t="s">
-        <v>965</v>
+        <v>730</v>
       </c>
       <c r="F89" t="s">
-        <v>967</v>
+        <v>535</v>
       </c>
       <c r="G89" t="s">
-        <v>968</v>
+        <v>732</v>
       </c>
       <c r="H89" t="s">
-        <v>970</v>
+        <v>726</v>
       </c>
       <c r="I89" t="s">
-        <v>971</v>
+        <v>734</v>
       </c>
       <c r="J89" t="s">
-        <v>972</v>
+        <v>735</v>
       </c>
       <c r="K89" t="s">
-        <v>966</v>
+        <v>731</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B90">
         <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D90" t="s">
-        <v>950</v>
+        <v>791</v>
       </c>
       <c r="E90" t="s">
-        <v>1002</v>
+        <v>610</v>
       </c>
       <c r="F90" t="s">
-        <v>1004</v>
+        <v>793</v>
       </c>
       <c r="G90" t="s">
-        <v>438</v>
+        <v>794</v>
       </c>
       <c r="H90" t="s">
-        <v>1006</v>
+        <v>796</v>
       </c>
       <c r="I90" t="s">
-        <v>1007</v>
+        <v>797</v>
       </c>
       <c r="J90" t="s">
-        <v>1008</v>
+        <v>798</v>
       </c>
       <c r="K90" t="s">
-        <v>1003</v>
+        <v>792</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B91">
         <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
+        <v>896</v>
       </c>
       <c r="E91" t="s">
-        <v>1032</v>
+        <v>897</v>
       </c>
       <c r="F91" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>1034</v>
+        <v>899</v>
       </c>
       <c r="H91" t="s">
-        <v>1036</v>
+        <v>901</v>
       </c>
       <c r="I91" t="s">
-        <v>1037</v>
+        <v>902</v>
       </c>
       <c r="J91" t="s">
-        <v>1038</v>
+        <v>903</v>
       </c>
       <c r="K91" t="s">
-        <v>1033</v>
+        <v>898</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B92">
         <v>84</v>
@@ -18223,902 +18721,1042 @@
         <v>934</v>
       </c>
       <c r="D92" t="s">
-        <v>1057</v>
+        <v>964</v>
       </c>
       <c r="E92" t="s">
-        <v>1058</v>
+        <v>965</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>967</v>
       </c>
       <c r="G92" t="s">
-        <v>1060</v>
+        <v>968</v>
       </c>
       <c r="H92" t="s">
-        <v>1062</v>
+        <v>970</v>
       </c>
       <c r="I92" t="s">
-        <v>1063</v>
+        <v>971</v>
       </c>
       <c r="J92" t="s">
-        <v>1064</v>
+        <v>972</v>
       </c>
       <c r="K92" t="s">
-        <v>1059</v>
+        <v>966</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B93">
         <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>950</v>
       </c>
       <c r="E93" t="s">
-        <v>1104</v>
+        <v>1002</v>
       </c>
       <c r="F93" t="s">
-        <v>1106</v>
+        <v>1004</v>
       </c>
       <c r="G93" t="s">
-        <v>1107</v>
+        <v>438</v>
       </c>
       <c r="H93" t="s">
-        <v>1109</v>
+        <v>1006</v>
       </c>
       <c r="I93" t="s">
-        <v>1110</v>
+        <v>1007</v>
       </c>
       <c r="J93" t="s">
-        <v>1111</v>
+        <v>1008</v>
       </c>
       <c r="K93" t="s">
-        <v>1105</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B94">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C94" t="s">
-        <v>1200</v>
+        <v>934</v>
       </c>
       <c r="D94" t="s">
-        <v>1201</v>
+        <v>213</v>
       </c>
       <c r="E94" t="s">
-        <v>1202</v>
+        <v>1032</v>
       </c>
       <c r="F94" t="s">
-        <v>1204</v>
+        <v>106</v>
       </c>
       <c r="G94" t="s">
-        <v>1205</v>
+        <v>1034</v>
       </c>
       <c r="H94" t="s">
-        <v>1207</v>
+        <v>1036</v>
       </c>
       <c r="I94" t="s">
-        <v>1208</v>
+        <v>1037</v>
       </c>
       <c r="J94" t="s">
-        <v>1209</v>
+        <v>1038</v>
       </c>
       <c r="K94" t="s">
-        <v>1203</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B95">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>1057</v>
       </c>
       <c r="E95" t="s">
-        <v>362</v>
+        <v>1058</v>
       </c>
       <c r="F95" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>364</v>
+        <v>1060</v>
       </c>
       <c r="H95" t="s">
-        <v>366</v>
+        <v>1062</v>
       </c>
       <c r="I95" t="s">
-        <v>367</v>
+        <v>1063</v>
       </c>
       <c r="J95" t="s">
-        <v>368</v>
+        <v>1064</v>
       </c>
       <c r="K95" t="s">
-        <v>363</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B96">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>473</v>
+        <v>1087</v>
       </c>
       <c r="D96" t="s">
-        <v>491</v>
+        <v>271</v>
       </c>
       <c r="E96" t="s">
-        <v>492</v>
+        <v>1104</v>
       </c>
       <c r="F96" t="s">
-        <v>75</v>
+        <v>1106</v>
       </c>
       <c r="G96" t="s">
-        <v>494</v>
+        <v>1107</v>
       </c>
       <c r="H96" t="s">
-        <v>496</v>
+        <v>1109</v>
       </c>
       <c r="I96" t="s">
-        <v>497</v>
+        <v>1110</v>
       </c>
       <c r="J96" t="s">
-        <v>498</v>
+        <v>1111</v>
       </c>
       <c r="K96" t="s">
-        <v>493</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B97">
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>473</v>
+        <v>1200</v>
       </c>
       <c r="D97" t="s">
-        <v>532</v>
+        <v>1201</v>
       </c>
       <c r="E97" t="s">
-        <v>533</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="s">
-        <v>535</v>
+        <v>1204</v>
       </c>
       <c r="G97" t="s">
-        <v>536</v>
+        <v>1205</v>
       </c>
       <c r="H97" t="s">
-        <v>538</v>
+        <v>1207</v>
       </c>
       <c r="I97" t="s">
-        <v>539</v>
+        <v>1208</v>
       </c>
       <c r="J97" t="s">
-        <v>540</v>
+        <v>1209</v>
       </c>
       <c r="K97" t="s">
-        <v>534</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B98">
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D98" t="s">
-        <v>643</v>
+        <v>353</v>
       </c>
       <c r="E98" t="s">
-        <v>644</v>
+        <v>362</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="G98" t="s">
-        <v>618</v>
+        <v>364</v>
       </c>
       <c r="H98" t="s">
-        <v>647</v>
+        <v>366</v>
       </c>
       <c r="I98" t="s">
-        <v>648</v>
+        <v>367</v>
       </c>
       <c r="J98" t="s">
-        <v>649</v>
+        <v>368</v>
       </c>
       <c r="K98" t="s">
-        <v>645</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B99">
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D99" t="s">
-        <v>736</v>
+        <v>491</v>
       </c>
       <c r="E99" t="s">
-        <v>737</v>
+        <v>492</v>
       </c>
       <c r="F99" t="s">
-        <v>739</v>
+        <v>75</v>
       </c>
       <c r="G99" t="s">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="H99" t="s">
-        <v>741</v>
+        <v>496</v>
       </c>
       <c r="I99" t="s">
-        <v>742</v>
+        <v>497</v>
       </c>
       <c r="J99" t="s">
-        <v>743</v>
+        <v>498</v>
       </c>
       <c r="K99" t="s">
-        <v>738</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B100">
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D100" t="s">
-        <v>807</v>
+        <v>532</v>
       </c>
       <c r="E100" t="s">
-        <v>808</v>
+        <v>533</v>
       </c>
       <c r="F100" t="s">
-        <v>810</v>
+        <v>535</v>
       </c>
       <c r="G100" t="s">
-        <v>811</v>
+        <v>536</v>
       </c>
       <c r="H100" t="s">
-        <v>813</v>
+        <v>538</v>
       </c>
       <c r="I100" t="s">
-        <v>814</v>
+        <v>539</v>
       </c>
       <c r="J100" t="s">
-        <v>815</v>
+        <v>540</v>
       </c>
       <c r="K100" t="s">
-        <v>809</v>
+        <v>534</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B101">
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D101" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E101" t="s">
-        <v>1016</v>
+        <v>644</v>
       </c>
       <c r="F101" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>1018</v>
+        <v>618</v>
       </c>
       <c r="H101" t="s">
-        <v>1020</v>
+        <v>647</v>
       </c>
       <c r="I101" t="s">
-        <v>1021</v>
+        <v>648</v>
       </c>
       <c r="J101" t="s">
-        <v>1022</v>
+        <v>649</v>
       </c>
       <c r="K101" t="s">
-        <v>1017</v>
+        <v>645</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B102">
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D102" t="s">
-        <v>1048</v>
+        <v>736</v>
       </c>
       <c r="E102" t="s">
-        <v>1049</v>
+        <v>737</v>
       </c>
       <c r="F102" t="s">
-        <v>1051</v>
+        <v>739</v>
       </c>
       <c r="G102" t="s">
-        <v>1052</v>
+        <v>604</v>
       </c>
       <c r="H102" t="s">
-        <v>1054</v>
+        <v>741</v>
       </c>
       <c r="I102" t="s">
-        <v>1055</v>
+        <v>742</v>
       </c>
       <c r="J102" t="s">
-        <v>1056</v>
+        <v>743</v>
       </c>
       <c r="K102" t="s">
-        <v>1050</v>
+        <v>738</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B103">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>159</v>
+        <v>773</v>
       </c>
       <c r="D103" t="s">
-        <v>227</v>
+        <v>807</v>
       </c>
       <c r="E103" t="s">
-        <v>228</v>
+        <v>808</v>
       </c>
       <c r="F103" t="s">
-        <v>230</v>
+        <v>810</v>
       </c>
       <c r="G103" t="s">
-        <v>231</v>
+        <v>811</v>
       </c>
       <c r="H103" t="s">
-        <v>233</v>
+        <v>813</v>
       </c>
       <c r="I103" t="s">
-        <v>234</v>
+        <v>814</v>
       </c>
       <c r="J103" t="s">
-        <v>235</v>
+        <v>815</v>
       </c>
       <c r="K103" t="s">
-        <v>229</v>
+        <v>809</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B104">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D104" t="s">
-        <v>266</v>
+        <v>650</v>
       </c>
       <c r="E104" t="s">
-        <v>267</v>
+        <v>1016</v>
       </c>
       <c r="F104" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G104" t="s">
-        <v>58</v>
+        <v>1018</v>
       </c>
       <c r="H104" t="s">
-        <v>270</v>
+        <v>1020</v>
       </c>
       <c r="I104" t="s">
-        <v>79</v>
+        <v>1021</v>
       </c>
       <c r="J104" t="s">
-        <v>79</v>
+        <v>1022</v>
       </c>
       <c r="K104" t="s">
-        <v>268</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B105">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D105" t="s">
-        <v>338</v>
+        <v>1048</v>
       </c>
       <c r="E105" t="s">
-        <v>339</v>
+        <v>1049</v>
       </c>
       <c r="F105" t="s">
-        <v>341</v>
+        <v>1051</v>
       </c>
       <c r="G105" t="s">
-        <v>342</v>
+        <v>1052</v>
       </c>
       <c r="H105" t="s">
-        <v>344</v>
+        <v>1054</v>
       </c>
       <c r="I105" t="s">
-        <v>345</v>
+        <v>1055</v>
       </c>
       <c r="J105" t="s">
-        <v>346</v>
+        <v>1056</v>
       </c>
       <c r="K105" t="s">
-        <v>340</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B106">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>591</v>
+        <v>1227</v>
       </c>
       <c r="D106" t="s">
-        <v>601</v>
+        <v>1247</v>
       </c>
       <c r="E106" t="s">
-        <v>602</v>
+        <v>1248</v>
       </c>
       <c r="F106" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G106" t="s">
         <v>604</v>
       </c>
       <c r="H106" t="s">
-        <v>606</v>
+        <v>1251</v>
       </c>
       <c r="I106" t="s">
-        <v>607</v>
+        <v>1252</v>
       </c>
       <c r="J106" t="s">
-        <v>608</v>
+        <v>1253</v>
       </c>
       <c r="K106" t="s">
-        <v>603</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B107">
         <v>82</v>
       </c>
       <c r="C107" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="E107" t="s">
-        <v>1009</v>
+        <v>228</v>
       </c>
       <c r="F107" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G107" t="s">
-        <v>1011</v>
+        <v>231</v>
       </c>
       <c r="H107" t="s">
-        <v>1013</v>
+        <v>233</v>
       </c>
       <c r="I107" t="s">
-        <v>1014</v>
+        <v>234</v>
       </c>
       <c r="J107" t="s">
-        <v>1015</v>
+        <v>235</v>
       </c>
       <c r="K107" t="s">
-        <v>1010</v>
+        <v>229</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B108">
         <v>82</v>
       </c>
       <c r="C108" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D108" t="s">
-        <v>1023</v>
+        <v>266</v>
       </c>
       <c r="E108" t="s">
-        <v>1024</v>
+        <v>267</v>
       </c>
       <c r="F108" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>1027</v>
+        <v>58</v>
       </c>
       <c r="H108" t="s">
-        <v>1029</v>
+        <v>270</v>
       </c>
       <c r="I108" t="s">
-        <v>1030</v>
+        <v>79</v>
       </c>
       <c r="J108" t="s">
-        <v>1031</v>
+        <v>79</v>
       </c>
       <c r="K108" t="s">
-        <v>1025</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B109">
         <v>82</v>
       </c>
       <c r="C109" t="s">
-        <v>1087</v>
+        <v>284</v>
       </c>
       <c r="D109" t="s">
-        <v>1112</v>
+        <v>338</v>
       </c>
       <c r="E109" t="s">
-        <v>1113</v>
+        <v>339</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>341</v>
       </c>
       <c r="G109" t="s">
-        <v>1115</v>
+        <v>342</v>
       </c>
       <c r="H109" t="s">
-        <v>1117</v>
+        <v>344</v>
       </c>
       <c r="I109" t="s">
-        <v>1118</v>
+        <v>345</v>
       </c>
       <c r="J109" t="s">
-        <v>1119</v>
+        <v>346</v>
       </c>
       <c r="K109" t="s">
-        <v>1114</v>
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B110">
         <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>1210</v>
+        <v>591</v>
       </c>
       <c r="D110" t="s">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="E110" t="s">
-        <v>89</v>
+        <v>602</v>
       </c>
       <c r="F110" t="s">
-        <v>1213</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s">
-        <v>1214</v>
+        <v>604</v>
       </c>
       <c r="H110" t="s">
-        <v>1216</v>
+        <v>606</v>
       </c>
       <c r="I110" t="s">
-        <v>1217</v>
+        <v>607</v>
       </c>
       <c r="J110" t="s">
-        <v>1218</v>
+        <v>608</v>
       </c>
       <c r="K110" t="s">
-        <v>1212</v>
+        <v>603</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B111">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C111" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D111" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E111" t="s">
-        <v>81</v>
+        <v>1009</v>
       </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>83</v>
+        <v>1011</v>
       </c>
       <c r="H111" t="s">
-        <v>85</v>
+        <v>1013</v>
       </c>
       <c r="I111" t="s">
-        <v>86</v>
+        <v>1014</v>
       </c>
       <c r="J111" t="s">
-        <v>87</v>
+        <v>1015</v>
       </c>
       <c r="K111" t="s">
-        <v>82</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B112">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C112" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D112" t="s">
-        <v>377</v>
+        <v>1023</v>
       </c>
       <c r="E112" t="s">
-        <v>378</v>
+        <v>1024</v>
       </c>
       <c r="F112" t="s">
-        <v>380</v>
+        <v>1026</v>
       </c>
       <c r="G112" t="s">
-        <v>381</v>
+        <v>1027</v>
       </c>
       <c r="H112" t="s">
-        <v>383</v>
+        <v>1029</v>
       </c>
       <c r="I112" t="s">
-        <v>384</v>
+        <v>1030</v>
       </c>
       <c r="J112" t="s">
-        <v>385</v>
+        <v>1031</v>
       </c>
       <c r="K112" t="s">
-        <v>379</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B113">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C113" t="s">
-        <v>473</v>
+        <v>1087</v>
       </c>
       <c r="D113" t="s">
-        <v>499</v>
+        <v>1112</v>
       </c>
       <c r="E113" t="s">
-        <v>500</v>
+        <v>1113</v>
       </c>
       <c r="F113" t="s">
-        <v>502</v>
+        <v>25</v>
       </c>
       <c r="G113" t="s">
-        <v>503</v>
+        <v>1115</v>
       </c>
       <c r="H113" t="s">
-        <v>505</v>
+        <v>1117</v>
       </c>
       <c r="I113" t="s">
-        <v>506</v>
+        <v>1118</v>
       </c>
       <c r="J113" t="s">
-        <v>507</v>
+        <v>1119</v>
       </c>
       <c r="K113" t="s">
-        <v>501</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B114">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>591</v>
+        <v>1210</v>
       </c>
       <c r="D114" t="s">
-        <v>616</v>
+        <v>1211</v>
       </c>
       <c r="E114" t="s">
-        <v>610</v>
+        <v>89</v>
       </c>
       <c r="F114" t="s">
-        <v>16</v>
+        <v>1213</v>
       </c>
       <c r="G114" t="s">
-        <v>618</v>
+        <v>1214</v>
       </c>
       <c r="H114" t="s">
-        <v>620</v>
+        <v>1216</v>
       </c>
       <c r="I114" t="s">
-        <v>621</v>
+        <v>1217</v>
       </c>
       <c r="J114" t="s">
-        <v>622</v>
+        <v>1218</v>
       </c>
       <c r="K114" t="s">
-        <v>617</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B115">
         <v>81</v>
       </c>
       <c r="C115" t="s">
-        <v>845</v>
+        <v>12</v>
       </c>
       <c r="D115" t="s">
-        <v>888</v>
+        <v>80</v>
       </c>
       <c r="E115" t="s">
-        <v>889</v>
+        <v>81</v>
       </c>
       <c r="F115" t="s">
         <v>25</v>
       </c>
       <c r="G115" t="s">
-        <v>891</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s">
-        <v>893</v>
+        <v>85</v>
       </c>
       <c r="I115" t="s">
-        <v>894</v>
+        <v>86</v>
       </c>
       <c r="J115" t="s">
-        <v>895</v>
+        <v>87</v>
       </c>
       <c r="K115" t="s">
-        <v>890</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B116">
         <v>81</v>
       </c>
       <c r="C116" t="s">
-        <v>1087</v>
+        <v>284</v>
       </c>
       <c r="D116" t="s">
-        <v>1120</v>
+        <v>377</v>
       </c>
       <c r="E116" t="s">
-        <v>1121</v>
+        <v>378</v>
       </c>
       <c r="F116" t="s">
-        <v>1123</v>
+        <v>380</v>
       </c>
       <c r="G116" t="s">
-        <v>1124</v>
+        <v>381</v>
       </c>
       <c r="H116" t="s">
-        <v>1126</v>
+        <v>383</v>
       </c>
       <c r="I116" t="s">
-        <v>1127</v>
+        <v>384</v>
       </c>
       <c r="J116" t="s">
-        <v>1128</v>
+        <v>385</v>
       </c>
       <c r="K116" t="s">
-        <v>1122</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1238</v>
+        <v>1276</v>
       </c>
       <c r="B117">
+        <v>81</v>
+      </c>
+      <c r="C117" t="s">
+        <v>473</v>
+      </c>
+      <c r="D117" t="s">
+        <v>499</v>
+      </c>
+      <c r="E117" t="s">
+        <v>500</v>
+      </c>
+      <c r="F117" t="s">
+        <v>502</v>
+      </c>
+      <c r="G117" t="s">
+        <v>503</v>
+      </c>
+      <c r="H117" t="s">
+        <v>505</v>
+      </c>
+      <c r="I117" t="s">
+        <v>506</v>
+      </c>
+      <c r="J117" t="s">
+        <v>507</v>
+      </c>
+      <c r="K117" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B118">
+        <v>81</v>
+      </c>
+      <c r="C118" t="s">
+        <v>591</v>
+      </c>
+      <c r="D118" t="s">
+        <v>616</v>
+      </c>
+      <c r="E118" t="s">
+        <v>610</v>
+      </c>
+      <c r="F118" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" t="s">
+        <v>618</v>
+      </c>
+      <c r="H118" t="s">
+        <v>620</v>
+      </c>
+      <c r="I118" t="s">
+        <v>621</v>
+      </c>
+      <c r="J118" t="s">
+        <v>622</v>
+      </c>
+      <c r="K118" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B119">
+        <v>81</v>
+      </c>
+      <c r="C119" t="s">
+        <v>845</v>
+      </c>
+      <c r="D119" t="s">
+        <v>888</v>
+      </c>
+      <c r="E119" t="s">
+        <v>889</v>
+      </c>
+      <c r="F119" t="s">
+        <v>25</v>
+      </c>
+      <c r="G119" t="s">
+        <v>891</v>
+      </c>
+      <c r="H119" t="s">
+        <v>893</v>
+      </c>
+      <c r="I119" t="s">
+        <v>894</v>
+      </c>
+      <c r="J119" t="s">
+        <v>895</v>
+      </c>
+      <c r="K119" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B120">
+        <v>81</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H120" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J120" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K120" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B121">
         <v>80</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C121" t="s">
         <v>934</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D121" t="s">
         <v>1039</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E121" t="s">
         <v>1040</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F121" t="s">
         <v>1042</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G121" t="s">
         <v>1043</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H121" t="s">
         <v>1045</v>
       </c>
-      <c r="I117" t="s">
+      <c r="I121" t="s">
         <v>1046</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J121" t="s">
         <v>1047</v>
       </c>
-      <c r="K117" t="s">
+      <c r="K121" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3960" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="1311">
   <si>
     <t>日期</t>
   </si>
@@ -3809,6 +3809,24 @@
   </si>
   <si>
     <t>研究80/技能60/学历85/行业100/企业78</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>硕士及以上（优秀本科亦可），化学/材料/机械/生物医学/药学等理工科专业；英文CET4-6；掌握AutoCAD及一种3D制图软件（SolidWorks/ProE/UG）者优先；协助产品设计、样品测试、测试报告与技术文件/作业指导书撰写、生产培训；参与生产工艺开发、验证新设备及新工艺。公司主营铁基可吸收血管支架。</t>
+  </si>
+  <si>
+    <t>智能匹配91分【社招（接受应届硕士）】|强烈推荐|铁基可吸收血管支架研发岗，方向直接匹配，材料学+支架设计+测试技能高度重合，硕士可投</t>
+  </si>
+  <si>
+    <t>研究90/技能85/学历100/行业100/企业88</t>
+  </si>
+  <si>
+    <t>元心科技系先健科技分拆、全球唯一专注铁基可吸收血管支架的企业，与硕士血管支架研究方向几乎完全一致；岗位明确要求硕士理工科背景（材料/机械/生物医学），并认可AutoCAD/3D建模与样品测试能力，正是本人材料学+支架设计+生物相容性评价技能所在；深圳为偏好城市，接受应届硕士，是切入可吸收血管支架研发顶级的精准平台，强烈推荐投递。</t>
+  </si>
+  <si>
+    <t>重点突出可降解/可吸收支架研究课题与材料学（铁基/镍钛/高分子）项目，量化降解行为、力学与生物相容性评价数据；单列掌握的AutoCAD/SolidWorks三维建模与有限元仿真能力；补充动物实验与产品测试经历，突出应届可到岗及长期研发意愿。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4363,7 +4381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10799,6 +10817,44 @@
       </c>
       <c r="L169" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B170" t="s">
+        <v>285</v>
+      </c>
+      <c r="C170" t="s">
+        <v>89</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E170" t="s">
+        <v>66</v>
+      </c>
+      <c r="F170" t="s">
+        <v>945</v>
+      </c>
+      <c r="G170">
+        <v>9</v>
+      </c>
+      <c r="H170" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I170">
+        <v>91</v>
+      </c>
+      <c r="J170" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K170" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L170" t="s">
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -10832,7 +10888,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10841,16 +10897,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10864,13 +10920,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -10898,7 +10954,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10913,7 +10969,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10923,31 +10979,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="B4">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="B5" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -10955,7 +11011,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -10963,15 +11019,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="B8">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="B9">
         <v>81</v>
@@ -10979,7 +11035,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -10987,15 +11043,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="B11" t="s">
-        <v>1227</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11005,15 +11061,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -11021,15 +11077,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="B17" s="5">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="B18" s="5">
         <v>81</v>
@@ -11037,7 +11093,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="B19" s="5">
         <v>6</v>
@@ -11045,7 +11101,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -11053,7 +11109,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11061,7 +11117,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -11069,7 +11125,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11077,7 +11133,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -11085,7 +11141,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -11093,7 +11149,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -11105,7 +11161,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -11123,7 +11179,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -13240,25 +13296,25 @@
         <v>82</v>
       </c>
       <c r="B111" t="s">
-        <v>1200</v>
+        <v>1265</v>
       </c>
       <c r="C111" t="s">
-        <v>1201</v>
+        <v>285</v>
       </c>
       <c r="D111" t="s">
-        <v>1202</v>
+        <v>89</v>
       </c>
       <c r="E111" t="s">
-        <v>1204</v>
+        <v>66</v>
       </c>
       <c r="F111" t="s">
-        <v>1205</v>
+        <v>945</v>
       </c>
       <c r="G111">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H111" t="s">
-        <v>1206</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -13266,25 +13322,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C112" t="s">
-        <v>72</v>
+        <v>1201</v>
       </c>
       <c r="D112" t="s">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="E112" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="F112" t="s">
-        <v>76</v>
+        <v>1205</v>
       </c>
       <c r="G112">
         <v>8</v>
       </c>
       <c r="H112" t="s">
-        <v>77</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -13295,22 +13351,22 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D113" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F113" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -13321,22 +13377,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D114" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -13347,22 +13403,22 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D115" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E115" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F115" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -13373,22 +13429,22 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D116" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -13399,22 +13455,22 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E117" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F117" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -13425,22 +13481,22 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E118" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F118" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -13451,22 +13507,22 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D119" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F119" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -13474,25 +13530,25 @@
         <v>91</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="E120" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13503,22 +13559,22 @@
         <v>159</v>
       </c>
       <c r="C121" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D121" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E121" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F121" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -13529,22 +13585,22 @@
         <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D122" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E122" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F122" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -13555,22 +13611,22 @@
         <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D123" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="E123" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F123" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -13581,22 +13637,22 @@
         <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F124" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13607,22 +13663,22 @@
         <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D125" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="E125" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -13633,22 +13689,22 @@
         <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D126" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="E126" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -13659,22 +13715,22 @@
         <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D127" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E127" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F127" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -13685,22 +13741,22 @@
         <v>159</v>
       </c>
       <c r="C128" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D128" t="s">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="E128" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="F128" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -13711,22 +13767,22 @@
         <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D129" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F129" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -13737,22 +13793,22 @@
         <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D130" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E130" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -13760,25 +13816,25 @@
         <v>102</v>
       </c>
       <c r="B131" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C131" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="D131" t="s">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="E131" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="F131" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -13789,22 +13845,22 @@
         <v>284</v>
       </c>
       <c r="C132" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D132" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E132" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="F132" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -13815,22 +13871,22 @@
         <v>284</v>
       </c>
       <c r="C133" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D133" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E133" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="F133" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -13841,22 +13897,22 @@
         <v>284</v>
       </c>
       <c r="C134" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D134" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="E134" t="s">
-        <v>356</v>
+        <v>98</v>
       </c>
       <c r="F134" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -13867,22 +13923,22 @@
         <v>284</v>
       </c>
       <c r="C135" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="E135" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="F135" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -13893,22 +13949,22 @@
         <v>284</v>
       </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="D136" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="E136" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="F136" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -13916,25 +13972,25 @@
         <v>108</v>
       </c>
       <c r="B137" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C137" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="D137" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E137" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F137" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -13945,22 +14001,22 @@
         <v>402</v>
       </c>
       <c r="C138" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D138" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E138" t="s">
         <v>66</v>
       </c>
       <c r="F138" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -13971,22 +14027,22 @@
         <v>402</v>
       </c>
       <c r="C139" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D139" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E139" t="s">
         <v>66</v>
       </c>
       <c r="F139" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -13997,22 +14053,22 @@
         <v>402</v>
       </c>
       <c r="C140" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D140" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E140" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F140" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -14020,25 +14076,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C141" t="s">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="D141" t="s">
-        <v>122</v>
+        <v>431</v>
       </c>
       <c r="E141" t="s">
-        <v>485</v>
+        <v>16</v>
       </c>
       <c r="F141" t="s">
-        <v>486</v>
+        <v>433</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>487</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -14049,22 +14105,22 @@
         <v>473</v>
       </c>
       <c r="C142" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D142" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="E142" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="F142" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -14075,22 +14131,22 @@
         <v>473</v>
       </c>
       <c r="C143" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D143" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="E143" t="s">
-        <v>502</v>
+        <v>75</v>
       </c>
       <c r="F143" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -14101,22 +14157,22 @@
         <v>473</v>
       </c>
       <c r="C144" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="D144" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="E144" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="F144" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -14127,22 +14183,22 @@
         <v>473</v>
       </c>
       <c r="C145" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="D145" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="F145" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -14150,25 +14206,25 @@
         <v>117</v>
       </c>
       <c r="B146" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C146" t="s">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="D146" t="s">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="E146" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F146" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -14179,22 +14235,22 @@
         <v>556</v>
       </c>
       <c r="C147" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D147" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E147" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="F147" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -14202,25 +14258,25 @@
         <v>119</v>
       </c>
       <c r="B148" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C148" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="D148" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="E148" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="F148" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -14231,22 +14287,22 @@
         <v>591</v>
       </c>
       <c r="C149" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D149" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E149" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F149" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -14257,22 +14313,22 @@
         <v>591</v>
       </c>
       <c r="C150" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="D150" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="E150" t="s">
         <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>468</v>
+        <v>618</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -14283,22 +14339,22 @@
         <v>591</v>
       </c>
       <c r="C151" t="s">
-        <v>643</v>
+        <v>557</v>
       </c>
       <c r="D151" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="E151" t="s">
         <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -14309,22 +14365,22 @@
         <v>591</v>
       </c>
       <c r="C152" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D152" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E152" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F152" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -14335,22 +14391,22 @@
         <v>591</v>
       </c>
       <c r="C153" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D153" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E153" t="s">
-        <v>661</v>
+        <v>66</v>
       </c>
       <c r="F153" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14361,22 +14417,22 @@
         <v>591</v>
       </c>
       <c r="C154" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D154" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E154" t="s">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="F154" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -14387,22 +14443,22 @@
         <v>591</v>
       </c>
       <c r="C155" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="D155" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E155" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F155" t="s">
-        <v>676</v>
+        <v>604</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -14410,25 +14466,25 @@
         <v>127</v>
       </c>
       <c r="B156" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C156" t="s">
-        <v>714</v>
+        <v>673</v>
       </c>
       <c r="D156" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="E156" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F156" t="s">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -14439,22 +14495,22 @@
         <v>697</v>
       </c>
       <c r="C157" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D157" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E157" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F157" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -14465,22 +14521,22 @@
         <v>697</v>
       </c>
       <c r="C158" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D158" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E158" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="F158" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -14491,22 +14547,22 @@
         <v>697</v>
       </c>
       <c r="C159" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D159" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="E159" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="F159" t="s">
-        <v>604</v>
+        <v>732</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14517,22 +14573,22 @@
         <v>697</v>
       </c>
       <c r="C160" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D160" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E160" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="F160" t="s">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -14543,22 +14599,22 @@
         <v>697</v>
       </c>
       <c r="C161" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D161" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="E161" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F161" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -14569,22 +14625,22 @@
         <v>697</v>
       </c>
       <c r="C162" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="D162" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E162" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F162" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14592,25 +14648,25 @@
         <v>134</v>
       </c>
       <c r="B163" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C163" t="s">
-        <v>791</v>
+        <v>760</v>
       </c>
       <c r="D163" t="s">
-        <v>610</v>
+        <v>761</v>
       </c>
       <c r="E163" t="s">
-        <v>793</v>
+        <v>763</v>
       </c>
       <c r="F163" t="s">
-        <v>794</v>
+        <v>764</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>795</v>
+        <v>765</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14621,22 +14677,22 @@
         <v>773</v>
       </c>
       <c r="C164" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="D164" t="s">
-        <v>808</v>
+        <v>610</v>
       </c>
       <c r="E164" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="F164" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14647,22 +14703,22 @@
         <v>773</v>
       </c>
       <c r="C165" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="D165" t="s">
-        <v>110</v>
+        <v>808</v>
       </c>
       <c r="E165" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F165" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14670,25 +14726,25 @@
         <v>137</v>
       </c>
       <c r="B166" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C166" t="s">
-        <v>888</v>
+        <v>816</v>
       </c>
       <c r="D166" t="s">
-        <v>889</v>
+        <v>110</v>
       </c>
       <c r="E166" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F166" t="s">
-        <v>891</v>
+        <v>818</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>892</v>
+        <v>819</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -14699,22 +14755,22 @@
         <v>845</v>
       </c>
       <c r="C167" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D167" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
       </c>
       <c r="F167" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -14725,22 +14781,22 @@
         <v>845</v>
       </c>
       <c r="C168" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D168" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="E168" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F168" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -14751,22 +14807,22 @@
         <v>845</v>
       </c>
       <c r="C169" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="D169" t="s">
         <v>585</v>
       </c>
       <c r="E169" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F169" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -14777,22 +14833,22 @@
         <v>845</v>
       </c>
       <c r="C170" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="D170" t="s">
-        <v>919</v>
+        <v>585</v>
       </c>
       <c r="E170" t="s">
-        <v>921</v>
+        <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14800,25 +14856,25 @@
         <v>142</v>
       </c>
       <c r="B171" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C171" t="s">
-        <v>964</v>
+        <v>918</v>
       </c>
       <c r="D171" t="s">
-        <v>965</v>
+        <v>919</v>
       </c>
       <c r="E171" t="s">
-        <v>967</v>
+        <v>921</v>
       </c>
       <c r="F171" t="s">
-        <v>968</v>
+        <v>922</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>969</v>
+        <v>923</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14829,22 +14885,22 @@
         <v>934</v>
       </c>
       <c r="C172" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="D172" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="E172" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="F172" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>1005</v>
+        <v>969</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14855,22 +14911,22 @@
         <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="D173" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="E173" t="s">
-        <v>16</v>
+        <v>1004</v>
       </c>
       <c r="F173" t="s">
-        <v>1011</v>
+        <v>438</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -14881,22 +14937,22 @@
         <v>934</v>
       </c>
       <c r="C174" t="s">
-        <v>650</v>
+        <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="E174" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -14907,22 +14963,22 @@
         <v>934</v>
       </c>
       <c r="C175" t="s">
-        <v>1023</v>
+        <v>650</v>
       </c>
       <c r="D175" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="E175" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="F175" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -14933,22 +14989,22 @@
         <v>934</v>
       </c>
       <c r="C176" t="s">
-        <v>213</v>
+        <v>1023</v>
       </c>
       <c r="D176" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="E176" t="s">
-        <v>106</v>
+        <v>1026</v>
       </c>
       <c r="F176" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14959,22 +15015,22 @@
         <v>934</v>
       </c>
       <c r="C177" t="s">
-        <v>1039</v>
+        <v>213</v>
       </c>
       <c r="D177" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="E177" t="s">
-        <v>1042</v>
+        <v>106</v>
       </c>
       <c r="F177" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -14985,22 +15041,22 @@
         <v>934</v>
       </c>
       <c r="C178" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="D178" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="E178" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="F178" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -15011,22 +15067,22 @@
         <v>934</v>
       </c>
       <c r="C179" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="D179" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="E179" t="s">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="F179" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -15037,22 +15093,22 @@
         <v>934</v>
       </c>
       <c r="C180" t="s">
-        <v>1082</v>
+        <v>1057</v>
       </c>
       <c r="D180" t="s">
-        <v>1083</v>
+        <v>1058</v>
       </c>
       <c r="E180" t="s">
-        <v>1085</v>
+        <v>16</v>
       </c>
       <c r="F180" t="s">
-        <v>959</v>
+        <v>1060</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>1086</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -15060,25 +15116,25 @@
         <v>152</v>
       </c>
       <c r="B181" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C181" t="s">
-        <v>271</v>
+        <v>1082</v>
       </c>
       <c r="D181" t="s">
-        <v>1104</v>
+        <v>1083</v>
       </c>
       <c r="E181" t="s">
-        <v>1106</v>
+        <v>1085</v>
       </c>
       <c r="F181" t="s">
-        <v>1107</v>
+        <v>959</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -15089,22 +15145,22 @@
         <v>1087</v>
       </c>
       <c r="C182" t="s">
-        <v>1112</v>
+        <v>271</v>
       </c>
       <c r="D182" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="E182" t="s">
-        <v>25</v>
+        <v>1106</v>
       </c>
       <c r="F182" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -15115,22 +15171,22 @@
         <v>1087</v>
       </c>
       <c r="C183" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="D183" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="E183" t="s">
-        <v>1123</v>
+        <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -15141,22 +15197,22 @@
         <v>1087</v>
       </c>
       <c r="C184" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
       <c r="D184" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="E184" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
       <c r="F184" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -15164,25 +15220,25 @@
         <v>156</v>
       </c>
       <c r="B185" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C185" t="s">
-        <v>1172</v>
+        <v>1129</v>
       </c>
       <c r="D185" t="s">
-        <v>122</v>
+        <v>1130</v>
       </c>
       <c r="E185" t="s">
-        <v>1174</v>
+        <v>1132</v>
       </c>
       <c r="F185" t="s">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>1176</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -15193,13 +15249,13 @@
         <v>1171</v>
       </c>
       <c r="C186" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D186" t="s">
-        <v>1179</v>
+        <v>122</v>
       </c>
       <c r="E186" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="F186" t="s">
         <v>1175</v>
@@ -15208,7 +15264,7 @@
         <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -15219,13 +15275,13 @@
         <v>1171</v>
       </c>
       <c r="C187" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D187" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="E187" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="F187" t="s">
         <v>1175</v>
@@ -15234,7 +15290,7 @@
         <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -15242,25 +15298,25 @@
         <v>159</v>
       </c>
       <c r="B188" t="s">
-        <v>1210</v>
+        <v>1171</v>
       </c>
       <c r="C188" t="s">
-        <v>1211</v>
+        <v>1184</v>
       </c>
       <c r="D188" t="s">
-        <v>89</v>
+        <v>1185</v>
       </c>
       <c r="E188" t="s">
-        <v>1213</v>
+        <v>1187</v>
       </c>
       <c r="F188" t="s">
-        <v>1214</v>
+        <v>1175</v>
       </c>
       <c r="G188">
         <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>1215</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -15268,25 +15324,25 @@
         <v>160</v>
       </c>
       <c r="B189" t="s">
-        <v>1227</v>
+        <v>1210</v>
       </c>
       <c r="C189" t="s">
-        <v>1247</v>
+        <v>1211</v>
       </c>
       <c r="D189" t="s">
-        <v>1248</v>
+        <v>89</v>
       </c>
       <c r="E189" t="s">
-        <v>66</v>
+        <v>1213</v>
       </c>
       <c r="F189" t="s">
-        <v>604</v>
+        <v>1214</v>
       </c>
       <c r="G189">
         <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>1250</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -15297,22 +15353,22 @@
         <v>1227</v>
       </c>
       <c r="C190" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="D190" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="E190" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F190" t="s">
-        <v>1257</v>
+        <v>604</v>
       </c>
       <c r="G190">
         <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -15323,13 +15379,13 @@
         <v>1227</v>
       </c>
       <c r="C191" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="D191" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="E191" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F191" t="s">
         <v>1257</v>
@@ -15338,7 +15394,7 @@
         <v>8</v>
       </c>
       <c r="H191" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -15346,25 +15402,25 @@
         <v>163</v>
       </c>
       <c r="B192" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="C192" t="s">
-        <v>271</v>
+        <v>1260</v>
       </c>
       <c r="D192" t="s">
-        <v>272</v>
+        <v>1261</v>
       </c>
       <c r="E192" t="s">
         <v>75</v>
       </c>
       <c r="F192" t="s">
-        <v>274</v>
+        <v>1257</v>
       </c>
       <c r="G192">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H192" t="s">
-        <v>275</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -15372,25 +15428,25 @@
         <v>164</v>
       </c>
       <c r="B193" t="s">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="C193" t="s">
-        <v>681</v>
+        <v>271</v>
       </c>
       <c r="D193" t="s">
-        <v>682</v>
+        <v>272</v>
       </c>
       <c r="E193" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F193" t="s">
-        <v>684</v>
+        <v>274</v>
       </c>
       <c r="G193">
         <v>7</v>
       </c>
       <c r="H193" t="s">
-        <v>685</v>
+        <v>275</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -15401,22 +15457,22 @@
         <v>591</v>
       </c>
       <c r="C194" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="D194" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="E194" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G194">
         <v>7</v>
       </c>
       <c r="H194" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -15424,25 +15480,25 @@
         <v>166</v>
       </c>
       <c r="B195" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C195" t="s">
-        <v>767</v>
+        <v>689</v>
       </c>
       <c r="D195" t="s">
-        <v>768</v>
+        <v>690</v>
       </c>
       <c r="E195" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F195" t="s">
-        <v>770</v>
+        <v>692</v>
       </c>
       <c r="G195">
         <v>7</v>
       </c>
       <c r="H195" t="s">
-        <v>771</v>
+        <v>693</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -15450,25 +15506,25 @@
         <v>167</v>
       </c>
       <c r="B196" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="C196" t="s">
-        <v>927</v>
+        <v>767</v>
       </c>
       <c r="D196" t="s">
-        <v>585</v>
+        <v>768</v>
       </c>
       <c r="E196" t="s">
         <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>929</v>
+        <v>770</v>
       </c>
       <c r="G196">
         <v>7</v>
       </c>
       <c r="H196" t="s">
-        <v>930</v>
+        <v>771</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15476,24 +15532,50 @@
         <v>168</v>
       </c>
       <c r="B197" t="s">
-        <v>1219</v>
+        <v>845</v>
       </c>
       <c r="C197" t="s">
-        <v>1220</v>
+        <v>927</v>
       </c>
       <c r="D197" t="s">
-        <v>1221</v>
+        <v>585</v>
       </c>
       <c r="E197" t="s">
-        <v>1223</v>
+        <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>1224</v>
+        <v>929</v>
       </c>
       <c r="G197">
         <v>7</v>
       </c>
       <c r="H197" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>169</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G198">
+        <v>7</v>
+      </c>
+      <c r="H198" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -15510,7 +15592,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15527,10 +15609,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -15557,12 +15639,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -15597,7 +15679,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -15632,7 +15714,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -15667,7 +15749,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -15702,7 +15784,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -15737,7 +15819,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -15772,7 +15854,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -15807,7 +15889,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -15842,7 +15924,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -15877,7 +15959,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -15912,7 +15994,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -15947,7 +16029,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -15982,7 +16064,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -16017,7 +16099,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -16052,7 +16134,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -16087,7 +16169,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -16122,7 +16204,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -16157,7 +16239,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B19">
         <v>91</v>
@@ -16192,42 +16274,42 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B20">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>1265</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>285</v>
       </c>
       <c r="E20" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>195</v>
+        <v>945</v>
       </c>
       <c r="H20" t="s">
-        <v>197</v>
+        <v>1268</v>
       </c>
       <c r="I20" t="s">
-        <v>198</v>
+        <v>1269</v>
       </c>
       <c r="J20" t="s">
-        <v>199</v>
+        <v>1270</v>
       </c>
       <c r="K20" t="s">
-        <v>193</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -16236,418 +16318,418 @@
         <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="G21" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="H21" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="I21" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="J21" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="K21" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B22">
         <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
-        <v>330</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
-        <v>331</v>
+        <v>220</v>
       </c>
       <c r="F22" t="s">
-        <v>333</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="H22" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="I22" t="s">
-        <v>336</v>
+        <v>225</v>
       </c>
       <c r="J22" t="s">
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="K22" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B23">
         <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="E23" t="s">
-        <v>443</v>
+        <v>331</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="G23" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="H23" t="s">
-        <v>446</v>
+        <v>197</v>
       </c>
       <c r="I23" t="s">
-        <v>447</v>
+        <v>336</v>
       </c>
       <c r="J23" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="K23" t="s">
-        <v>444</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B24">
         <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D24" t="s">
-        <v>774</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>775</v>
+        <v>443</v>
       </c>
       <c r="F24" t="s">
-        <v>777</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>778</v>
+        <v>438</v>
       </c>
       <c r="H24" t="s">
-        <v>780</v>
+        <v>446</v>
       </c>
       <c r="I24" t="s">
-        <v>781</v>
+        <v>447</v>
       </c>
       <c r="J24" t="s">
-        <v>782</v>
+        <v>448</v>
       </c>
       <c r="K24" t="s">
-        <v>776</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B25">
         <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>1087</v>
+        <v>773</v>
       </c>
       <c r="D25" t="s">
-        <v>1138</v>
+        <v>774</v>
       </c>
       <c r="E25" t="s">
-        <v>1139</v>
+        <v>775</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>777</v>
       </c>
       <c r="G25" t="s">
-        <v>1141</v>
+        <v>778</v>
       </c>
       <c r="H25" t="s">
-        <v>1143</v>
+        <v>780</v>
       </c>
       <c r="I25" t="s">
-        <v>1144</v>
+        <v>781</v>
       </c>
       <c r="J25" t="s">
-        <v>1145</v>
+        <v>782</v>
       </c>
       <c r="K25" t="s">
-        <v>1140</v>
+        <v>776</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B26">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>1087</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>1138</v>
       </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>1139</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>139</v>
+        <v>1141</v>
       </c>
       <c r="H26" t="s">
-        <v>141</v>
+        <v>1143</v>
       </c>
       <c r="I26" t="s">
-        <v>142</v>
+        <v>1144</v>
       </c>
       <c r="J26" t="s">
-        <v>143</v>
+        <v>1145</v>
       </c>
       <c r="K26" t="s">
-        <v>137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B27">
         <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="G27" t="s">
-        <v>438</v>
+        <v>139</v>
       </c>
       <c r="H27" t="s">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
-        <v>441</v>
+        <v>142</v>
       </c>
       <c r="J27" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="K27" t="s">
-        <v>437</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B28">
         <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="D28" t="s">
-        <v>557</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
-        <v>564</v>
+        <v>436</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H28" t="s">
-        <v>567</v>
+        <v>440</v>
       </c>
       <c r="I28" t="s">
-        <v>568</v>
+        <v>441</v>
       </c>
       <c r="J28" t="s">
-        <v>569</v>
+        <v>442</v>
       </c>
       <c r="K28" t="s">
-        <v>565</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B29">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D29" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="E29" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="F29" t="s">
-        <v>595</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>596</v>
+        <v>468</v>
       </c>
       <c r="H29" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="I29" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="J29" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="K29" t="s">
-        <v>594</v>
+        <v>565</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B30">
         <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D30" t="s">
-        <v>707</v>
+        <v>592</v>
       </c>
       <c r="E30" t="s">
-        <v>708</v>
+        <v>593</v>
       </c>
       <c r="F30" t="s">
-        <v>318</v>
+        <v>595</v>
       </c>
       <c r="G30" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H30" t="s">
-        <v>711</v>
+        <v>598</v>
       </c>
       <c r="I30" t="s">
-        <v>712</v>
+        <v>599</v>
       </c>
       <c r="J30" t="s">
-        <v>713</v>
+        <v>600</v>
       </c>
       <c r="K30" t="s">
-        <v>709</v>
+        <v>594</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B31">
         <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D31" t="s">
-        <v>846</v>
+        <v>707</v>
       </c>
       <c r="E31" t="s">
-        <v>847</v>
+        <v>708</v>
       </c>
       <c r="F31" t="s">
-        <v>849</v>
+        <v>318</v>
       </c>
       <c r="G31" t="s">
-        <v>850</v>
+        <v>604</v>
       </c>
       <c r="H31" t="s">
-        <v>852</v>
+        <v>711</v>
       </c>
       <c r="I31" t="s">
-        <v>853</v>
+        <v>712</v>
       </c>
       <c r="J31" t="s">
-        <v>854</v>
+        <v>713</v>
       </c>
       <c r="K31" t="s">
-        <v>848</v>
+        <v>709</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B32">
         <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D32" t="s">
-        <v>277</v>
+        <v>846</v>
       </c>
       <c r="E32" t="s">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>849</v>
       </c>
       <c r="G32" t="s">
-        <v>937</v>
+        <v>850</v>
       </c>
       <c r="H32" t="s">
-        <v>939</v>
+        <v>852</v>
       </c>
       <c r="I32" t="s">
-        <v>940</v>
+        <v>853</v>
       </c>
       <c r="J32" t="s">
-        <v>941</v>
+        <v>854</v>
       </c>
       <c r="K32" t="s">
-        <v>936</v>
+        <v>848</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -16656,33 +16738,33 @@
         <v>934</v>
       </c>
       <c r="D33" t="s">
-        <v>942</v>
+        <v>277</v>
       </c>
       <c r="E33" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="H33" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="I33" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="J33" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="K33" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B34">
         <v>89</v>
@@ -16691,453 +16773,453 @@
         <v>934</v>
       </c>
       <c r="D34" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="E34" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>438</v>
+        <v>945</v>
       </c>
       <c r="H34" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="I34" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="J34" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="K34" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>950</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>951</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>954</v>
       </c>
       <c r="I35" t="s">
-        <v>37</v>
+        <v>955</v>
       </c>
       <c r="J35" t="s">
-        <v>38</v>
+        <v>956</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>952</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B36">
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E36" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H36" t="s">
         <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J36" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K36" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B37">
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D37" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J37" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K37" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B38">
         <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E38" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H38" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J38" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K38" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B39">
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D39" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F39" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G39" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H39" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I39" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B40">
         <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D40" t="s">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="E40" t="s">
-        <v>610</v>
+        <v>699</v>
       </c>
       <c r="F40" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="G40" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="H40" t="s">
-        <v>842</v>
+        <v>704</v>
       </c>
       <c r="I40" t="s">
-        <v>843</v>
+        <v>705</v>
       </c>
       <c r="J40" t="s">
-        <v>844</v>
+        <v>706</v>
       </c>
       <c r="K40" t="s">
-        <v>838</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B41">
         <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D41" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="E41" t="s">
-        <v>856</v>
+        <v>610</v>
       </c>
       <c r="F41" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="G41" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="H41" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="I41" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="J41" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="K41" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B42">
         <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D42" t="s">
-        <v>643</v>
+        <v>855</v>
       </c>
       <c r="E42" t="s">
-        <v>957</v>
+        <v>856</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>858</v>
       </c>
       <c r="G42" t="s">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="H42" t="s">
-        <v>961</v>
+        <v>861</v>
       </c>
       <c r="I42" t="s">
-        <v>962</v>
+        <v>862</v>
       </c>
       <c r="J42" t="s">
-        <v>963</v>
+        <v>863</v>
       </c>
       <c r="K42" t="s">
-        <v>958</v>
+        <v>857</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B43">
         <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D43" t="s">
-        <v>1228</v>
+        <v>643</v>
       </c>
       <c r="E43" t="s">
-        <v>1229</v>
+        <v>957</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>1231</v>
+        <v>959</v>
       </c>
       <c r="H43" t="s">
-        <v>1233</v>
+        <v>961</v>
       </c>
       <c r="I43" t="s">
-        <v>1234</v>
+        <v>962</v>
       </c>
       <c r="J43" t="s">
-        <v>1235</v>
+        <v>963</v>
       </c>
       <c r="K43" t="s">
-        <v>1230</v>
+        <v>958</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B44">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D44" t="s">
-        <v>184</v>
+        <v>1228</v>
       </c>
       <c r="E44" t="s">
-        <v>185</v>
+        <v>1229</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>131</v>
+        <v>1231</v>
       </c>
       <c r="H44" t="s">
-        <v>188</v>
+        <v>1233</v>
       </c>
       <c r="I44" t="s">
-        <v>189</v>
+        <v>1234</v>
       </c>
       <c r="J44" t="s">
-        <v>190</v>
+        <v>1235</v>
       </c>
       <c r="K44" t="s">
-        <v>186</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B45">
         <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D45" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F45" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G45" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H45" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I45" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J45" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K45" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B46">
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E46" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F46" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G46" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H46" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I46" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J46" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K46" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B47">
         <v>87</v>
@@ -17149,7 +17231,7 @@
         <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F47" t="s">
         <v>66</v>
@@ -17167,327 +17249,327 @@
         <v>79</v>
       </c>
       <c r="K47" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B48">
         <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E48" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F48" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G48" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H48" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I48" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B49">
         <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D49" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E49" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G49" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H49" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I49" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J49" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K49" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B50">
         <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D50" t="s">
-        <v>864</v>
+        <v>570</v>
       </c>
       <c r="E50" t="s">
-        <v>865</v>
+        <v>571</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="H50" t="s">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="I50" t="s">
-        <v>870</v>
+        <v>576</v>
       </c>
       <c r="J50" t="s">
-        <v>871</v>
+        <v>577</v>
       </c>
       <c r="K50" t="s">
-        <v>866</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B51">
         <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D51" t="s">
-        <v>950</v>
+        <v>864</v>
       </c>
       <c r="E51" t="s">
-        <v>996</v>
+        <v>865</v>
       </c>
       <c r="F51" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>438</v>
+        <v>867</v>
       </c>
       <c r="H51" t="s">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="I51" t="s">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J51" t="s">
-        <v>1001</v>
+        <v>871</v>
       </c>
       <c r="K51" t="s">
-        <v>997</v>
+        <v>866</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B52">
         <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D52" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="E52" t="s">
-        <v>1097</v>
+        <v>996</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>1099</v>
+        <v>438</v>
       </c>
       <c r="H52" t="s">
-        <v>1101</v>
+        <v>999</v>
       </c>
       <c r="I52" t="s">
-        <v>1102</v>
+        <v>1000</v>
       </c>
       <c r="J52" t="s">
-        <v>1103</v>
+        <v>1001</v>
       </c>
       <c r="K52" t="s">
-        <v>1098</v>
+        <v>997</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B53">
         <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D53" t="s">
-        <v>1156</v>
+        <v>964</v>
       </c>
       <c r="E53" t="s">
-        <v>1157</v>
+        <v>1097</v>
       </c>
       <c r="F53" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>1159</v>
+        <v>1099</v>
       </c>
       <c r="H53" t="s">
-        <v>1161</v>
+        <v>1101</v>
       </c>
       <c r="I53" t="s">
-        <v>1162</v>
+        <v>1102</v>
       </c>
       <c r="J53" t="s">
-        <v>1163</v>
+        <v>1103</v>
       </c>
       <c r="K53" t="s">
-        <v>1158</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B54">
         <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>1227</v>
+        <v>1155</v>
       </c>
       <c r="D54" t="s">
-        <v>1236</v>
+        <v>1156</v>
       </c>
       <c r="E54" t="s">
-        <v>610</v>
+        <v>1157</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G54" t="s">
-        <v>604</v>
+        <v>1159</v>
       </c>
       <c r="H54" t="s">
-        <v>1239</v>
+        <v>1161</v>
       </c>
       <c r="I54" t="s">
-        <v>1240</v>
+        <v>1162</v>
       </c>
       <c r="J54" t="s">
-        <v>1241</v>
+        <v>1163</v>
       </c>
       <c r="K54" t="s">
-        <v>1237</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B55">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>284</v>
+        <v>1227</v>
       </c>
       <c r="D55" t="s">
-        <v>369</v>
+        <v>1236</v>
       </c>
       <c r="E55" t="s">
-        <v>370</v>
+        <v>610</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>372</v>
+        <v>604</v>
       </c>
       <c r="H55" t="s">
-        <v>374</v>
+        <v>1239</v>
       </c>
       <c r="I55" t="s">
-        <v>375</v>
+        <v>1240</v>
       </c>
       <c r="J55" t="s">
-        <v>376</v>
+        <v>1241</v>
       </c>
       <c r="K55" t="s">
-        <v>371</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B56">
         <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E56" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F56" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H56" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I56" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J56" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K56" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B57">
         <v>86</v>
@@ -17496,138 +17578,138 @@
         <v>402</v>
       </c>
       <c r="D57" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H57" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I57" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J57" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K57" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B58">
         <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D58" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E58" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F58" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H58" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I58" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J58" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K58" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B59">
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D59" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E59" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G59" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H59" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I59" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J59" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K59" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B60">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D60" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
       <c r="E60" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H60" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="I60" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="J60" t="s">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="K60" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B61">
         <v>86</v>
@@ -17636,33 +17718,33 @@
         <v>591</v>
       </c>
       <c r="D61" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E61" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F61" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="H61" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="I61" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="J61" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="K61" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -17671,103 +17753,103 @@
         <v>591</v>
       </c>
       <c r="D62" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E62" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G62" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H62" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="I62" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J62" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="K62" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B63">
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D63" t="s">
-        <v>829</v>
+        <v>635</v>
       </c>
       <c r="E63" t="s">
-        <v>830</v>
+        <v>636</v>
       </c>
       <c r="F63" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>832</v>
+        <v>638</v>
       </c>
       <c r="H63" t="s">
-        <v>834</v>
+        <v>640</v>
       </c>
       <c r="I63" t="s">
-        <v>835</v>
+        <v>641</v>
       </c>
       <c r="J63" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="K63" t="s">
-        <v>831</v>
+        <v>637</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B64">
         <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D64" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E64" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="F64" t="s">
-        <v>380</v>
+        <v>785</v>
       </c>
       <c r="G64" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
       <c r="H64" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="I64" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="J64" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="K64" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B65">
         <v>86</v>
@@ -17776,68 +17858,68 @@
         <v>845</v>
       </c>
       <c r="D65" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E65" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G65" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H65" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I65" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J65" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K65" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B66">
         <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D66" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="E66" t="s">
-        <v>974</v>
+        <v>881</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>468</v>
+        <v>883</v>
       </c>
       <c r="H66" t="s">
-        <v>977</v>
+        <v>885</v>
       </c>
       <c r="I66" t="s">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="J66" t="s">
-        <v>979</v>
+        <v>887</v>
       </c>
       <c r="K66" t="s">
-        <v>975</v>
+        <v>882</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B67">
         <v>86</v>
@@ -17846,33 +17928,33 @@
         <v>934</v>
       </c>
       <c r="D67" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E67" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="F67" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="H67" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="I67" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J67" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="K67" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B68">
         <v>86</v>
@@ -17881,68 +17963,68 @@
         <v>934</v>
       </c>
       <c r="D68" t="s">
-        <v>1073</v>
+        <v>980</v>
       </c>
       <c r="E68" t="s">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="F68" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G68" t="s">
-        <v>1077</v>
+        <v>984</v>
       </c>
       <c r="H68" t="s">
-        <v>1079</v>
+        <v>986</v>
       </c>
       <c r="I68" t="s">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="J68" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="K68" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B69">
         <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D69" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E69" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="F69" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="G69" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="H69" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="I69" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="J69" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="K69" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B70">
         <v>86</v>
@@ -17951,103 +18033,103 @@
         <v>1087</v>
       </c>
       <c r="D70" t="s">
-        <v>1146</v>
+        <v>1088</v>
       </c>
       <c r="E70" t="s">
-        <v>1147</v>
+        <v>1089</v>
       </c>
       <c r="F70" t="s">
-        <v>1149</v>
+        <v>1091</v>
       </c>
       <c r="G70" t="s">
-        <v>1150</v>
+        <v>1092</v>
       </c>
       <c r="H70" t="s">
-        <v>1152</v>
+        <v>1094</v>
       </c>
       <c r="I70" t="s">
-        <v>1153</v>
+        <v>1095</v>
       </c>
       <c r="J70" t="s">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="K70" t="s">
-        <v>1148</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B71">
         <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D71" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="E71" t="s">
-        <v>610</v>
+        <v>1147</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G71" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
       <c r="H71" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
       <c r="I71" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="J71" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="K71" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B72">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>1164</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>610</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>58</v>
+        <v>1166</v>
       </c>
       <c r="H72" t="s">
-        <v>60</v>
+        <v>1168</v>
       </c>
       <c r="I72" t="s">
-        <v>61</v>
+        <v>1169</v>
       </c>
       <c r="J72" t="s">
-        <v>62</v>
+        <v>1170</v>
       </c>
       <c r="K72" t="s">
-        <v>57</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B73">
         <v>85</v>
@@ -18056,173 +18138,173 @@
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="E73" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F73" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H73" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I73" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="J73" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K73" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B74">
         <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E74" t="s">
-        <v>308</v>
+        <v>89</v>
       </c>
       <c r="F74" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G74" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
       <c r="H74" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="I74" t="s">
-        <v>313</v>
+        <v>134</v>
       </c>
       <c r="J74" t="s">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="K74" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B75">
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E75" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G75" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H75" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="I75" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="J75" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="K75" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B76">
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D76" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E76" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="F76" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="H76" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="I76" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="J76" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="K76" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B77">
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D77" t="s">
-        <v>774</v>
+        <v>474</v>
       </c>
       <c r="E77" t="s">
-        <v>783</v>
+        <v>475</v>
       </c>
       <c r="F77" t="s">
-        <v>785</v>
+        <v>477</v>
       </c>
       <c r="G77" t="s">
-        <v>786</v>
+        <v>478</v>
       </c>
       <c r="H77" t="s">
-        <v>788</v>
+        <v>480</v>
       </c>
       <c r="I77" t="s">
-        <v>789</v>
+        <v>481</v>
       </c>
       <c r="J77" t="s">
-        <v>790</v>
+        <v>482</v>
       </c>
       <c r="K77" t="s">
-        <v>784</v>
+        <v>476</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B78">
         <v>85</v>
@@ -18231,33 +18313,33 @@
         <v>773</v>
       </c>
       <c r="D78" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="E78" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F78" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="G78" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H78" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="I78" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="J78" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K78" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B79">
         <v>85</v>
@@ -18266,68 +18348,68 @@
         <v>773</v>
       </c>
       <c r="D79" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="E79" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F79" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G79" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="H79" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="I79" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J79" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="K79" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B80">
         <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D80" t="s">
-        <v>989</v>
+        <v>821</v>
       </c>
       <c r="E80" t="s">
-        <v>990</v>
+        <v>822</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="G80" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="H80" t="s">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="I80" t="s">
-        <v>994</v>
+        <v>827</v>
       </c>
       <c r="J80" t="s">
-        <v>995</v>
+        <v>828</v>
       </c>
       <c r="K80" t="s">
-        <v>991</v>
+        <v>823</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B81">
         <v>85</v>
@@ -18336,243 +18418,243 @@
         <v>934</v>
       </c>
       <c r="D81" t="s">
-        <v>1065</v>
+        <v>989</v>
       </c>
       <c r="E81" t="s">
-        <v>1066</v>
+        <v>990</v>
       </c>
       <c r="F81" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="H81" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="I81" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="J81" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
       <c r="K81" t="s">
-        <v>1067</v>
+        <v>991</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B82">
         <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D82" t="s">
-        <v>1242</v>
+        <v>1065</v>
       </c>
       <c r="E82" t="s">
-        <v>610</v>
+        <v>1066</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G82" t="s">
-        <v>604</v>
+        <v>1068</v>
       </c>
       <c r="H82" t="s">
-        <v>312</v>
+        <v>1070</v>
       </c>
       <c r="I82" t="s">
-        <v>1245</v>
+        <v>1071</v>
       </c>
       <c r="J82" t="s">
-        <v>1246</v>
+        <v>1072</v>
       </c>
       <c r="K82" t="s">
-        <v>1243</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B83">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>12</v>
+        <v>1227</v>
       </c>
       <c r="D83" t="s">
-        <v>144</v>
+        <v>1242</v>
       </c>
       <c r="E83" t="s">
-        <v>145</v>
+        <v>610</v>
       </c>
       <c r="F83" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>148</v>
+        <v>604</v>
       </c>
       <c r="H83" t="s">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="I83" t="s">
-        <v>151</v>
+        <v>1245</v>
       </c>
       <c r="J83" t="s">
-        <v>152</v>
+        <v>1246</v>
       </c>
       <c r="K83" t="s">
-        <v>146</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B84">
         <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
         <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="F84" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G84" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="H84" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I84" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="J84" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="K84" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E85" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F85" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="G85" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="H85" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="I85" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="J85" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="K85" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D86" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="E86" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="F86" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="G86" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="H86" t="s">
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="I86" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J86" t="s">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="K86" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B87">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D87" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="E87" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G87" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H87" t="s">
-        <v>718</v>
+        <v>488</v>
       </c>
       <c r="I87" t="s">
-        <v>719</v>
+        <v>489</v>
       </c>
       <c r="J87" t="s">
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K87" t="s">
-        <v>716</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B88">
         <v>84</v>
@@ -18581,33 +18663,33 @@
         <v>697</v>
       </c>
       <c r="D88" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E88" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="H88" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I88" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="J88" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K88" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B89">
         <v>84</v>
@@ -18616,138 +18698,138 @@
         <v>697</v>
       </c>
       <c r="D89" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E89" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F89" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G89" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H89" t="s">
         <v>726</v>
       </c>
       <c r="I89" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="J89" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="K89" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B90">
         <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D90" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="E90" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="F90" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="G90" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="H90" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I90" t="s">
-        <v>797</v>
+        <v>734</v>
       </c>
       <c r="J90" t="s">
-        <v>798</v>
+        <v>735</v>
       </c>
       <c r="K90" t="s">
-        <v>792</v>
+        <v>731</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B91">
         <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D91" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="E91" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="F91" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="G91" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H91" t="s">
-        <v>901</v>
+        <v>796</v>
       </c>
       <c r="I91" t="s">
-        <v>902</v>
+        <v>797</v>
       </c>
       <c r="J91" t="s">
-        <v>903</v>
+        <v>798</v>
       </c>
       <c r="K91" t="s">
-        <v>898</v>
+        <v>792</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B92">
         <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D92" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="E92" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="F92" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G92" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="H92" t="s">
-        <v>970</v>
+        <v>901</v>
       </c>
       <c r="I92" t="s">
-        <v>971</v>
+        <v>902</v>
       </c>
       <c r="J92" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="K92" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B93">
         <v>84</v>
@@ -18756,33 +18838,33 @@
         <v>934</v>
       </c>
       <c r="D93" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="E93" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="F93" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="G93" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="H93" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="I93" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="J93" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K93" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B94">
         <v>84</v>
@@ -18791,33 +18873,33 @@
         <v>934</v>
       </c>
       <c r="D94" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="E94" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="F94" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="G94" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="H94" t="s">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="I94" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="J94" t="s">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="K94" t="s">
-        <v>1033</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B95">
         <v>84</v>
@@ -18826,173 +18908,173 @@
         <v>934</v>
       </c>
       <c r="D95" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="E95" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="F95" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G95" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="H95" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="I95" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="J95" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="K95" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B96">
         <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D96" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="E96" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F96" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="H96" t="s">
-        <v>1109</v>
+        <v>1062</v>
       </c>
       <c r="I96" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="J96" t="s">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K96" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B97">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>1200</v>
+        <v>1087</v>
       </c>
       <c r="D97" t="s">
-        <v>1201</v>
+        <v>271</v>
       </c>
       <c r="E97" t="s">
-        <v>1202</v>
+        <v>1104</v>
       </c>
       <c r="F97" t="s">
-        <v>1204</v>
+        <v>1106</v>
       </c>
       <c r="G97" t="s">
-        <v>1205</v>
+        <v>1107</v>
       </c>
       <c r="H97" t="s">
-        <v>1207</v>
+        <v>1109</v>
       </c>
       <c r="I97" t="s">
-        <v>1208</v>
+        <v>1110</v>
       </c>
       <c r="J97" t="s">
-        <v>1209</v>
+        <v>1111</v>
       </c>
       <c r="K97" t="s">
-        <v>1203</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B98">
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>284</v>
+        <v>1200</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>1201</v>
       </c>
       <c r="E98" t="s">
-        <v>362</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="s">
-        <v>356</v>
+        <v>1204</v>
       </c>
       <c r="G98" t="s">
-        <v>364</v>
+        <v>1205</v>
       </c>
       <c r="H98" t="s">
-        <v>366</v>
+        <v>1207</v>
       </c>
       <c r="I98" t="s">
-        <v>367</v>
+        <v>1208</v>
       </c>
       <c r="J98" t="s">
-        <v>368</v>
+        <v>1209</v>
       </c>
       <c r="K98" t="s">
-        <v>363</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B99">
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D99" t="s">
-        <v>491</v>
+        <v>353</v>
       </c>
       <c r="E99" t="s">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="G99" t="s">
-        <v>494</v>
+        <v>364</v>
       </c>
       <c r="H99" t="s">
-        <v>496</v>
+        <v>366</v>
       </c>
       <c r="I99" t="s">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="J99" t="s">
-        <v>498</v>
+        <v>368</v>
       </c>
       <c r="K99" t="s">
-        <v>493</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B100">
         <v>83</v>
@@ -19001,173 +19083,173 @@
         <v>473</v>
       </c>
       <c r="D100" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="E100" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="F100" t="s">
-        <v>535</v>
+        <v>75</v>
       </c>
       <c r="G100" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="H100" t="s">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="I100" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="J100" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="K100" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B101">
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D101" t="s">
-        <v>643</v>
+        <v>532</v>
       </c>
       <c r="E101" t="s">
-        <v>644</v>
+        <v>533</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="G101" t="s">
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="H101" t="s">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="I101" t="s">
-        <v>648</v>
+        <v>539</v>
       </c>
       <c r="J101" t="s">
-        <v>649</v>
+        <v>540</v>
       </c>
       <c r="K101" t="s">
-        <v>645</v>
+        <v>534</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B102">
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="D102" t="s">
-        <v>736</v>
+        <v>643</v>
       </c>
       <c r="E102" t="s">
-        <v>737</v>
+        <v>644</v>
       </c>
       <c r="F102" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="H102" t="s">
-        <v>741</v>
+        <v>647</v>
       </c>
       <c r="I102" t="s">
-        <v>742</v>
+        <v>648</v>
       </c>
       <c r="J102" t="s">
-        <v>743</v>
+        <v>649</v>
       </c>
       <c r="K102" t="s">
-        <v>738</v>
+        <v>645</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B103">
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D103" t="s">
-        <v>807</v>
+        <v>736</v>
       </c>
       <c r="E103" t="s">
-        <v>808</v>
+        <v>737</v>
       </c>
       <c r="F103" t="s">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="G103" t="s">
-        <v>811</v>
+        <v>604</v>
       </c>
       <c r="H103" t="s">
-        <v>813</v>
+        <v>741</v>
       </c>
       <c r="I103" t="s">
-        <v>814</v>
+        <v>742</v>
       </c>
       <c r="J103" t="s">
-        <v>815</v>
+        <v>743</v>
       </c>
       <c r="K103" t="s">
-        <v>809</v>
+        <v>738</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B104">
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D104" t="s">
-        <v>650</v>
+        <v>807</v>
       </c>
       <c r="E104" t="s">
-        <v>1016</v>
+        <v>808</v>
       </c>
       <c r="F104" t="s">
-        <v>66</v>
+        <v>810</v>
       </c>
       <c r="G104" t="s">
-        <v>1018</v>
+        <v>811</v>
       </c>
       <c r="H104" t="s">
-        <v>1020</v>
+        <v>813</v>
       </c>
       <c r="I104" t="s">
-        <v>1021</v>
+        <v>814</v>
       </c>
       <c r="J104" t="s">
-        <v>1022</v>
+        <v>815</v>
       </c>
       <c r="K104" t="s">
-        <v>1017</v>
+        <v>809</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B105">
         <v>83</v>
@@ -19176,103 +19258,103 @@
         <v>934</v>
       </c>
       <c r="D105" t="s">
-        <v>1048</v>
+        <v>650</v>
       </c>
       <c r="E105" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="F105" t="s">
-        <v>1051</v>
+        <v>66</v>
       </c>
       <c r="G105" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="H105" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="I105" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="J105" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="K105" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B106">
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D106" t="s">
-        <v>1247</v>
+        <v>1048</v>
       </c>
       <c r="E106" t="s">
-        <v>1248</v>
+        <v>1049</v>
       </c>
       <c r="F106" t="s">
-        <v>66</v>
+        <v>1051</v>
       </c>
       <c r="G106" t="s">
-        <v>604</v>
+        <v>1052</v>
       </c>
       <c r="H106" t="s">
-        <v>1251</v>
+        <v>1054</v>
       </c>
       <c r="I106" t="s">
-        <v>1252</v>
+        <v>1055</v>
       </c>
       <c r="J106" t="s">
-        <v>1253</v>
+        <v>1056</v>
       </c>
       <c r="K106" t="s">
-        <v>1249</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B107">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D107" t="s">
-        <v>227</v>
+        <v>1247</v>
       </c>
       <c r="E107" t="s">
-        <v>228</v>
+        <v>1248</v>
       </c>
       <c r="F107" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="G107" t="s">
-        <v>231</v>
+        <v>604</v>
       </c>
       <c r="H107" t="s">
-        <v>233</v>
+        <v>1251</v>
       </c>
       <c r="I107" t="s">
-        <v>234</v>
+        <v>1252</v>
       </c>
       <c r="J107" t="s">
-        <v>235</v>
+        <v>1253</v>
       </c>
       <c r="K107" t="s">
-        <v>229</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B108">
         <v>82</v>
@@ -19281,138 +19363,138 @@
         <v>159</v>
       </c>
       <c r="D108" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="E108" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="F108" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G108" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="H108" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="I108" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="J108" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="K108" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B109">
         <v>82</v>
       </c>
       <c r="C109" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D109" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="E109" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="F109" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="G109" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="H109" t="s">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="I109" t="s">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="J109" t="s">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="K109" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B110">
         <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>591</v>
+        <v>284</v>
       </c>
       <c r="D110" t="s">
-        <v>601</v>
+        <v>338</v>
       </c>
       <c r="E110" t="s">
-        <v>602</v>
+        <v>339</v>
       </c>
       <c r="F110" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="G110" t="s">
-        <v>604</v>
+        <v>342</v>
       </c>
       <c r="H110" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="I110" t="s">
-        <v>607</v>
+        <v>345</v>
       </c>
       <c r="J110" t="s">
-        <v>608</v>
+        <v>346</v>
       </c>
       <c r="K110" t="s">
-        <v>603</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B111">
         <v>82</v>
       </c>
       <c r="C111" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D111" t="s">
-        <v>13</v>
+        <v>601</v>
       </c>
       <c r="E111" t="s">
-        <v>1009</v>
+        <v>602</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G111" t="s">
-        <v>1011</v>
+        <v>604</v>
       </c>
       <c r="H111" t="s">
-        <v>1013</v>
+        <v>606</v>
       </c>
       <c r="I111" t="s">
-        <v>1014</v>
+        <v>607</v>
       </c>
       <c r="J111" t="s">
-        <v>1015</v>
+        <v>608</v>
       </c>
       <c r="K111" t="s">
-        <v>1010</v>
+        <v>603</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B112">
         <v>82</v>
@@ -19421,342 +19503,377 @@
         <v>934</v>
       </c>
       <c r="D112" t="s">
-        <v>1023</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="F112" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G112" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="H112" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="I112" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="J112" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="K112" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B113">
         <v>82</v>
       </c>
       <c r="C113" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D113" t="s">
-        <v>1112</v>
+        <v>1023</v>
       </c>
       <c r="E113" t="s">
-        <v>1113</v>
+        <v>1024</v>
       </c>
       <c r="F113" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="G113" t="s">
-        <v>1115</v>
+        <v>1027</v>
       </c>
       <c r="H113" t="s">
-        <v>1117</v>
+        <v>1029</v>
       </c>
       <c r="I113" t="s">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="J113" t="s">
-        <v>1119</v>
+        <v>1031</v>
       </c>
       <c r="K113" t="s">
-        <v>1114</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B114">
         <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>1210</v>
+        <v>1087</v>
       </c>
       <c r="D114" t="s">
-        <v>1211</v>
+        <v>1112</v>
       </c>
       <c r="E114" t="s">
-        <v>89</v>
+        <v>1113</v>
       </c>
       <c r="F114" t="s">
-        <v>1213</v>
+        <v>25</v>
       </c>
       <c r="G114" t="s">
-        <v>1214</v>
+        <v>1115</v>
       </c>
       <c r="H114" t="s">
-        <v>1216</v>
+        <v>1117</v>
       </c>
       <c r="I114" t="s">
-        <v>1217</v>
+        <v>1118</v>
       </c>
       <c r="J114" t="s">
-        <v>1218</v>
+        <v>1119</v>
       </c>
       <c r="K114" t="s">
-        <v>1212</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B115">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>1210</v>
       </c>
       <c r="D115" t="s">
-        <v>80</v>
+        <v>1211</v>
       </c>
       <c r="E115" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F115" t="s">
-        <v>25</v>
+        <v>1213</v>
       </c>
       <c r="G115" t="s">
-        <v>83</v>
+        <v>1214</v>
       </c>
       <c r="H115" t="s">
-        <v>85</v>
+        <v>1216</v>
       </c>
       <c r="I115" t="s">
-        <v>86</v>
+        <v>1217</v>
       </c>
       <c r="J115" t="s">
-        <v>87</v>
+        <v>1218</v>
       </c>
       <c r="K115" t="s">
-        <v>82</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B116">
         <v>81</v>
       </c>
       <c r="C116" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="E116" t="s">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="F116" t="s">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="H116" t="s">
-        <v>383</v>
+        <v>85</v>
       </c>
       <c r="I116" t="s">
-        <v>384</v>
+        <v>86</v>
       </c>
       <c r="J116" t="s">
-        <v>385</v>
+        <v>87</v>
       </c>
       <c r="K116" t="s">
-        <v>379</v>
+        <v>82</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B117">
         <v>81</v>
       </c>
       <c r="C117" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D117" t="s">
-        <v>499</v>
+        <v>377</v>
       </c>
       <c r="E117" t="s">
-        <v>500</v>
+        <v>378</v>
       </c>
       <c r="F117" t="s">
-        <v>502</v>
+        <v>380</v>
       </c>
       <c r="G117" t="s">
-        <v>503</v>
+        <v>381</v>
       </c>
       <c r="H117" t="s">
-        <v>505</v>
+        <v>383</v>
       </c>
       <c r="I117" t="s">
-        <v>506</v>
+        <v>384</v>
       </c>
       <c r="J117" t="s">
-        <v>507</v>
+        <v>385</v>
       </c>
       <c r="K117" t="s">
-        <v>501</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B118">
         <v>81</v>
       </c>
       <c r="C118" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D118" t="s">
-        <v>616</v>
+        <v>499</v>
       </c>
       <c r="E118" t="s">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="F118" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="G118" t="s">
-        <v>618</v>
+        <v>503</v>
       </c>
       <c r="H118" t="s">
-        <v>620</v>
+        <v>505</v>
       </c>
       <c r="I118" t="s">
-        <v>621</v>
+        <v>506</v>
       </c>
       <c r="J118" t="s">
-        <v>622</v>
+        <v>507</v>
       </c>
       <c r="K118" t="s">
-        <v>617</v>
+        <v>501</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B119">
         <v>81</v>
       </c>
       <c r="C119" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D119" t="s">
-        <v>888</v>
+        <v>616</v>
       </c>
       <c r="E119" t="s">
-        <v>889</v>
+        <v>610</v>
       </c>
       <c r="F119" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G119" t="s">
-        <v>891</v>
+        <v>618</v>
       </c>
       <c r="H119" t="s">
-        <v>893</v>
+        <v>620</v>
       </c>
       <c r="I119" t="s">
-        <v>894</v>
+        <v>621</v>
       </c>
       <c r="J119" t="s">
-        <v>895</v>
+        <v>622</v>
       </c>
       <c r="K119" t="s">
-        <v>890</v>
+        <v>617</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B120">
         <v>81</v>
       </c>
       <c r="C120" t="s">
-        <v>1087</v>
+        <v>845</v>
       </c>
       <c r="D120" t="s">
-        <v>1120</v>
+        <v>888</v>
       </c>
       <c r="E120" t="s">
-        <v>1121</v>
+        <v>889</v>
       </c>
       <c r="F120" t="s">
-        <v>1123</v>
+        <v>25</v>
       </c>
       <c r="G120" t="s">
-        <v>1124</v>
+        <v>891</v>
       </c>
       <c r="H120" t="s">
-        <v>1126</v>
+        <v>893</v>
       </c>
       <c r="I120" t="s">
-        <v>1127</v>
+        <v>894</v>
       </c>
       <c r="J120" t="s">
-        <v>1128</v>
+        <v>895</v>
       </c>
       <c r="K120" t="s">
-        <v>1122</v>
+        <v>890</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B121">
+        <v>81</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H121" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I121" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J121" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K121" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B122">
         <v>80</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C122" t="s">
         <v>934</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D122" t="s">
         <v>1039</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E122" t="s">
         <v>1040</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F122" t="s">
         <v>1042</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G122" t="s">
         <v>1043</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H122" t="s">
         <v>1045</v>
       </c>
-      <c r="I121" t="s">
+      <c r="I122" t="s">
         <v>1046</v>
       </c>
-      <c r="J121" t="s">
+      <c r="J122" t="s">
         <v>1047</v>
       </c>
-      <c r="K121" t="s">
+      <c r="K122" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3986" uniqueCount="1311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1340">
   <si>
     <t>日期</t>
   </si>
@@ -3827,6 +3827,93 @@
   </si>
   <si>
     <t>重点突出可降解/可吸收支架研究课题与材料学（铁基/镍钛/高分子）项目，量化降解行为、力学与生物相容性评价数据；单列掌握的AutoCAD/SolidWorks三维建模与有限元仿真能力；补充动物实验与产品测试经历，突出应届可到岗及长期研发意愿。</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>本科及以上，机械/材料等专业，4年以上介入/植入类产品研发经验；负责介入/植入器械材料选型、结构设计、工装夹具设计、测试分析、风险管理、验证确认及转产。</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|介入/植入器械研发岗，方向与材料/结构技能匹配度高</t>
+  </si>
+  <si>
+    <t>研究80/技能78/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>先健科技为港股上市的介入植介入械头部企业，其可降解支架与镍钛金属器械业务与候选人研究方向高度契合。该岗位负责介入/植入器械的材料选型与结构设计，正对应候选人硕士阶段血管支架方向的研究训练。作为上市公司研发岗，技术平台成熟、成长路径清晰，是进入介入医疗核心企业的优质机会。</t>
+  </si>
+  <si>
+    <t>简历中突出硕士期间血管支架材料选型、结构设计与力学验证工作，列出使用过的材料力学测试（金相/DSC/SEM等）与设计工具；强调风险管理与验证确认意识，量化完成的项目经验，体现应对4年经验要求的能力。</t>
+  </si>
+  <si>
+    <t>研发工程师（镍钛合金方向）</t>
+  </si>
+  <si>
+    <t>负责镍钛合金材料研究与支架结构研发，镍钛材料特性掌握、工艺开发与验证；赛诺医疗为冠脉/外周支架领军企业，工作地天津/苏州。</t>
+  </si>
+  <si>
+    <t>苏州/天津</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com/job_detail/89f387871395662a0Hd80t21FVU~.html</t>
+  </si>
+  <si>
+    <t>智能匹配89分【社招】|强烈推荐|镍钛合金支架研发方向直接匹配，材料学+支架设计技能高度重合</t>
+  </si>
+  <si>
+    <t>研究88/技能80/学历95/行业100/企业95</t>
+  </si>
+  <si>
+    <t>赛诺医疗是国内冠脉支架/外周支架龙头（BuMA等）上市公司。该镍钛合金方向研发岗与候选人硕士阶段血管支架材料研究方向完全契合，涉及镍钛材料特性与支架结构研发，正对应候选人的材料学与支架设计双重技能。硕士学历可投且为上市公司核心研发岗，强烈推荐投递。</t>
+  </si>
+  <si>
+    <t>针对镍钛合金方向重点展开：描述镍钛（NiTi）材料研究经历、超弹性/形状记忆合金性能测试、支架结构设计与有限元。突出掌握的力学与材料学方法，将科研成果对应到支架应用的工程问题，并注明熟练使用SolidWorks等结构设计工具。</t>
+  </si>
+  <si>
+    <t>研发工程师（动物实验/生物相容性）</t>
+  </si>
+  <si>
+    <t>负责产品研发过程中的动物实验与生物相容性评价，涉及植入实验、组织学观察与ISO 10993相关评价。</t>
+  </si>
+  <si>
+    <t>https://www.zhipin.com/job_detail/99cfc2f4dcb6775b3nN73ti_EVE~.html</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|动物实验+生物相容性评价为候选人核心技能，介入器械研发直接应用</t>
+  </si>
+  <si>
+    <t>研究78/技能75/学历90/行业100/企业95</t>
+  </si>
+  <si>
+    <t>该岗位聚焦动物实验与生物相容性评价，正是候选人四大核心技能中的两项（动物实验、生物相容性评价）。赛诺医疗为冠脉/外周支架龙头企业，此岗位可直接将候选人在血管支架课题中积累的动物植入实验与体外生物相容性评价能力落地，是实践性强的技术岗位，匹配度极高。</t>
+  </si>
+  <si>
+    <t>突出动物实验设计执行、植入/组织切片/影像随访经验，以及细胞毒性、溶血、凝血、ISO 10993等生物相容性评价经历。用具体实验数据量化（如实验动物模型、随访周期、评价指标通过情况），强调合规与安全性意识。</t>
+  </si>
+  <si>
+    <t>豪泰医疗（迈瑞控股）</t>
+  </si>
+  <si>
+    <t>研发/技术工程师（冠脉球囊/导管/导丝）</t>
+  </si>
+  <si>
+    <t>面向社招，负责冠脉通路的球囊、导管、导丝以及电生理、外周介入产品研发，涉及材料选型、结构设计与工艺优化。</t>
+  </si>
+  <si>
+    <t>https://app.mokahr.com/social-recruitment/apt/140851</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|冠脉球囊/导管/导丝介入器械研发，方向相关匹配</t>
+  </si>
+  <si>
+    <t>研究85/技能70/学历90/行业100/企业88</t>
+  </si>
+  <si>
+    <t>豪泰医疗为迈瑞医疗控股的血管介入企业，专注冠脉球囊、导管、导丝及外周介入产品，是知名上市医疗器械集团（迈瑞）体系下的介入业务研发平台。岗位涉及介入导管/球囊研发，与候选人血管介入器械方向相关，能依托上市公司平台获得规范的研发成长路径，值得投递。</t>
+  </si>
+  <si>
+    <t>简历突出介入器械相关的材料学基础与结构设计能力，将硕士血管支架课题中材料/结构/加工经验迁移到球囊与导管研发；强调对介入输送系统、镍钛导丝等材料的理解，弱化纯支架视角，突出跨品类学习能力与工程执行力。</t>
   </si>
   <si>
     <t>投递日期</t>
@@ -4381,7 +4468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10855,6 +10942,158 @@
       </c>
       <c r="L170" t="s">
         <v>1270</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B171" t="s">
+        <v>950</v>
+      </c>
+      <c r="C171" t="s">
+        <v>463</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E171" t="s">
+        <v>66</v>
+      </c>
+      <c r="F171" t="s">
+        <v>438</v>
+      </c>
+      <c r="G171">
+        <v>8</v>
+      </c>
+      <c r="H171" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I171">
+        <v>84</v>
+      </c>
+      <c r="J171" t="s">
+        <v>1274</v>
+      </c>
+      <c r="K171" t="s">
+        <v>1275</v>
+      </c>
+      <c r="L171" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B172" t="s">
+        <v>219</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G172">
+        <v>9</v>
+      </c>
+      <c r="H172" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I172">
+        <v>89</v>
+      </c>
+      <c r="J172" t="s">
+        <v>1282</v>
+      </c>
+      <c r="K172" t="s">
+        <v>1283</v>
+      </c>
+      <c r="L172" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B173" t="s">
+        <v>219</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E173" t="s">
+        <v>98</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G173">
+        <v>8</v>
+      </c>
+      <c r="H173" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I173">
+        <v>83</v>
+      </c>
+      <c r="J173" t="s">
+        <v>1289</v>
+      </c>
+      <c r="K173" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L173" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E174" t="s">
+        <v>66</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G174">
+        <v>8</v>
+      </c>
+      <c r="H174" t="s">
+        <v>1296</v>
+      </c>
+      <c r="I174">
+        <v>83</v>
+      </c>
+      <c r="J174" t="s">
+        <v>1297</v>
+      </c>
+      <c r="K174" t="s">
+        <v>1298</v>
+      </c>
+      <c r="L174" t="s">
+        <v>1299</v>
       </c>
     </row>
   </sheetData>
@@ -10888,7 +11127,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1271</v>
+        <v>1300</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10897,16 +11136,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1272</v>
+        <v>1301</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1273</v>
+        <v>1302</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1274</v>
+        <v>1303</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1275</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10920,13 +11159,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1276</v>
+        <v>1305</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1277</v>
+        <v>1306</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1278</v>
+        <v>1307</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -10954,7 +11193,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -10969,7 +11208,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1283</v>
+        <v>1312</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10979,31 +11218,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1284</v>
+        <v>1313</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1285</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1286</v>
+        <v>1315</v>
       </c>
       <c r="B4">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1287</v>
+        <v>1316</v>
       </c>
       <c r="B5" t="s">
-        <v>1288</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1289</v>
+        <v>1318</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -11011,7 +11250,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1290</v>
+        <v>1319</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -11019,23 +11258,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1291</v>
+        <v>1320</v>
       </c>
       <c r="B8">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1292</v>
+        <v>1321</v>
       </c>
       <c r="B9">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1293</v>
+        <v>1322</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -11043,15 +11282,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1294</v>
+        <v>1323</v>
       </c>
       <c r="B11" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1295</v>
+        <v>1324</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11061,15 +11300,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1296</v>
+        <v>1325</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1297</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1298</v>
+        <v>1327</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -11077,23 +11316,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1299</v>
+        <v>1328</v>
       </c>
       <c r="B17" s="5">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1300</v>
+        <v>1329</v>
       </c>
       <c r="B18" s="5">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1301</v>
+        <v>1330</v>
       </c>
       <c r="B19" s="5">
         <v>6</v>
@@ -11101,7 +11340,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1302</v>
+        <v>1331</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -11109,7 +11348,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1303</v>
+        <v>1332</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11117,7 +11356,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1304</v>
+        <v>1333</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -11125,7 +11364,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1305</v>
+        <v>1334</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11133,7 +11372,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1306</v>
+        <v>1335</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -11141,7 +11380,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1307</v>
+        <v>1336</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -11149,7 +11388,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1308</v>
+        <v>1337</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -11161,7 +11400,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1309</v>
+        <v>1338</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -11179,7 +11418,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1310</v>
+        <v>1339</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -13322,25 +13561,25 @@
         <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>1200</v>
+        <v>1271</v>
       </c>
       <c r="C112" t="s">
-        <v>1201</v>
+        <v>219</v>
       </c>
       <c r="D112" t="s">
-        <v>1202</v>
+        <v>1277</v>
       </c>
       <c r="E112" t="s">
-        <v>1204</v>
+        <v>1279</v>
       </c>
       <c r="F112" t="s">
-        <v>1205</v>
+        <v>1280</v>
       </c>
       <c r="G112">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H112" t="s">
-        <v>1206</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -13348,25 +13587,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C113" t="s">
-        <v>72</v>
+        <v>1201</v>
       </c>
       <c r="D113" t="s">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="E113" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="s">
-        <v>76</v>
+        <v>1205</v>
       </c>
       <c r="G113">
         <v>8</v>
       </c>
       <c r="H113" t="s">
-        <v>77</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -13377,22 +13616,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F114" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G114">
         <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,22 +13642,22 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D115" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F115" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G115">
         <v>8</v>
       </c>
       <c r="H115" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -13429,22 +13668,22 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E116" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F116" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -13455,22 +13694,22 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D117" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
       </c>
       <c r="F117" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -13481,22 +13720,22 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D118" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E118" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="F118" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -13507,22 +13746,22 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E119" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F119" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -13533,22 +13772,22 @@
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F120" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13556,25 +13795,25 @@
         <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="D121" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="E121" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F121" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -13585,22 +13824,22 @@
         <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D122" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E122" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="F122" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -13611,22 +13850,22 @@
         <v>159</v>
       </c>
       <c r="C123" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D123" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E123" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F123" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -13637,22 +13876,22 @@
         <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D124" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="E124" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F124" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13663,22 +13902,22 @@
         <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="E125" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F125" t="s">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -13689,22 +13928,22 @@
         <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D126" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="E126" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F126" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -13715,22 +13954,22 @@
         <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D127" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F127" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -13741,22 +13980,22 @@
         <v>159</v>
       </c>
       <c r="C128" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D128" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E128" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -13767,22 +14006,22 @@
         <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D129" t="s">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="E129" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="F129" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -13793,22 +14032,22 @@
         <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D130" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F130" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -13819,22 +14058,22 @@
         <v>159</v>
       </c>
       <c r="C131" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D131" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E131" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -13842,25 +14081,25 @@
         <v>103</v>
       </c>
       <c r="B132" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C132" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="D132" t="s">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="E132" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="F132" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,22 +14110,22 @@
         <v>284</v>
       </c>
       <c r="C133" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D133" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="E133" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="F133" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -13897,22 +14136,22 @@
         <v>284</v>
       </c>
       <c r="C134" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D134" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E134" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="F134" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -13923,22 +14162,22 @@
         <v>284</v>
       </c>
       <c r="C135" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D135" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="E135" t="s">
-        <v>356</v>
+        <v>98</v>
       </c>
       <c r="F135" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -13949,22 +14188,22 @@
         <v>284</v>
       </c>
       <c r="C136" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="E136" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="F136" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -13975,22 +14214,22 @@
         <v>284</v>
       </c>
       <c r="C137" t="s">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="D137" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="E137" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="F137" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -13998,25 +14237,25 @@
         <v>109</v>
       </c>
       <c r="B138" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C138" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="D138" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E138" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F138" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,22 +14266,22 @@
         <v>402</v>
       </c>
       <c r="C139" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D139" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E139" t="s">
         <v>66</v>
       </c>
       <c r="F139" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -14053,22 +14292,22 @@
         <v>402</v>
       </c>
       <c r="C140" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D140" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E140" t="s">
         <v>66</v>
       </c>
       <c r="F140" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -14079,22 +14318,22 @@
         <v>402</v>
       </c>
       <c r="C141" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D141" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E141" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F141" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -14102,25 +14341,25 @@
         <v>113</v>
       </c>
       <c r="B142" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C142" t="s">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="D142" t="s">
-        <v>122</v>
+        <v>431</v>
       </c>
       <c r="E142" t="s">
-        <v>485</v>
+        <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>486</v>
+        <v>433</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>487</v>
+        <v>434</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -14131,22 +14370,22 @@
         <v>473</v>
       </c>
       <c r="C143" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D143" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="E143" t="s">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="F143" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -14157,22 +14396,22 @@
         <v>473</v>
       </c>
       <c r="C144" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D144" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="E144" t="s">
-        <v>502</v>
+        <v>75</v>
       </c>
       <c r="F144" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -14183,22 +14422,22 @@
         <v>473</v>
       </c>
       <c r="C145" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="D145" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="E145" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="F145" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -14209,22 +14448,22 @@
         <v>473</v>
       </c>
       <c r="C146" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="D146" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E146" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="F146" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -14232,25 +14471,25 @@
         <v>118</v>
       </c>
       <c r="B147" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C147" t="s">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="D147" t="s">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="E147" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F147" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -14261,22 +14500,22 @@
         <v>556</v>
       </c>
       <c r="C148" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D148" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E148" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="F148" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -14284,25 +14523,25 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C149" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="D149" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="E149" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="F149" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -14313,22 +14552,22 @@
         <v>591</v>
       </c>
       <c r="C150" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D150" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E150" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F150" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -14339,22 +14578,22 @@
         <v>591</v>
       </c>
       <c r="C151" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="D151" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="E151" t="s">
         <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>468</v>
+        <v>618</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -14365,22 +14604,22 @@
         <v>591</v>
       </c>
       <c r="C152" t="s">
-        <v>643</v>
+        <v>557</v>
       </c>
       <c r="D152" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="E152" t="s">
         <v>16</v>
       </c>
       <c r="F152" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -14391,22 +14630,22 @@
         <v>591</v>
       </c>
       <c r="C153" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D153" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E153" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F153" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14417,22 +14656,22 @@
         <v>591</v>
       </c>
       <c r="C154" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D154" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E154" t="s">
-        <v>661</v>
+        <v>66</v>
       </c>
       <c r="F154" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -14443,22 +14682,22 @@
         <v>591</v>
       </c>
       <c r="C155" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D155" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E155" t="s">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="F155" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -14469,22 +14708,22 @@
         <v>591</v>
       </c>
       <c r="C156" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="D156" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E156" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F156" t="s">
-        <v>676</v>
+        <v>604</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -14492,25 +14731,25 @@
         <v>128</v>
       </c>
       <c r="B157" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C157" t="s">
-        <v>714</v>
+        <v>673</v>
       </c>
       <c r="D157" t="s">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="E157" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F157" t="s">
-        <v>604</v>
+        <v>676</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -14521,22 +14760,22 @@
         <v>697</v>
       </c>
       <c r="C158" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D158" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E158" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F158" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -14547,22 +14786,22 @@
         <v>697</v>
       </c>
       <c r="C159" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D159" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E159" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14573,22 +14812,22 @@
         <v>697</v>
       </c>
       <c r="C160" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D160" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="E160" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="F160" t="s">
-        <v>604</v>
+        <v>732</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -14599,22 +14838,22 @@
         <v>697</v>
       </c>
       <c r="C161" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D161" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E161" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="F161" t="s">
-        <v>748</v>
+        <v>604</v>
       </c>
       <c r="G161">
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -14625,22 +14864,22 @@
         <v>697</v>
       </c>
       <c r="C162" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D162" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="E162" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F162" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14651,22 +14890,22 @@
         <v>697</v>
       </c>
       <c r="C163" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="D163" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E163" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F163" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14674,25 +14913,25 @@
         <v>135</v>
       </c>
       <c r="B164" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C164" t="s">
-        <v>791</v>
+        <v>760</v>
       </c>
       <c r="D164" t="s">
-        <v>610</v>
+        <v>761</v>
       </c>
       <c r="E164" t="s">
-        <v>793</v>
+        <v>763</v>
       </c>
       <c r="F164" t="s">
-        <v>794</v>
+        <v>764</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>795</v>
+        <v>765</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14703,22 +14942,22 @@
         <v>773</v>
       </c>
       <c r="C165" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="D165" t="s">
-        <v>808</v>
+        <v>610</v>
       </c>
       <c r="E165" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="F165" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14729,22 +14968,22 @@
         <v>773</v>
       </c>
       <c r="C166" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="D166" t="s">
-        <v>110</v>
+        <v>808</v>
       </c>
       <c r="E166" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F166" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -14752,25 +14991,25 @@
         <v>138</v>
       </c>
       <c r="B167" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C167" t="s">
-        <v>888</v>
+        <v>816</v>
       </c>
       <c r="D167" t="s">
-        <v>889</v>
+        <v>110</v>
       </c>
       <c r="E167" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F167" t="s">
-        <v>891</v>
+        <v>818</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>892</v>
+        <v>819</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -14781,22 +15020,22 @@
         <v>845</v>
       </c>
       <c r="C168" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D168" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
       </c>
       <c r="F168" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -14807,22 +15046,22 @@
         <v>845</v>
       </c>
       <c r="C169" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D169" t="s">
-        <v>585</v>
+        <v>897</v>
       </c>
       <c r="E169" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F169" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -14833,22 +15072,22 @@
         <v>845</v>
       </c>
       <c r="C170" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="D170" t="s">
         <v>585</v>
       </c>
       <c r="E170" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F170" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14859,22 +15098,22 @@
         <v>845</v>
       </c>
       <c r="C171" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="D171" t="s">
-        <v>919</v>
+        <v>585</v>
       </c>
       <c r="E171" t="s">
-        <v>921</v>
+        <v>16</v>
       </c>
       <c r="F171" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14882,25 +15121,25 @@
         <v>143</v>
       </c>
       <c r="B172" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C172" t="s">
-        <v>964</v>
+        <v>918</v>
       </c>
       <c r="D172" t="s">
-        <v>965</v>
+        <v>919</v>
       </c>
       <c r="E172" t="s">
-        <v>967</v>
+        <v>921</v>
       </c>
       <c r="F172" t="s">
-        <v>968</v>
+        <v>922</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>969</v>
+        <v>923</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14911,22 +15150,22 @@
         <v>934</v>
       </c>
       <c r="C173" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="D173" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="E173" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="F173" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>1005</v>
+        <v>969</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -14937,22 +15176,22 @@
         <v>934</v>
       </c>
       <c r="C174" t="s">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="D174" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="E174" t="s">
-        <v>16</v>
+        <v>1004</v>
       </c>
       <c r="F174" t="s">
-        <v>1011</v>
+        <v>438</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -14963,22 +15202,22 @@
         <v>934</v>
       </c>
       <c r="C175" t="s">
-        <v>650</v>
+        <v>13</v>
       </c>
       <c r="D175" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="E175" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F175" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -14989,22 +15228,22 @@
         <v>934</v>
       </c>
       <c r="C176" t="s">
-        <v>1023</v>
+        <v>650</v>
       </c>
       <c r="D176" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="E176" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="F176" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -15015,22 +15254,22 @@
         <v>934</v>
       </c>
       <c r="C177" t="s">
-        <v>213</v>
+        <v>1023</v>
       </c>
       <c r="D177" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="E177" t="s">
-        <v>106</v>
+        <v>1026</v>
       </c>
       <c r="F177" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -15041,22 +15280,22 @@
         <v>934</v>
       </c>
       <c r="C178" t="s">
-        <v>1039</v>
+        <v>213</v>
       </c>
       <c r="D178" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="E178" t="s">
-        <v>1042</v>
+        <v>106</v>
       </c>
       <c r="F178" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -15067,22 +15306,22 @@
         <v>934</v>
       </c>
       <c r="C179" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="D179" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="E179" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="F179" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -15093,22 +15332,22 @@
         <v>934</v>
       </c>
       <c r="C180" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="D180" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="E180" t="s">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="F180" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -15119,22 +15358,22 @@
         <v>934</v>
       </c>
       <c r="C181" t="s">
-        <v>1082</v>
+        <v>1057</v>
       </c>
       <c r="D181" t="s">
-        <v>1083</v>
+        <v>1058</v>
       </c>
       <c r="E181" t="s">
-        <v>1085</v>
+        <v>16</v>
       </c>
       <c r="F181" t="s">
-        <v>959</v>
+        <v>1060</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>1086</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -15142,25 +15381,25 @@
         <v>153</v>
       </c>
       <c r="B182" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C182" t="s">
-        <v>271</v>
+        <v>1082</v>
       </c>
       <c r="D182" t="s">
-        <v>1104</v>
+        <v>1083</v>
       </c>
       <c r="E182" t="s">
-        <v>1106</v>
+        <v>1085</v>
       </c>
       <c r="F182" t="s">
-        <v>1107</v>
+        <v>959</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -15171,22 +15410,22 @@
         <v>1087</v>
       </c>
       <c r="C183" t="s">
-        <v>1112</v>
+        <v>271</v>
       </c>
       <c r="D183" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="E183" t="s">
-        <v>25</v>
+        <v>1106</v>
       </c>
       <c r="F183" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -15197,22 +15436,22 @@
         <v>1087</v>
       </c>
       <c r="C184" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="D184" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="E184" t="s">
-        <v>1123</v>
+        <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -15223,22 +15462,22 @@
         <v>1087</v>
       </c>
       <c r="C185" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
       <c r="D185" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="E185" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
       <c r="F185" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -15246,25 +15485,25 @@
         <v>157</v>
       </c>
       <c r="B186" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C186" t="s">
-        <v>1172</v>
+        <v>1129</v>
       </c>
       <c r="D186" t="s">
-        <v>122</v>
+        <v>1130</v>
       </c>
       <c r="E186" t="s">
-        <v>1174</v>
+        <v>1132</v>
       </c>
       <c r="F186" t="s">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="G186">
         <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>1176</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -15275,13 +15514,13 @@
         <v>1171</v>
       </c>
       <c r="C187" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D187" t="s">
-        <v>1179</v>
+        <v>122</v>
       </c>
       <c r="E187" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="F187" t="s">
         <v>1175</v>
@@ -15290,7 +15529,7 @@
         <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -15301,13 +15540,13 @@
         <v>1171</v>
       </c>
       <c r="C188" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D188" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="E188" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="F188" t="s">
         <v>1175</v>
@@ -15316,7 +15555,7 @@
         <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -15324,25 +15563,25 @@
         <v>160</v>
       </c>
       <c r="B189" t="s">
-        <v>1210</v>
+        <v>1171</v>
       </c>
       <c r="C189" t="s">
-        <v>1211</v>
+        <v>1184</v>
       </c>
       <c r="D189" t="s">
-        <v>89</v>
+        <v>1185</v>
       </c>
       <c r="E189" t="s">
-        <v>1213</v>
+        <v>1187</v>
       </c>
       <c r="F189" t="s">
-        <v>1214</v>
+        <v>1175</v>
       </c>
       <c r="G189">
         <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>1215</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -15350,25 +15589,25 @@
         <v>161</v>
       </c>
       <c r="B190" t="s">
-        <v>1227</v>
+        <v>1210</v>
       </c>
       <c r="C190" t="s">
-        <v>1247</v>
+        <v>1211</v>
       </c>
       <c r="D190" t="s">
-        <v>1248</v>
+        <v>89</v>
       </c>
       <c r="E190" t="s">
-        <v>66</v>
+        <v>1213</v>
       </c>
       <c r="F190" t="s">
-        <v>604</v>
+        <v>1214</v>
       </c>
       <c r="G190">
         <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>1250</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -15379,22 +15618,22 @@
         <v>1227</v>
       </c>
       <c r="C191" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="D191" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="E191" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F191" t="s">
-        <v>1257</v>
+        <v>604</v>
       </c>
       <c r="G191">
         <v>8</v>
       </c>
       <c r="H191" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -15405,13 +15644,13 @@
         <v>1227</v>
       </c>
       <c r="C192" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="D192" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="E192" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F192" t="s">
         <v>1257</v>
@@ -15420,7 +15659,7 @@
         <v>8</v>
       </c>
       <c r="H192" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -15428,25 +15667,25 @@
         <v>164</v>
       </c>
       <c r="B193" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="C193" t="s">
-        <v>271</v>
+        <v>1260</v>
       </c>
       <c r="D193" t="s">
-        <v>272</v>
+        <v>1261</v>
       </c>
       <c r="E193" t="s">
         <v>75</v>
       </c>
       <c r="F193" t="s">
-        <v>274</v>
+        <v>1257</v>
       </c>
       <c r="G193">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H193" t="s">
-        <v>275</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -15454,25 +15693,25 @@
         <v>165</v>
       </c>
       <c r="B194" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="C194" t="s">
-        <v>681</v>
+        <v>950</v>
       </c>
       <c r="D194" t="s">
-        <v>682</v>
+        <v>463</v>
       </c>
       <c r="E194" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F194" t="s">
-        <v>684</v>
+        <v>438</v>
       </c>
       <c r="G194">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H194" t="s">
-        <v>685</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -15480,25 +15719,25 @@
         <v>166</v>
       </c>
       <c r="B195" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="C195" t="s">
-        <v>689</v>
+        <v>219</v>
       </c>
       <c r="D195" t="s">
-        <v>690</v>
+        <v>1285</v>
       </c>
       <c r="E195" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F195" t="s">
-        <v>692</v>
+        <v>1287</v>
       </c>
       <c r="G195">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H195" t="s">
-        <v>693</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -15506,25 +15745,25 @@
         <v>167</v>
       </c>
       <c r="B196" t="s">
-        <v>697</v>
+        <v>1271</v>
       </c>
       <c r="C196" t="s">
-        <v>767</v>
+        <v>1292</v>
       </c>
       <c r="D196" t="s">
-        <v>768</v>
+        <v>1293</v>
       </c>
       <c r="E196" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F196" t="s">
-        <v>770</v>
+        <v>1295</v>
       </c>
       <c r="G196">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H196" t="s">
-        <v>771</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15532,25 +15771,25 @@
         <v>168</v>
       </c>
       <c r="B197" t="s">
-        <v>845</v>
+        <v>159</v>
       </c>
       <c r="C197" t="s">
-        <v>927</v>
+        <v>271</v>
       </c>
       <c r="D197" t="s">
-        <v>585</v>
+        <v>272</v>
       </c>
       <c r="E197" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F197" t="s">
-        <v>929</v>
+        <v>274</v>
       </c>
       <c r="G197">
         <v>7</v>
       </c>
       <c r="H197" t="s">
-        <v>930</v>
+        <v>275</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -15558,24 +15797,128 @@
         <v>169</v>
       </c>
       <c r="B198" t="s">
-        <v>1219</v>
+        <v>591</v>
       </c>
       <c r="C198" t="s">
-        <v>1220</v>
+        <v>681</v>
       </c>
       <c r="D198" t="s">
-        <v>1221</v>
+        <v>682</v>
       </c>
       <c r="E198" t="s">
-        <v>1223</v>
+        <v>25</v>
       </c>
       <c r="F198" t="s">
-        <v>1224</v>
+        <v>684</v>
       </c>
       <c r="G198">
         <v>7</v>
       </c>
       <c r="H198" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>170</v>
+      </c>
+      <c r="B199" t="s">
+        <v>591</v>
+      </c>
+      <c r="C199" t="s">
+        <v>689</v>
+      </c>
+      <c r="D199" t="s">
+        <v>690</v>
+      </c>
+      <c r="E199" t="s">
+        <v>66</v>
+      </c>
+      <c r="F199" t="s">
+        <v>692</v>
+      </c>
+      <c r="G199">
+        <v>7</v>
+      </c>
+      <c r="H199" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>171</v>
+      </c>
+      <c r="B200" t="s">
+        <v>697</v>
+      </c>
+      <c r="C200" t="s">
+        <v>767</v>
+      </c>
+      <c r="D200" t="s">
+        <v>768</v>
+      </c>
+      <c r="E200" t="s">
+        <v>25</v>
+      </c>
+      <c r="F200" t="s">
+        <v>770</v>
+      </c>
+      <c r="G200">
+        <v>7</v>
+      </c>
+      <c r="H200" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>172</v>
+      </c>
+      <c r="B201" t="s">
+        <v>845</v>
+      </c>
+      <c r="C201" t="s">
+        <v>927</v>
+      </c>
+      <c r="D201" t="s">
+        <v>585</v>
+      </c>
+      <c r="E201" t="s">
+        <v>25</v>
+      </c>
+      <c r="F201" t="s">
+        <v>929</v>
+      </c>
+      <c r="G201">
+        <v>7</v>
+      </c>
+      <c r="H201" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>173</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E202" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G202">
+        <v>7</v>
+      </c>
+      <c r="H202" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -15592,7 +15935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15609,10 +15952,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1279</v>
+        <v>1308</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1280</v>
+        <v>1309</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -15639,12 +15982,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1281</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -15679,7 +16022,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -15714,7 +16057,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -15749,7 +16092,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -15784,7 +16127,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -15819,7 +16162,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -15854,7 +16197,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -15889,7 +16232,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -15924,7 +16267,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -15959,7 +16302,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -15994,7 +16337,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -16029,7 +16372,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -16064,7 +16407,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -16099,7 +16442,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -16134,7 +16477,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -16169,7 +16512,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -16204,7 +16547,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -16239,7 +16582,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B19">
         <v>91</v>
@@ -16274,7 +16617,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B20">
         <v>91</v>
@@ -16309,7 +16652,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -16344,7 +16687,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -16379,7 +16722,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -16414,7 +16757,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -16449,7 +16792,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -16484,7 +16827,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B26">
         <v>90</v>
@@ -16519,7 +16862,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -16554,7 +16897,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -16589,7 +16932,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -16624,7 +16967,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -16659,7 +17002,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -16694,7 +17037,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -16729,7 +17072,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -16764,7 +17107,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B34">
         <v>89</v>
@@ -16799,7 +17142,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B35">
         <v>89</v>
@@ -16834,427 +17177,427 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B36">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H36" t="s">
         <v>1282</v>
       </c>
-      <c r="B36">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" t="s">
-        <v>36</v>
-      </c>
       <c r="I36" t="s">
-        <v>37</v>
+        <v>1283</v>
       </c>
       <c r="J36" t="s">
-        <v>38</v>
+        <v>1284</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B37">
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="H37" t="s">
         <v>36</v>
       </c>
       <c r="I37" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="J37" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K37" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B38">
         <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
-        <v>387</v>
+        <v>201</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="H38" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s">
-        <v>392</v>
+        <v>205</v>
       </c>
       <c r="J38" t="s">
-        <v>393</v>
+        <v>206</v>
       </c>
       <c r="K38" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B39">
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="E39" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="H39" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="I39" t="s">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="K39" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B40">
         <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D40" t="s">
-        <v>698</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>699</v>
+        <v>449</v>
       </c>
       <c r="F40" t="s">
-        <v>701</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>704</v>
+        <v>452</v>
       </c>
       <c r="I40" t="s">
-        <v>705</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s">
-        <v>706</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B41">
         <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D41" t="s">
-        <v>837</v>
+        <v>698</v>
       </c>
       <c r="E41" t="s">
-        <v>610</v>
+        <v>699</v>
       </c>
       <c r="F41" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="G41" t="s">
-        <v>840</v>
+        <v>702</v>
       </c>
       <c r="H41" t="s">
-        <v>842</v>
+        <v>704</v>
       </c>
       <c r="I41" t="s">
-        <v>843</v>
+        <v>705</v>
       </c>
       <c r="J41" t="s">
-        <v>844</v>
+        <v>706</v>
       </c>
       <c r="K41" t="s">
-        <v>838</v>
+        <v>700</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B42">
         <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D42" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="E42" t="s">
-        <v>856</v>
+        <v>610</v>
       </c>
       <c r="F42" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="G42" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="H42" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="I42" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="J42" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="K42" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B43">
         <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D43" t="s">
-        <v>643</v>
+        <v>855</v>
       </c>
       <c r="E43" t="s">
-        <v>957</v>
+        <v>856</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>858</v>
       </c>
       <c r="G43" t="s">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="H43" t="s">
-        <v>961</v>
+        <v>861</v>
       </c>
       <c r="I43" t="s">
-        <v>962</v>
+        <v>862</v>
       </c>
       <c r="J43" t="s">
-        <v>963</v>
+        <v>863</v>
       </c>
       <c r="K43" t="s">
-        <v>958</v>
+        <v>857</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B44">
         <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D44" t="s">
-        <v>1228</v>
+        <v>643</v>
       </c>
       <c r="E44" t="s">
-        <v>1229</v>
+        <v>957</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>1231</v>
+        <v>959</v>
       </c>
       <c r="H44" t="s">
-        <v>1233</v>
+        <v>961</v>
       </c>
       <c r="I44" t="s">
-        <v>1234</v>
+        <v>962</v>
       </c>
       <c r="J44" t="s">
-        <v>1235</v>
+        <v>963</v>
       </c>
       <c r="K44" t="s">
-        <v>1230</v>
+        <v>958</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B45">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>1228</v>
       </c>
       <c r="E45" t="s">
-        <v>185</v>
+        <v>1229</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>131</v>
+        <v>1231</v>
       </c>
       <c r="H45" t="s">
-        <v>188</v>
+        <v>1233</v>
       </c>
       <c r="I45" t="s">
-        <v>189</v>
+        <v>1234</v>
       </c>
       <c r="J45" t="s">
-        <v>190</v>
+        <v>1235</v>
       </c>
       <c r="K45" t="s">
-        <v>186</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B46">
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D46" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="F46" t="s">
-        <v>356</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
-        <v>357</v>
+        <v>131</v>
       </c>
       <c r="H46" t="s">
-        <v>359</v>
+        <v>188</v>
       </c>
       <c r="I46" t="s">
-        <v>360</v>
+        <v>189</v>
       </c>
       <c r="J46" t="s">
-        <v>361</v>
+        <v>190</v>
       </c>
       <c r="K46" t="s">
-        <v>355</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B47">
         <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>353</v>
       </c>
       <c r="E47" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="G47" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="H47" t="s">
-        <v>456</v>
+        <v>359</v>
       </c>
       <c r="I47" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="K47" t="s">
-        <v>454</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B48">
         <v>87</v>
@@ -17266,7 +17609,7 @@
         <v>63</v>
       </c>
       <c r="E48" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F48" t="s">
         <v>66</v>
@@ -17284,327 +17627,327 @@
         <v>79</v>
       </c>
       <c r="K48" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B49">
         <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D49" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="F49" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="G49" t="s">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="H49" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="I49" t="s">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="J49" t="s">
-        <v>515</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B50">
         <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D50" t="s">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>510</v>
       </c>
       <c r="G50" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H50" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="I50" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="J50" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="K50" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B51">
         <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>845</v>
+        <v>556</v>
       </c>
       <c r="D51" t="s">
-        <v>864</v>
+        <v>570</v>
       </c>
       <c r="E51" t="s">
-        <v>865</v>
+        <v>571</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="H51" t="s">
-        <v>869</v>
+        <v>575</v>
       </c>
       <c r="I51" t="s">
-        <v>870</v>
+        <v>576</v>
       </c>
       <c r="J51" t="s">
-        <v>871</v>
+        <v>577</v>
       </c>
       <c r="K51" t="s">
-        <v>866</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B52">
         <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D52" t="s">
-        <v>950</v>
+        <v>864</v>
       </c>
       <c r="E52" t="s">
-        <v>996</v>
+        <v>865</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>438</v>
+        <v>867</v>
       </c>
       <c r="H52" t="s">
-        <v>999</v>
+        <v>869</v>
       </c>
       <c r="I52" t="s">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J52" t="s">
-        <v>1001</v>
+        <v>871</v>
       </c>
       <c r="K52" t="s">
-        <v>997</v>
+        <v>866</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B53">
         <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D53" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="E53" t="s">
-        <v>1097</v>
+        <v>996</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G53" t="s">
-        <v>1099</v>
+        <v>438</v>
       </c>
       <c r="H53" t="s">
-        <v>1101</v>
+        <v>999</v>
       </c>
       <c r="I53" t="s">
-        <v>1102</v>
+        <v>1000</v>
       </c>
       <c r="J53" t="s">
-        <v>1103</v>
+        <v>1001</v>
       </c>
       <c r="K53" t="s">
-        <v>1098</v>
+        <v>997</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B54">
         <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D54" t="s">
-        <v>1156</v>
+        <v>964</v>
       </c>
       <c r="E54" t="s">
-        <v>1157</v>
+        <v>1097</v>
       </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>1159</v>
+        <v>1099</v>
       </c>
       <c r="H54" t="s">
-        <v>1161</v>
+        <v>1101</v>
       </c>
       <c r="I54" t="s">
-        <v>1162</v>
+        <v>1102</v>
       </c>
       <c r="J54" t="s">
-        <v>1163</v>
+        <v>1103</v>
       </c>
       <c r="K54" t="s">
-        <v>1158</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B55">
         <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>1227</v>
+        <v>1155</v>
       </c>
       <c r="D55" t="s">
-        <v>1236</v>
+        <v>1156</v>
       </c>
       <c r="E55" t="s">
-        <v>610</v>
+        <v>1157</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G55" t="s">
-        <v>604</v>
+        <v>1159</v>
       </c>
       <c r="H55" t="s">
-        <v>1239</v>
+        <v>1161</v>
       </c>
       <c r="I55" t="s">
-        <v>1240</v>
+        <v>1162</v>
       </c>
       <c r="J55" t="s">
-        <v>1241</v>
+        <v>1163</v>
       </c>
       <c r="K55" t="s">
-        <v>1237</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B56">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C56" t="s">
-        <v>284</v>
+        <v>1227</v>
       </c>
       <c r="D56" t="s">
-        <v>369</v>
+        <v>1236</v>
       </c>
       <c r="E56" t="s">
-        <v>370</v>
+        <v>610</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>372</v>
+        <v>604</v>
       </c>
       <c r="H56" t="s">
-        <v>374</v>
+        <v>1239</v>
       </c>
       <c r="I56" t="s">
-        <v>375</v>
+        <v>1240</v>
       </c>
       <c r="J56" t="s">
-        <v>376</v>
+        <v>1241</v>
       </c>
       <c r="K56" t="s">
-        <v>371</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B57">
         <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="E57" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="H57" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="I57" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="J57" t="s">
-        <v>462</v>
+        <v>376</v>
       </c>
       <c r="K57" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B58">
         <v>86</v>
@@ -17613,138 +17956,138 @@
         <v>402</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="E58" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G58" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="H58" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I58" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J58" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="K58" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B59">
         <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D59" t="s">
-        <v>541</v>
+        <v>322</v>
       </c>
       <c r="E59" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="F59" t="s">
-        <v>544</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="H59" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="I59" t="s">
-        <v>548</v>
+        <v>471</v>
       </c>
       <c r="J59" t="s">
-        <v>549</v>
+        <v>472</v>
       </c>
       <c r="K59" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B60">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="D60" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E60" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>544</v>
       </c>
       <c r="G60" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="H60" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="I60" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="J60" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="K60" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B61">
         <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="D61" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
       <c r="E61" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="H61" t="s">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="I61" t="s">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="J61" t="s">
-        <v>615</v>
+        <v>563</v>
       </c>
       <c r="K61" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -17753,33 +18096,33 @@
         <v>591</v>
       </c>
       <c r="D62" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="E62" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="H62" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="I62" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="J62" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="K62" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B63">
         <v>86</v>
@@ -17788,103 +18131,103 @@
         <v>591</v>
       </c>
       <c r="D63" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E63" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G63" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H63" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="I63" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J63" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="K63" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B64">
         <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D64" t="s">
-        <v>829</v>
+        <v>635</v>
       </c>
       <c r="E64" t="s">
-        <v>830</v>
+        <v>636</v>
       </c>
       <c r="F64" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>832</v>
+        <v>638</v>
       </c>
       <c r="H64" t="s">
-        <v>834</v>
+        <v>640</v>
       </c>
       <c r="I64" t="s">
-        <v>835</v>
+        <v>641</v>
       </c>
       <c r="J64" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="K64" t="s">
-        <v>831</v>
+        <v>637</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B65">
         <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D65" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E65" t="s">
-        <v>873</v>
+        <v>830</v>
       </c>
       <c r="F65" t="s">
-        <v>380</v>
+        <v>785</v>
       </c>
       <c r="G65" t="s">
-        <v>875</v>
+        <v>832</v>
       </c>
       <c r="H65" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
       <c r="I65" t="s">
-        <v>878</v>
+        <v>835</v>
       </c>
       <c r="J65" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="K65" t="s">
-        <v>874</v>
+        <v>831</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B66">
         <v>86</v>
@@ -17893,68 +18236,68 @@
         <v>845</v>
       </c>
       <c r="D66" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="E66" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="G66" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="H66" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="I66" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J66" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K66" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B67">
         <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D67" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="E67" t="s">
-        <v>974</v>
+        <v>881</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>468</v>
+        <v>883</v>
       </c>
       <c r="H67" t="s">
-        <v>977</v>
+        <v>885</v>
       </c>
       <c r="I67" t="s">
-        <v>978</v>
+        <v>886</v>
       </c>
       <c r="J67" t="s">
-        <v>979</v>
+        <v>887</v>
       </c>
       <c r="K67" t="s">
-        <v>975</v>
+        <v>882</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B68">
         <v>86</v>
@@ -17963,33 +18306,33 @@
         <v>934</v>
       </c>
       <c r="D68" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E68" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="F68" t="s">
-        <v>983</v>
+        <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>984</v>
+        <v>468</v>
       </c>
       <c r="H68" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="I68" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J68" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="K68" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B69">
         <v>86</v>
@@ -17998,68 +18341,68 @@
         <v>934</v>
       </c>
       <c r="D69" t="s">
-        <v>1073</v>
+        <v>980</v>
       </c>
       <c r="E69" t="s">
-        <v>1074</v>
+        <v>981</v>
       </c>
       <c r="F69" t="s">
-        <v>1076</v>
+        <v>983</v>
       </c>
       <c r="G69" t="s">
-        <v>1077</v>
+        <v>984</v>
       </c>
       <c r="H69" t="s">
-        <v>1079</v>
+        <v>986</v>
       </c>
       <c r="I69" t="s">
-        <v>1080</v>
+        <v>987</v>
       </c>
       <c r="J69" t="s">
-        <v>1081</v>
+        <v>988</v>
       </c>
       <c r="K69" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B70">
         <v>86</v>
       </c>
       <c r="C70" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D70" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E70" t="s">
-        <v>1089</v>
+        <v>1074</v>
       </c>
       <c r="F70" t="s">
-        <v>1091</v>
+        <v>1076</v>
       </c>
       <c r="G70" t="s">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="H70" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="I70" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="J70" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="K70" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B71">
         <v>86</v>
@@ -18068,103 +18411,103 @@
         <v>1087</v>
       </c>
       <c r="D71" t="s">
-        <v>1146</v>
+        <v>1088</v>
       </c>
       <c r="E71" t="s">
-        <v>1147</v>
+        <v>1089</v>
       </c>
       <c r="F71" t="s">
-        <v>1149</v>
+        <v>1091</v>
       </c>
       <c r="G71" t="s">
-        <v>1150</v>
+        <v>1092</v>
       </c>
       <c r="H71" t="s">
-        <v>1152</v>
+        <v>1094</v>
       </c>
       <c r="I71" t="s">
-        <v>1153</v>
+        <v>1095</v>
       </c>
       <c r="J71" t="s">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="K71" t="s">
-        <v>1148</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B72">
         <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>1155</v>
+        <v>1087</v>
       </c>
       <c r="D72" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="E72" t="s">
-        <v>610</v>
+        <v>1147</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>1149</v>
       </c>
       <c r="G72" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
       <c r="H72" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
       <c r="I72" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="J72" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="K72" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B73">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>1155</v>
       </c>
       <c r="D73" t="s">
-        <v>55</v>
+        <v>1164</v>
       </c>
       <c r="E73" t="s">
-        <v>56</v>
+        <v>610</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>58</v>
+        <v>1166</v>
       </c>
       <c r="H73" t="s">
-        <v>60</v>
+        <v>1168</v>
       </c>
       <c r="I73" t="s">
-        <v>61</v>
+        <v>1169</v>
       </c>
       <c r="J73" t="s">
-        <v>62</v>
+        <v>1170</v>
       </c>
       <c r="K73" t="s">
-        <v>57</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B74">
         <v>85</v>
@@ -18173,173 +18516,173 @@
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="E74" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H74" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I74" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="J74" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K74" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B75">
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="E75" t="s">
-        <v>308</v>
+        <v>89</v>
       </c>
       <c r="F75" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G75" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
       <c r="H75" t="s">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="I75" t="s">
-        <v>313</v>
+        <v>134</v>
       </c>
       <c r="J75" t="s">
-        <v>314</v>
+        <v>135</v>
       </c>
       <c r="K75" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B76">
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E76" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G76" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="H76" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="I76" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="J76" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
       <c r="K76" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B77">
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D77" t="s">
-        <v>474</v>
+        <v>55</v>
       </c>
       <c r="E77" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="F77" t="s">
-        <v>477</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="H77" t="s">
-        <v>480</v>
+        <v>407</v>
       </c>
       <c r="I77" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="J77" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="K77" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B78">
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D78" t="s">
-        <v>774</v>
+        <v>474</v>
       </c>
       <c r="E78" t="s">
-        <v>783</v>
+        <v>475</v>
       </c>
       <c r="F78" t="s">
-        <v>785</v>
+        <v>477</v>
       </c>
       <c r="G78" t="s">
-        <v>786</v>
+        <v>478</v>
       </c>
       <c r="H78" t="s">
-        <v>788</v>
+        <v>480</v>
       </c>
       <c r="I78" t="s">
-        <v>789</v>
+        <v>481</v>
       </c>
       <c r="J78" t="s">
-        <v>790</v>
+        <v>482</v>
       </c>
       <c r="K78" t="s">
-        <v>784</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B79">
         <v>85</v>
@@ -18348,33 +18691,33 @@
         <v>773</v>
       </c>
       <c r="D79" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="E79" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F79" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="G79" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H79" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="I79" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="J79" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K79" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B80">
         <v>85</v>
@@ -18383,68 +18726,68 @@
         <v>773</v>
       </c>
       <c r="D80" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="E80" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F80" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G80" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="H80" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="I80" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J80" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="K80" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B81">
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D81" t="s">
-        <v>989</v>
+        <v>821</v>
       </c>
       <c r="E81" t="s">
-        <v>990</v>
+        <v>822</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>777</v>
       </c>
       <c r="G81" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="H81" t="s">
-        <v>993</v>
+        <v>826</v>
       </c>
       <c r="I81" t="s">
-        <v>994</v>
+        <v>827</v>
       </c>
       <c r="J81" t="s">
-        <v>995</v>
+        <v>828</v>
       </c>
       <c r="K81" t="s">
-        <v>991</v>
+        <v>823</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B82">
         <v>85</v>
@@ -18453,243 +18796,243 @@
         <v>934</v>
       </c>
       <c r="D82" t="s">
-        <v>1065</v>
+        <v>989</v>
       </c>
       <c r="E82" t="s">
-        <v>1066</v>
+        <v>990</v>
       </c>
       <c r="F82" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="H82" t="s">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="I82" t="s">
-        <v>1071</v>
+        <v>994</v>
       </c>
       <c r="J82" t="s">
-        <v>1072</v>
+        <v>995</v>
       </c>
       <c r="K82" t="s">
-        <v>1067</v>
+        <v>991</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B83">
         <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D83" t="s">
-        <v>1242</v>
+        <v>1065</v>
       </c>
       <c r="E83" t="s">
-        <v>610</v>
+        <v>1066</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="G83" t="s">
-        <v>604</v>
+        <v>1068</v>
       </c>
       <c r="H83" t="s">
-        <v>312</v>
+        <v>1070</v>
       </c>
       <c r="I83" t="s">
-        <v>1245</v>
+        <v>1071</v>
       </c>
       <c r="J83" t="s">
-        <v>1246</v>
+        <v>1072</v>
       </c>
       <c r="K83" t="s">
-        <v>1243</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B84">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>1227</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>1242</v>
       </c>
       <c r="E84" t="s">
-        <v>145</v>
+        <v>610</v>
       </c>
       <c r="F84" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>148</v>
+        <v>604</v>
       </c>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="I84" t="s">
-        <v>151</v>
+        <v>1245</v>
       </c>
       <c r="J84" t="s">
-        <v>152</v>
+        <v>1246</v>
       </c>
       <c r="K84" t="s">
-        <v>146</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B85">
         <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
         <v>144</v>
       </c>
       <c r="E85" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="F85" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G85" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="H85" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I85" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="J85" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="K85" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D86" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="E86" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="F86" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="G86" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="H86" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="I86" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="J86" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="K86" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B87">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="D87" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="E87" t="s">
-        <v>122</v>
+        <v>411</v>
       </c>
       <c r="F87" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="G87" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="H87" t="s">
-        <v>488</v>
+        <v>415</v>
       </c>
       <c r="I87" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J87" t="s">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="K87" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B88">
         <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D88" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="E88" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>485</v>
       </c>
       <c r="G88" t="s">
-        <v>604</v>
+        <v>486</v>
       </c>
       <c r="H88" t="s">
-        <v>718</v>
+        <v>488</v>
       </c>
       <c r="I88" t="s">
-        <v>719</v>
+        <v>489</v>
       </c>
       <c r="J88" t="s">
-        <v>720</v>
+        <v>490</v>
       </c>
       <c r="K88" t="s">
-        <v>716</v>
+        <v>484</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B89">
         <v>84</v>
@@ -18698,33 +19041,33 @@
         <v>697</v>
       </c>
       <c r="D89" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E89" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F89" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="H89" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I89" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="J89" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K89" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B90">
         <v>84</v>
@@ -18733,138 +19076,138 @@
         <v>697</v>
       </c>
       <c r="D90" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E90" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="F90" t="s">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="G90" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H90" t="s">
         <v>726</v>
       </c>
       <c r="I90" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="J90" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="K90" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B91">
         <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D91" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="E91" t="s">
-        <v>610</v>
+        <v>730</v>
       </c>
       <c r="F91" t="s">
-        <v>793</v>
+        <v>535</v>
       </c>
       <c r="G91" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="H91" t="s">
-        <v>796</v>
+        <v>726</v>
       </c>
       <c r="I91" t="s">
-        <v>797</v>
+        <v>734</v>
       </c>
       <c r="J91" t="s">
-        <v>798</v>
+        <v>735</v>
       </c>
       <c r="K91" t="s">
-        <v>792</v>
+        <v>731</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B92">
         <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="D92" t="s">
-        <v>896</v>
+        <v>791</v>
       </c>
       <c r="E92" t="s">
-        <v>897</v>
+        <v>610</v>
       </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="G92" t="s">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H92" t="s">
-        <v>901</v>
+        <v>796</v>
       </c>
       <c r="I92" t="s">
-        <v>902</v>
+        <v>797</v>
       </c>
       <c r="J92" t="s">
-        <v>903</v>
+        <v>798</v>
       </c>
       <c r="K92" t="s">
-        <v>898</v>
+        <v>792</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B93">
         <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D93" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="E93" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="F93" t="s">
-        <v>967</v>
+        <v>25</v>
       </c>
       <c r="G93" t="s">
-        <v>968</v>
+        <v>899</v>
       </c>
       <c r="H93" t="s">
-        <v>970</v>
+        <v>901</v>
       </c>
       <c r="I93" t="s">
-        <v>971</v>
+        <v>902</v>
       </c>
       <c r="J93" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="K93" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B94">
         <v>84</v>
@@ -18873,33 +19216,33 @@
         <v>934</v>
       </c>
       <c r="D94" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="E94" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="F94" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="G94" t="s">
-        <v>438</v>
+        <v>968</v>
       </c>
       <c r="H94" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="I94" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="J94" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="K94" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B95">
         <v>84</v>
@@ -18908,33 +19251,33 @@
         <v>934</v>
       </c>
       <c r="D95" t="s">
-        <v>213</v>
+        <v>950</v>
       </c>
       <c r="E95" t="s">
-        <v>1032</v>
+        <v>1002</v>
       </c>
       <c r="F95" t="s">
-        <v>106</v>
+        <v>1004</v>
       </c>
       <c r="G95" t="s">
-        <v>1034</v>
+        <v>438</v>
       </c>
       <c r="H95" t="s">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="I95" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="J95" t="s">
-        <v>1038</v>
+        <v>1008</v>
       </c>
       <c r="K95" t="s">
-        <v>1033</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B96">
         <v>84</v>
@@ -18943,937 +19286,1077 @@
         <v>934</v>
       </c>
       <c r="D96" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="E96" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="F96" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G96" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="H96" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="I96" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="J96" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="K96" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B97">
         <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>1057</v>
       </c>
       <c r="E97" t="s">
-        <v>1104</v>
+        <v>1058</v>
       </c>
       <c r="F97" t="s">
-        <v>1106</v>
+        <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="H97" t="s">
-        <v>1109</v>
+        <v>1062</v>
       </c>
       <c r="I97" t="s">
-        <v>1110</v>
+        <v>1063</v>
       </c>
       <c r="J97" t="s">
-        <v>1111</v>
+        <v>1064</v>
       </c>
       <c r="K97" t="s">
-        <v>1105</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B98">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C98" t="s">
-        <v>1200</v>
+        <v>1087</v>
       </c>
       <c r="D98" t="s">
-        <v>1201</v>
+        <v>271</v>
       </c>
       <c r="E98" t="s">
-        <v>1202</v>
+        <v>1104</v>
       </c>
       <c r="F98" t="s">
-        <v>1204</v>
+        <v>1106</v>
       </c>
       <c r="G98" t="s">
-        <v>1205</v>
+        <v>1107</v>
       </c>
       <c r="H98" t="s">
-        <v>1207</v>
+        <v>1109</v>
       </c>
       <c r="I98" t="s">
-        <v>1208</v>
+        <v>1110</v>
       </c>
       <c r="J98" t="s">
-        <v>1209</v>
+        <v>1111</v>
       </c>
       <c r="K98" t="s">
-        <v>1203</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B99">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>284</v>
+        <v>1271</v>
       </c>
       <c r="D99" t="s">
-        <v>353</v>
+        <v>950</v>
       </c>
       <c r="E99" t="s">
-        <v>362</v>
+        <v>463</v>
       </c>
       <c r="F99" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
       <c r="G99" t="s">
-        <v>364</v>
+        <v>438</v>
       </c>
       <c r="H99" t="s">
-        <v>366</v>
+        <v>1274</v>
       </c>
       <c r="I99" t="s">
-        <v>367</v>
+        <v>1275</v>
       </c>
       <c r="J99" t="s">
-        <v>368</v>
+        <v>1276</v>
       </c>
       <c r="K99" t="s">
-        <v>363</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B100">
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>473</v>
+        <v>1200</v>
       </c>
       <c r="D100" t="s">
-        <v>491</v>
+        <v>1201</v>
       </c>
       <c r="E100" t="s">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>1204</v>
       </c>
       <c r="G100" t="s">
-        <v>494</v>
+        <v>1205</v>
       </c>
       <c r="H100" t="s">
-        <v>496</v>
+        <v>1207</v>
       </c>
       <c r="I100" t="s">
-        <v>497</v>
+        <v>1208</v>
       </c>
       <c r="J100" t="s">
-        <v>498</v>
+        <v>1209</v>
       </c>
       <c r="K100" t="s">
-        <v>493</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B101">
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D101" t="s">
-        <v>532</v>
+        <v>353</v>
       </c>
       <c r="E101" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F101" t="s">
-        <v>535</v>
+        <v>356</v>
       </c>
       <c r="G101" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="H101" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="I101" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
       <c r="J101" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="K101" t="s">
-        <v>534</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B102">
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D102" t="s">
-        <v>643</v>
+        <v>491</v>
       </c>
       <c r="E102" t="s">
-        <v>644</v>
+        <v>492</v>
       </c>
       <c r="F102" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s">
-        <v>618</v>
+        <v>494</v>
       </c>
       <c r="H102" t="s">
-        <v>647</v>
+        <v>496</v>
       </c>
       <c r="I102" t="s">
-        <v>648</v>
+        <v>497</v>
       </c>
       <c r="J102" t="s">
-        <v>649</v>
+        <v>498</v>
       </c>
       <c r="K102" t="s">
-        <v>645</v>
+        <v>493</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B103">
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D103" t="s">
-        <v>736</v>
+        <v>532</v>
       </c>
       <c r="E103" t="s">
-        <v>737</v>
+        <v>533</v>
       </c>
       <c r="F103" t="s">
-        <v>739</v>
+        <v>535</v>
       </c>
       <c r="G103" t="s">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="H103" t="s">
-        <v>741</v>
+        <v>538</v>
       </c>
       <c r="I103" t="s">
-        <v>742</v>
+        <v>539</v>
       </c>
       <c r="J103" t="s">
-        <v>743</v>
+        <v>540</v>
       </c>
       <c r="K103" t="s">
-        <v>738</v>
+        <v>534</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B104">
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>773</v>
+        <v>591</v>
       </c>
       <c r="D104" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="E104" t="s">
-        <v>808</v>
+        <v>644</v>
       </c>
       <c r="F104" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>811</v>
+        <v>618</v>
       </c>
       <c r="H104" t="s">
-        <v>813</v>
+        <v>647</v>
       </c>
       <c r="I104" t="s">
-        <v>814</v>
+        <v>648</v>
       </c>
       <c r="J104" t="s">
-        <v>815</v>
+        <v>649</v>
       </c>
       <c r="K104" t="s">
-        <v>809</v>
+        <v>645</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B105">
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D105" t="s">
-        <v>650</v>
+        <v>736</v>
       </c>
       <c r="E105" t="s">
-        <v>1016</v>
+        <v>737</v>
       </c>
       <c r="F105" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="G105" t="s">
-        <v>1018</v>
+        <v>604</v>
       </c>
       <c r="H105" t="s">
-        <v>1020</v>
+        <v>741</v>
       </c>
       <c r="I105" t="s">
-        <v>1021</v>
+        <v>742</v>
       </c>
       <c r="J105" t="s">
-        <v>1022</v>
+        <v>743</v>
       </c>
       <c r="K105" t="s">
-        <v>1017</v>
+        <v>738</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B106">
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D106" t="s">
-        <v>1048</v>
+        <v>807</v>
       </c>
       <c r="E106" t="s">
-        <v>1049</v>
+        <v>808</v>
       </c>
       <c r="F106" t="s">
-        <v>1051</v>
+        <v>810</v>
       </c>
       <c r="G106" t="s">
-        <v>1052</v>
+        <v>811</v>
       </c>
       <c r="H106" t="s">
-        <v>1054</v>
+        <v>813</v>
       </c>
       <c r="I106" t="s">
-        <v>1055</v>
+        <v>814</v>
       </c>
       <c r="J106" t="s">
-        <v>1056</v>
+        <v>815</v>
       </c>
       <c r="K106" t="s">
-        <v>1050</v>
+        <v>809</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B107">
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D107" t="s">
-        <v>1247</v>
+        <v>650</v>
       </c>
       <c r="E107" t="s">
-        <v>1248</v>
+        <v>1016</v>
       </c>
       <c r="F107" t="s">
         <v>66</v>
       </c>
       <c r="G107" t="s">
-        <v>604</v>
+        <v>1018</v>
       </c>
       <c r="H107" t="s">
-        <v>1251</v>
+        <v>1020</v>
       </c>
       <c r="I107" t="s">
-        <v>1252</v>
+        <v>1021</v>
       </c>
       <c r="J107" t="s">
-        <v>1253</v>
+        <v>1022</v>
       </c>
       <c r="K107" t="s">
-        <v>1249</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B108">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D108" t="s">
-        <v>227</v>
+        <v>1048</v>
       </c>
       <c r="E108" t="s">
-        <v>228</v>
+        <v>1049</v>
       </c>
       <c r="F108" t="s">
-        <v>230</v>
+        <v>1051</v>
       </c>
       <c r="G108" t="s">
-        <v>231</v>
+        <v>1052</v>
       </c>
       <c r="H108" t="s">
-        <v>233</v>
+        <v>1054</v>
       </c>
       <c r="I108" t="s">
-        <v>234</v>
+        <v>1055</v>
       </c>
       <c r="J108" t="s">
-        <v>235</v>
+        <v>1056</v>
       </c>
       <c r="K108" t="s">
-        <v>229</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B109">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D109" t="s">
-        <v>266</v>
+        <v>1247</v>
       </c>
       <c r="E109" t="s">
-        <v>267</v>
+        <v>1248</v>
       </c>
       <c r="F109" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G109" t="s">
-        <v>58</v>
+        <v>604</v>
       </c>
       <c r="H109" t="s">
-        <v>270</v>
+        <v>1251</v>
       </c>
       <c r="I109" t="s">
-        <v>79</v>
+        <v>1252</v>
       </c>
       <c r="J109" t="s">
-        <v>79</v>
+        <v>1253</v>
       </c>
       <c r="K109" t="s">
-        <v>268</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B110">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>284</v>
+        <v>1271</v>
       </c>
       <c r="D110" t="s">
-        <v>338</v>
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>339</v>
+        <v>1285</v>
       </c>
       <c r="F110" t="s">
-        <v>341</v>
+        <v>98</v>
       </c>
       <c r="G110" t="s">
-        <v>342</v>
+        <v>1287</v>
       </c>
       <c r="H110" t="s">
-        <v>344</v>
+        <v>1289</v>
       </c>
       <c r="I110" t="s">
-        <v>345</v>
+        <v>1290</v>
       </c>
       <c r="J110" t="s">
-        <v>346</v>
+        <v>1291</v>
       </c>
       <c r="K110" t="s">
-        <v>340</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B111">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C111" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="D111" t="s">
-        <v>601</v>
+        <v>1292</v>
       </c>
       <c r="E111" t="s">
-        <v>602</v>
+        <v>1293</v>
       </c>
       <c r="F111" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G111" t="s">
-        <v>604</v>
+        <v>1295</v>
       </c>
       <c r="H111" t="s">
-        <v>606</v>
+        <v>1297</v>
       </c>
       <c r="I111" t="s">
-        <v>607</v>
+        <v>1298</v>
       </c>
       <c r="J111" t="s">
-        <v>608</v>
+        <v>1299</v>
       </c>
       <c r="K111" t="s">
-        <v>603</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B112">
         <v>82</v>
       </c>
       <c r="C112" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D112" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="E112" t="s">
-        <v>1009</v>
+        <v>228</v>
       </c>
       <c r="F112" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G112" t="s">
-        <v>1011</v>
+        <v>231</v>
       </c>
       <c r="H112" t="s">
-        <v>1013</v>
+        <v>233</v>
       </c>
       <c r="I112" t="s">
-        <v>1014</v>
+        <v>234</v>
       </c>
       <c r="J112" t="s">
-        <v>1015</v>
+        <v>235</v>
       </c>
       <c r="K112" t="s">
-        <v>1010</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B113">
         <v>82</v>
       </c>
       <c r="C113" t="s">
-        <v>934</v>
+        <v>159</v>
       </c>
       <c r="D113" t="s">
-        <v>1023</v>
+        <v>266</v>
       </c>
       <c r="E113" t="s">
-        <v>1024</v>
+        <v>267</v>
       </c>
       <c r="F113" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G113" t="s">
-        <v>1027</v>
+        <v>58</v>
       </c>
       <c r="H113" t="s">
-        <v>1029</v>
+        <v>270</v>
       </c>
       <c r="I113" t="s">
-        <v>1030</v>
+        <v>79</v>
       </c>
       <c r="J113" t="s">
-        <v>1031</v>
+        <v>79</v>
       </c>
       <c r="K113" t="s">
-        <v>1025</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B114">
         <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>1087</v>
+        <v>284</v>
       </c>
       <c r="D114" t="s">
-        <v>1112</v>
+        <v>338</v>
       </c>
       <c r="E114" t="s">
-        <v>1113</v>
+        <v>339</v>
       </c>
       <c r="F114" t="s">
-        <v>25</v>
+        <v>341</v>
       </c>
       <c r="G114" t="s">
-        <v>1115</v>
+        <v>342</v>
       </c>
       <c r="H114" t="s">
-        <v>1117</v>
+        <v>344</v>
       </c>
       <c r="I114" t="s">
-        <v>1118</v>
+        <v>345</v>
       </c>
       <c r="J114" t="s">
-        <v>1119</v>
+        <v>346</v>
       </c>
       <c r="K114" t="s">
-        <v>1114</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B115">
         <v>82</v>
       </c>
       <c r="C115" t="s">
-        <v>1210</v>
+        <v>591</v>
       </c>
       <c r="D115" t="s">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="E115" t="s">
-        <v>89</v>
+        <v>602</v>
       </c>
       <c r="F115" t="s">
-        <v>1213</v>
+        <v>75</v>
       </c>
       <c r="G115" t="s">
-        <v>1214</v>
+        <v>604</v>
       </c>
       <c r="H115" t="s">
-        <v>1216</v>
+        <v>606</v>
       </c>
       <c r="I115" t="s">
-        <v>1217</v>
+        <v>607</v>
       </c>
       <c r="J115" t="s">
-        <v>1218</v>
+        <v>608</v>
       </c>
       <c r="K115" t="s">
-        <v>1212</v>
+        <v>603</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B116">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D116" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E116" t="s">
-        <v>81</v>
+        <v>1009</v>
       </c>
       <c r="F116" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>83</v>
+        <v>1011</v>
       </c>
       <c r="H116" t="s">
-        <v>85</v>
+        <v>1013</v>
       </c>
       <c r="I116" t="s">
-        <v>86</v>
+        <v>1014</v>
       </c>
       <c r="J116" t="s">
-        <v>87</v>
+        <v>1015</v>
       </c>
       <c r="K116" t="s">
-        <v>82</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B117">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C117" t="s">
-        <v>284</v>
+        <v>934</v>
       </c>
       <c r="D117" t="s">
-        <v>377</v>
+        <v>1023</v>
       </c>
       <c r="E117" t="s">
-        <v>378</v>
+        <v>1024</v>
       </c>
       <c r="F117" t="s">
-        <v>380</v>
+        <v>1026</v>
       </c>
       <c r="G117" t="s">
-        <v>381</v>
+        <v>1027</v>
       </c>
       <c r="H117" t="s">
-        <v>383</v>
+        <v>1029</v>
       </c>
       <c r="I117" t="s">
-        <v>384</v>
+        <v>1030</v>
       </c>
       <c r="J117" t="s">
-        <v>385</v>
+        <v>1031</v>
       </c>
       <c r="K117" t="s">
-        <v>379</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B118">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C118" t="s">
-        <v>473</v>
+        <v>1087</v>
       </c>
       <c r="D118" t="s">
-        <v>499</v>
+        <v>1112</v>
       </c>
       <c r="E118" t="s">
-        <v>500</v>
+        <v>1113</v>
       </c>
       <c r="F118" t="s">
-        <v>502</v>
+        <v>25</v>
       </c>
       <c r="G118" t="s">
-        <v>503</v>
+        <v>1115</v>
       </c>
       <c r="H118" t="s">
-        <v>505</v>
+        <v>1117</v>
       </c>
       <c r="I118" t="s">
-        <v>506</v>
+        <v>1118</v>
       </c>
       <c r="J118" t="s">
-        <v>507</v>
+        <v>1119</v>
       </c>
       <c r="K118" t="s">
-        <v>501</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B119">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C119" t="s">
-        <v>591</v>
+        <v>1210</v>
       </c>
       <c r="D119" t="s">
-        <v>616</v>
+        <v>1211</v>
       </c>
       <c r="E119" t="s">
-        <v>610</v>
+        <v>89</v>
       </c>
       <c r="F119" t="s">
-        <v>16</v>
+        <v>1213</v>
       </c>
       <c r="G119" t="s">
-        <v>618</v>
+        <v>1214</v>
       </c>
       <c r="H119" t="s">
-        <v>620</v>
+        <v>1216</v>
       </c>
       <c r="I119" t="s">
-        <v>621</v>
+        <v>1217</v>
       </c>
       <c r="J119" t="s">
-        <v>622</v>
+        <v>1218</v>
       </c>
       <c r="K119" t="s">
-        <v>617</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B120">
         <v>81</v>
       </c>
       <c r="C120" t="s">
-        <v>845</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>888</v>
+        <v>80</v>
       </c>
       <c r="E120" t="s">
-        <v>889</v>
+        <v>81</v>
       </c>
       <c r="F120" t="s">
         <v>25</v>
       </c>
       <c r="G120" t="s">
-        <v>891</v>
+        <v>83</v>
       </c>
       <c r="H120" t="s">
-        <v>893</v>
+        <v>85</v>
       </c>
       <c r="I120" t="s">
-        <v>894</v>
+        <v>86</v>
       </c>
       <c r="J120" t="s">
-        <v>895</v>
+        <v>87</v>
       </c>
       <c r="K120" t="s">
-        <v>890</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B121">
         <v>81</v>
       </c>
       <c r="C121" t="s">
-        <v>1087</v>
+        <v>284</v>
       </c>
       <c r="D121" t="s">
-        <v>1120</v>
+        <v>377</v>
       </c>
       <c r="E121" t="s">
-        <v>1121</v>
+        <v>378</v>
       </c>
       <c r="F121" t="s">
-        <v>1123</v>
+        <v>380</v>
       </c>
       <c r="G121" t="s">
-        <v>1124</v>
+        <v>381</v>
       </c>
       <c r="H121" t="s">
-        <v>1126</v>
+        <v>383</v>
       </c>
       <c r="I121" t="s">
-        <v>1127</v>
+        <v>384</v>
       </c>
       <c r="J121" t="s">
-        <v>1128</v>
+        <v>385</v>
       </c>
       <c r="K121" t="s">
-        <v>1122</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1282</v>
+        <v>1311</v>
       </c>
       <c r="B122">
+        <v>81</v>
+      </c>
+      <c r="C122" t="s">
+        <v>473</v>
+      </c>
+      <c r="D122" t="s">
+        <v>499</v>
+      </c>
+      <c r="E122" t="s">
+        <v>500</v>
+      </c>
+      <c r="F122" t="s">
+        <v>502</v>
+      </c>
+      <c r="G122" t="s">
+        <v>503</v>
+      </c>
+      <c r="H122" t="s">
+        <v>505</v>
+      </c>
+      <c r="I122" t="s">
+        <v>506</v>
+      </c>
+      <c r="J122" t="s">
+        <v>507</v>
+      </c>
+      <c r="K122" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B123">
+        <v>81</v>
+      </c>
+      <c r="C123" t="s">
+        <v>591</v>
+      </c>
+      <c r="D123" t="s">
+        <v>616</v>
+      </c>
+      <c r="E123" t="s">
+        <v>610</v>
+      </c>
+      <c r="F123" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s">
+        <v>618</v>
+      </c>
+      <c r="H123" t="s">
+        <v>620</v>
+      </c>
+      <c r="I123" t="s">
+        <v>621</v>
+      </c>
+      <c r="J123" t="s">
+        <v>622</v>
+      </c>
+      <c r="K123" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B124">
+        <v>81</v>
+      </c>
+      <c r="C124" t="s">
+        <v>845</v>
+      </c>
+      <c r="D124" t="s">
+        <v>888</v>
+      </c>
+      <c r="E124" t="s">
+        <v>889</v>
+      </c>
+      <c r="F124" t="s">
+        <v>25</v>
+      </c>
+      <c r="G124" t="s">
+        <v>891</v>
+      </c>
+      <c r="H124" t="s">
+        <v>893</v>
+      </c>
+      <c r="I124" t="s">
+        <v>894</v>
+      </c>
+      <c r="J124" t="s">
+        <v>895</v>
+      </c>
+      <c r="K124" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B125">
+        <v>81</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F125" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H125" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I125" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J125" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K125" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B126">
         <v>80</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C126" t="s">
         <v>934</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D126" t="s">
         <v>1039</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E126" t="s">
         <v>1040</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F126" t="s">
         <v>1042</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G126" t="s">
         <v>1043</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H126" t="s">
         <v>1045</v>
       </c>
-      <c r="I122" t="s">
+      <c r="I126" t="s">
         <v>1046</v>
       </c>
-      <c r="J122" t="s">
+      <c r="J126" t="s">
         <v>1047</v>
       </c>
-      <c r="K122" t="s">
+      <c r="K126" t="s">
         <v>1041</v>
       </c>
     </row>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1341">
   <si>
     <t>日期</t>
   </si>
@@ -3986,6 +3986,9 @@
   </si>
   <si>
     <t>数据更新日期</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
   </si>
   <si>
     <t>匹配度评分分布</t>
@@ -11285,12 +11288,12 @@
         <v>1323</v>
       </c>
       <c r="B11" t="s">
-        <v>1271</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11300,15 +11303,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -11316,7 +11319,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B17" s="5">
         <v>77</v>
@@ -11324,7 +11327,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B18" s="5">
         <v>84</v>
@@ -11332,7 +11335,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B19" s="5">
         <v>6</v>
@@ -11340,7 +11343,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -11348,7 +11351,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11356,7 +11359,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -11364,7 +11367,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11372,7 +11375,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -11380,7 +11383,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -11388,7 +11391,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -11400,7 +11403,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -11418,7 +11421,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>

--- a/求职记录.xlsx
+++ b/求职记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="1408">
   <si>
     <t>日期</t>
   </si>
@@ -3916,6 +3916,210 @@
     <t>简历突出介入器械相关的材料学基础与结构设计能力，将硕士血管支架课题中材料/结构/加工经验迁移到球囊与导管研发；强调对介入输送系统、镍钛导丝等材料的理解，弱化纯支架视角，突出跨品类学习能力与工程执行力。</t>
   </si>
   <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>心玮医疗</t>
+  </si>
+  <si>
+    <t>工艺工程师</t>
+  </si>
+  <si>
+    <t>金属材料、镍钛材料或机械等专业本科及以上，掌握材料加工、材料力学、材料物理化学等知识，熟练三维制图软件，有支架类研发或工艺经验者优先，英语读写熟练可查阅英文文献。</t>
+  </si>
+  <si>
+    <t>https://www.heartcare.com.cn/job</t>
+  </si>
+  <si>
+    <t>智能匹配78分【社招】|值得考虑|神经介入上市企业，镍钛/金属材料支架工艺岗，材料学相关</t>
+  </si>
+  <si>
+    <t>研究80/技能60/学历85/行业100/企业90</t>
+  </si>
+  <si>
+    <t>心玮为神经介入上市企业，岗位涉及镍钛支架材料加工与本硕金属材料背景契合，上海岗位符合城市偏好，可作为神经介入支架方向的匹配选择。</t>
+  </si>
+  <si>
+    <t>突出金属材料/镍钛合金性能测试与加工工艺认知；强调三维制图与材料力学分析能力；补充支架类产品的材料选型经验。</t>
+  </si>
+  <si>
+    <t>康誉医疗（河北康誉医疗器械有限公司）</t>
+  </si>
+  <si>
+    <t>机械、高分子材料等专业本科(985/211)或硕士以上学历；两年以上三类医疗器械研发经验优先，负责支架产品研发全流程（策划、开发、评审、工艺验证、DHF/DMR文件撰写），熟悉ISO13485，具备英文文献阅读能力。</t>
+  </si>
+  <si>
+    <t>北京-大兴区</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1981333257.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|血管支架研发全流程岗位，材料+支架设计技能与方向高度重合</t>
+  </si>
+  <si>
+    <t>研究90/技能75/学历95/行业100/企业80</t>
+  </si>
+  <si>
+    <t>明确负责支架产品研发全流程（策划、开发、工艺验证、DHF/DMR），与硕士血管支架研究方向和材料学/支架设计核心技能高度重合，北京岗位符合城市偏好，是匹配度极高的研发岗。</t>
+  </si>
+  <si>
+    <t>突出血管支架结构设计与材料学研究项目；量化工艺验证与性能试验数据；补充ISO13485与三类器械研发流程认知及英文文献阅读能力。</t>
+  </si>
+  <si>
+    <t>机械、高分子材料等专业本科(985/211)或硕士以上学历；两年以上三类医疗器械研发经验，有支架/球囊研发经验者优先；能推进新产品研发、完成DHF/DMR文件、注册技术资料撰写，熟悉ISO13485体系。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1980803319.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|介入球囊/支架研发岗，材料+设计技能匹配，方向相关</t>
+  </si>
+  <si>
+    <t>研究80/技能75/学历95/行业100/企业80</t>
+  </si>
+  <si>
+    <t>岗位涉及介入球囊/支架新产品研发与DHF/DMR注册资料撰写，需高分子材料背景，与本硕材料学及血管介入支架方向相关，北京岗位符合城市偏好，为有价值的介入器械研发岗。</t>
+  </si>
+  <si>
+    <t>突出高分子材料选择与介入球囊/支架研发经历；补充DFD/DMR与注册资料撰写能力；强调ISO13485体系与英文文献阅读能力。</t>
+  </si>
+  <si>
+    <t>北京先瑞达</t>
+  </si>
+  <si>
+    <t>高分子材料、生物医学、机械等相关专业硕士及以上，3年以上医疗器械行业研发经验，血管介入或植入产品经验优先；负责新产品设计开发、风险分析、样品试制、设计验证与确认，英语读写良好。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1953886005.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配86分【社招】|强烈推荐|血管介入/植入产品研发，硕士+材料/生物医学背景高度匹配</t>
+  </si>
+  <si>
+    <t>研究80/技能80/学历100/行业100/企业85</t>
+  </si>
+  <si>
+    <t>先瑞达为血管介入球囊(DCB/PTA)企业，岗位需高分子材料/生物医学/机械硕士，负责新产品设计开发与设计验证，与硕士生物医学工程背景及材料学、支架设计技能吻合，北京岗位符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出血管介入/植入产品设计开发项目；强化材料学与生物相容性评价能力；量化设计验证与风险分析过程；补充英文文献读写能力。</t>
+  </si>
+  <si>
+    <t>杭州晙杨科技有限公司</t>
+  </si>
+  <si>
+    <t>介入球囊导管研发工程师</t>
+  </si>
+  <si>
+    <t>本科及以上，1-3年经验；负责开发介入导管，需对心血管球囊介入导管有一定了解，熟悉供应商及成型工艺；属介入医疗器械研发方向。</t>
+  </si>
+  <si>
+    <t>https://www.liepin.com/job/1984479475.shtml</t>
+  </si>
+  <si>
+    <t>智能匹配78分【社招】|值得考虑|介入球囊导管研发岗，介入方向相关，成型/材料工艺</t>
+  </si>
+  <si>
+    <t>研究80/技能65/学历85/行业100/企业78</t>
+  </si>
+  <si>
+    <t>岗位为介入球囊导管研发，与本硕介入医疗器械方向发展相关，涉及材料与成型工艺，可作为介入导管方向的补充匹配岗位。</t>
+  </si>
+  <si>
+    <t>突出介入导管/输送系统及球囊相关项目了解；补充高分子材料成型工艺经验；强调供应商对接与工艺验证能力。</t>
+  </si>
+  <si>
+    <t>上海腾复医疗科技有限公司</t>
+  </si>
+  <si>
+    <t>硕士及以上学历，材料、机械设计等相关专业；约2年医疗器械研发工作经验（心血管/介入类产品研发优先）；熟练使用三维制图软件；负责三类微创伤介入产品研发（含结构设计）。</t>
+  </si>
+  <si>
+    <t>https://www.tendfo.com/Job</t>
+  </si>
+  <si>
+    <t>智能匹配84分【社招】|强烈推荐|三类微创伤介入产品研发（含结构设计），材料+设计技能匹配，硕士</t>
+  </si>
+  <si>
+    <t>研究80/技能75/学历100/行业100/企业82</t>
+  </si>
+  <si>
+    <t>岗位需材料/机械硕士负责三类微创伤介入产品研发含结构设计，与本硕材料学+支架结构设计技能及介入器械方向匹配，上海岗位符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出介入器械结构设计项目；强调材料学背景与三维制图/建模能力；量化结构设计与性能评价数据；补充心血管介入产品了解。</t>
+  </si>
+  <si>
+    <t>心凯诺医疗</t>
+  </si>
+  <si>
+    <t>研发工程师/主管（介入球囊·导管·支架）</t>
+  </si>
+  <si>
+    <t>承担三类介入球囊、导管、支架类医疗器械产品开发，负责产品设计、样品研制、工艺研究。神经介入与外周介入双布局（颅内密网支架、动脉瘤支架、颈动脉等）；要求具有医疗器械研发、球囊/导管/支架类产品开发经验，硕士优先，材料学/生物医学工程背景。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=dn9a_-gY295K0Rci_xozVf0c4J0R6Rg6j1kZv9B8Ue2rEKOu_JuMqX2aBwQjUgz_dw7KqJnD0bP9aYz4hDNe7qcUAbehEaCpqkROoMBzJOHBlL2A0boeWZqPH0kXlQoYqekA5Qz8Uf2sA8NxBnYqOZ0eqE8YTLfN5b0gC4B5-1XZSwJlgN2QrXh0TpRzQH6VgCwU3D8s9aB6nFqL4M7PzJ0KbXwO2iAq2yRjM3xZgC6gVlT0mYtS8cJzL1vOqYwEo9B</t>
+  </si>
+  <si>
+    <t>智能匹配85分【社招】|强烈推荐|神经+外周介入球囊/导管/支架研发，密网支架方向相关，硕士优先</t>
+  </si>
+  <si>
+    <t>心凯诺布局神经介入与外周介入（颅内密网支架、动脉瘤支架等），岗位做介入球囊/导管/支架产品研发，硕士+材料/生物医学工程背景优先，与硕士血管支架研究方向及材料学/支架设计技能高度契合，上海符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出支架/介入器械产品设计与样品研制项目；强化材料学与神经/外周介入器械了解；补充工艺研究与设计验证能力；量化支架性能评价数据。</t>
+  </si>
+  <si>
+    <t>上海恩盛医疗</t>
+  </si>
+  <si>
+    <t>参与新产品的设计开发，负责血管介入器械（外周静脉介入）球囊、导管等产品研发；有血管介入器械、球囊、导管研发经验者优先；熟悉模具设计、高分子材料成型；生物医学工程/材料学背景契合。</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=UvFJIRP8uMMiqt1yJOUmphQ1-AFJpF_jiAuoQbXgjcf7pq3K1ZCUpf2CecwmxtgKzQC-3aw_TWs2gDrfFZ8lx3pVx1zJqeHRZtpTzIA5I9hPG30xq-WX9Da28cTXdTAGRxF6eAgNURlLjW6N8ZlTGcUWXqhsbg0eEfDMHOMw4CVr1dbZWbKUeQ</t>
+  </si>
+  <si>
+    <t>智能匹配83分【社招】|强烈推荐|外周静脉介入球囊/导管研发，材料+设计技能匹配，介入相关</t>
+  </si>
+  <si>
+    <t>研究80/技能78/学历88/行业100/企业82</t>
+  </si>
+  <si>
+    <t>岗位负责血管介入器械球囊/导管研发，需高分子材料成型与模具设计经验，生物医学工程/材料学背景契合，与本硕介入器械方向及材料学技能相关，上海岗位符合城市偏好。</t>
+  </si>
+  <si>
+    <t>突出血管介入导管/球囊研发项目；强调高分子材料成型与模具设计能力；补充生物相容性与介入器械设计验证经验。</t>
+  </si>
+  <si>
+    <t>北京永益润成科技</t>
+  </si>
+  <si>
+    <t>医疗器械研发助理工程师（微导管·球囊导管）</t>
+  </si>
+  <si>
+    <t>负责微导管、球囊导管等产品相关工作，参与研发及注册文件/体系考核文件编写；要求医疗器械研发相关经验，掌握高分子材料，适合应届硕士及初级研发人员；微导管、球囊导管介入类产品方向。</t>
+  </si>
+  <si>
+    <t>北京-昌平区</t>
+  </si>
+  <si>
+    <t>https://weixin.sogou.com/link?url=wNGwDnc-fYArBcMIrH2Hz_rbq5DpoyYV2FqzkmlIGcZ3hK2SDwR5xl6DvMVb3xo0ffr5dAaKCK46fE4Q3NPsbLX9RiwpV3zg5mM4VJpZGvw_0ujZk_cVLgl45wJCT9eIzUi5JxxRa0ZjFY8LRRvd_KBoYugnUdxs4xadU1S-Zj32-j2KiwUw</t>
+  </si>
+  <si>
+    <t>智能匹配79分【社招】|值得考虑|微导管/球囊导管介入研发助理，适合应届硕士，材料学+注册文件</t>
+  </si>
+  <si>
+    <t>研究80/技能60/学历100/行业100/企业75</t>
+  </si>
+  <si>
+    <t>岗位适合应届硕士，负责微导管/球囊导管介入产品研发与注册文件，对高分子材料有要求，北京岗位符合城市偏好，是最适合应届生起步的介入器械研发岗，可重点投递。</t>
+  </si>
+  <si>
+    <t>突出高分子材料项目与介入导管方向了解；补充材料学测试能力；强调研发与注册/体系文件编写认知；突出应届硕士能快速上手。</t>
+  </si>
+  <si>
     <t>投递日期</t>
   </si>
   <si>
@@ -3986,9 +4190,6 @@
   </si>
   <si>
     <t>数据更新日期</t>
-  </si>
-  <si>
-    <t>2026-08-22</t>
   </si>
   <si>
     <t>匹配度评分分布</t>
@@ -4471,7 +4672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11097,6 +11298,348 @@
       </c>
       <c r="L174" t="s">
         <v>1299</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E175" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G175">
+        <v>8</v>
+      </c>
+      <c r="H175" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I175">
+        <v>78</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1306</v>
+      </c>
+      <c r="K175" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L175" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C176" t="s">
+        <v>610</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G176">
+        <v>9</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I176">
+        <v>86</v>
+      </c>
+      <c r="J176" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K176" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L176" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C177" t="s">
+        <v>830</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G177">
+        <v>8</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I177">
+        <v>83</v>
+      </c>
+      <c r="J177" t="s">
+        <v>1320</v>
+      </c>
+      <c r="K177" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L177" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C178" t="s">
+        <v>89</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E178" t="s">
+        <v>25</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G178">
+        <v>9</v>
+      </c>
+      <c r="H178" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I178">
+        <v>86</v>
+      </c>
+      <c r="J178" t="s">
+        <v>1327</v>
+      </c>
+      <c r="K178" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L178" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E179" t="s">
+        <v>147</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G179">
+        <v>8</v>
+      </c>
+      <c r="H179" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I179">
+        <v>78</v>
+      </c>
+      <c r="J179" t="s">
+        <v>1335</v>
+      </c>
+      <c r="K179" t="s">
+        <v>1336</v>
+      </c>
+      <c r="L179" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C180" t="s">
+        <v>122</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E180" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G180">
+        <v>8</v>
+      </c>
+      <c r="H180" t="s">
+        <v>1341</v>
+      </c>
+      <c r="I180">
+        <v>84</v>
+      </c>
+      <c r="J180" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K180" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L180" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E181" t="s">
+        <v>16</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G181">
+        <v>9</v>
+      </c>
+      <c r="H181" t="s">
+        <v>1349</v>
+      </c>
+      <c r="I181">
+        <v>85</v>
+      </c>
+      <c r="J181" t="s">
+        <v>312</v>
+      </c>
+      <c r="K181" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L181" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C182" t="s">
+        <v>110</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E182" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G182">
+        <v>8</v>
+      </c>
+      <c r="H182" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I182">
+        <v>83</v>
+      </c>
+      <c r="J182" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K182" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L182" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G183">
+        <v>8</v>
+      </c>
+      <c r="H183" t="s">
+        <v>1364</v>
+      </c>
+      <c r="I183">
+        <v>79</v>
+      </c>
+      <c r="J183" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K183" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L183" t="s">
+        <v>1367</v>
       </c>
     </row>
   </sheetData>
@@ -11130,7 +11673,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1300</v>
+        <v>1368</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -11139,16 +11682,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1301</v>
+        <v>1369</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1302</v>
+        <v>1370</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1303</v>
+        <v>1371</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1304</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -11162,13 +11705,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1305</v>
+        <v>1373</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1306</v>
+        <v>1374</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>473</v>
@@ -11196,7 +11739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -11211,7 +11754,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1312</v>
+        <v>1380</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -11221,31 +11764,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1313</v>
+        <v>1381</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1314</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1315</v>
+        <v>1383</v>
       </c>
       <c r="B4">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1316</v>
+        <v>1384</v>
       </c>
       <c r="B5" t="s">
-        <v>1317</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1318</v>
+        <v>1386</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -11253,7 +11796,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1319</v>
+        <v>1387</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -11261,23 +11804,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1320</v>
+        <v>1388</v>
       </c>
       <c r="B8">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1321</v>
+        <v>1389</v>
       </c>
       <c r="B9">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1322</v>
+        <v>1390</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -11285,15 +11828,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1323</v>
+        <v>1391</v>
       </c>
       <c r="B11" t="s">
-        <v>1324</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1325</v>
+        <v>1392</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -11303,15 +11846,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1326</v>
+        <v>1393</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1327</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1328</v>
+        <v>1395</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -11319,23 +11862,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1329</v>
+        <v>1396</v>
       </c>
       <c r="B17" s="5">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1330</v>
+        <v>1397</v>
       </c>
       <c r="B18" s="5">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1331</v>
+        <v>1398</v>
       </c>
       <c r="B19" s="5">
         <v>6</v>
@@ -11343,7 +11886,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1332</v>
+        <v>1399</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -11351,7 +11894,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1333</v>
+        <v>1400</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11359,7 +11902,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1334</v>
+        <v>1401</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -11367,7 +11910,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1335</v>
+        <v>1402</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11375,7 +11918,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1336</v>
+        <v>1403</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -11383,7 +11926,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1337</v>
+        <v>1404</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -11391,7 +11934,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1338</v>
+        <v>1405</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -11403,7 +11946,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1339</v>
+        <v>1406</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>0</v>
@@ -11421,7 +11964,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1340</v>
+        <v>1407</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>7</v>
@@ -13590,25 +14133,25 @@
         <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="C113" t="s">
-        <v>1201</v>
+        <v>1309</v>
       </c>
       <c r="D113" t="s">
-        <v>1202</v>
+        <v>610</v>
       </c>
       <c r="E113" t="s">
-        <v>1204</v>
+        <v>1311</v>
       </c>
       <c r="F113" t="s">
-        <v>1205</v>
+        <v>1312</v>
       </c>
       <c r="G113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H113" t="s">
-        <v>1206</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -13616,25 +14159,25 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>1300</v>
       </c>
       <c r="C114" t="s">
-        <v>72</v>
+        <v>1323</v>
       </c>
       <c r="D114" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E114" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
-        <v>76</v>
+        <v>1325</v>
       </c>
       <c r="G114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H114" t="s">
-        <v>77</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -13642,25 +14185,25 @@
         <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>1300</v>
       </c>
       <c r="C115" t="s">
-        <v>80</v>
+        <v>1345</v>
       </c>
       <c r="D115" t="s">
-        <v>81</v>
+        <v>1346</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>83</v>
+        <v>1348</v>
       </c>
       <c r="G115">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H115" t="s">
-        <v>84</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -13668,25 +14211,25 @@
         <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>1201</v>
       </c>
       <c r="D116" t="s">
-        <v>104</v>
+        <v>1202</v>
       </c>
       <c r="E116" t="s">
-        <v>106</v>
+        <v>1204</v>
       </c>
       <c r="F116" t="s">
-        <v>107</v>
+        <v>1205</v>
       </c>
       <c r="G116">
         <v>8</v>
       </c>
       <c r="H116" t="s">
-        <v>108</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -13697,22 +14240,22 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D117" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E117" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F117" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G117">
         <v>8</v>
       </c>
       <c r="H117" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -13723,22 +14266,22 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D118" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E118" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F118" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="G118">
         <v>8</v>
       </c>
       <c r="H118" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -13749,22 +14292,22 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D119" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E119" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F119" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G119">
         <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -13775,22 +14318,22 @@
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E120" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="F120" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13801,22 +14344,22 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D121" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E121" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -13824,25 +14367,25 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="D122" t="s">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="E122" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="F122" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="G122">
         <v>8</v>
       </c>
       <c r="H122" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -13850,25 +14393,25 @@
         <v>94</v>
       </c>
       <c r="B123" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="D123" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="E123" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="F123" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="G123">
         <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -13876,25 +14419,25 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="D124" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="E124" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="G124">
         <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13905,22 +14448,22 @@
         <v>159</v>
       </c>
       <c r="C125" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D125" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="E125" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F125" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -13931,22 +14474,22 @@
         <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="D126" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="E126" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F126" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="G126">
         <v>8</v>
       </c>
       <c r="H126" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -13957,22 +14500,22 @@
         <v>159</v>
       </c>
       <c r="C127" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D127" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="E127" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="F127" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="G127">
         <v>8</v>
       </c>
       <c r="H127" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -13983,22 +14526,22 @@
         <v>159</v>
       </c>
       <c r="C128" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="E128" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F128" t="s">
-        <v>251</v>
+        <v>76</v>
       </c>
       <c r="G128">
         <v>8</v>
       </c>
       <c r="H128" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -14009,22 +14552,22 @@
         <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D129" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E129" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G129">
         <v>8</v>
       </c>
       <c r="H129" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -14035,22 +14578,22 @@
         <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D130" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E130" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="G130">
         <v>8</v>
       </c>
       <c r="H130" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -14061,22 +14604,22 @@
         <v>159</v>
       </c>
       <c r="C131" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D131" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E131" t="s">
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>58</v>
+        <v>251</v>
       </c>
       <c r="G131">
         <v>8</v>
       </c>
       <c r="H131" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -14087,22 +14630,22 @@
         <v>159</v>
       </c>
       <c r="C132" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="D132" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="E132" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="F132" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="G132">
         <v>8</v>
       </c>
       <c r="H132" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -14110,25 +14653,25 @@
         <v>104</v>
       </c>
       <c r="B133" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C133" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="D133" t="s">
-        <v>316</v>
+        <v>122</v>
       </c>
       <c r="E133" t="s">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="F133" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="G133">
         <v>8</v>
       </c>
       <c r="H133" t="s">
-        <v>320</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -14136,25 +14679,25 @@
         <v>105</v>
       </c>
       <c r="B134" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C134" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="D134" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="E134" t="s">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="G134">
         <v>8</v>
       </c>
       <c r="H134" t="s">
-        <v>343</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -14162,25 +14705,25 @@
         <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="C135" t="s">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="D135" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="E135" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="F135" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="G135">
         <v>8</v>
       </c>
       <c r="H135" t="s">
-        <v>351</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -14191,22 +14734,22 @@
         <v>284</v>
       </c>
       <c r="C136" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="D136" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="E136" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="F136" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="G136">
         <v>8</v>
       </c>
       <c r="H136" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -14217,22 +14760,22 @@
         <v>284</v>
       </c>
       <c r="C137" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="D137" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E137" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="F137" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="G137">
         <v>8</v>
       </c>
       <c r="H137" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -14243,22 +14786,22 @@
         <v>284</v>
       </c>
       <c r="C138" t="s">
-        <v>144</v>
+        <v>347</v>
       </c>
       <c r="D138" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="E138" t="s">
-        <v>396</v>
+        <v>98</v>
       </c>
       <c r="F138" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="G138">
         <v>8</v>
       </c>
       <c r="H138" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -14266,25 +14809,25 @@
         <v>110</v>
       </c>
       <c r="B139" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C139" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="D139" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="E139" t="s">
-        <v>66</v>
+        <v>356</v>
       </c>
       <c r="F139" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="G139">
         <v>8</v>
       </c>
       <c r="H139" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -14292,25 +14835,25 @@
         <v>111</v>
       </c>
       <c r="B140" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C140" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="D140" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="E140" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="F140" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="G140">
         <v>8</v>
       </c>
       <c r="H140" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -14318,25 +14861,25 @@
         <v>112</v>
       </c>
       <c r="B141" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="C141" t="s">
-        <v>424</v>
+        <v>144</v>
       </c>
       <c r="D141" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E141" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="F141" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="G141">
         <v>8</v>
       </c>
       <c r="H141" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -14347,22 +14890,22 @@
         <v>402</v>
       </c>
       <c r="C142" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="D142" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E142" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F142" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="G142">
         <v>8</v>
       </c>
       <c r="H142" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -14370,25 +14913,25 @@
         <v>114</v>
       </c>
       <c r="B143" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C143" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
+        <v>419</v>
       </c>
       <c r="E143" t="s">
-        <v>485</v>
+        <v>66</v>
       </c>
       <c r="F143" t="s">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143" t="s">
-        <v>487</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -14396,25 +14939,25 @@
         <v>115</v>
       </c>
       <c r="B144" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C144" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="D144" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="E144" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F144" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="G144">
         <v>8</v>
       </c>
       <c r="H144" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -14422,25 +14965,25 @@
         <v>116</v>
       </c>
       <c r="B145" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="C145" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="D145" t="s">
-        <v>500</v>
+        <v>431</v>
       </c>
       <c r="E145" t="s">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>503</v>
+        <v>433</v>
       </c>
       <c r="G145">
         <v>8</v>
       </c>
       <c r="H145" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -14451,22 +14994,22 @@
         <v>473</v>
       </c>
       <c r="C146" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="D146" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="E146" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="F146" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="G146">
         <v>8</v>
       </c>
       <c r="H146" t="s">
-        <v>537</v>
+        <v>487</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -14477,22 +15020,22 @@
         <v>473</v>
       </c>
       <c r="C147" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="D147" t="s">
-        <v>551</v>
+        <v>492</v>
       </c>
       <c r="E147" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F147" t="s">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="G147">
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -14500,25 +15043,25 @@
         <v>119</v>
       </c>
       <c r="B148" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C148" t="s">
-        <v>578</v>
+        <v>499</v>
       </c>
       <c r="D148" t="s">
-        <v>579</v>
+        <v>500</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>502</v>
       </c>
       <c r="F148" t="s">
-        <v>581</v>
+        <v>503</v>
       </c>
       <c r="G148">
         <v>8</v>
       </c>
       <c r="H148" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -14526,25 +15069,25 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="C149" t="s">
-        <v>584</v>
+        <v>532</v>
       </c>
       <c r="D149" t="s">
-        <v>585</v>
+        <v>533</v>
       </c>
       <c r="E149" t="s">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="F149" t="s">
-        <v>588</v>
+        <v>536</v>
       </c>
       <c r="G149">
         <v>8</v>
       </c>
       <c r="H149" t="s">
-        <v>589</v>
+        <v>537</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -14552,25 +15095,25 @@
         <v>121</v>
       </c>
       <c r="B150" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="C150" t="s">
-        <v>601</v>
+        <v>550</v>
       </c>
       <c r="D150" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
       <c r="E150" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="G150">
         <v>8</v>
       </c>
       <c r="H150" t="s">
-        <v>605</v>
+        <v>554</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -14578,25 +15121,25 @@
         <v>122</v>
       </c>
       <c r="B151" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C151" t="s">
-        <v>616</v>
+        <v>578</v>
       </c>
       <c r="D151" t="s">
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="E151" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F151" t="s">
-        <v>618</v>
+        <v>581</v>
       </c>
       <c r="G151">
         <v>8</v>
       </c>
       <c r="H151" t="s">
-        <v>619</v>
+        <v>582</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -14604,25 +15147,25 @@
         <v>123</v>
       </c>
       <c r="B152" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="C152" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="D152" t="s">
-        <v>623</v>
+        <v>585</v>
       </c>
       <c r="E152" t="s">
-        <v>16</v>
+        <v>587</v>
       </c>
       <c r="F152" t="s">
-        <v>468</v>
+        <v>588</v>
       </c>
       <c r="G152">
         <v>8</v>
       </c>
       <c r="H152" t="s">
-        <v>625</v>
+        <v>589</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -14633,22 +15176,22 @@
         <v>591</v>
       </c>
       <c r="C153" t="s">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="D153" t="s">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="E153" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F153" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="G153">
         <v>8</v>
       </c>
       <c r="H153" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14659,22 +15202,22 @@
         <v>591</v>
       </c>
       <c r="C154" t="s">
-        <v>650</v>
+        <v>616</v>
       </c>
       <c r="D154" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="E154" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F154" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="G154">
         <v>8</v>
       </c>
       <c r="H154" t="s">
-        <v>654</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -14685,22 +15228,22 @@
         <v>591</v>
       </c>
       <c r="C155" t="s">
-        <v>658</v>
+        <v>557</v>
       </c>
       <c r="D155" t="s">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="E155" t="s">
-        <v>661</v>
+        <v>16</v>
       </c>
       <c r="F155" t="s">
-        <v>662</v>
+        <v>468</v>
       </c>
       <c r="G155">
         <v>8</v>
       </c>
       <c r="H155" t="s">
-        <v>663</v>
+        <v>625</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -14711,22 +15254,22 @@
         <v>591</v>
       </c>
       <c r="C156" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="D156" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="E156" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F156" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G156">
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -14737,22 +15280,22 @@
         <v>591</v>
       </c>
       <c r="C157" t="s">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="D157" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="E157" t="s">
         <v>66</v>
       </c>
       <c r="F157" t="s">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="G157">
         <v>8</v>
       </c>
       <c r="H157" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -14760,25 +15303,25 @@
         <v>129</v>
       </c>
       <c r="B158" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C158" t="s">
-        <v>714</v>
+        <v>658</v>
       </c>
       <c r="D158" t="s">
-        <v>715</v>
+        <v>659</v>
       </c>
       <c r="E158" t="s">
-        <v>16</v>
+        <v>661</v>
       </c>
       <c r="F158" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="G158">
         <v>8</v>
       </c>
       <c r="H158" t="s">
-        <v>717</v>
+        <v>663</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -14786,25 +15329,25 @@
         <v>130</v>
       </c>
       <c r="B159" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C159" t="s">
-        <v>721</v>
+        <v>666</v>
       </c>
       <c r="D159" t="s">
-        <v>722</v>
+        <v>667</v>
       </c>
       <c r="E159" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F159" t="s">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="G159">
         <v>8</v>
       </c>
       <c r="H159" t="s">
-        <v>725</v>
+        <v>669</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14812,25 +15355,25 @@
         <v>131</v>
       </c>
       <c r="B160" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="C160" t="s">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="D160" t="s">
-        <v>730</v>
+        <v>674</v>
       </c>
       <c r="E160" t="s">
-        <v>535</v>
+        <v>66</v>
       </c>
       <c r="F160" t="s">
-        <v>732</v>
+        <v>676</v>
       </c>
       <c r="G160">
         <v>8</v>
       </c>
       <c r="H160" t="s">
-        <v>733</v>
+        <v>677</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -14841,13 +15384,13 @@
         <v>697</v>
       </c>
       <c r="C161" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="D161" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="E161" t="s">
-        <v>739</v>
+        <v>16</v>
       </c>
       <c r="F161" t="s">
         <v>604</v>
@@ -14856,7 +15399,7 @@
         <v>8</v>
       </c>
       <c r="H161" t="s">
-        <v>740</v>
+        <v>717</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -14867,22 +15410,22 @@
         <v>697</v>
       </c>
       <c r="C162" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="D162" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="E162" t="s">
-        <v>747</v>
+        <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="G162">
         <v>8</v>
       </c>
       <c r="H162" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14893,22 +15436,22 @@
         <v>697</v>
       </c>
       <c r="C163" t="s">
-        <v>753</v>
+        <v>729</v>
       </c>
       <c r="D163" t="s">
-        <v>754</v>
+        <v>730</v>
       </c>
       <c r="E163" t="s">
-        <v>756</v>
+        <v>535</v>
       </c>
       <c r="F163" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="G163">
         <v>8</v>
       </c>
       <c r="H163" t="s">
-        <v>758</v>
+        <v>733</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14919,22 +15462,22 @@
         <v>697</v>
       </c>
       <c r="C164" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="D164" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="E164" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="F164" t="s">
-        <v>764</v>
+        <v>604</v>
       </c>
       <c r="G164">
         <v>8</v>
       </c>
       <c r="H164" t="s">
-        <v>765</v>
+        <v>740</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14942,25 +15485,25 @@
         <v>136</v>
       </c>
       <c r="B165" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C165" t="s">
-        <v>791</v>
+        <v>744</v>
       </c>
       <c r="D165" t="s">
-        <v>610</v>
+        <v>745</v>
       </c>
       <c r="E165" t="s">
-        <v>793</v>
+        <v>747</v>
       </c>
       <c r="F165" t="s">
-        <v>794</v>
+        <v>748</v>
       </c>
       <c r="G165">
         <v>8</v>
       </c>
       <c r="H165" t="s">
-        <v>795</v>
+        <v>749</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14968,25 +15511,25 @@
         <v>137</v>
       </c>
       <c r="B166" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C166" t="s">
-        <v>807</v>
+        <v>753</v>
       </c>
       <c r="D166" t="s">
-        <v>808</v>
+        <v>754</v>
       </c>
       <c r="E166" t="s">
-        <v>810</v>
+        <v>756</v>
       </c>
       <c r="F166" t="s">
-        <v>811</v>
+        <v>757</v>
       </c>
       <c r="G166">
         <v>8</v>
       </c>
       <c r="H166" t="s">
-        <v>812</v>
+        <v>758</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -14994,25 +15537,25 @@
         <v>138</v>
       </c>
       <c r="B167" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="C167" t="s">
-        <v>816</v>
+        <v>760</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>761</v>
       </c>
       <c r="E167" t="s">
-        <v>16</v>
+        <v>763</v>
       </c>
       <c r="F167" t="s">
-        <v>818</v>
+        <v>764</v>
       </c>
       <c r="G167">
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>819</v>
+        <v>765</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -15020,25 +15563,25 @@
         <v>139</v>
       </c>
       <c r="B168" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C168" t="s">
-        <v>888</v>
+        <v>791</v>
       </c>
       <c r="D168" t="s">
-        <v>889</v>
+        <v>610</v>
       </c>
       <c r="E168" t="s">
-        <v>25</v>
+        <v>793</v>
       </c>
       <c r="F168" t="s">
-        <v>891</v>
+        <v>794</v>
       </c>
       <c r="G168">
         <v>8</v>
       </c>
       <c r="H168" t="s">
-        <v>892</v>
+        <v>795</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -15046,25 +15589,25 @@
         <v>140</v>
       </c>
       <c r="B169" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C169" t="s">
-        <v>896</v>
+        <v>807</v>
       </c>
       <c r="D169" t="s">
-        <v>897</v>
+        <v>808</v>
       </c>
       <c r="E169" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="F169" t="s">
-        <v>899</v>
+        <v>811</v>
       </c>
       <c r="G169">
         <v>8</v>
       </c>
       <c r="H169" t="s">
-        <v>900</v>
+        <v>812</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -15072,25 +15615,25 @@
         <v>141</v>
       </c>
       <c r="B170" t="s">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C170" t="s">
-        <v>904</v>
+        <v>816</v>
       </c>
       <c r="D170" t="s">
-        <v>585</v>
+        <v>110</v>
       </c>
       <c r="E170" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>906</v>
+        <v>818</v>
       </c>
       <c r="G170">
         <v>8</v>
       </c>
       <c r="H170" t="s">
-        <v>907</v>
+        <v>819</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -15101,22 +15644,22 @@
         <v>845</v>
       </c>
       <c r="C171" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="D171" t="s">
-        <v>585</v>
+        <v>889</v>
       </c>
       <c r="E171" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F171" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="G171">
         <v>8</v>
       </c>
       <c r="H171" t="s">
-        <v>914</v>
+        <v>892</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -15127,22 +15670,22 @@
         <v>845</v>
       </c>
       <c r="C172" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="D172" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="E172" t="s">
-        <v>921</v>
+        <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="G172">
         <v>8</v>
       </c>
       <c r="H172" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -15150,25 +15693,25 @@
         <v>144</v>
       </c>
       <c r="B173" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C173" t="s">
-        <v>964</v>
+        <v>904</v>
       </c>
       <c r="D173" t="s">
-        <v>965</v>
+        <v>585</v>
       </c>
       <c r="E173" t="s">
-        <v>967</v>
+        <v>66</v>
       </c>
       <c r="F173" t="s">
-        <v>968</v>
+        <v>906</v>
       </c>
       <c r="G173">
         <v>8</v>
       </c>
       <c r="H173" t="s">
-        <v>969</v>
+        <v>907</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -15176,25 +15719,25 @@
         <v>145</v>
       </c>
       <c r="B174" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C174" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="D174" t="s">
-        <v>1002</v>
+        <v>585</v>
       </c>
       <c r="E174" t="s">
-        <v>1004</v>
+        <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>438</v>
+        <v>913</v>
       </c>
       <c r="G174">
         <v>8</v>
       </c>
       <c r="H174" t="s">
-        <v>1005</v>
+        <v>914</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -15202,25 +15745,25 @@
         <v>146</v>
       </c>
       <c r="B175" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="C175" t="s">
-        <v>13</v>
+        <v>918</v>
       </c>
       <c r="D175" t="s">
-        <v>1009</v>
+        <v>919</v>
       </c>
       <c r="E175" t="s">
-        <v>16</v>
+        <v>921</v>
       </c>
       <c r="F175" t="s">
-        <v>1011</v>
+        <v>922</v>
       </c>
       <c r="G175">
         <v>8</v>
       </c>
       <c r="H175" t="s">
-        <v>1012</v>
+        <v>923</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -15231,22 +15774,22 @@
         <v>934</v>
       </c>
       <c r="C176" t="s">
-        <v>650</v>
+        <v>964</v>
       </c>
       <c r="D176" t="s">
-        <v>1016</v>
+        <v>965</v>
       </c>
       <c r="E176" t="s">
-        <v>66</v>
+        <v>967</v>
       </c>
       <c r="F176" t="s">
-        <v>1018</v>
+        <v>968</v>
       </c>
       <c r="G176">
         <v>8</v>
       </c>
       <c r="H176" t="s">
-        <v>1019</v>
+        <v>969</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -15257,22 +15800,22 @@
         <v>934</v>
       </c>
       <c r="C177" t="s">
-        <v>1023</v>
+        <v>950</v>
       </c>
       <c r="D177" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
       <c r="E177" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="F177" t="s">
-        <v>1027</v>
+        <v>438</v>
       </c>
       <c r="G177">
         <v>8</v>
       </c>
       <c r="H177" t="s">
-        <v>1028</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -15283,22 +15826,22 @@
         <v>934</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
       <c r="D178" t="s">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="E178" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F178" t="s">
-        <v>1034</v>
+        <v>1011</v>
       </c>
       <c r="G178">
         <v>8</v>
       </c>
       <c r="H178" t="s">
-        <v>1035</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -15309,22 +15852,22 @@
         <v>934</v>
       </c>
       <c r="C179" t="s">
-        <v>1039</v>
+        <v>650</v>
       </c>
       <c r="D179" t="s">
-        <v>1040</v>
+        <v>1016</v>
       </c>
       <c r="E179" t="s">
-        <v>1042</v>
+        <v>66</v>
       </c>
       <c r="F179" t="s">
-        <v>1043</v>
+        <v>1018</v>
       </c>
       <c r="G179">
         <v>8</v>
       </c>
       <c r="H179" t="s">
-        <v>1044</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -15335,22 +15878,22 @@
         <v>934</v>
       </c>
       <c r="C180" t="s">
-        <v>1048</v>
+        <v>1023</v>
       </c>
       <c r="D180" t="s">
-        <v>1049</v>
+        <v>1024</v>
       </c>
       <c r="E180" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="F180" t="s">
-        <v>1052</v>
+        <v>1027</v>
       </c>
       <c r="G180">
         <v>8</v>
       </c>
       <c r="H180" t="s">
-        <v>1053</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -15361,22 +15904,22 @@
         <v>934</v>
       </c>
       <c r="C181" t="s">
-        <v>1057</v>
+        <v>213</v>
       </c>
       <c r="D181" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="E181" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F181" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="G181">
         <v>8</v>
       </c>
       <c r="H181" t="s">
-        <v>1061</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -15387,22 +15930,22 @@
         <v>934</v>
       </c>
       <c r="C182" t="s">
-        <v>1082</v>
+        <v>1039</v>
       </c>
       <c r="D182" t="s">
-        <v>1083</v>
+        <v>1040</v>
       </c>
       <c r="E182" t="s">
-        <v>1085</v>
+        <v>1042</v>
       </c>
       <c r="F182" t="s">
-        <v>959</v>
+        <v>1043</v>
       </c>
       <c r="G182">
         <v>8</v>
       </c>
       <c r="H182" t="s">
-        <v>1086</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -15410,25 +15953,25 @@
         <v>154</v>
       </c>
       <c r="B183" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C183" t="s">
-        <v>271</v>
+        <v>1048</v>
       </c>
       <c r="D183" t="s">
-        <v>1104</v>
+        <v>1049</v>
       </c>
       <c r="E183" t="s">
-        <v>1106</v>
+        <v>1051</v>
       </c>
       <c r="F183" t="s">
-        <v>1107</v>
+        <v>1052</v>
       </c>
       <c r="G183">
         <v>8</v>
       </c>
       <c r="H183" t="s">
-        <v>1108</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -15436,25 +15979,25 @@
         <v>155</v>
       </c>
       <c r="B184" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C184" t="s">
-        <v>1112</v>
+        <v>1057</v>
       </c>
       <c r="D184" t="s">
-        <v>1113</v>
+        <v>1058</v>
       </c>
       <c r="E184" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F184" t="s">
-        <v>1115</v>
+        <v>1060</v>
       </c>
       <c r="G184">
         <v>8</v>
       </c>
       <c r="H184" t="s">
-        <v>1116</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -15462,25 +16005,25 @@
         <v>156</v>
       </c>
       <c r="B185" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="C185" t="s">
-        <v>1120</v>
+        <v>1082</v>
       </c>
       <c r="D185" t="s">
-        <v>1121</v>
+        <v>1083</v>
       </c>
       <c r="E185" t="s">
-        <v>1123</v>
+        <v>1085</v>
       </c>
       <c r="F185" t="s">
-        <v>1124</v>
+        <v>959</v>
       </c>
       <c r="G185">
         <v>8</v>
       </c>
       <c r="H185" t="s">
-        <v>1125</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -15491,22 +16034,22 @@
         <v>1087</v>
       </c>
       <c r="C186" t="s">
-        <v>1129</v>
+        <v>271</v>
       </c>
       <c r="D186" t="s">
-        <v>1130</v>
+        <v>1104</v>
       </c>
       <c r="E186" t="s">
-        <v>1132</v>
+        <v>1106</v>
       </c>
       <c r="F186" t="s">
-        <v>1133</v>
+        <v>1107</v>
       </c>
       <c r="G186">
         <v>8</v>
       </c>
       <c r="H186" t="s">
-        <v>1134</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -15514,25 +16057,25 @@
         <v>158</v>
       </c>
       <c r="B187" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C187" t="s">
-        <v>1172</v>
+        <v>1112</v>
       </c>
       <c r="D187" t="s">
-        <v>122</v>
+        <v>1113</v>
       </c>
       <c r="E187" t="s">
-        <v>1174</v>
+        <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>1175</v>
+        <v>1115</v>
       </c>
       <c r="G187">
         <v>8</v>
       </c>
       <c r="H187" t="s">
-        <v>1176</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -15540,25 +16083,25 @@
         <v>159</v>
       </c>
       <c r="B188" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C188" t="s">
-        <v>1178</v>
+        <v>1120</v>
       </c>
       <c r="D188" t="s">
-        <v>1179</v>
+        <v>1121</v>
       </c>
       <c r="E188" t="s">
-        <v>1181</v>
+        <v>1123</v>
       </c>
       <c r="F188" t="s">
-        <v>1175</v>
+        <v>1124</v>
       </c>
       <c r="G188">
         <v>8</v>
       </c>
       <c r="H188" t="s">
-        <v>1182</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -15566,25 +16109,25 @@
         <v>160</v>
       </c>
       <c r="B189" t="s">
-        <v>1171</v>
+        <v>1087</v>
       </c>
       <c r="C189" t="s">
-        <v>1184</v>
+        <v>1129</v>
       </c>
       <c r="D189" t="s">
-        <v>1185</v>
+        <v>1130</v>
       </c>
       <c r="E189" t="s">
-        <v>1187</v>
+        <v>1132</v>
       </c>
       <c r="F189" t="s">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="G189">
         <v>8</v>
       </c>
       <c r="H189" t="s">
-        <v>1188</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -15592,25 +16135,25 @@
         <v>161</v>
       </c>
       <c r="B190" t="s">
-        <v>1210</v>
+        <v>1171</v>
       </c>
       <c r="C190" t="s">
-        <v>1211</v>
+        <v>1172</v>
       </c>
       <c r="D190" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E190" t="s">
-        <v>1213</v>
+        <v>1174</v>
       </c>
       <c r="F190" t="s">
-        <v>1214</v>
+        <v>1175</v>
       </c>
       <c r="G190">
         <v>8</v>
       </c>
       <c r="H190" t="s">
-        <v>1215</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -15618,25 +16161,25 @@
         <v>162</v>
       </c>
       <c r="B191" t="s">
-        <v>1227</v>
+        <v>1171</v>
       </c>
       <c r="C191" t="s">
-        <v>1247</v>
+        <v>1178</v>
       </c>
       <c r="D191" t="s">
-        <v>1248</v>
+        <v>1179</v>
       </c>
       <c r="E191" t="s">
-        <v>66</v>
+        <v>1181</v>
       </c>
       <c r="F191" t="s">
-        <v>604</v>
+        <v>1175</v>
       </c>
       <c r="G191">
         <v>8</v>
       </c>
       <c r="H191" t="s">
-        <v>1250</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -15644,25 +16187,25 @@
         <v>163</v>
       </c>
       <c r="B192" t="s">
-        <v>1227</v>
+        <v>1171</v>
       </c>
       <c r="C192" t="s">
-        <v>1254</v>
+        <v>1184</v>
       </c>
       <c r="D192" t="s">
-        <v>1255</v>
+        <v>1185</v>
       </c>
       <c r="E192" t="s">
-        <v>25</v>
+        <v>1187</v>
       </c>
       <c r="F192" t="s">
-        <v>1257</v>
+        <v>1175</v>
       </c>
       <c r="G192">
         <v>8</v>
       </c>
       <c r="H192" t="s">
-        <v>1258</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -15670,25 +16213,25 @@
         <v>164</v>
       </c>
       <c r="B193" t="s">
-        <v>1227</v>
+        <v>1210</v>
       </c>
       <c r="C193" t="s">
-        <v>1260</v>
+        <v>1211</v>
       </c>
       <c r="D193" t="s">
-        <v>1261</v>
+        <v>89</v>
       </c>
       <c r="E193" t="s">
-        <v>75</v>
+        <v>1213</v>
       </c>
       <c r="F193" t="s">
-        <v>1257</v>
+        <v>1214</v>
       </c>
       <c r="G193">
         <v>8</v>
       </c>
       <c r="H193" t="s">
-        <v>1263</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -15696,25 +16239,25 @@
         <v>165</v>
       </c>
       <c r="B194" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="C194" t="s">
-        <v>950</v>
+        <v>1247</v>
       </c>
       <c r="D194" t="s">
-        <v>463</v>
+        <v>1248</v>
       </c>
       <c r="E194" t="s">
         <v>66</v>
       </c>
       <c r="F194" t="s">
-        <v>438</v>
+        <v>604</v>
       </c>
       <c r="G194">
         <v>8</v>
       </c>
       <c r="H194" t="s">
-        <v>1273</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -15722,25 +16265,25 @@
         <v>166</v>
       </c>
       <c r="B195" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="C195" t="s">
-        <v>219</v>
+        <v>1254</v>
       </c>
       <c r="D195" t="s">
-        <v>1285</v>
+        <v>1255</v>
       </c>
       <c r="E195" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>1287</v>
+        <v>1257</v>
       </c>
       <c r="G195">
         <v>8</v>
       </c>
       <c r="H195" t="s">
-        <v>1288</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -15748,25 +16291,25 @@
         <v>167</v>
       </c>
       <c r="B196" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="C196" t="s">
-        <v>1292</v>
+        <v>1260</v>
       </c>
       <c r="D196" t="s">
-        <v>1293</v>
+        <v>1261</v>
       </c>
       <c r="E196" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F196" t="s">
-        <v>1295</v>
+        <v>1257</v>
       </c>
       <c r="G196">
         <v>8</v>
       </c>
       <c r="H196" t="s">
-        <v>1296</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15774,25 +16317,25 @@
         <v>168</v>
       </c>
       <c r="B197" t="s">
-        <v>159</v>
+        <v>1271</v>
       </c>
       <c r="C197" t="s">
-        <v>271</v>
+        <v>950</v>
       </c>
       <c r="D197" t="s">
-        <v>272</v>
+        <v>463</v>
       </c>
       <c r="E197" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F197" t="s">
-        <v>274</v>
+        <v>438</v>
       </c>
       <c r="G197">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H197" t="s">
-        <v>275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -15800,25 +16343,25 @@
         <v>169</v>
       </c>
       <c r="B198" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="C198" t="s">
-        <v>681</v>
+        <v>219</v>
       </c>
       <c r="D198" t="s">
-        <v>682</v>
+        <v>1285</v>
       </c>
       <c r="E198" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="F198" t="s">
-        <v>684</v>
+        <v>1287</v>
       </c>
       <c r="G198">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H198" t="s">
-        <v>685</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -15826,25 +16369,25 @@
         <v>170</v>
       </c>
       <c r="B199" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="C199" t="s">
-        <v>689</v>
+        <v>1292</v>
       </c>
       <c r="D199" t="s">
-        <v>690</v>
+        <v>1293</v>
       </c>
       <c r="E199" t="s">
         <v>66</v>
       </c>
       <c r="F199" t="s">
-        <v>692</v>
+        <v>1295</v>
       </c>
       <c r="G199">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H199" t="s">
-        <v>693</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -15852,25 +16395,25 @@
         <v>171</v>
       </c>
       <c r="B200" t="s">
-        <v>697</v>
+        <v>1300</v>
       </c>
       <c r="C200" t="s">
-        <v>767</v>
+        <v>1301</v>
       </c>
       <c r="D200" t="s">
-        <v>768</v>
+        <v>1302</v>
       </c>
       <c r="E200" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>770</v>
+        <v>1304</v>
       </c>
       <c r="G200">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H200" t="s">
-        <v>771</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -15878,25 +16421,25 @@
         <v>172</v>
       </c>
       <c r="B201" t="s">
-        <v>845</v>
+        <v>1300</v>
       </c>
       <c r="C201" t="s">
-        <v>927</v>
+        <v>1309</v>
       </c>
       <c r="D201" t="s">
-        <v>585</v>
+        <v>830</v>
       </c>
       <c r="E201" t="s">
-        <v>25</v>
+        <v>1311</v>
       </c>
       <c r="F201" t="s">
-        <v>929</v>
+        <v>1318</v>
       </c>
       <c r="G201">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H201" t="s">
-        <v>930</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -15904,24 +16447,258 @@
         <v>173</v>
       </c>
       <c r="B202" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E202" t="s">
+        <v>147</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G202">
+        <v>8</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>174</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D203" t="s">
+        <v>122</v>
+      </c>
+      <c r="E203" t="s">
+        <v>16</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G203">
+        <v>8</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>175</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D204" t="s">
+        <v>110</v>
+      </c>
+      <c r="E204" t="s">
+        <v>16</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G204">
+        <v>8</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>176</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G205">
+        <v>8</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>177</v>
+      </c>
+      <c r="B206" t="s">
+        <v>159</v>
+      </c>
+      <c r="C206" t="s">
+        <v>271</v>
+      </c>
+      <c r="D206" t="s">
+        <v>272</v>
+      </c>
+      <c r="E206" t="s">
+        <v>75</v>
+      </c>
+      <c r="F206" t="s">
+        <v>274</v>
+      </c>
+      <c r="G206">
+        <v>7</v>
+      </c>
+      <c r="H206" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>178</v>
+      </c>
+      <c r="B207" t="s">
+        <v>591</v>
+      </c>
+      <c r="C207" t="s">
+        <v>681</v>
+      </c>
+      <c r="D207" t="s">
+        <v>682</v>
+      </c>
+      <c r="E207" t="s">
+        <v>25</v>
+      </c>
+      <c r="F207" t="s">
+        <v>684</v>
+      </c>
+      <c r="G207">
+        <v>7</v>
+      </c>
+      <c r="H207" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>179</v>
+      </c>
+      <c r="B208" t="s">
+        <v>591</v>
+      </c>
+      <c r="C208" t="s">
+        <v>689</v>
+      </c>
+      <c r="D208" t="s">
+        <v>690</v>
+      </c>
+      <c r="E208" t="s">
+        <v>66</v>
+      </c>
+      <c r="F208" t="s">
+        <v>692</v>
+      </c>
+      <c r="G208">
+        <v>7</v>
+      </c>
+      <c r="H208" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>180</v>
+      </c>
+      <c r="B209" t="s">
+        <v>697</v>
+      </c>
+      <c r="C209" t="s">
+        <v>767</v>
+      </c>
+      <c r="D209" t="s">
+        <v>768</v>
+      </c>
+      <c r="E209" t="s">
+        <v>25</v>
+      </c>
+      <c r="F209" t="s">
+        <v>770</v>
+      </c>
+      <c r="G209">
+        <v>7</v>
+      </c>
+      <c r="H209" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>181</v>
+      </c>
+      <c r="B210" t="s">
+        <v>845</v>
+      </c>
+      <c r="C210" t="s">
+        <v>927</v>
+      </c>
+      <c r="D210" t="s">
+        <v>585</v>
+      </c>
+      <c r="E210" t="s">
+        <v>25</v>
+      </c>
+      <c r="F210" t="s">
+        <v>929</v>
+      </c>
+      <c r="G210">
+        <v>7</v>
+      </c>
+      <c r="H210" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>182</v>
+      </c>
+      <c r="B211" t="s">
         <v>1219</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C211" t="s">
         <v>1220</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D211" t="s">
         <v>1221</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E211" t="s">
         <v>1223</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F211" t="s">
         <v>1224</v>
       </c>
-      <c r="G202">
+      <c r="G211">
         <v>7</v>
       </c>
-      <c r="H202" t="s">
+      <c r="H211" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -15938,7 +16715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -15955,10 +16732,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1308</v>
+        <v>1376</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1309</v>
+        <v>1377</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -15985,12 +16762,12 @@
         <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1310</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -16025,7 +16802,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B3">
         <v>97</v>
@@ -16060,7 +16837,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B4">
         <v>97</v>
@@ -16095,7 +16872,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B5">
         <v>95</v>
@@ -16130,7 +16907,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B6">
         <v>95</v>
@@ -16165,7 +16942,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -16200,7 +16977,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B8">
         <v>93</v>
@@ -16235,7 +17012,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B9">
         <v>93</v>
@@ -16270,7 +17047,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B10">
         <v>93</v>
@@ -16305,7 +17082,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B11">
         <v>92</v>
@@ -16340,7 +17117,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B12">
         <v>92</v>
@@ -16375,7 +17152,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B13">
         <v>92</v>
@@ -16410,7 +17187,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B14">
         <v>91</v>
@@ -16445,7 +17222,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B15">
         <v>91</v>
@@ -16480,7 +17257,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B16">
         <v>91</v>
@@ -16515,7 +17292,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B17">
         <v>91</v>
@@ -16550,7 +17327,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B18">
         <v>91</v>
@@ -16585,7 +17362,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B19">
         <v>91</v>
@@ -16620,7 +17397,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B20">
         <v>91</v>
@@ -16655,7 +17432,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -16690,7 +17467,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B22">
         <v>90</v>
@@ -16725,7 +17502,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -16760,7 +17537,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -16795,7 +17572,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -16830,7 +17607,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B26">
         <v>90</v>
@@ -16865,7 +17642,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B27">
         <v>89</v>
@@ -16900,7 +17677,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B28">
         <v>89</v>
@@ -16935,7 +17712,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B29">
         <v>89</v>
@@ -16970,7 +17747,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -17005,7 +17782,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B31">
         <v>89</v>
@@ -17040,7 +17817,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B32">
         <v>89</v>
@@ -17075,7 +17852,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B33">
         <v>89</v>
@@ -17110,7 +17887,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B34">
         <v>89</v>
@@ -17145,7 +17922,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B35">
         <v>89</v>
@@ -17180,7 +17957,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B36">
         <v>89</v>
@@ -17215,7 +17992,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B37">
         <v>88</v>
@@ -17250,7 +18027,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B38">
         <v>88</v>
@@ -17285,7 +18062,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B39">
         <v>88</v>
@@ -17320,7 +18097,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B40">
         <v>88</v>
@@ -17355,7 +18132,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B41">
         <v>88</v>
@@ -17390,7 +18167,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B42">
         <v>88</v>
@@ -17425,7 +18202,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B43">
         <v>88</v>
@@ -17460,7 +18237,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B44">
         <v>88</v>
@@ -17495,7 +18272,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B45">
         <v>88</v>
@@ -17530,7 +18307,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B46">
         <v>87</v>
@@ -17565,7 +18342,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B47">
         <v>87</v>
@@ -17600,7 +18377,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B48">
         <v>87</v>
@@ -17635,7 +18412,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B49">
         <v>87</v>
@@ -17670,7 +18447,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B50">
         <v>87</v>
@@ -17705,7 +18482,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B51">
         <v>87</v>
@@ -17740,7 +18517,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B52">
         <v>87</v>
@@ -17775,7 +18552,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B53">
         <v>87</v>
@@ -17810,7 +18587,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B54">
         <v>87</v>
@@ -17845,7 +18622,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B55">
         <v>87</v>
@@ -17880,7 +18657,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B56">
         <v>87</v>
@@ -17915,7 +18692,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B57">
         <v>86</v>
@@ -17950,7 +18727,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B58">
         <v>86</v>
@@ -17985,7 +18762,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B59">
         <v>86</v>
@@ -18020,7 +18797,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B60">
         <v>86</v>
@@ -18055,7 +18832,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B61">
         <v>86</v>
@@ -18090,7 +18867,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B62">
         <v>86</v>
@@ -18125,7 +18902,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B63">
         <v>86</v>
@@ -18160,7 +18937,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B64">
         <v>86</v>
@@ -18195,7 +18972,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B65">
         <v>86</v>
@@ -18230,7 +19007,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B66">
         <v>86</v>
@@ -18265,7 +19042,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B67">
         <v>86</v>
@@ -18300,7 +19077,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B68">
         <v>86</v>
@@ -18335,7 +19112,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B69">
         <v>86</v>
@@ -18370,7 +19147,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B70">
         <v>86</v>
@@ -18405,7 +19182,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B71">
         <v>86</v>
@@ -18440,7 +19217,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B72">
         <v>86</v>
@@ -18475,7 +19252,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B73">
         <v>86</v>
@@ -18510,252 +19287,252 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B74">
+        <v>86</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E74" t="s">
+        <v>610</v>
+      </c>
+      <c r="F74" t="s">
         <v>1311</v>
       </c>
-      <c r="B74">
-        <v>85</v>
-      </c>
-      <c r="C74" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" t="s">
-        <v>55</v>
-      </c>
-      <c r="E74" t="s">
-        <v>56</v>
-      </c>
-      <c r="F74" t="s">
-        <v>16</v>
-      </c>
       <c r="G74" t="s">
-        <v>58</v>
+        <v>1312</v>
       </c>
       <c r="H74" t="s">
-        <v>60</v>
+        <v>1314</v>
       </c>
       <c r="I74" t="s">
-        <v>61</v>
+        <v>1315</v>
       </c>
       <c r="J74" t="s">
-        <v>62</v>
+        <v>1316</v>
       </c>
       <c r="K74" t="s">
-        <v>57</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B75">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>12</v>
+        <v>1300</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>1323</v>
       </c>
       <c r="E75" t="s">
         <v>89</v>
       </c>
       <c r="F75" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="G75" t="s">
-        <v>131</v>
+        <v>1325</v>
       </c>
       <c r="H75" t="s">
-        <v>133</v>
+        <v>1327</v>
       </c>
       <c r="I75" t="s">
-        <v>134</v>
+        <v>1328</v>
       </c>
       <c r="J75" t="s">
-        <v>135</v>
+        <v>1329</v>
       </c>
       <c r="K75" t="s">
-        <v>129</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B76">
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>284</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="F76" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="H76" t="s">
-        <v>312</v>
+        <v>60</v>
       </c>
       <c r="I76" t="s">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="J76" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
       <c r="K76" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B77">
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E77" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G77" t="s">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="H77" t="s">
-        <v>407</v>
+        <v>133</v>
       </c>
       <c r="I77" t="s">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="J77" t="s">
-        <v>409</v>
+        <v>135</v>
       </c>
       <c r="K77" t="s">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B78">
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="D78" t="s">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="E78" t="s">
-        <v>475</v>
+        <v>308</v>
       </c>
       <c r="F78" t="s">
-        <v>477</v>
+        <v>147</v>
       </c>
       <c r="G78" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="H78" t="s">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="I78" t="s">
-        <v>481</v>
+        <v>313</v>
       </c>
       <c r="J78" t="s">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="K78" t="s">
-        <v>476</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B79">
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>773</v>
+        <v>402</v>
       </c>
       <c r="D79" t="s">
-        <v>774</v>
+        <v>55</v>
       </c>
       <c r="E79" t="s">
-        <v>783</v>
+        <v>403</v>
       </c>
       <c r="F79" t="s">
-        <v>785</v>
+        <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>786</v>
+        <v>405</v>
       </c>
       <c r="H79" t="s">
-        <v>788</v>
+        <v>407</v>
       </c>
       <c r="I79" t="s">
-        <v>789</v>
+        <v>408</v>
       </c>
       <c r="J79" t="s">
-        <v>790</v>
+        <v>409</v>
       </c>
       <c r="K79" t="s">
-        <v>784</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B80">
         <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D80" t="s">
-        <v>799</v>
+        <v>474</v>
       </c>
       <c r="E80" t="s">
-        <v>800</v>
+        <v>475</v>
       </c>
       <c r="F80" t="s">
-        <v>793</v>
+        <v>477</v>
       </c>
       <c r="G80" t="s">
-        <v>802</v>
+        <v>478</v>
       </c>
       <c r="H80" t="s">
-        <v>804</v>
+        <v>480</v>
       </c>
       <c r="I80" t="s">
-        <v>805</v>
+        <v>481</v>
       </c>
       <c r="J80" t="s">
-        <v>806</v>
+        <v>482</v>
       </c>
       <c r="K80" t="s">
-        <v>801</v>
+        <v>476</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B81">
         <v>85</v>
@@ -18764,558 +19541,558 @@
         <v>773</v>
       </c>
       <c r="D81" t="s">
-        <v>821</v>
+        <v>774</v>
       </c>
       <c r="E81" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="F81" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="G81" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="H81" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="I81" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="J81" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="K81" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B82">
         <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D82" t="s">
-        <v>989</v>
+        <v>799</v>
       </c>
       <c r="E82" t="s">
-        <v>990</v>
+        <v>800</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>793</v>
       </c>
       <c r="G82" t="s">
-        <v>959</v>
+        <v>802</v>
       </c>
       <c r="H82" t="s">
-        <v>993</v>
+        <v>804</v>
       </c>
       <c r="I82" t="s">
-        <v>994</v>
+        <v>805</v>
       </c>
       <c r="J82" t="s">
-        <v>995</v>
+        <v>806</v>
       </c>
       <c r="K82" t="s">
-        <v>991</v>
+        <v>801</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B83">
         <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D83" t="s">
-        <v>1065</v>
+        <v>821</v>
       </c>
       <c r="E83" t="s">
-        <v>1066</v>
+        <v>822</v>
       </c>
       <c r="F83" t="s">
-        <v>147</v>
+        <v>777</v>
       </c>
       <c r="G83" t="s">
-        <v>1068</v>
+        <v>824</v>
       </c>
       <c r="H83" t="s">
-        <v>1070</v>
+        <v>826</v>
       </c>
       <c r="I83" t="s">
-        <v>1071</v>
+        <v>827</v>
       </c>
       <c r="J83" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="K83" t="s">
-        <v>1067</v>
+        <v>823</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B84">
         <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>1227</v>
+        <v>934</v>
       </c>
       <c r="D84" t="s">
-        <v>1242</v>
+        <v>989</v>
       </c>
       <c r="E84" t="s">
-        <v>610</v>
+        <v>990</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G84" t="s">
-        <v>604</v>
+        <v>959</v>
       </c>
       <c r="H84" t="s">
-        <v>312</v>
+        <v>993</v>
       </c>
       <c r="I84" t="s">
-        <v>1245</v>
+        <v>994</v>
       </c>
       <c r="J84" t="s">
-        <v>1246</v>
+        <v>995</v>
       </c>
       <c r="K84" t="s">
-        <v>1243</v>
+        <v>991</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B85">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>934</v>
       </c>
       <c r="D85" t="s">
-        <v>144</v>
+        <v>1065</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>1066</v>
       </c>
       <c r="F85" t="s">
         <v>147</v>
       </c>
       <c r="G85" t="s">
-        <v>148</v>
+        <v>1068</v>
       </c>
       <c r="H85" t="s">
-        <v>150</v>
+        <v>1070</v>
       </c>
       <c r="I85" t="s">
-        <v>151</v>
+        <v>1071</v>
       </c>
       <c r="J85" t="s">
-        <v>152</v>
+        <v>1072</v>
       </c>
       <c r="K85" t="s">
-        <v>146</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B86">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>284</v>
+        <v>1227</v>
       </c>
       <c r="D86" t="s">
-        <v>144</v>
+        <v>1242</v>
       </c>
       <c r="E86" t="s">
-        <v>394</v>
+        <v>610</v>
       </c>
       <c r="F86" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>397</v>
+        <v>604</v>
       </c>
       <c r="H86" t="s">
-        <v>399</v>
+        <v>312</v>
       </c>
       <c r="I86" t="s">
-        <v>400</v>
+        <v>1245</v>
       </c>
       <c r="J86" t="s">
-        <v>401</v>
+        <v>1246</v>
       </c>
       <c r="K86" t="s">
-        <v>395</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B87">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>402</v>
+        <v>1300</v>
       </c>
       <c r="D87" t="s">
-        <v>410</v>
+        <v>1345</v>
       </c>
       <c r="E87" t="s">
-        <v>411</v>
+        <v>1346</v>
       </c>
       <c r="F87" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>413</v>
+        <v>1348</v>
       </c>
       <c r="H87" t="s">
-        <v>415</v>
+        <v>312</v>
       </c>
       <c r="I87" t="s">
-        <v>416</v>
+        <v>1350</v>
       </c>
       <c r="J87" t="s">
-        <v>417</v>
+        <v>1351</v>
       </c>
       <c r="K87" t="s">
-        <v>412</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B88">
         <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>473</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>483</v>
+        <v>144</v>
       </c>
       <c r="E88" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F88" t="s">
-        <v>485</v>
+        <v>147</v>
       </c>
       <c r="G88" t="s">
-        <v>486</v>
+        <v>148</v>
       </c>
       <c r="H88" t="s">
-        <v>488</v>
+        <v>150</v>
       </c>
       <c r="I88" t="s">
-        <v>489</v>
+        <v>151</v>
       </c>
       <c r="J88" t="s">
-        <v>490</v>
+        <v>152</v>
       </c>
       <c r="K88" t="s">
-        <v>484</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B89">
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>697</v>
+        <v>284</v>
       </c>
       <c r="D89" t="s">
-        <v>714</v>
+        <v>144</v>
       </c>
       <c r="E89" t="s">
-        <v>715</v>
+        <v>394</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="G89" t="s">
-        <v>604</v>
+        <v>397</v>
       </c>
       <c r="H89" t="s">
-        <v>718</v>
+        <v>399</v>
       </c>
       <c r="I89" t="s">
-        <v>719</v>
+        <v>400</v>
       </c>
       <c r="J89" t="s">
-        <v>720</v>
+        <v>401</v>
       </c>
       <c r="K89" t="s">
-        <v>716</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B90">
         <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="D90" t="s">
-        <v>721</v>
+        <v>410</v>
       </c>
       <c r="E90" t="s">
-        <v>722</v>
+        <v>411</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G90" t="s">
-        <v>724</v>
+        <v>413</v>
       </c>
       <c r="H90" t="s">
-        <v>726</v>
+        <v>415</v>
       </c>
       <c r="I90" t="s">
-        <v>727</v>
+        <v>416</v>
       </c>
       <c r="J90" t="s">
-        <v>728</v>
+        <v>417</v>
       </c>
       <c r="K90" t="s">
-        <v>723</v>
+        <v>412</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B91">
         <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>697</v>
+        <v>473</v>
       </c>
       <c r="D91" t="s">
-        <v>729</v>
+        <v>483</v>
       </c>
       <c r="E91" t="s">
-        <v>730</v>
+        <v>122</v>
       </c>
       <c r="F91" t="s">
-        <v>535</v>
+        <v>485</v>
       </c>
       <c r="G91" t="s">
-        <v>732</v>
+        <v>486</v>
       </c>
       <c r="H91" t="s">
-        <v>726</v>
+        <v>488</v>
       </c>
       <c r="I91" t="s">
-        <v>734</v>
+        <v>489</v>
       </c>
       <c r="J91" t="s">
-        <v>735</v>
+        <v>490</v>
       </c>
       <c r="K91" t="s">
-        <v>731</v>
+        <v>484</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B92">
         <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>773</v>
+        <v>697</v>
       </c>
       <c r="D92" t="s">
-        <v>791</v>
+        <v>714</v>
       </c>
       <c r="E92" t="s">
-        <v>610</v>
+        <v>715</v>
       </c>
       <c r="F92" t="s">
-        <v>793</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>794</v>
+        <v>604</v>
       </c>
       <c r="H92" t="s">
-        <v>796</v>
+        <v>718</v>
       </c>
       <c r="I92" t="s">
-        <v>797</v>
+        <v>719</v>
       </c>
       <c r="J92" t="s">
-        <v>798</v>
+        <v>720</v>
       </c>
       <c r="K92" t="s">
-        <v>792</v>
+        <v>716</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B93">
         <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>845</v>
+        <v>697</v>
       </c>
       <c r="D93" t="s">
-        <v>896</v>
+        <v>721</v>
       </c>
       <c r="E93" t="s">
-        <v>897</v>
+        <v>722</v>
       </c>
       <c r="F93" t="s">
         <v>25</v>
       </c>
       <c r="G93" t="s">
-        <v>899</v>
+        <v>724</v>
       </c>
       <c r="H93" t="s">
-        <v>901</v>
+        <v>726</v>
       </c>
       <c r="I93" t="s">
-        <v>902</v>
+        <v>727</v>
       </c>
       <c r="J93" t="s">
-        <v>903</v>
+        <v>728</v>
       </c>
       <c r="K93" t="s">
-        <v>898</v>
+        <v>723</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B94">
         <v>84</v>
       </c>
       <c r="C94" t="s">
-        <v>934</v>
+        <v>697</v>
       </c>
       <c r="D94" t="s">
-        <v>964</v>
+        <v>729</v>
       </c>
       <c r="E94" t="s">
-        <v>965</v>
+        <v>730</v>
       </c>
       <c r="F94" t="s">
-        <v>967</v>
+        <v>535</v>
       </c>
       <c r="G94" t="s">
-        <v>968</v>
+        <v>732</v>
       </c>
       <c r="H94" t="s">
-        <v>970</v>
+        <v>726</v>
       </c>
       <c r="I94" t="s">
-        <v>971</v>
+        <v>734</v>
       </c>
       <c r="J94" t="s">
-        <v>972</v>
+        <v>735</v>
       </c>
       <c r="K94" t="s">
-        <v>966</v>
+        <v>731</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B95">
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="D95" t="s">
-        <v>950</v>
+        <v>791</v>
       </c>
       <c r="E95" t="s">
-        <v>1002</v>
+        <v>610</v>
       </c>
       <c r="F95" t="s">
-        <v>1004</v>
+        <v>793</v>
       </c>
       <c r="G95" t="s">
-        <v>438</v>
+        <v>794</v>
       </c>
       <c r="H95" t="s">
-        <v>1006</v>
+        <v>796</v>
       </c>
       <c r="I95" t="s">
-        <v>1007</v>
+        <v>797</v>
       </c>
       <c r="J95" t="s">
-        <v>1008</v>
+        <v>798</v>
       </c>
       <c r="K95" t="s">
-        <v>1003</v>
+        <v>792</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B96">
         <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>934</v>
+        <v>845</v>
       </c>
       <c r="D96" t="s">
-        <v>213</v>
+        <v>896</v>
       </c>
       <c r="E96" t="s">
-        <v>1032</v>
+        <v>897</v>
       </c>
       <c r="F96" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="G96" t="s">
-        <v>1034</v>
+        <v>899</v>
       </c>
       <c r="H96" t="s">
-        <v>1036</v>
+        <v>901</v>
       </c>
       <c r="I96" t="s">
-        <v>1037</v>
+        <v>902</v>
       </c>
       <c r="J96" t="s">
-        <v>1038</v>
+        <v>903</v>
       </c>
       <c r="K96" t="s">
-        <v>1033</v>
+        <v>898</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B97">
         <v>84</v>
@@ -19324,1042 +20101,1252 @@
         <v>934</v>
       </c>
       <c r="D97" t="s">
-        <v>1057</v>
+        <v>964</v>
       </c>
       <c r="E97" t="s">
-        <v>1058</v>
+        <v>965</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
+        <v>967</v>
       </c>
       <c r="G97" t="s">
-        <v>1060</v>
+        <v>968</v>
       </c>
       <c r="H97" t="s">
-        <v>1062</v>
+        <v>970</v>
       </c>
       <c r="I97" t="s">
-        <v>1063</v>
+        <v>971</v>
       </c>
       <c r="J97" t="s">
-        <v>1064</v>
+        <v>972</v>
       </c>
       <c r="K97" t="s">
-        <v>1059</v>
+        <v>966</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B98">
         <v>84</v>
       </c>
       <c r="C98" t="s">
-        <v>1087</v>
+        <v>934</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>950</v>
       </c>
       <c r="E98" t="s">
-        <v>1104</v>
+        <v>1002</v>
       </c>
       <c r="F98" t="s">
-        <v>1106</v>
+        <v>1004</v>
       </c>
       <c r="G98" t="s">
-        <v>1107</v>
+        <v>438</v>
       </c>
       <c r="H98" t="s">
-        <v>1109</v>
+        <v>1006</v>
       </c>
       <c r="I98" t="s">
-        <v>1110</v>
+        <v>1007</v>
       </c>
       <c r="J98" t="s">
-        <v>1111</v>
+        <v>1008</v>
       </c>
       <c r="K98" t="s">
-        <v>1105</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B99">
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>1271</v>
+        <v>934</v>
       </c>
       <c r="D99" t="s">
-        <v>950</v>
+        <v>213</v>
       </c>
       <c r="E99" t="s">
-        <v>463</v>
+        <v>1032</v>
       </c>
       <c r="F99" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="G99" t="s">
-        <v>438</v>
+        <v>1034</v>
       </c>
       <c r="H99" t="s">
-        <v>1274</v>
+        <v>1036</v>
       </c>
       <c r="I99" t="s">
-        <v>1275</v>
+        <v>1037</v>
       </c>
       <c r="J99" t="s">
-        <v>1276</v>
+        <v>1038</v>
       </c>
       <c r="K99" t="s">
-        <v>1272</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B100">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>1200</v>
+        <v>934</v>
       </c>
       <c r="D100" t="s">
-        <v>1201</v>
+        <v>1057</v>
       </c>
       <c r="E100" t="s">
-        <v>1202</v>
+        <v>1058</v>
       </c>
       <c r="F100" t="s">
-        <v>1204</v>
+        <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>1205</v>
+        <v>1060</v>
       </c>
       <c r="H100" t="s">
-        <v>1207</v>
+        <v>1062</v>
       </c>
       <c r="I100" t="s">
-        <v>1208</v>
+        <v>1063</v>
       </c>
       <c r="J100" t="s">
-        <v>1209</v>
+        <v>1064</v>
       </c>
       <c r="K100" t="s">
-        <v>1203</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B101">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C101" t="s">
-        <v>284</v>
+        <v>1087</v>
       </c>
       <c r="D101" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
       <c r="E101" t="s">
-        <v>362</v>
+        <v>1104</v>
       </c>
       <c r="F101" t="s">
-        <v>356</v>
+        <v>1106</v>
       </c>
       <c r="G101" t="s">
-        <v>364</v>
+        <v>1107</v>
       </c>
       <c r="H101" t="s">
-        <v>366</v>
+        <v>1109</v>
       </c>
       <c r="I101" t="s">
-        <v>367</v>
+        <v>1110</v>
       </c>
       <c r="J101" t="s">
-        <v>368</v>
+        <v>1111</v>
       </c>
       <c r="K101" t="s">
-        <v>363</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B102">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>473</v>
+        <v>1271</v>
       </c>
       <c r="D102" t="s">
-        <v>491</v>
+        <v>950</v>
       </c>
       <c r="E102" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="F102" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G102" t="s">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="H102" t="s">
-        <v>496</v>
+        <v>1274</v>
       </c>
       <c r="I102" t="s">
-        <v>497</v>
+        <v>1275</v>
       </c>
       <c r="J102" t="s">
-        <v>498</v>
+        <v>1276</v>
       </c>
       <c r="K102" t="s">
-        <v>493</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B103">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>473</v>
+        <v>1300</v>
       </c>
       <c r="D103" t="s">
-        <v>532</v>
+        <v>1338</v>
       </c>
       <c r="E103" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="F103" t="s">
-        <v>535</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>536</v>
+        <v>1340</v>
       </c>
       <c r="H103" t="s">
-        <v>538</v>
+        <v>1342</v>
       </c>
       <c r="I103" t="s">
-        <v>539</v>
+        <v>1343</v>
       </c>
       <c r="J103" t="s">
-        <v>540</v>
+        <v>1344</v>
       </c>
       <c r="K103" t="s">
-        <v>534</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B104">
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>591</v>
+        <v>1200</v>
       </c>
       <c r="D104" t="s">
-        <v>643</v>
+        <v>1201</v>
       </c>
       <c r="E104" t="s">
-        <v>644</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="s">
-        <v>16</v>
+        <v>1204</v>
       </c>
       <c r="G104" t="s">
-        <v>618</v>
+        <v>1205</v>
       </c>
       <c r="H104" t="s">
-        <v>647</v>
+        <v>1207</v>
       </c>
       <c r="I104" t="s">
-        <v>648</v>
+        <v>1208</v>
       </c>
       <c r="J104" t="s">
-        <v>649</v>
+        <v>1209</v>
       </c>
       <c r="K104" t="s">
-        <v>645</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B105">
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>697</v>
+        <v>284</v>
       </c>
       <c r="D105" t="s">
-        <v>736</v>
+        <v>353</v>
       </c>
       <c r="E105" t="s">
-        <v>737</v>
+        <v>362</v>
       </c>
       <c r="F105" t="s">
-        <v>739</v>
+        <v>356</v>
       </c>
       <c r="G105" t="s">
-        <v>604</v>
+        <v>364</v>
       </c>
       <c r="H105" t="s">
-        <v>741</v>
+        <v>366</v>
       </c>
       <c r="I105" t="s">
-        <v>742</v>
+        <v>367</v>
       </c>
       <c r="J105" t="s">
-        <v>743</v>
+        <v>368</v>
       </c>
       <c r="K105" t="s">
-        <v>738</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B106">
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>773</v>
+        <v>473</v>
       </c>
       <c r="D106" t="s">
-        <v>807</v>
+        <v>491</v>
       </c>
       <c r="E106" t="s">
-        <v>808</v>
+        <v>492</v>
       </c>
       <c r="F106" t="s">
-        <v>810</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>811</v>
+        <v>494</v>
       </c>
       <c r="H106" t="s">
-        <v>813</v>
+        <v>496</v>
       </c>
       <c r="I106" t="s">
-        <v>814</v>
+        <v>497</v>
       </c>
       <c r="J106" t="s">
-        <v>815</v>
+        <v>498</v>
       </c>
       <c r="K106" t="s">
-        <v>809</v>
+        <v>493</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B107">
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>934</v>
+        <v>473</v>
       </c>
       <c r="D107" t="s">
-        <v>650</v>
+        <v>532</v>
       </c>
       <c r="E107" t="s">
-        <v>1016</v>
+        <v>533</v>
       </c>
       <c r="F107" t="s">
-        <v>66</v>
+        <v>535</v>
       </c>
       <c r="G107" t="s">
-        <v>1018</v>
+        <v>536</v>
       </c>
       <c r="H107" t="s">
-        <v>1020</v>
+        <v>538</v>
       </c>
       <c r="I107" t="s">
-        <v>1021</v>
+        <v>539</v>
       </c>
       <c r="J107" t="s">
-        <v>1022</v>
+        <v>540</v>
       </c>
       <c r="K107" t="s">
-        <v>1017</v>
+        <v>534</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B108">
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>934</v>
+        <v>591</v>
       </c>
       <c r="D108" t="s">
-        <v>1048</v>
+        <v>643</v>
       </c>
       <c r="E108" t="s">
-        <v>1049</v>
+        <v>644</v>
       </c>
       <c r="F108" t="s">
-        <v>1051</v>
+        <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>1052</v>
+        <v>618</v>
       </c>
       <c r="H108" t="s">
-        <v>1054</v>
+        <v>647</v>
       </c>
       <c r="I108" t="s">
-        <v>1055</v>
+        <v>648</v>
       </c>
       <c r="J108" t="s">
-        <v>1056</v>
+        <v>649</v>
       </c>
       <c r="K108" t="s">
-        <v>1050</v>
+        <v>645</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B109">
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>1227</v>
+        <v>697</v>
       </c>
       <c r="D109" t="s">
-        <v>1247</v>
+        <v>736</v>
       </c>
       <c r="E109" t="s">
-        <v>1248</v>
+        <v>737</v>
       </c>
       <c r="F109" t="s">
-        <v>66</v>
+        <v>739</v>
       </c>
       <c r="G109" t="s">
         <v>604</v>
       </c>
       <c r="H109" t="s">
-        <v>1251</v>
+        <v>741</v>
       </c>
       <c r="I109" t="s">
-        <v>1252</v>
+        <v>742</v>
       </c>
       <c r="J109" t="s">
-        <v>1253</v>
+        <v>743</v>
       </c>
       <c r="K109" t="s">
-        <v>1249</v>
+        <v>738</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B110">
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>1271</v>
+        <v>773</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>807</v>
       </c>
       <c r="E110" t="s">
-        <v>1285</v>
+        <v>808</v>
       </c>
       <c r="F110" t="s">
-        <v>98</v>
+        <v>810</v>
       </c>
       <c r="G110" t="s">
-        <v>1287</v>
+        <v>811</v>
       </c>
       <c r="H110" t="s">
-        <v>1289</v>
+        <v>813</v>
       </c>
       <c r="I110" t="s">
-        <v>1290</v>
+        <v>814</v>
       </c>
       <c r="J110" t="s">
-        <v>1291</v>
+        <v>815</v>
       </c>
       <c r="K110" t="s">
-        <v>1286</v>
+        <v>809</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B111">
         <v>83</v>
       </c>
       <c r="C111" t="s">
-        <v>1271</v>
+        <v>934</v>
       </c>
       <c r="D111" t="s">
-        <v>1292</v>
+        <v>650</v>
       </c>
       <c r="E111" t="s">
-        <v>1293</v>
+        <v>1016</v>
       </c>
       <c r="F111" t="s">
         <v>66</v>
       </c>
       <c r="G111" t="s">
-        <v>1295</v>
+        <v>1018</v>
       </c>
       <c r="H111" t="s">
-        <v>1297</v>
+        <v>1020</v>
       </c>
       <c r="I111" t="s">
-        <v>1298</v>
+        <v>1021</v>
       </c>
       <c r="J111" t="s">
-        <v>1299</v>
+        <v>1022</v>
       </c>
       <c r="K111" t="s">
-        <v>1294</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B112">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C112" t="s">
-        <v>159</v>
+        <v>934</v>
       </c>
       <c r="D112" t="s">
-        <v>227</v>
+        <v>1048</v>
       </c>
       <c r="E112" t="s">
-        <v>228</v>
+        <v>1049</v>
       </c>
       <c r="F112" t="s">
-        <v>230</v>
+        <v>1051</v>
       </c>
       <c r="G112" t="s">
-        <v>231</v>
+        <v>1052</v>
       </c>
       <c r="H112" t="s">
-        <v>233</v>
+        <v>1054</v>
       </c>
       <c r="I112" t="s">
-        <v>234</v>
+        <v>1055</v>
       </c>
       <c r="J112" t="s">
-        <v>235</v>
+        <v>1056</v>
       </c>
       <c r="K112" t="s">
-        <v>229</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B113">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C113" t="s">
-        <v>159</v>
+        <v>1227</v>
       </c>
       <c r="D113" t="s">
-        <v>266</v>
+        <v>1247</v>
       </c>
       <c r="E113" t="s">
-        <v>267</v>
+        <v>1248</v>
       </c>
       <c r="F113" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G113" t="s">
-        <v>58</v>
+        <v>604</v>
       </c>
       <c r="H113" t="s">
-        <v>270</v>
+        <v>1251</v>
       </c>
       <c r="I113" t="s">
-        <v>79</v>
+        <v>1252</v>
       </c>
       <c r="J113" t="s">
-        <v>79</v>
+        <v>1253</v>
       </c>
       <c r="K113" t="s">
-        <v>268</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B114">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C114" t="s">
-        <v>284</v>
+        <v>1271</v>
       </c>
       <c r="D114" t="s">
-        <v>338</v>
+        <v>219</v>
       </c>
       <c r="E114" t="s">
-        <v>339</v>
+        <v>1285</v>
       </c>
       <c r="F114" t="s">
-        <v>341</v>
+        <v>98</v>
       </c>
       <c r="G114" t="s">
-        <v>342</v>
+        <v>1287</v>
       </c>
       <c r="H114" t="s">
-        <v>344</v>
+        <v>1289</v>
       </c>
       <c r="I114" t="s">
-        <v>345</v>
+        <v>1290</v>
       </c>
       <c r="J114" t="s">
-        <v>346</v>
+        <v>1291</v>
       </c>
       <c r="K114" t="s">
-        <v>340</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B115">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C115" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="D115" t="s">
-        <v>601</v>
+        <v>1292</v>
       </c>
       <c r="E115" t="s">
-        <v>602</v>
+        <v>1293</v>
       </c>
       <c r="F115" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G115" t="s">
-        <v>604</v>
+        <v>1295</v>
       </c>
       <c r="H115" t="s">
-        <v>606</v>
+        <v>1297</v>
       </c>
       <c r="I115" t="s">
-        <v>607</v>
+        <v>1298</v>
       </c>
       <c r="J115" t="s">
-        <v>608</v>
+        <v>1299</v>
       </c>
       <c r="K115" t="s">
-        <v>603</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B116">
+        <v>83</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E116" t="s">
+        <v>830</v>
+      </c>
+      <c r="F116" t="s">
         <v>1311</v>
       </c>
-      <c r="B116">
-        <v>82</v>
-      </c>
-      <c r="C116" t="s">
-        <v>934</v>
-      </c>
-      <c r="D116" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F116" t="s">
-        <v>16</v>
-      </c>
       <c r="G116" t="s">
-        <v>1011</v>
+        <v>1318</v>
       </c>
       <c r="H116" t="s">
-        <v>1013</v>
+        <v>1320</v>
       </c>
       <c r="I116" t="s">
-        <v>1014</v>
+        <v>1321</v>
       </c>
       <c r="J116" t="s">
-        <v>1015</v>
+        <v>1322</v>
       </c>
       <c r="K116" t="s">
-        <v>1010</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="B117">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C117" t="s">
-        <v>934</v>
+        <v>1300</v>
       </c>
       <c r="D117" t="s">
-        <v>1023</v>
+        <v>1352</v>
       </c>
       <c r="E117" t="s">
-        <v>1024</v>
+        <v>110</v>
       </c>
       <c r="F117" t="s">
-        <v>1026</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>1027</v>
+        <v>1354</v>
       </c>
       <c r="H117" t="s">
-        <v>1029</v>
+        <v>1356</v>
       </c>
       <c r="I117" t="s">
-        <v>1030</v>
+        <v>1357</v>
       </c>
       <c r="J117" t="s">
-        <v>1031</v>
+        <v>1358</v>
       </c>
       <c r="K117" t="s">
-        <v>1025</v>
+        <v>1353</v>
       </c>
